--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>168</v>
+        <v>27</v>
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AD3" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AD5" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>2</v>
+        <v>157</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AD7" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AD9" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -2037,16 +2037,16 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>428</v>
+        <v>1</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD10" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>166</v>
+        <v>428</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="AD11" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>35</v>
+        <v>166</v>
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AD13" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AD15" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="AB17" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AD17" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -2669,16 +2669,16 @@
         </is>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>478</v>
+        <v>4</v>
       </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -2748,16 +2748,16 @@
         </is>
       </c>
       <c r="AB19" s="7" t="n">
-        <v>183</v>
+        <v>6</v>
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD19" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>51</v>
+        <v>478</v>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AD21" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="AD23" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AD24" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AD25" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AD26" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -3220,16 +3220,16 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>515</v>
+        <v>3</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD27" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD28" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -3338,16 +3338,16 @@
         </is>
       </c>
       <c r="AB29" s="7" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD29" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>42</v>
+        <v>515</v>
       </c>
       <c r="AC30" s="4" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="AD30" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AD31" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AD32" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="AB33" s="7" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="AC33" s="7" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AD33" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -3638,16 +3638,16 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>453</v>
+        <v>42</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD34" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -3679,16 +3679,16 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD35" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -3720,16 +3720,16 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD36" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -3761,16 +3761,16 @@
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD37" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>147</v>
+        <v>453</v>
       </c>
       <c r="AC38" s="4" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="AD38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="AB39" s="7" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AC39" s="7" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="AD39" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>5</v>
+        <v>136</v>
       </c>
       <c r="AC40" s="4" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AD40" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="AB41" s="7" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="AC41" s="7" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AD41" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -3966,16 +3966,16 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>518</v>
+        <v>45</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD42" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -4007,16 +4007,16 @@
         </is>
       </c>
       <c r="AB43" s="7" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="AC43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD43" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -4048,16 +4048,16 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD44" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -4089,16 +4089,16 @@
         </is>
       </c>
       <c r="AB45" s="7" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="AC45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD45" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD46" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>1</v>
+        <v>518</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AD47" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="AC48" s="4" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="AD48" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AD49" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -4294,16 +4294,16 @@
         </is>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>474</v>
+        <v>57</v>
       </c>
       <c r="AC50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD50" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -4335,16 +4335,16 @@
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD51" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -4376,16 +4376,16 @@
         </is>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD52" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -4417,16 +4417,16 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD53" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -4458,16 +4458,16 @@
         </is>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD54" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -4499,16 +4499,16 @@
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD55" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="AD56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="AD57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -4622,16 +4622,16 @@
         </is>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>430</v>
+        <v>138</v>
       </c>
       <c r="AC58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD58" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -4663,16 +4663,16 @@
         </is>
       </c>
       <c r="AB59" s="7" t="n">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="AC59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD59" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD60" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -4745,16 +4745,16 @@
         </is>
       </c>
       <c r="AB61" s="7" t="n">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="AC61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD61" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -4786,16 +4786,16 @@
         </is>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="AC62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD62" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -4827,16 +4827,16 @@
         </is>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD63" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -4868,16 +4868,16 @@
         </is>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD64" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>2</v>
+        <v>430</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AD65" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -4950,16 +4950,16 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>478</v>
+        <v>27</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -4991,11 +4991,11 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD67" s="7" t="inlineStr">
@@ -5032,11 +5032,11 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD68" s="4" t="inlineStr">
@@ -5073,11 +5073,11 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD69" s="7" t="inlineStr">
@@ -5114,11 +5114,11 @@
         </is>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD70" s="4" t="inlineStr">
@@ -5155,11 +5155,11 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD71" s="7" t="inlineStr">
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD72" s="4" t="inlineStr">
@@ -5237,11 +5237,11 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD73" s="7" t="inlineStr">
@@ -5278,11 +5278,11 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD74" s="4" t="inlineStr">
@@ -5319,16 +5319,16 @@
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD75" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -5360,16 +5360,16 @@
         </is>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD76" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -5401,16 +5401,16 @@
         </is>
       </c>
       <c r="AB77" s="7" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AC77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD77" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -5442,16 +5442,16 @@
         </is>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -5483,11 +5483,11 @@
         </is>
       </c>
       <c r="AB79" s="7" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AC79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD79" s="7" t="inlineStr">
@@ -5524,11 +5524,11 @@
         </is>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD80" s="4" t="inlineStr">
@@ -5565,11 +5565,11 @@
         </is>
       </c>
       <c r="AB81" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD81" s="7" t="inlineStr">
@@ -5606,11 +5606,11 @@
         </is>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD82" s="4" t="inlineStr">
@@ -5647,11 +5647,11 @@
         </is>
       </c>
       <c r="AB83" s="7" t="n">
-        <v>324</v>
+        <v>443</v>
       </c>
       <c r="AC83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD83" s="7" t="inlineStr">
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD84" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -5729,16 +5729,16 @@
         </is>
       </c>
       <c r="AB85" s="7" t="n">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD85" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -5770,16 +5770,16 @@
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD86" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -5811,16 +5811,16 @@
         </is>
       </c>
       <c r="AB87" s="7" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="AC87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD87" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD88" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
     </row>
@@ -5893,16 +5893,16 @@
         </is>
       </c>
       <c r="AB89" s="7" t="n">
-        <v>8</v>
+        <v>129</v>
       </c>
       <c r="AC89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD89" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -5938,12 +5938,12 @@
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD90" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -5975,16 +5975,16 @@
         </is>
       </c>
       <c r="AB91" s="7" t="n">
-        <v>327</v>
+        <v>7</v>
       </c>
       <c r="AC91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD91" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -6016,16 +6016,16 @@
         </is>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>176</v>
+        <v>2</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD92" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -6057,16 +6057,16 @@
         </is>
       </c>
       <c r="AB93" s="7" t="n">
-        <v>51</v>
+        <v>324</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD93" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -6098,16 +6098,16 @@
         </is>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD94" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -6139,16 +6139,16 @@
         </is>
       </c>
       <c r="AB95" s="7" t="n">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD95" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -6180,16 +6180,16 @@
         </is>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD96" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -6221,16 +6221,16 @@
         </is>
       </c>
       <c r="AB97" s="7" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD97" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -6262,16 +6262,16 @@
         </is>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD98" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -6303,16 +6303,16 @@
         </is>
       </c>
       <c r="AB99" s="7" t="n">
-        <v>319</v>
+        <v>1</v>
       </c>
       <c r="AC99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD99" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -6344,16 +6344,16 @@
         </is>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="AC100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD100" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -6385,16 +6385,16 @@
         </is>
       </c>
       <c r="AB101" s="7" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD101" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -6426,16 +6426,16 @@
         </is>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>31</v>
+        <v>327</v>
       </c>
       <c r="AC102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD102" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -6467,16 +6467,16 @@
         </is>
       </c>
       <c r="AB103" s="7" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD103" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>3</v>
+        <v>176</v>
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD104" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -6549,16 +6549,16 @@
         </is>
       </c>
       <c r="AB105" s="7" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="AC105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD105" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD106" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -6631,16 +6631,16 @@
         </is>
       </c>
       <c r="AB107" s="7" t="n">
-        <v>332</v>
+        <v>156</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD107" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -6672,16 +6672,16 @@
         </is>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD108" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -6713,16 +6713,16 @@
         </is>
       </c>
       <c r="AB109" s="7" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD109" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -6754,16 +6754,16 @@
         </is>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD110" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -6795,16 +6795,16 @@
         </is>
       </c>
       <c r="AB111" s="7" t="n">
-        <v>141</v>
+        <v>319</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD111" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -6836,16 +6836,16 @@
         </is>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD112" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -6877,16 +6877,16 @@
         </is>
       </c>
       <c r="AB113" s="7" t="n">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD113" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD114" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -6959,16 +6959,16 @@
         </is>
       </c>
       <c r="AB115" s="7" t="n">
-        <v>323</v>
+        <v>31</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD115" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -7000,16 +7000,16 @@
         </is>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD116" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -7041,16 +7041,16 @@
         </is>
       </c>
       <c r="AB117" s="7" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD117" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -7082,16 +7082,16 @@
         </is>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD118" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -7123,16 +7123,16 @@
         </is>
       </c>
       <c r="AB119" s="7" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD119" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -7164,16 +7164,16 @@
         </is>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="AC120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD120" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -7205,16 +7205,16 @@
         </is>
       </c>
       <c r="AB121" s="7" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AC121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD121" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -7246,16 +7246,16 @@
         </is>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>2</v>
+        <v>158</v>
       </c>
       <c r="AC122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD122" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -7287,16 +7287,16 @@
         </is>
       </c>
       <c r="AB123" s="7" t="n">
-        <v>350</v>
+        <v>54</v>
       </c>
       <c r="AC123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD123" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -7328,16 +7328,16 @@
         </is>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="AC124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD124" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -7369,16 +7369,16 @@
         </is>
       </c>
       <c r="AB125" s="7" t="n">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="AC125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD125" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -7410,16 +7410,16 @@
         </is>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD126" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -7451,16 +7451,16 @@
         </is>
       </c>
       <c r="AB127" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD127" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -7492,16 +7492,16 @@
         </is>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD128" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -7533,16 +7533,16 @@
         </is>
       </c>
       <c r="AB129" s="7" t="n">
-        <v>3</v>
+        <v>323</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD129" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -7574,16 +7574,16 @@
         </is>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD130" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -7615,16 +7615,16 @@
         </is>
       </c>
       <c r="AB131" s="7" t="n">
-        <v>319</v>
+        <v>132</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD131" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -7656,16 +7656,16 @@
         </is>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD132" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -7697,16 +7697,16 @@
         </is>
       </c>
       <c r="AB133" s="7" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD133" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -7738,16 +7738,16 @@
         </is>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD134" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -7779,16 +7779,16 @@
         </is>
       </c>
       <c r="AB135" s="7" t="n">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD135" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -7820,16 +7820,16 @@
         </is>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD136" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -7861,16 +7861,16 @@
         </is>
       </c>
       <c r="AB137" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD137" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -7902,16 +7902,16 @@
         </is>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>2</v>
+        <v>350</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD138" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -7943,16 +7943,16 @@
         </is>
       </c>
       <c r="AB139" s="7" t="n">
-        <v>325</v>
+        <v>23</v>
       </c>
       <c r="AC139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD139" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -7984,11 +7984,11 @@
         </is>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD140" s="4" t="inlineStr">
@@ -8025,11 +8025,11 @@
         </is>
       </c>
       <c r="AB141" s="7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AC141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD141" s="7" t="inlineStr">
@@ -8066,11 +8066,11 @@
         </is>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD142" s="4" t="inlineStr">
@@ -8107,16 +8107,16 @@
         </is>
       </c>
       <c r="AB143" s="7" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD143" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
     </row>
@@ -8148,16 +8148,16 @@
         </is>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="AC144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD144" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -8189,16 +8189,16 @@
         </is>
       </c>
       <c r="AB145" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD145" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -8230,16 +8230,16 @@
         </is>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD146" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -8270,9 +8270,19 @@
           <t>com.logistics.rider.foody</t>
         </is>
       </c>
-      <c r="AB147" s="7" t="n"/>
-      <c r="AC147" s="7" t="n"/>
-      <c r="AD147" s="7" t="n"/>
+      <c r="AB147" s="7" t="n">
+        <v>319</v>
+      </c>
+      <c r="AC147" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD147" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="T148" s="4" t="inlineStr">
@@ -8291,9 +8301,19 @@
       <c r="X148" s="4" t="n"/>
       <c r="Y148" s="4" t="n"/>
       <c r="Z148" s="4" t="n"/>
-      <c r="AB148" s="4" t="n"/>
-      <c r="AC148" s="4" t="n"/>
-      <c r="AD148" s="4" t="n"/>
+      <c r="AB148" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC148" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD148" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="T149" s="7" t="inlineStr">
@@ -8312,9 +8332,19 @@
       <c r="X149" s="7" t="n"/>
       <c r="Y149" s="7" t="n"/>
       <c r="Z149" s="7" t="n"/>
-      <c r="AB149" s="7" t="n"/>
-      <c r="AC149" s="7" t="n"/>
-      <c r="AD149" s="7" t="n"/>
+      <c r="AB149" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AC149" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD149" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="T150" s="4" t="inlineStr">
@@ -8333,9 +8363,19 @@
       <c r="X150" s="4" t="n"/>
       <c r="Y150" s="4" t="n"/>
       <c r="Z150" s="4" t="n"/>
-      <c r="AB150" s="4" t="n"/>
-      <c r="AC150" s="4" t="n"/>
-      <c r="AD150" s="4" t="n"/>
+      <c r="AB150" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC150" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD150" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="T151" s="7" t="inlineStr">
@@ -8354,9 +8394,19 @@
       <c r="X151" s="7" t="n"/>
       <c r="Y151" s="7" t="n"/>
       <c r="Z151" s="7" t="n"/>
-      <c r="AB151" s="7" t="n"/>
-      <c r="AC151" s="7" t="n"/>
-      <c r="AD151" s="7" t="n"/>
+      <c r="AB151" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC151" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD151" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="T152" s="4" t="inlineStr">
@@ -8375,9 +8425,19 @@
       <c r="X152" s="4" t="n"/>
       <c r="Y152" s="4" t="n"/>
       <c r="Z152" s="4" t="n"/>
-      <c r="AB152" s="4" t="n"/>
-      <c r="AC152" s="4" t="n"/>
-      <c r="AD152" s="4" t="n"/>
+      <c r="AB152" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AC152" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD152" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="T153" s="7" t="inlineStr">
@@ -8396,9 +8456,19 @@
       <c r="X153" s="7" t="n"/>
       <c r="Y153" s="7" t="n"/>
       <c r="Z153" s="7" t="n"/>
-      <c r="AB153" s="7" t="n"/>
-      <c r="AC153" s="7" t="n"/>
-      <c r="AD153" s="7" t="n"/>
+      <c r="AB153" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC153" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD153" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="T154" s="4" t="inlineStr">
@@ -8417,9 +8487,19 @@
       <c r="X154" s="4" t="n"/>
       <c r="Y154" s="4" t="n"/>
       <c r="Z154" s="4" t="n"/>
-      <c r="AB154" s="4" t="n"/>
-      <c r="AC154" s="4" t="n"/>
-      <c r="AD154" s="4" t="n"/>
+      <c r="AB154" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC154" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD154" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="T155" s="7" t="inlineStr">
@@ -8438,9 +8518,19 @@
       <c r="X155" s="7" t="n"/>
       <c r="Y155" s="7" t="n"/>
       <c r="Z155" s="7" t="n"/>
-      <c r="AB155" s="7" t="n"/>
-      <c r="AC155" s="7" t="n"/>
-      <c r="AD155" s="7" t="n"/>
+      <c r="AB155" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC155" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD155" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="T156" s="4" t="inlineStr">
@@ -8459,9 +8549,19 @@
       <c r="X156" s="4" t="n"/>
       <c r="Y156" s="4" t="n"/>
       <c r="Z156" s="4" t="n"/>
-      <c r="AB156" s="4" t="n"/>
-      <c r="AC156" s="4" t="n"/>
-      <c r="AD156" s="4" t="n"/>
+      <c r="AB156" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="AC156" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD156" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="T157" s="7" t="inlineStr">
@@ -8480,9 +8580,19 @@
       <c r="X157" s="7" t="n"/>
       <c r="Y157" s="7" t="n"/>
       <c r="Z157" s="7" t="n"/>
-      <c r="AB157" s="7" t="n"/>
-      <c r="AC157" s="7" t="n"/>
-      <c r="AD157" s="7" t="n"/>
+      <c r="AB157" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC157" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD157" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="T158" s="4" t="inlineStr">
@@ -8501,9 +8611,19 @@
       <c r="X158" s="4" t="n"/>
       <c r="Y158" s="4" t="n"/>
       <c r="Z158" s="4" t="n"/>
-      <c r="AB158" s="4" t="n"/>
-      <c r="AC158" s="4" t="n"/>
-      <c r="AD158" s="4" t="n"/>
+      <c r="AB158" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AC158" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD158" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="T159" s="7" t="inlineStr">
@@ -8522,9 +8642,19 @@
       <c r="X159" s="7" t="n"/>
       <c r="Y159" s="7" t="n"/>
       <c r="Z159" s="7" t="n"/>
-      <c r="AB159" s="7" t="n"/>
-      <c r="AC159" s="7" t="n"/>
-      <c r="AD159" s="7" t="n"/>
+      <c r="AB159" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC159" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD159" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="T160" s="4" t="inlineStr">
@@ -8543,9 +8673,19 @@
       <c r="X160" s="4" t="n"/>
       <c r="Y160" s="4" t="n"/>
       <c r="Z160" s="4" t="n"/>
-      <c r="AB160" s="4" t="n"/>
-      <c r="AC160" s="4" t="n"/>
-      <c r="AD160" s="4" t="n"/>
+      <c r="AB160" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC160" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD160" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="T161" s="7" t="inlineStr">
@@ -8564,9 +8704,19 @@
       <c r="X161" s="7" t="n"/>
       <c r="Y161" s="7" t="n"/>
       <c r="Z161" s="7" t="n"/>
-      <c r="AB161" s="7" t="n"/>
-      <c r="AC161" s="7" t="n"/>
-      <c r="AD161" s="7" t="n"/>
+      <c r="AB161" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AC161" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD161" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="T162" s="4" t="inlineStr">
@@ -8585,9 +8735,19 @@
       <c r="X162" s="4" t="n"/>
       <c r="Y162" s="4" t="n"/>
       <c r="Z162" s="4" t="n"/>
-      <c r="AB162" s="4" t="n"/>
-      <c r="AC162" s="4" t="n"/>
-      <c r="AD162" s="4" t="n"/>
+      <c r="AB162" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC162" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD162" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="T163" s="7" t="inlineStr">
@@ -8606,9 +8766,19 @@
       <c r="X163" s="7" t="n"/>
       <c r="Y163" s="7" t="n"/>
       <c r="Z163" s="7" t="n"/>
-      <c r="AB163" s="7" t="n"/>
-      <c r="AC163" s="7" t="n"/>
-      <c r="AD163" s="7" t="n"/>
+      <c r="AB163" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC163" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD163" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="T164" s="4" t="inlineStr">
@@ -8627,9 +8797,19 @@
       <c r="X164" s="4" t="n"/>
       <c r="Y164" s="4" t="n"/>
       <c r="Z164" s="4" t="n"/>
-      <c r="AB164" s="4" t="n"/>
-      <c r="AC164" s="4" t="n"/>
-      <c r="AD164" s="4" t="n"/>
+      <c r="AB164" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC164" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD164" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="T165" s="7" t="inlineStr">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -716,10 +716,10 @@
         <v>0.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -752,10 +752,10 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -788,10 +788,10 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -824,10 +824,10 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -860,10 +860,10 @@
         <v>0.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -896,10 +896,10 @@
         <v>0.95</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -932,10 +932,10 @@
         <v>0.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -968,10 +968,10 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1004,10 +1004,10 @@
         <v>0.95</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1040,10 +1040,10 @@
         <v>0.95</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD235"/>
+  <dimension ref="A1:AD164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1344,15 +1344,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>103</v>
       </c>
@@ -1429,15 +1423,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>13</v>
       </c>
@@ -1514,15 +1502,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>64</v>
       </c>
@@ -1593,15 +1575,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>30</v>
       </c>
@@ -1678,15 +1654,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>21</v>
       </c>
@@ -1763,15 +1733,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>73</v>
       </c>
@@ -1848,15 +1812,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>15</v>
       </c>
@@ -1927,15 +1885,9 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>1</v>
       </c>
@@ -2014,15 +1966,9 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>105</v>
       </c>
@@ -2093,15 +2039,9 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>19</v>
       </c>
@@ -2172,15 +2112,9 @@
         <f>$B$2+H12+M12</f>
         <v/>
       </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>82</v>
       </c>
@@ -2251,15 +2185,9 @@
         <f>$B$2+H13+M13</f>
         <v/>
       </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>25</v>
       </c>
@@ -2330,15 +2258,9 @@
         <f>$B$2+H14+M14</f>
         <v/>
       </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>15</v>
       </c>
@@ -2409,15 +2331,9 @@
         <f>$B$2+H15+M15</f>
         <v/>
       </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>75</v>
       </c>
@@ -2488,15 +2404,9 @@
         <f>$B$2+H16+M16</f>
         <v/>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>9</v>
       </c>
@@ -2567,15 +2477,9 @@
         <f>$B$2+H17+M17</f>
         <v/>
       </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>1</v>
       </c>
@@ -2646,15 +2550,9 @@
         <f>$B$2+H18+M18</f>
         <v/>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>145</v>
       </c>
@@ -2725,15 +2623,9 @@
         <f>$B$2+H19+M19</f>
         <v/>
       </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>19</v>
       </c>
@@ -2780,19 +2672,9 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>5365</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>74</v>
       </c>
@@ -2839,19 +2721,9 @@
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>5741</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>26</v>
       </c>
@@ -2898,19 +2770,9 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>5451</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>9</v>
       </c>
@@ -2957,19 +2819,9 @@
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>5458</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
         <v>74</v>
       </c>
@@ -3016,19 +2868,9 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>5664</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
         <v>11</v>
       </c>
@@ -3075,19 +2917,9 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>5241</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>101</v>
       </c>
@@ -3134,19 +2966,9 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>5102</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
         <v>11</v>
       </c>
@@ -3193,19 +3015,9 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>5388</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
         <v>73</v>
       </c>
@@ -3252,19 +3064,9 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
         <v>31</v>
       </c>
@@ -3311,19 +3113,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>5348</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>13</v>
       </c>
@@ -3370,19 +3162,9 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>5329</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
         <v>78</v>
       </c>
@@ -3429,19 +3211,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>5436</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
@@ -3497,19 +3269,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>5081</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>9</v>
       </c>
@@ -3570,19 +3332,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>5034</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
@@ -3611,19 +3363,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>119</v>
       </c>
@@ -3652,19 +3394,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>5513</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>13</v>
       </c>
@@ -3693,19 +3425,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>5477</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>67</v>
       </c>
@@ -3734,19 +3456,9 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>5526</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
         <v>32</v>
       </c>
@@ -3775,19 +3487,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>14969</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
         <v>13</v>
       </c>
@@ -3816,19 +3518,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>14818</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>93</v>
       </c>
@@ -3857,19 +3549,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>15263</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>12</v>
       </c>
@@ -3898,19 +3580,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>2</v>
       </c>
@@ -3939,19 +3611,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>14968</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>113</v>
       </c>
@@ -3980,19 +3642,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>14113</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>12</v>
       </c>
@@ -4021,19 +3673,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>14162</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>69</v>
       </c>
@@ -4062,19 +3704,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>40</v>
       </c>
@@ -4103,19 +3735,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>17</v>
       </c>
@@ -4144,19 +3766,9 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>15546</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>83</v>
       </c>
@@ -4185,19 +3797,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>14882</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>9</v>
       </c>
@@ -4226,19 +3828,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>14998</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>124</v>
       </c>
@@ -4267,19 +3859,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>14354</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>19</v>
       </c>
@@ -4308,19 +3890,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>14362</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>55</v>
       </c>
@@ -4349,19 +3921,9 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>15089</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
         <v>35</v>
       </c>
@@ -4390,19 +3952,9 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>14802</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>15</v>
       </c>
@@ -4431,19 +3983,9 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>15349</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>82</v>
       </c>
@@ -4472,19 +4014,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>14872</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>1</v>
       </c>
@@ -4513,19 +4045,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>77546</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>14</v>
       </c>
@@ -4554,19 +4076,9 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>77823</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>2</v>
       </c>
@@ -4595,19 +4107,9 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>81723</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
         <v>101</v>
       </c>
@@ -4636,19 +4138,9 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>78398</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
         <v>10</v>
       </c>
@@ -4677,19 +4169,9 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>78030</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
         <v>72</v>
       </c>
@@ -4718,19 +4200,9 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>76646</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
         <v>35</v>
       </c>
@@ -4759,19 +4231,9 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>76742</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
         <v>13</v>
       </c>
@@ -4800,19 +4262,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>79003</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>71</v>
       </c>
@@ -4841,19 +4293,9 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>78849</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
         <v>8</v>
       </c>
@@ -4882,19 +4324,9 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>80667</v>
-      </c>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
         <v>2</v>
       </c>
@@ -4923,19 +4355,9 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>78640</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>125</v>
       </c>
@@ -4964,19 +4386,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>79108</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>11</v>
       </c>
@@ -5005,19 +4417,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>76911</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>67</v>
       </c>
@@ -5046,19 +4448,9 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>77273</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>27</v>
       </c>
@@ -5087,19 +4479,9 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>80657</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
         <v>17</v>
       </c>
@@ -5128,19 +4510,9 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>79898</v>
-      </c>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
         <v>85</v>
       </c>
@@ -5169,19 +4541,9 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>82443</v>
-      </c>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
         <v>14</v>
       </c>
@@ -5210,19 +4572,9 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>80658</v>
-      </c>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
         <v>4</v>
       </c>
@@ -5251,19 +4603,9 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
         <v>126</v>
       </c>
@@ -5292,19 +4634,9 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>715</v>
-      </c>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
         <v>23</v>
       </c>
@@ -5333,19 +4665,9 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>745</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>65</v>
       </c>
@@ -5374,19 +4696,9 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>702</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
         <v>28</v>
       </c>
@@ -5415,19 +4727,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>743</v>
-      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
         <v>19</v>
       </c>
@@ -5456,19 +4758,9 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>700</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>91</v>
       </c>
@@ -5497,19 +4789,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>21</v>
       </c>
@@ -5538,19 +4820,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>750</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
         <v>2</v>
       </c>
@@ -5579,19 +4851,9 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>729</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
         <v>99</v>
       </c>
@@ -5620,19 +4882,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>748</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>12</v>
       </c>
@@ -5661,19 +4913,9 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>736</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
         <v>70</v>
       </c>
@@ -5702,19 +4944,9 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>737</v>
-      </c>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
         <v>30</v>
       </c>
@@ -5743,19 +4975,9 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>707</v>
-      </c>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
         <v>15</v>
       </c>
@@ -5784,19 +5006,9 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>713</v>
-      </c>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
         <v>73</v>
       </c>
@@ -5825,19 +5037,9 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>786</v>
-      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
         <v>5</v>
       </c>
@@ -5866,19 +5068,9 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>730</v>
-      </c>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
         <v>1</v>
       </c>
@@ -5907,19 +5099,9 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>726</v>
-      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
         <v>107</v>
       </c>
@@ -5948,19 +5130,9 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>695</v>
-      </c>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
         <v>13</v>
       </c>
@@ -5989,19 +5161,9 @@
       </c>
     </row>
     <row r="92">
-      <c r="T92" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V92" s="4" t="n">
-        <v>47976</v>
-      </c>
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
       <c r="X92" s="4" t="n">
         <v>56</v>
       </c>
@@ -6030,19 +5192,9 @@
       </c>
     </row>
     <row r="93">
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U93" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>47122</v>
-      </c>
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
         <v>32</v>
       </c>
@@ -6071,19 +5223,9 @@
       </c>
     </row>
     <row r="94">
-      <c r="T94" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>47233</v>
-      </c>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
         <v>13</v>
       </c>
@@ -6112,19 +5254,9 @@
       </c>
     </row>
     <row r="95">
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>48580</v>
-      </c>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
         <v>78</v>
       </c>
@@ -6153,19 +5285,9 @@
       </c>
     </row>
     <row r="96">
-      <c r="T96" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V96" s="4" t="n">
-        <v>47383</v>
-      </c>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
       <c r="X96" s="4" t="n">
         <v>10</v>
       </c>
@@ -6194,19 +5316,9 @@
       </c>
     </row>
     <row r="97">
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V97" s="7" t="n">
-        <v>46456</v>
-      </c>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
         <v>1</v>
       </c>
@@ -6235,19 +5347,9 @@
       </c>
     </row>
     <row r="98">
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>46400</v>
-      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
         <v>114</v>
       </c>
@@ -6276,19 +5378,9 @@
       </c>
     </row>
     <row r="99">
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V99" s="7" t="n">
-        <v>47755</v>
-      </c>
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
         <v>15</v>
       </c>
@@ -6317,19 +5409,9 @@
       </c>
     </row>
     <row r="100">
-      <c r="T100" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>47520</v>
-      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
         <v>53</v>
       </c>
@@ -6358,19 +5440,9 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U101" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V101" s="7" t="n">
-        <v>47354</v>
-      </c>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
         <v>32</v>
       </c>
@@ -6399,19 +5471,9 @@
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n">
-        <v>49015</v>
-      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
         <v>14</v>
       </c>
@@ -6440,19 +5502,9 @@
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V103" s="7" t="n">
-        <v>48832</v>
-      </c>
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
         <v>80</v>
       </c>
@@ -6481,19 +5533,9 @@
       </c>
     </row>
     <row r="104">
-      <c r="T104" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U104" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V104" s="4" t="n">
-        <v>46644</v>
-      </c>
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="4" t="n"/>
+      <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
         <v>1</v>
       </c>
@@ -6522,19 +5564,9 @@
       </c>
     </row>
     <row r="105">
-      <c r="T105" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U105" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>46416</v>
-      </c>
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
         <v>9</v>
       </c>
@@ -6563,19 +5595,9 @@
       </c>
     </row>
     <row r="106">
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="n">
-        <v>48419</v>
-      </c>
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="4" t="n"/>
+      <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
         <v>4</v>
       </c>
@@ -6604,19 +5626,9 @@
       </c>
     </row>
     <row r="107">
-      <c r="T107" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U107" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V107" s="7" t="n">
-        <v>47500</v>
-      </c>
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
         <v>97</v>
       </c>
@@ -6645,19 +5657,9 @@
       </c>
     </row>
     <row r="108">
-      <c r="T108" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U108" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V108" s="4" t="n">
-        <v>47954</v>
-      </c>
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="4" t="n"/>
+      <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
         <v>10</v>
       </c>
@@ -6686,19 +5688,9 @@
       </c>
     </row>
     <row r="109">
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U109" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V109" s="7" t="n">
-        <v>49088</v>
-      </c>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
         <v>52</v>
       </c>
@@ -6727,19 +5719,9 @@
       </c>
     </row>
     <row r="110">
-      <c r="T110" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U110" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V110" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="n"/>
       <c r="X110" s="4" t="n">
         <v>37</v>
       </c>
@@ -6768,19 +5750,9 @@
       </c>
     </row>
     <row r="111">
-      <c r="T111" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U111" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V111" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
       <c r="X111" s="7" t="n">
         <v>18</v>
       </c>
@@ -6809,19 +5781,9 @@
       </c>
     </row>
     <row r="112">
-      <c r="T112" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U112" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V112" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="4" t="n"/>
+      <c r="V112" s="4" t="n"/>
       <c r="X112" s="4" t="n">
         <v>64</v>
       </c>
@@ -6850,19 +5812,9 @@
       </c>
     </row>
     <row r="113">
-      <c r="T113" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U113" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V113" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
         <v>7</v>
       </c>
@@ -6891,19 +5843,9 @@
       </c>
     </row>
     <row r="114">
-      <c r="T114" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U114" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V114" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="n"/>
       <c r="X114" s="4" t="n">
         <v>106</v>
       </c>
@@ -6932,19 +5874,9 @@
       </c>
     </row>
     <row r="115">
-      <c r="T115" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U115" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V115" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
       <c r="X115" s="7" t="n">
         <v>14</v>
       </c>
@@ -6973,19 +5905,9 @@
       </c>
     </row>
     <row r="116">
-      <c r="T116" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U116" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V116" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T116" s="4" t="n"/>
+      <c r="U116" s="4" t="n"/>
+      <c r="V116" s="4" t="n"/>
       <c r="X116" s="4" t="n">
         <v>65</v>
       </c>
@@ -7014,19 +5936,9 @@
       </c>
     </row>
     <row r="117">
-      <c r="T117" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U117" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V117" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
       <c r="X117" s="7" t="n">
         <v>24</v>
       </c>
@@ -7055,19 +5967,9 @@
       </c>
     </row>
     <row r="118">
-      <c r="T118" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U118" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V118" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T118" s="4" t="n"/>
+      <c r="U118" s="4" t="n"/>
+      <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
         <v>14</v>
       </c>
@@ -7096,19 +5998,9 @@
       </c>
     </row>
     <row r="119">
-      <c r="T119" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U119" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V119" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
         <v>66</v>
       </c>
@@ -7137,19 +6029,9 @@
       </c>
     </row>
     <row r="120">
-      <c r="T120" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U120" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T120" s="4" t="n"/>
+      <c r="U120" s="4" t="n"/>
+      <c r="V120" s="4" t="n"/>
       <c r="X120" s="4" t="n">
         <v>1</v>
       </c>
@@ -7178,19 +6060,9 @@
       </c>
     </row>
     <row r="121">
-      <c r="T121" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U121" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T121" s="7" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
       <c r="X121" s="7" t="n">
         <v>9</v>
       </c>
@@ -7219,19 +6091,9 @@
       </c>
     </row>
     <row r="122">
-      <c r="T122" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U122" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V122" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T122" s="4" t="n"/>
+      <c r="U122" s="4" t="n"/>
+      <c r="V122" s="4" t="n"/>
       <c r="X122" s="4" t="n">
         <v>116</v>
       </c>
@@ -7260,19 +6122,9 @@
       </c>
     </row>
     <row r="123">
-      <c r="T123" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U123" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V123" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T123" s="7" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
       <c r="X123" s="7" t="n">
         <v>17</v>
       </c>
@@ -7301,19 +6153,9 @@
       </c>
     </row>
     <row r="124">
-      <c r="T124" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U124" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T124" s="4" t="n"/>
+      <c r="U124" s="4" t="n"/>
+      <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
         <v>52</v>
       </c>
@@ -7342,19 +6184,9 @@
       </c>
     </row>
     <row r="125">
-      <c r="T125" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V125" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T125" s="7" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
         <v>38</v>
       </c>
@@ -7383,19 +6215,9 @@
       </c>
     </row>
     <row r="126">
-      <c r="T126" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U126" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V126" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T126" s="4" t="n"/>
+      <c r="U126" s="4" t="n"/>
+      <c r="V126" s="4" t="n"/>
       <c r="X126" s="4" t="n">
         <v>19</v>
       </c>
@@ -7424,19 +6246,9 @@
       </c>
     </row>
     <row r="127">
-      <c r="T127" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U127" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V127" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T127" s="7" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
       <c r="X127" s="7" t="n">
         <v>79</v>
       </c>
@@ -7465,19 +6277,9 @@
       </c>
     </row>
     <row r="128">
-      <c r="T128" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U128" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V128" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T128" s="4" t="n"/>
+      <c r="U128" s="4" t="n"/>
+      <c r="V128" s="4" t="n"/>
       <c r="X128" s="4" t="n">
         <v>9</v>
       </c>
@@ -7506,19 +6308,9 @@
       </c>
     </row>
     <row r="129">
-      <c r="T129" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U129" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V129" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T129" s="7" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
       <c r="X129" s="7" t="n">
         <v>1</v>
       </c>
@@ -7547,19 +6339,9 @@
       </c>
     </row>
     <row r="130">
-      <c r="T130" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U130" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V130" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T130" s="4" t="n"/>
+      <c r="U130" s="4" t="n"/>
+      <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
         <v>134</v>
       </c>
@@ -7588,19 +6370,9 @@
       </c>
     </row>
     <row r="131">
-      <c r="T131" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U131" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V131" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T131" s="7" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
         <v>22</v>
       </c>
@@ -7629,19 +6401,9 @@
       </c>
     </row>
     <row r="132">
-      <c r="T132" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U132" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V132" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T132" s="4" t="n"/>
+      <c r="U132" s="4" t="n"/>
+      <c r="V132" s="4" t="n"/>
       <c r="X132" s="4" t="n">
         <v>65</v>
       </c>
@@ -7670,19 +6432,9 @@
       </c>
     </row>
     <row r="133">
-      <c r="T133" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U133" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V133" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T133" s="7" t="n"/>
+      <c r="U133" s="7" t="n"/>
+      <c r="V133" s="7" t="n"/>
       <c r="X133" s="7" t="n">
         <v>29</v>
       </c>
@@ -7711,19 +6463,9 @@
       </c>
     </row>
     <row r="134">
-      <c r="T134" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U134" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V134" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="4" t="n"/>
+      <c r="V134" s="4" t="n"/>
       <c r="X134" s="4" t="n">
         <v>12</v>
       </c>
@@ -7752,19 +6494,9 @@
       </c>
     </row>
     <row r="135">
-      <c r="T135" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U135" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V135" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T135" s="7" t="n"/>
+      <c r="U135" s="7" t="n"/>
+      <c r="V135" s="7" t="n"/>
       <c r="X135" s="7" t="n">
         <v>82</v>
       </c>
@@ -7793,19 +6525,9 @@
       </c>
     </row>
     <row r="136">
-      <c r="T136" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U136" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V136" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T136" s="4" t="n"/>
+      <c r="U136" s="4" t="n"/>
+      <c r="V136" s="4" t="n"/>
       <c r="X136" s="4" t="n">
         <v>1</v>
       </c>
@@ -7834,19 +6556,9 @@
       </c>
     </row>
     <row r="137">
-      <c r="T137" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U137" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V137" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T137" s="7" t="n"/>
+      <c r="U137" s="7" t="n"/>
+      <c r="V137" s="7" t="n"/>
       <c r="X137" s="7" t="n">
         <v>7</v>
       </c>
@@ -7875,19 +6587,9 @@
       </c>
     </row>
     <row r="138">
-      <c r="T138" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U138" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V138" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T138" s="4" t="n"/>
+      <c r="U138" s="4" t="n"/>
+      <c r="V138" s="4" t="n"/>
       <c r="X138" s="4" t="n">
         <v>1</v>
       </c>
@@ -7916,19 +6618,9 @@
       </c>
     </row>
     <row r="139">
-      <c r="T139" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U139" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V139" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T139" s="7" t="n"/>
+      <c r="U139" s="7" t="n"/>
+      <c r="V139" s="7" t="n"/>
       <c r="X139" s="7" t="n">
         <v>107</v>
       </c>
@@ -7957,19 +6649,9 @@
       </c>
     </row>
     <row r="140">
-      <c r="T140" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U140" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V140" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T140" s="4" t="n"/>
+      <c r="U140" s="4" t="n"/>
+      <c r="V140" s="4" t="n"/>
       <c r="X140" s="4" t="n">
         <v>24</v>
       </c>
@@ -7998,19 +6680,9 @@
       </c>
     </row>
     <row r="141">
-      <c r="T141" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U141" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V141" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T141" s="7" t="n"/>
+      <c r="U141" s="7" t="n"/>
+      <c r="V141" s="7" t="n"/>
       <c r="X141" s="7" t="n">
         <v>68</v>
       </c>
@@ -8039,19 +6711,9 @@
       </c>
     </row>
     <row r="142">
-      <c r="T142" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U142" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V142" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T142" s="4" t="n"/>
+      <c r="U142" s="4" t="n"/>
+      <c r="V142" s="4" t="n"/>
       <c r="X142" s="4" t="n">
         <v>18</v>
       </c>
@@ -8080,19 +6742,9 @@
       </c>
     </row>
     <row r="143">
-      <c r="T143" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U143" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V143" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T143" s="7" t="n"/>
+      <c r="U143" s="7" t="n"/>
+      <c r="V143" s="7" t="n"/>
       <c r="X143" s="7" t="n">
         <v>12</v>
       </c>
@@ -8121,19 +6773,9 @@
       </c>
     </row>
     <row r="144">
-      <c r="T144" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U144" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V144" s="4" t="n">
-        <v>9927</v>
-      </c>
+      <c r="T144" s="4" t="n"/>
+      <c r="U144" s="4" t="n"/>
+      <c r="V144" s="4" t="n"/>
       <c r="X144" s="4" t="n">
         <v>70</v>
       </c>
@@ -8162,19 +6804,9 @@
       </c>
     </row>
     <row r="145">
-      <c r="T145" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U145" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V145" s="7" t="n">
-        <v>9839</v>
-      </c>
+      <c r="T145" s="7" t="n"/>
+      <c r="U145" s="7" t="n"/>
+      <c r="V145" s="7" t="n"/>
       <c r="X145" s="7" t="n">
         <v>2</v>
       </c>
@@ -8203,19 +6835,9 @@
       </c>
     </row>
     <row r="146">
-      <c r="T146" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U146" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V146" s="4" t="n">
-        <v>9918</v>
-      </c>
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
       <c r="X146" s="4" t="n">
         <v>6</v>
       </c>
@@ -8244,19 +6866,9 @@
       </c>
     </row>
     <row r="147">
-      <c r="T147" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U147" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V147" s="7" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T147" s="7" t="n"/>
+      <c r="U147" s="7" t="n"/>
+      <c r="V147" s="7" t="n"/>
       <c r="X147" s="7" t="n">
         <v>2</v>
       </c>
@@ -8285,19 +6897,9 @@
       </c>
     </row>
     <row r="148">
-      <c r="T148" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U148" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V148" s="4" t="n">
-        <v>10050</v>
-      </c>
+      <c r="T148" s="4" t="n"/>
+      <c r="U148" s="4" t="n"/>
+      <c r="V148" s="4" t="n"/>
       <c r="X148" s="4" t="n"/>
       <c r="Y148" s="4" t="n"/>
       <c r="Z148" s="4" t="n"/>
@@ -8316,19 +6918,9 @@
       </c>
     </row>
     <row r="149">
-      <c r="T149" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U149" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V149" s="7" t="n">
-        <v>9768</v>
-      </c>
+      <c r="T149" s="7" t="n"/>
+      <c r="U149" s="7" t="n"/>
+      <c r="V149" s="7" t="n"/>
       <c r="X149" s="7" t="n"/>
       <c r="Y149" s="7" t="n"/>
       <c r="Z149" s="7" t="n"/>
@@ -8347,19 +6939,9 @@
       </c>
     </row>
     <row r="150">
-      <c r="T150" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U150" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="n">
-        <v>9920</v>
-      </c>
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="4" t="n"/>
+      <c r="V150" s="4" t="n"/>
       <c r="X150" s="4" t="n"/>
       <c r="Y150" s="4" t="n"/>
       <c r="Z150" s="4" t="n"/>
@@ -8378,19 +6960,9 @@
       </c>
     </row>
     <row r="151">
-      <c r="T151" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V151" s="7" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T151" s="7" t="n"/>
+      <c r="U151" s="7" t="n"/>
+      <c r="V151" s="7" t="n"/>
       <c r="X151" s="7" t="n"/>
       <c r="Y151" s="7" t="n"/>
       <c r="Z151" s="7" t="n"/>
@@ -8409,19 +6981,9 @@
       </c>
     </row>
     <row r="152">
-      <c r="T152" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U152" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="n">
-        <v>10434</v>
-      </c>
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="4" t="n"/>
+      <c r="V152" s="4" t="n"/>
       <c r="X152" s="4" t="n"/>
       <c r="Y152" s="4" t="n"/>
       <c r="Z152" s="4" t="n"/>
@@ -8440,19 +7002,9 @@
       </c>
     </row>
     <row r="153">
-      <c r="T153" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U153" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V153" s="7" t="n">
-        <v>10284</v>
-      </c>
+      <c r="T153" s="7" t="n"/>
+      <c r="U153" s="7" t="n"/>
+      <c r="V153" s="7" t="n"/>
       <c r="X153" s="7" t="n"/>
       <c r="Y153" s="7" t="n"/>
       <c r="Z153" s="7" t="n"/>
@@ -8471,19 +7023,9 @@
       </c>
     </row>
     <row r="154">
-      <c r="T154" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U154" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="n">
-        <v>10458</v>
-      </c>
+      <c r="T154" s="4" t="n"/>
+      <c r="U154" s="4" t="n"/>
+      <c r="V154" s="4" t="n"/>
       <c r="X154" s="4" t="n"/>
       <c r="Y154" s="4" t="n"/>
       <c r="Z154" s="4" t="n"/>
@@ -8502,19 +7044,9 @@
       </c>
     </row>
     <row r="155">
-      <c r="T155" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V155" s="7" t="n">
-        <v>10153</v>
-      </c>
+      <c r="T155" s="7" t="n"/>
+      <c r="U155" s="7" t="n"/>
+      <c r="V155" s="7" t="n"/>
       <c r="X155" s="7" t="n"/>
       <c r="Y155" s="7" t="n"/>
       <c r="Z155" s="7" t="n"/>
@@ -8533,19 +7065,9 @@
       </c>
     </row>
     <row r="156">
-      <c r="T156" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U156" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="n">
-        <v>9843</v>
-      </c>
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="4" t="n"/>
+      <c r="V156" s="4" t="n"/>
       <c r="X156" s="4" t="n"/>
       <c r="Y156" s="4" t="n"/>
       <c r="Z156" s="4" t="n"/>
@@ -8564,19 +7086,9 @@
       </c>
     </row>
     <row r="157">
-      <c r="T157" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U157" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V157" s="7" t="n">
-        <v>10433</v>
-      </c>
+      <c r="T157" s="7" t="n"/>
+      <c r="U157" s="7" t="n"/>
+      <c r="V157" s="7" t="n"/>
       <c r="X157" s="7" t="n"/>
       <c r="Y157" s="7" t="n"/>
       <c r="Z157" s="7" t="n"/>
@@ -8595,19 +7107,9 @@
       </c>
     </row>
     <row r="158">
-      <c r="T158" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U158" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V158" s="4" t="n">
-        <v>10670</v>
-      </c>
+      <c r="T158" s="4" t="n"/>
+      <c r="U158" s="4" t="n"/>
+      <c r="V158" s="4" t="n"/>
       <c r="X158" s="4" t="n"/>
       <c r="Y158" s="4" t="n"/>
       <c r="Z158" s="4" t="n"/>
@@ -8626,19 +7128,9 @@
       </c>
     </row>
     <row r="159">
-      <c r="T159" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U159" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V159" s="7" t="n">
-        <v>10599</v>
-      </c>
+      <c r="T159" s="7" t="n"/>
+      <c r="U159" s="7" t="n"/>
+      <c r="V159" s="7" t="n"/>
       <c r="X159" s="7" t="n"/>
       <c r="Y159" s="7" t="n"/>
       <c r="Z159" s="7" t="n"/>
@@ -8657,19 +7149,9 @@
       </c>
     </row>
     <row r="160">
-      <c r="T160" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U160" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="n">
-        <v>10619</v>
-      </c>
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="4" t="n"/>
+      <c r="V160" s="4" t="n"/>
       <c r="X160" s="4" t="n"/>
       <c r="Y160" s="4" t="n"/>
       <c r="Z160" s="4" t="n"/>
@@ -8688,19 +7170,9 @@
       </c>
     </row>
     <row r="161">
-      <c r="T161" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U161" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V161" s="7" t="n">
-        <v>10415</v>
-      </c>
+      <c r="T161" s="7" t="n"/>
+      <c r="U161" s="7" t="n"/>
+      <c r="V161" s="7" t="n"/>
       <c r="X161" s="7" t="n"/>
       <c r="Y161" s="7" t="n"/>
       <c r="Z161" s="7" t="n"/>
@@ -8719,19 +7191,9 @@
       </c>
     </row>
     <row r="162">
-      <c r="T162" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U162" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation50987</t>
-        </is>
-      </c>
-      <c r="V162" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="4" t="n"/>
+      <c r="V162" s="4" t="n"/>
       <c r="X162" s="4" t="n"/>
       <c r="Y162" s="4" t="n"/>
       <c r="Z162" s="4" t="n"/>
@@ -8750,19 +7212,9 @@
       </c>
     </row>
     <row r="163">
-      <c r="T163" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U163" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation75114</t>
-        </is>
-      </c>
-      <c r="V163" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T163" s="7" t="n"/>
+      <c r="U163" s="7" t="n"/>
+      <c r="V163" s="7" t="n"/>
       <c r="X163" s="7" t="n"/>
       <c r="Y163" s="7" t="n"/>
       <c r="Z163" s="7" t="n"/>
@@ -8781,19 +7233,9 @@
       </c>
     </row>
     <row r="164">
-      <c r="T164" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U164" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V164" s="4" t="n">
-        <v>21493</v>
-      </c>
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="4" t="n"/>
+      <c r="V164" s="4" t="n"/>
       <c r="X164" s="4" t="n"/>
       <c r="Y164" s="4" t="n"/>
       <c r="Z164" s="4" t="n"/>
@@ -8810,1497 +7252,6 @@
           <t>com.logistics.rider.foody</t>
         </is>
       </c>
-    </row>
-    <row r="165">
-      <c r="T165" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U165" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V165" s="7" t="n">
-        <v>21012</v>
-      </c>
-      <c r="X165" s="7" t="n"/>
-      <c r="Y165" s="7" t="n"/>
-      <c r="Z165" s="7" t="n"/>
-      <c r="AB165" s="7" t="n"/>
-      <c r="AC165" s="7" t="n"/>
-      <c r="AD165" s="7" t="n"/>
-    </row>
-    <row r="166">
-      <c r="T166" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U166" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V166" s="4" t="n">
-        <v>21635</v>
-      </c>
-      <c r="X166" s="4" t="n"/>
-      <c r="Y166" s="4" t="n"/>
-      <c r="Z166" s="4" t="n"/>
-      <c r="AB166" s="4" t="n"/>
-      <c r="AC166" s="4" t="n"/>
-      <c r="AD166" s="4" t="n"/>
-    </row>
-    <row r="167">
-      <c r="T167" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U167" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V167" s="7" t="n">
-        <v>21969</v>
-      </c>
-      <c r="X167" s="7" t="n"/>
-      <c r="Y167" s="7" t="n"/>
-      <c r="Z167" s="7" t="n"/>
-      <c r="AB167" s="7" t="n"/>
-      <c r="AC167" s="7" t="n"/>
-      <c r="AD167" s="7" t="n"/>
-    </row>
-    <row r="168">
-      <c r="T168" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U168" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V168" s="4" t="n">
-        <v>21723</v>
-      </c>
-      <c r="X168" s="4" t="n"/>
-      <c r="Y168" s="4" t="n"/>
-      <c r="Z168" s="4" t="n"/>
-      <c r="AB168" s="4" t="n"/>
-      <c r="AC168" s="4" t="n"/>
-      <c r="AD168" s="4" t="n"/>
-    </row>
-    <row r="169">
-      <c r="T169" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U169" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V169" s="7" t="n">
-        <v>20879</v>
-      </c>
-      <c r="X169" s="7" t="n"/>
-      <c r="Y169" s="7" t="n"/>
-      <c r="Z169" s="7" t="n"/>
-      <c r="AB169" s="7" t="n"/>
-      <c r="AC169" s="7" t="n"/>
-      <c r="AD169" s="7" t="n"/>
-    </row>
-    <row r="170">
-      <c r="T170" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U170" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V170" s="4" t="n">
-        <v>20783</v>
-      </c>
-      <c r="X170" s="4" t="n"/>
-      <c r="Y170" s="4" t="n"/>
-      <c r="Z170" s="4" t="n"/>
-      <c r="AB170" s="4" t="n"/>
-      <c r="AC170" s="4" t="n"/>
-      <c r="AD170" s="4" t="n"/>
-    </row>
-    <row r="171">
-      <c r="T171" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U171" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V171" s="7" t="n">
-        <v>21875</v>
-      </c>
-      <c r="X171" s="7" t="n"/>
-      <c r="Y171" s="7" t="n"/>
-      <c r="Z171" s="7" t="n"/>
-      <c r="AB171" s="7" t="n"/>
-      <c r="AC171" s="7" t="n"/>
-      <c r="AD171" s="7" t="n"/>
-    </row>
-    <row r="172">
-      <c r="T172" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U172" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V172" s="4" t="n">
-        <v>22103</v>
-      </c>
-      <c r="X172" s="4" t="n"/>
-      <c r="Y172" s="4" t="n"/>
-      <c r="Z172" s="4" t="n"/>
-      <c r="AB172" s="4" t="n"/>
-      <c r="AC172" s="4" t="n"/>
-      <c r="AD172" s="4" t="n"/>
-    </row>
-    <row r="173">
-      <c r="T173" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U173" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V173" s="7" t="n">
-        <v>22799</v>
-      </c>
-      <c r="X173" s="7" t="n"/>
-      <c r="Y173" s="7" t="n"/>
-      <c r="Z173" s="7" t="n"/>
-      <c r="AB173" s="7" t="n"/>
-      <c r="AC173" s="7" t="n"/>
-      <c r="AD173" s="7" t="n"/>
-    </row>
-    <row r="174">
-      <c r="T174" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U174" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V174" s="4" t="n">
-        <v>22705</v>
-      </c>
-      <c r="X174" s="4" t="n"/>
-      <c r="Y174" s="4" t="n"/>
-      <c r="Z174" s="4" t="n"/>
-      <c r="AB174" s="4" t="n"/>
-      <c r="AC174" s="4" t="n"/>
-      <c r="AD174" s="4" t="n"/>
-    </row>
-    <row r="175">
-      <c r="T175" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U175" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V175" s="7" t="n">
-        <v>21885</v>
-      </c>
-      <c r="X175" s="7" t="n"/>
-      <c r="Y175" s="7" t="n"/>
-      <c r="Z175" s="7" t="n"/>
-      <c r="AB175" s="7" t="n"/>
-      <c r="AC175" s="7" t="n"/>
-      <c r="AD175" s="7" t="n"/>
-    </row>
-    <row r="176">
-      <c r="T176" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U176" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V176" s="4" t="n">
-        <v>21360</v>
-      </c>
-      <c r="X176" s="4" t="n"/>
-      <c r="Y176" s="4" t="n"/>
-      <c r="Z176" s="4" t="n"/>
-      <c r="AB176" s="4" t="n"/>
-      <c r="AC176" s="4" t="n"/>
-      <c r="AD176" s="4" t="n"/>
-    </row>
-    <row r="177">
-      <c r="T177" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U177" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V177" s="7" t="n">
-        <v>20612</v>
-      </c>
-      <c r="X177" s="7" t="n"/>
-      <c r="Y177" s="7" t="n"/>
-      <c r="Z177" s="7" t="n"/>
-      <c r="AB177" s="7" t="n"/>
-      <c r="AC177" s="7" t="n"/>
-      <c r="AD177" s="7" t="n"/>
-    </row>
-    <row r="178">
-      <c r="T178" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U178" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V178" s="4" t="n">
-        <v>22101</v>
-      </c>
-      <c r="X178" s="4" t="n"/>
-      <c r="Y178" s="4" t="n"/>
-      <c r="Z178" s="4" t="n"/>
-      <c r="AB178" s="4" t="n"/>
-      <c r="AC178" s="4" t="n"/>
-      <c r="AD178" s="4" t="n"/>
-    </row>
-    <row r="179">
-      <c r="T179" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U179" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V179" s="7" t="n">
-        <v>22665</v>
-      </c>
-      <c r="X179" s="7" t="n"/>
-      <c r="Y179" s="7" t="n"/>
-      <c r="Z179" s="7" t="n"/>
-      <c r="AB179" s="7" t="n"/>
-      <c r="AC179" s="7" t="n"/>
-      <c r="AD179" s="7" t="n"/>
-    </row>
-    <row r="180">
-      <c r="T180" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U180" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V180" s="4" t="n">
-        <v>22473</v>
-      </c>
-      <c r="X180" s="4" t="n"/>
-      <c r="Y180" s="4" t="n"/>
-      <c r="Z180" s="4" t="n"/>
-      <c r="AB180" s="4" t="n"/>
-      <c r="AC180" s="4" t="n"/>
-      <c r="AD180" s="4" t="n"/>
-    </row>
-    <row r="181">
-      <c r="T181" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U181" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V181" s="7" t="n">
-        <v>22903</v>
-      </c>
-      <c r="X181" s="7" t="n"/>
-      <c r="Y181" s="7" t="n"/>
-      <c r="Z181" s="7" t="n"/>
-      <c r="AB181" s="7" t="n"/>
-      <c r="AC181" s="7" t="n"/>
-      <c r="AD181" s="7" t="n"/>
-    </row>
-    <row r="182">
-      <c r="T182" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U182" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V182" s="4" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X182" s="4" t="n"/>
-      <c r="Y182" s="4" t="n"/>
-      <c r="Z182" s="4" t="n"/>
-      <c r="AB182" s="4" t="n"/>
-      <c r="AC182" s="4" t="n"/>
-      <c r="AD182" s="4" t="n"/>
-    </row>
-    <row r="183">
-      <c r="T183" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U183" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V183" s="7" t="n">
-        <v>16721</v>
-      </c>
-      <c r="X183" s="7" t="n"/>
-      <c r="Y183" s="7" t="n"/>
-      <c r="Z183" s="7" t="n"/>
-      <c r="AB183" s="7" t="n"/>
-      <c r="AC183" s="7" t="n"/>
-      <c r="AD183" s="7" t="n"/>
-    </row>
-    <row r="184">
-      <c r="T184" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U184" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V184" s="4" t="n">
-        <v>16586</v>
-      </c>
-      <c r="X184" s="4" t="n"/>
-      <c r="Y184" s="4" t="n"/>
-      <c r="Z184" s="4" t="n"/>
-      <c r="AB184" s="4" t="n"/>
-      <c r="AC184" s="4" t="n"/>
-      <c r="AD184" s="4" t="n"/>
-    </row>
-    <row r="185">
-      <c r="T185" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U185" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V185" s="7" t="n">
-        <v>16419</v>
-      </c>
-      <c r="X185" s="7" t="n"/>
-      <c r="Y185" s="7" t="n"/>
-      <c r="Z185" s="7" t="n"/>
-      <c r="AB185" s="7" t="n"/>
-      <c r="AC185" s="7" t="n"/>
-      <c r="AD185" s="7" t="n"/>
-    </row>
-    <row r="186">
-      <c r="T186" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U186" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V186" s="4" t="n">
-        <v>15946</v>
-      </c>
-      <c r="X186" s="4" t="n"/>
-      <c r="Y186" s="4" t="n"/>
-      <c r="Z186" s="4" t="n"/>
-      <c r="AB186" s="4" t="n"/>
-      <c r="AC186" s="4" t="n"/>
-      <c r="AD186" s="4" t="n"/>
-    </row>
-    <row r="187">
-      <c r="T187" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U187" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V187" s="7" t="n">
-        <v>16042</v>
-      </c>
-      <c r="X187" s="7" t="n"/>
-      <c r="Y187" s="7" t="n"/>
-      <c r="Z187" s="7" t="n"/>
-      <c r="AB187" s="7" t="n"/>
-      <c r="AC187" s="7" t="n"/>
-      <c r="AD187" s="7" t="n"/>
-    </row>
-    <row r="188">
-      <c r="T188" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U188" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V188" s="4" t="n">
-        <v>16409</v>
-      </c>
-      <c r="X188" s="4" t="n"/>
-      <c r="Y188" s="4" t="n"/>
-      <c r="Z188" s="4" t="n"/>
-      <c r="AB188" s="4" t="n"/>
-      <c r="AC188" s="4" t="n"/>
-      <c r="AD188" s="4" t="n"/>
-    </row>
-    <row r="189">
-      <c r="T189" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U189" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V189" s="7" t="n">
-        <v>16831</v>
-      </c>
-      <c r="X189" s="7" t="n"/>
-      <c r="Y189" s="7" t="n"/>
-      <c r="Z189" s="7" t="n"/>
-      <c r="AB189" s="7" t="n"/>
-      <c r="AC189" s="7" t="n"/>
-      <c r="AD189" s="7" t="n"/>
-    </row>
-    <row r="190">
-      <c r="T190" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U190" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V190" s="4" t="n">
-        <v>16886</v>
-      </c>
-      <c r="X190" s="4" t="n"/>
-      <c r="Y190" s="4" t="n"/>
-      <c r="Z190" s="4" t="n"/>
-      <c r="AB190" s="4" t="n"/>
-      <c r="AC190" s="4" t="n"/>
-      <c r="AD190" s="4" t="n"/>
-    </row>
-    <row r="191">
-      <c r="T191" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U191" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V191" s="7" t="n">
-        <v>16694</v>
-      </c>
-      <c r="X191" s="7" t="n"/>
-      <c r="Y191" s="7" t="n"/>
-      <c r="Z191" s="7" t="n"/>
-      <c r="AB191" s="7" t="n"/>
-      <c r="AC191" s="7" t="n"/>
-      <c r="AD191" s="7" t="n"/>
-    </row>
-    <row r="192">
-      <c r="T192" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U192" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V192" s="4" t="n">
-        <v>16659</v>
-      </c>
-      <c r="X192" s="4" t="n"/>
-      <c r="Y192" s="4" t="n"/>
-      <c r="Z192" s="4" t="n"/>
-      <c r="AB192" s="4" t="n"/>
-      <c r="AC192" s="4" t="n"/>
-      <c r="AD192" s="4" t="n"/>
-    </row>
-    <row r="193">
-      <c r="T193" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U193" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V193" s="7" t="n">
-        <v>16268</v>
-      </c>
-      <c r="X193" s="7" t="n"/>
-      <c r="Y193" s="7" t="n"/>
-      <c r="Z193" s="7" t="n"/>
-      <c r="AB193" s="7" t="n"/>
-      <c r="AC193" s="7" t="n"/>
-      <c r="AD193" s="7" t="n"/>
-    </row>
-    <row r="194">
-      <c r="T194" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U194" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V194" s="4" t="n">
-        <v>16259</v>
-      </c>
-      <c r="X194" s="4" t="n"/>
-      <c r="Y194" s="4" t="n"/>
-      <c r="Z194" s="4" t="n"/>
-      <c r="AB194" s="4" t="n"/>
-      <c r="AC194" s="4" t="n"/>
-      <c r="AD194" s="4" t="n"/>
-    </row>
-    <row r="195">
-      <c r="T195" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U195" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V195" s="7" t="n">
-        <v>16600</v>
-      </c>
-      <c r="X195" s="7" t="n"/>
-      <c r="Y195" s="7" t="n"/>
-      <c r="Z195" s="7" t="n"/>
-      <c r="AB195" s="7" t="n"/>
-      <c r="AC195" s="7" t="n"/>
-      <c r="AD195" s="7" t="n"/>
-    </row>
-    <row r="196">
-      <c r="T196" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U196" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V196" s="4" t="n">
-        <v>16913</v>
-      </c>
-      <c r="X196" s="4" t="n"/>
-      <c r="Y196" s="4" t="n"/>
-      <c r="Z196" s="4" t="n"/>
-      <c r="AB196" s="4" t="n"/>
-      <c r="AC196" s="4" t="n"/>
-      <c r="AD196" s="4" t="n"/>
-    </row>
-    <row r="197">
-      <c r="T197" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U197" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V197" s="7" t="n">
-        <v>16991</v>
-      </c>
-      <c r="X197" s="7" t="n"/>
-      <c r="Y197" s="7" t="n"/>
-      <c r="Z197" s="7" t="n"/>
-      <c r="AB197" s="7" t="n"/>
-      <c r="AC197" s="7" t="n"/>
-      <c r="AD197" s="7" t="n"/>
-    </row>
-    <row r="198">
-      <c r="T198" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U198" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V198" s="4" t="n">
-        <v>17365</v>
-      </c>
-      <c r="X198" s="4" t="n"/>
-      <c r="Y198" s="4" t="n"/>
-      <c r="Z198" s="4" t="n"/>
-      <c r="AB198" s="4" t="n"/>
-      <c r="AC198" s="4" t="n"/>
-      <c r="AD198" s="4" t="n"/>
-    </row>
-    <row r="199">
-      <c r="T199" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U199" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V199" s="7" t="n">
-        <v>16944</v>
-      </c>
-      <c r="X199" s="7" t="n"/>
-      <c r="Y199" s="7" t="n"/>
-      <c r="Z199" s="7" t="n"/>
-      <c r="AB199" s="7" t="n"/>
-      <c r="AC199" s="7" t="n"/>
-      <c r="AD199" s="7" t="n"/>
-    </row>
-    <row r="200">
-      <c r="T200" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U200" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V200" s="4" t="n">
-        <v>724</v>
-      </c>
-      <c r="X200" s="4" t="n"/>
-      <c r="Y200" s="4" t="n"/>
-      <c r="Z200" s="4" t="n"/>
-      <c r="AB200" s="4" t="n"/>
-      <c r="AC200" s="4" t="n"/>
-      <c r="AD200" s="4" t="n"/>
-    </row>
-    <row r="201">
-      <c r="T201" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U201" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V201" s="7" t="n">
-        <v>746</v>
-      </c>
-      <c r="X201" s="7" t="n"/>
-      <c r="Y201" s="7" t="n"/>
-      <c r="Z201" s="7" t="n"/>
-      <c r="AB201" s="7" t="n"/>
-      <c r="AC201" s="7" t="n"/>
-      <c r="AD201" s="7" t="n"/>
-    </row>
-    <row r="202">
-      <c r="T202" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U202" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V202" s="4" t="n">
-        <v>723</v>
-      </c>
-      <c r="X202" s="4" t="n"/>
-      <c r="Y202" s="4" t="n"/>
-      <c r="Z202" s="4" t="n"/>
-      <c r="AB202" s="4" t="n"/>
-      <c r="AC202" s="4" t="n"/>
-      <c r="AD202" s="4" t="n"/>
-    </row>
-    <row r="203">
-      <c r="T203" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U203" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V203" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="X203" s="7" t="n"/>
-      <c r="Y203" s="7" t="n"/>
-      <c r="Z203" s="7" t="n"/>
-      <c r="AB203" s="7" t="n"/>
-      <c r="AC203" s="7" t="n"/>
-      <c r="AD203" s="7" t="n"/>
-    </row>
-    <row r="204">
-      <c r="T204" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U204" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V204" s="4" t="n">
-        <v>735</v>
-      </c>
-      <c r="X204" s="4" t="n"/>
-      <c r="Y204" s="4" t="n"/>
-      <c r="Z204" s="4" t="n"/>
-      <c r="AB204" s="4" t="n"/>
-      <c r="AC204" s="4" t="n"/>
-      <c r="AD204" s="4" t="n"/>
-    </row>
-    <row r="205">
-      <c r="T205" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U205" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V205" s="7" t="n">
-        <v>714</v>
-      </c>
-      <c r="X205" s="7" t="n"/>
-      <c r="Y205" s="7" t="n"/>
-      <c r="Z205" s="7" t="n"/>
-      <c r="AB205" s="7" t="n"/>
-      <c r="AC205" s="7" t="n"/>
-      <c r="AD205" s="7" t="n"/>
-    </row>
-    <row r="206">
-      <c r="T206" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U206" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V206" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X206" s="4" t="n"/>
-      <c r="Y206" s="4" t="n"/>
-      <c r="Z206" s="4" t="n"/>
-      <c r="AB206" s="4" t="n"/>
-      <c r="AC206" s="4" t="n"/>
-      <c r="AD206" s="4" t="n"/>
-    </row>
-    <row r="207">
-      <c r="T207" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U207" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V207" s="7" t="n">
-        <v>729</v>
-      </c>
-      <c r="X207" s="7" t="n"/>
-      <c r="Y207" s="7" t="n"/>
-      <c r="Z207" s="7" t="n"/>
-      <c r="AB207" s="7" t="n"/>
-      <c r="AC207" s="7" t="n"/>
-      <c r="AD207" s="7" t="n"/>
-    </row>
-    <row r="208">
-      <c r="T208" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U208" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V208" s="4" t="n">
-        <v>719</v>
-      </c>
-      <c r="X208" s="4" t="n"/>
-      <c r="Y208" s="4" t="n"/>
-      <c r="Z208" s="4" t="n"/>
-      <c r="AB208" s="4" t="n"/>
-      <c r="AC208" s="4" t="n"/>
-      <c r="AD208" s="4" t="n"/>
-    </row>
-    <row r="209">
-      <c r="T209" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U209" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V209" s="7" t="n">
-        <v>719</v>
-      </c>
-      <c r="X209" s="7" t="n"/>
-      <c r="Y209" s="7" t="n"/>
-      <c r="Z209" s="7" t="n"/>
-      <c r="AB209" s="7" t="n"/>
-      <c r="AC209" s="7" t="n"/>
-      <c r="AD209" s="7" t="n"/>
-    </row>
-    <row r="210">
-      <c r="T210" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U210" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V210" s="4" t="n">
-        <v>730</v>
-      </c>
-      <c r="X210" s="4" t="n"/>
-      <c r="Y210" s="4" t="n"/>
-      <c r="Z210" s="4" t="n"/>
-      <c r="AB210" s="4" t="n"/>
-      <c r="AC210" s="4" t="n"/>
-      <c r="AD210" s="4" t="n"/>
-    </row>
-    <row r="211">
-      <c r="T211" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U211" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V211" s="7" t="n">
-        <v>740</v>
-      </c>
-      <c r="X211" s="7" t="n"/>
-      <c r="Y211" s="7" t="n"/>
-      <c r="Z211" s="7" t="n"/>
-      <c r="AB211" s="7" t="n"/>
-      <c r="AC211" s="7" t="n"/>
-      <c r="AD211" s="7" t="n"/>
-    </row>
-    <row r="212">
-      <c r="T212" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U212" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V212" s="4" t="n">
-        <v>708</v>
-      </c>
-      <c r="X212" s="4" t="n"/>
-      <c r="Y212" s="4" t="n"/>
-      <c r="Z212" s="4" t="n"/>
-      <c r="AB212" s="4" t="n"/>
-      <c r="AC212" s="4" t="n"/>
-      <c r="AD212" s="4" t="n"/>
-    </row>
-    <row r="213">
-      <c r="T213" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U213" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V213" s="7" t="n">
-        <v>698</v>
-      </c>
-      <c r="X213" s="7" t="n"/>
-      <c r="Y213" s="7" t="n"/>
-      <c r="Z213" s="7" t="n"/>
-      <c r="AB213" s="7" t="n"/>
-      <c r="AC213" s="7" t="n"/>
-      <c r="AD213" s="7" t="n"/>
-    </row>
-    <row r="214">
-      <c r="T214" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U214" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V214" s="4" t="n">
-        <v>691</v>
-      </c>
-      <c r="X214" s="4" t="n"/>
-      <c r="Y214" s="4" t="n"/>
-      <c r="Z214" s="4" t="n"/>
-      <c r="AB214" s="4" t="n"/>
-      <c r="AC214" s="4" t="n"/>
-      <c r="AD214" s="4" t="n"/>
-    </row>
-    <row r="215">
-      <c r="T215" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U215" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V215" s="7" t="n">
-        <v>695</v>
-      </c>
-      <c r="X215" s="7" t="n"/>
-      <c r="Y215" s="7" t="n"/>
-      <c r="Z215" s="7" t="n"/>
-      <c r="AB215" s="7" t="n"/>
-      <c r="AC215" s="7" t="n"/>
-      <c r="AD215" s="7" t="n"/>
-    </row>
-    <row r="216">
-      <c r="T216" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U216" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V216" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X216" s="4" t="n"/>
-      <c r="Y216" s="4" t="n"/>
-      <c r="Z216" s="4" t="n"/>
-      <c r="AB216" s="4" t="n"/>
-      <c r="AC216" s="4" t="n"/>
-      <c r="AD216" s="4" t="n"/>
-    </row>
-    <row r="217">
-      <c r="T217" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U217" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V217" s="7" t="n">
-        <v>701</v>
-      </c>
-      <c r="X217" s="7" t="n"/>
-      <c r="Y217" s="7" t="n"/>
-      <c r="Z217" s="7" t="n"/>
-      <c r="AB217" s="7" t="n"/>
-      <c r="AC217" s="7" t="n"/>
-      <c r="AD217" s="7" t="n"/>
-    </row>
-    <row r="218">
-      <c r="T218" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U218" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V218" s="4" t="n">
-        <v>2188</v>
-      </c>
-      <c r="X218" s="4" t="n"/>
-      <c r="Y218" s="4" t="n"/>
-      <c r="Z218" s="4" t="n"/>
-      <c r="AB218" s="4" t="n"/>
-      <c r="AC218" s="4" t="n"/>
-      <c r="AD218" s="4" t="n"/>
-    </row>
-    <row r="219">
-      <c r="T219" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U219" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V219" s="7" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X219" s="7" t="n"/>
-      <c r="Y219" s="7" t="n"/>
-      <c r="Z219" s="7" t="n"/>
-      <c r="AB219" s="7" t="n"/>
-      <c r="AC219" s="7" t="n"/>
-      <c r="AD219" s="7" t="n"/>
-    </row>
-    <row r="220">
-      <c r="T220" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U220" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V220" s="4" t="n">
-        <v>2338</v>
-      </c>
-      <c r="X220" s="4" t="n"/>
-      <c r="Y220" s="4" t="n"/>
-      <c r="Z220" s="4" t="n"/>
-      <c r="AB220" s="4" t="n"/>
-      <c r="AC220" s="4" t="n"/>
-      <c r="AD220" s="4" t="n"/>
-    </row>
-    <row r="221">
-      <c r="T221" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U221" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V221" s="7" t="n">
-        <v>2152</v>
-      </c>
-      <c r="X221" s="7" t="n"/>
-      <c r="Y221" s="7" t="n"/>
-      <c r="Z221" s="7" t="n"/>
-      <c r="AB221" s="7" t="n"/>
-      <c r="AC221" s="7" t="n"/>
-      <c r="AD221" s="7" t="n"/>
-    </row>
-    <row r="222">
-      <c r="T222" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U222" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V222" s="4" t="n">
-        <v>2003</v>
-      </c>
-      <c r="X222" s="4" t="n"/>
-      <c r="Y222" s="4" t="n"/>
-      <c r="Z222" s="4" t="n"/>
-      <c r="AB222" s="4" t="n"/>
-      <c r="AC222" s="4" t="n"/>
-      <c r="AD222" s="4" t="n"/>
-    </row>
-    <row r="223">
-      <c r="T223" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U223" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V223" s="7" t="n">
-        <v>1895</v>
-      </c>
-      <c r="X223" s="7" t="n"/>
-      <c r="Y223" s="7" t="n"/>
-      <c r="Z223" s="7" t="n"/>
-      <c r="AB223" s="7" t="n"/>
-      <c r="AC223" s="7" t="n"/>
-      <c r="AD223" s="7" t="n"/>
-    </row>
-    <row r="224">
-      <c r="T224" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U224" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V224" s="4" t="n">
-        <v>1935</v>
-      </c>
-      <c r="X224" s="4" t="n"/>
-      <c r="Y224" s="4" t="n"/>
-      <c r="Z224" s="4" t="n"/>
-      <c r="AB224" s="4" t="n"/>
-      <c r="AC224" s="4" t="n"/>
-      <c r="AD224" s="4" t="n"/>
-    </row>
-    <row r="225">
-      <c r="T225" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U225" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V225" s="7" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X225" s="7" t="n"/>
-      <c r="Y225" s="7" t="n"/>
-      <c r="Z225" s="7" t="n"/>
-      <c r="AB225" s="7" t="n"/>
-      <c r="AC225" s="7" t="n"/>
-      <c r="AD225" s="7" t="n"/>
-    </row>
-    <row r="226">
-      <c r="T226" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U226" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V226" s="4" t="n">
-        <v>2049</v>
-      </c>
-      <c r="X226" s="4" t="n"/>
-      <c r="Y226" s="4" t="n"/>
-      <c r="Z226" s="4" t="n"/>
-      <c r="AB226" s="4" t="n"/>
-      <c r="AC226" s="4" t="n"/>
-      <c r="AD226" s="4" t="n"/>
-    </row>
-    <row r="227">
-      <c r="T227" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U227" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V227" s="7" t="n">
-        <v>2325</v>
-      </c>
-      <c r="X227" s="7" t="n"/>
-      <c r="Y227" s="7" t="n"/>
-      <c r="Z227" s="7" t="n"/>
-      <c r="AB227" s="7" t="n"/>
-      <c r="AC227" s="7" t="n"/>
-      <c r="AD227" s="7" t="n"/>
-    </row>
-    <row r="228">
-      <c r="T228" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U228" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V228" s="4" t="n">
-        <v>2216</v>
-      </c>
-      <c r="X228" s="4" t="n"/>
-      <c r="Y228" s="4" t="n"/>
-      <c r="Z228" s="4" t="n"/>
-      <c r="AB228" s="4" t="n"/>
-      <c r="AC228" s="4" t="n"/>
-      <c r="AD228" s="4" t="n"/>
-    </row>
-    <row r="229">
-      <c r="T229" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U229" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V229" s="7" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X229" s="7" t="n"/>
-      <c r="Y229" s="7" t="n"/>
-      <c r="Z229" s="7" t="n"/>
-      <c r="AB229" s="7" t="n"/>
-      <c r="AC229" s="7" t="n"/>
-      <c r="AD229" s="7" t="n"/>
-    </row>
-    <row r="230">
-      <c r="T230" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U230" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V230" s="4" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X230" s="4" t="n"/>
-      <c r="Y230" s="4" t="n"/>
-      <c r="Z230" s="4" t="n"/>
-      <c r="AB230" s="4" t="n"/>
-      <c r="AC230" s="4" t="n"/>
-      <c r="AD230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="T231" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U231" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V231" s="7" t="n">
-        <v>2035</v>
-      </c>
-      <c r="X231" s="7" t="n"/>
-      <c r="Y231" s="7" t="n"/>
-      <c r="Z231" s="7" t="n"/>
-      <c r="AB231" s="7" t="n"/>
-      <c r="AC231" s="7" t="n"/>
-      <c r="AD231" s="7" t="n"/>
-    </row>
-    <row r="232">
-      <c r="T232" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U232" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V232" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="X232" s="4" t="n"/>
-      <c r="Y232" s="4" t="n"/>
-      <c r="Z232" s="4" t="n"/>
-      <c r="AB232" s="4" t="n"/>
-      <c r="AC232" s="4" t="n"/>
-      <c r="AD232" s="4" t="n"/>
-    </row>
-    <row r="233">
-      <c r="T233" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U233" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V233" s="7" t="n">
-        <v>2156</v>
-      </c>
-      <c r="X233" s="7" t="n"/>
-      <c r="Y233" s="7" t="n"/>
-      <c r="Z233" s="7" t="n"/>
-      <c r="AB233" s="7" t="n"/>
-      <c r="AC233" s="7" t="n"/>
-      <c r="AD233" s="7" t="n"/>
-    </row>
-    <row r="234">
-      <c r="T234" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U234" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V234" s="4" t="n">
-        <v>2437</v>
-      </c>
-      <c r="X234" s="4" t="n"/>
-      <c r="Y234" s="4" t="n"/>
-      <c r="Z234" s="4" t="n"/>
-      <c r="AB234" s="4" t="n"/>
-      <c r="AC234" s="4" t="n"/>
-      <c r="AD234" s="4" t="n"/>
-    </row>
-    <row r="235">
-      <c r="T235" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U235" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V235" s="7" t="n">
-        <v>2214</v>
-      </c>
-      <c r="X235" s="7" t="n"/>
-      <c r="Y235" s="7" t="n"/>
-      <c r="Z235" s="7" t="n"/>
-      <c r="AB235" s="7" t="n"/>
-      <c r="AC235" s="7" t="n"/>
-      <c r="AD235" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD164"/>
+  <dimension ref="A1:AD172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2661,17 +2661,41 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
+      <c r="D20" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C20)</f>
+        <v/>
+      </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
+      <c r="G20" s="4">
+        <f>ROUND((1-E20/D20)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>MIN(1,(G20-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
+      <c r="K20" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>ROUND(100*(1-K20/D20),2)</f>
+        <v/>
+      </c>
+      <c r="M20" s="4">
+        <f>MAX(0,(L20-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>$B$2+H20+M20</f>
+        <v/>
+      </c>
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
@@ -3301,7 +3325,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D19)</f>
+        <f>AVERAGE(D2:D20)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3311,7 +3335,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H19)</f>
+        <f>AVERAGE(H2:H20)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -6900,9 +6924,19 @@
       <c r="T148" s="4" t="n"/>
       <c r="U148" s="4" t="n"/>
       <c r="V148" s="4" t="n"/>
-      <c r="X148" s="4" t="n"/>
-      <c r="Y148" s="4" t="n"/>
-      <c r="Z148" s="4" t="n"/>
+      <c r="X148" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y148" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z148" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB148" s="4" t="n">
         <v>33</v>
       </c>
@@ -6921,9 +6955,19 @@
       <c r="T149" s="7" t="n"/>
       <c r="U149" s="7" t="n"/>
       <c r="V149" s="7" t="n"/>
-      <c r="X149" s="7" t="n"/>
-      <c r="Y149" s="7" t="n"/>
-      <c r="Z149" s="7" t="n"/>
+      <c r="X149" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y149" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z149" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB149" s="7" t="n">
         <v>140</v>
       </c>
@@ -6942,9 +6986,19 @@
       <c r="T150" s="4" t="n"/>
       <c r="U150" s="4" t="n"/>
       <c r="V150" s="4" t="n"/>
-      <c r="X150" s="4" t="n"/>
-      <c r="Y150" s="4" t="n"/>
-      <c r="Z150" s="4" t="n"/>
+      <c r="X150" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y150" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z150" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB150" s="4" t="n">
         <v>47</v>
       </c>
@@ -6963,9 +7017,19 @@
       <c r="T151" s="7" t="n"/>
       <c r="U151" s="7" t="n"/>
       <c r="V151" s="7" t="n"/>
-      <c r="X151" s="7" t="n"/>
-      <c r="Y151" s="7" t="n"/>
-      <c r="Z151" s="7" t="n"/>
+      <c r="X151" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y151" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z151" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB151" s="7" t="n">
         <v>42</v>
       </c>
@@ -6984,9 +7048,19 @@
       <c r="T152" s="4" t="n"/>
       <c r="U152" s="4" t="n"/>
       <c r="V152" s="4" t="n"/>
-      <c r="X152" s="4" t="n"/>
-      <c r="Y152" s="4" t="n"/>
-      <c r="Z152" s="4" t="n"/>
+      <c r="X152" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y152" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z152" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB152" s="4" t="n">
         <v>128</v>
       </c>
@@ -7005,9 +7079,19 @@
       <c r="T153" s="7" t="n"/>
       <c r="U153" s="7" t="n"/>
       <c r="V153" s="7" t="n"/>
-      <c r="X153" s="7" t="n"/>
-      <c r="Y153" s="7" t="n"/>
-      <c r="Z153" s="7" t="n"/>
+      <c r="X153" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y153" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z153" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB153" s="7" t="n">
         <v>5</v>
       </c>
@@ -7026,9 +7110,19 @@
       <c r="T154" s="4" t="n"/>
       <c r="U154" s="4" t="n"/>
       <c r="V154" s="4" t="n"/>
-      <c r="X154" s="4" t="n"/>
-      <c r="Y154" s="4" t="n"/>
-      <c r="Z154" s="4" t="n"/>
+      <c r="X154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y154" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z154" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB154" s="4" t="n">
         <v>5</v>
       </c>
@@ -7047,9 +7141,19 @@
       <c r="T155" s="7" t="n"/>
       <c r="U155" s="7" t="n"/>
       <c r="V155" s="7" t="n"/>
-      <c r="X155" s="7" t="n"/>
-      <c r="Y155" s="7" t="n"/>
-      <c r="Z155" s="7" t="n"/>
+      <c r="X155" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y155" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z155" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB155" s="7" t="n">
         <v>2</v>
       </c>
@@ -7068,9 +7172,19 @@
       <c r="T156" s="4" t="n"/>
       <c r="U156" s="4" t="n"/>
       <c r="V156" s="4" t="n"/>
-      <c r="X156" s="4" t="n"/>
-      <c r="Y156" s="4" t="n"/>
-      <c r="Z156" s="4" t="n"/>
+      <c r="X156" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y156" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z156" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB156" s="4" t="n">
         <v>325</v>
       </c>
@@ -7253,6 +7367,174 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="T165" s="7" t="n"/>
+      <c r="U165" s="7" t="n"/>
+      <c r="V165" s="7" t="n"/>
+      <c r="X165" s="7" t="n"/>
+      <c r="Y165" s="7" t="n"/>
+      <c r="Z165" s="7" t="n"/>
+      <c r="AB165" s="7" t="n">
+        <v>380</v>
+      </c>
+      <c r="AC165" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD165" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="4" t="n"/>
+      <c r="V166" s="4" t="n"/>
+      <c r="X166" s="4" t="n"/>
+      <c r="Y166" s="4" t="n"/>
+      <c r="Z166" s="4" t="n"/>
+      <c r="AB166" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC166" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD166" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="T167" s="7" t="n"/>
+      <c r="U167" s="7" t="n"/>
+      <c r="V167" s="7" t="n"/>
+      <c r="X167" s="7" t="n"/>
+      <c r="Y167" s="7" t="n"/>
+      <c r="Z167" s="7" t="n"/>
+      <c r="AB167" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC167" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD167" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="4" t="n"/>
+      <c r="V168" s="4" t="n"/>
+      <c r="X168" s="4" t="n"/>
+      <c r="Y168" s="4" t="n"/>
+      <c r="Z168" s="4" t="n"/>
+      <c r="AB168" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AC168" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD168" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="T169" s="7" t="n"/>
+      <c r="U169" s="7" t="n"/>
+      <c r="V169" s="7" t="n"/>
+      <c r="X169" s="7" t="n"/>
+      <c r="Y169" s="7" t="n"/>
+      <c r="Z169" s="7" t="n"/>
+      <c r="AB169" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC169" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD169" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="4" t="n"/>
+      <c r="V170" s="4" t="n"/>
+      <c r="X170" s="4" t="n"/>
+      <c r="Y170" s="4" t="n"/>
+      <c r="Z170" s="4" t="n"/>
+      <c r="AB170" s="4" t="n">
+        <v>154</v>
+      </c>
+      <c r="AC170" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD170" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="T171" s="7" t="n"/>
+      <c r="U171" s="7" t="n"/>
+      <c r="V171" s="7" t="n"/>
+      <c r="X171" s="7" t="n"/>
+      <c r="Y171" s="7" t="n"/>
+      <c r="Z171" s="7" t="n"/>
+      <c r="AB171" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC171" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD171" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="4" t="n"/>
+      <c r="V172" s="4" t="n"/>
+      <c r="X172" s="4" t="n"/>
+      <c r="Y172" s="4" t="n"/>
+      <c r="Z172" s="4" t="n"/>
+      <c r="AB172" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC172" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD172" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD172"/>
+  <dimension ref="A1:AD181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2734,17 +2734,41 @@
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="D21" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C21)</f>
+        <v/>
+      </c>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="G21" s="7">
+        <f>ROUND((1-E21/D21)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H21" s="7">
+        <f>MIN(1,(G21-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
+      <c r="K21" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="7">
+        <f>ROUND(100*(1-K21/D21),2)</f>
+        <v/>
+      </c>
+      <c r="M21" s="7">
+        <f>MAX(0,(L21-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N21" s="7">
+        <f>$B$2+H21+M21</f>
+        <v/>
+      </c>
       <c r="T21" s="7" t="n"/>
       <c r="U21" s="7" t="n"/>
       <c r="V21" s="7" t="n"/>
@@ -3325,7 +3349,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D20)</f>
+        <f>AVERAGE(D2:D21)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3335,7 +3359,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H20)</f>
+        <f>AVERAGE(H2:H21)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -7018,7 +7042,7 @@
       <c r="U151" s="7" t="n"/>
       <c r="V151" s="7" t="n"/>
       <c r="X151" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y151" s="7" t="inlineStr">
         <is>
@@ -7203,9 +7227,19 @@
       <c r="T157" s="7" t="n"/>
       <c r="U157" s="7" t="n"/>
       <c r="V157" s="7" t="n"/>
-      <c r="X157" s="7" t="n"/>
-      <c r="Y157" s="7" t="n"/>
-      <c r="Z157" s="7" t="n"/>
+      <c r="X157" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y157" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z157" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB157" s="7" t="n">
         <v>30</v>
       </c>
@@ -7224,9 +7258,19 @@
       <c r="T158" s="4" t="n"/>
       <c r="U158" s="4" t="n"/>
       <c r="V158" s="4" t="n"/>
-      <c r="X158" s="4" t="n"/>
-      <c r="Y158" s="4" t="n"/>
-      <c r="Z158" s="4" t="n"/>
+      <c r="X158" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y158" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z158" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB158" s="4" t="n">
         <v>150</v>
       </c>
@@ -7245,9 +7289,19 @@
       <c r="T159" s="7" t="n"/>
       <c r="U159" s="7" t="n"/>
       <c r="V159" s="7" t="n"/>
-      <c r="X159" s="7" t="n"/>
-      <c r="Y159" s="7" t="n"/>
-      <c r="Z159" s="7" t="n"/>
+      <c r="X159" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y159" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z159" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB159" s="7" t="n">
         <v>46</v>
       </c>
@@ -7266,9 +7320,19 @@
       <c r="T160" s="4" t="n"/>
       <c r="U160" s="4" t="n"/>
       <c r="V160" s="4" t="n"/>
-      <c r="X160" s="4" t="n"/>
-      <c r="Y160" s="4" t="n"/>
-      <c r="Z160" s="4" t="n"/>
+      <c r="X160" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y160" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z160" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB160" s="4" t="n">
         <v>46</v>
       </c>
@@ -7287,9 +7351,19 @@
       <c r="T161" s="7" t="n"/>
       <c r="U161" s="7" t="n"/>
       <c r="V161" s="7" t="n"/>
-      <c r="X161" s="7" t="n"/>
-      <c r="Y161" s="7" t="n"/>
-      <c r="Z161" s="7" t="n"/>
+      <c r="X161" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y161" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z161" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB161" s="7" t="n">
         <v>110</v>
       </c>
@@ -7308,9 +7382,19 @@
       <c r="T162" s="4" t="n"/>
       <c r="U162" s="4" t="n"/>
       <c r="V162" s="4" t="n"/>
-      <c r="X162" s="4" t="n"/>
-      <c r="Y162" s="4" t="n"/>
-      <c r="Z162" s="4" t="n"/>
+      <c r="X162" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="Y162" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z162" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB162" s="4" t="n">
         <v>2</v>
       </c>
@@ -7329,9 +7413,19 @@
       <c r="T163" s="7" t="n"/>
       <c r="U163" s="7" t="n"/>
       <c r="V163" s="7" t="n"/>
-      <c r="X163" s="7" t="n"/>
-      <c r="Y163" s="7" t="n"/>
-      <c r="Z163" s="7" t="n"/>
+      <c r="X163" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y163" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z163" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB163" s="7" t="n">
         <v>5</v>
       </c>
@@ -7350,9 +7444,19 @@
       <c r="T164" s="4" t="n"/>
       <c r="U164" s="4" t="n"/>
       <c r="V164" s="4" t="n"/>
-      <c r="X164" s="4" t="n"/>
-      <c r="Y164" s="4" t="n"/>
-      <c r="Z164" s="4" t="n"/>
+      <c r="X164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y164" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z164" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB164" s="4" t="n">
         <v>2</v>
       </c>
@@ -7535,6 +7639,195 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="T173" s="7" t="n"/>
+      <c r="U173" s="7" t="n"/>
+      <c r="V173" s="7" t="n"/>
+      <c r="X173" s="7" t="n"/>
+      <c r="Y173" s="7" t="n"/>
+      <c r="Z173" s="7" t="n"/>
+      <c r="AB173" s="7" t="n">
+        <v>367</v>
+      </c>
+      <c r="AC173" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD173" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="n"/>
+      <c r="V174" s="4" t="n"/>
+      <c r="X174" s="4" t="n"/>
+      <c r="Y174" s="4" t="n"/>
+      <c r="Z174" s="4" t="n"/>
+      <c r="AB174" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC174" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD174" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="T175" s="7" t="n"/>
+      <c r="U175" s="7" t="n"/>
+      <c r="V175" s="7" t="n"/>
+      <c r="X175" s="7" t="n"/>
+      <c r="Y175" s="7" t="n"/>
+      <c r="Z175" s="7" t="n"/>
+      <c r="AB175" s="7" t="n">
+        <v>166</v>
+      </c>
+      <c r="AC175" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD175" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="4" t="n"/>
+      <c r="V176" s="4" t="n"/>
+      <c r="X176" s="4" t="n"/>
+      <c r="Y176" s="4" t="n"/>
+      <c r="Z176" s="4" t="n"/>
+      <c r="AB176" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC176" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD176" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="T177" s="7" t="n"/>
+      <c r="U177" s="7" t="n"/>
+      <c r="V177" s="7" t="n"/>
+      <c r="X177" s="7" t="n"/>
+      <c r="Y177" s="7" t="n"/>
+      <c r="Z177" s="7" t="n"/>
+      <c r="AB177" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC177" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD177" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="T178" s="4" t="n"/>
+      <c r="U178" s="4" t="n"/>
+      <c r="V178" s="4" t="n"/>
+      <c r="X178" s="4" t="n"/>
+      <c r="Y178" s="4" t="n"/>
+      <c r="Z178" s="4" t="n"/>
+      <c r="AB178" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="AC178" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD178" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="T179" s="7" t="n"/>
+      <c r="U179" s="7" t="n"/>
+      <c r="V179" s="7" t="n"/>
+      <c r="X179" s="7" t="n"/>
+      <c r="Y179" s="7" t="n"/>
+      <c r="Z179" s="7" t="n"/>
+      <c r="AB179" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC179" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD179" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="T180" s="4" t="n"/>
+      <c r="U180" s="4" t="n"/>
+      <c r="V180" s="4" t="n"/>
+      <c r="X180" s="4" t="n"/>
+      <c r="Y180" s="4" t="n"/>
+      <c r="Z180" s="4" t="n"/>
+      <c r="AB180" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC180" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD180" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="T181" s="7" t="n"/>
+      <c r="U181" s="7" t="n"/>
+      <c r="V181" s="7" t="n"/>
+      <c r="X181" s="7" t="n"/>
+      <c r="Y181" s="7" t="n"/>
+      <c r="Z181" s="7" t="n"/>
+      <c r="AB181" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC181" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD181" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD235"/>
+  <dimension ref="A1:AD261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2769,29 +2769,49 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
+      <c r="D20" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C20)</f>
+        <v/>
+      </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
+      <c r="G20" s="4">
+        <f>ROUND((1-E20/D20)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>MIN(1,(G20-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
+      <c r="K20" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>ROUND(100*(1-K20/D20),2)</f>
+        <v/>
+      </c>
+      <c r="M20" s="4">
+        <f>MAX(0,(L20-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>$B$2+H20+M20</f>
+        <v/>
+      </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr"/>
       <c r="V20" s="4" t="n">
-        <v>5365</v>
+        <v>1</v>
       </c>
       <c r="X20" s="4" t="n">
         <v>74</v>
@@ -2828,29 +2848,49 @@
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="D21" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C21)</f>
+        <v/>
+      </c>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="G21" s="7">
+        <f>ROUND((1-E21/D21)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H21" s="7">
+        <f>MIN(1,(G21-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
+      <c r="K21" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="7">
+        <f>ROUND(100*(1-K21/D21),2)</f>
+        <v/>
+      </c>
+      <c r="M21" s="7">
+        <f>MAX(0,(L21-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N21" s="7">
+        <f>$B$2+H21+M21</f>
+        <v/>
+      </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr"/>
       <c r="V21" s="7" t="n">
-        <v>5741</v>
+        <v>1</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>26</v>
@@ -2900,7 +2940,7 @@
       <c r="N22" s="4" t="n"/>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
@@ -2909,7 +2949,7 @@
         </is>
       </c>
       <c r="V22" s="4" t="n">
-        <v>5451</v>
+        <v>5365</v>
       </c>
       <c r="X22" s="4" t="n">
         <v>9</v>
@@ -2959,7 +2999,7 @@
       <c r="N23" s="7" t="n"/>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
@@ -2968,7 +3008,7 @@
         </is>
       </c>
       <c r="V23" s="7" t="n">
-        <v>5458</v>
+        <v>5741</v>
       </c>
       <c r="X23" s="7" t="n">
         <v>74</v>
@@ -3018,7 +3058,7 @@
       <c r="N24" s="4" t="n"/>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
@@ -3027,7 +3067,7 @@
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>5664</v>
+        <v>5451</v>
       </c>
       <c r="X24" s="4" t="n">
         <v>11</v>
@@ -3077,7 +3117,7 @@
       <c r="N25" s="7" t="n"/>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -3086,7 +3126,7 @@
         </is>
       </c>
       <c r="V25" s="7" t="n">
-        <v>5241</v>
+        <v>5458</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>101</v>
@@ -3136,7 +3176,7 @@
       <c r="N26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
@@ -3145,7 +3185,7 @@
         </is>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5102</v>
+        <v>5664</v>
       </c>
       <c r="X26" s="4" t="n">
         <v>11</v>
@@ -3195,7 +3235,7 @@
       <c r="N27" s="7" t="n"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -3204,7 +3244,7 @@
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>5388</v>
+        <v>5241</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>73</v>
@@ -3254,7 +3294,7 @@
       <c r="N28" s="4" t="n"/>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
@@ -3263,7 +3303,7 @@
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5339</v>
+        <v>5102</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>31</v>
@@ -3313,7 +3353,7 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -3322,7 +3362,7 @@
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>5348</v>
+        <v>5388</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>13</v>
@@ -3372,7 +3412,7 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3381,7 +3421,7 @@
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5329</v>
+        <v>5339</v>
       </c>
       <c r="X30" s="4" t="n">
         <v>78</v>
@@ -3431,7 +3471,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -3440,7 +3480,7 @@
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>5436</v>
+        <v>5348</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>1</v>
@@ -3499,7 +3539,7 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3508,7 +3548,7 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5081</v>
+        <v>5329</v>
       </c>
       <c r="X32" s="4" t="n">
         <v>9</v>
@@ -3539,7 +3579,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D19)</f>
+        <f>AVERAGE(D2:D21)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3549,7 +3589,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H19)</f>
+        <f>AVERAGE(H2:H21)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3572,7 +3612,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -3581,7 +3621,7 @@
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>5034</v>
+        <v>5436</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>1</v>
@@ -3613,7 +3653,7 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3622,7 +3662,7 @@
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5557</v>
+        <v>5081</v>
       </c>
       <c r="X34" s="4" t="n">
         <v>119</v>
@@ -3654,7 +3694,7 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -3663,7 +3703,7 @@
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>5513</v>
+        <v>5034</v>
       </c>
       <c r="X35" s="7" t="n">
         <v>13</v>
@@ -3695,7 +3735,7 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
@@ -3704,7 +3744,7 @@
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>5477</v>
+        <v>5557</v>
       </c>
       <c r="X36" s="4" t="n">
         <v>67</v>
@@ -3736,7 +3776,7 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
@@ -3745,7 +3785,7 @@
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>5526</v>
+        <v>5513</v>
       </c>
       <c r="X37" s="7" t="n">
         <v>32</v>
@@ -3777,16 +3817,16 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>14969</v>
+        <v>5477</v>
       </c>
       <c r="X38" s="4" t="n">
         <v>13</v>
@@ -3818,16 +3858,16 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V39" s="7" t="n">
-        <v>14818</v>
+        <v>5526</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>93</v>
@@ -3859,16 +3899,16 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V40" s="4" t="n">
-        <v>15263</v>
+        <v>5339</v>
       </c>
       <c r="X40" s="4" t="n">
         <v>12</v>
@@ -3900,16 +3940,16 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>14815</v>
+        <v>4933</v>
       </c>
       <c r="X41" s="7" t="n">
         <v>2</v>
@@ -3941,7 +3981,7 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
@@ -3950,7 +3990,7 @@
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>14968</v>
+        <v>14969</v>
       </c>
       <c r="X42" s="4" t="n">
         <v>113</v>
@@ -3982,7 +4022,7 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
@@ -3991,7 +4031,7 @@
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>14113</v>
+        <v>14818</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>12</v>
@@ -4023,7 +4063,7 @@
     <row r="44">
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U44" s="4" t="inlineStr">
@@ -4032,7 +4072,7 @@
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>14162</v>
+        <v>15263</v>
       </c>
       <c r="X44" s="4" t="n">
         <v>69</v>
@@ -4064,7 +4104,7 @@
     <row r="45">
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
@@ -4105,7 +4145,7 @@
     <row r="46">
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
@@ -4114,7 +4154,7 @@
         </is>
       </c>
       <c r="V46" s="4" t="n">
-        <v>14815</v>
+        <v>14968</v>
       </c>
       <c r="X46" s="4" t="n">
         <v>17</v>
@@ -4146,7 +4186,7 @@
     <row r="47">
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
@@ -4155,7 +4195,7 @@
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>15546</v>
+        <v>14113</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>83</v>
@@ -4187,7 +4227,7 @@
     <row r="48">
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
@@ -4196,7 +4236,7 @@
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>14882</v>
+        <v>14162</v>
       </c>
       <c r="X48" s="4" t="n">
         <v>9</v>
@@ -4228,7 +4268,7 @@
     <row r="49">
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
@@ -4237,7 +4277,7 @@
         </is>
       </c>
       <c r="V49" s="7" t="n">
-        <v>14998</v>
+        <v>14815</v>
       </c>
       <c r="X49" s="7" t="n">
         <v>124</v>
@@ -4269,7 +4309,7 @@
     <row r="50">
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U50" s="4" t="inlineStr">
@@ -4278,7 +4318,7 @@
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>14354</v>
+        <v>14815</v>
       </c>
       <c r="X50" s="4" t="n">
         <v>19</v>
@@ -4310,7 +4350,7 @@
     <row r="51">
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
@@ -4319,7 +4359,7 @@
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>14362</v>
+        <v>15546</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>55</v>
@@ -4351,7 +4391,7 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
@@ -4360,7 +4400,7 @@
         </is>
       </c>
       <c r="V52" s="4" t="n">
-        <v>15089</v>
+        <v>14882</v>
       </c>
       <c r="X52" s="4" t="n">
         <v>35</v>
@@ -4392,7 +4432,7 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
@@ -4401,7 +4441,7 @@
         </is>
       </c>
       <c r="V53" s="7" t="n">
-        <v>14802</v>
+        <v>14998</v>
       </c>
       <c r="X53" s="7" t="n">
         <v>15</v>
@@ -4433,7 +4473,7 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
@@ -4442,7 +4482,7 @@
         </is>
       </c>
       <c r="V54" s="4" t="n">
-        <v>15349</v>
+        <v>14354</v>
       </c>
       <c r="X54" s="4" t="n">
         <v>82</v>
@@ -4474,7 +4514,7 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
@@ -4483,7 +4523,7 @@
         </is>
       </c>
       <c r="V55" s="7" t="n">
-        <v>14872</v>
+        <v>14362</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>1</v>
@@ -4515,16 +4555,16 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>77546</v>
+        <v>15089</v>
       </c>
       <c r="X56" s="4" t="n">
         <v>14</v>
@@ -4556,16 +4596,16 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V57" s="7" t="n">
-        <v>77823</v>
+        <v>14802</v>
       </c>
       <c r="X57" s="7" t="n">
         <v>2</v>
@@ -4597,16 +4637,16 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U58" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V58" s="4" t="n">
-        <v>81723</v>
+        <v>15349</v>
       </c>
       <c r="X58" s="4" t="n">
         <v>101</v>
@@ -4638,16 +4678,16 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V59" s="7" t="n">
-        <v>78398</v>
+        <v>14872</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>10</v>
@@ -4679,16 +4719,16 @@
     <row r="60">
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U60" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V60" s="4" t="n">
-        <v>78030</v>
+        <v>15054</v>
       </c>
       <c r="X60" s="4" t="n">
         <v>72</v>
@@ -4720,16 +4760,16 @@
     <row r="61">
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V61" s="7" t="n">
-        <v>76646</v>
+        <v>14169</v>
       </c>
       <c r="X61" s="7" t="n">
         <v>35</v>
@@ -4761,7 +4801,7 @@
     <row r="62">
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U62" s="4" t="inlineStr">
@@ -4770,7 +4810,7 @@
         </is>
       </c>
       <c r="V62" s="4" t="n">
-        <v>76742</v>
+        <v>77546</v>
       </c>
       <c r="X62" s="4" t="n">
         <v>13</v>
@@ -4802,7 +4842,7 @@
     <row r="63">
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
@@ -4811,7 +4851,7 @@
         </is>
       </c>
       <c r="V63" s="7" t="n">
-        <v>79003</v>
+        <v>77823</v>
       </c>
       <c r="X63" s="7" t="n">
         <v>71</v>
@@ -4843,7 +4883,7 @@
     <row r="64">
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr">
@@ -4852,7 +4892,7 @@
         </is>
       </c>
       <c r="V64" s="4" t="n">
-        <v>78849</v>
+        <v>81723</v>
       </c>
       <c r="X64" s="4" t="n">
         <v>8</v>
@@ -4884,7 +4924,7 @@
     <row r="65">
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
@@ -4893,7 +4933,7 @@
         </is>
       </c>
       <c r="V65" s="7" t="n">
-        <v>80667</v>
+        <v>78398</v>
       </c>
       <c r="X65" s="7" t="n">
         <v>2</v>
@@ -4925,7 +4965,7 @@
     <row r="66">
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr">
@@ -4934,7 +4974,7 @@
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>78640</v>
+        <v>78030</v>
       </c>
       <c r="X66" s="4" t="n">
         <v>125</v>
@@ -4966,7 +5006,7 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
@@ -4975,7 +5015,7 @@
         </is>
       </c>
       <c r="V67" s="7" t="n">
-        <v>79108</v>
+        <v>76646</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>11</v>
@@ -5007,7 +5047,7 @@
     <row r="68">
       <c r="T68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U68" s="4" t="inlineStr">
@@ -5016,7 +5056,7 @@
         </is>
       </c>
       <c r="V68" s="4" t="n">
-        <v>76911</v>
+        <v>76742</v>
       </c>
       <c r="X68" s="4" t="n">
         <v>67</v>
@@ -5048,7 +5088,7 @@
     <row r="69">
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
@@ -5057,7 +5097,7 @@
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>77273</v>
+        <v>79003</v>
       </c>
       <c r="X69" s="7" t="n">
         <v>27</v>
@@ -5089,7 +5129,7 @@
     <row r="70">
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U70" s="4" t="inlineStr">
@@ -5098,7 +5138,7 @@
         </is>
       </c>
       <c r="V70" s="4" t="n">
-        <v>80657</v>
+        <v>78849</v>
       </c>
       <c r="X70" s="4" t="n">
         <v>17</v>
@@ -5130,7 +5170,7 @@
     <row r="71">
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U71" s="7" t="inlineStr">
@@ -5139,7 +5179,7 @@
         </is>
       </c>
       <c r="V71" s="7" t="n">
-        <v>79898</v>
+        <v>80667</v>
       </c>
       <c r="X71" s="7" t="n">
         <v>85</v>
@@ -5171,7 +5211,7 @@
     <row r="72">
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U72" s="4" t="inlineStr">
@@ -5180,7 +5220,7 @@
         </is>
       </c>
       <c r="V72" s="4" t="n">
-        <v>82443</v>
+        <v>78640</v>
       </c>
       <c r="X72" s="4" t="n">
         <v>14</v>
@@ -5212,7 +5252,7 @@
     <row r="73">
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U73" s="7" t="inlineStr">
@@ -5221,7 +5261,7 @@
         </is>
       </c>
       <c r="V73" s="7" t="n">
-        <v>80658</v>
+        <v>79108</v>
       </c>
       <c r="X73" s="7" t="n">
         <v>4</v>
@@ -5253,16 +5293,16 @@
     <row r="74">
       <c r="T74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U74" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V74" s="4" t="n">
-        <v>721</v>
+        <v>76911</v>
       </c>
       <c r="X74" s="4" t="n">
         <v>126</v>
@@ -5294,16 +5334,16 @@
     <row r="75">
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U75" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V75" s="7" t="n">
-        <v>715</v>
+        <v>77273</v>
       </c>
       <c r="X75" s="7" t="n">
         <v>23</v>
@@ -5335,16 +5375,16 @@
     <row r="76">
       <c r="T76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U76" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V76" s="4" t="n">
-        <v>745</v>
+        <v>80657</v>
       </c>
       <c r="X76" s="4" t="n">
         <v>65</v>
@@ -5376,16 +5416,16 @@
     <row r="77">
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U77" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V77" s="7" t="n">
-        <v>702</v>
+        <v>79898</v>
       </c>
       <c r="X77" s="7" t="n">
         <v>28</v>
@@ -5417,16 +5457,16 @@
     <row r="78">
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V78" s="4" t="n">
-        <v>743</v>
+        <v>82443</v>
       </c>
       <c r="X78" s="4" t="n">
         <v>19</v>
@@ -5458,16 +5498,16 @@
     <row r="79">
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U79" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V79" s="7" t="n">
-        <v>700</v>
+        <v>80658</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>91</v>
@@ -5499,16 +5539,16 @@
     <row r="80">
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U80" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V80" s="4" t="n">
-        <v>696</v>
+        <v>78475</v>
       </c>
       <c r="X80" s="4" t="n">
         <v>21</v>
@@ -5540,16 +5580,16 @@
     <row r="81">
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U81" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V81" s="7" t="n">
-        <v>750</v>
+        <v>76874</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>2</v>
@@ -5581,7 +5621,7 @@
     <row r="82">
       <c r="T82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U82" s="4" t="inlineStr">
@@ -5590,7 +5630,7 @@
         </is>
       </c>
       <c r="V82" s="4" t="n">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="X82" s="4" t="n">
         <v>99</v>
@@ -5622,7 +5662,7 @@
     <row r="83">
       <c r="T83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U83" s="7" t="inlineStr">
@@ -5631,7 +5671,7 @@
         </is>
       </c>
       <c r="V83" s="7" t="n">
-        <v>748</v>
+        <v>715</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>12</v>
@@ -5663,7 +5703,7 @@
     <row r="84">
       <c r="T84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U84" s="4" t="inlineStr">
@@ -5672,7 +5712,7 @@
         </is>
       </c>
       <c r="V84" s="4" t="n">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="X84" s="4" t="n">
         <v>70</v>
@@ -5704,7 +5744,7 @@
     <row r="85">
       <c r="T85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U85" s="7" t="inlineStr">
@@ -5713,7 +5753,7 @@
         </is>
       </c>
       <c r="V85" s="7" t="n">
-        <v>737</v>
+        <v>702</v>
       </c>
       <c r="X85" s="7" t="n">
         <v>30</v>
@@ -5745,7 +5785,7 @@
     <row r="86">
       <c r="T86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U86" s="4" t="inlineStr">
@@ -5754,7 +5794,7 @@
         </is>
       </c>
       <c r="V86" s="4" t="n">
-        <v>707</v>
+        <v>743</v>
       </c>
       <c r="X86" s="4" t="n">
         <v>15</v>
@@ -5786,7 +5826,7 @@
     <row r="87">
       <c r="T87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U87" s="7" t="inlineStr">
@@ -5795,7 +5835,7 @@
         </is>
       </c>
       <c r="V87" s="7" t="n">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>73</v>
@@ -5827,7 +5867,7 @@
     <row r="88">
       <c r="T88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U88" s="4" t="inlineStr">
@@ -5836,7 +5876,7 @@
         </is>
       </c>
       <c r="V88" s="4" t="n">
-        <v>786</v>
+        <v>696</v>
       </c>
       <c r="X88" s="4" t="n">
         <v>5</v>
@@ -5868,7 +5908,7 @@
     <row r="89">
       <c r="T89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U89" s="7" t="inlineStr">
@@ -5877,7 +5917,7 @@
         </is>
       </c>
       <c r="V89" s="7" t="n">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>1</v>
@@ -5909,7 +5949,7 @@
     <row r="90">
       <c r="T90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U90" s="4" t="inlineStr">
@@ -5918,7 +5958,7 @@
         </is>
       </c>
       <c r="V90" s="4" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="X90" s="4" t="n">
         <v>107</v>
@@ -5950,7 +5990,7 @@
     <row r="91">
       <c r="T91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U91" s="7" t="inlineStr">
@@ -5959,7 +5999,7 @@
         </is>
       </c>
       <c r="V91" s="7" t="n">
-        <v>695</v>
+        <v>748</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>13</v>
@@ -5991,16 +6031,16 @@
     <row r="92">
       <c r="T92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U92" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V92" s="4" t="n">
-        <v>47976</v>
+        <v>736</v>
       </c>
       <c r="X92" s="4" t="n">
         <v>56</v>
@@ -6032,16 +6072,16 @@
     <row r="93">
       <c r="T93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U93" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V93" s="7" t="n">
-        <v>47122</v>
+        <v>737</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>32</v>
@@ -6073,16 +6113,16 @@
     <row r="94">
       <c r="T94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U94" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V94" s="4" t="n">
-        <v>47233</v>
+        <v>707</v>
       </c>
       <c r="X94" s="4" t="n">
         <v>13</v>
@@ -6114,16 +6154,16 @@
     <row r="95">
       <c r="T95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U95" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V95" s="7" t="n">
-        <v>48580</v>
+        <v>713</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>78</v>
@@ -6155,16 +6195,16 @@
     <row r="96">
       <c r="T96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U96" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V96" s="4" t="n">
-        <v>47383</v>
+        <v>786</v>
       </c>
       <c r="X96" s="4" t="n">
         <v>10</v>
@@ -6196,16 +6236,16 @@
     <row r="97">
       <c r="T97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U97" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V97" s="7" t="n">
-        <v>46456</v>
+        <v>730</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>1</v>
@@ -6237,16 +6277,16 @@
     <row r="98">
       <c r="T98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U98" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V98" s="4" t="n">
-        <v>46400</v>
+        <v>726</v>
       </c>
       <c r="X98" s="4" t="n">
         <v>114</v>
@@ -6278,16 +6318,16 @@
     <row r="99">
       <c r="T99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U99" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V99" s="7" t="n">
-        <v>47755</v>
+        <v>695</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>15</v>
@@ -6319,16 +6359,16 @@
     <row r="100">
       <c r="T100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U100" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V100" s="4" t="n">
-        <v>47520</v>
+        <v>693</v>
       </c>
       <c r="X100" s="4" t="n">
         <v>53</v>
@@ -6360,16 +6400,16 @@
     <row r="101">
       <c r="T101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U101" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V101" s="7" t="n">
-        <v>47354</v>
+        <v>686</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>32</v>
@@ -6401,7 +6441,7 @@
     <row r="102">
       <c r="T102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U102" s="4" t="inlineStr">
@@ -6410,7 +6450,7 @@
         </is>
       </c>
       <c r="V102" s="4" t="n">
-        <v>49015</v>
+        <v>47976</v>
       </c>
       <c r="X102" s="4" t="n">
         <v>14</v>
@@ -6442,7 +6482,7 @@
     <row r="103">
       <c r="T103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U103" s="7" t="inlineStr">
@@ -6451,7 +6491,7 @@
         </is>
       </c>
       <c r="V103" s="7" t="n">
-        <v>48832</v>
+        <v>47122</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>80</v>
@@ -6483,7 +6523,7 @@
     <row r="104">
       <c r="T104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U104" s="4" t="inlineStr">
@@ -6492,7 +6532,7 @@
         </is>
       </c>
       <c r="V104" s="4" t="n">
-        <v>46644</v>
+        <v>47233</v>
       </c>
       <c r="X104" s="4" t="n">
         <v>1</v>
@@ -6524,7 +6564,7 @@
     <row r="105">
       <c r="T105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U105" s="7" t="inlineStr">
@@ -6533,7 +6573,7 @@
         </is>
       </c>
       <c r="V105" s="7" t="n">
-        <v>46416</v>
+        <v>48580</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>9</v>
@@ -6565,7 +6605,7 @@
     <row r="106">
       <c r="T106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U106" s="4" t="inlineStr">
@@ -6574,7 +6614,7 @@
         </is>
       </c>
       <c r="V106" s="4" t="n">
-        <v>48419</v>
+        <v>47383</v>
       </c>
       <c r="X106" s="4" t="n">
         <v>4</v>
@@ -6606,7 +6646,7 @@
     <row r="107">
       <c r="T107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U107" s="7" t="inlineStr">
@@ -6615,7 +6655,7 @@
         </is>
       </c>
       <c r="V107" s="7" t="n">
-        <v>47500</v>
+        <v>46456</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>97</v>
@@ -6647,7 +6687,7 @@
     <row r="108">
       <c r="T108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U108" s="4" t="inlineStr">
@@ -6656,7 +6696,7 @@
         </is>
       </c>
       <c r="V108" s="4" t="n">
-        <v>47954</v>
+        <v>46400</v>
       </c>
       <c r="X108" s="4" t="n">
         <v>10</v>
@@ -6688,7 +6728,7 @@
     <row r="109">
       <c r="T109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U109" s="7" t="inlineStr">
@@ -6697,7 +6737,7 @@
         </is>
       </c>
       <c r="V109" s="7" t="n">
-        <v>49088</v>
+        <v>47755</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>52</v>
@@ -6729,16 +6769,16 @@
     <row r="110">
       <c r="T110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U110" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V110" s="4" t="n">
-        <v>1</v>
+        <v>47520</v>
       </c>
       <c r="X110" s="4" t="n">
         <v>37</v>
@@ -6770,16 +6810,16 @@
     <row r="111">
       <c r="T111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U111" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V111" s="7" t="n">
-        <v>1</v>
+        <v>47354</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>18</v>
@@ -6811,16 +6851,16 @@
     <row r="112">
       <c r="T112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U112" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V112" s="4" t="n">
-        <v>1</v>
+        <v>49015</v>
       </c>
       <c r="X112" s="4" t="n">
         <v>64</v>
@@ -6852,16 +6892,16 @@
     <row r="113">
       <c r="T113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U113" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V113" s="7" t="n">
-        <v>1</v>
+        <v>48832</v>
       </c>
       <c r="X113" s="7" t="n">
         <v>7</v>
@@ -6893,16 +6933,16 @@
     <row r="114">
       <c r="T114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U114" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V114" s="4" t="n">
-        <v>1</v>
+        <v>46644</v>
       </c>
       <c r="X114" s="4" t="n">
         <v>106</v>
@@ -6934,16 +6974,16 @@
     <row r="115">
       <c r="T115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U115" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V115" s="7" t="n">
-        <v>1</v>
+        <v>46416</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>14</v>
@@ -6975,16 +7015,16 @@
     <row r="116">
       <c r="T116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U116" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V116" s="4" t="n">
-        <v>1</v>
+        <v>48419</v>
       </c>
       <c r="X116" s="4" t="n">
         <v>65</v>
@@ -7016,16 +7056,16 @@
     <row r="117">
       <c r="T117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V117" s="7" t="n">
-        <v>1</v>
+        <v>47500</v>
       </c>
       <c r="X117" s="7" t="n">
         <v>24</v>
@@ -7057,16 +7097,16 @@
     <row r="118">
       <c r="T118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U118" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V118" s="4" t="n">
-        <v>1</v>
+        <v>47954</v>
       </c>
       <c r="X118" s="4" t="n">
         <v>14</v>
@@ -7098,16 +7138,16 @@
     <row r="119">
       <c r="T119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U119" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V119" s="7" t="n">
-        <v>1</v>
+        <v>49088</v>
       </c>
       <c r="X119" s="7" t="n">
         <v>66</v>
@@ -7139,16 +7179,16 @@
     <row r="120">
       <c r="T120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U120" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V120" s="4" t="n">
-        <v>1</v>
+        <v>48111</v>
       </c>
       <c r="X120" s="4" t="n">
         <v>1</v>
@@ -7180,16 +7220,16 @@
     <row r="121">
       <c r="T121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U121" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V121" s="7" t="n">
-        <v>1</v>
+        <v>46535</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>9</v>
@@ -7221,7 +7261,7 @@
     <row r="122">
       <c r="T122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U122" s="4" t="inlineStr">
@@ -7262,7 +7302,7 @@
     <row r="123">
       <c r="T123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
@@ -7303,7 +7343,7 @@
     <row r="124">
       <c r="T124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U124" s="4" t="inlineStr">
@@ -7344,7 +7384,7 @@
     <row r="125">
       <c r="T125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U125" s="7" t="inlineStr">
@@ -7385,12 +7425,12 @@
     <row r="126">
       <c r="T126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U126" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V126" s="4" t="n">
@@ -7426,12 +7466,12 @@
     <row r="127">
       <c r="T127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U127" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V127" s="7" t="n">
@@ -7467,12 +7507,12 @@
     <row r="128">
       <c r="T128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U128" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V128" s="4" t="n">
@@ -7508,12 +7548,12 @@
     <row r="129">
       <c r="T129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V129" s="7" t="n">
@@ -7549,12 +7589,12 @@
     <row r="130">
       <c r="T130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U130" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V130" s="4" t="n">
@@ -7590,12 +7630,12 @@
     <row r="131">
       <c r="T131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U131" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V131" s="7" t="n">
@@ -7631,12 +7671,12 @@
     <row r="132">
       <c r="T132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U132" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V132" s="4" t="n">
@@ -7672,12 +7712,12 @@
     <row r="133">
       <c r="T133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V133" s="7" t="n">
@@ -7713,12 +7753,12 @@
     <row r="134">
       <c r="T134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U134" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V134" s="4" t="n">
@@ -7754,12 +7794,12 @@
     <row r="135">
       <c r="T135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U135" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V135" s="7" t="n">
@@ -7795,12 +7835,12 @@
     <row r="136">
       <c r="T136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U136" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V136" s="4" t="n">
@@ -7836,12 +7876,12 @@
     <row r="137">
       <c r="T137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U137" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V137" s="7" t="n">
@@ -7877,12 +7917,12 @@
     <row r="138">
       <c r="T138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U138" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V138" s="4" t="n">
@@ -7918,12 +7958,12 @@
     <row r="139">
       <c r="T139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V139" s="7" t="n">
@@ -7959,7 +7999,7 @@
     <row r="140">
       <c r="T140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U140" s="4" t="inlineStr">
@@ -8000,7 +8040,7 @@
     <row r="141">
       <c r="T141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
@@ -8041,7 +8081,7 @@
     <row r="142">
       <c r="T142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U142" s="4" t="inlineStr">
@@ -8082,7 +8122,7 @@
     <row r="143">
       <c r="T143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
@@ -8123,16 +8163,16 @@
     <row r="144">
       <c r="T144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U144" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V144" s="4" t="n">
-        <v>9927</v>
+        <v>1</v>
       </c>
       <c r="X144" s="4" t="n">
         <v>70</v>
@@ -8164,16 +8204,16 @@
     <row r="145">
       <c r="T145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U145" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V145" s="7" t="n">
-        <v>9839</v>
+        <v>1</v>
       </c>
       <c r="X145" s="7" t="n">
         <v>2</v>
@@ -8205,16 +8245,16 @@
     <row r="146">
       <c r="T146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U146" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V146" s="4" t="n">
-        <v>9918</v>
+        <v>1</v>
       </c>
       <c r="X146" s="4" t="n">
         <v>6</v>
@@ -8246,16 +8286,16 @@
     <row r="147">
       <c r="T147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V147" s="7" t="n">
-        <v>10435</v>
+        <v>1</v>
       </c>
       <c r="X147" s="7" t="n">
         <v>2</v>
@@ -8287,20 +8327,30 @@
     <row r="148">
       <c r="T148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U148" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V148" s="4" t="n">
-        <v>10050</v>
-      </c>
-      <c r="X148" s="4" t="n"/>
-      <c r="Y148" s="4" t="n"/>
-      <c r="Z148" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X148" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y148" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z148" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB148" s="4" t="n">
         <v>33</v>
       </c>
@@ -8318,20 +8368,30 @@
     <row r="149">
       <c r="T149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U149" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V149" s="7" t="n">
-        <v>9768</v>
-      </c>
-      <c r="X149" s="7" t="n"/>
-      <c r="Y149" s="7" t="n"/>
-      <c r="Z149" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X149" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y149" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z149" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB149" s="7" t="n">
         <v>140</v>
       </c>
@@ -8349,20 +8409,30 @@
     <row r="150">
       <c r="T150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U150" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V150" s="4" t="n">
-        <v>9920</v>
-      </c>
-      <c r="X150" s="4" t="n"/>
-      <c r="Y150" s="4" t="n"/>
-      <c r="Z150" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X150" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y150" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z150" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB150" s="4" t="n">
         <v>47</v>
       </c>
@@ -8380,20 +8450,30 @@
     <row r="151">
       <c r="T151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V151" s="7" t="n">
-        <v>10435</v>
-      </c>
-      <c r="X151" s="7" t="n"/>
-      <c r="Y151" s="7" t="n"/>
-      <c r="Z151" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X151" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y151" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z151" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB151" s="7" t="n">
         <v>42</v>
       </c>
@@ -8411,20 +8491,30 @@
     <row r="152">
       <c r="T152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U152" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+        </is>
+      </c>
+      <c r="V152" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X152" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y152" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z152" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="V152" s="4" t="n">
-        <v>10434</v>
-      </c>
-      <c r="X152" s="4" t="n"/>
-      <c r="Y152" s="4" t="n"/>
-      <c r="Z152" s="4" t="n"/>
       <c r="AB152" s="4" t="n">
         <v>128</v>
       </c>
@@ -8442,20 +8532,30 @@
     <row r="153">
       <c r="T153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V153" s="7" t="n">
-        <v>10284</v>
-      </c>
-      <c r="X153" s="7" t="n"/>
-      <c r="Y153" s="7" t="n"/>
-      <c r="Z153" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X153" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y153" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z153" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB153" s="7" t="n">
         <v>5</v>
       </c>
@@ -8473,20 +8573,30 @@
     <row r="154">
       <c r="T154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U154" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V154" s="4" t="n">
-        <v>10458</v>
-      </c>
-      <c r="X154" s="4" t="n"/>
-      <c r="Y154" s="4" t="n"/>
-      <c r="Z154" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y154" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z154" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB154" s="4" t="n">
         <v>5</v>
       </c>
@@ -8504,20 +8614,30 @@
     <row r="155">
       <c r="T155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U155" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V155" s="7" t="n">
-        <v>10153</v>
-      </c>
-      <c r="X155" s="7" t="n"/>
-      <c r="Y155" s="7" t="n"/>
-      <c r="Z155" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X155" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y155" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z155" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB155" s="7" t="n">
         <v>2</v>
       </c>
@@ -8535,20 +8655,30 @@
     <row r="156">
       <c r="T156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U156" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V156" s="4" t="n">
-        <v>9843</v>
-      </c>
-      <c r="X156" s="4" t="n"/>
-      <c r="Y156" s="4" t="n"/>
-      <c r="Z156" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X156" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y156" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z156" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB156" s="4" t="n">
         <v>325</v>
       </c>
@@ -8566,20 +8696,30 @@
     <row r="157">
       <c r="T157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V157" s="7" t="n">
-        <v>10433</v>
-      </c>
-      <c r="X157" s="7" t="n"/>
-      <c r="Y157" s="7" t="n"/>
-      <c r="Z157" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X157" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y157" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z157" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB157" s="7" t="n">
         <v>30</v>
       </c>
@@ -8597,20 +8737,30 @@
     <row r="158">
       <c r="T158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U158" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V158" s="4" t="n">
-        <v>10670</v>
-      </c>
-      <c r="X158" s="4" t="n"/>
-      <c r="Y158" s="4" t="n"/>
-      <c r="Z158" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X158" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y158" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z158" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB158" s="4" t="n">
         <v>150</v>
       </c>
@@ -8628,20 +8778,30 @@
     <row r="159">
       <c r="T159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V159" s="7" t="n">
-        <v>10599</v>
-      </c>
-      <c r="X159" s="7" t="n"/>
-      <c r="Y159" s="7" t="n"/>
-      <c r="Z159" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X159" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y159" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z159" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB159" s="7" t="n">
         <v>46</v>
       </c>
@@ -8659,7 +8819,7 @@
     <row r="160">
       <c r="T160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U160" s="4" t="inlineStr">
@@ -8668,11 +8828,21 @@
         </is>
       </c>
       <c r="V160" s="4" t="n">
-        <v>10619</v>
-      </c>
-      <c r="X160" s="4" t="n"/>
-      <c r="Y160" s="4" t="n"/>
-      <c r="Z160" s="4" t="n"/>
+        <v>9927</v>
+      </c>
+      <c r="X160" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y160" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z160" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB160" s="4" t="n">
         <v>46</v>
       </c>
@@ -8690,7 +8860,7 @@
     <row r="161">
       <c r="T161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
@@ -8699,11 +8869,21 @@
         </is>
       </c>
       <c r="V161" s="7" t="n">
-        <v>10415</v>
-      </c>
-      <c r="X161" s="7" t="n"/>
-      <c r="Y161" s="7" t="n"/>
-      <c r="Z161" s="7" t="n"/>
+        <v>9839</v>
+      </c>
+      <c r="X161" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y161" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z161" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB161" s="7" t="n">
         <v>110</v>
       </c>
@@ -8721,20 +8901,30 @@
     <row r="162">
       <c r="T162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U162" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation50987</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V162" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X162" s="4" t="n"/>
-      <c r="Y162" s="4" t="n"/>
-      <c r="Z162" s="4" t="n"/>
+        <v>9918</v>
+      </c>
+      <c r="X162" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="Y162" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z162" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB162" s="4" t="n">
         <v>2</v>
       </c>
@@ -8752,20 +8942,30 @@
     <row r="163">
       <c r="T163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation75114</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V163" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X163" s="7" t="n"/>
-      <c r="Y163" s="7" t="n"/>
-      <c r="Z163" s="7" t="n"/>
+        <v>10435</v>
+      </c>
+      <c r="X163" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y163" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z163" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB163" s="7" t="n">
         <v>5</v>
       </c>
@@ -8783,20 +8983,30 @@
     <row r="164">
       <c r="T164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U164" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V164" s="4" t="n">
-        <v>21493</v>
-      </c>
-      <c r="X164" s="4" t="n"/>
-      <c r="Y164" s="4" t="n"/>
-      <c r="Z164" s="4" t="n"/>
+        <v>10050</v>
+      </c>
+      <c r="X164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y164" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z164" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB164" s="4" t="n">
         <v>2</v>
       </c>
@@ -8814,359 +9024,529 @@
     <row r="165">
       <c r="T165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V165" s="7" t="n">
-        <v>21012</v>
+        <v>9768</v>
       </c>
       <c r="X165" s="7" t="n"/>
       <c r="Y165" s="7" t="n"/>
       <c r="Z165" s="7" t="n"/>
-      <c r="AB165" s="7" t="n"/>
-      <c r="AC165" s="7" t="n"/>
-      <c r="AD165" s="7" t="n"/>
+      <c r="AB165" s="7" t="n">
+        <v>380</v>
+      </c>
+      <c r="AC165" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD165" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="T166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U166" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V166" s="4" t="n">
-        <v>21635</v>
+        <v>9920</v>
       </c>
       <c r="X166" s="4" t="n"/>
       <c r="Y166" s="4" t="n"/>
       <c r="Z166" s="4" t="n"/>
-      <c r="AB166" s="4" t="n"/>
-      <c r="AC166" s="4" t="n"/>
-      <c r="AD166" s="4" t="n"/>
+      <c r="AB166" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC166" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD166" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="T167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V167" s="7" t="n">
-        <v>21969</v>
+        <v>10435</v>
       </c>
       <c r="X167" s="7" t="n"/>
       <c r="Y167" s="7" t="n"/>
       <c r="Z167" s="7" t="n"/>
-      <c r="AB167" s="7" t="n"/>
-      <c r="AC167" s="7" t="n"/>
-      <c r="AD167" s="7" t="n"/>
+      <c r="AB167" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC167" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD167" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="T168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U168" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V168" s="4" t="n">
-        <v>21723</v>
+        <v>10434</v>
       </c>
       <c r="X168" s="4" t="n"/>
       <c r="Y168" s="4" t="n"/>
       <c r="Z168" s="4" t="n"/>
-      <c r="AB168" s="4" t="n"/>
-      <c r="AC168" s="4" t="n"/>
-      <c r="AD168" s="4" t="n"/>
+      <c r="AB168" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AC168" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD168" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="T169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U169" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V169" s="7" t="n">
-        <v>20879</v>
+        <v>10284</v>
       </c>
       <c r="X169" s="7" t="n"/>
       <c r="Y169" s="7" t="n"/>
       <c r="Z169" s="7" t="n"/>
-      <c r="AB169" s="7" t="n"/>
-      <c r="AC169" s="7" t="n"/>
-      <c r="AD169" s="7" t="n"/>
+      <c r="AB169" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC169" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD169" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="T170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U170" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V170" s="4" t="n">
-        <v>20783</v>
+        <v>10458</v>
       </c>
       <c r="X170" s="4" t="n"/>
       <c r="Y170" s="4" t="n"/>
       <c r="Z170" s="4" t="n"/>
-      <c r="AB170" s="4" t="n"/>
-      <c r="AC170" s="4" t="n"/>
-      <c r="AD170" s="4" t="n"/>
+      <c r="AB170" s="4" t="n">
+        <v>154</v>
+      </c>
+      <c r="AC170" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD170" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="T171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U171" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V171" s="7" t="n">
-        <v>21875</v>
+        <v>10153</v>
       </c>
       <c r="X171" s="7" t="n"/>
       <c r="Y171" s="7" t="n"/>
       <c r="Z171" s="7" t="n"/>
-      <c r="AB171" s="7" t="n"/>
-      <c r="AC171" s="7" t="n"/>
-      <c r="AD171" s="7" t="n"/>
+      <c r="AB171" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC171" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD171" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="T172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U172" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V172" s="4" t="n">
-        <v>22103</v>
+        <v>9843</v>
       </c>
       <c r="X172" s="4" t="n"/>
       <c r="Y172" s="4" t="n"/>
       <c r="Z172" s="4" t="n"/>
-      <c r="AB172" s="4" t="n"/>
-      <c r="AC172" s="4" t="n"/>
-      <c r="AD172" s="4" t="n"/>
+      <c r="AB172" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC172" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD172" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="T173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V173" s="7" t="n">
-        <v>22799</v>
+        <v>10433</v>
       </c>
       <c r="X173" s="7" t="n"/>
       <c r="Y173" s="7" t="n"/>
       <c r="Z173" s="7" t="n"/>
-      <c r="AB173" s="7" t="n"/>
-      <c r="AC173" s="7" t="n"/>
-      <c r="AD173" s="7" t="n"/>
+      <c r="AB173" s="7" t="n">
+        <v>367</v>
+      </c>
+      <c r="AC173" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD173" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="T174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U174" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V174" s="4" t="n">
-        <v>22705</v>
+        <v>10670</v>
       </c>
       <c r="X174" s="4" t="n"/>
       <c r="Y174" s="4" t="n"/>
       <c r="Z174" s="4" t="n"/>
-      <c r="AB174" s="4" t="n"/>
-      <c r="AC174" s="4" t="n"/>
-      <c r="AD174" s="4" t="n"/>
+      <c r="AB174" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC174" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD174" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="T175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V175" s="7" t="n">
-        <v>21885</v>
+        <v>10599</v>
       </c>
       <c r="X175" s="7" t="n"/>
       <c r="Y175" s="7" t="n"/>
       <c r="Z175" s="7" t="n"/>
-      <c r="AB175" s="7" t="n"/>
-      <c r="AC175" s="7" t="n"/>
-      <c r="AD175" s="7" t="n"/>
+      <c r="AB175" s="7" t="n">
+        <v>166</v>
+      </c>
+      <c r="AC175" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD175" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="T176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U176" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V176" s="4" t="n">
-        <v>21360</v>
+        <v>10619</v>
       </c>
       <c r="X176" s="4" t="n"/>
       <c r="Y176" s="4" t="n"/>
       <c r="Z176" s="4" t="n"/>
-      <c r="AB176" s="4" t="n"/>
-      <c r="AC176" s="4" t="n"/>
-      <c r="AD176" s="4" t="n"/>
+      <c r="AB176" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC176" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD176" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="T177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U177" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V177" s="7" t="n">
-        <v>20612</v>
+        <v>10415</v>
       </c>
       <c r="X177" s="7" t="n"/>
       <c r="Y177" s="7" t="n"/>
       <c r="Z177" s="7" t="n"/>
-      <c r="AB177" s="7" t="n"/>
-      <c r="AC177" s="7" t="n"/>
-      <c r="AD177" s="7" t="n"/>
+      <c r="AB177" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC177" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD177" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="T178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U178" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V178" s="4" t="n">
-        <v>22101</v>
+        <v>10065</v>
       </c>
       <c r="X178" s="4" t="n"/>
       <c r="Y178" s="4" t="n"/>
       <c r="Z178" s="4" t="n"/>
-      <c r="AB178" s="4" t="n"/>
-      <c r="AC178" s="4" t="n"/>
-      <c r="AD178" s="4" t="n"/>
+      <c r="AB178" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="AC178" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD178" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="T179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V179" s="7" t="n">
-        <v>22665</v>
+        <v>10158</v>
       </c>
       <c r="X179" s="7" t="n"/>
       <c r="Y179" s="7" t="n"/>
       <c r="Z179" s="7" t="n"/>
-      <c r="AB179" s="7" t="n"/>
-      <c r="AC179" s="7" t="n"/>
-      <c r="AD179" s="7" t="n"/>
+      <c r="AB179" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC179" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD179" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="T180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U180" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation50987</t>
         </is>
       </c>
       <c r="V180" s="4" t="n">
-        <v>22473</v>
+        <v>1</v>
       </c>
       <c r="X180" s="4" t="n"/>
       <c r="Y180" s="4" t="n"/>
       <c r="Z180" s="4" t="n"/>
-      <c r="AB180" s="4" t="n"/>
-      <c r="AC180" s="4" t="n"/>
-      <c r="AD180" s="4" t="n"/>
+      <c r="AB180" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC180" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD180" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="T181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U181" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation75114</t>
         </is>
       </c>
       <c r="V181" s="7" t="n">
-        <v>22903</v>
+        <v>1</v>
       </c>
       <c r="X181" s="7" t="n"/>
       <c r="Y181" s="7" t="n"/>
       <c r="Z181" s="7" t="n"/>
-      <c r="AB181" s="7" t="n"/>
-      <c r="AC181" s="7" t="n"/>
-      <c r="AD181" s="7" t="n"/>
+      <c r="AB181" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC181" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD181" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="T182" s="4" t="inlineStr">
@@ -9176,11 +9556,11 @@
       </c>
       <c r="U182" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V182" s="4" t="n">
-        <v>16634</v>
+        <v>21493</v>
       </c>
       <c r="X182" s="4" t="n"/>
       <c r="Y182" s="4" t="n"/>
@@ -9197,11 +9577,11 @@
       </c>
       <c r="U183" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V183" s="7" t="n">
-        <v>16721</v>
+        <v>21012</v>
       </c>
       <c r="X183" s="7" t="n"/>
       <c r="Y183" s="7" t="n"/>
@@ -9218,11 +9598,11 @@
       </c>
       <c r="U184" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V184" s="4" t="n">
-        <v>16586</v>
+        <v>21635</v>
       </c>
       <c r="X184" s="4" t="n"/>
       <c r="Y184" s="4" t="n"/>
@@ -9239,11 +9619,11 @@
       </c>
       <c r="U185" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V185" s="7" t="n">
-        <v>16419</v>
+        <v>21969</v>
       </c>
       <c r="X185" s="7" t="n"/>
       <c r="Y185" s="7" t="n"/>
@@ -9260,11 +9640,11 @@
       </c>
       <c r="U186" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V186" s="4" t="n">
-        <v>15946</v>
+        <v>21723</v>
       </c>
       <c r="X186" s="4" t="n"/>
       <c r="Y186" s="4" t="n"/>
@@ -9281,11 +9661,11 @@
       </c>
       <c r="U187" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V187" s="7" t="n">
-        <v>16042</v>
+        <v>20879</v>
       </c>
       <c r="X187" s="7" t="n"/>
       <c r="Y187" s="7" t="n"/>
@@ -9302,11 +9682,11 @@
       </c>
       <c r="U188" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V188" s="4" t="n">
-        <v>16409</v>
+        <v>20783</v>
       </c>
       <c r="X188" s="4" t="n"/>
       <c r="Y188" s="4" t="n"/>
@@ -9323,11 +9703,11 @@
       </c>
       <c r="U189" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V189" s="7" t="n">
-        <v>16831</v>
+        <v>21875</v>
       </c>
       <c r="X189" s="7" t="n"/>
       <c r="Y189" s="7" t="n"/>
@@ -9344,11 +9724,11 @@
       </c>
       <c r="U190" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V190" s="4" t="n">
-        <v>16886</v>
+        <v>22103</v>
       </c>
       <c r="X190" s="4" t="n"/>
       <c r="Y190" s="4" t="n"/>
@@ -9365,11 +9745,11 @@
       </c>
       <c r="U191" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V191" s="7" t="n">
-        <v>16694</v>
+        <v>22799</v>
       </c>
       <c r="X191" s="7" t="n"/>
       <c r="Y191" s="7" t="n"/>
@@ -9386,11 +9766,11 @@
       </c>
       <c r="U192" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V192" s="4" t="n">
-        <v>16659</v>
+        <v>22705</v>
       </c>
       <c r="X192" s="4" t="n"/>
       <c r="Y192" s="4" t="n"/>
@@ -9407,11 +9787,11 @@
       </c>
       <c r="U193" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V193" s="7" t="n">
-        <v>16268</v>
+        <v>21885</v>
       </c>
       <c r="X193" s="7" t="n"/>
       <c r="Y193" s="7" t="n"/>
@@ -9428,11 +9808,11 @@
       </c>
       <c r="U194" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V194" s="4" t="n">
-        <v>16259</v>
+        <v>21360</v>
       </c>
       <c r="X194" s="4" t="n"/>
       <c r="Y194" s="4" t="n"/>
@@ -9449,11 +9829,11 @@
       </c>
       <c r="U195" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V195" s="7" t="n">
-        <v>16600</v>
+        <v>20612</v>
       </c>
       <c r="X195" s="7" t="n"/>
       <c r="Y195" s="7" t="n"/>
@@ -9470,11 +9850,11 @@
       </c>
       <c r="U196" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V196" s="4" t="n">
-        <v>16913</v>
+        <v>22101</v>
       </c>
       <c r="X196" s="4" t="n"/>
       <c r="Y196" s="4" t="n"/>
@@ -9491,11 +9871,11 @@
       </c>
       <c r="U197" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V197" s="7" t="n">
-        <v>16991</v>
+        <v>22665</v>
       </c>
       <c r="X197" s="7" t="n"/>
       <c r="Y197" s="7" t="n"/>
@@ -9512,11 +9892,11 @@
       </c>
       <c r="U198" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V198" s="4" t="n">
-        <v>17365</v>
+        <v>22473</v>
       </c>
       <c r="X198" s="4" t="n"/>
       <c r="Y198" s="4" t="n"/>
@@ -9533,11 +9913,11 @@
       </c>
       <c r="U199" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V199" s="7" t="n">
-        <v>16944</v>
+        <v>22903</v>
       </c>
       <c r="X199" s="7" t="n"/>
       <c r="Y199" s="7" t="n"/>
@@ -9549,16 +9929,16 @@
     <row r="200">
       <c r="T200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U200" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V200" s="4" t="n">
-        <v>724</v>
+        <v>21829</v>
       </c>
       <c r="X200" s="4" t="n"/>
       <c r="Y200" s="4" t="n"/>
@@ -9570,16 +9950,16 @@
     <row r="201">
       <c r="T201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U201" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V201" s="7" t="n">
-        <v>746</v>
+        <v>20959</v>
       </c>
       <c r="X201" s="7" t="n"/>
       <c r="Y201" s="7" t="n"/>
@@ -9591,16 +9971,16 @@
     <row r="202">
       <c r="T202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U202" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V202" s="4" t="n">
-        <v>723</v>
+        <v>16634</v>
       </c>
       <c r="X202" s="4" t="n"/>
       <c r="Y202" s="4" t="n"/>
@@ -9612,16 +9992,16 @@
     <row r="203">
       <c r="T203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U203" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V203" s="7" t="n">
-        <v>708</v>
+        <v>16721</v>
       </c>
       <c r="X203" s="7" t="n"/>
       <c r="Y203" s="7" t="n"/>
@@ -9633,16 +10013,16 @@
     <row r="204">
       <c r="T204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U204" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V204" s="4" t="n">
-        <v>735</v>
+        <v>16586</v>
       </c>
       <c r="X204" s="4" t="n"/>
       <c r="Y204" s="4" t="n"/>
@@ -9654,16 +10034,16 @@
     <row r="205">
       <c r="T205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U205" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V205" s="7" t="n">
-        <v>714</v>
+        <v>16419</v>
       </c>
       <c r="X205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
@@ -9675,16 +10055,16 @@
     <row r="206">
       <c r="T206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U206" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V206" s="4" t="n">
-        <v>706</v>
+        <v>15946</v>
       </c>
       <c r="X206" s="4" t="n"/>
       <c r="Y206" s="4" t="n"/>
@@ -9696,16 +10076,16 @@
     <row r="207">
       <c r="T207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U207" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V207" s="7" t="n">
-        <v>729</v>
+        <v>16042</v>
       </c>
       <c r="X207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
@@ -9717,16 +10097,16 @@
     <row r="208">
       <c r="T208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U208" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V208" s="4" t="n">
-        <v>719</v>
+        <v>16409</v>
       </c>
       <c r="X208" s="4" t="n"/>
       <c r="Y208" s="4" t="n"/>
@@ -9738,16 +10118,16 @@
     <row r="209">
       <c r="T209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U209" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V209" s="7" t="n">
-        <v>719</v>
+        <v>16831</v>
       </c>
       <c r="X209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
@@ -9759,16 +10139,16 @@
     <row r="210">
       <c r="T210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U210" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V210" s="4" t="n">
-        <v>730</v>
+        <v>16886</v>
       </c>
       <c r="X210" s="4" t="n"/>
       <c r="Y210" s="4" t="n"/>
@@ -9780,16 +10160,16 @@
     <row r="211">
       <c r="T211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U211" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V211" s="7" t="n">
-        <v>740</v>
+        <v>16694</v>
       </c>
       <c r="X211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
@@ -9801,16 +10181,16 @@
     <row r="212">
       <c r="T212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U212" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V212" s="4" t="n">
-        <v>708</v>
+        <v>16659</v>
       </c>
       <c r="X212" s="4" t="n"/>
       <c r="Y212" s="4" t="n"/>
@@ -9822,16 +10202,16 @@
     <row r="213">
       <c r="T213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U213" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V213" s="7" t="n">
-        <v>698</v>
+        <v>16268</v>
       </c>
       <c r="X213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
@@ -9843,16 +10223,16 @@
     <row r="214">
       <c r="T214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U214" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V214" s="4" t="n">
-        <v>691</v>
+        <v>16259</v>
       </c>
       <c r="X214" s="4" t="n"/>
       <c r="Y214" s="4" t="n"/>
@@ -9864,16 +10244,16 @@
     <row r="215">
       <c r="T215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U215" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V215" s="7" t="n">
-        <v>695</v>
+        <v>16600</v>
       </c>
       <c r="X215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
@@ -9885,16 +10265,16 @@
     <row r="216">
       <c r="T216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U216" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V216" s="4" t="n">
-        <v>706</v>
+        <v>16913</v>
       </c>
       <c r="X216" s="4" t="n"/>
       <c r="Y216" s="4" t="n"/>
@@ -9906,16 +10286,16 @@
     <row r="217">
       <c r="T217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U217" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V217" s="7" t="n">
-        <v>701</v>
+        <v>16991</v>
       </c>
       <c r="X217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
@@ -9927,16 +10307,16 @@
     <row r="218">
       <c r="T218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U218" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V218" s="4" t="n">
-        <v>2188</v>
+        <v>17365</v>
       </c>
       <c r="X218" s="4" t="n"/>
       <c r="Y218" s="4" t="n"/>
@@ -9948,16 +10328,16 @@
     <row r="219">
       <c r="T219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U219" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V219" s="7" t="n">
-        <v>2046</v>
+        <v>16944</v>
       </c>
       <c r="X219" s="7" t="n"/>
       <c r="Y219" s="7" t="n"/>
@@ -9969,16 +10349,16 @@
     <row r="220">
       <c r="T220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U220" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V220" s="4" t="n">
-        <v>2338</v>
+        <v>16518</v>
       </c>
       <c r="X220" s="4" t="n"/>
       <c r="Y220" s="4" t="n"/>
@@ -9990,16 +10370,16 @@
     <row r="221">
       <c r="T221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U221" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V221" s="7" t="n">
-        <v>2152</v>
+        <v>16634</v>
       </c>
       <c r="X221" s="7" t="n"/>
       <c r="Y221" s="7" t="n"/>
@@ -10011,16 +10391,16 @@
     <row r="222">
       <c r="T222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U222" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V222" s="4" t="n">
-        <v>2003</v>
+        <v>724</v>
       </c>
       <c r="X222" s="4" t="n"/>
       <c r="Y222" s="4" t="n"/>
@@ -10032,16 +10412,16 @@
     <row r="223">
       <c r="T223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U223" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V223" s="7" t="n">
-        <v>1895</v>
+        <v>746</v>
       </c>
       <c r="X223" s="7" t="n"/>
       <c r="Y223" s="7" t="n"/>
@@ -10053,16 +10433,16 @@
     <row r="224">
       <c r="T224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U224" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V224" s="4" t="n">
-        <v>1935</v>
+        <v>723</v>
       </c>
       <c r="X224" s="4" t="n"/>
       <c r="Y224" s="4" t="n"/>
@@ -10074,16 +10454,16 @@
     <row r="225">
       <c r="T225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U225" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V225" s="7" t="n">
-        <v>2037</v>
+        <v>708</v>
       </c>
       <c r="X225" s="7" t="n"/>
       <c r="Y225" s="7" t="n"/>
@@ -10095,16 +10475,16 @@
     <row r="226">
       <c r="T226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U226" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V226" s="4" t="n">
-        <v>2049</v>
+        <v>735</v>
       </c>
       <c r="X226" s="4" t="n"/>
       <c r="Y226" s="4" t="n"/>
@@ -10116,16 +10496,16 @@
     <row r="227">
       <c r="T227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U227" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V227" s="7" t="n">
-        <v>2325</v>
+        <v>714</v>
       </c>
       <c r="X227" s="7" t="n"/>
       <c r="Y227" s="7" t="n"/>
@@ -10137,16 +10517,16 @@
     <row r="228">
       <c r="T228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U228" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V228" s="4" t="n">
-        <v>2216</v>
+        <v>706</v>
       </c>
       <c r="X228" s="4" t="n"/>
       <c r="Y228" s="4" t="n"/>
@@ -10158,16 +10538,16 @@
     <row r="229">
       <c r="T229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U229" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V229" s="7" t="n">
-        <v>2037</v>
+        <v>729</v>
       </c>
       <c r="X229" s="7" t="n"/>
       <c r="Y229" s="7" t="n"/>
@@ -10179,16 +10559,16 @@
     <row r="230">
       <c r="T230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U230" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V230" s="4" t="n">
-        <v>2046</v>
+        <v>719</v>
       </c>
       <c r="X230" s="4" t="n"/>
       <c r="Y230" s="4" t="n"/>
@@ -10200,16 +10580,16 @@
     <row r="231">
       <c r="T231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U231" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V231" s="7" t="n">
-        <v>2035</v>
+        <v>719</v>
       </c>
       <c r="X231" s="7" t="n"/>
       <c r="Y231" s="7" t="n"/>
@@ -10221,16 +10601,16 @@
     <row r="232">
       <c r="T232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U232" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V232" s="4" t="n">
-        <v>2182</v>
+        <v>730</v>
       </c>
       <c r="X232" s="4" t="n"/>
       <c r="Y232" s="4" t="n"/>
@@ -10242,16 +10622,16 @@
     <row r="233">
       <c r="T233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U233" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V233" s="7" t="n">
-        <v>2156</v>
+        <v>740</v>
       </c>
       <c r="X233" s="7" t="n"/>
       <c r="Y233" s="7" t="n"/>
@@ -10263,16 +10643,16 @@
     <row r="234">
       <c r="T234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U234" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V234" s="4" t="n">
-        <v>2437</v>
+        <v>708</v>
       </c>
       <c r="X234" s="4" t="n"/>
       <c r="Y234" s="4" t="n"/>
@@ -10284,16 +10664,16 @@
     <row r="235">
       <c r="T235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U235" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V235" s="7" t="n">
-        <v>2214</v>
+        <v>698</v>
       </c>
       <c r="X235" s="7" t="n"/>
       <c r="Y235" s="7" t="n"/>
@@ -10301,6 +10681,552 @@
       <c r="AB235" s="7" t="n"/>
       <c r="AC235" s="7" t="n"/>
       <c r="AD235" s="7" t="n"/>
+    </row>
+    <row r="236">
+      <c r="T236" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U236" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V236" s="4" t="n">
+        <v>691</v>
+      </c>
+      <c r="X236" s="4" t="n"/>
+      <c r="Y236" s="4" t="n"/>
+      <c r="Z236" s="4" t="n"/>
+      <c r="AB236" s="4" t="n"/>
+      <c r="AC236" s="4" t="n"/>
+      <c r="AD236" s="4" t="n"/>
+    </row>
+    <row r="237">
+      <c r="T237" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="U237" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V237" s="7" t="n">
+        <v>695</v>
+      </c>
+      <c r="X237" s="7" t="n"/>
+      <c r="Y237" s="7" t="n"/>
+      <c r="Z237" s="7" t="n"/>
+      <c r="AB237" s="7" t="n"/>
+      <c r="AC237" s="7" t="n"/>
+      <c r="AD237" s="7" t="n"/>
+    </row>
+    <row r="238">
+      <c r="T238" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="U238" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V238" s="4" t="n">
+        <v>706</v>
+      </c>
+      <c r="X238" s="4" t="n"/>
+      <c r="Y238" s="4" t="n"/>
+      <c r="Z238" s="4" t="n"/>
+      <c r="AB238" s="4" t="n"/>
+      <c r="AC238" s="4" t="n"/>
+      <c r="AD238" s="4" t="n"/>
+    </row>
+    <row r="239">
+      <c r="T239" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="U239" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V239" s="7" t="n">
+        <v>701</v>
+      </c>
+      <c r="X239" s="7" t="n"/>
+      <c r="Y239" s="7" t="n"/>
+      <c r="Z239" s="7" t="n"/>
+      <c r="AB239" s="7" t="n"/>
+      <c r="AC239" s="7" t="n"/>
+      <c r="AD239" s="7" t="n"/>
+    </row>
+    <row r="240">
+      <c r="T240" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U240" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V240" s="4" t="n">
+        <v>706</v>
+      </c>
+      <c r="X240" s="4" t="n"/>
+      <c r="Y240" s="4" t="n"/>
+      <c r="Z240" s="4" t="n"/>
+      <c r="AB240" s="4" t="n"/>
+      <c r="AC240" s="4" t="n"/>
+      <c r="AD240" s="4" t="n"/>
+    </row>
+    <row r="241">
+      <c r="T241" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U241" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V241" s="7" t="n">
+        <v>704</v>
+      </c>
+      <c r="X241" s="7" t="n"/>
+      <c r="Y241" s="7" t="n"/>
+      <c r="Z241" s="7" t="n"/>
+      <c r="AB241" s="7" t="n"/>
+      <c r="AC241" s="7" t="n"/>
+      <c r="AD241" s="7" t="n"/>
+    </row>
+    <row r="242">
+      <c r="T242" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U242" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V242" s="4" t="n">
+        <v>2188</v>
+      </c>
+      <c r="X242" s="4" t="n"/>
+      <c r="Y242" s="4" t="n"/>
+      <c r="Z242" s="4" t="n"/>
+      <c r="AB242" s="4" t="n"/>
+      <c r="AC242" s="4" t="n"/>
+      <c r="AD242" s="4" t="n"/>
+    </row>
+    <row r="243">
+      <c r="T243" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="U243" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V243" s="7" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X243" s="7" t="n"/>
+      <c r="Y243" s="7" t="n"/>
+      <c r="Z243" s="7" t="n"/>
+      <c r="AB243" s="7" t="n"/>
+      <c r="AC243" s="7" t="n"/>
+      <c r="AD243" s="7" t="n"/>
+    </row>
+    <row r="244">
+      <c r="T244" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="U244" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V244" s="4" t="n">
+        <v>2338</v>
+      </c>
+      <c r="X244" s="4" t="n"/>
+      <c r="Y244" s="4" t="n"/>
+      <c r="Z244" s="4" t="n"/>
+      <c r="AB244" s="4" t="n"/>
+      <c r="AC244" s="4" t="n"/>
+      <c r="AD244" s="4" t="n"/>
+    </row>
+    <row r="245">
+      <c r="T245" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="U245" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V245" s="7" t="n">
+        <v>2152</v>
+      </c>
+      <c r="X245" s="7" t="n"/>
+      <c r="Y245" s="7" t="n"/>
+      <c r="Z245" s="7" t="n"/>
+      <c r="AB245" s="7" t="n"/>
+      <c r="AC245" s="7" t="n"/>
+      <c r="AD245" s="7" t="n"/>
+    </row>
+    <row r="246">
+      <c r="T246" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="U246" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V246" s="4" t="n">
+        <v>2003</v>
+      </c>
+      <c r="X246" s="4" t="n"/>
+      <c r="Y246" s="4" t="n"/>
+      <c r="Z246" s="4" t="n"/>
+      <c r="AB246" s="4" t="n"/>
+      <c r="AC246" s="4" t="n"/>
+      <c r="AD246" s="4" t="n"/>
+    </row>
+    <row r="247">
+      <c r="T247" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="U247" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V247" s="7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="X247" s="7" t="n"/>
+      <c r="Y247" s="7" t="n"/>
+      <c r="Z247" s="7" t="n"/>
+      <c r="AB247" s="7" t="n"/>
+      <c r="AC247" s="7" t="n"/>
+      <c r="AD247" s="7" t="n"/>
+    </row>
+    <row r="248">
+      <c r="T248" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="U248" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V248" s="4" t="n">
+        <v>1935</v>
+      </c>
+      <c r="X248" s="4" t="n"/>
+      <c r="Y248" s="4" t="n"/>
+      <c r="Z248" s="4" t="n"/>
+      <c r="AB248" s="4" t="n"/>
+      <c r="AC248" s="4" t="n"/>
+      <c r="AD248" s="4" t="n"/>
+    </row>
+    <row r="249">
+      <c r="T249" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U249" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V249" s="7" t="n">
+        <v>2037</v>
+      </c>
+      <c r="X249" s="7" t="n"/>
+      <c r="Y249" s="7" t="n"/>
+      <c r="Z249" s="7" t="n"/>
+      <c r="AB249" s="7" t="n"/>
+      <c r="AC249" s="7" t="n"/>
+      <c r="AD249" s="7" t="n"/>
+    </row>
+    <row r="250">
+      <c r="T250" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="U250" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V250" s="4" t="n">
+        <v>2049</v>
+      </c>
+      <c r="X250" s="4" t="n"/>
+      <c r="Y250" s="4" t="n"/>
+      <c r="Z250" s="4" t="n"/>
+      <c r="AB250" s="4" t="n"/>
+      <c r="AC250" s="4" t="n"/>
+      <c r="AD250" s="4" t="n"/>
+    </row>
+    <row r="251">
+      <c r="T251" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="U251" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V251" s="7" t="n">
+        <v>2325</v>
+      </c>
+      <c r="X251" s="7" t="n"/>
+      <c r="Y251" s="7" t="n"/>
+      <c r="Z251" s="7" t="n"/>
+      <c r="AB251" s="7" t="n"/>
+      <c r="AC251" s="7" t="n"/>
+      <c r="AD251" s="7" t="n"/>
+    </row>
+    <row r="252">
+      <c r="T252" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="U252" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V252" s="4" t="n">
+        <v>2216</v>
+      </c>
+      <c r="X252" s="4" t="n"/>
+      <c r="Y252" s="4" t="n"/>
+      <c r="Z252" s="4" t="n"/>
+      <c r="AB252" s="4" t="n"/>
+      <c r="AC252" s="4" t="n"/>
+      <c r="AD252" s="4" t="n"/>
+    </row>
+    <row r="253">
+      <c r="T253" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="U253" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V253" s="7" t="n">
+        <v>2037</v>
+      </c>
+      <c r="X253" s="7" t="n"/>
+      <c r="Y253" s="7" t="n"/>
+      <c r="Z253" s="7" t="n"/>
+      <c r="AB253" s="7" t="n"/>
+      <c r="AC253" s="7" t="n"/>
+      <c r="AD253" s="7" t="n"/>
+    </row>
+    <row r="254">
+      <c r="T254" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U254" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V254" s="4" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X254" s="4" t="n"/>
+      <c r="Y254" s="4" t="n"/>
+      <c r="Z254" s="4" t="n"/>
+      <c r="AB254" s="4" t="n"/>
+      <c r="AC254" s="4" t="n"/>
+      <c r="AD254" s="4" t="n"/>
+    </row>
+    <row r="255">
+      <c r="T255" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="U255" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V255" s="7" t="n">
+        <v>2035</v>
+      </c>
+      <c r="X255" s="7" t="n"/>
+      <c r="Y255" s="7" t="n"/>
+      <c r="Z255" s="7" t="n"/>
+      <c r="AB255" s="7" t="n"/>
+      <c r="AC255" s="7" t="n"/>
+      <c r="AD255" s="7" t="n"/>
+    </row>
+    <row r="256">
+      <c r="T256" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U256" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V256" s="4" t="n">
+        <v>2182</v>
+      </c>
+      <c r="X256" s="4" t="n"/>
+      <c r="Y256" s="4" t="n"/>
+      <c r="Z256" s="4" t="n"/>
+      <c r="AB256" s="4" t="n"/>
+      <c r="AC256" s="4" t="n"/>
+      <c r="AD256" s="4" t="n"/>
+    </row>
+    <row r="257">
+      <c r="T257" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="U257" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V257" s="7" t="n">
+        <v>2156</v>
+      </c>
+      <c r="X257" s="7" t="n"/>
+      <c r="Y257" s="7" t="n"/>
+      <c r="Z257" s="7" t="n"/>
+      <c r="AB257" s="7" t="n"/>
+      <c r="AC257" s="7" t="n"/>
+      <c r="AD257" s="7" t="n"/>
+    </row>
+    <row r="258">
+      <c r="T258" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="U258" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V258" s="4" t="n">
+        <v>2437</v>
+      </c>
+      <c r="X258" s="4" t="n"/>
+      <c r="Y258" s="4" t="n"/>
+      <c r="Z258" s="4" t="n"/>
+      <c r="AB258" s="4" t="n"/>
+      <c r="AC258" s="4" t="n"/>
+      <c r="AD258" s="4" t="n"/>
+    </row>
+    <row r="259">
+      <c r="T259" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="U259" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V259" s="7" t="n">
+        <v>2214</v>
+      </c>
+      <c r="X259" s="7" t="n"/>
+      <c r="Y259" s="7" t="n"/>
+      <c r="Z259" s="7" t="n"/>
+      <c r="AB259" s="7" t="n"/>
+      <c r="AC259" s="7" t="n"/>
+      <c r="AD259" s="7" t="n"/>
+    </row>
+    <row r="260">
+      <c r="T260" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U260" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V260" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="X260" s="4" t="n"/>
+      <c r="Y260" s="4" t="n"/>
+      <c r="Z260" s="4" t="n"/>
+      <c r="AB260" s="4" t="n"/>
+      <c r="AC260" s="4" t="n"/>
+      <c r="AD260" s="4" t="n"/>
+    </row>
+    <row r="261">
+      <c r="T261" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U261" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V261" s="7" t="n">
+        <v>1973</v>
+      </c>
+      <c r="X261" s="7" t="n"/>
+      <c r="Y261" s="7" t="n"/>
+      <c r="Z261" s="7" t="n"/>
+      <c r="AB261" s="7" t="n"/>
+      <c r="AC261" s="7" t="n"/>
+      <c r="AD261" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -716,10 +716,10 @@
         <v>0.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -752,10 +752,10 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -788,10 +788,10 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -824,10 +824,10 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -860,10 +860,10 @@
         <v>0.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -896,10 +896,10 @@
         <v>0.95</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -932,10 +932,10 @@
         <v>0.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -968,10 +968,10 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1004,10 +1004,10 @@
         <v>0.95</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1040,10 +1040,10 @@
         <v>0.95</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD261"/>
+  <dimension ref="A1:AD191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1344,15 +1344,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>103</v>
       </c>
@@ -1429,15 +1423,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>13</v>
       </c>
@@ -1514,15 +1502,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>64</v>
       </c>
@@ -1593,15 +1575,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>30</v>
       </c>
@@ -1678,15 +1654,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>21</v>
       </c>
@@ -1763,15 +1733,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>73</v>
       </c>
@@ -1848,15 +1812,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>15</v>
       </c>
@@ -1927,15 +1885,9 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>1</v>
       </c>
@@ -2014,15 +1966,9 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>105</v>
       </c>
@@ -2093,15 +2039,9 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>19</v>
       </c>
@@ -2172,15 +2112,9 @@
         <f>$B$2+H12+M12</f>
         <v/>
       </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>82</v>
       </c>
@@ -2251,15 +2185,9 @@
         <f>$B$2+H13+M13</f>
         <v/>
       </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>25</v>
       </c>
@@ -2330,15 +2258,9 @@
         <f>$B$2+H14+M14</f>
         <v/>
       </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>15</v>
       </c>
@@ -2409,15 +2331,9 @@
         <f>$B$2+H15+M15</f>
         <v/>
       </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>75</v>
       </c>
@@ -2488,15 +2404,9 @@
         <f>$B$2+H16+M16</f>
         <v/>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>9</v>
       </c>
@@ -2567,15 +2477,9 @@
         <f>$B$2+H17+M17</f>
         <v/>
       </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>1</v>
       </c>
@@ -2646,15 +2550,9 @@
         <f>$B$2+H18+M18</f>
         <v/>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>145</v>
       </c>
@@ -2725,15 +2623,9 @@
         <f>$B$2+H19+M19</f>
         <v/>
       </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>19</v>
       </c>
@@ -2804,15 +2696,9 @@
         <f>$B$2+H20+M20</f>
         <v/>
       </c>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>74</v>
       </c>
@@ -2883,15 +2769,9 @@
         <f>$B$2+H21+M21</f>
         <v/>
       </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr"/>
-      <c r="V21" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>26</v>
       </c>
@@ -2927,30 +2807,44 @@
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="D22" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C22)</f>
+        <v/>
+      </c>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="G22" s="4">
+        <f>ROUND((1-E22/D22)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>MIN(1,(G22-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>5365</v>
-      </c>
+      <c r="K22" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="4">
+        <f>ROUND(100*(1-K22/D22),2)</f>
+        <v/>
+      </c>
+      <c r="M22" s="4">
+        <f>MAX(0,(L22-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N22" s="4">
+        <f>$B$2+H22+M22</f>
+        <v/>
+      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>9</v>
       </c>
@@ -2997,19 +2891,9 @@
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>5741</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
         <v>74</v>
       </c>
@@ -3056,19 +2940,9 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>5451</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
         <v>11</v>
       </c>
@@ -3115,19 +2989,9 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>5458</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>101</v>
       </c>
@@ -3174,19 +3038,9 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>5664</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
         <v>11</v>
       </c>
@@ -3233,19 +3087,9 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>5241</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
         <v>73</v>
       </c>
@@ -3292,19 +3136,9 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>5102</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
         <v>31</v>
       </c>
@@ -3351,19 +3185,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>5388</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>13</v>
       </c>
@@ -3410,19 +3234,9 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
         <v>78</v>
       </c>
@@ -3469,19 +3283,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>5348</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
@@ -3537,19 +3341,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>5329</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>9</v>
       </c>
@@ -3579,7 +3373,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D21)</f>
+        <f>AVERAGE(D2:D22)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3589,7 +3383,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H21)</f>
+        <f>AVERAGE(H2:H22)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3610,19 +3404,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>5436</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
@@ -3651,19 +3435,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>5081</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>119</v>
       </c>
@@ -3692,19 +3466,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>5034</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>13</v>
       </c>
@@ -3733,19 +3497,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>67</v>
       </c>
@@ -3774,19 +3528,9 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>5513</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
         <v>32</v>
       </c>
@@ -3815,19 +3559,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>5477</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
         <v>13</v>
       </c>
@@ -3856,19 +3590,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>5526</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>93</v>
       </c>
@@ -3897,19 +3621,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>12</v>
       </c>
@@ -3938,19 +3652,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>4933</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>2</v>
       </c>
@@ -3979,19 +3683,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>14969</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>113</v>
       </c>
@@ -4020,19 +3714,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>14818</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>12</v>
       </c>
@@ -4061,19 +3745,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>15263</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>69</v>
       </c>
@@ -4102,19 +3776,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>40</v>
       </c>
@@ -4143,19 +3807,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>14968</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>17</v>
       </c>
@@ -4184,19 +3838,9 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>14113</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>83</v>
       </c>
@@ -4225,19 +3869,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>14162</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>9</v>
       </c>
@@ -4266,19 +3900,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>124</v>
       </c>
@@ -4307,19 +3931,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>19</v>
       </c>
@@ -4348,19 +3962,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>15546</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>55</v>
       </c>
@@ -4389,19 +3993,9 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>14882</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
         <v>35</v>
       </c>
@@ -4430,19 +4024,9 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>14998</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>15</v>
       </c>
@@ -4471,19 +4055,9 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>14354</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>82</v>
       </c>
@@ -4512,19 +4086,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>14362</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>1</v>
       </c>
@@ -4553,19 +4117,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>15089</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>14</v>
       </c>
@@ -4594,19 +4148,9 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>14802</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>2</v>
       </c>
@@ -4635,19 +4179,9 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>15349</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
         <v>101</v>
       </c>
@@ -4676,19 +4210,9 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>14872</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
         <v>10</v>
       </c>
@@ -4717,19 +4241,9 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>15054</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
         <v>72</v>
       </c>
@@ -4758,19 +4272,9 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>14169</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
         <v>35</v>
       </c>
@@ -4799,19 +4303,9 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>77546</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
         <v>13</v>
       </c>
@@ -4840,19 +4334,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>77823</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>71</v>
       </c>
@@ -4881,19 +4365,9 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>81723</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
         <v>8</v>
       </c>
@@ -4922,19 +4396,9 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>78398</v>
-      </c>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
         <v>2</v>
       </c>
@@ -4963,19 +4427,9 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>78030</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>125</v>
       </c>
@@ -5004,19 +4458,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>76646</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>11</v>
       </c>
@@ -5045,19 +4489,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>76742</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>67</v>
       </c>
@@ -5086,19 +4520,9 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>79003</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>27</v>
       </c>
@@ -5127,19 +4551,9 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>78849</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
         <v>17</v>
       </c>
@@ -5168,19 +4582,9 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>80667</v>
-      </c>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
         <v>85</v>
       </c>
@@ -5209,19 +4613,9 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>78640</v>
-      </c>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
         <v>14</v>
       </c>
@@ -5250,19 +4644,9 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>79108</v>
-      </c>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
         <v>4</v>
       </c>
@@ -5291,19 +4675,9 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>76911</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
         <v>126</v>
       </c>
@@ -5332,19 +4706,9 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>77273</v>
-      </c>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
         <v>23</v>
       </c>
@@ -5373,19 +4737,9 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>80657</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>65</v>
       </c>
@@ -5414,19 +4768,9 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>79898</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
         <v>28</v>
       </c>
@@ -5455,19 +4799,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>82443</v>
-      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
         <v>19</v>
       </c>
@@ -5496,19 +4830,9 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>80658</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>91</v>
       </c>
@@ -5537,19 +4861,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>78475</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>21</v>
       </c>
@@ -5578,19 +4892,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>76874</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
         <v>2</v>
       </c>
@@ -5619,19 +4923,9 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
         <v>99</v>
       </c>
@@ -5660,19 +4954,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>715</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>12</v>
       </c>
@@ -5701,19 +4985,9 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>745</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
         <v>70</v>
       </c>
@@ -5742,19 +5016,9 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>702</v>
-      </c>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
         <v>30</v>
       </c>
@@ -5783,19 +5047,9 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>743</v>
-      </c>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
         <v>15</v>
       </c>
@@ -5824,19 +5078,9 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>700</v>
-      </c>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
         <v>73</v>
       </c>
@@ -5865,19 +5109,9 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
         <v>5</v>
       </c>
@@ -5906,19 +5140,9 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>750</v>
-      </c>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
         <v>1</v>
       </c>
@@ -5947,19 +5171,9 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>729</v>
-      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
         <v>107</v>
       </c>
@@ -5988,19 +5202,9 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>748</v>
-      </c>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
         <v>13</v>
       </c>
@@ -6029,19 +5233,9 @@
       </c>
     </row>
     <row r="92">
-      <c r="T92" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V92" s="4" t="n">
-        <v>736</v>
-      </c>
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
       <c r="X92" s="4" t="n">
         <v>56</v>
       </c>
@@ -6070,19 +5264,9 @@
       </c>
     </row>
     <row r="93">
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U93" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>737</v>
-      </c>
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
         <v>32</v>
       </c>
@@ -6111,19 +5295,9 @@
       </c>
     </row>
     <row r="94">
-      <c r="T94" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>707</v>
-      </c>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
         <v>13</v>
       </c>
@@ -6152,19 +5326,9 @@
       </c>
     </row>
     <row r="95">
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>713</v>
-      </c>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
         <v>78</v>
       </c>
@@ -6193,19 +5357,9 @@
       </c>
     </row>
     <row r="96">
-      <c r="T96" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V96" s="4" t="n">
-        <v>786</v>
-      </c>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
       <c r="X96" s="4" t="n">
         <v>10</v>
       </c>
@@ -6234,19 +5388,9 @@
       </c>
     </row>
     <row r="97">
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V97" s="7" t="n">
-        <v>730</v>
-      </c>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
         <v>1</v>
       </c>
@@ -6275,19 +5419,9 @@
       </c>
     </row>
     <row r="98">
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>726</v>
-      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
         <v>114</v>
       </c>
@@ -6316,19 +5450,9 @@
       </c>
     </row>
     <row r="99">
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V99" s="7" t="n">
-        <v>695</v>
-      </c>
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
         <v>15</v>
       </c>
@@ -6357,19 +5481,9 @@
       </c>
     </row>
     <row r="100">
-      <c r="T100" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>693</v>
-      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
         <v>53</v>
       </c>
@@ -6398,19 +5512,9 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U101" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V101" s="7" t="n">
-        <v>686</v>
-      </c>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
         <v>32</v>
       </c>
@@ -6439,19 +5543,9 @@
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n">
-        <v>47976</v>
-      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
         <v>14</v>
       </c>
@@ -6480,19 +5574,9 @@
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V103" s="7" t="n">
-        <v>47122</v>
-      </c>
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
         <v>80</v>
       </c>
@@ -6521,19 +5605,9 @@
       </c>
     </row>
     <row r="104">
-      <c r="T104" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U104" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V104" s="4" t="n">
-        <v>47233</v>
-      </c>
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="4" t="n"/>
+      <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
         <v>1</v>
       </c>
@@ -6562,19 +5636,9 @@
       </c>
     </row>
     <row r="105">
-      <c r="T105" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U105" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>48580</v>
-      </c>
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
         <v>9</v>
       </c>
@@ -6603,19 +5667,9 @@
       </c>
     </row>
     <row r="106">
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="n">
-        <v>47383</v>
-      </c>
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="4" t="n"/>
+      <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
         <v>4</v>
       </c>
@@ -6644,19 +5698,9 @@
       </c>
     </row>
     <row r="107">
-      <c r="T107" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U107" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V107" s="7" t="n">
-        <v>46456</v>
-      </c>
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
         <v>97</v>
       </c>
@@ -6685,19 +5729,9 @@
       </c>
     </row>
     <row r="108">
-      <c r="T108" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U108" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V108" s="4" t="n">
-        <v>46400</v>
-      </c>
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="4" t="n"/>
+      <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
         <v>10</v>
       </c>
@@ -6726,19 +5760,9 @@
       </c>
     </row>
     <row r="109">
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U109" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V109" s="7" t="n">
-        <v>47755</v>
-      </c>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
         <v>52</v>
       </c>
@@ -6767,19 +5791,9 @@
       </c>
     </row>
     <row r="110">
-      <c r="T110" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U110" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V110" s="4" t="n">
-        <v>47520</v>
-      </c>
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="n"/>
       <c r="X110" s="4" t="n">
         <v>37</v>
       </c>
@@ -6808,19 +5822,9 @@
       </c>
     </row>
     <row r="111">
-      <c r="T111" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U111" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V111" s="7" t="n">
-        <v>47354</v>
-      </c>
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
       <c r="X111" s="7" t="n">
         <v>18</v>
       </c>
@@ -6849,19 +5853,9 @@
       </c>
     </row>
     <row r="112">
-      <c r="T112" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U112" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V112" s="4" t="n">
-        <v>49015</v>
-      </c>
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="4" t="n"/>
+      <c r="V112" s="4" t="n"/>
       <c r="X112" s="4" t="n">
         <v>64</v>
       </c>
@@ -6890,19 +5884,9 @@
       </c>
     </row>
     <row r="113">
-      <c r="T113" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U113" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V113" s="7" t="n">
-        <v>48832</v>
-      </c>
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
         <v>7</v>
       </c>
@@ -6931,19 +5915,9 @@
       </c>
     </row>
     <row r="114">
-      <c r="T114" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U114" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V114" s="4" t="n">
-        <v>46644</v>
-      </c>
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="n"/>
       <c r="X114" s="4" t="n">
         <v>106</v>
       </c>
@@ -6972,19 +5946,9 @@
       </c>
     </row>
     <row r="115">
-      <c r="T115" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U115" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V115" s="7" t="n">
-        <v>46416</v>
-      </c>
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
       <c r="X115" s="7" t="n">
         <v>14</v>
       </c>
@@ -7013,19 +5977,9 @@
       </c>
     </row>
     <row r="116">
-      <c r="T116" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U116" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V116" s="4" t="n">
-        <v>48419</v>
-      </c>
+      <c r="T116" s="4" t="n"/>
+      <c r="U116" s="4" t="n"/>
+      <c r="V116" s="4" t="n"/>
       <c r="X116" s="4" t="n">
         <v>65</v>
       </c>
@@ -7054,19 +6008,9 @@
       </c>
     </row>
     <row r="117">
-      <c r="T117" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U117" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V117" s="7" t="n">
-        <v>47500</v>
-      </c>
+      <c r="T117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
       <c r="X117" s="7" t="n">
         <v>24</v>
       </c>
@@ -7095,19 +6039,9 @@
       </c>
     </row>
     <row r="118">
-      <c r="T118" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U118" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V118" s="4" t="n">
-        <v>47954</v>
-      </c>
+      <c r="T118" s="4" t="n"/>
+      <c r="U118" s="4" t="n"/>
+      <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
         <v>14</v>
       </c>
@@ -7136,19 +6070,9 @@
       </c>
     </row>
     <row r="119">
-      <c r="T119" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U119" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V119" s="7" t="n">
-        <v>49088</v>
-      </c>
+      <c r="T119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
         <v>66</v>
       </c>
@@ -7177,19 +6101,9 @@
       </c>
     </row>
     <row r="120">
-      <c r="T120" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U120" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="n">
-        <v>48111</v>
-      </c>
+      <c r="T120" s="4" t="n"/>
+      <c r="U120" s="4" t="n"/>
+      <c r="V120" s="4" t="n"/>
       <c r="X120" s="4" t="n">
         <v>1</v>
       </c>
@@ -7218,19 +6132,9 @@
       </c>
     </row>
     <row r="121">
-      <c r="T121" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U121" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>46535</v>
-      </c>
+      <c r="T121" s="7" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
       <c r="X121" s="7" t="n">
         <v>9</v>
       </c>
@@ -7259,19 +6163,9 @@
       </c>
     </row>
     <row r="122">
-      <c r="T122" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U122" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V122" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T122" s="4" t="n"/>
+      <c r="U122" s="4" t="n"/>
+      <c r="V122" s="4" t="n"/>
       <c r="X122" s="4" t="n">
         <v>116</v>
       </c>
@@ -7300,19 +6194,9 @@
       </c>
     </row>
     <row r="123">
-      <c r="T123" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U123" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V123" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T123" s="7" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
       <c r="X123" s="7" t="n">
         <v>17</v>
       </c>
@@ -7341,19 +6225,9 @@
       </c>
     </row>
     <row r="124">
-      <c r="T124" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U124" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T124" s="4" t="n"/>
+      <c r="U124" s="4" t="n"/>
+      <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
         <v>52</v>
       </c>
@@ -7382,19 +6256,9 @@
       </c>
     </row>
     <row r="125">
-      <c r="T125" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V125" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T125" s="7" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
         <v>38</v>
       </c>
@@ -7423,19 +6287,9 @@
       </c>
     </row>
     <row r="126">
-      <c r="T126" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U126" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V126" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T126" s="4" t="n"/>
+      <c r="U126" s="4" t="n"/>
+      <c r="V126" s="4" t="n"/>
       <c r="X126" s="4" t="n">
         <v>19</v>
       </c>
@@ -7464,19 +6318,9 @@
       </c>
     </row>
     <row r="127">
-      <c r="T127" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U127" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V127" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T127" s="7" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
       <c r="X127" s="7" t="n">
         <v>79</v>
       </c>
@@ -7505,19 +6349,9 @@
       </c>
     </row>
     <row r="128">
-      <c r="T128" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U128" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V128" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T128" s="4" t="n"/>
+      <c r="U128" s="4" t="n"/>
+      <c r="V128" s="4" t="n"/>
       <c r="X128" s="4" t="n">
         <v>9</v>
       </c>
@@ -7546,19 +6380,9 @@
       </c>
     </row>
     <row r="129">
-      <c r="T129" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U129" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V129" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T129" s="7" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
       <c r="X129" s="7" t="n">
         <v>1</v>
       </c>
@@ -7587,19 +6411,9 @@
       </c>
     </row>
     <row r="130">
-      <c r="T130" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U130" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V130" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T130" s="4" t="n"/>
+      <c r="U130" s="4" t="n"/>
+      <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
         <v>134</v>
       </c>
@@ -7628,19 +6442,9 @@
       </c>
     </row>
     <row r="131">
-      <c r="T131" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U131" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V131" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T131" s="7" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
         <v>22</v>
       </c>
@@ -7669,19 +6473,9 @@
       </c>
     </row>
     <row r="132">
-      <c r="T132" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U132" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V132" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T132" s="4" t="n"/>
+      <c r="U132" s="4" t="n"/>
+      <c r="V132" s="4" t="n"/>
       <c r="X132" s="4" t="n">
         <v>65</v>
       </c>
@@ -7710,19 +6504,9 @@
       </c>
     </row>
     <row r="133">
-      <c r="T133" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U133" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V133" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T133" s="7" t="n"/>
+      <c r="U133" s="7" t="n"/>
+      <c r="V133" s="7" t="n"/>
       <c r="X133" s="7" t="n">
         <v>29</v>
       </c>
@@ -7751,19 +6535,9 @@
       </c>
     </row>
     <row r="134">
-      <c r="T134" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U134" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V134" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="4" t="n"/>
+      <c r="V134" s="4" t="n"/>
       <c r="X134" s="4" t="n">
         <v>12</v>
       </c>
@@ -7792,19 +6566,9 @@
       </c>
     </row>
     <row r="135">
-      <c r="T135" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U135" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V135" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T135" s="7" t="n"/>
+      <c r="U135" s="7" t="n"/>
+      <c r="V135" s="7" t="n"/>
       <c r="X135" s="7" t="n">
         <v>82</v>
       </c>
@@ -7833,19 +6597,9 @@
       </c>
     </row>
     <row r="136">
-      <c r="T136" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U136" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V136" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T136" s="4" t="n"/>
+      <c r="U136" s="4" t="n"/>
+      <c r="V136" s="4" t="n"/>
       <c r="X136" s="4" t="n">
         <v>1</v>
       </c>
@@ -7874,19 +6628,9 @@
       </c>
     </row>
     <row r="137">
-      <c r="T137" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U137" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V137" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T137" s="7" t="n"/>
+      <c r="U137" s="7" t="n"/>
+      <c r="V137" s="7" t="n"/>
       <c r="X137" s="7" t="n">
         <v>7</v>
       </c>
@@ -7915,19 +6659,9 @@
       </c>
     </row>
     <row r="138">
-      <c r="T138" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U138" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V138" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T138" s="4" t="n"/>
+      <c r="U138" s="4" t="n"/>
+      <c r="V138" s="4" t="n"/>
       <c r="X138" s="4" t="n">
         <v>1</v>
       </c>
@@ -7956,19 +6690,9 @@
       </c>
     </row>
     <row r="139">
-      <c r="T139" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U139" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V139" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T139" s="7" t="n"/>
+      <c r="U139" s="7" t="n"/>
+      <c r="V139" s="7" t="n"/>
       <c r="X139" s="7" t="n">
         <v>107</v>
       </c>
@@ -7997,19 +6721,9 @@
       </c>
     </row>
     <row r="140">
-      <c r="T140" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U140" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V140" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T140" s="4" t="n"/>
+      <c r="U140" s="4" t="n"/>
+      <c r="V140" s="4" t="n"/>
       <c r="X140" s="4" t="n">
         <v>24</v>
       </c>
@@ -8038,19 +6752,9 @@
       </c>
     </row>
     <row r="141">
-      <c r="T141" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U141" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V141" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T141" s="7" t="n"/>
+      <c r="U141" s="7" t="n"/>
+      <c r="V141" s="7" t="n"/>
       <c r="X141" s="7" t="n">
         <v>68</v>
       </c>
@@ -8079,19 +6783,9 @@
       </c>
     </row>
     <row r="142">
-      <c r="T142" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U142" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V142" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T142" s="4" t="n"/>
+      <c r="U142" s="4" t="n"/>
+      <c r="V142" s="4" t="n"/>
       <c r="X142" s="4" t="n">
         <v>18</v>
       </c>
@@ -8120,19 +6814,9 @@
       </c>
     </row>
     <row r="143">
-      <c r="T143" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U143" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V143" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T143" s="7" t="n"/>
+      <c r="U143" s="7" t="n"/>
+      <c r="V143" s="7" t="n"/>
       <c r="X143" s="7" t="n">
         <v>12</v>
       </c>
@@ -8161,19 +6845,9 @@
       </c>
     </row>
     <row r="144">
-      <c r="T144" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U144" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V144" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T144" s="4" t="n"/>
+      <c r="U144" s="4" t="n"/>
+      <c r="V144" s="4" t="n"/>
       <c r="X144" s="4" t="n">
         <v>70</v>
       </c>
@@ -8202,19 +6876,9 @@
       </c>
     </row>
     <row r="145">
-      <c r="T145" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U145" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V145" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T145" s="7" t="n"/>
+      <c r="U145" s="7" t="n"/>
+      <c r="V145" s="7" t="n"/>
       <c r="X145" s="7" t="n">
         <v>2</v>
       </c>
@@ -8243,19 +6907,9 @@
       </c>
     </row>
     <row r="146">
-      <c r="T146" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U146" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V146" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
       <c r="X146" s="4" t="n">
         <v>6</v>
       </c>
@@ -8284,19 +6938,9 @@
       </c>
     </row>
     <row r="147">
-      <c r="T147" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U147" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V147" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T147" s="7" t="n"/>
+      <c r="U147" s="7" t="n"/>
+      <c r="V147" s="7" t="n"/>
       <c r="X147" s="7" t="n">
         <v>2</v>
       </c>
@@ -8325,19 +6969,9 @@
       </c>
     </row>
     <row r="148">
-      <c r="T148" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U148" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V148" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T148" s="4" t="n"/>
+      <c r="U148" s="4" t="n"/>
+      <c r="V148" s="4" t="n"/>
       <c r="X148" s="4" t="n">
         <v>115</v>
       </c>
@@ -8366,19 +7000,9 @@
       </c>
     </row>
     <row r="149">
-      <c r="T149" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U149" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V149" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T149" s="7" t="n"/>
+      <c r="U149" s="7" t="n"/>
+      <c r="V149" s="7" t="n"/>
       <c r="X149" s="7" t="n">
         <v>20</v>
       </c>
@@ -8407,19 +7031,9 @@
       </c>
     </row>
     <row r="150">
-      <c r="T150" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U150" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="4" t="n"/>
+      <c r="V150" s="4" t="n"/>
       <c r="X150" s="4" t="n">
         <v>69</v>
       </c>
@@ -8448,19 +7062,9 @@
       </c>
     </row>
     <row r="151">
-      <c r="T151" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V151" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T151" s="7" t="n"/>
+      <c r="U151" s="7" t="n"/>
+      <c r="V151" s="7" t="n"/>
       <c r="X151" s="7" t="n">
         <v>41</v>
       </c>
@@ -8489,19 +7093,9 @@
       </c>
     </row>
     <row r="152">
-      <c r="T152" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U152" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="4" t="n"/>
+      <c r="V152" s="4" t="n"/>
       <c r="X152" s="4" t="n">
         <v>5</v>
       </c>
@@ -8530,19 +7124,9 @@
       </c>
     </row>
     <row r="153">
-      <c r="T153" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U153" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V153" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T153" s="7" t="n"/>
+      <c r="U153" s="7" t="n"/>
+      <c r="V153" s="7" t="n"/>
       <c r="X153" s="7" t="n">
         <v>95</v>
       </c>
@@ -8571,19 +7155,9 @@
       </c>
     </row>
     <row r="154">
-      <c r="T154" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U154" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T154" s="4" t="n"/>
+      <c r="U154" s="4" t="n"/>
+      <c r="V154" s="4" t="n"/>
       <c r="X154" s="4" t="n">
         <v>1</v>
       </c>
@@ -8612,19 +7186,9 @@
       </c>
     </row>
     <row r="155">
-      <c r="T155" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V155" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T155" s="7" t="n"/>
+      <c r="U155" s="7" t="n"/>
+      <c r="V155" s="7" t="n"/>
       <c r="X155" s="7" t="n">
         <v>9</v>
       </c>
@@ -8653,19 +7217,9 @@
       </c>
     </row>
     <row r="156">
-      <c r="T156" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U156" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="4" t="n"/>
+      <c r="V156" s="4" t="n"/>
       <c r="X156" s="4" t="n">
         <v>2</v>
       </c>
@@ -8694,19 +7248,9 @@
       </c>
     </row>
     <row r="157">
-      <c r="T157" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U157" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V157" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T157" s="7" t="n"/>
+      <c r="U157" s="7" t="n"/>
+      <c r="V157" s="7" t="n"/>
       <c r="X157" s="7" t="n">
         <v>114</v>
       </c>
@@ -8735,19 +7279,9 @@
       </c>
     </row>
     <row r="158">
-      <c r="T158" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U158" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V158" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T158" s="4" t="n"/>
+      <c r="U158" s="4" t="n"/>
+      <c r="V158" s="4" t="n"/>
       <c r="X158" s="4" t="n">
         <v>16</v>
       </c>
@@ -8776,19 +7310,9 @@
       </c>
     </row>
     <row r="159">
-      <c r="T159" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U159" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V159" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T159" s="7" t="n"/>
+      <c r="U159" s="7" t="n"/>
+      <c r="V159" s="7" t="n"/>
       <c r="X159" s="7" t="n">
         <v>60</v>
       </c>
@@ -8817,19 +7341,9 @@
       </c>
     </row>
     <row r="160">
-      <c r="T160" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U160" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="n">
-        <v>9927</v>
-      </c>
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="4" t="n"/>
+      <c r="V160" s="4" t="n"/>
       <c r="X160" s="4" t="n">
         <v>41</v>
       </c>
@@ -8858,19 +7372,9 @@
       </c>
     </row>
     <row r="161">
-      <c r="T161" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U161" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V161" s="7" t="n">
-        <v>9839</v>
-      </c>
+      <c r="T161" s="7" t="n"/>
+      <c r="U161" s="7" t="n"/>
+      <c r="V161" s="7" t="n"/>
       <c r="X161" s="7" t="n">
         <v>14</v>
       </c>
@@ -8899,19 +7403,9 @@
       </c>
     </row>
     <row r="162">
-      <c r="T162" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U162" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V162" s="4" t="n">
-        <v>9918</v>
-      </c>
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="4" t="n"/>
+      <c r="V162" s="4" t="n"/>
       <c r="X162" s="4" t="n">
         <v>84</v>
       </c>
@@ -8940,19 +7434,9 @@
       </c>
     </row>
     <row r="163">
-      <c r="T163" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U163" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V163" s="7" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T163" s="7" t="n"/>
+      <c r="U163" s="7" t="n"/>
+      <c r="V163" s="7" t="n"/>
       <c r="X163" s="7" t="n">
         <v>8</v>
       </c>
@@ -8981,19 +7465,9 @@
       </c>
     </row>
     <row r="164">
-      <c r="T164" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U164" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V164" s="4" t="n">
-        <v>10050</v>
-      </c>
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="4" t="n"/>
+      <c r="V164" s="4" t="n"/>
       <c r="X164" s="4" t="n">
         <v>1</v>
       </c>
@@ -9022,22 +7496,22 @@
       </c>
     </row>
     <row r="165">
-      <c r="T165" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U165" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V165" s="7" t="n">
-        <v>9768</v>
-      </c>
-      <c r="X165" s="7" t="n"/>
-      <c r="Y165" s="7" t="n"/>
-      <c r="Z165" s="7" t="n"/>
+      <c r="T165" s="7" t="n"/>
+      <c r="U165" s="7" t="n"/>
+      <c r="V165" s="7" t="n"/>
+      <c r="X165" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="Y165" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z165" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB165" s="7" t="n">
         <v>380</v>
       </c>
@@ -9053,22 +7527,22 @@
       </c>
     </row>
     <row r="166">
-      <c r="T166" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U166" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V166" s="4" t="n">
-        <v>9920</v>
-      </c>
-      <c r="X166" s="4" t="n"/>
-      <c r="Y166" s="4" t="n"/>
-      <c r="Z166" s="4" t="n"/>
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="4" t="n"/>
+      <c r="V166" s="4" t="n"/>
+      <c r="X166" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y166" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z166" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB166" s="4" t="n">
         <v>29</v>
       </c>
@@ -9084,22 +7558,22 @@
       </c>
     </row>
     <row r="167">
-      <c r="T167" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U167" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V167" s="7" t="n">
-        <v>10435</v>
-      </c>
-      <c r="X167" s="7" t="n"/>
-      <c r="Y167" s="7" t="n"/>
-      <c r="Z167" s="7" t="n"/>
+      <c r="T167" s="7" t="n"/>
+      <c r="U167" s="7" t="n"/>
+      <c r="V167" s="7" t="n"/>
+      <c r="X167" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y167" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z167" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB167" s="7" t="n">
         <v>157</v>
       </c>
@@ -9115,22 +7589,22 @@
       </c>
     </row>
     <row r="168">
-      <c r="T168" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U168" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V168" s="4" t="n">
-        <v>10434</v>
-      </c>
-      <c r="X168" s="4" t="n"/>
-      <c r="Y168" s="4" t="n"/>
-      <c r="Z168" s="4" t="n"/>
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="4" t="n"/>
+      <c r="V168" s="4" t="n"/>
+      <c r="X168" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y168" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z168" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB168" s="4" t="n">
         <v>54</v>
       </c>
@@ -9146,22 +7620,22 @@
       </c>
     </row>
     <row r="169">
-      <c r="T169" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U169" s="7" t="inlineStr">
+      <c r="T169" s="7" t="n"/>
+      <c r="U169" s="7" t="n"/>
+      <c r="V169" s="7" t="n"/>
+      <c r="X169" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y169" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z169" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="V169" s="7" t="n">
-        <v>10284</v>
-      </c>
-      <c r="X169" s="7" t="n"/>
-      <c r="Y169" s="7" t="n"/>
-      <c r="Z169" s="7" t="n"/>
       <c r="AB169" s="7" t="n">
         <v>43</v>
       </c>
@@ -9177,22 +7651,22 @@
       </c>
     </row>
     <row r="170">
-      <c r="T170" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U170" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V170" s="4" t="n">
-        <v>10458</v>
-      </c>
-      <c r="X170" s="4" t="n"/>
-      <c r="Y170" s="4" t="n"/>
-      <c r="Z170" s="4" t="n"/>
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="4" t="n"/>
+      <c r="V170" s="4" t="n"/>
+      <c r="X170" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y170" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z170" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB170" s="4" t="n">
         <v>154</v>
       </c>
@@ -9208,22 +7682,22 @@
       </c>
     </row>
     <row r="171">
-      <c r="T171" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U171" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V171" s="7" t="n">
-        <v>10153</v>
-      </c>
-      <c r="X171" s="7" t="n"/>
-      <c r="Y171" s="7" t="n"/>
-      <c r="Z171" s="7" t="n"/>
+      <c r="T171" s="7" t="n"/>
+      <c r="U171" s="7" t="n"/>
+      <c r="V171" s="7" t="n"/>
+      <c r="X171" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y171" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z171" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB171" s="7" t="n">
         <v>2</v>
       </c>
@@ -9239,19 +7713,9 @@
       </c>
     </row>
     <row r="172">
-      <c r="T172" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U172" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V172" s="4" t="n">
-        <v>9843</v>
-      </c>
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="4" t="n"/>
+      <c r="V172" s="4" t="n"/>
       <c r="X172" s="4" t="n"/>
       <c r="Y172" s="4" t="n"/>
       <c r="Z172" s="4" t="n"/>
@@ -9270,19 +7734,9 @@
       </c>
     </row>
     <row r="173">
-      <c r="T173" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U173" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V173" s="7" t="n">
-        <v>10433</v>
-      </c>
+      <c r="T173" s="7" t="n"/>
+      <c r="U173" s="7" t="n"/>
+      <c r="V173" s="7" t="n"/>
       <c r="X173" s="7" t="n"/>
       <c r="Y173" s="7" t="n"/>
       <c r="Z173" s="7" t="n"/>
@@ -9301,19 +7755,9 @@
       </c>
     </row>
     <row r="174">
-      <c r="T174" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U174" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V174" s="4" t="n">
-        <v>10670</v>
-      </c>
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="n"/>
+      <c r="V174" s="4" t="n"/>
       <c r="X174" s="4" t="n"/>
       <c r="Y174" s="4" t="n"/>
       <c r="Z174" s="4" t="n"/>
@@ -9332,19 +7776,9 @@
       </c>
     </row>
     <row r="175">
-      <c r="T175" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U175" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V175" s="7" t="n">
-        <v>10599</v>
-      </c>
+      <c r="T175" s="7" t="n"/>
+      <c r="U175" s="7" t="n"/>
+      <c r="V175" s="7" t="n"/>
       <c r="X175" s="7" t="n"/>
       <c r="Y175" s="7" t="n"/>
       <c r="Z175" s="7" t="n"/>
@@ -9363,19 +7797,9 @@
       </c>
     </row>
     <row r="176">
-      <c r="T176" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U176" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V176" s="4" t="n">
-        <v>10619</v>
-      </c>
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="4" t="n"/>
+      <c r="V176" s="4" t="n"/>
       <c r="X176" s="4" t="n"/>
       <c r="Y176" s="4" t="n"/>
       <c r="Z176" s="4" t="n"/>
@@ -9394,19 +7818,9 @@
       </c>
     </row>
     <row r="177">
-      <c r="T177" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U177" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V177" s="7" t="n">
-        <v>10415</v>
-      </c>
+      <c r="T177" s="7" t="n"/>
+      <c r="U177" s="7" t="n"/>
+      <c r="V177" s="7" t="n"/>
       <c r="X177" s="7" t="n"/>
       <c r="Y177" s="7" t="n"/>
       <c r="Z177" s="7" t="n"/>
@@ -9425,19 +7839,9 @@
       </c>
     </row>
     <row r="178">
-      <c r="T178" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U178" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V178" s="4" t="n">
-        <v>10065</v>
-      </c>
+      <c r="T178" s="4" t="n"/>
+      <c r="U178" s="4" t="n"/>
+      <c r="V178" s="4" t="n"/>
       <c r="X178" s="4" t="n"/>
       <c r="Y178" s="4" t="n"/>
       <c r="Z178" s="4" t="n"/>
@@ -9456,19 +7860,9 @@
       </c>
     </row>
     <row r="179">
-      <c r="T179" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U179" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V179" s="7" t="n">
-        <v>10158</v>
-      </c>
+      <c r="T179" s="7" t="n"/>
+      <c r="U179" s="7" t="n"/>
+      <c r="V179" s="7" t="n"/>
       <c r="X179" s="7" t="n"/>
       <c r="Y179" s="7" t="n"/>
       <c r="Z179" s="7" t="n"/>
@@ -9487,19 +7881,9 @@
       </c>
     </row>
     <row r="180">
-      <c r="T180" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U180" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation50987</t>
-        </is>
-      </c>
-      <c r="V180" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T180" s="4" t="n"/>
+      <c r="U180" s="4" t="n"/>
+      <c r="V180" s="4" t="n"/>
       <c r="X180" s="4" t="n"/>
       <c r="Y180" s="4" t="n"/>
       <c r="Z180" s="4" t="n"/>
@@ -9518,19 +7902,9 @@
       </c>
     </row>
     <row r="181">
-      <c r="T181" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U181" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation75114</t>
-        </is>
-      </c>
-      <c r="V181" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T181" s="7" t="n"/>
+      <c r="U181" s="7" t="n"/>
+      <c r="V181" s="7" t="n"/>
       <c r="X181" s="7" t="n"/>
       <c r="Y181" s="7" t="n"/>
       <c r="Z181" s="7" t="n"/>
@@ -9549,1684 +7923,214 @@
       </c>
     </row>
     <row r="182">
-      <c r="T182" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U182" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V182" s="4" t="n">
-        <v>21493</v>
-      </c>
+      <c r="T182" s="4" t="n"/>
+      <c r="U182" s="4" t="n"/>
+      <c r="V182" s="4" t="n"/>
       <c r="X182" s="4" t="n"/>
       <c r="Y182" s="4" t="n"/>
       <c r="Z182" s="4" t="n"/>
-      <c r="AB182" s="4" t="n"/>
-      <c r="AC182" s="4" t="n"/>
-      <c r="AD182" s="4" t="n"/>
+      <c r="AB182" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="AC182" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD182" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="183">
-      <c r="T183" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U183" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V183" s="7" t="n">
-        <v>21012</v>
-      </c>
+      <c r="T183" s="7" t="n"/>
+      <c r="U183" s="7" t="n"/>
+      <c r="V183" s="7" t="n"/>
       <c r="X183" s="7" t="n"/>
       <c r="Y183" s="7" t="n"/>
       <c r="Z183" s="7" t="n"/>
-      <c r="AB183" s="7" t="n"/>
-      <c r="AC183" s="7" t="n"/>
-      <c r="AD183" s="7" t="n"/>
+      <c r="AB183" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC183" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD183" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="184">
-      <c r="T184" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U184" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V184" s="4" t="n">
-        <v>21635</v>
-      </c>
+      <c r="T184" s="4" t="n"/>
+      <c r="U184" s="4" t="n"/>
+      <c r="V184" s="4" t="n"/>
       <c r="X184" s="4" t="n"/>
       <c r="Y184" s="4" t="n"/>
       <c r="Z184" s="4" t="n"/>
-      <c r="AB184" s="4" t="n"/>
-      <c r="AC184" s="4" t="n"/>
-      <c r="AD184" s="4" t="n"/>
+      <c r="AB184" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="AC184" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD184" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="185">
-      <c r="T185" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U185" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V185" s="7" t="n">
-        <v>21969</v>
-      </c>
+      <c r="T185" s="7" t="n"/>
+      <c r="U185" s="7" t="n"/>
+      <c r="V185" s="7" t="n"/>
       <c r="X185" s="7" t="n"/>
       <c r="Y185" s="7" t="n"/>
       <c r="Z185" s="7" t="n"/>
-      <c r="AB185" s="7" t="n"/>
-      <c r="AC185" s="7" t="n"/>
-      <c r="AD185" s="7" t="n"/>
+      <c r="AB185" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC185" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD185" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="T186" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U186" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V186" s="4" t="n">
-        <v>21723</v>
-      </c>
+      <c r="T186" s="4" t="n"/>
+      <c r="U186" s="4" t="n"/>
+      <c r="V186" s="4" t="n"/>
       <c r="X186" s="4" t="n"/>
       <c r="Y186" s="4" t="n"/>
       <c r="Z186" s="4" t="n"/>
-      <c r="AB186" s="4" t="n"/>
-      <c r="AC186" s="4" t="n"/>
-      <c r="AD186" s="4" t="n"/>
+      <c r="AB186" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD186" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="187">
-      <c r="T187" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U187" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V187" s="7" t="n">
-        <v>20879</v>
-      </c>
+      <c r="T187" s="7" t="n"/>
+      <c r="U187" s="7" t="n"/>
+      <c r="V187" s="7" t="n"/>
       <c r="X187" s="7" t="n"/>
       <c r="Y187" s="7" t="n"/>
       <c r="Z187" s="7" t="n"/>
-      <c r="AB187" s="7" t="n"/>
-      <c r="AC187" s="7" t="n"/>
-      <c r="AD187" s="7" t="n"/>
+      <c r="AB187" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC187" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD187" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
     </row>
     <row r="188">
-      <c r="T188" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U188" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V188" s="4" t="n">
-        <v>20783</v>
-      </c>
+      <c r="T188" s="4" t="n"/>
+      <c r="U188" s="4" t="n"/>
+      <c r="V188" s="4" t="n"/>
       <c r="X188" s="4" t="n"/>
       <c r="Y188" s="4" t="n"/>
       <c r="Z188" s="4" t="n"/>
-      <c r="AB188" s="4" t="n"/>
-      <c r="AC188" s="4" t="n"/>
-      <c r="AD188" s="4" t="n"/>
+      <c r="AB188" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC188" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD188" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="189">
-      <c r="T189" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U189" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V189" s="7" t="n">
-        <v>21875</v>
-      </c>
+      <c r="T189" s="7" t="n"/>
+      <c r="U189" s="7" t="n"/>
+      <c r="V189" s="7" t="n"/>
       <c r="X189" s="7" t="n"/>
       <c r="Y189" s="7" t="n"/>
       <c r="Z189" s="7" t="n"/>
-      <c r="AB189" s="7" t="n"/>
-      <c r="AC189" s="7" t="n"/>
-      <c r="AD189" s="7" t="n"/>
+      <c r="AB189" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC189" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD189" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="190">
-      <c r="T190" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U190" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V190" s="4" t="n">
-        <v>22103</v>
-      </c>
+      <c r="T190" s="4" t="n"/>
+      <c r="U190" s="4" t="n"/>
+      <c r="V190" s="4" t="n"/>
       <c r="X190" s="4" t="n"/>
       <c r="Y190" s="4" t="n"/>
       <c r="Z190" s="4" t="n"/>
-      <c r="AB190" s="4" t="n"/>
-      <c r="AC190" s="4" t="n"/>
-      <c r="AD190" s="4" t="n"/>
+      <c r="AB190" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC190" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD190" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="T191" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U191" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V191" s="7" t="n">
-        <v>22799</v>
-      </c>
+      <c r="T191" s="7" t="n"/>
+      <c r="U191" s="7" t="n"/>
+      <c r="V191" s="7" t="n"/>
       <c r="X191" s="7" t="n"/>
       <c r="Y191" s="7" t="n"/>
       <c r="Z191" s="7" t="n"/>
-      <c r="AB191" s="7" t="n"/>
-      <c r="AC191" s="7" t="n"/>
-      <c r="AD191" s="7" t="n"/>
-    </row>
-    <row r="192">
-      <c r="T192" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U192" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V192" s="4" t="n">
-        <v>22705</v>
-      </c>
-      <c r="X192" s="4" t="n"/>
-      <c r="Y192" s="4" t="n"/>
-      <c r="Z192" s="4" t="n"/>
-      <c r="AB192" s="4" t="n"/>
-      <c r="AC192" s="4" t="n"/>
-      <c r="AD192" s="4" t="n"/>
-    </row>
-    <row r="193">
-      <c r="T193" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U193" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V193" s="7" t="n">
-        <v>21885</v>
-      </c>
-      <c r="X193" s="7" t="n"/>
-      <c r="Y193" s="7" t="n"/>
-      <c r="Z193" s="7" t="n"/>
-      <c r="AB193" s="7" t="n"/>
-      <c r="AC193" s="7" t="n"/>
-      <c r="AD193" s="7" t="n"/>
-    </row>
-    <row r="194">
-      <c r="T194" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U194" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V194" s="4" t="n">
-        <v>21360</v>
-      </c>
-      <c r="X194" s="4" t="n"/>
-      <c r="Y194" s="4" t="n"/>
-      <c r="Z194" s="4" t="n"/>
-      <c r="AB194" s="4" t="n"/>
-      <c r="AC194" s="4" t="n"/>
-      <c r="AD194" s="4" t="n"/>
-    </row>
-    <row r="195">
-      <c r="T195" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U195" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V195" s="7" t="n">
-        <v>20612</v>
-      </c>
-      <c r="X195" s="7" t="n"/>
-      <c r="Y195" s="7" t="n"/>
-      <c r="Z195" s="7" t="n"/>
-      <c r="AB195" s="7" t="n"/>
-      <c r="AC195" s="7" t="n"/>
-      <c r="AD195" s="7" t="n"/>
-    </row>
-    <row r="196">
-      <c r="T196" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U196" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V196" s="4" t="n">
-        <v>22101</v>
-      </c>
-      <c r="X196" s="4" t="n"/>
-      <c r="Y196" s="4" t="n"/>
-      <c r="Z196" s="4" t="n"/>
-      <c r="AB196" s="4" t="n"/>
-      <c r="AC196" s="4" t="n"/>
-      <c r="AD196" s="4" t="n"/>
-    </row>
-    <row r="197">
-      <c r="T197" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U197" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V197" s="7" t="n">
-        <v>22665</v>
-      </c>
-      <c r="X197" s="7" t="n"/>
-      <c r="Y197" s="7" t="n"/>
-      <c r="Z197" s="7" t="n"/>
-      <c r="AB197" s="7" t="n"/>
-      <c r="AC197" s="7" t="n"/>
-      <c r="AD197" s="7" t="n"/>
-    </row>
-    <row r="198">
-      <c r="T198" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U198" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V198" s="4" t="n">
-        <v>22473</v>
-      </c>
-      <c r="X198" s="4" t="n"/>
-      <c r="Y198" s="4" t="n"/>
-      <c r="Z198" s="4" t="n"/>
-      <c r="AB198" s="4" t="n"/>
-      <c r="AC198" s="4" t="n"/>
-      <c r="AD198" s="4" t="n"/>
-    </row>
-    <row r="199">
-      <c r="T199" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U199" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V199" s="7" t="n">
-        <v>22903</v>
-      </c>
-      <c r="X199" s="7" t="n"/>
-      <c r="Y199" s="7" t="n"/>
-      <c r="Z199" s="7" t="n"/>
-      <c r="AB199" s="7" t="n"/>
-      <c r="AC199" s="7" t="n"/>
-      <c r="AD199" s="7" t="n"/>
-    </row>
-    <row r="200">
-      <c r="T200" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U200" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V200" s="4" t="n">
-        <v>21829</v>
-      </c>
-      <c r="X200" s="4" t="n"/>
-      <c r="Y200" s="4" t="n"/>
-      <c r="Z200" s="4" t="n"/>
-      <c r="AB200" s="4" t="n"/>
-      <c r="AC200" s="4" t="n"/>
-      <c r="AD200" s="4" t="n"/>
-    </row>
-    <row r="201">
-      <c r="T201" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U201" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V201" s="7" t="n">
-        <v>20959</v>
-      </c>
-      <c r="X201" s="7" t="n"/>
-      <c r="Y201" s="7" t="n"/>
-      <c r="Z201" s="7" t="n"/>
-      <c r="AB201" s="7" t="n"/>
-      <c r="AC201" s="7" t="n"/>
-      <c r="AD201" s="7" t="n"/>
-    </row>
-    <row r="202">
-      <c r="T202" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U202" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V202" s="4" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X202" s="4" t="n"/>
-      <c r="Y202" s="4" t="n"/>
-      <c r="Z202" s="4" t="n"/>
-      <c r="AB202" s="4" t="n"/>
-      <c r="AC202" s="4" t="n"/>
-      <c r="AD202" s="4" t="n"/>
-    </row>
-    <row r="203">
-      <c r="T203" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U203" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V203" s="7" t="n">
-        <v>16721</v>
-      </c>
-      <c r="X203" s="7" t="n"/>
-      <c r="Y203" s="7" t="n"/>
-      <c r="Z203" s="7" t="n"/>
-      <c r="AB203" s="7" t="n"/>
-      <c r="AC203" s="7" t="n"/>
-      <c r="AD203" s="7" t="n"/>
-    </row>
-    <row r="204">
-      <c r="T204" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U204" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V204" s="4" t="n">
-        <v>16586</v>
-      </c>
-      <c r="X204" s="4" t="n"/>
-      <c r="Y204" s="4" t="n"/>
-      <c r="Z204" s="4" t="n"/>
-      <c r="AB204" s="4" t="n"/>
-      <c r="AC204" s="4" t="n"/>
-      <c r="AD204" s="4" t="n"/>
-    </row>
-    <row r="205">
-      <c r="T205" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U205" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V205" s="7" t="n">
-        <v>16419</v>
-      </c>
-      <c r="X205" s="7" t="n"/>
-      <c r="Y205" s="7" t="n"/>
-      <c r="Z205" s="7" t="n"/>
-      <c r="AB205" s="7" t="n"/>
-      <c r="AC205" s="7" t="n"/>
-      <c r="AD205" s="7" t="n"/>
-    </row>
-    <row r="206">
-      <c r="T206" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U206" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V206" s="4" t="n">
-        <v>15946</v>
-      </c>
-      <c r="X206" s="4" t="n"/>
-      <c r="Y206" s="4" t="n"/>
-      <c r="Z206" s="4" t="n"/>
-      <c r="AB206" s="4" t="n"/>
-      <c r="AC206" s="4" t="n"/>
-      <c r="AD206" s="4" t="n"/>
-    </row>
-    <row r="207">
-      <c r="T207" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U207" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V207" s="7" t="n">
-        <v>16042</v>
-      </c>
-      <c r="X207" s="7" t="n"/>
-      <c r="Y207" s="7" t="n"/>
-      <c r="Z207" s="7" t="n"/>
-      <c r="AB207" s="7" t="n"/>
-      <c r="AC207" s="7" t="n"/>
-      <c r="AD207" s="7" t="n"/>
-    </row>
-    <row r="208">
-      <c r="T208" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U208" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V208" s="4" t="n">
-        <v>16409</v>
-      </c>
-      <c r="X208" s="4" t="n"/>
-      <c r="Y208" s="4" t="n"/>
-      <c r="Z208" s="4" t="n"/>
-      <c r="AB208" s="4" t="n"/>
-      <c r="AC208" s="4" t="n"/>
-      <c r="AD208" s="4" t="n"/>
-    </row>
-    <row r="209">
-      <c r="T209" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U209" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V209" s="7" t="n">
-        <v>16831</v>
-      </c>
-      <c r="X209" s="7" t="n"/>
-      <c r="Y209" s="7" t="n"/>
-      <c r="Z209" s="7" t="n"/>
-      <c r="AB209" s="7" t="n"/>
-      <c r="AC209" s="7" t="n"/>
-      <c r="AD209" s="7" t="n"/>
-    </row>
-    <row r="210">
-      <c r="T210" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U210" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V210" s="4" t="n">
-        <v>16886</v>
-      </c>
-      <c r="X210" s="4" t="n"/>
-      <c r="Y210" s="4" t="n"/>
-      <c r="Z210" s="4" t="n"/>
-      <c r="AB210" s="4" t="n"/>
-      <c r="AC210" s="4" t="n"/>
-      <c r="AD210" s="4" t="n"/>
-    </row>
-    <row r="211">
-      <c r="T211" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U211" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V211" s="7" t="n">
-        <v>16694</v>
-      </c>
-      <c r="X211" s="7" t="n"/>
-      <c r="Y211" s="7" t="n"/>
-      <c r="Z211" s="7" t="n"/>
-      <c r="AB211" s="7" t="n"/>
-      <c r="AC211" s="7" t="n"/>
-      <c r="AD211" s="7" t="n"/>
-    </row>
-    <row r="212">
-      <c r="T212" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U212" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V212" s="4" t="n">
-        <v>16659</v>
-      </c>
-      <c r="X212" s="4" t="n"/>
-      <c r="Y212" s="4" t="n"/>
-      <c r="Z212" s="4" t="n"/>
-      <c r="AB212" s="4" t="n"/>
-      <c r="AC212" s="4" t="n"/>
-      <c r="AD212" s="4" t="n"/>
-    </row>
-    <row r="213">
-      <c r="T213" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U213" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V213" s="7" t="n">
-        <v>16268</v>
-      </c>
-      <c r="X213" s="7" t="n"/>
-      <c r="Y213" s="7" t="n"/>
-      <c r="Z213" s="7" t="n"/>
-      <c r="AB213" s="7" t="n"/>
-      <c r="AC213" s="7" t="n"/>
-      <c r="AD213" s="7" t="n"/>
-    </row>
-    <row r="214">
-      <c r="T214" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U214" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V214" s="4" t="n">
-        <v>16259</v>
-      </c>
-      <c r="X214" s="4" t="n"/>
-      <c r="Y214" s="4" t="n"/>
-      <c r="Z214" s="4" t="n"/>
-      <c r="AB214" s="4" t="n"/>
-      <c r="AC214" s="4" t="n"/>
-      <c r="AD214" s="4" t="n"/>
-    </row>
-    <row r="215">
-      <c r="T215" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U215" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V215" s="7" t="n">
-        <v>16600</v>
-      </c>
-      <c r="X215" s="7" t="n"/>
-      <c r="Y215" s="7" t="n"/>
-      <c r="Z215" s="7" t="n"/>
-      <c r="AB215" s="7" t="n"/>
-      <c r="AC215" s="7" t="n"/>
-      <c r="AD215" s="7" t="n"/>
-    </row>
-    <row r="216">
-      <c r="T216" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U216" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V216" s="4" t="n">
-        <v>16913</v>
-      </c>
-      <c r="X216" s="4" t="n"/>
-      <c r="Y216" s="4" t="n"/>
-      <c r="Z216" s="4" t="n"/>
-      <c r="AB216" s="4" t="n"/>
-      <c r="AC216" s="4" t="n"/>
-      <c r="AD216" s="4" t="n"/>
-    </row>
-    <row r="217">
-      <c r="T217" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U217" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V217" s="7" t="n">
-        <v>16991</v>
-      </c>
-      <c r="X217" s="7" t="n"/>
-      <c r="Y217" s="7" t="n"/>
-      <c r="Z217" s="7" t="n"/>
-      <c r="AB217" s="7" t="n"/>
-      <c r="AC217" s="7" t="n"/>
-      <c r="AD217" s="7" t="n"/>
-    </row>
-    <row r="218">
-      <c r="T218" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U218" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V218" s="4" t="n">
-        <v>17365</v>
-      </c>
-      <c r="X218" s="4" t="n"/>
-      <c r="Y218" s="4" t="n"/>
-      <c r="Z218" s="4" t="n"/>
-      <c r="AB218" s="4" t="n"/>
-      <c r="AC218" s="4" t="n"/>
-      <c r="AD218" s="4" t="n"/>
-    </row>
-    <row r="219">
-      <c r="T219" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U219" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V219" s="7" t="n">
-        <v>16944</v>
-      </c>
-      <c r="X219" s="7" t="n"/>
-      <c r="Y219" s="7" t="n"/>
-      <c r="Z219" s="7" t="n"/>
-      <c r="AB219" s="7" t="n"/>
-      <c r="AC219" s="7" t="n"/>
-      <c r="AD219" s="7" t="n"/>
-    </row>
-    <row r="220">
-      <c r="T220" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U220" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V220" s="4" t="n">
-        <v>16518</v>
-      </c>
-      <c r="X220" s="4" t="n"/>
-      <c r="Y220" s="4" t="n"/>
-      <c r="Z220" s="4" t="n"/>
-      <c r="AB220" s="4" t="n"/>
-      <c r="AC220" s="4" t="n"/>
-      <c r="AD220" s="4" t="n"/>
-    </row>
-    <row r="221">
-      <c r="T221" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U221" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V221" s="7" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X221" s="7" t="n"/>
-      <c r="Y221" s="7" t="n"/>
-      <c r="Z221" s="7" t="n"/>
-      <c r="AB221" s="7" t="n"/>
-      <c r="AC221" s="7" t="n"/>
-      <c r="AD221" s="7" t="n"/>
-    </row>
-    <row r="222">
-      <c r="T222" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U222" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V222" s="4" t="n">
-        <v>724</v>
-      </c>
-      <c r="X222" s="4" t="n"/>
-      <c r="Y222" s="4" t="n"/>
-      <c r="Z222" s="4" t="n"/>
-      <c r="AB222" s="4" t="n"/>
-      <c r="AC222" s="4" t="n"/>
-      <c r="AD222" s="4" t="n"/>
-    </row>
-    <row r="223">
-      <c r="T223" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U223" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V223" s="7" t="n">
-        <v>746</v>
-      </c>
-      <c r="X223" s="7" t="n"/>
-      <c r="Y223" s="7" t="n"/>
-      <c r="Z223" s="7" t="n"/>
-      <c r="AB223" s="7" t="n"/>
-      <c r="AC223" s="7" t="n"/>
-      <c r="AD223" s="7" t="n"/>
-    </row>
-    <row r="224">
-      <c r="T224" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U224" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V224" s="4" t="n">
-        <v>723</v>
-      </c>
-      <c r="X224" s="4" t="n"/>
-      <c r="Y224" s="4" t="n"/>
-      <c r="Z224" s="4" t="n"/>
-      <c r="AB224" s="4" t="n"/>
-      <c r="AC224" s="4" t="n"/>
-      <c r="AD224" s="4" t="n"/>
-    </row>
-    <row r="225">
-      <c r="T225" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U225" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V225" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="X225" s="7" t="n"/>
-      <c r="Y225" s="7" t="n"/>
-      <c r="Z225" s="7" t="n"/>
-      <c r="AB225" s="7" t="n"/>
-      <c r="AC225" s="7" t="n"/>
-      <c r="AD225" s="7" t="n"/>
-    </row>
-    <row r="226">
-      <c r="T226" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U226" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V226" s="4" t="n">
-        <v>735</v>
-      </c>
-      <c r="X226" s="4" t="n"/>
-      <c r="Y226" s="4" t="n"/>
-      <c r="Z226" s="4" t="n"/>
-      <c r="AB226" s="4" t="n"/>
-      <c r="AC226" s="4" t="n"/>
-      <c r="AD226" s="4" t="n"/>
-    </row>
-    <row r="227">
-      <c r="T227" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U227" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V227" s="7" t="n">
-        <v>714</v>
-      </c>
-      <c r="X227" s="7" t="n"/>
-      <c r="Y227" s="7" t="n"/>
-      <c r="Z227" s="7" t="n"/>
-      <c r="AB227" s="7" t="n"/>
-      <c r="AC227" s="7" t="n"/>
-      <c r="AD227" s="7" t="n"/>
-    </row>
-    <row r="228">
-      <c r="T228" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U228" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V228" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X228" s="4" t="n"/>
-      <c r="Y228" s="4" t="n"/>
-      <c r="Z228" s="4" t="n"/>
-      <c r="AB228" s="4" t="n"/>
-      <c r="AC228" s="4" t="n"/>
-      <c r="AD228" s="4" t="n"/>
-    </row>
-    <row r="229">
-      <c r="T229" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U229" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V229" s="7" t="n">
-        <v>729</v>
-      </c>
-      <c r="X229" s="7" t="n"/>
-      <c r="Y229" s="7" t="n"/>
-      <c r="Z229" s="7" t="n"/>
-      <c r="AB229" s="7" t="n"/>
-      <c r="AC229" s="7" t="n"/>
-      <c r="AD229" s="7" t="n"/>
-    </row>
-    <row r="230">
-      <c r="T230" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U230" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V230" s="4" t="n">
-        <v>719</v>
-      </c>
-      <c r="X230" s="4" t="n"/>
-      <c r="Y230" s="4" t="n"/>
-      <c r="Z230" s="4" t="n"/>
-      <c r="AB230" s="4" t="n"/>
-      <c r="AC230" s="4" t="n"/>
-      <c r="AD230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="T231" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U231" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V231" s="7" t="n">
-        <v>719</v>
-      </c>
-      <c r="X231" s="7" t="n"/>
-      <c r="Y231" s="7" t="n"/>
-      <c r="Z231" s="7" t="n"/>
-      <c r="AB231" s="7" t="n"/>
-      <c r="AC231" s="7" t="n"/>
-      <c r="AD231" s="7" t="n"/>
-    </row>
-    <row r="232">
-      <c r="T232" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U232" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V232" s="4" t="n">
-        <v>730</v>
-      </c>
-      <c r="X232" s="4" t="n"/>
-      <c r="Y232" s="4" t="n"/>
-      <c r="Z232" s="4" t="n"/>
-      <c r="AB232" s="4" t="n"/>
-      <c r="AC232" s="4" t="n"/>
-      <c r="AD232" s="4" t="n"/>
-    </row>
-    <row r="233">
-      <c r="T233" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U233" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V233" s="7" t="n">
-        <v>740</v>
-      </c>
-      <c r="X233" s="7" t="n"/>
-      <c r="Y233" s="7" t="n"/>
-      <c r="Z233" s="7" t="n"/>
-      <c r="AB233" s="7" t="n"/>
-      <c r="AC233" s="7" t="n"/>
-      <c r="AD233" s="7" t="n"/>
-    </row>
-    <row r="234">
-      <c r="T234" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U234" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V234" s="4" t="n">
-        <v>708</v>
-      </c>
-      <c r="X234" s="4" t="n"/>
-      <c r="Y234" s="4" t="n"/>
-      <c r="Z234" s="4" t="n"/>
-      <c r="AB234" s="4" t="n"/>
-      <c r="AC234" s="4" t="n"/>
-      <c r="AD234" s="4" t="n"/>
-    </row>
-    <row r="235">
-      <c r="T235" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U235" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V235" s="7" t="n">
-        <v>698</v>
-      </c>
-      <c r="X235" s="7" t="n"/>
-      <c r="Y235" s="7" t="n"/>
-      <c r="Z235" s="7" t="n"/>
-      <c r="AB235" s="7" t="n"/>
-      <c r="AC235" s="7" t="n"/>
-      <c r="AD235" s="7" t="n"/>
-    </row>
-    <row r="236">
-      <c r="T236" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U236" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V236" s="4" t="n">
-        <v>691</v>
-      </c>
-      <c r="X236" s="4" t="n"/>
-      <c r="Y236" s="4" t="n"/>
-      <c r="Z236" s="4" t="n"/>
-      <c r="AB236" s="4" t="n"/>
-      <c r="AC236" s="4" t="n"/>
-      <c r="AD236" s="4" t="n"/>
-    </row>
-    <row r="237">
-      <c r="T237" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U237" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V237" s="7" t="n">
-        <v>695</v>
-      </c>
-      <c r="X237" s="7" t="n"/>
-      <c r="Y237" s="7" t="n"/>
-      <c r="Z237" s="7" t="n"/>
-      <c r="AB237" s="7" t="n"/>
-      <c r="AC237" s="7" t="n"/>
-      <c r="AD237" s="7" t="n"/>
-    </row>
-    <row r="238">
-      <c r="T238" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U238" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V238" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X238" s="4" t="n"/>
-      <c r="Y238" s="4" t="n"/>
-      <c r="Z238" s="4" t="n"/>
-      <c r="AB238" s="4" t="n"/>
-      <c r="AC238" s="4" t="n"/>
-      <c r="AD238" s="4" t="n"/>
-    </row>
-    <row r="239">
-      <c r="T239" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U239" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V239" s="7" t="n">
-        <v>701</v>
-      </c>
-      <c r="X239" s="7" t="n"/>
-      <c r="Y239" s="7" t="n"/>
-      <c r="Z239" s="7" t="n"/>
-      <c r="AB239" s="7" t="n"/>
-      <c r="AC239" s="7" t="n"/>
-      <c r="AD239" s="7" t="n"/>
-    </row>
-    <row r="240">
-      <c r="T240" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U240" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V240" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X240" s="4" t="n"/>
-      <c r="Y240" s="4" t="n"/>
-      <c r="Z240" s="4" t="n"/>
-      <c r="AB240" s="4" t="n"/>
-      <c r="AC240" s="4" t="n"/>
-      <c r="AD240" s="4" t="n"/>
-    </row>
-    <row r="241">
-      <c r="T241" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U241" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V241" s="7" t="n">
-        <v>704</v>
-      </c>
-      <c r="X241" s="7" t="n"/>
-      <c r="Y241" s="7" t="n"/>
-      <c r="Z241" s="7" t="n"/>
-      <c r="AB241" s="7" t="n"/>
-      <c r="AC241" s="7" t="n"/>
-      <c r="AD241" s="7" t="n"/>
-    </row>
-    <row r="242">
-      <c r="T242" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U242" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V242" s="4" t="n">
-        <v>2188</v>
-      </c>
-      <c r="X242" s="4" t="n"/>
-      <c r="Y242" s="4" t="n"/>
-      <c r="Z242" s="4" t="n"/>
-      <c r="AB242" s="4" t="n"/>
-      <c r="AC242" s="4" t="n"/>
-      <c r="AD242" s="4" t="n"/>
-    </row>
-    <row r="243">
-      <c r="T243" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U243" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V243" s="7" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X243" s="7" t="n"/>
-      <c r="Y243" s="7" t="n"/>
-      <c r="Z243" s="7" t="n"/>
-      <c r="AB243" s="7" t="n"/>
-      <c r="AC243" s="7" t="n"/>
-      <c r="AD243" s="7" t="n"/>
-    </row>
-    <row r="244">
-      <c r="T244" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U244" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V244" s="4" t="n">
-        <v>2338</v>
-      </c>
-      <c r="X244" s="4" t="n"/>
-      <c r="Y244" s="4" t="n"/>
-      <c r="Z244" s="4" t="n"/>
-      <c r="AB244" s="4" t="n"/>
-      <c r="AC244" s="4" t="n"/>
-      <c r="AD244" s="4" t="n"/>
-    </row>
-    <row r="245">
-      <c r="T245" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U245" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V245" s="7" t="n">
-        <v>2152</v>
-      </c>
-      <c r="X245" s="7" t="n"/>
-      <c r="Y245" s="7" t="n"/>
-      <c r="Z245" s="7" t="n"/>
-      <c r="AB245" s="7" t="n"/>
-      <c r="AC245" s="7" t="n"/>
-      <c r="AD245" s="7" t="n"/>
-    </row>
-    <row r="246">
-      <c r="T246" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U246" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V246" s="4" t="n">
-        <v>2003</v>
-      </c>
-      <c r="X246" s="4" t="n"/>
-      <c r="Y246" s="4" t="n"/>
-      <c r="Z246" s="4" t="n"/>
-      <c r="AB246" s="4" t="n"/>
-      <c r="AC246" s="4" t="n"/>
-      <c r="AD246" s="4" t="n"/>
-    </row>
-    <row r="247">
-      <c r="T247" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U247" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V247" s="7" t="n">
-        <v>1895</v>
-      </c>
-      <c r="X247" s="7" t="n"/>
-      <c r="Y247" s="7" t="n"/>
-      <c r="Z247" s="7" t="n"/>
-      <c r="AB247" s="7" t="n"/>
-      <c r="AC247" s="7" t="n"/>
-      <c r="AD247" s="7" t="n"/>
-    </row>
-    <row r="248">
-      <c r="T248" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U248" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V248" s="4" t="n">
-        <v>1935</v>
-      </c>
-      <c r="X248" s="4" t="n"/>
-      <c r="Y248" s="4" t="n"/>
-      <c r="Z248" s="4" t="n"/>
-      <c r="AB248" s="4" t="n"/>
-      <c r="AC248" s="4" t="n"/>
-      <c r="AD248" s="4" t="n"/>
-    </row>
-    <row r="249">
-      <c r="T249" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U249" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V249" s="7" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X249" s="7" t="n"/>
-      <c r="Y249" s="7" t="n"/>
-      <c r="Z249" s="7" t="n"/>
-      <c r="AB249" s="7" t="n"/>
-      <c r="AC249" s="7" t="n"/>
-      <c r="AD249" s="7" t="n"/>
-    </row>
-    <row r="250">
-      <c r="T250" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U250" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V250" s="4" t="n">
-        <v>2049</v>
-      </c>
-      <c r="X250" s="4" t="n"/>
-      <c r="Y250" s="4" t="n"/>
-      <c r="Z250" s="4" t="n"/>
-      <c r="AB250" s="4" t="n"/>
-      <c r="AC250" s="4" t="n"/>
-      <c r="AD250" s="4" t="n"/>
-    </row>
-    <row r="251">
-      <c r="T251" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U251" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V251" s="7" t="n">
-        <v>2325</v>
-      </c>
-      <c r="X251" s="7" t="n"/>
-      <c r="Y251" s="7" t="n"/>
-      <c r="Z251" s="7" t="n"/>
-      <c r="AB251" s="7" t="n"/>
-      <c r="AC251" s="7" t="n"/>
-      <c r="AD251" s="7" t="n"/>
-    </row>
-    <row r="252">
-      <c r="T252" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U252" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V252" s="4" t="n">
-        <v>2216</v>
-      </c>
-      <c r="X252" s="4" t="n"/>
-      <c r="Y252" s="4" t="n"/>
-      <c r="Z252" s="4" t="n"/>
-      <c r="AB252" s="4" t="n"/>
-      <c r="AC252" s="4" t="n"/>
-      <c r="AD252" s="4" t="n"/>
-    </row>
-    <row r="253">
-      <c r="T253" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U253" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V253" s="7" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X253" s="7" t="n"/>
-      <c r="Y253" s="7" t="n"/>
-      <c r="Z253" s="7" t="n"/>
-      <c r="AB253" s="7" t="n"/>
-      <c r="AC253" s="7" t="n"/>
-      <c r="AD253" s="7" t="n"/>
-    </row>
-    <row r="254">
-      <c r="T254" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U254" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V254" s="4" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X254" s="4" t="n"/>
-      <c r="Y254" s="4" t="n"/>
-      <c r="Z254" s="4" t="n"/>
-      <c r="AB254" s="4" t="n"/>
-      <c r="AC254" s="4" t="n"/>
-      <c r="AD254" s="4" t="n"/>
-    </row>
-    <row r="255">
-      <c r="T255" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U255" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V255" s="7" t="n">
-        <v>2035</v>
-      </c>
-      <c r="X255" s="7" t="n"/>
-      <c r="Y255" s="7" t="n"/>
-      <c r="Z255" s="7" t="n"/>
-      <c r="AB255" s="7" t="n"/>
-      <c r="AC255" s="7" t="n"/>
-      <c r="AD255" s="7" t="n"/>
-    </row>
-    <row r="256">
-      <c r="T256" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U256" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V256" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="X256" s="4" t="n"/>
-      <c r="Y256" s="4" t="n"/>
-      <c r="Z256" s="4" t="n"/>
-      <c r="AB256" s="4" t="n"/>
-      <c r="AC256" s="4" t="n"/>
-      <c r="AD256" s="4" t="n"/>
-    </row>
-    <row r="257">
-      <c r="T257" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U257" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V257" s="7" t="n">
-        <v>2156</v>
-      </c>
-      <c r="X257" s="7" t="n"/>
-      <c r="Y257" s="7" t="n"/>
-      <c r="Z257" s="7" t="n"/>
-      <c r="AB257" s="7" t="n"/>
-      <c r="AC257" s="7" t="n"/>
-      <c r="AD257" s="7" t="n"/>
-    </row>
-    <row r="258">
-      <c r="T258" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U258" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V258" s="4" t="n">
-        <v>2437</v>
-      </c>
-      <c r="X258" s="4" t="n"/>
-      <c r="Y258" s="4" t="n"/>
-      <c r="Z258" s="4" t="n"/>
-      <c r="AB258" s="4" t="n"/>
-      <c r="AC258" s="4" t="n"/>
-      <c r="AD258" s="4" t="n"/>
-    </row>
-    <row r="259">
-      <c r="T259" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U259" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V259" s="7" t="n">
-        <v>2214</v>
-      </c>
-      <c r="X259" s="7" t="n"/>
-      <c r="Y259" s="7" t="n"/>
-      <c r="Z259" s="7" t="n"/>
-      <c r="AB259" s="7" t="n"/>
-      <c r="AC259" s="7" t="n"/>
-      <c r="AD259" s="7" t="n"/>
-    </row>
-    <row r="260">
-      <c r="T260" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U260" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V260" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="X260" s="4" t="n"/>
-      <c r="Y260" s="4" t="n"/>
-      <c r="Z260" s="4" t="n"/>
-      <c r="AB260" s="4" t="n"/>
-      <c r="AC260" s="4" t="n"/>
-      <c r="AD260" s="4" t="n"/>
-    </row>
-    <row r="261">
-      <c r="T261" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U261" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V261" s="7" t="n">
-        <v>1973</v>
-      </c>
-      <c r="X261" s="7" t="n"/>
-      <c r="Y261" s="7" t="n"/>
-      <c r="Z261" s="7" t="n"/>
-      <c r="AB261" s="7" t="n"/>
-      <c r="AC261" s="7" t="n"/>
-      <c r="AD261" s="7" t="n"/>
+      <c r="AB191" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC191" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD191" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD261"/>
+  <dimension ref="A1:AD287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2927,29 +2927,49 @@
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="D22" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C22)</f>
+        <v/>
+      </c>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="G22" s="4">
+        <f>ROUND((1-E22/D22)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>MIN(1,(G22-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
+      <c r="K22" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="4">
+        <f>ROUND(100*(1-K22/D22),2)</f>
+        <v/>
+      </c>
+      <c r="M22" s="4">
+        <f>MAX(0,(L22-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N22" s="4">
+        <f>$B$2+H22+M22</f>
+        <v/>
+      </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr"/>
       <c r="V22" s="4" t="n">
-        <v>5365</v>
+        <v>1</v>
       </c>
       <c r="X22" s="4" t="n">
         <v>9</v>
@@ -2986,29 +3006,49 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
+      <c r="D23" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C23)</f>
+        <v/>
+      </c>
       <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+      <c r="G23" s="7">
+        <f>ROUND((1-E23/D23)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H23" s="7">
+        <f>MIN(1,(G23-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
+      <c r="K23" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="7">
+        <f>ROUND(100*(1-K23/D23),2)</f>
+        <v/>
+      </c>
+      <c r="M23" s="7">
+        <f>MAX(0,(L23-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N23" s="7">
+        <f>$B$2+H23+M23</f>
+        <v/>
+      </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr"/>
       <c r="V23" s="7" t="n">
-        <v>5741</v>
+        <v>1</v>
       </c>
       <c r="X23" s="7" t="n">
         <v>74</v>
@@ -3058,7 +3098,7 @@
       <c r="N24" s="4" t="n"/>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
@@ -3067,7 +3107,7 @@
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>5451</v>
+        <v>5365</v>
       </c>
       <c r="X24" s="4" t="n">
         <v>11</v>
@@ -3117,7 +3157,7 @@
       <c r="N25" s="7" t="n"/>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -3126,7 +3166,7 @@
         </is>
       </c>
       <c r="V25" s="7" t="n">
-        <v>5458</v>
+        <v>5741</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>101</v>
@@ -3176,7 +3216,7 @@
       <c r="N26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
@@ -3185,7 +3225,7 @@
         </is>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5664</v>
+        <v>5451</v>
       </c>
       <c r="X26" s="4" t="n">
         <v>11</v>
@@ -3235,7 +3275,7 @@
       <c r="N27" s="7" t="n"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -3244,7 +3284,7 @@
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>5241</v>
+        <v>5458</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>73</v>
@@ -3294,7 +3334,7 @@
       <c r="N28" s="4" t="n"/>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
@@ -3303,7 +3343,7 @@
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5102</v>
+        <v>5664</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>31</v>
@@ -3353,7 +3393,7 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -3362,7 +3402,7 @@
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>5388</v>
+        <v>5241</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>13</v>
@@ -3412,7 +3452,7 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3421,7 +3461,7 @@
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5339</v>
+        <v>5102</v>
       </c>
       <c r="X30" s="4" t="n">
         <v>78</v>
@@ -3471,7 +3511,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -3480,7 +3520,7 @@
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>5348</v>
+        <v>5388</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>1</v>
@@ -3539,7 +3579,7 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3548,7 +3588,7 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5329</v>
+        <v>5339</v>
       </c>
       <c r="X32" s="4" t="n">
         <v>9</v>
@@ -3579,7 +3619,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D21)</f>
+        <f>AVERAGE(D2:D23)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3589,7 +3629,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H21)</f>
+        <f>AVERAGE(H2:H23)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3612,7 +3652,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -3621,7 +3661,7 @@
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>5436</v>
+        <v>5348</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>1</v>
@@ -3653,7 +3693,7 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3662,7 +3702,7 @@
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5081</v>
+        <v>5329</v>
       </c>
       <c r="X34" s="4" t="n">
         <v>119</v>
@@ -3694,7 +3734,7 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -3703,7 +3743,7 @@
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>5034</v>
+        <v>5436</v>
       </c>
       <c r="X35" s="7" t="n">
         <v>13</v>
@@ -3735,7 +3775,7 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
@@ -3744,7 +3784,7 @@
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>5557</v>
+        <v>5081</v>
       </c>
       <c r="X36" s="4" t="n">
         <v>67</v>
@@ -3776,7 +3816,7 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
@@ -3785,7 +3825,7 @@
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>5513</v>
+        <v>5034</v>
       </c>
       <c r="X37" s="7" t="n">
         <v>32</v>
@@ -3817,7 +3857,7 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
@@ -3826,7 +3866,7 @@
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>5477</v>
+        <v>5557</v>
       </c>
       <c r="X38" s="4" t="n">
         <v>13</v>
@@ -3858,7 +3898,7 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
@@ -3867,7 +3907,7 @@
         </is>
       </c>
       <c r="V39" s="7" t="n">
-        <v>5526</v>
+        <v>5513</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>93</v>
@@ -3899,7 +3939,7 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
@@ -3908,7 +3948,7 @@
         </is>
       </c>
       <c r="V40" s="4" t="n">
-        <v>5339</v>
+        <v>5477</v>
       </c>
       <c r="X40" s="4" t="n">
         <v>12</v>
@@ -3940,7 +3980,7 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
@@ -3949,7 +3989,7 @@
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>4933</v>
+        <v>5526</v>
       </c>
       <c r="X41" s="7" t="n">
         <v>2</v>
@@ -3981,16 +4021,16 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>14969</v>
+        <v>5339</v>
       </c>
       <c r="X42" s="4" t="n">
         <v>113</v>
@@ -4022,16 +4062,16 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>14818</v>
+        <v>4933</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>12</v>
@@ -4063,16 +4103,16 @@
     <row r="44">
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U44" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>15263</v>
+        <v>4866</v>
       </c>
       <c r="X44" s="4" t="n">
         <v>69</v>
@@ -4104,16 +4144,16 @@
     <row r="45">
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V45" s="7" t="n">
-        <v>14815</v>
+        <v>5232</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>40</v>
@@ -4145,7 +4185,7 @@
     <row r="46">
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
@@ -4154,7 +4194,7 @@
         </is>
       </c>
       <c r="V46" s="4" t="n">
-        <v>14968</v>
+        <v>14969</v>
       </c>
       <c r="X46" s="4" t="n">
         <v>17</v>
@@ -4186,7 +4226,7 @@
     <row r="47">
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
@@ -4195,7 +4235,7 @@
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>14113</v>
+        <v>14818</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>83</v>
@@ -4227,7 +4267,7 @@
     <row r="48">
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
@@ -4236,7 +4276,7 @@
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>14162</v>
+        <v>15263</v>
       </c>
       <c r="X48" s="4" t="n">
         <v>9</v>
@@ -4268,7 +4308,7 @@
     <row r="49">
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
@@ -4309,7 +4349,7 @@
     <row r="50">
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U50" s="4" t="inlineStr">
@@ -4318,7 +4358,7 @@
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>14815</v>
+        <v>14968</v>
       </c>
       <c r="X50" s="4" t="n">
         <v>19</v>
@@ -4350,7 +4390,7 @@
     <row r="51">
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
@@ -4359,7 +4399,7 @@
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>15546</v>
+        <v>14113</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>55</v>
@@ -4391,7 +4431,7 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
@@ -4400,7 +4440,7 @@
         </is>
       </c>
       <c r="V52" s="4" t="n">
-        <v>14882</v>
+        <v>14162</v>
       </c>
       <c r="X52" s="4" t="n">
         <v>35</v>
@@ -4432,7 +4472,7 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
@@ -4441,7 +4481,7 @@
         </is>
       </c>
       <c r="V53" s="7" t="n">
-        <v>14998</v>
+        <v>14815</v>
       </c>
       <c r="X53" s="7" t="n">
         <v>15</v>
@@ -4473,7 +4513,7 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
@@ -4482,7 +4522,7 @@
         </is>
       </c>
       <c r="V54" s="4" t="n">
-        <v>14354</v>
+        <v>14815</v>
       </c>
       <c r="X54" s="4" t="n">
         <v>82</v>
@@ -4514,7 +4554,7 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
@@ -4523,7 +4563,7 @@
         </is>
       </c>
       <c r="V55" s="7" t="n">
-        <v>14362</v>
+        <v>15546</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>1</v>
@@ -4555,7 +4595,7 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
@@ -4564,7 +4604,7 @@
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>15089</v>
+        <v>14882</v>
       </c>
       <c r="X56" s="4" t="n">
         <v>14</v>
@@ -4596,7 +4636,7 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
@@ -4605,7 +4645,7 @@
         </is>
       </c>
       <c r="V57" s="7" t="n">
-        <v>14802</v>
+        <v>14998</v>
       </c>
       <c r="X57" s="7" t="n">
         <v>2</v>
@@ -4637,7 +4677,7 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U58" s="4" t="inlineStr">
@@ -4646,7 +4686,7 @@
         </is>
       </c>
       <c r="V58" s="4" t="n">
-        <v>15349</v>
+        <v>14354</v>
       </c>
       <c r="X58" s="4" t="n">
         <v>101</v>
@@ -4678,7 +4718,7 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
@@ -4687,7 +4727,7 @@
         </is>
       </c>
       <c r="V59" s="7" t="n">
-        <v>14872</v>
+        <v>14362</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>10</v>
@@ -4719,7 +4759,7 @@
     <row r="60">
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U60" s="4" t="inlineStr">
@@ -4728,7 +4768,7 @@
         </is>
       </c>
       <c r="V60" s="4" t="n">
-        <v>15054</v>
+        <v>15089</v>
       </c>
       <c r="X60" s="4" t="n">
         <v>72</v>
@@ -4760,7 +4800,7 @@
     <row r="61">
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
@@ -4769,7 +4809,7 @@
         </is>
       </c>
       <c r="V61" s="7" t="n">
-        <v>14169</v>
+        <v>14802</v>
       </c>
       <c r="X61" s="7" t="n">
         <v>35</v>
@@ -4801,16 +4841,16 @@
     <row r="62">
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U62" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V62" s="4" t="n">
-        <v>77546</v>
+        <v>15349</v>
       </c>
       <c r="X62" s="4" t="n">
         <v>13</v>
@@ -4842,16 +4882,16 @@
     <row r="63">
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V63" s="7" t="n">
-        <v>77823</v>
+        <v>14872</v>
       </c>
       <c r="X63" s="7" t="n">
         <v>71</v>
@@ -4883,16 +4923,16 @@
     <row r="64">
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V64" s="4" t="n">
-        <v>81723</v>
+        <v>15054</v>
       </c>
       <c r="X64" s="4" t="n">
         <v>8</v>
@@ -4924,16 +4964,16 @@
     <row r="65">
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V65" s="7" t="n">
-        <v>78398</v>
+        <v>14169</v>
       </c>
       <c r="X65" s="7" t="n">
         <v>2</v>
@@ -4965,16 +5005,16 @@
     <row r="66">
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>78030</v>
+        <v>14056</v>
       </c>
       <c r="X66" s="4" t="n">
         <v>125</v>
@@ -5006,16 +5046,16 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V67" s="7" t="n">
-        <v>76646</v>
+        <v>15058</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>11</v>
@@ -5047,7 +5087,7 @@
     <row r="68">
       <c r="T68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U68" s="4" t="inlineStr">
@@ -5056,7 +5096,7 @@
         </is>
       </c>
       <c r="V68" s="4" t="n">
-        <v>76742</v>
+        <v>77546</v>
       </c>
       <c r="X68" s="4" t="n">
         <v>67</v>
@@ -5088,7 +5128,7 @@
     <row r="69">
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
@@ -5097,7 +5137,7 @@
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>79003</v>
+        <v>77823</v>
       </c>
       <c r="X69" s="7" t="n">
         <v>27</v>
@@ -5129,7 +5169,7 @@
     <row r="70">
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U70" s="4" t="inlineStr">
@@ -5138,7 +5178,7 @@
         </is>
       </c>
       <c r="V70" s="4" t="n">
-        <v>78849</v>
+        <v>81723</v>
       </c>
       <c r="X70" s="4" t="n">
         <v>17</v>
@@ -5170,7 +5210,7 @@
     <row r="71">
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U71" s="7" t="inlineStr">
@@ -5179,7 +5219,7 @@
         </is>
       </c>
       <c r="V71" s="7" t="n">
-        <v>80667</v>
+        <v>78398</v>
       </c>
       <c r="X71" s="7" t="n">
         <v>85</v>
@@ -5211,7 +5251,7 @@
     <row r="72">
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U72" s="4" t="inlineStr">
@@ -5220,7 +5260,7 @@
         </is>
       </c>
       <c r="V72" s="4" t="n">
-        <v>78640</v>
+        <v>78030</v>
       </c>
       <c r="X72" s="4" t="n">
         <v>14</v>
@@ -5252,7 +5292,7 @@
     <row r="73">
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U73" s="7" t="inlineStr">
@@ -5261,7 +5301,7 @@
         </is>
       </c>
       <c r="V73" s="7" t="n">
-        <v>79108</v>
+        <v>76646</v>
       </c>
       <c r="X73" s="7" t="n">
         <v>4</v>
@@ -5293,7 +5333,7 @@
     <row r="74">
       <c r="T74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U74" s="4" t="inlineStr">
@@ -5302,7 +5342,7 @@
         </is>
       </c>
       <c r="V74" s="4" t="n">
-        <v>76911</v>
+        <v>76742</v>
       </c>
       <c r="X74" s="4" t="n">
         <v>126</v>
@@ -5334,7 +5374,7 @@
     <row r="75">
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U75" s="7" t="inlineStr">
@@ -5343,7 +5383,7 @@
         </is>
       </c>
       <c r="V75" s="7" t="n">
-        <v>77273</v>
+        <v>79003</v>
       </c>
       <c r="X75" s="7" t="n">
         <v>23</v>
@@ -5375,7 +5415,7 @@
     <row r="76">
       <c r="T76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U76" s="4" t="inlineStr">
@@ -5384,7 +5424,7 @@
         </is>
       </c>
       <c r="V76" s="4" t="n">
-        <v>80657</v>
+        <v>78849</v>
       </c>
       <c r="X76" s="4" t="n">
         <v>65</v>
@@ -5416,7 +5456,7 @@
     <row r="77">
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U77" s="7" t="inlineStr">
@@ -5425,7 +5465,7 @@
         </is>
       </c>
       <c r="V77" s="7" t="n">
-        <v>79898</v>
+        <v>80667</v>
       </c>
       <c r="X77" s="7" t="n">
         <v>28</v>
@@ -5457,7 +5497,7 @@
     <row r="78">
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U78" s="4" t="inlineStr">
@@ -5466,7 +5506,7 @@
         </is>
       </c>
       <c r="V78" s="4" t="n">
-        <v>82443</v>
+        <v>78640</v>
       </c>
       <c r="X78" s="4" t="n">
         <v>19</v>
@@ -5498,7 +5538,7 @@
     <row r="79">
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U79" s="7" t="inlineStr">
@@ -5507,7 +5547,7 @@
         </is>
       </c>
       <c r="V79" s="7" t="n">
-        <v>80658</v>
+        <v>79108</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>91</v>
@@ -5539,7 +5579,7 @@
     <row r="80">
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U80" s="4" t="inlineStr">
@@ -5548,7 +5588,7 @@
         </is>
       </c>
       <c r="V80" s="4" t="n">
-        <v>78475</v>
+        <v>76911</v>
       </c>
       <c r="X80" s="4" t="n">
         <v>21</v>
@@ -5580,7 +5620,7 @@
     <row r="81">
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U81" s="7" t="inlineStr">
@@ -5589,7 +5629,7 @@
         </is>
       </c>
       <c r="V81" s="7" t="n">
-        <v>76874</v>
+        <v>77273</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>2</v>
@@ -5621,16 +5661,16 @@
     <row r="82">
       <c r="T82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U82" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V82" s="4" t="n">
-        <v>721</v>
+        <v>80657</v>
       </c>
       <c r="X82" s="4" t="n">
         <v>99</v>
@@ -5662,16 +5702,16 @@
     <row r="83">
       <c r="T83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U83" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V83" s="7" t="n">
-        <v>715</v>
+        <v>79898</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>12</v>
@@ -5703,16 +5743,16 @@
     <row r="84">
       <c r="T84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U84" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V84" s="4" t="n">
-        <v>745</v>
+        <v>82443</v>
       </c>
       <c r="X84" s="4" t="n">
         <v>70</v>
@@ -5744,16 +5784,16 @@
     <row r="85">
       <c r="T85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U85" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V85" s="7" t="n">
-        <v>702</v>
+        <v>80658</v>
       </c>
       <c r="X85" s="7" t="n">
         <v>30</v>
@@ -5785,16 +5825,16 @@
     <row r="86">
       <c r="T86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U86" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V86" s="4" t="n">
-        <v>743</v>
+        <v>78475</v>
       </c>
       <c r="X86" s="4" t="n">
         <v>15</v>
@@ -5826,16 +5866,16 @@
     <row r="87">
       <c r="T87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U87" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V87" s="7" t="n">
-        <v>700</v>
+        <v>76874</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>73</v>
@@ -5867,16 +5907,16 @@
     <row r="88">
       <c r="T88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U88" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V88" s="4" t="n">
-        <v>696</v>
+        <v>77058</v>
       </c>
       <c r="X88" s="4" t="n">
         <v>5</v>
@@ -5908,16 +5948,16 @@
     <row r="89">
       <c r="T89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U89" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V89" s="7" t="n">
-        <v>750</v>
+        <v>79206</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>1</v>
@@ -5949,7 +5989,7 @@
     <row r="90">
       <c r="T90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U90" s="4" t="inlineStr">
@@ -5958,7 +5998,7 @@
         </is>
       </c>
       <c r="V90" s="4" t="n">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="X90" s="4" t="n">
         <v>107</v>
@@ -5990,7 +6030,7 @@
     <row r="91">
       <c r="T91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U91" s="7" t="inlineStr">
@@ -5999,7 +6039,7 @@
         </is>
       </c>
       <c r="V91" s="7" t="n">
-        <v>748</v>
+        <v>715</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>13</v>
@@ -6031,7 +6071,7 @@
     <row r="92">
       <c r="T92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U92" s="4" t="inlineStr">
@@ -6040,7 +6080,7 @@
         </is>
       </c>
       <c r="V92" s="4" t="n">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="X92" s="4" t="n">
         <v>56</v>
@@ -6072,7 +6112,7 @@
     <row r="93">
       <c r="T93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U93" s="7" t="inlineStr">
@@ -6081,7 +6121,7 @@
         </is>
       </c>
       <c r="V93" s="7" t="n">
-        <v>737</v>
+        <v>702</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>32</v>
@@ -6113,7 +6153,7 @@
     <row r="94">
       <c r="T94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U94" s="4" t="inlineStr">
@@ -6122,7 +6162,7 @@
         </is>
       </c>
       <c r="V94" s="4" t="n">
-        <v>707</v>
+        <v>743</v>
       </c>
       <c r="X94" s="4" t="n">
         <v>13</v>
@@ -6154,7 +6194,7 @@
     <row r="95">
       <c r="T95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U95" s="7" t="inlineStr">
@@ -6163,7 +6203,7 @@
         </is>
       </c>
       <c r="V95" s="7" t="n">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>78</v>
@@ -6195,7 +6235,7 @@
     <row r="96">
       <c r="T96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U96" s="4" t="inlineStr">
@@ -6204,7 +6244,7 @@
         </is>
       </c>
       <c r="V96" s="4" t="n">
-        <v>786</v>
+        <v>696</v>
       </c>
       <c r="X96" s="4" t="n">
         <v>10</v>
@@ -6236,7 +6276,7 @@
     <row r="97">
       <c r="T97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U97" s="7" t="inlineStr">
@@ -6245,7 +6285,7 @@
         </is>
       </c>
       <c r="V97" s="7" t="n">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>1</v>
@@ -6277,7 +6317,7 @@
     <row r="98">
       <c r="T98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U98" s="4" t="inlineStr">
@@ -6286,7 +6326,7 @@
         </is>
       </c>
       <c r="V98" s="4" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="X98" s="4" t="n">
         <v>114</v>
@@ -6318,7 +6358,7 @@
     <row r="99">
       <c r="T99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U99" s="7" t="inlineStr">
@@ -6327,7 +6367,7 @@
         </is>
       </c>
       <c r="V99" s="7" t="n">
-        <v>695</v>
+        <v>748</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>15</v>
@@ -6359,7 +6399,7 @@
     <row r="100">
       <c r="T100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U100" s="4" t="inlineStr">
@@ -6368,7 +6408,7 @@
         </is>
       </c>
       <c r="V100" s="4" t="n">
-        <v>693</v>
+        <v>736</v>
       </c>
       <c r="X100" s="4" t="n">
         <v>53</v>
@@ -6400,7 +6440,7 @@
     <row r="101">
       <c r="T101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U101" s="7" t="inlineStr">
@@ -6409,7 +6449,7 @@
         </is>
       </c>
       <c r="V101" s="7" t="n">
-        <v>686</v>
+        <v>737</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>32</v>
@@ -6441,16 +6481,16 @@
     <row r="102">
       <c r="T102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U102" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V102" s="4" t="n">
-        <v>47976</v>
+        <v>707</v>
       </c>
       <c r="X102" s="4" t="n">
         <v>14</v>
@@ -6482,16 +6522,16 @@
     <row r="103">
       <c r="T103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U103" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V103" s="7" t="n">
-        <v>47122</v>
+        <v>713</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>80</v>
@@ -6523,16 +6563,16 @@
     <row r="104">
       <c r="T104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U104" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V104" s="4" t="n">
-        <v>47233</v>
+        <v>786</v>
       </c>
       <c r="X104" s="4" t="n">
         <v>1</v>
@@ -6564,16 +6604,16 @@
     <row r="105">
       <c r="T105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U105" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V105" s="7" t="n">
-        <v>48580</v>
+        <v>730</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>9</v>
@@ -6605,16 +6645,16 @@
     <row r="106">
       <c r="T106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U106" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V106" s="4" t="n">
-        <v>47383</v>
+        <v>726</v>
       </c>
       <c r="X106" s="4" t="n">
         <v>4</v>
@@ -6646,16 +6686,16 @@
     <row r="107">
       <c r="T107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U107" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V107" s="7" t="n">
-        <v>46456</v>
+        <v>695</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>97</v>
@@ -6687,16 +6727,16 @@
     <row r="108">
       <c r="T108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U108" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V108" s="4" t="n">
-        <v>46400</v>
+        <v>693</v>
       </c>
       <c r="X108" s="4" t="n">
         <v>10</v>
@@ -6728,16 +6768,16 @@
     <row r="109">
       <c r="T109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U109" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V109" s="7" t="n">
-        <v>47755</v>
+        <v>686</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>52</v>
@@ -6769,16 +6809,16 @@
     <row r="110">
       <c r="T110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U110" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V110" s="4" t="n">
-        <v>47520</v>
+        <v>673</v>
       </c>
       <c r="X110" s="4" t="n">
         <v>37</v>
@@ -6810,16 +6850,16 @@
     <row r="111">
       <c r="T111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U111" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V111" s="7" t="n">
-        <v>47354</v>
+        <v>752</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>18</v>
@@ -6851,7 +6891,7 @@
     <row r="112">
       <c r="T112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U112" s="4" t="inlineStr">
@@ -6860,7 +6900,7 @@
         </is>
       </c>
       <c r="V112" s="4" t="n">
-        <v>49015</v>
+        <v>47976</v>
       </c>
       <c r="X112" s="4" t="n">
         <v>64</v>
@@ -6892,7 +6932,7 @@
     <row r="113">
       <c r="T113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U113" s="7" t="inlineStr">
@@ -6901,7 +6941,7 @@
         </is>
       </c>
       <c r="V113" s="7" t="n">
-        <v>48832</v>
+        <v>47122</v>
       </c>
       <c r="X113" s="7" t="n">
         <v>7</v>
@@ -6933,7 +6973,7 @@
     <row r="114">
       <c r="T114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U114" s="4" t="inlineStr">
@@ -6942,7 +6982,7 @@
         </is>
       </c>
       <c r="V114" s="4" t="n">
-        <v>46644</v>
+        <v>47233</v>
       </c>
       <c r="X114" s="4" t="n">
         <v>106</v>
@@ -6974,7 +7014,7 @@
     <row r="115">
       <c r="T115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U115" s="7" t="inlineStr">
@@ -6983,7 +7023,7 @@
         </is>
       </c>
       <c r="V115" s="7" t="n">
-        <v>46416</v>
+        <v>48580</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>14</v>
@@ -7015,7 +7055,7 @@
     <row r="116">
       <c r="T116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U116" s="4" t="inlineStr">
@@ -7024,7 +7064,7 @@
         </is>
       </c>
       <c r="V116" s="4" t="n">
-        <v>48419</v>
+        <v>47383</v>
       </c>
       <c r="X116" s="4" t="n">
         <v>65</v>
@@ -7056,7 +7096,7 @@
     <row r="117">
       <c r="T117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
@@ -7065,7 +7105,7 @@
         </is>
       </c>
       <c r="V117" s="7" t="n">
-        <v>47500</v>
+        <v>46456</v>
       </c>
       <c r="X117" s="7" t="n">
         <v>24</v>
@@ -7097,7 +7137,7 @@
     <row r="118">
       <c r="T118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U118" s="4" t="inlineStr">
@@ -7106,7 +7146,7 @@
         </is>
       </c>
       <c r="V118" s="4" t="n">
-        <v>47954</v>
+        <v>46400</v>
       </c>
       <c r="X118" s="4" t="n">
         <v>14</v>
@@ -7138,7 +7178,7 @@
     <row r="119">
       <c r="T119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U119" s="7" t="inlineStr">
@@ -7147,7 +7187,7 @@
         </is>
       </c>
       <c r="V119" s="7" t="n">
-        <v>49088</v>
+        <v>47755</v>
       </c>
       <c r="X119" s="7" t="n">
         <v>66</v>
@@ -7179,7 +7219,7 @@
     <row r="120">
       <c r="T120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U120" s="4" t="inlineStr">
@@ -7188,7 +7228,7 @@
         </is>
       </c>
       <c r="V120" s="4" t="n">
-        <v>48111</v>
+        <v>47520</v>
       </c>
       <c r="X120" s="4" t="n">
         <v>1</v>
@@ -7220,7 +7260,7 @@
     <row r="121">
       <c r="T121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U121" s="7" t="inlineStr">
@@ -7229,7 +7269,7 @@
         </is>
       </c>
       <c r="V121" s="7" t="n">
-        <v>46535</v>
+        <v>47354</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>9</v>
@@ -7261,16 +7301,16 @@
     <row r="122">
       <c r="T122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U122" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V122" s="4" t="n">
-        <v>1</v>
+        <v>49015</v>
       </c>
       <c r="X122" s="4" t="n">
         <v>116</v>
@@ -7302,16 +7342,16 @@
     <row r="123">
       <c r="T123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V123" s="7" t="n">
-        <v>1</v>
+        <v>48832</v>
       </c>
       <c r="X123" s="7" t="n">
         <v>17</v>
@@ -7343,16 +7383,16 @@
     <row r="124">
       <c r="T124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U124" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V124" s="4" t="n">
-        <v>1</v>
+        <v>46644</v>
       </c>
       <c r="X124" s="4" t="n">
         <v>52</v>
@@ -7384,16 +7424,16 @@
     <row r="125">
       <c r="T125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U125" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V125" s="7" t="n">
-        <v>1</v>
+        <v>46416</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>38</v>
@@ -7425,16 +7465,16 @@
     <row r="126">
       <c r="T126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U126" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V126" s="4" t="n">
-        <v>1</v>
+        <v>48419</v>
       </c>
       <c r="X126" s="4" t="n">
         <v>19</v>
@@ -7466,16 +7506,16 @@
     <row r="127">
       <c r="T127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U127" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V127" s="7" t="n">
-        <v>1</v>
+        <v>47500</v>
       </c>
       <c r="X127" s="7" t="n">
         <v>79</v>
@@ -7507,16 +7547,16 @@
     <row r="128">
       <c r="T128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U128" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V128" s="4" t="n">
-        <v>1</v>
+        <v>47954</v>
       </c>
       <c r="X128" s="4" t="n">
         <v>9</v>
@@ -7548,16 +7588,16 @@
     <row r="129">
       <c r="T129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V129" s="7" t="n">
-        <v>1</v>
+        <v>49088</v>
       </c>
       <c r="X129" s="7" t="n">
         <v>1</v>
@@ -7589,16 +7629,16 @@
     <row r="130">
       <c r="T130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U130" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V130" s="4" t="n">
-        <v>1</v>
+        <v>48111</v>
       </c>
       <c r="X130" s="4" t="n">
         <v>134</v>
@@ -7630,16 +7670,16 @@
     <row r="131">
       <c r="T131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U131" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V131" s="7" t="n">
-        <v>1</v>
+        <v>46535</v>
       </c>
       <c r="X131" s="7" t="n">
         <v>22</v>
@@ -7671,16 +7711,16 @@
     <row r="132">
       <c r="T132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U132" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V132" s="4" t="n">
-        <v>1</v>
+        <v>46063</v>
       </c>
       <c r="X132" s="4" t="n">
         <v>65</v>
@@ -7712,16 +7752,16 @@
     <row r="133">
       <c r="T133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V133" s="7" t="n">
-        <v>1</v>
+        <v>48085</v>
       </c>
       <c r="X133" s="7" t="n">
         <v>29</v>
@@ -7753,7 +7793,7 @@
     <row r="134">
       <c r="T134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U134" s="4" t="inlineStr">
@@ -7794,7 +7834,7 @@
     <row r="135">
       <c r="T135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U135" s="7" t="inlineStr">
@@ -7835,7 +7875,7 @@
     <row r="136">
       <c r="T136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U136" s="4" t="inlineStr">
@@ -7876,7 +7916,7 @@
     <row r="137">
       <c r="T137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U137" s="7" t="inlineStr">
@@ -7917,7 +7957,7 @@
     <row r="138">
       <c r="T138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U138" s="4" t="inlineStr">
@@ -7958,7 +7998,7 @@
     <row r="139">
       <c r="T139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
@@ -7999,12 +8039,12 @@
     <row r="140">
       <c r="T140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U140" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V140" s="4" t="n">
@@ -8040,12 +8080,12 @@
     <row r="141">
       <c r="T141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V141" s="7" t="n">
@@ -8081,12 +8121,12 @@
     <row r="142">
       <c r="T142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U142" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V142" s="4" t="n">
@@ -8122,12 +8162,12 @@
     <row r="143">
       <c r="T143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V143" s="7" t="n">
@@ -8163,12 +8203,12 @@
     <row r="144">
       <c r="T144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U144" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V144" s="4" t="n">
@@ -8204,12 +8244,12 @@
     <row r="145">
       <c r="T145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U145" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V145" s="7" t="n">
@@ -8245,12 +8285,12 @@
     <row r="146">
       <c r="T146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U146" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V146" s="4" t="n">
@@ -8286,12 +8326,12 @@
     <row r="147">
       <c r="T147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V147" s="7" t="n">
@@ -8327,12 +8367,12 @@
     <row r="148">
       <c r="T148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U148" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V148" s="4" t="n">
@@ -8368,12 +8408,12 @@
     <row r="149">
       <c r="T149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U149" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V149" s="7" t="n">
@@ -8409,12 +8449,12 @@
     <row r="150">
       <c r="T150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U150" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V150" s="4" t="n">
@@ -8450,12 +8490,12 @@
     <row r="151">
       <c r="T151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V151" s="7" t="n">
@@ -8491,12 +8531,12 @@
     <row r="152">
       <c r="T152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U152" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V152" s="4" t="n">
@@ -8532,12 +8572,12 @@
     <row r="153">
       <c r="T153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V153" s="7" t="n">
@@ -8573,7 +8613,7 @@
     <row r="154">
       <c r="T154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U154" s="4" t="inlineStr">
@@ -8614,7 +8654,7 @@
     <row r="155">
       <c r="T155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U155" s="7" t="inlineStr">
@@ -8655,7 +8695,7 @@
     <row r="156">
       <c r="T156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U156" s="4" t="inlineStr">
@@ -8696,7 +8736,7 @@
     <row r="157">
       <c r="T157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -8737,7 +8777,7 @@
     <row r="158">
       <c r="T158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U158" s="4" t="inlineStr">
@@ -8778,7 +8818,7 @@
     <row r="159">
       <c r="T159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
@@ -8819,16 +8859,16 @@
     <row r="160">
       <c r="T160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U160" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V160" s="4" t="n">
-        <v>9927</v>
+        <v>1</v>
       </c>
       <c r="X160" s="4" t="n">
         <v>41</v>
@@ -8860,16 +8900,16 @@
     <row r="161">
       <c r="T161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V161" s="7" t="n">
-        <v>9839</v>
+        <v>1</v>
       </c>
       <c r="X161" s="7" t="n">
         <v>14</v>
@@ -8901,16 +8941,16 @@
     <row r="162">
       <c r="T162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U162" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V162" s="4" t="n">
-        <v>9918</v>
+        <v>1</v>
       </c>
       <c r="X162" s="4" t="n">
         <v>84</v>
@@ -8942,16 +8982,16 @@
     <row r="163">
       <c r="T163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V163" s="7" t="n">
-        <v>10435</v>
+        <v>1</v>
       </c>
       <c r="X163" s="7" t="n">
         <v>8</v>
@@ -8983,16 +9023,16 @@
     <row r="164">
       <c r="T164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U164" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V164" s="4" t="n">
-        <v>10050</v>
+        <v>1</v>
       </c>
       <c r="X164" s="4" t="n">
         <v>1</v>
@@ -9024,20 +9064,30 @@
     <row r="165">
       <c r="T165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V165" s="7" t="n">
-        <v>9768</v>
-      </c>
-      <c r="X165" s="7" t="n"/>
-      <c r="Y165" s="7" t="n"/>
-      <c r="Z165" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X165" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="Y165" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z165" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB165" s="7" t="n">
         <v>380</v>
       </c>
@@ -9055,20 +9105,30 @@
     <row r="166">
       <c r="T166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U166" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V166" s="4" t="n">
-        <v>9920</v>
-      </c>
-      <c r="X166" s="4" t="n"/>
-      <c r="Y166" s="4" t="n"/>
-      <c r="Z166" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X166" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y166" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z166" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB166" s="4" t="n">
         <v>29</v>
       </c>
@@ -9086,20 +9146,30 @@
     <row r="167">
       <c r="T167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V167" s="7" t="n">
-        <v>10435</v>
-      </c>
-      <c r="X167" s="7" t="n"/>
-      <c r="Y167" s="7" t="n"/>
-      <c r="Z167" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X167" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y167" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z167" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB167" s="7" t="n">
         <v>157</v>
       </c>
@@ -9117,20 +9187,30 @@
     <row r="168">
       <c r="T168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U168" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V168" s="4" t="n">
-        <v>10434</v>
-      </c>
-      <c r="X168" s="4" t="n"/>
-      <c r="Y168" s="4" t="n"/>
-      <c r="Z168" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X168" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y168" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z168" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB168" s="4" t="n">
         <v>54</v>
       </c>
@@ -9148,20 +9228,30 @@
     <row r="169">
       <c r="T169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U169" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+        </is>
+      </c>
+      <c r="V169" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X169" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y169" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z169" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="V169" s="7" t="n">
-        <v>10284</v>
-      </c>
-      <c r="X169" s="7" t="n"/>
-      <c r="Y169" s="7" t="n"/>
-      <c r="Z169" s="7" t="n"/>
       <c r="AB169" s="7" t="n">
         <v>43</v>
       </c>
@@ -9179,20 +9269,30 @@
     <row r="170">
       <c r="T170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U170" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V170" s="4" t="n">
-        <v>10458</v>
-      </c>
-      <c r="X170" s="4" t="n"/>
-      <c r="Y170" s="4" t="n"/>
-      <c r="Z170" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X170" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y170" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z170" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB170" s="4" t="n">
         <v>154</v>
       </c>
@@ -9210,20 +9310,30 @@
     <row r="171">
       <c r="T171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U171" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V171" s="7" t="n">
-        <v>10153</v>
-      </c>
-      <c r="X171" s="7" t="n"/>
-      <c r="Y171" s="7" t="n"/>
-      <c r="Z171" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X171" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y171" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z171" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB171" s="7" t="n">
         <v>2</v>
       </c>
@@ -9241,20 +9351,30 @@
     <row r="172">
       <c r="T172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U172" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V172" s="4" t="n">
-        <v>9843</v>
-      </c>
-      <c r="X172" s="4" t="n"/>
-      <c r="Y172" s="4" t="n"/>
-      <c r="Z172" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X172" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y172" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z172" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB172" s="4" t="n">
         <v>5</v>
       </c>
@@ -9272,20 +9392,30 @@
     <row r="173">
       <c r="T173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V173" s="7" t="n">
-        <v>10433</v>
-      </c>
-      <c r="X173" s="7" t="n"/>
-      <c r="Y173" s="7" t="n"/>
-      <c r="Z173" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X173" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y173" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z173" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB173" s="7" t="n">
         <v>367</v>
       </c>
@@ -9303,20 +9433,30 @@
     <row r="174">
       <c r="T174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U174" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V174" s="4" t="n">
-        <v>10670</v>
-      </c>
-      <c r="X174" s="4" t="n"/>
-      <c r="Y174" s="4" t="n"/>
-      <c r="Z174" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X174" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y174" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z174" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB174" s="4" t="n">
         <v>38</v>
       </c>
@@ -9334,20 +9474,30 @@
     <row r="175">
       <c r="T175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V175" s="7" t="n">
-        <v>10599</v>
-      </c>
-      <c r="X175" s="7" t="n"/>
-      <c r="Y175" s="7" t="n"/>
-      <c r="Z175" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X175" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y175" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z175" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB175" s="7" t="n">
         <v>166</v>
       </c>
@@ -9365,7 +9515,7 @@
     <row r="176">
       <c r="T176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U176" s="4" t="inlineStr">
@@ -9374,11 +9524,21 @@
         </is>
       </c>
       <c r="V176" s="4" t="n">
-        <v>10619</v>
-      </c>
-      <c r="X176" s="4" t="n"/>
-      <c r="Y176" s="4" t="n"/>
-      <c r="Z176" s="4" t="n"/>
+        <v>9927</v>
+      </c>
+      <c r="X176" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y176" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z176" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB176" s="4" t="n">
         <v>55</v>
       </c>
@@ -9396,7 +9556,7 @@
     <row r="177">
       <c r="T177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U177" s="7" t="inlineStr">
@@ -9405,11 +9565,21 @@
         </is>
       </c>
       <c r="V177" s="7" t="n">
-        <v>10415</v>
-      </c>
-      <c r="X177" s="7" t="n"/>
-      <c r="Y177" s="7" t="n"/>
-      <c r="Z177" s="7" t="n"/>
+        <v>9839</v>
+      </c>
+      <c r="X177" s="7" t="n">
+        <v>133</v>
+      </c>
+      <c r="Y177" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z177" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB177" s="7" t="n">
         <v>41</v>
       </c>
@@ -9427,7 +9597,7 @@
     <row r="178">
       <c r="T178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U178" s="4" t="inlineStr">
@@ -9436,11 +9606,21 @@
         </is>
       </c>
       <c r="V178" s="4" t="n">
-        <v>10065</v>
-      </c>
-      <c r="X178" s="4" t="n"/>
-      <c r="Y178" s="4" t="n"/>
-      <c r="Z178" s="4" t="n"/>
+        <v>9918</v>
+      </c>
+      <c r="X178" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y178" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z178" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB178" s="4" t="n">
         <v>153</v>
       </c>
@@ -9458,7 +9638,7 @@
     <row r="179">
       <c r="T179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr">
@@ -9467,11 +9647,21 @@
         </is>
       </c>
       <c r="V179" s="7" t="n">
-        <v>10158</v>
-      </c>
-      <c r="X179" s="7" t="n"/>
-      <c r="Y179" s="7" t="n"/>
-      <c r="Z179" s="7" t="n"/>
+        <v>10435</v>
+      </c>
+      <c r="X179" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y179" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z179" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB179" s="7" t="n">
         <v>4</v>
       </c>
@@ -9489,16 +9679,16 @@
     <row r="180">
       <c r="T180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U180" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation50987</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V180" s="4" t="n">
-        <v>1</v>
+        <v>10050</v>
       </c>
       <c r="X180" s="4" t="n"/>
       <c r="Y180" s="4" t="n"/>
@@ -9520,16 +9710,16 @@
     <row r="181">
       <c r="T181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U181" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation75114</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V181" s="7" t="n">
-        <v>1</v>
+        <v>9768</v>
       </c>
       <c r="X181" s="7" t="n"/>
       <c r="Y181" s="7" t="n"/>
@@ -9551,385 +9741,565 @@
     <row r="182">
       <c r="T182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U182" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V182" s="4" t="n">
-        <v>21493</v>
+        <v>9920</v>
       </c>
       <c r="X182" s="4" t="n"/>
       <c r="Y182" s="4" t="n"/>
       <c r="Z182" s="4" t="n"/>
-      <c r="AB182" s="4" t="n"/>
-      <c r="AC182" s="4" t="n"/>
-      <c r="AD182" s="4" t="n"/>
+      <c r="AB182" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="AC182" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD182" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="T183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U183" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V183" s="7" t="n">
-        <v>21012</v>
+        <v>10435</v>
       </c>
       <c r="X183" s="7" t="n"/>
       <c r="Y183" s="7" t="n"/>
       <c r="Z183" s="7" t="n"/>
-      <c r="AB183" s="7" t="n"/>
-      <c r="AC183" s="7" t="n"/>
-      <c r="AD183" s="7" t="n"/>
+      <c r="AB183" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC183" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD183" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="T184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U184" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V184" s="4" t="n">
-        <v>21635</v>
+        <v>10434</v>
       </c>
       <c r="X184" s="4" t="n"/>
       <c r="Y184" s="4" t="n"/>
       <c r="Z184" s="4" t="n"/>
-      <c r="AB184" s="4" t="n"/>
-      <c r="AC184" s="4" t="n"/>
-      <c r="AD184" s="4" t="n"/>
+      <c r="AB184" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="AC184" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD184" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="T185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U185" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V185" s="7" t="n">
-        <v>21969</v>
+        <v>10284</v>
       </c>
       <c r="X185" s="7" t="n"/>
       <c r="Y185" s="7" t="n"/>
       <c r="Z185" s="7" t="n"/>
-      <c r="AB185" s="7" t="n"/>
-      <c r="AC185" s="7" t="n"/>
-      <c r="AD185" s="7" t="n"/>
+      <c r="AB185" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC185" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD185" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="T186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U186" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V186" s="4" t="n">
-        <v>21723</v>
+        <v>10458</v>
       </c>
       <c r="X186" s="4" t="n"/>
       <c r="Y186" s="4" t="n"/>
       <c r="Z186" s="4" t="n"/>
-      <c r="AB186" s="4" t="n"/>
-      <c r="AC186" s="4" t="n"/>
-      <c r="AD186" s="4" t="n"/>
+      <c r="AB186" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD186" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="T187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U187" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V187" s="7" t="n">
-        <v>20879</v>
+        <v>10153</v>
       </c>
       <c r="X187" s="7" t="n"/>
       <c r="Y187" s="7" t="n"/>
       <c r="Z187" s="7" t="n"/>
-      <c r="AB187" s="7" t="n"/>
-      <c r="AC187" s="7" t="n"/>
-      <c r="AD187" s="7" t="n"/>
+      <c r="AB187" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC187" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD187" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="T188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U188" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V188" s="4" t="n">
-        <v>20783</v>
+        <v>9843</v>
       </c>
       <c r="X188" s="4" t="n"/>
       <c r="Y188" s="4" t="n"/>
       <c r="Z188" s="4" t="n"/>
-      <c r="AB188" s="4" t="n"/>
-      <c r="AC188" s="4" t="n"/>
-      <c r="AD188" s="4" t="n"/>
+      <c r="AB188" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC188" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD188" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="T189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U189" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V189" s="7" t="n">
-        <v>21875</v>
+        <v>10433</v>
       </c>
       <c r="X189" s="7" t="n"/>
       <c r="Y189" s="7" t="n"/>
       <c r="Z189" s="7" t="n"/>
-      <c r="AB189" s="7" t="n"/>
-      <c r="AC189" s="7" t="n"/>
-      <c r="AD189" s="7" t="n"/>
+      <c r="AB189" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC189" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD189" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="T190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U190" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V190" s="4" t="n">
-        <v>22103</v>
+        <v>10670</v>
       </c>
       <c r="X190" s="4" t="n"/>
       <c r="Y190" s="4" t="n"/>
       <c r="Z190" s="4" t="n"/>
-      <c r="AB190" s="4" t="n"/>
-      <c r="AC190" s="4" t="n"/>
-      <c r="AD190" s="4" t="n"/>
+      <c r="AB190" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC190" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD190" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="T191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U191" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V191" s="7" t="n">
-        <v>22799</v>
+        <v>10599</v>
       </c>
       <c r="X191" s="7" t="n"/>
       <c r="Y191" s="7" t="n"/>
       <c r="Z191" s="7" t="n"/>
-      <c r="AB191" s="7" t="n"/>
-      <c r="AC191" s="7" t="n"/>
-      <c r="AD191" s="7" t="n"/>
+      <c r="AB191" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC191" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD191" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="T192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U192" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V192" s="4" t="n">
-        <v>22705</v>
+        <v>10619</v>
       </c>
       <c r="X192" s="4" t="n"/>
       <c r="Y192" s="4" t="n"/>
       <c r="Z192" s="4" t="n"/>
-      <c r="AB192" s="4" t="n"/>
-      <c r="AC192" s="4" t="n"/>
-      <c r="AD192" s="4" t="n"/>
+      <c r="AB192" s="4" t="n">
+        <v>292</v>
+      </c>
+      <c r="AC192" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD192" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="T193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U193" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V193" s="7" t="n">
-        <v>21885</v>
+        <v>10415</v>
       </c>
       <c r="X193" s="7" t="n"/>
       <c r="Y193" s="7" t="n"/>
       <c r="Z193" s="7" t="n"/>
-      <c r="AB193" s="7" t="n"/>
-      <c r="AC193" s="7" t="n"/>
-      <c r="AD193" s="7" t="n"/>
+      <c r="AB193" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC193" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD193" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="T194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U194" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V194" s="4" t="n">
-        <v>21360</v>
+        <v>10065</v>
       </c>
       <c r="X194" s="4" t="n"/>
       <c r="Y194" s="4" t="n"/>
       <c r="Z194" s="4" t="n"/>
-      <c r="AB194" s="4" t="n"/>
-      <c r="AC194" s="4" t="n"/>
-      <c r="AD194" s="4" t="n"/>
+      <c r="AB194" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC194" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD194" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="T195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U195" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V195" s="7" t="n">
-        <v>20612</v>
+        <v>10158</v>
       </c>
       <c r="X195" s="7" t="n"/>
       <c r="Y195" s="7" t="n"/>
       <c r="Z195" s="7" t="n"/>
-      <c r="AB195" s="7" t="n"/>
-      <c r="AC195" s="7" t="n"/>
-      <c r="AD195" s="7" t="n"/>
+      <c r="AB195" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC195" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD195" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="T196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U196" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V196" s="4" t="n">
-        <v>22101</v>
+        <v>10333</v>
       </c>
       <c r="X196" s="4" t="n"/>
       <c r="Y196" s="4" t="n"/>
       <c r="Z196" s="4" t="n"/>
-      <c r="AB196" s="4" t="n"/>
-      <c r="AC196" s="4" t="n"/>
-      <c r="AD196" s="4" t="n"/>
+      <c r="AB196" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC196" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD196" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="T197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U197" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V197" s="7" t="n">
-        <v>22665</v>
+        <v>10414</v>
       </c>
       <c r="X197" s="7" t="n"/>
       <c r="Y197" s="7" t="n"/>
       <c r="Z197" s="7" t="n"/>
-      <c r="AB197" s="7" t="n"/>
-      <c r="AC197" s="7" t="n"/>
-      <c r="AD197" s="7" t="n"/>
+      <c r="AB197" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="AC197" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD197" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="T198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U198" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation50987</t>
         </is>
       </c>
       <c r="V198" s="4" t="n">
-        <v>22473</v>
+        <v>1</v>
       </c>
       <c r="X198" s="4" t="n"/>
       <c r="Y198" s="4" t="n"/>
       <c r="Z198" s="4" t="n"/>
-      <c r="AB198" s="4" t="n"/>
-      <c r="AC198" s="4" t="n"/>
-      <c r="AD198" s="4" t="n"/>
+      <c r="AB198" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC198" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD198" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="T199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U199" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation75114</t>
         </is>
       </c>
       <c r="V199" s="7" t="n">
-        <v>22903</v>
+        <v>1</v>
       </c>
       <c r="X199" s="7" t="n"/>
       <c r="Y199" s="7" t="n"/>
       <c r="Z199" s="7" t="n"/>
-      <c r="AB199" s="7" t="n"/>
-      <c r="AC199" s="7" t="n"/>
-      <c r="AD199" s="7" t="n"/>
+      <c r="AB199" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC199" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD199" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="T200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U200" s="4" t="inlineStr">
@@ -9938,19 +10308,29 @@
         </is>
       </c>
       <c r="V200" s="4" t="n">
-        <v>21829</v>
+        <v>21493</v>
       </c>
       <c r="X200" s="4" t="n"/>
       <c r="Y200" s="4" t="n"/>
       <c r="Z200" s="4" t="n"/>
-      <c r="AB200" s="4" t="n"/>
-      <c r="AC200" s="4" t="n"/>
-      <c r="AD200" s="4" t="n"/>
+      <c r="AB200" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC200" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD200" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="T201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U201" s="7" t="inlineStr">
@@ -9959,7 +10339,7 @@
         </is>
       </c>
       <c r="V201" s="7" t="n">
-        <v>20959</v>
+        <v>21012</v>
       </c>
       <c r="X201" s="7" t="n"/>
       <c r="Y201" s="7" t="n"/>
@@ -9971,16 +10351,16 @@
     <row r="202">
       <c r="T202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U202" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V202" s="4" t="n">
-        <v>16634</v>
+        <v>21635</v>
       </c>
       <c r="X202" s="4" t="n"/>
       <c r="Y202" s="4" t="n"/>
@@ -9992,16 +10372,16 @@
     <row r="203">
       <c r="T203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U203" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V203" s="7" t="n">
-        <v>16721</v>
+        <v>21969</v>
       </c>
       <c r="X203" s="7" t="n"/>
       <c r="Y203" s="7" t="n"/>
@@ -10013,16 +10393,16 @@
     <row r="204">
       <c r="T204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U204" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V204" s="4" t="n">
-        <v>16586</v>
+        <v>21723</v>
       </c>
       <c r="X204" s="4" t="n"/>
       <c r="Y204" s="4" t="n"/>
@@ -10034,16 +10414,16 @@
     <row r="205">
       <c r="T205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U205" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V205" s="7" t="n">
-        <v>16419</v>
+        <v>20879</v>
       </c>
       <c r="X205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
@@ -10055,16 +10435,16 @@
     <row r="206">
       <c r="T206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U206" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V206" s="4" t="n">
-        <v>15946</v>
+        <v>20783</v>
       </c>
       <c r="X206" s="4" t="n"/>
       <c r="Y206" s="4" t="n"/>
@@ -10076,16 +10456,16 @@
     <row r="207">
       <c r="T207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U207" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V207" s="7" t="n">
-        <v>16042</v>
+        <v>21875</v>
       </c>
       <c r="X207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
@@ -10097,16 +10477,16 @@
     <row r="208">
       <c r="T208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U208" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V208" s="4" t="n">
-        <v>16409</v>
+        <v>22103</v>
       </c>
       <c r="X208" s="4" t="n"/>
       <c r="Y208" s="4" t="n"/>
@@ -10118,16 +10498,16 @@
     <row r="209">
       <c r="T209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U209" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V209" s="7" t="n">
-        <v>16831</v>
+        <v>22799</v>
       </c>
       <c r="X209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
@@ -10139,16 +10519,16 @@
     <row r="210">
       <c r="T210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U210" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V210" s="4" t="n">
-        <v>16886</v>
+        <v>22705</v>
       </c>
       <c r="X210" s="4" t="n"/>
       <c r="Y210" s="4" t="n"/>
@@ -10160,16 +10540,16 @@
     <row r="211">
       <c r="T211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U211" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V211" s="7" t="n">
-        <v>16694</v>
+        <v>21885</v>
       </c>
       <c r="X211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
@@ -10181,16 +10561,16 @@
     <row r="212">
       <c r="T212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U212" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V212" s="4" t="n">
-        <v>16659</v>
+        <v>21360</v>
       </c>
       <c r="X212" s="4" t="n"/>
       <c r="Y212" s="4" t="n"/>
@@ -10202,16 +10582,16 @@
     <row r="213">
       <c r="T213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U213" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V213" s="7" t="n">
-        <v>16268</v>
+        <v>20612</v>
       </c>
       <c r="X213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
@@ -10223,16 +10603,16 @@
     <row r="214">
       <c r="T214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U214" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V214" s="4" t="n">
-        <v>16259</v>
+        <v>22101</v>
       </c>
       <c r="X214" s="4" t="n"/>
       <c r="Y214" s="4" t="n"/>
@@ -10244,16 +10624,16 @@
     <row r="215">
       <c r="T215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U215" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V215" s="7" t="n">
-        <v>16600</v>
+        <v>22665</v>
       </c>
       <c r="X215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
@@ -10265,16 +10645,16 @@
     <row r="216">
       <c r="T216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U216" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V216" s="4" t="n">
-        <v>16913</v>
+        <v>22473</v>
       </c>
       <c r="X216" s="4" t="n"/>
       <c r="Y216" s="4" t="n"/>
@@ -10286,16 +10666,16 @@
     <row r="217">
       <c r="T217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U217" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V217" s="7" t="n">
-        <v>16991</v>
+        <v>22903</v>
       </c>
       <c r="X217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
@@ -10307,16 +10687,16 @@
     <row r="218">
       <c r="T218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U218" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V218" s="4" t="n">
-        <v>17365</v>
+        <v>21829</v>
       </c>
       <c r="X218" s="4" t="n"/>
       <c r="Y218" s="4" t="n"/>
@@ -10328,16 +10708,16 @@
     <row r="219">
       <c r="T219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U219" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V219" s="7" t="n">
-        <v>16944</v>
+        <v>20959</v>
       </c>
       <c r="X219" s="7" t="n"/>
       <c r="Y219" s="7" t="n"/>
@@ -10349,16 +10729,16 @@
     <row r="220">
       <c r="T220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U220" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V220" s="4" t="n">
-        <v>16518</v>
+        <v>20856</v>
       </c>
       <c r="X220" s="4" t="n"/>
       <c r="Y220" s="4" t="n"/>
@@ -10370,16 +10750,16 @@
     <row r="221">
       <c r="T221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U221" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V221" s="7" t="n">
-        <v>16634</v>
+        <v>23061</v>
       </c>
       <c r="X221" s="7" t="n"/>
       <c r="Y221" s="7" t="n"/>
@@ -10396,11 +10776,11 @@
       </c>
       <c r="U222" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V222" s="4" t="n">
-        <v>724</v>
+        <v>16634</v>
       </c>
       <c r="X222" s="4" t="n"/>
       <c r="Y222" s="4" t="n"/>
@@ -10417,11 +10797,11 @@
       </c>
       <c r="U223" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V223" s="7" t="n">
-        <v>746</v>
+        <v>16721</v>
       </c>
       <c r="X223" s="7" t="n"/>
       <c r="Y223" s="7" t="n"/>
@@ -10438,11 +10818,11 @@
       </c>
       <c r="U224" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V224" s="4" t="n">
-        <v>723</v>
+        <v>16586</v>
       </c>
       <c r="X224" s="4" t="n"/>
       <c r="Y224" s="4" t="n"/>
@@ -10459,11 +10839,11 @@
       </c>
       <c r="U225" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V225" s="7" t="n">
-        <v>708</v>
+        <v>16419</v>
       </c>
       <c r="X225" s="7" t="n"/>
       <c r="Y225" s="7" t="n"/>
@@ -10480,11 +10860,11 @@
       </c>
       <c r="U226" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V226" s="4" t="n">
-        <v>735</v>
+        <v>15946</v>
       </c>
       <c r="X226" s="4" t="n"/>
       <c r="Y226" s="4" t="n"/>
@@ -10501,11 +10881,11 @@
       </c>
       <c r="U227" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V227" s="7" t="n">
-        <v>714</v>
+        <v>16042</v>
       </c>
       <c r="X227" s="7" t="n"/>
       <c r="Y227" s="7" t="n"/>
@@ -10522,11 +10902,11 @@
       </c>
       <c r="U228" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V228" s="4" t="n">
-        <v>706</v>
+        <v>16409</v>
       </c>
       <c r="X228" s="4" t="n"/>
       <c r="Y228" s="4" t="n"/>
@@ -10543,11 +10923,11 @@
       </c>
       <c r="U229" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V229" s="7" t="n">
-        <v>729</v>
+        <v>16831</v>
       </c>
       <c r="X229" s="7" t="n"/>
       <c r="Y229" s="7" t="n"/>
@@ -10564,11 +10944,11 @@
       </c>
       <c r="U230" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V230" s="4" t="n">
-        <v>719</v>
+        <v>16886</v>
       </c>
       <c r="X230" s="4" t="n"/>
       <c r="Y230" s="4" t="n"/>
@@ -10585,11 +10965,11 @@
       </c>
       <c r="U231" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V231" s="7" t="n">
-        <v>719</v>
+        <v>16694</v>
       </c>
       <c r="X231" s="7" t="n"/>
       <c r="Y231" s="7" t="n"/>
@@ -10606,11 +10986,11 @@
       </c>
       <c r="U232" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V232" s="4" t="n">
-        <v>730</v>
+        <v>16659</v>
       </c>
       <c r="X232" s="4" t="n"/>
       <c r="Y232" s="4" t="n"/>
@@ -10627,11 +11007,11 @@
       </c>
       <c r="U233" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V233" s="7" t="n">
-        <v>740</v>
+        <v>16268</v>
       </c>
       <c r="X233" s="7" t="n"/>
       <c r="Y233" s="7" t="n"/>
@@ -10648,11 +11028,11 @@
       </c>
       <c r="U234" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V234" s="4" t="n">
-        <v>708</v>
+        <v>16259</v>
       </c>
       <c r="X234" s="4" t="n"/>
       <c r="Y234" s="4" t="n"/>
@@ -10669,11 +11049,11 @@
       </c>
       <c r="U235" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V235" s="7" t="n">
-        <v>698</v>
+        <v>16600</v>
       </c>
       <c r="X235" s="7" t="n"/>
       <c r="Y235" s="7" t="n"/>
@@ -10690,11 +11070,11 @@
       </c>
       <c r="U236" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V236" s="4" t="n">
-        <v>691</v>
+        <v>16913</v>
       </c>
       <c r="X236" s="4" t="n"/>
       <c r="Y236" s="4" t="n"/>
@@ -10711,11 +11091,11 @@
       </c>
       <c r="U237" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V237" s="7" t="n">
-        <v>695</v>
+        <v>16991</v>
       </c>
       <c r="X237" s="7" t="n"/>
       <c r="Y237" s="7" t="n"/>
@@ -10732,11 +11112,11 @@
       </c>
       <c r="U238" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V238" s="4" t="n">
-        <v>706</v>
+        <v>17365</v>
       </c>
       <c r="X238" s="4" t="n"/>
       <c r="Y238" s="4" t="n"/>
@@ -10753,11 +11133,11 @@
       </c>
       <c r="U239" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V239" s="7" t="n">
-        <v>701</v>
+        <v>16944</v>
       </c>
       <c r="X239" s="7" t="n"/>
       <c r="Y239" s="7" t="n"/>
@@ -10774,11 +11154,11 @@
       </c>
       <c r="U240" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V240" s="4" t="n">
-        <v>706</v>
+        <v>16518</v>
       </c>
       <c r="X240" s="4" t="n"/>
       <c r="Y240" s="4" t="n"/>
@@ -10795,11 +11175,11 @@
       </c>
       <c r="U241" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V241" s="7" t="n">
-        <v>704</v>
+        <v>16634</v>
       </c>
       <c r="X241" s="7" t="n"/>
       <c r="Y241" s="7" t="n"/>
@@ -10811,16 +11191,16 @@
     <row r="242">
       <c r="T242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U242" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V242" s="4" t="n">
-        <v>2188</v>
+        <v>16711</v>
       </c>
       <c r="X242" s="4" t="n"/>
       <c r="Y242" s="4" t="n"/>
@@ -10832,16 +11212,16 @@
     <row r="243">
       <c r="T243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U243" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V243" s="7" t="n">
-        <v>2046</v>
+        <v>17379</v>
       </c>
       <c r="X243" s="7" t="n"/>
       <c r="Y243" s="7" t="n"/>
@@ -10853,16 +11233,16 @@
     <row r="244">
       <c r="T244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U244" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V244" s="4" t="n">
-        <v>2338</v>
+        <v>724</v>
       </c>
       <c r="X244" s="4" t="n"/>
       <c r="Y244" s="4" t="n"/>
@@ -10874,16 +11254,16 @@
     <row r="245">
       <c r="T245" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U245" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V245" s="7" t="n">
-        <v>2152</v>
+        <v>746</v>
       </c>
       <c r="X245" s="7" t="n"/>
       <c r="Y245" s="7" t="n"/>
@@ -10895,16 +11275,16 @@
     <row r="246">
       <c r="T246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U246" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V246" s="4" t="n">
-        <v>2003</v>
+        <v>723</v>
       </c>
       <c r="X246" s="4" t="n"/>
       <c r="Y246" s="4" t="n"/>
@@ -10916,16 +11296,16 @@
     <row r="247">
       <c r="T247" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U247" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V247" s="7" t="n">
-        <v>1895</v>
+        <v>708</v>
       </c>
       <c r="X247" s="7" t="n"/>
       <c r="Y247" s="7" t="n"/>
@@ -10937,16 +11317,16 @@
     <row r="248">
       <c r="T248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U248" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V248" s="4" t="n">
-        <v>1935</v>
+        <v>735</v>
       </c>
       <c r="X248" s="4" t="n"/>
       <c r="Y248" s="4" t="n"/>
@@ -10958,16 +11338,16 @@
     <row r="249">
       <c r="T249" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U249" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V249" s="7" t="n">
-        <v>2037</v>
+        <v>714</v>
       </c>
       <c r="X249" s="7" t="n"/>
       <c r="Y249" s="7" t="n"/>
@@ -10979,16 +11359,16 @@
     <row r="250">
       <c r="T250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U250" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V250" s="4" t="n">
-        <v>2049</v>
+        <v>706</v>
       </c>
       <c r="X250" s="4" t="n"/>
       <c r="Y250" s="4" t="n"/>
@@ -11000,16 +11380,16 @@
     <row r="251">
       <c r="T251" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U251" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V251" s="7" t="n">
-        <v>2325</v>
+        <v>729</v>
       </c>
       <c r="X251" s="7" t="n"/>
       <c r="Y251" s="7" t="n"/>
@@ -11021,16 +11401,16 @@
     <row r="252">
       <c r="T252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U252" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V252" s="4" t="n">
-        <v>2216</v>
+        <v>719</v>
       </c>
       <c r="X252" s="4" t="n"/>
       <c r="Y252" s="4" t="n"/>
@@ -11042,16 +11422,16 @@
     <row r="253">
       <c r="T253" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U253" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V253" s="7" t="n">
-        <v>2037</v>
+        <v>719</v>
       </c>
       <c r="X253" s="7" t="n"/>
       <c r="Y253" s="7" t="n"/>
@@ -11063,16 +11443,16 @@
     <row r="254">
       <c r="T254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U254" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V254" s="4" t="n">
-        <v>2046</v>
+        <v>730</v>
       </c>
       <c r="X254" s="4" t="n"/>
       <c r="Y254" s="4" t="n"/>
@@ -11084,16 +11464,16 @@
     <row r="255">
       <c r="T255" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U255" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V255" s="7" t="n">
-        <v>2035</v>
+        <v>740</v>
       </c>
       <c r="X255" s="7" t="n"/>
       <c r="Y255" s="7" t="n"/>
@@ -11105,16 +11485,16 @@
     <row r="256">
       <c r="T256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U256" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V256" s="4" t="n">
-        <v>2182</v>
+        <v>708</v>
       </c>
       <c r="X256" s="4" t="n"/>
       <c r="Y256" s="4" t="n"/>
@@ -11126,16 +11506,16 @@
     <row r="257">
       <c r="T257" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U257" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V257" s="7" t="n">
-        <v>2156</v>
+        <v>698</v>
       </c>
       <c r="X257" s="7" t="n"/>
       <c r="Y257" s="7" t="n"/>
@@ -11147,16 +11527,16 @@
     <row r="258">
       <c r="T258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U258" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V258" s="4" t="n">
-        <v>2437</v>
+        <v>691</v>
       </c>
       <c r="X258" s="4" t="n"/>
       <c r="Y258" s="4" t="n"/>
@@ -11168,16 +11548,16 @@
     <row r="259">
       <c r="T259" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U259" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V259" s="7" t="n">
-        <v>2214</v>
+        <v>695</v>
       </c>
       <c r="X259" s="7" t="n"/>
       <c r="Y259" s="7" t="n"/>
@@ -11189,16 +11569,16 @@
     <row r="260">
       <c r="T260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U260" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V260" s="4" t="n">
-        <v>2200</v>
+        <v>706</v>
       </c>
       <c r="X260" s="4" t="n"/>
       <c r="Y260" s="4" t="n"/>
@@ -11210,16 +11590,16 @@
     <row r="261">
       <c r="T261" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U261" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V261" s="7" t="n">
-        <v>1973</v>
+        <v>701</v>
       </c>
       <c r="X261" s="7" t="n"/>
       <c r="Y261" s="7" t="n"/>
@@ -11227,6 +11607,552 @@
       <c r="AB261" s="7" t="n"/>
       <c r="AC261" s="7" t="n"/>
       <c r="AD261" s="7" t="n"/>
+    </row>
+    <row r="262">
+      <c r="T262" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U262" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V262" s="4" t="n">
+        <v>706</v>
+      </c>
+      <c r="X262" s="4" t="n"/>
+      <c r="Y262" s="4" t="n"/>
+      <c r="Z262" s="4" t="n"/>
+      <c r="AB262" s="4" t="n"/>
+      <c r="AC262" s="4" t="n"/>
+      <c r="AD262" s="4" t="n"/>
+    </row>
+    <row r="263">
+      <c r="T263" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U263" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V263" s="7" t="n">
+        <v>704</v>
+      </c>
+      <c r="X263" s="7" t="n"/>
+      <c r="Y263" s="7" t="n"/>
+      <c r="Z263" s="7" t="n"/>
+      <c r="AB263" s="7" t="n"/>
+      <c r="AC263" s="7" t="n"/>
+      <c r="AD263" s="7" t="n"/>
+    </row>
+    <row r="264">
+      <c r="T264" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U264" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V264" s="4" t="n">
+        <v>670</v>
+      </c>
+      <c r="X264" s="4" t="n"/>
+      <c r="Y264" s="4" t="n"/>
+      <c r="Z264" s="4" t="n"/>
+      <c r="AB264" s="4" t="n"/>
+      <c r="AC264" s="4" t="n"/>
+      <c r="AD264" s="4" t="n"/>
+    </row>
+    <row r="265">
+      <c r="T265" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U265" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V265" s="7" t="n">
+        <v>694</v>
+      </c>
+      <c r="X265" s="7" t="n"/>
+      <c r="Y265" s="7" t="n"/>
+      <c r="Z265" s="7" t="n"/>
+      <c r="AB265" s="7" t="n"/>
+      <c r="AC265" s="7" t="n"/>
+      <c r="AD265" s="7" t="n"/>
+    </row>
+    <row r="266">
+      <c r="T266" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U266" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V266" s="4" t="n">
+        <v>2188</v>
+      </c>
+      <c r="X266" s="4" t="n"/>
+      <c r="Y266" s="4" t="n"/>
+      <c r="Z266" s="4" t="n"/>
+      <c r="AB266" s="4" t="n"/>
+      <c r="AC266" s="4" t="n"/>
+      <c r="AD266" s="4" t="n"/>
+    </row>
+    <row r="267">
+      <c r="T267" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="U267" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V267" s="7" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X267" s="7" t="n"/>
+      <c r="Y267" s="7" t="n"/>
+      <c r="Z267" s="7" t="n"/>
+      <c r="AB267" s="7" t="n"/>
+      <c r="AC267" s="7" t="n"/>
+      <c r="AD267" s="7" t="n"/>
+    </row>
+    <row r="268">
+      <c r="T268" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="U268" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V268" s="4" t="n">
+        <v>2338</v>
+      </c>
+      <c r="X268" s="4" t="n"/>
+      <c r="Y268" s="4" t="n"/>
+      <c r="Z268" s="4" t="n"/>
+      <c r="AB268" s="4" t="n"/>
+      <c r="AC268" s="4" t="n"/>
+      <c r="AD268" s="4" t="n"/>
+    </row>
+    <row r="269">
+      <c r="T269" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="U269" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V269" s="7" t="n">
+        <v>2152</v>
+      </c>
+      <c r="X269" s="7" t="n"/>
+      <c r="Y269" s="7" t="n"/>
+      <c r="Z269" s="7" t="n"/>
+      <c r="AB269" s="7" t="n"/>
+      <c r="AC269" s="7" t="n"/>
+      <c r="AD269" s="7" t="n"/>
+    </row>
+    <row r="270">
+      <c r="T270" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="U270" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V270" s="4" t="n">
+        <v>2003</v>
+      </c>
+      <c r="X270" s="4" t="n"/>
+      <c r="Y270" s="4" t="n"/>
+      <c r="Z270" s="4" t="n"/>
+      <c r="AB270" s="4" t="n"/>
+      <c r="AC270" s="4" t="n"/>
+      <c r="AD270" s="4" t="n"/>
+    </row>
+    <row r="271">
+      <c r="T271" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="U271" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V271" s="7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="X271" s="7" t="n"/>
+      <c r="Y271" s="7" t="n"/>
+      <c r="Z271" s="7" t="n"/>
+      <c r="AB271" s="7" t="n"/>
+      <c r="AC271" s="7" t="n"/>
+      <c r="AD271" s="7" t="n"/>
+    </row>
+    <row r="272">
+      <c r="T272" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="U272" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V272" s="4" t="n">
+        <v>1935</v>
+      </c>
+      <c r="X272" s="4" t="n"/>
+      <c r="Y272" s="4" t="n"/>
+      <c r="Z272" s="4" t="n"/>
+      <c r="AB272" s="4" t="n"/>
+      <c r="AC272" s="4" t="n"/>
+      <c r="AD272" s="4" t="n"/>
+    </row>
+    <row r="273">
+      <c r="T273" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U273" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V273" s="7" t="n">
+        <v>2037</v>
+      </c>
+      <c r="X273" s="7" t="n"/>
+      <c r="Y273" s="7" t="n"/>
+      <c r="Z273" s="7" t="n"/>
+      <c r="AB273" s="7" t="n"/>
+      <c r="AC273" s="7" t="n"/>
+      <c r="AD273" s="7" t="n"/>
+    </row>
+    <row r="274">
+      <c r="T274" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="U274" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V274" s="4" t="n">
+        <v>2049</v>
+      </c>
+      <c r="X274" s="4" t="n"/>
+      <c r="Y274" s="4" t="n"/>
+      <c r="Z274" s="4" t="n"/>
+      <c r="AB274" s="4" t="n"/>
+      <c r="AC274" s="4" t="n"/>
+      <c r="AD274" s="4" t="n"/>
+    </row>
+    <row r="275">
+      <c r="T275" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="U275" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V275" s="7" t="n">
+        <v>2325</v>
+      </c>
+      <c r="X275" s="7" t="n"/>
+      <c r="Y275" s="7" t="n"/>
+      <c r="Z275" s="7" t="n"/>
+      <c r="AB275" s="7" t="n"/>
+      <c r="AC275" s="7" t="n"/>
+      <c r="AD275" s="7" t="n"/>
+    </row>
+    <row r="276">
+      <c r="T276" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="U276" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V276" s="4" t="n">
+        <v>2216</v>
+      </c>
+      <c r="X276" s="4" t="n"/>
+      <c r="Y276" s="4" t="n"/>
+      <c r="Z276" s="4" t="n"/>
+      <c r="AB276" s="4" t="n"/>
+      <c r="AC276" s="4" t="n"/>
+      <c r="AD276" s="4" t="n"/>
+    </row>
+    <row r="277">
+      <c r="T277" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="U277" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V277" s="7" t="n">
+        <v>2037</v>
+      </c>
+      <c r="X277" s="7" t="n"/>
+      <c r="Y277" s="7" t="n"/>
+      <c r="Z277" s="7" t="n"/>
+      <c r="AB277" s="7" t="n"/>
+      <c r="AC277" s="7" t="n"/>
+      <c r="AD277" s="7" t="n"/>
+    </row>
+    <row r="278">
+      <c r="T278" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U278" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V278" s="4" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X278" s="4" t="n"/>
+      <c r="Y278" s="4" t="n"/>
+      <c r="Z278" s="4" t="n"/>
+      <c r="AB278" s="4" t="n"/>
+      <c r="AC278" s="4" t="n"/>
+      <c r="AD278" s="4" t="n"/>
+    </row>
+    <row r="279">
+      <c r="T279" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="U279" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V279" s="7" t="n">
+        <v>2035</v>
+      </c>
+      <c r="X279" s="7" t="n"/>
+      <c r="Y279" s="7" t="n"/>
+      <c r="Z279" s="7" t="n"/>
+      <c r="AB279" s="7" t="n"/>
+      <c r="AC279" s="7" t="n"/>
+      <c r="AD279" s="7" t="n"/>
+    </row>
+    <row r="280">
+      <c r="T280" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U280" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V280" s="4" t="n">
+        <v>2182</v>
+      </c>
+      <c r="X280" s="4" t="n"/>
+      <c r="Y280" s="4" t="n"/>
+      <c r="Z280" s="4" t="n"/>
+      <c r="AB280" s="4" t="n"/>
+      <c r="AC280" s="4" t="n"/>
+      <c r="AD280" s="4" t="n"/>
+    </row>
+    <row r="281">
+      <c r="T281" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="U281" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V281" s="7" t="n">
+        <v>2156</v>
+      </c>
+      <c r="X281" s="7" t="n"/>
+      <c r="Y281" s="7" t="n"/>
+      <c r="Z281" s="7" t="n"/>
+      <c r="AB281" s="7" t="n"/>
+      <c r="AC281" s="7" t="n"/>
+      <c r="AD281" s="7" t="n"/>
+    </row>
+    <row r="282">
+      <c r="T282" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="U282" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V282" s="4" t="n">
+        <v>2437</v>
+      </c>
+      <c r="X282" s="4" t="n"/>
+      <c r="Y282" s="4" t="n"/>
+      <c r="Z282" s="4" t="n"/>
+      <c r="AB282" s="4" t="n"/>
+      <c r="AC282" s="4" t="n"/>
+      <c r="AD282" s="4" t="n"/>
+    </row>
+    <row r="283">
+      <c r="T283" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="U283" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V283" s="7" t="n">
+        <v>2214</v>
+      </c>
+      <c r="X283" s="7" t="n"/>
+      <c r="Y283" s="7" t="n"/>
+      <c r="Z283" s="7" t="n"/>
+      <c r="AB283" s="7" t="n"/>
+      <c r="AC283" s="7" t="n"/>
+      <c r="AD283" s="7" t="n"/>
+    </row>
+    <row r="284">
+      <c r="T284" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U284" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V284" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="X284" s="4" t="n"/>
+      <c r="Y284" s="4" t="n"/>
+      <c r="Z284" s="4" t="n"/>
+      <c r="AB284" s="4" t="n"/>
+      <c r="AC284" s="4" t="n"/>
+      <c r="AD284" s="4" t="n"/>
+    </row>
+    <row r="285">
+      <c r="T285" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U285" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V285" s="7" t="n">
+        <v>1973</v>
+      </c>
+      <c r="X285" s="7" t="n"/>
+      <c r="Y285" s="7" t="n"/>
+      <c r="Z285" s="7" t="n"/>
+      <c r="AB285" s="7" t="n"/>
+      <c r="AC285" s="7" t="n"/>
+      <c r="AD285" s="7" t="n"/>
+    </row>
+    <row r="286">
+      <c r="T286" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U286" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V286" s="4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="X286" s="4" t="n"/>
+      <c r="Y286" s="4" t="n"/>
+      <c r="Z286" s="4" t="n"/>
+      <c r="AB286" s="4" t="n"/>
+      <c r="AC286" s="4" t="n"/>
+      <c r="AD286" s="4" t="n"/>
+    </row>
+    <row r="287">
+      <c r="T287" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U287" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V287" s="7" t="n">
+        <v>2075</v>
+      </c>
+      <c r="X287" s="7" t="n"/>
+      <c r="Y287" s="7" t="n"/>
+      <c r="Z287" s="7" t="n"/>
+      <c r="AB287" s="7" t="n"/>
+      <c r="AC287" s="7" t="n"/>
+      <c r="AD287" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -716,10 +716,10 @@
         <v>0.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -752,10 +752,10 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -788,10 +788,10 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -824,10 +824,10 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -860,10 +860,10 @@
         <v>0.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -896,10 +896,10 @@
         <v>0.95</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -932,10 +932,10 @@
         <v>0.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -968,10 +968,10 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1004,10 +1004,10 @@
         <v>0.95</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1040,10 +1040,10 @@
         <v>0.95</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD287"/>
+  <dimension ref="A1:AD179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1344,15 +1344,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>103</v>
       </c>
@@ -1429,15 +1423,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>13</v>
       </c>
@@ -1514,15 +1502,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>64</v>
       </c>
@@ -1593,15 +1575,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>30</v>
       </c>
@@ -1678,15 +1654,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>21</v>
       </c>
@@ -1701,7 +1671,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1710,7 +1680,7 @@
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -1763,15 +1733,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>73</v>
       </c>
@@ -1786,7 +1750,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>157</v>
+        <v>2</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1795,7 +1759,7 @@
       </c>
       <c r="AD7" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -1848,15 +1812,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>15</v>
       </c>
@@ -1871,7 +1829,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1880,7 +1838,7 @@
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -1927,15 +1885,9 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>1</v>
       </c>
@@ -1950,7 +1902,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -1959,7 +1911,7 @@
       </c>
       <c r="AD9" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -2014,15 +1966,9 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>105</v>
       </c>
@@ -2037,16 +1983,16 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>1</v>
+        <v>428</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD10" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -2093,15 +2039,9 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>19</v>
       </c>
@@ -2116,7 +2056,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>428</v>
+        <v>27</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2125,7 +2065,7 @@
       </c>
       <c r="AD11" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -2172,15 +2112,9 @@
         <f>$B$2+H12+M12</f>
         <v/>
       </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>82</v>
       </c>
@@ -2195,7 +2129,7 @@
         </is>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
@@ -2204,7 +2138,7 @@
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -2251,15 +2185,9 @@
         <f>$B$2+H13+M13</f>
         <v/>
       </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>25</v>
       </c>
@@ -2274,7 +2202,7 @@
         </is>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
@@ -2283,7 +2211,7 @@
       </c>
       <c r="AD13" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -2330,15 +2258,9 @@
         <f>$B$2+H14+M14</f>
         <v/>
       </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>15</v>
       </c>
@@ -2353,7 +2275,7 @@
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2362,7 +2284,7 @@
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -2409,15 +2331,9 @@
         <f>$B$2+H15+M15</f>
         <v/>
       </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>75</v>
       </c>
@@ -2432,7 +2348,7 @@
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2441,7 +2357,7 @@
       </c>
       <c r="AD15" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -2488,15 +2404,9 @@
         <f>$B$2+H16+M16</f>
         <v/>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>9</v>
       </c>
@@ -2511,7 +2421,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2520,7 +2430,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -2567,15 +2477,9 @@
         <f>$B$2+H17+M17</f>
         <v/>
       </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>1</v>
       </c>
@@ -2590,7 +2494,7 @@
         </is>
       </c>
       <c r="AB17" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC17" s="7" t="inlineStr">
         <is>
@@ -2599,7 +2503,7 @@
       </c>
       <c r="AD17" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2550,9 @@
         <f>$B$2+H18+M18</f>
         <v/>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>145</v>
       </c>
@@ -2669,16 +2567,16 @@
         </is>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>4</v>
+        <v>478</v>
       </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -2725,15 +2623,9 @@
         <f>$B$2+H19+M19</f>
         <v/>
       </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>19</v>
       </c>
@@ -2748,16 +2640,16 @@
         </is>
       </c>
       <c r="AB19" s="7" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AC19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD19" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -2804,15 +2696,9 @@
         <f>$B$2+H20+M20</f>
         <v/>
       </c>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>74</v>
       </c>
@@ -2827,7 +2713,7 @@
         </is>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>478</v>
+        <v>183</v>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
@@ -2836,7 +2722,7 @@
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -2883,15 +2769,9 @@
         <f>$B$2+H21+M21</f>
         <v/>
       </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr"/>
-      <c r="V21" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>26</v>
       </c>
@@ -2906,7 +2786,7 @@
         </is>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -2915,7 +2795,7 @@
       </c>
       <c r="AD21" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -2962,15 +2842,9 @@
         <f>$B$2+H22+M22</f>
         <v/>
       </c>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>9</v>
       </c>
@@ -2985,7 +2859,7 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2994,7 +2868,7 @@
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
     </row>
@@ -3041,15 +2915,9 @@
         <f>$B$2+H23+M23</f>
         <v/>
       </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr"/>
-      <c r="V23" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
         <v>74</v>
       </c>
@@ -3064,7 +2932,7 @@
         </is>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -3073,7 +2941,7 @@
       </c>
       <c r="AD23" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -3096,19 +2964,9 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>5365</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
         <v>11</v>
       </c>
@@ -3123,7 +2981,7 @@
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
@@ -3132,7 +2990,7 @@
       </c>
       <c r="AD24" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -3155,19 +3013,9 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>5741</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>101</v>
       </c>
@@ -3182,7 +3030,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -3191,7 +3039,7 @@
       </c>
       <c r="AD25" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
@@ -3214,19 +3062,9 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>5451</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
         <v>11</v>
       </c>
@@ -3241,7 +3079,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -3250,7 +3088,7 @@
       </c>
       <c r="AD26" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
@@ -3273,19 +3111,9 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>5458</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
         <v>73</v>
       </c>
@@ -3300,16 +3128,16 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>3</v>
+        <v>515</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD27" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -3332,19 +3160,9 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>5664</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
         <v>31</v>
       </c>
@@ -3359,16 +3177,16 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD28" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -3391,19 +3209,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>5241</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>13</v>
       </c>
@@ -3418,16 +3226,16 @@
         </is>
       </c>
       <c r="AB29" s="7" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD29" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -3450,19 +3258,9 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>5102</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
         <v>78</v>
       </c>
@@ -3477,7 +3275,7 @@
         </is>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>515</v>
+        <v>54</v>
       </c>
       <c r="AC30" s="4" t="inlineStr">
         <is>
@@ -3486,7 +3284,7 @@
       </c>
       <c r="AD30" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -3509,19 +3307,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>5388</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
@@ -3536,7 +3324,7 @@
         </is>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3545,7 +3333,7 @@
       </c>
       <c r="AD31" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -3577,19 +3365,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>9</v>
       </c>
@@ -3604,7 +3382,7 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
@@ -3613,7 +3391,7 @@
       </c>
       <c r="AD32" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
@@ -3650,19 +3428,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>5348</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
@@ -3677,7 +3445,7 @@
         </is>
       </c>
       <c r="AB33" s="7" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="AC33" s="7" t="inlineStr">
         <is>
@@ -3686,24 +3454,14 @@
       </c>
       <c r="AD33" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>5329</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>119</v>
       </c>
@@ -3718,33 +3476,23 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>42</v>
+        <v>453</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD34" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>5436</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>13</v>
       </c>
@@ -3759,33 +3507,23 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD35" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>5081</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>67</v>
       </c>
@@ -3800,33 +3538,23 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD36" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>5034</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
         <v>32</v>
       </c>
@@ -3841,33 +3569,23 @@
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD37" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
         <v>13</v>
       </c>
@@ -3882,7 +3600,7 @@
         </is>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>453</v>
+        <v>147</v>
       </c>
       <c r="AC38" s="4" t="inlineStr">
         <is>
@@ -3891,24 +3609,14 @@
       </c>
       <c r="AD38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>5513</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>93</v>
       </c>
@@ -3923,7 +3631,7 @@
         </is>
       </c>
       <c r="AB39" s="7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AC39" s="7" t="inlineStr">
         <is>
@@ -3932,24 +3640,14 @@
       </c>
       <c r="AD39" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>5477</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>12</v>
       </c>
@@ -3964,7 +3662,7 @@
         </is>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>136</v>
+        <v>5</v>
       </c>
       <c r="AC40" s="4" t="inlineStr">
         <is>
@@ -3973,24 +3671,14 @@
       </c>
       <c r="AD40" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>5526</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>2</v>
       </c>
@@ -4005,7 +3693,7 @@
         </is>
       </c>
       <c r="AB41" s="7" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="AC41" s="7" t="inlineStr">
         <is>
@@ -4014,24 +3702,14 @@
       </c>
       <c r="AD41" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>113</v>
       </c>
@@ -4046,33 +3724,23 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>45</v>
+        <v>518</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD42" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>4933</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>12</v>
       </c>
@@ -4087,33 +3755,23 @@
         </is>
       </c>
       <c r="AB43" s="7" t="n">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="AC43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD43" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>4866</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>69</v>
       </c>
@@ -4128,33 +3786,23 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD44" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>5232</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>40</v>
       </c>
@@ -4169,33 +3817,23 @@
         </is>
       </c>
       <c r="AB45" s="7" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="AC45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD45" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>14969</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>17</v>
       </c>
@@ -4210,33 +3848,23 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD46" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>14818</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>83</v>
       </c>
@@ -4251,7 +3879,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>518</v>
+        <v>1</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -4260,24 +3888,14 @@
       </c>
       <c r="AD47" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>15263</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>9</v>
       </c>
@@ -4292,7 +3910,7 @@
         </is>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="AC48" s="4" t="inlineStr">
         <is>
@@ -4301,24 +3919,14 @@
       </c>
       <c r="AD48" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>124</v>
       </c>
@@ -4333,7 +3941,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4342,24 +3950,14 @@
       </c>
       <c r="AD49" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>14968</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>19</v>
       </c>
@@ -4374,33 +3972,23 @@
         </is>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>57</v>
+        <v>474</v>
       </c>
       <c r="AC50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD50" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>14113</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>55</v>
       </c>
@@ -4415,33 +4003,23 @@
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD51" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>14162</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
         <v>35</v>
       </c>
@@ -4456,33 +4034,23 @@
         </is>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD52" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>15</v>
       </c>
@@ -4497,33 +4065,23 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD53" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>82</v>
       </c>
@@ -4538,33 +4096,23 @@
         </is>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>4</v>
+        <v>129</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD54" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>15546</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>1</v>
       </c>
@@ -4579,33 +4127,23 @@
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD55" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>14882</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>14</v>
       </c>
@@ -4620,7 +4158,7 @@
         </is>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>474</v>
+        <v>1</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -4629,24 +4167,14 @@
       </c>
       <c r="AD56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>14998</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>2</v>
       </c>
@@ -4661,7 +4189,7 @@
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -4670,24 +4198,14 @@
       </c>
       <c r="AD57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>14354</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
         <v>101</v>
       </c>
@@ -4702,33 +4220,23 @@
         </is>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>138</v>
+        <v>430</v>
       </c>
       <c r="AC58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD58" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>14362</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
         <v>10</v>
       </c>
@@ -4743,33 +4251,23 @@
         </is>
       </c>
       <c r="AB59" s="7" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="AC59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD59" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>15089</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
         <v>72</v>
       </c>
@@ -4784,33 +4282,23 @@
         </is>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD60" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>14802</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
         <v>35</v>
       </c>
@@ -4825,33 +4313,23 @@
         </is>
       </c>
       <c r="AB61" s="7" t="n">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="AC61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD61" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>15349</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
         <v>13</v>
       </c>
@@ -4866,33 +4344,23 @@
         </is>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="AC62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD62" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>14872</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>71</v>
       </c>
@@ -4907,33 +4375,23 @@
         </is>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD63" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>15054</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
         <v>8</v>
       </c>
@@ -4948,33 +4406,23 @@
         </is>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD64" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>14169</v>
-      </c>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
         <v>2</v>
       </c>
@@ -4989,7 +4437,7 @@
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>430</v>
+        <v>2</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4998,24 +4446,14 @@
       </c>
       <c r="AD65" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>14056</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>125</v>
       </c>
@@ -5030,33 +4468,23 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>27</v>
+        <v>478</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>15058</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>11</v>
       </c>
@@ -5071,33 +4499,23 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD67" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>77546</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>67</v>
       </c>
@@ -5112,33 +4530,23 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>50</v>
+        <v>162</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD68" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>77823</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>27</v>
       </c>
@@ -5153,33 +4561,23 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD69" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>81723</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
         <v>17</v>
       </c>
@@ -5194,11 +4592,11 @@
         </is>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD70" s="4" t="inlineStr">
@@ -5208,19 +4606,9 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>78398</v>
-      </c>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
         <v>85</v>
       </c>
@@ -5235,11 +4623,11 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD71" s="7" t="inlineStr">
@@ -5249,19 +4637,9 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>78030</v>
-      </c>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
         <v>14</v>
       </c>
@@ -5276,11 +4654,11 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD72" s="4" t="inlineStr">
@@ -5290,19 +4668,9 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>76646</v>
-      </c>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
         <v>4</v>
       </c>
@@ -5317,11 +4685,11 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD73" s="7" t="inlineStr">
@@ -5331,19 +4699,9 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>76742</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
         <v>126</v>
       </c>
@@ -5358,11 +4716,11 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD74" s="4" t="inlineStr">
@@ -5372,19 +4730,9 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>79003</v>
-      </c>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
         <v>23</v>
       </c>
@@ -5399,11 +4747,11 @@
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD75" s="7" t="inlineStr">
@@ -5413,19 +4761,9 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>78849</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>65</v>
       </c>
@@ -5440,11 +4778,11 @@
         </is>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD76" s="4" t="inlineStr">
@@ -5454,19 +4792,9 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>80667</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
         <v>28</v>
       </c>
@@ -5481,11 +4809,11 @@
         </is>
       </c>
       <c r="AB77" s="7" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="AC77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD77" s="7" t="inlineStr">
@@ -5495,19 +4823,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>78640</v>
-      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
         <v>19</v>
       </c>
@@ -5522,33 +4840,23 @@
         </is>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>79108</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>91</v>
       </c>
@@ -5563,11 +4871,11 @@
         </is>
       </c>
       <c r="AB79" s="7" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AC79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD79" s="7" t="inlineStr">
@@ -5577,19 +4885,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>76911</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>21</v>
       </c>
@@ -5604,11 +4902,11 @@
         </is>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD80" s="4" t="inlineStr">
@@ -5618,19 +4916,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>77273</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
         <v>2</v>
       </c>
@@ -5645,11 +4933,11 @@
         </is>
       </c>
       <c r="AB81" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD81" s="7" t="inlineStr">
@@ -5659,19 +4947,9 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>80657</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
         <v>99</v>
       </c>
@@ -5686,11 +4964,11 @@
         </is>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD82" s="4" t="inlineStr">
@@ -5700,19 +4978,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>79898</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>12</v>
       </c>
@@ -5727,11 +4995,11 @@
         </is>
       </c>
       <c r="AB83" s="7" t="n">
-        <v>443</v>
+        <v>324</v>
       </c>
       <c r="AC83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD83" s="7" t="inlineStr">
@@ -5741,19 +5009,9 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>82443</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
         <v>70</v>
       </c>
@@ -5768,11 +5026,11 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD84" s="4" t="inlineStr">
@@ -5782,19 +5040,9 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>80658</v>
-      </c>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
         <v>30</v>
       </c>
@@ -5809,11 +5057,11 @@
         </is>
       </c>
       <c r="AB85" s="7" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD85" s="7" t="inlineStr">
@@ -5823,19 +5071,9 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>78475</v>
-      </c>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
         <v>15</v>
       </c>
@@ -5850,11 +5088,11 @@
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD86" s="4" t="inlineStr">
@@ -5864,19 +5102,9 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>76874</v>
-      </c>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
         <v>73</v>
       </c>
@@ -5891,33 +5119,23 @@
         </is>
       </c>
       <c r="AB87" s="7" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="AC87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD87" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>77058</v>
-      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
         <v>5</v>
       </c>
@@ -5936,29 +5154,19 @@
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD88" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>79206</v>
-      </c>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
         <v>1</v>
       </c>
@@ -5973,33 +5181,23 @@
         </is>
       </c>
       <c r="AB89" s="7" t="n">
-        <v>129</v>
+        <v>8</v>
       </c>
       <c r="AC89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD89" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
         <v>107</v>
       </c>
@@ -6018,29 +5216,19 @@
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD90" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>715</v>
-      </c>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
         <v>13</v>
       </c>
@@ -6055,33 +5243,23 @@
         </is>
       </c>
       <c r="AB91" s="7" t="n">
-        <v>7</v>
+        <v>327</v>
       </c>
       <c r="AC91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD91" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="T92" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V92" s="4" t="n">
-        <v>745</v>
-      </c>
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
       <c r="X92" s="4" t="n">
         <v>56</v>
       </c>
@@ -6096,33 +5274,23 @@
         </is>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD92" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U93" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>702</v>
-      </c>
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
         <v>32</v>
       </c>
@@ -6137,33 +5305,23 @@
         </is>
       </c>
       <c r="AB93" s="7" t="n">
-        <v>324</v>
+        <v>176</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD93" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="T94" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>743</v>
-      </c>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
         <v>13</v>
       </c>
@@ -6178,33 +5336,23 @@
         </is>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD94" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>700</v>
-      </c>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
         <v>78</v>
       </c>
@@ -6219,33 +5367,23 @@
         </is>
       </c>
       <c r="AB95" s="7" t="n">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD95" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="T96" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V96" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
       <c r="X96" s="4" t="n">
         <v>10</v>
       </c>
@@ -6260,33 +5398,23 @@
         </is>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD96" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V97" s="7" t="n">
-        <v>750</v>
-      </c>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
         <v>1</v>
       </c>
@@ -6301,33 +5429,23 @@
         </is>
       </c>
       <c r="AB97" s="7" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD97" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>729</v>
-      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
         <v>114</v>
       </c>
@@ -6342,33 +5460,23 @@
         </is>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>136</v>
+        <v>2</v>
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD98" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V99" s="7" t="n">
-        <v>748</v>
-      </c>
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
         <v>15</v>
       </c>
@@ -6383,33 +5491,23 @@
         </is>
       </c>
       <c r="AB99" s="7" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
       <c r="AC99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD99" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="T100" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>736</v>
-      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
         <v>53</v>
       </c>
@@ -6424,33 +5522,23 @@
         </is>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AC100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD100" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U101" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V101" s="7" t="n">
-        <v>737</v>
-      </c>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
         <v>32</v>
       </c>
@@ -6465,33 +5553,23 @@
         </is>
       </c>
       <c r="AB101" s="7" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="AC101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD101" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n">
-        <v>707</v>
-      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
         <v>14</v>
       </c>
@@ -6506,33 +5584,23 @@
         </is>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>327</v>
+        <v>51</v>
       </c>
       <c r="AC102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD102" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V103" s="7" t="n">
-        <v>713</v>
-      </c>
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
         <v>80</v>
       </c>
@@ -6547,33 +5615,23 @@
         </is>
       </c>
       <c r="AB103" s="7" t="n">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD103" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="T104" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U104" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V104" s="4" t="n">
-        <v>786</v>
-      </c>
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="4" t="n"/>
+      <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
         <v>1</v>
       </c>
@@ -6588,33 +5646,23 @@
         </is>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>176</v>
+        <v>3</v>
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD104" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="T105" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U105" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>730</v>
-      </c>
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
         <v>9</v>
       </c>
@@ -6629,33 +5677,23 @@
         </is>
       </c>
       <c r="AB105" s="7" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="AC105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD105" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="n">
-        <v>726</v>
-      </c>
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="4" t="n"/>
+      <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
         <v>4</v>
       </c>
@@ -6670,33 +5708,23 @@
         </is>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD106" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="T107" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U107" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V107" s="7" t="n">
-        <v>695</v>
-      </c>
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
         <v>97</v>
       </c>
@@ -6711,33 +5739,23 @@
         </is>
       </c>
       <c r="AB107" s="7" t="n">
-        <v>156</v>
+        <v>332</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD107" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="T108" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U108" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V108" s="4" t="n">
-        <v>693</v>
-      </c>
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="4" t="n"/>
+      <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
         <v>10</v>
       </c>
@@ -6752,33 +5770,23 @@
         </is>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD108" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U109" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V109" s="7" t="n">
-        <v>686</v>
-      </c>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
         <v>52</v>
       </c>
@@ -6793,33 +5801,23 @@
         </is>
       </c>
       <c r="AB109" s="7" t="n">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD109" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="T110" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U110" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V110" s="4" t="n">
-        <v>673</v>
-      </c>
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="n"/>
       <c r="X110" s="4" t="n">
         <v>37</v>
       </c>
@@ -6834,33 +5832,23 @@
         </is>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD110" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="T111" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U111" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V111" s="7" t="n">
-        <v>752</v>
-      </c>
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
       <c r="X111" s="7" t="n">
         <v>18</v>
       </c>
@@ -6875,33 +5863,23 @@
         </is>
       </c>
       <c r="AB111" s="7" t="n">
-        <v>319</v>
+        <v>141</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD111" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="T112" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U112" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V112" s="4" t="n">
-        <v>47976</v>
-      </c>
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="4" t="n"/>
+      <c r="V112" s="4" t="n"/>
       <c r="X112" s="4" t="n">
         <v>64</v>
       </c>
@@ -6916,33 +5894,23 @@
         </is>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD112" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="T113" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U113" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V113" s="7" t="n">
-        <v>47122</v>
-      </c>
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
         <v>7</v>
       </c>
@@ -6957,33 +5925,23 @@
         </is>
       </c>
       <c r="AB113" s="7" t="n">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD113" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="T114" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U114" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V114" s="4" t="n">
-        <v>47233</v>
-      </c>
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="n"/>
       <c r="X114" s="4" t="n">
         <v>106</v>
       </c>
@@ -6998,33 +5956,23 @@
         </is>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD114" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="T115" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U115" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V115" s="7" t="n">
-        <v>48580</v>
-      </c>
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
       <c r="X115" s="7" t="n">
         <v>14</v>
       </c>
@@ -7039,33 +5987,23 @@
         </is>
       </c>
       <c r="AB115" s="7" t="n">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD115" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="T116" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U116" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V116" s="4" t="n">
-        <v>47383</v>
-      </c>
+      <c r="T116" s="4" t="n"/>
+      <c r="U116" s="4" t="n"/>
+      <c r="V116" s="4" t="n"/>
       <c r="X116" s="4" t="n">
         <v>65</v>
       </c>
@@ -7080,33 +6018,23 @@
         </is>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD116" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="T117" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U117" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V117" s="7" t="n">
-        <v>46456</v>
-      </c>
+      <c r="T117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
       <c r="X117" s="7" t="n">
         <v>24</v>
       </c>
@@ -7121,33 +6049,23 @@
         </is>
       </c>
       <c r="AB117" s="7" t="n">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD117" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="T118" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U118" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V118" s="4" t="n">
-        <v>46400</v>
-      </c>
+      <c r="T118" s="4" t="n"/>
+      <c r="U118" s="4" t="n"/>
+      <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
         <v>14</v>
       </c>
@@ -7162,33 +6080,23 @@
         </is>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD118" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="T119" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U119" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V119" s="7" t="n">
-        <v>47755</v>
-      </c>
+      <c r="T119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
         <v>66</v>
       </c>
@@ -7203,33 +6111,23 @@
         </is>
       </c>
       <c r="AB119" s="7" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD119" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="T120" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U120" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="n">
-        <v>47520</v>
-      </c>
+      <c r="T120" s="4" t="n"/>
+      <c r="U120" s="4" t="n"/>
+      <c r="V120" s="4" t="n"/>
       <c r="X120" s="4" t="n">
         <v>1</v>
       </c>
@@ -7244,33 +6142,23 @@
         </is>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="AC120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD120" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="T121" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U121" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>47354</v>
-      </c>
+      <c r="T121" s="7" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
       <c r="X121" s="7" t="n">
         <v>9</v>
       </c>
@@ -7285,33 +6173,23 @@
         </is>
       </c>
       <c r="AB121" s="7" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AC121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD121" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="T122" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U122" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V122" s="4" t="n">
-        <v>49015</v>
-      </c>
+      <c r="T122" s="4" t="n"/>
+      <c r="U122" s="4" t="n"/>
+      <c r="V122" s="4" t="n"/>
       <c r="X122" s="4" t="n">
         <v>116</v>
       </c>
@@ -7326,33 +6204,23 @@
         </is>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="AC122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD122" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="T123" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U123" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V123" s="7" t="n">
-        <v>48832</v>
-      </c>
+      <c r="T123" s="7" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
       <c r="X123" s="7" t="n">
         <v>17</v>
       </c>
@@ -7367,33 +6235,23 @@
         </is>
       </c>
       <c r="AB123" s="7" t="n">
-        <v>54</v>
+        <v>350</v>
       </c>
       <c r="AC123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD123" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="T124" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U124" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="n">
-        <v>46644</v>
-      </c>
+      <c r="T124" s="4" t="n"/>
+      <c r="U124" s="4" t="n"/>
+      <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
         <v>52</v>
       </c>
@@ -7408,33 +6266,23 @@
         </is>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AC124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD124" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="T125" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V125" s="7" t="n">
-        <v>46416</v>
-      </c>
+      <c r="T125" s="7" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
         <v>38</v>
       </c>
@@ -7449,33 +6297,23 @@
         </is>
       </c>
       <c r="AB125" s="7" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="AC125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD125" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="T126" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U126" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V126" s="4" t="n">
-        <v>48419</v>
-      </c>
+      <c r="T126" s="4" t="n"/>
+      <c r="U126" s="4" t="n"/>
+      <c r="V126" s="4" t="n"/>
       <c r="X126" s="4" t="n">
         <v>19</v>
       </c>
@@ -7490,33 +6328,23 @@
         </is>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD126" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="T127" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U127" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V127" s="7" t="n">
-        <v>47500</v>
-      </c>
+      <c r="T127" s="7" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
       <c r="X127" s="7" t="n">
         <v>79</v>
       </c>
@@ -7531,33 +6359,23 @@
         </is>
       </c>
       <c r="AB127" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD127" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="T128" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U128" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V128" s="4" t="n">
-        <v>47954</v>
-      </c>
+      <c r="T128" s="4" t="n"/>
+      <c r="U128" s="4" t="n"/>
+      <c r="V128" s="4" t="n"/>
       <c r="X128" s="4" t="n">
         <v>9</v>
       </c>
@@ -7572,33 +6390,23 @@
         </is>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD128" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="T129" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U129" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V129" s="7" t="n">
-        <v>49088</v>
-      </c>
+      <c r="T129" s="7" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
       <c r="X129" s="7" t="n">
         <v>1</v>
       </c>
@@ -7613,33 +6421,23 @@
         </is>
       </c>
       <c r="AB129" s="7" t="n">
-        <v>323</v>
+        <v>3</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD129" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="T130" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U130" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V130" s="4" t="n">
-        <v>48111</v>
-      </c>
+      <c r="T130" s="4" t="n"/>
+      <c r="U130" s="4" t="n"/>
+      <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
         <v>134</v>
       </c>
@@ -7654,33 +6452,23 @@
         </is>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD130" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="T131" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U131" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V131" s="7" t="n">
-        <v>46535</v>
-      </c>
+      <c r="T131" s="7" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
         <v>22</v>
       </c>
@@ -7695,33 +6483,23 @@
         </is>
       </c>
       <c r="AB131" s="7" t="n">
-        <v>132</v>
+        <v>319</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD131" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="T132" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U132" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V132" s="4" t="n">
-        <v>46063</v>
-      </c>
+      <c r="T132" s="4" t="n"/>
+      <c r="U132" s="4" t="n"/>
+      <c r="V132" s="4" t="n"/>
       <c r="X132" s="4" t="n">
         <v>65</v>
       </c>
@@ -7736,33 +6514,23 @@
         </is>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD132" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="T133" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U133" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V133" s="7" t="n">
-        <v>48085</v>
-      </c>
+      <c r="T133" s="7" t="n"/>
+      <c r="U133" s="7" t="n"/>
+      <c r="V133" s="7" t="n"/>
       <c r="X133" s="7" t="n">
         <v>29</v>
       </c>
@@ -7777,33 +6545,23 @@
         </is>
       </c>
       <c r="AB133" s="7" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD133" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="T134" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U134" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V134" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="4" t="n"/>
+      <c r="V134" s="4" t="n"/>
       <c r="X134" s="4" t="n">
         <v>12</v>
       </c>
@@ -7818,33 +6576,23 @@
         </is>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD134" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="T135" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U135" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V135" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T135" s="7" t="n"/>
+      <c r="U135" s="7" t="n"/>
+      <c r="V135" s="7" t="n"/>
       <c r="X135" s="7" t="n">
         <v>82</v>
       </c>
@@ -7859,33 +6607,23 @@
         </is>
       </c>
       <c r="AB135" s="7" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD135" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="T136" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U136" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V136" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T136" s="4" t="n"/>
+      <c r="U136" s="4" t="n"/>
+      <c r="V136" s="4" t="n"/>
       <c r="X136" s="4" t="n">
         <v>1</v>
       </c>
@@ -7900,33 +6638,23 @@
         </is>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD136" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="T137" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U137" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V137" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T137" s="7" t="n"/>
+      <c r="U137" s="7" t="n"/>
+      <c r="V137" s="7" t="n"/>
       <c r="X137" s="7" t="n">
         <v>7</v>
       </c>
@@ -7941,33 +6669,23 @@
         </is>
       </c>
       <c r="AB137" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD137" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="T138" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U138" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V138" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T138" s="4" t="n"/>
+      <c r="U138" s="4" t="n"/>
+      <c r="V138" s="4" t="n"/>
       <c r="X138" s="4" t="n">
         <v>1</v>
       </c>
@@ -7982,33 +6700,23 @@
         </is>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>350</v>
+        <v>2</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD138" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="T139" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U139" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V139" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T139" s="7" t="n"/>
+      <c r="U139" s="7" t="n"/>
+      <c r="V139" s="7" t="n"/>
       <c r="X139" s="7" t="n">
         <v>107</v>
       </c>
@@ -8023,33 +6731,23 @@
         </is>
       </c>
       <c r="AB139" s="7" t="n">
-        <v>23</v>
+        <v>325</v>
       </c>
       <c r="AC139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD139" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="T140" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U140" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V140" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T140" s="4" t="n"/>
+      <c r="U140" s="4" t="n"/>
+      <c r="V140" s="4" t="n"/>
       <c r="X140" s="4" t="n">
         <v>24</v>
       </c>
@@ -8064,33 +6762,23 @@
         </is>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD140" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="T141" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U141" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V141" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T141" s="7" t="n"/>
+      <c r="U141" s="7" t="n"/>
+      <c r="V141" s="7" t="n"/>
       <c r="X141" s="7" t="n">
         <v>68</v>
       </c>
@@ -8105,33 +6793,23 @@
         </is>
       </c>
       <c r="AB141" s="7" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AC141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD141" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="T142" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U142" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V142" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T142" s="4" t="n"/>
+      <c r="U142" s="4" t="n"/>
+      <c r="V142" s="4" t="n"/>
       <c r="X142" s="4" t="n">
         <v>18</v>
       </c>
@@ -8146,33 +6824,23 @@
         </is>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD142" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="T143" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U143" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V143" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T143" s="7" t="n"/>
+      <c r="U143" s="7" t="n"/>
+      <c r="V143" s="7" t="n"/>
       <c r="X143" s="7" t="n">
         <v>12</v>
       </c>
@@ -8187,33 +6855,23 @@
         </is>
       </c>
       <c r="AB143" s="7" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD143" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="T144" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U144" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V144" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T144" s="4" t="n"/>
+      <c r="U144" s="4" t="n"/>
+      <c r="V144" s="4" t="n"/>
       <c r="X144" s="4" t="n">
         <v>70</v>
       </c>
@@ -8228,33 +6886,23 @@
         </is>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="AC144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD144" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="T145" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U145" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V145" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T145" s="7" t="n"/>
+      <c r="U145" s="7" t="n"/>
+      <c r="V145" s="7" t="n"/>
       <c r="X145" s="7" t="n">
         <v>2</v>
       </c>
@@ -8269,33 +6917,23 @@
         </is>
       </c>
       <c r="AB145" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD145" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="T146" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U146" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V146" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
       <c r="X146" s="4" t="n">
         <v>6</v>
       </c>
@@ -8310,33 +6948,23 @@
         </is>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD146" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="T147" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U147" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V147" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T147" s="7" t="n"/>
+      <c r="U147" s="7" t="n"/>
+      <c r="V147" s="7" t="n"/>
       <c r="X147" s="7" t="n">
         <v>2</v>
       </c>
@@ -8351,11 +6979,11 @@
         </is>
       </c>
       <c r="AB147" s="7" t="n">
-        <v>319</v>
+        <v>380</v>
       </c>
       <c r="AC147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AD147" s="7" t="inlineStr">
@@ -8365,19 +6993,9 @@
       </c>
     </row>
     <row r="148">
-      <c r="T148" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U148" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V148" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T148" s="4" t="n"/>
+      <c r="U148" s="4" t="n"/>
+      <c r="V148" s="4" t="n"/>
       <c r="X148" s="4" t="n">
         <v>115</v>
       </c>
@@ -8392,11 +7010,11 @@
         </is>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AC148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AD148" s="4" t="inlineStr">
@@ -8406,19 +7024,9 @@
       </c>
     </row>
     <row r="149">
-      <c r="T149" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U149" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V149" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T149" s="7" t="n"/>
+      <c r="U149" s="7" t="n"/>
+      <c r="V149" s="7" t="n"/>
       <c r="X149" s="7" t="n">
         <v>20</v>
       </c>
@@ -8433,11 +7041,11 @@
         </is>
       </c>
       <c r="AB149" s="7" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="AC149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AD149" s="7" t="inlineStr">
@@ -8447,19 +7055,9 @@
       </c>
     </row>
     <row r="150">
-      <c r="T150" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U150" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="4" t="n"/>
+      <c r="V150" s="4" t="n"/>
       <c r="X150" s="4" t="n">
         <v>69</v>
       </c>
@@ -8474,11 +7072,11 @@
         </is>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AD150" s="4" t="inlineStr">
@@ -8488,19 +7086,9 @@
       </c>
     </row>
     <row r="151">
-      <c r="T151" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V151" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T151" s="7" t="n"/>
+      <c r="U151" s="7" t="n"/>
+      <c r="V151" s="7" t="n"/>
       <c r="X151" s="7" t="n">
         <v>41</v>
       </c>
@@ -8515,33 +7103,23 @@
         </is>
       </c>
       <c r="AB151" s="7" t="n">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="AC151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AD151" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="T152" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U152" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="4" t="n"/>
+      <c r="V152" s="4" t="n"/>
       <c r="X152" s="4" t="n">
         <v>5</v>
       </c>
@@ -8556,33 +7134,23 @@
         </is>
       </c>
       <c r="AB152" s="4" t="n">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="AC152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AD152" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="T153" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U153" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V153" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T153" s="7" t="n"/>
+      <c r="U153" s="7" t="n"/>
+      <c r="V153" s="7" t="n"/>
       <c r="X153" s="7" t="n">
         <v>95</v>
       </c>
@@ -8601,29 +7169,19 @@
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AD153" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="T154" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U154" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T154" s="4" t="n"/>
+      <c r="U154" s="4" t="n"/>
+      <c r="V154" s="4" t="n"/>
       <c r="X154" s="4" t="n">
         <v>1</v>
       </c>
@@ -8638,33 +7196,23 @@
         </is>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>5</v>
+        <v>367</v>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD154" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="T155" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V155" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T155" s="7" t="n"/>
+      <c r="U155" s="7" t="n"/>
+      <c r="V155" s="7" t="n"/>
       <c r="X155" s="7" t="n">
         <v>9</v>
       </c>
@@ -8679,33 +7227,23 @@
         </is>
       </c>
       <c r="AB155" s="7" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="AC155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD155" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="T156" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U156" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="4" t="n"/>
+      <c r="V156" s="4" t="n"/>
       <c r="X156" s="4" t="n">
         <v>2</v>
       </c>
@@ -8720,33 +7258,23 @@
         </is>
       </c>
       <c r="AB156" s="4" t="n">
-        <v>325</v>
+        <v>166</v>
       </c>
       <c r="AC156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD156" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="T157" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U157" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V157" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T157" s="7" t="n"/>
+      <c r="U157" s="7" t="n"/>
+      <c r="V157" s="7" t="n"/>
       <c r="X157" s="7" t="n">
         <v>114</v>
       </c>
@@ -8761,33 +7289,23 @@
         </is>
       </c>
       <c r="AB157" s="7" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AC157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD157" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="T158" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U158" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V158" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T158" s="4" t="n"/>
+      <c r="U158" s="4" t="n"/>
+      <c r="V158" s="4" t="n"/>
       <c r="X158" s="4" t="n">
         <v>16</v>
       </c>
@@ -8802,33 +7320,23 @@
         </is>
       </c>
       <c r="AB158" s="4" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AC158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD158" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="T159" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U159" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V159" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T159" s="7" t="n"/>
+      <c r="U159" s="7" t="n"/>
+      <c r="V159" s="7" t="n"/>
       <c r="X159" s="7" t="n">
         <v>60</v>
       </c>
@@ -8843,33 +7351,23 @@
         </is>
       </c>
       <c r="AB159" s="7" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="AC159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD159" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="T160" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U160" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="4" t="n"/>
+      <c r="V160" s="4" t="n"/>
       <c r="X160" s="4" t="n">
         <v>41</v>
       </c>
@@ -8884,33 +7382,23 @@
         </is>
       </c>
       <c r="AB160" s="4" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="AC160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD160" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="T161" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U161" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V161" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T161" s="7" t="n"/>
+      <c r="U161" s="7" t="n"/>
+      <c r="V161" s="7" t="n"/>
       <c r="X161" s="7" t="n">
         <v>14</v>
       </c>
@@ -8925,33 +7413,23 @@
         </is>
       </c>
       <c r="AB161" s="7" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="AC161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD161" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="T162" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U162" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V162" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="4" t="n"/>
+      <c r="V162" s="4" t="n"/>
       <c r="X162" s="4" t="n">
         <v>84</v>
       </c>
@@ -8966,33 +7444,23 @@
         </is>
       </c>
       <c r="AB162" s="4" t="n">
-        <v>2</v>
+        <v>388</v>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD162" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="T163" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U163" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V163" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T163" s="7" t="n"/>
+      <c r="U163" s="7" t="n"/>
+      <c r="V163" s="7" t="n"/>
       <c r="X163" s="7" t="n">
         <v>8</v>
       </c>
@@ -9007,33 +7475,23 @@
         </is>
       </c>
       <c r="AB163" s="7" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="AC163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD163" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="T164" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U164" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V164" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="4" t="n"/>
+      <c r="V164" s="4" t="n"/>
       <c r="X164" s="4" t="n">
         <v>1</v>
       </c>
@@ -9048,33 +7506,23 @@
         </is>
       </c>
       <c r="AB164" s="4" t="n">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="AC164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD164" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="T165" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U165" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V165" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T165" s="7" t="n"/>
+      <c r="U165" s="7" t="n"/>
+      <c r="V165" s="7" t="n"/>
       <c r="X165" s="7" t="n">
         <v>144</v>
       </c>
@@ -9089,33 +7537,23 @@
         </is>
       </c>
       <c r="AB165" s="7" t="n">
-        <v>380</v>
+        <v>45</v>
       </c>
       <c r="AC165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD165" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="T166" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U166" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V166" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="4" t="n"/>
+      <c r="V166" s="4" t="n"/>
       <c r="X166" s="4" t="n">
         <v>16</v>
       </c>
@@ -9130,33 +7568,23 @@
         </is>
       </c>
       <c r="AB166" s="4" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="AC166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD166" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="T167" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U167" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V167" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T167" s="7" t="n"/>
+      <c r="U167" s="7" t="n"/>
+      <c r="V167" s="7" t="n"/>
       <c r="X167" s="7" t="n">
         <v>66</v>
       </c>
@@ -9171,33 +7599,23 @@
         </is>
       </c>
       <c r="AB167" s="7" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="AC167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD167" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="T168" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U168" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V168" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="4" t="n"/>
+      <c r="V168" s="4" t="n"/>
       <c r="X168" s="4" t="n">
         <v>35</v>
       </c>
@@ -9212,33 +7630,23 @@
         </is>
       </c>
       <c r="AB168" s="4" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="AC168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD168" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="T169" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U169" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V169" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T169" s="7" t="n"/>
+      <c r="U169" s="7" t="n"/>
+      <c r="V169" s="7" t="n"/>
       <c r="X169" s="7" t="n">
         <v>15</v>
       </c>
@@ -9253,33 +7661,23 @@
         </is>
       </c>
       <c r="AB169" s="7" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="AC169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD169" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="T170" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U170" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V170" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="4" t="n"/>
+      <c r="V170" s="4" t="n"/>
       <c r="X170" s="4" t="n">
         <v>83</v>
       </c>
@@ -9294,33 +7692,23 @@
         </is>
       </c>
       <c r="AB170" s="4" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="AC170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD170" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="T171" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U171" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V171" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T171" s="7" t="n"/>
+      <c r="U171" s="7" t="n"/>
+      <c r="V171" s="7" t="n"/>
       <c r="X171" s="7" t="n">
         <v>6</v>
       </c>
@@ -9335,33 +7723,23 @@
         </is>
       </c>
       <c r="AB171" s="7" t="n">
-        <v>2</v>
+        <v>292</v>
       </c>
       <c r="AC171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD171" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="T172" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U172" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V172" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="4" t="n"/>
+      <c r="V172" s="4" t="n"/>
       <c r="X172" s="4" t="n">
         <v>104</v>
       </c>
@@ -9376,33 +7754,23 @@
         </is>
       </c>
       <c r="AB172" s="4" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="AC172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD172" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="T173" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U173" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V173" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T173" s="7" t="n"/>
+      <c r="U173" s="7" t="n"/>
+      <c r="V173" s="7" t="n"/>
       <c r="X173" s="7" t="n">
         <v>17</v>
       </c>
@@ -9417,33 +7785,23 @@
         </is>
       </c>
       <c r="AB173" s="7" t="n">
-        <v>367</v>
+        <v>157</v>
       </c>
       <c r="AC173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD173" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="T174" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U174" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V174" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="n"/>
+      <c r="V174" s="4" t="n"/>
       <c r="X174" s="4" t="n">
         <v>72</v>
       </c>
@@ -9458,33 +7816,23 @@
         </is>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AC174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD174" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="T175" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U175" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V175" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T175" s="7" t="n"/>
+      <c r="U175" s="7" t="n"/>
+      <c r="V175" s="7" t="n"/>
       <c r="X175" s="7" t="n">
         <v>43</v>
       </c>
@@ -9499,33 +7847,23 @@
         </is>
       </c>
       <c r="AB175" s="7" t="n">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="AC175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD175" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="T176" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U176" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V176" s="4" t="n">
-        <v>9927</v>
-      </c>
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="4" t="n"/>
+      <c r="V176" s="4" t="n"/>
       <c r="X176" s="4" t="n">
         <v>20</v>
       </c>
@@ -9540,33 +7878,23 @@
         </is>
       </c>
       <c r="AB176" s="4" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="AC176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD176" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="T177" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U177" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V177" s="7" t="n">
-        <v>9839</v>
-      </c>
+      <c r="T177" s="7" t="n"/>
+      <c r="U177" s="7" t="n"/>
+      <c r="V177" s="7" t="n"/>
       <c r="X177" s="7" t="n">
         <v>133</v>
       </c>
@@ -9581,33 +7909,23 @@
         </is>
       </c>
       <c r="AB177" s="7" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="AC177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD177" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="T178" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U178" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V178" s="4" t="n">
-        <v>9918</v>
-      </c>
+      <c r="T178" s="4" t="n"/>
+      <c r="U178" s="4" t="n"/>
+      <c r="V178" s="4" t="n"/>
       <c r="X178" s="4" t="n">
         <v>7</v>
       </c>
@@ -9622,33 +7940,23 @@
         </is>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="AC178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD178" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="T179" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U179" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V179" s="7" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T179" s="7" t="n"/>
+      <c r="U179" s="7" t="n"/>
+      <c r="V179" s="7" t="n"/>
       <c r="X179" s="7" t="n">
         <v>2</v>
       </c>
@@ -9662,2497 +7970,9 @@
           <t>com.logistics.rider.foody</t>
         </is>
       </c>
-      <c r="AB179" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC179" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AD179" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="T180" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U180" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V180" s="4" t="n">
-        <v>10050</v>
-      </c>
-      <c r="X180" s="4" t="n"/>
-      <c r="Y180" s="4" t="n"/>
-      <c r="Z180" s="4" t="n"/>
-      <c r="AB180" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC180" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AD180" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="T181" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U181" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V181" s="7" t="n">
-        <v>9768</v>
-      </c>
-      <c r="X181" s="7" t="n"/>
-      <c r="Y181" s="7" t="n"/>
-      <c r="Z181" s="7" t="n"/>
-      <c r="AB181" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC181" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AD181" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="T182" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U182" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V182" s="4" t="n">
-        <v>9920</v>
-      </c>
-      <c r="X182" s="4" t="n"/>
-      <c r="Y182" s="4" t="n"/>
-      <c r="Z182" s="4" t="n"/>
-      <c r="AB182" s="4" t="n">
-        <v>388</v>
-      </c>
-      <c r="AC182" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD182" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="T183" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U183" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V183" s="7" t="n">
-        <v>10435</v>
-      </c>
-      <c r="X183" s="7" t="n"/>
-      <c r="Y183" s="7" t="n"/>
-      <c r="Z183" s="7" t="n"/>
-      <c r="AB183" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC183" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD183" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="T184" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U184" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V184" s="4" t="n">
-        <v>10434</v>
-      </c>
-      <c r="X184" s="4" t="n"/>
-      <c r="Y184" s="4" t="n"/>
-      <c r="Z184" s="4" t="n"/>
-      <c r="AB184" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="AC184" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD184" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="T185" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U185" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V185" s="7" t="n">
-        <v>10284</v>
-      </c>
-      <c r="X185" s="7" t="n"/>
-      <c r="Y185" s="7" t="n"/>
-      <c r="Z185" s="7" t="n"/>
-      <c r="AB185" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="AC185" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD185" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="T186" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U186" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V186" s="4" t="n">
-        <v>10458</v>
-      </c>
-      <c r="X186" s="4" t="n"/>
-      <c r="Y186" s="4" t="n"/>
-      <c r="Z186" s="4" t="n"/>
-      <c r="AB186" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="AC186" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD186" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="T187" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U187" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V187" s="7" t="n">
-        <v>10153</v>
-      </c>
-      <c r="X187" s="7" t="n"/>
-      <c r="Y187" s="7" t="n"/>
-      <c r="Z187" s="7" t="n"/>
-      <c r="AB187" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC187" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD187" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="T188" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U188" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V188" s="4" t="n">
-        <v>9843</v>
-      </c>
-      <c r="X188" s="4" t="n"/>
-      <c r="Y188" s="4" t="n"/>
-      <c r="Z188" s="4" t="n"/>
-      <c r="AB188" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="AC188" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD188" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="T189" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U189" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V189" s="7" t="n">
-        <v>10433</v>
-      </c>
-      <c r="X189" s="7" t="n"/>
-      <c r="Y189" s="7" t="n"/>
-      <c r="Z189" s="7" t="n"/>
-      <c r="AB189" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC189" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD189" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="T190" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U190" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V190" s="4" t="n">
-        <v>10670</v>
-      </c>
-      <c r="X190" s="4" t="n"/>
-      <c r="Y190" s="4" t="n"/>
-      <c r="Z190" s="4" t="n"/>
-      <c r="AB190" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC190" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD190" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="T191" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U191" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V191" s="7" t="n">
-        <v>10599</v>
-      </c>
-      <c r="X191" s="7" t="n"/>
-      <c r="Y191" s="7" t="n"/>
-      <c r="Z191" s="7" t="n"/>
-      <c r="AB191" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC191" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AD191" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="T192" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U192" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V192" s="4" t="n">
-        <v>10619</v>
-      </c>
-      <c r="X192" s="4" t="n"/>
-      <c r="Y192" s="4" t="n"/>
-      <c r="Z192" s="4" t="n"/>
-      <c r="AB192" s="4" t="n">
-        <v>292</v>
-      </c>
-      <c r="AC192" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD192" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="T193" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U193" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V193" s="7" t="n">
-        <v>10415</v>
-      </c>
-      <c r="X193" s="7" t="n"/>
-      <c r="Y193" s="7" t="n"/>
-      <c r="Z193" s="7" t="n"/>
-      <c r="AB193" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC193" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD193" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="T194" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U194" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V194" s="4" t="n">
-        <v>10065</v>
-      </c>
-      <c r="X194" s="4" t="n"/>
-      <c r="Y194" s="4" t="n"/>
-      <c r="Z194" s="4" t="n"/>
-      <c r="AB194" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="AC194" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD194" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="T195" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U195" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V195" s="7" t="n">
-        <v>10158</v>
-      </c>
-      <c r="X195" s="7" t="n"/>
-      <c r="Y195" s="7" t="n"/>
-      <c r="Z195" s="7" t="n"/>
-      <c r="AB195" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AC195" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD195" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="T196" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U196" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V196" s="4" t="n">
-        <v>10333</v>
-      </c>
-      <c r="X196" s="4" t="n"/>
-      <c r="Y196" s="4" t="n"/>
-      <c r="Z196" s="4" t="n"/>
-      <c r="AB196" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC196" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD196" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="T197" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U197" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V197" s="7" t="n">
-        <v>10414</v>
-      </c>
-      <c r="X197" s="7" t="n"/>
-      <c r="Y197" s="7" t="n"/>
-      <c r="Z197" s="7" t="n"/>
-      <c r="AB197" s="7" t="n">
-        <v>122</v>
-      </c>
-      <c r="AC197" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD197" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="T198" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U198" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation50987</t>
-        </is>
-      </c>
-      <c r="V198" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X198" s="4" t="n"/>
-      <c r="Y198" s="4" t="n"/>
-      <c r="Z198" s="4" t="n"/>
-      <c r="AB198" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC198" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD198" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="T199" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U199" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation75114</t>
-        </is>
-      </c>
-      <c r="V199" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X199" s="7" t="n"/>
-      <c r="Y199" s="7" t="n"/>
-      <c r="Z199" s="7" t="n"/>
-      <c r="AB199" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC199" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD199" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="T200" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U200" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V200" s="4" t="n">
-        <v>21493</v>
-      </c>
-      <c r="X200" s="4" t="n"/>
-      <c r="Y200" s="4" t="n"/>
-      <c r="Z200" s="4" t="n"/>
-      <c r="AB200" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC200" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AD200" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="T201" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U201" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V201" s="7" t="n">
-        <v>21012</v>
-      </c>
-      <c r="X201" s="7" t="n"/>
-      <c r="Y201" s="7" t="n"/>
-      <c r="Z201" s="7" t="n"/>
-      <c r="AB201" s="7" t="n"/>
-      <c r="AC201" s="7" t="n"/>
-      <c r="AD201" s="7" t="n"/>
-    </row>
-    <row r="202">
-      <c r="T202" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U202" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V202" s="4" t="n">
-        <v>21635</v>
-      </c>
-      <c r="X202" s="4" t="n"/>
-      <c r="Y202" s="4" t="n"/>
-      <c r="Z202" s="4" t="n"/>
-      <c r="AB202" s="4" t="n"/>
-      <c r="AC202" s="4" t="n"/>
-      <c r="AD202" s="4" t="n"/>
-    </row>
-    <row r="203">
-      <c r="T203" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U203" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V203" s="7" t="n">
-        <v>21969</v>
-      </c>
-      <c r="X203" s="7" t="n"/>
-      <c r="Y203" s="7" t="n"/>
-      <c r="Z203" s="7" t="n"/>
-      <c r="AB203" s="7" t="n"/>
-      <c r="AC203" s="7" t="n"/>
-      <c r="AD203" s="7" t="n"/>
-    </row>
-    <row r="204">
-      <c r="T204" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U204" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V204" s="4" t="n">
-        <v>21723</v>
-      </c>
-      <c r="X204" s="4" t="n"/>
-      <c r="Y204" s="4" t="n"/>
-      <c r="Z204" s="4" t="n"/>
-      <c r="AB204" s="4" t="n"/>
-      <c r="AC204" s="4" t="n"/>
-      <c r="AD204" s="4" t="n"/>
-    </row>
-    <row r="205">
-      <c r="T205" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U205" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V205" s="7" t="n">
-        <v>20879</v>
-      </c>
-      <c r="X205" s="7" t="n"/>
-      <c r="Y205" s="7" t="n"/>
-      <c r="Z205" s="7" t="n"/>
-      <c r="AB205" s="7" t="n"/>
-      <c r="AC205" s="7" t="n"/>
-      <c r="AD205" s="7" t="n"/>
-    </row>
-    <row r="206">
-      <c r="T206" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U206" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V206" s="4" t="n">
-        <v>20783</v>
-      </c>
-      <c r="X206" s="4" t="n"/>
-      <c r="Y206" s="4" t="n"/>
-      <c r="Z206" s="4" t="n"/>
-      <c r="AB206" s="4" t="n"/>
-      <c r="AC206" s="4" t="n"/>
-      <c r="AD206" s="4" t="n"/>
-    </row>
-    <row r="207">
-      <c r="T207" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U207" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V207" s="7" t="n">
-        <v>21875</v>
-      </c>
-      <c r="X207" s="7" t="n"/>
-      <c r="Y207" s="7" t="n"/>
-      <c r="Z207" s="7" t="n"/>
-      <c r="AB207" s="7" t="n"/>
-      <c r="AC207" s="7" t="n"/>
-      <c r="AD207" s="7" t="n"/>
-    </row>
-    <row r="208">
-      <c r="T208" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U208" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V208" s="4" t="n">
-        <v>22103</v>
-      </c>
-      <c r="X208" s="4" t="n"/>
-      <c r="Y208" s="4" t="n"/>
-      <c r="Z208" s="4" t="n"/>
-      <c r="AB208" s="4" t="n"/>
-      <c r="AC208" s="4" t="n"/>
-      <c r="AD208" s="4" t="n"/>
-    </row>
-    <row r="209">
-      <c r="T209" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U209" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V209" s="7" t="n">
-        <v>22799</v>
-      </c>
-      <c r="X209" s="7" t="n"/>
-      <c r="Y209" s="7" t="n"/>
-      <c r="Z209" s="7" t="n"/>
-      <c r="AB209" s="7" t="n"/>
-      <c r="AC209" s="7" t="n"/>
-      <c r="AD209" s="7" t="n"/>
-    </row>
-    <row r="210">
-      <c r="T210" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U210" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V210" s="4" t="n">
-        <v>22705</v>
-      </c>
-      <c r="X210" s="4" t="n"/>
-      <c r="Y210" s="4" t="n"/>
-      <c r="Z210" s="4" t="n"/>
-      <c r="AB210" s="4" t="n"/>
-      <c r="AC210" s="4" t="n"/>
-      <c r="AD210" s="4" t="n"/>
-    </row>
-    <row r="211">
-      <c r="T211" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U211" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V211" s="7" t="n">
-        <v>21885</v>
-      </c>
-      <c r="X211" s="7" t="n"/>
-      <c r="Y211" s="7" t="n"/>
-      <c r="Z211" s="7" t="n"/>
-      <c r="AB211" s="7" t="n"/>
-      <c r="AC211" s="7" t="n"/>
-      <c r="AD211" s="7" t="n"/>
-    </row>
-    <row r="212">
-      <c r="T212" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U212" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V212" s="4" t="n">
-        <v>21360</v>
-      </c>
-      <c r="X212" s="4" t="n"/>
-      <c r="Y212" s="4" t="n"/>
-      <c r="Z212" s="4" t="n"/>
-      <c r="AB212" s="4" t="n"/>
-      <c r="AC212" s="4" t="n"/>
-      <c r="AD212" s="4" t="n"/>
-    </row>
-    <row r="213">
-      <c r="T213" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U213" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V213" s="7" t="n">
-        <v>20612</v>
-      </c>
-      <c r="X213" s="7" t="n"/>
-      <c r="Y213" s="7" t="n"/>
-      <c r="Z213" s="7" t="n"/>
-      <c r="AB213" s="7" t="n"/>
-      <c r="AC213" s="7" t="n"/>
-      <c r="AD213" s="7" t="n"/>
-    </row>
-    <row r="214">
-      <c r="T214" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U214" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V214" s="4" t="n">
-        <v>22101</v>
-      </c>
-      <c r="X214" s="4" t="n"/>
-      <c r="Y214" s="4" t="n"/>
-      <c r="Z214" s="4" t="n"/>
-      <c r="AB214" s="4" t="n"/>
-      <c r="AC214" s="4" t="n"/>
-      <c r="AD214" s="4" t="n"/>
-    </row>
-    <row r="215">
-      <c r="T215" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U215" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V215" s="7" t="n">
-        <v>22665</v>
-      </c>
-      <c r="X215" s="7" t="n"/>
-      <c r="Y215" s="7" t="n"/>
-      <c r="Z215" s="7" t="n"/>
-      <c r="AB215" s="7" t="n"/>
-      <c r="AC215" s="7" t="n"/>
-      <c r="AD215" s="7" t="n"/>
-    </row>
-    <row r="216">
-      <c r="T216" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U216" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V216" s="4" t="n">
-        <v>22473</v>
-      </c>
-      <c r="X216" s="4" t="n"/>
-      <c r="Y216" s="4" t="n"/>
-      <c r="Z216" s="4" t="n"/>
-      <c r="AB216" s="4" t="n"/>
-      <c r="AC216" s="4" t="n"/>
-      <c r="AD216" s="4" t="n"/>
-    </row>
-    <row r="217">
-      <c r="T217" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U217" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V217" s="7" t="n">
-        <v>22903</v>
-      </c>
-      <c r="X217" s="7" t="n"/>
-      <c r="Y217" s="7" t="n"/>
-      <c r="Z217" s="7" t="n"/>
-      <c r="AB217" s="7" t="n"/>
-      <c r="AC217" s="7" t="n"/>
-      <c r="AD217" s="7" t="n"/>
-    </row>
-    <row r="218">
-      <c r="T218" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U218" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V218" s="4" t="n">
-        <v>21829</v>
-      </c>
-      <c r="X218" s="4" t="n"/>
-      <c r="Y218" s="4" t="n"/>
-      <c r="Z218" s="4" t="n"/>
-      <c r="AB218" s="4" t="n"/>
-      <c r="AC218" s="4" t="n"/>
-      <c r="AD218" s="4" t="n"/>
-    </row>
-    <row r="219">
-      <c r="T219" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U219" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V219" s="7" t="n">
-        <v>20959</v>
-      </c>
-      <c r="X219" s="7" t="n"/>
-      <c r="Y219" s="7" t="n"/>
-      <c r="Z219" s="7" t="n"/>
-      <c r="AB219" s="7" t="n"/>
-      <c r="AC219" s="7" t="n"/>
-      <c r="AD219" s="7" t="n"/>
-    </row>
-    <row r="220">
-      <c r="T220" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U220" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V220" s="4" t="n">
-        <v>20856</v>
-      </c>
-      <c r="X220" s="4" t="n"/>
-      <c r="Y220" s="4" t="n"/>
-      <c r="Z220" s="4" t="n"/>
-      <c r="AB220" s="4" t="n"/>
-      <c r="AC220" s="4" t="n"/>
-      <c r="AD220" s="4" t="n"/>
-    </row>
-    <row r="221">
-      <c r="T221" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U221" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V221" s="7" t="n">
-        <v>23061</v>
-      </c>
-      <c r="X221" s="7" t="n"/>
-      <c r="Y221" s="7" t="n"/>
-      <c r="Z221" s="7" t="n"/>
-      <c r="AB221" s="7" t="n"/>
-      <c r="AC221" s="7" t="n"/>
-      <c r="AD221" s="7" t="n"/>
-    </row>
-    <row r="222">
-      <c r="T222" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U222" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V222" s="4" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X222" s="4" t="n"/>
-      <c r="Y222" s="4" t="n"/>
-      <c r="Z222" s="4" t="n"/>
-      <c r="AB222" s="4" t="n"/>
-      <c r="AC222" s="4" t="n"/>
-      <c r="AD222" s="4" t="n"/>
-    </row>
-    <row r="223">
-      <c r="T223" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U223" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V223" s="7" t="n">
-        <v>16721</v>
-      </c>
-      <c r="X223" s="7" t="n"/>
-      <c r="Y223" s="7" t="n"/>
-      <c r="Z223" s="7" t="n"/>
-      <c r="AB223" s="7" t="n"/>
-      <c r="AC223" s="7" t="n"/>
-      <c r="AD223" s="7" t="n"/>
-    </row>
-    <row r="224">
-      <c r="T224" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U224" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V224" s="4" t="n">
-        <v>16586</v>
-      </c>
-      <c r="X224" s="4" t="n"/>
-      <c r="Y224" s="4" t="n"/>
-      <c r="Z224" s="4" t="n"/>
-      <c r="AB224" s="4" t="n"/>
-      <c r="AC224" s="4" t="n"/>
-      <c r="AD224" s="4" t="n"/>
-    </row>
-    <row r="225">
-      <c r="T225" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U225" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V225" s="7" t="n">
-        <v>16419</v>
-      </c>
-      <c r="X225" s="7" t="n"/>
-      <c r="Y225" s="7" t="n"/>
-      <c r="Z225" s="7" t="n"/>
-      <c r="AB225" s="7" t="n"/>
-      <c r="AC225" s="7" t="n"/>
-      <c r="AD225" s="7" t="n"/>
-    </row>
-    <row r="226">
-      <c r="T226" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U226" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V226" s="4" t="n">
-        <v>15946</v>
-      </c>
-      <c r="X226" s="4" t="n"/>
-      <c r="Y226" s="4" t="n"/>
-      <c r="Z226" s="4" t="n"/>
-      <c r="AB226" s="4" t="n"/>
-      <c r="AC226" s="4" t="n"/>
-      <c r="AD226" s="4" t="n"/>
-    </row>
-    <row r="227">
-      <c r="T227" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U227" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V227" s="7" t="n">
-        <v>16042</v>
-      </c>
-      <c r="X227" s="7" t="n"/>
-      <c r="Y227" s="7" t="n"/>
-      <c r="Z227" s="7" t="n"/>
-      <c r="AB227" s="7" t="n"/>
-      <c r="AC227" s="7" t="n"/>
-      <c r="AD227" s="7" t="n"/>
-    </row>
-    <row r="228">
-      <c r="T228" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U228" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V228" s="4" t="n">
-        <v>16409</v>
-      </c>
-      <c r="X228" s="4" t="n"/>
-      <c r="Y228" s="4" t="n"/>
-      <c r="Z228" s="4" t="n"/>
-      <c r="AB228" s="4" t="n"/>
-      <c r="AC228" s="4" t="n"/>
-      <c r="AD228" s="4" t="n"/>
-    </row>
-    <row r="229">
-      <c r="T229" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U229" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V229" s="7" t="n">
-        <v>16831</v>
-      </c>
-      <c r="X229" s="7" t="n"/>
-      <c r="Y229" s="7" t="n"/>
-      <c r="Z229" s="7" t="n"/>
-      <c r="AB229" s="7" t="n"/>
-      <c r="AC229" s="7" t="n"/>
-      <c r="AD229" s="7" t="n"/>
-    </row>
-    <row r="230">
-      <c r="T230" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U230" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V230" s="4" t="n">
-        <v>16886</v>
-      </c>
-      <c r="X230" s="4" t="n"/>
-      <c r="Y230" s="4" t="n"/>
-      <c r="Z230" s="4" t="n"/>
-      <c r="AB230" s="4" t="n"/>
-      <c r="AC230" s="4" t="n"/>
-      <c r="AD230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="T231" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U231" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V231" s="7" t="n">
-        <v>16694</v>
-      </c>
-      <c r="X231" s="7" t="n"/>
-      <c r="Y231" s="7" t="n"/>
-      <c r="Z231" s="7" t="n"/>
-      <c r="AB231" s="7" t="n"/>
-      <c r="AC231" s="7" t="n"/>
-      <c r="AD231" s="7" t="n"/>
-    </row>
-    <row r="232">
-      <c r="T232" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U232" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V232" s="4" t="n">
-        <v>16659</v>
-      </c>
-      <c r="X232" s="4" t="n"/>
-      <c r="Y232" s="4" t="n"/>
-      <c r="Z232" s="4" t="n"/>
-      <c r="AB232" s="4" t="n"/>
-      <c r="AC232" s="4" t="n"/>
-      <c r="AD232" s="4" t="n"/>
-    </row>
-    <row r="233">
-      <c r="T233" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U233" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V233" s="7" t="n">
-        <v>16268</v>
-      </c>
-      <c r="X233" s="7" t="n"/>
-      <c r="Y233" s="7" t="n"/>
-      <c r="Z233" s="7" t="n"/>
-      <c r="AB233" s="7" t="n"/>
-      <c r="AC233" s="7" t="n"/>
-      <c r="AD233" s="7" t="n"/>
-    </row>
-    <row r="234">
-      <c r="T234" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U234" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V234" s="4" t="n">
-        <v>16259</v>
-      </c>
-      <c r="X234" s="4" t="n"/>
-      <c r="Y234" s="4" t="n"/>
-      <c r="Z234" s="4" t="n"/>
-      <c r="AB234" s="4" t="n"/>
-      <c r="AC234" s="4" t="n"/>
-      <c r="AD234" s="4" t="n"/>
-    </row>
-    <row r="235">
-      <c r="T235" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U235" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V235" s="7" t="n">
-        <v>16600</v>
-      </c>
-      <c r="X235" s="7" t="n"/>
-      <c r="Y235" s="7" t="n"/>
-      <c r="Z235" s="7" t="n"/>
-      <c r="AB235" s="7" t="n"/>
-      <c r="AC235" s="7" t="n"/>
-      <c r="AD235" s="7" t="n"/>
-    </row>
-    <row r="236">
-      <c r="T236" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U236" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V236" s="4" t="n">
-        <v>16913</v>
-      </c>
-      <c r="X236" s="4" t="n"/>
-      <c r="Y236" s="4" t="n"/>
-      <c r="Z236" s="4" t="n"/>
-      <c r="AB236" s="4" t="n"/>
-      <c r="AC236" s="4" t="n"/>
-      <c r="AD236" s="4" t="n"/>
-    </row>
-    <row r="237">
-      <c r="T237" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U237" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V237" s="7" t="n">
-        <v>16991</v>
-      </c>
-      <c r="X237" s="7" t="n"/>
-      <c r="Y237" s="7" t="n"/>
-      <c r="Z237" s="7" t="n"/>
-      <c r="AB237" s="7" t="n"/>
-      <c r="AC237" s="7" t="n"/>
-      <c r="AD237" s="7" t="n"/>
-    </row>
-    <row r="238">
-      <c r="T238" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U238" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V238" s="4" t="n">
-        <v>17365</v>
-      </c>
-      <c r="X238" s="4" t="n"/>
-      <c r="Y238" s="4" t="n"/>
-      <c r="Z238" s="4" t="n"/>
-      <c r="AB238" s="4" t="n"/>
-      <c r="AC238" s="4" t="n"/>
-      <c r="AD238" s="4" t="n"/>
-    </row>
-    <row r="239">
-      <c r="T239" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U239" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V239" s="7" t="n">
-        <v>16944</v>
-      </c>
-      <c r="X239" s="7" t="n"/>
-      <c r="Y239" s="7" t="n"/>
-      <c r="Z239" s="7" t="n"/>
-      <c r="AB239" s="7" t="n"/>
-      <c r="AC239" s="7" t="n"/>
-      <c r="AD239" s="7" t="n"/>
-    </row>
-    <row r="240">
-      <c r="T240" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U240" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V240" s="4" t="n">
-        <v>16518</v>
-      </c>
-      <c r="X240" s="4" t="n"/>
-      <c r="Y240" s="4" t="n"/>
-      <c r="Z240" s="4" t="n"/>
-      <c r="AB240" s="4" t="n"/>
-      <c r="AC240" s="4" t="n"/>
-      <c r="AD240" s="4" t="n"/>
-    </row>
-    <row r="241">
-      <c r="T241" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U241" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V241" s="7" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X241" s="7" t="n"/>
-      <c r="Y241" s="7" t="n"/>
-      <c r="Z241" s="7" t="n"/>
-      <c r="AB241" s="7" t="n"/>
-      <c r="AC241" s="7" t="n"/>
-      <c r="AD241" s="7" t="n"/>
-    </row>
-    <row r="242">
-      <c r="T242" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U242" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V242" s="4" t="n">
-        <v>16711</v>
-      </c>
-      <c r="X242" s="4" t="n"/>
-      <c r="Y242" s="4" t="n"/>
-      <c r="Z242" s="4" t="n"/>
-      <c r="AB242" s="4" t="n"/>
-      <c r="AC242" s="4" t="n"/>
-      <c r="AD242" s="4" t="n"/>
-    </row>
-    <row r="243">
-      <c r="T243" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U243" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V243" s="7" t="n">
-        <v>17379</v>
-      </c>
-      <c r="X243" s="7" t="n"/>
-      <c r="Y243" s="7" t="n"/>
-      <c r="Z243" s="7" t="n"/>
-      <c r="AB243" s="7" t="n"/>
-      <c r="AC243" s="7" t="n"/>
-      <c r="AD243" s="7" t="n"/>
-    </row>
-    <row r="244">
-      <c r="T244" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U244" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V244" s="4" t="n">
-        <v>724</v>
-      </c>
-      <c r="X244" s="4" t="n"/>
-      <c r="Y244" s="4" t="n"/>
-      <c r="Z244" s="4" t="n"/>
-      <c r="AB244" s="4" t="n"/>
-      <c r="AC244" s="4" t="n"/>
-      <c r="AD244" s="4" t="n"/>
-    </row>
-    <row r="245">
-      <c r="T245" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U245" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V245" s="7" t="n">
-        <v>746</v>
-      </c>
-      <c r="X245" s="7" t="n"/>
-      <c r="Y245" s="7" t="n"/>
-      <c r="Z245" s="7" t="n"/>
-      <c r="AB245" s="7" t="n"/>
-      <c r="AC245" s="7" t="n"/>
-      <c r="AD245" s="7" t="n"/>
-    </row>
-    <row r="246">
-      <c r="T246" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U246" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V246" s="4" t="n">
-        <v>723</v>
-      </c>
-      <c r="X246" s="4" t="n"/>
-      <c r="Y246" s="4" t="n"/>
-      <c r="Z246" s="4" t="n"/>
-      <c r="AB246" s="4" t="n"/>
-      <c r="AC246" s="4" t="n"/>
-      <c r="AD246" s="4" t="n"/>
-    </row>
-    <row r="247">
-      <c r="T247" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U247" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V247" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="X247" s="7" t="n"/>
-      <c r="Y247" s="7" t="n"/>
-      <c r="Z247" s="7" t="n"/>
-      <c r="AB247" s="7" t="n"/>
-      <c r="AC247" s="7" t="n"/>
-      <c r="AD247" s="7" t="n"/>
-    </row>
-    <row r="248">
-      <c r="T248" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U248" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V248" s="4" t="n">
-        <v>735</v>
-      </c>
-      <c r="X248" s="4" t="n"/>
-      <c r="Y248" s="4" t="n"/>
-      <c r="Z248" s="4" t="n"/>
-      <c r="AB248" s="4" t="n"/>
-      <c r="AC248" s="4" t="n"/>
-      <c r="AD248" s="4" t="n"/>
-    </row>
-    <row r="249">
-      <c r="T249" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U249" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V249" s="7" t="n">
-        <v>714</v>
-      </c>
-      <c r="X249" s="7" t="n"/>
-      <c r="Y249" s="7" t="n"/>
-      <c r="Z249" s="7" t="n"/>
-      <c r="AB249" s="7" t="n"/>
-      <c r="AC249" s="7" t="n"/>
-      <c r="AD249" s="7" t="n"/>
-    </row>
-    <row r="250">
-      <c r="T250" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U250" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V250" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X250" s="4" t="n"/>
-      <c r="Y250" s="4" t="n"/>
-      <c r="Z250" s="4" t="n"/>
-      <c r="AB250" s="4" t="n"/>
-      <c r="AC250" s="4" t="n"/>
-      <c r="AD250" s="4" t="n"/>
-    </row>
-    <row r="251">
-      <c r="T251" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U251" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V251" s="7" t="n">
-        <v>729</v>
-      </c>
-      <c r="X251" s="7" t="n"/>
-      <c r="Y251" s="7" t="n"/>
-      <c r="Z251" s="7" t="n"/>
-      <c r="AB251" s="7" t="n"/>
-      <c r="AC251" s="7" t="n"/>
-      <c r="AD251" s="7" t="n"/>
-    </row>
-    <row r="252">
-      <c r="T252" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U252" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V252" s="4" t="n">
-        <v>719</v>
-      </c>
-      <c r="X252" s="4" t="n"/>
-      <c r="Y252" s="4" t="n"/>
-      <c r="Z252" s="4" t="n"/>
-      <c r="AB252" s="4" t="n"/>
-      <c r="AC252" s="4" t="n"/>
-      <c r="AD252" s="4" t="n"/>
-    </row>
-    <row r="253">
-      <c r="T253" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U253" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V253" s="7" t="n">
-        <v>719</v>
-      </c>
-      <c r="X253" s="7" t="n"/>
-      <c r="Y253" s="7" t="n"/>
-      <c r="Z253" s="7" t="n"/>
-      <c r="AB253" s="7" t="n"/>
-      <c r="AC253" s="7" t="n"/>
-      <c r="AD253" s="7" t="n"/>
-    </row>
-    <row r="254">
-      <c r="T254" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U254" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V254" s="4" t="n">
-        <v>730</v>
-      </c>
-      <c r="X254" s="4" t="n"/>
-      <c r="Y254" s="4" t="n"/>
-      <c r="Z254" s="4" t="n"/>
-      <c r="AB254" s="4" t="n"/>
-      <c r="AC254" s="4" t="n"/>
-      <c r="AD254" s="4" t="n"/>
-    </row>
-    <row r="255">
-      <c r="T255" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U255" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V255" s="7" t="n">
-        <v>740</v>
-      </c>
-      <c r="X255" s="7" t="n"/>
-      <c r="Y255" s="7" t="n"/>
-      <c r="Z255" s="7" t="n"/>
-      <c r="AB255" s="7" t="n"/>
-      <c r="AC255" s="7" t="n"/>
-      <c r="AD255" s="7" t="n"/>
-    </row>
-    <row r="256">
-      <c r="T256" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U256" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V256" s="4" t="n">
-        <v>708</v>
-      </c>
-      <c r="X256" s="4" t="n"/>
-      <c r="Y256" s="4" t="n"/>
-      <c r="Z256" s="4" t="n"/>
-      <c r="AB256" s="4" t="n"/>
-      <c r="AC256" s="4" t="n"/>
-      <c r="AD256" s="4" t="n"/>
-    </row>
-    <row r="257">
-      <c r="T257" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U257" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V257" s="7" t="n">
-        <v>698</v>
-      </c>
-      <c r="X257" s="7" t="n"/>
-      <c r="Y257" s="7" t="n"/>
-      <c r="Z257" s="7" t="n"/>
-      <c r="AB257" s="7" t="n"/>
-      <c r="AC257" s="7" t="n"/>
-      <c r="AD257" s="7" t="n"/>
-    </row>
-    <row r="258">
-      <c r="T258" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U258" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V258" s="4" t="n">
-        <v>691</v>
-      </c>
-      <c r="X258" s="4" t="n"/>
-      <c r="Y258" s="4" t="n"/>
-      <c r="Z258" s="4" t="n"/>
-      <c r="AB258" s="4" t="n"/>
-      <c r="AC258" s="4" t="n"/>
-      <c r="AD258" s="4" t="n"/>
-    </row>
-    <row r="259">
-      <c r="T259" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U259" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V259" s="7" t="n">
-        <v>695</v>
-      </c>
-      <c r="X259" s="7" t="n"/>
-      <c r="Y259" s="7" t="n"/>
-      <c r="Z259" s="7" t="n"/>
-      <c r="AB259" s="7" t="n"/>
-      <c r="AC259" s="7" t="n"/>
-      <c r="AD259" s="7" t="n"/>
-    </row>
-    <row r="260">
-      <c r="T260" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U260" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V260" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X260" s="4" t="n"/>
-      <c r="Y260" s="4" t="n"/>
-      <c r="Z260" s="4" t="n"/>
-      <c r="AB260" s="4" t="n"/>
-      <c r="AC260" s="4" t="n"/>
-      <c r="AD260" s="4" t="n"/>
-    </row>
-    <row r="261">
-      <c r="T261" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U261" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V261" s="7" t="n">
-        <v>701</v>
-      </c>
-      <c r="X261" s="7" t="n"/>
-      <c r="Y261" s="7" t="n"/>
-      <c r="Z261" s="7" t="n"/>
-      <c r="AB261" s="7" t="n"/>
-      <c r="AC261" s="7" t="n"/>
-      <c r="AD261" s="7" t="n"/>
-    </row>
-    <row r="262">
-      <c r="T262" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U262" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V262" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X262" s="4" t="n"/>
-      <c r="Y262" s="4" t="n"/>
-      <c r="Z262" s="4" t="n"/>
-      <c r="AB262" s="4" t="n"/>
-      <c r="AC262" s="4" t="n"/>
-      <c r="AD262" s="4" t="n"/>
-    </row>
-    <row r="263">
-      <c r="T263" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U263" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V263" s="7" t="n">
-        <v>704</v>
-      </c>
-      <c r="X263" s="7" t="n"/>
-      <c r="Y263" s="7" t="n"/>
-      <c r="Z263" s="7" t="n"/>
-      <c r="AB263" s="7" t="n"/>
-      <c r="AC263" s="7" t="n"/>
-      <c r="AD263" s="7" t="n"/>
-    </row>
-    <row r="264">
-      <c r="T264" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U264" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V264" s="4" t="n">
-        <v>670</v>
-      </c>
-      <c r="X264" s="4" t="n"/>
-      <c r="Y264" s="4" t="n"/>
-      <c r="Z264" s="4" t="n"/>
-      <c r="AB264" s="4" t="n"/>
-      <c r="AC264" s="4" t="n"/>
-      <c r="AD264" s="4" t="n"/>
-    </row>
-    <row r="265">
-      <c r="T265" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U265" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V265" s="7" t="n">
-        <v>694</v>
-      </c>
-      <c r="X265" s="7" t="n"/>
-      <c r="Y265" s="7" t="n"/>
-      <c r="Z265" s="7" t="n"/>
-      <c r="AB265" s="7" t="n"/>
-      <c r="AC265" s="7" t="n"/>
-      <c r="AD265" s="7" t="n"/>
-    </row>
-    <row r="266">
-      <c r="T266" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U266" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V266" s="4" t="n">
-        <v>2188</v>
-      </c>
-      <c r="X266" s="4" t="n"/>
-      <c r="Y266" s="4" t="n"/>
-      <c r="Z266" s="4" t="n"/>
-      <c r="AB266" s="4" t="n"/>
-      <c r="AC266" s="4" t="n"/>
-      <c r="AD266" s="4" t="n"/>
-    </row>
-    <row r="267">
-      <c r="T267" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U267" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V267" s="7" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X267" s="7" t="n"/>
-      <c r="Y267" s="7" t="n"/>
-      <c r="Z267" s="7" t="n"/>
-      <c r="AB267" s="7" t="n"/>
-      <c r="AC267" s="7" t="n"/>
-      <c r="AD267" s="7" t="n"/>
-    </row>
-    <row r="268">
-      <c r="T268" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U268" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V268" s="4" t="n">
-        <v>2338</v>
-      </c>
-      <c r="X268" s="4" t="n"/>
-      <c r="Y268" s="4" t="n"/>
-      <c r="Z268" s="4" t="n"/>
-      <c r="AB268" s="4" t="n"/>
-      <c r="AC268" s="4" t="n"/>
-      <c r="AD268" s="4" t="n"/>
-    </row>
-    <row r="269">
-      <c r="T269" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U269" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V269" s="7" t="n">
-        <v>2152</v>
-      </c>
-      <c r="X269" s="7" t="n"/>
-      <c r="Y269" s="7" t="n"/>
-      <c r="Z269" s="7" t="n"/>
-      <c r="AB269" s="7" t="n"/>
-      <c r="AC269" s="7" t="n"/>
-      <c r="AD269" s="7" t="n"/>
-    </row>
-    <row r="270">
-      <c r="T270" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U270" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V270" s="4" t="n">
-        <v>2003</v>
-      </c>
-      <c r="X270" s="4" t="n"/>
-      <c r="Y270" s="4" t="n"/>
-      <c r="Z270" s="4" t="n"/>
-      <c r="AB270" s="4" t="n"/>
-      <c r="AC270" s="4" t="n"/>
-      <c r="AD270" s="4" t="n"/>
-    </row>
-    <row r="271">
-      <c r="T271" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U271" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V271" s="7" t="n">
-        <v>1895</v>
-      </c>
-      <c r="X271" s="7" t="n"/>
-      <c r="Y271" s="7" t="n"/>
-      <c r="Z271" s="7" t="n"/>
-      <c r="AB271" s="7" t="n"/>
-      <c r="AC271" s="7" t="n"/>
-      <c r="AD271" s="7" t="n"/>
-    </row>
-    <row r="272">
-      <c r="T272" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U272" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V272" s="4" t="n">
-        <v>1935</v>
-      </c>
-      <c r="X272" s="4" t="n"/>
-      <c r="Y272" s="4" t="n"/>
-      <c r="Z272" s="4" t="n"/>
-      <c r="AB272" s="4" t="n"/>
-      <c r="AC272" s="4" t="n"/>
-      <c r="AD272" s="4" t="n"/>
-    </row>
-    <row r="273">
-      <c r="T273" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U273" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V273" s="7" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X273" s="7" t="n"/>
-      <c r="Y273" s="7" t="n"/>
-      <c r="Z273" s="7" t="n"/>
-      <c r="AB273" s="7" t="n"/>
-      <c r="AC273" s="7" t="n"/>
-      <c r="AD273" s="7" t="n"/>
-    </row>
-    <row r="274">
-      <c r="T274" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U274" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V274" s="4" t="n">
-        <v>2049</v>
-      </c>
-      <c r="X274" s="4" t="n"/>
-      <c r="Y274" s="4" t="n"/>
-      <c r="Z274" s="4" t="n"/>
-      <c r="AB274" s="4" t="n"/>
-      <c r="AC274" s="4" t="n"/>
-      <c r="AD274" s="4" t="n"/>
-    </row>
-    <row r="275">
-      <c r="T275" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U275" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V275" s="7" t="n">
-        <v>2325</v>
-      </c>
-      <c r="X275" s="7" t="n"/>
-      <c r="Y275" s="7" t="n"/>
-      <c r="Z275" s="7" t="n"/>
-      <c r="AB275" s="7" t="n"/>
-      <c r="AC275" s="7" t="n"/>
-      <c r="AD275" s="7" t="n"/>
-    </row>
-    <row r="276">
-      <c r="T276" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U276" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V276" s="4" t="n">
-        <v>2216</v>
-      </c>
-      <c r="X276" s="4" t="n"/>
-      <c r="Y276" s="4" t="n"/>
-      <c r="Z276" s="4" t="n"/>
-      <c r="AB276" s="4" t="n"/>
-      <c r="AC276" s="4" t="n"/>
-      <c r="AD276" s="4" t="n"/>
-    </row>
-    <row r="277">
-      <c r="T277" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U277" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V277" s="7" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X277" s="7" t="n"/>
-      <c r="Y277" s="7" t="n"/>
-      <c r="Z277" s="7" t="n"/>
-      <c r="AB277" s="7" t="n"/>
-      <c r="AC277" s="7" t="n"/>
-      <c r="AD277" s="7" t="n"/>
-    </row>
-    <row r="278">
-      <c r="T278" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U278" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V278" s="4" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X278" s="4" t="n"/>
-      <c r="Y278" s="4" t="n"/>
-      <c r="Z278" s="4" t="n"/>
-      <c r="AB278" s="4" t="n"/>
-      <c r="AC278" s="4" t="n"/>
-      <c r="AD278" s="4" t="n"/>
-    </row>
-    <row r="279">
-      <c r="T279" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U279" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V279" s="7" t="n">
-        <v>2035</v>
-      </c>
-      <c r="X279" s="7" t="n"/>
-      <c r="Y279" s="7" t="n"/>
-      <c r="Z279" s="7" t="n"/>
-      <c r="AB279" s="7" t="n"/>
-      <c r="AC279" s="7" t="n"/>
-      <c r="AD279" s="7" t="n"/>
-    </row>
-    <row r="280">
-      <c r="T280" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U280" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V280" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="X280" s="4" t="n"/>
-      <c r="Y280" s="4" t="n"/>
-      <c r="Z280" s="4" t="n"/>
-      <c r="AB280" s="4" t="n"/>
-      <c r="AC280" s="4" t="n"/>
-      <c r="AD280" s="4" t="n"/>
-    </row>
-    <row r="281">
-      <c r="T281" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U281" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V281" s="7" t="n">
-        <v>2156</v>
-      </c>
-      <c r="X281" s="7" t="n"/>
-      <c r="Y281" s="7" t="n"/>
-      <c r="Z281" s="7" t="n"/>
-      <c r="AB281" s="7" t="n"/>
-      <c r="AC281" s="7" t="n"/>
-      <c r="AD281" s="7" t="n"/>
-    </row>
-    <row r="282">
-      <c r="T282" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U282" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V282" s="4" t="n">
-        <v>2437</v>
-      </c>
-      <c r="X282" s="4" t="n"/>
-      <c r="Y282" s="4" t="n"/>
-      <c r="Z282" s="4" t="n"/>
-      <c r="AB282" s="4" t="n"/>
-      <c r="AC282" s="4" t="n"/>
-      <c r="AD282" s="4" t="n"/>
-    </row>
-    <row r="283">
-      <c r="T283" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U283" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V283" s="7" t="n">
-        <v>2214</v>
-      </c>
-      <c r="X283" s="7" t="n"/>
-      <c r="Y283" s="7" t="n"/>
-      <c r="Z283" s="7" t="n"/>
-      <c r="AB283" s="7" t="n"/>
-      <c r="AC283" s="7" t="n"/>
-      <c r="AD283" s="7" t="n"/>
-    </row>
-    <row r="284">
-      <c r="T284" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U284" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V284" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="X284" s="4" t="n"/>
-      <c r="Y284" s="4" t="n"/>
-      <c r="Z284" s="4" t="n"/>
-      <c r="AB284" s="4" t="n"/>
-      <c r="AC284" s="4" t="n"/>
-      <c r="AD284" s="4" t="n"/>
-    </row>
-    <row r="285">
-      <c r="T285" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U285" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V285" s="7" t="n">
-        <v>1973</v>
-      </c>
-      <c r="X285" s="7" t="n"/>
-      <c r="Y285" s="7" t="n"/>
-      <c r="Z285" s="7" t="n"/>
-      <c r="AB285" s="7" t="n"/>
-      <c r="AC285" s="7" t="n"/>
-      <c r="AD285" s="7" t="n"/>
-    </row>
-    <row r="286">
-      <c r="T286" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U286" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V286" s="4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="X286" s="4" t="n"/>
-      <c r="Y286" s="4" t="n"/>
-      <c r="Z286" s="4" t="n"/>
-      <c r="AB286" s="4" t="n"/>
-      <c r="AC286" s="4" t="n"/>
-      <c r="AD286" s="4" t="n"/>
-    </row>
-    <row r="287">
-      <c r="T287" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U287" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V287" s="7" t="n">
-        <v>2075</v>
-      </c>
-      <c r="X287" s="7" t="n"/>
-      <c r="Y287" s="7" t="n"/>
-      <c r="Z287" s="7" t="n"/>
-      <c r="AB287" s="7" t="n"/>
-      <c r="AC287" s="7" t="n"/>
-      <c r="AD287" s="7" t="n"/>
+      <c r="AB179" s="7" t="n"/>
+      <c r="AC179" s="7" t="n"/>
+      <c r="AD179" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD287"/>
+  <dimension ref="A1:AD298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3085,29 +3085,49 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
+      <c r="D24" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C24)</f>
+        <v/>
+      </c>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
+      <c r="G24" s="4">
+        <f>ROUND((1-E24/D24)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H24" s="4">
+        <f>MIN(1,(G24-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="K24" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="4">
+        <f>ROUND(100*(1-K24/D24),2)</f>
+        <v/>
+      </c>
+      <c r="M24" s="4">
+        <f>MAX(0,(L24-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N24" s="4">
+        <f>$B$2+H24+M24</f>
+        <v/>
+      </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr"/>
       <c r="V24" s="4" t="n">
-        <v>5365</v>
+        <v>1</v>
       </c>
       <c r="X24" s="4" t="n">
         <v>11</v>
@@ -3157,7 +3177,7 @@
       <c r="N25" s="7" t="n"/>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -3166,7 +3186,7 @@
         </is>
       </c>
       <c r="V25" s="7" t="n">
-        <v>5741</v>
+        <v>5365</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>101</v>
@@ -3216,7 +3236,7 @@
       <c r="N26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
@@ -3225,7 +3245,7 @@
         </is>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5451</v>
+        <v>5741</v>
       </c>
       <c r="X26" s="4" t="n">
         <v>11</v>
@@ -3275,7 +3295,7 @@
       <c r="N27" s="7" t="n"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -3284,7 +3304,7 @@
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>5458</v>
+        <v>5451</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>73</v>
@@ -3334,7 +3354,7 @@
       <c r="N28" s="4" t="n"/>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
@@ -3343,7 +3363,7 @@
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5664</v>
+        <v>5458</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>31</v>
@@ -3393,7 +3413,7 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -3402,7 +3422,7 @@
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>5241</v>
+        <v>5664</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>13</v>
@@ -3452,7 +3472,7 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3461,7 +3481,7 @@
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5102</v>
+        <v>5241</v>
       </c>
       <c r="X30" s="4" t="n">
         <v>78</v>
@@ -3511,7 +3531,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -3520,7 +3540,7 @@
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>5388</v>
+        <v>5102</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>1</v>
@@ -3579,7 +3599,7 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3588,7 +3608,7 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5339</v>
+        <v>5388</v>
       </c>
       <c r="X32" s="4" t="n">
         <v>9</v>
@@ -3619,7 +3639,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D23)</f>
+        <f>AVERAGE(D2:D24)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3629,7 +3649,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H23)</f>
+        <f>AVERAGE(H2:H24)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3652,7 +3672,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -3661,7 +3681,7 @@
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>5348</v>
+        <v>5339</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>1</v>
@@ -3693,7 +3713,7 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3702,7 +3722,7 @@
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5329</v>
+        <v>5348</v>
       </c>
       <c r="X34" s="4" t="n">
         <v>119</v>
@@ -3734,7 +3754,7 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -3743,7 +3763,7 @@
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>5436</v>
+        <v>5329</v>
       </c>
       <c r="X35" s="7" t="n">
         <v>13</v>
@@ -3775,7 +3795,7 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
@@ -3784,7 +3804,7 @@
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>5081</v>
+        <v>5436</v>
       </c>
       <c r="X36" s="4" t="n">
         <v>67</v>
@@ -3816,7 +3836,7 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
@@ -3825,7 +3845,7 @@
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>5034</v>
+        <v>5081</v>
       </c>
       <c r="X37" s="7" t="n">
         <v>32</v>
@@ -3857,7 +3877,7 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
@@ -3866,7 +3886,7 @@
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>5557</v>
+        <v>5034</v>
       </c>
       <c r="X38" s="4" t="n">
         <v>13</v>
@@ -3898,7 +3918,7 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
@@ -3907,7 +3927,7 @@
         </is>
       </c>
       <c r="V39" s="7" t="n">
-        <v>5513</v>
+        <v>5557</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>93</v>
@@ -3939,7 +3959,7 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
@@ -3948,7 +3968,7 @@
         </is>
       </c>
       <c r="V40" s="4" t="n">
-        <v>5477</v>
+        <v>5513</v>
       </c>
       <c r="X40" s="4" t="n">
         <v>12</v>
@@ -3980,7 +4000,7 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
@@ -3989,7 +4009,7 @@
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>5526</v>
+        <v>5477</v>
       </c>
       <c r="X41" s="7" t="n">
         <v>2</v>
@@ -4021,7 +4041,7 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
@@ -4030,7 +4050,7 @@
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>5339</v>
+        <v>5526</v>
       </c>
       <c r="X42" s="4" t="n">
         <v>113</v>
@@ -4062,7 +4082,7 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
@@ -4071,7 +4091,7 @@
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>4933</v>
+        <v>5339</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>12</v>
@@ -4103,7 +4123,7 @@
     <row r="44">
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U44" s="4" t="inlineStr">
@@ -4112,7 +4132,7 @@
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>4866</v>
+        <v>4933</v>
       </c>
       <c r="X44" s="4" t="n">
         <v>69</v>
@@ -4144,7 +4164,7 @@
     <row r="45">
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
@@ -4153,7 +4173,7 @@
         </is>
       </c>
       <c r="V45" s="7" t="n">
-        <v>5232</v>
+        <v>4866</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>40</v>
@@ -4185,16 +4205,16 @@
     <row r="46">
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V46" s="4" t="n">
-        <v>14969</v>
+        <v>5232</v>
       </c>
       <c r="X46" s="4" t="n">
         <v>17</v>
@@ -4226,16 +4246,16 @@
     <row r="47">
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>14818</v>
+        <v>5576</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>83</v>
@@ -4267,7 +4287,7 @@
     <row r="48">
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
@@ -4276,7 +4296,7 @@
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>15263</v>
+        <v>14969</v>
       </c>
       <c r="X48" s="4" t="n">
         <v>9</v>
@@ -4308,7 +4328,7 @@
     <row r="49">
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
@@ -4317,7 +4337,7 @@
         </is>
       </c>
       <c r="V49" s="7" t="n">
-        <v>14815</v>
+        <v>14818</v>
       </c>
       <c r="X49" s="7" t="n">
         <v>124</v>
@@ -4349,7 +4369,7 @@
     <row r="50">
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U50" s="4" t="inlineStr">
@@ -4358,7 +4378,7 @@
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>14968</v>
+        <v>15263</v>
       </c>
       <c r="X50" s="4" t="n">
         <v>19</v>
@@ -4390,7 +4410,7 @@
     <row r="51">
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
@@ -4399,7 +4419,7 @@
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>14113</v>
+        <v>14815</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>55</v>
@@ -4431,7 +4451,7 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
@@ -4440,7 +4460,7 @@
         </is>
       </c>
       <c r="V52" s="4" t="n">
-        <v>14162</v>
+        <v>14968</v>
       </c>
       <c r="X52" s="4" t="n">
         <v>35</v>
@@ -4472,7 +4492,7 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
@@ -4481,7 +4501,7 @@
         </is>
       </c>
       <c r="V53" s="7" t="n">
-        <v>14815</v>
+        <v>14113</v>
       </c>
       <c r="X53" s="7" t="n">
         <v>15</v>
@@ -4513,7 +4533,7 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
@@ -4522,7 +4542,7 @@
         </is>
       </c>
       <c r="V54" s="4" t="n">
-        <v>14815</v>
+        <v>14162</v>
       </c>
       <c r="X54" s="4" t="n">
         <v>82</v>
@@ -4554,7 +4574,7 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
@@ -4563,7 +4583,7 @@
         </is>
       </c>
       <c r="V55" s="7" t="n">
-        <v>15546</v>
+        <v>14815</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>1</v>
@@ -4595,7 +4615,7 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
@@ -4604,7 +4624,7 @@
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>14882</v>
+        <v>14815</v>
       </c>
       <c r="X56" s="4" t="n">
         <v>14</v>
@@ -4636,7 +4656,7 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
@@ -4645,7 +4665,7 @@
         </is>
       </c>
       <c r="V57" s="7" t="n">
-        <v>14998</v>
+        <v>15546</v>
       </c>
       <c r="X57" s="7" t="n">
         <v>2</v>
@@ -4677,7 +4697,7 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U58" s="4" t="inlineStr">
@@ -4686,7 +4706,7 @@
         </is>
       </c>
       <c r="V58" s="4" t="n">
-        <v>14354</v>
+        <v>14882</v>
       </c>
       <c r="X58" s="4" t="n">
         <v>101</v>
@@ -4718,7 +4738,7 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
@@ -4727,7 +4747,7 @@
         </is>
       </c>
       <c r="V59" s="7" t="n">
-        <v>14362</v>
+        <v>14998</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>10</v>
@@ -4759,7 +4779,7 @@
     <row r="60">
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U60" s="4" t="inlineStr">
@@ -4768,7 +4788,7 @@
         </is>
       </c>
       <c r="V60" s="4" t="n">
-        <v>15089</v>
+        <v>14354</v>
       </c>
       <c r="X60" s="4" t="n">
         <v>72</v>
@@ -4800,7 +4820,7 @@
     <row r="61">
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
@@ -4809,7 +4829,7 @@
         </is>
       </c>
       <c r="V61" s="7" t="n">
-        <v>14802</v>
+        <v>14362</v>
       </c>
       <c r="X61" s="7" t="n">
         <v>35</v>
@@ -4841,7 +4861,7 @@
     <row r="62">
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U62" s="4" t="inlineStr">
@@ -4850,7 +4870,7 @@
         </is>
       </c>
       <c r="V62" s="4" t="n">
-        <v>15349</v>
+        <v>15089</v>
       </c>
       <c r="X62" s="4" t="n">
         <v>13</v>
@@ -4882,7 +4902,7 @@
     <row r="63">
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
@@ -4891,7 +4911,7 @@
         </is>
       </c>
       <c r="V63" s="7" t="n">
-        <v>14872</v>
+        <v>14802</v>
       </c>
       <c r="X63" s="7" t="n">
         <v>71</v>
@@ -4923,7 +4943,7 @@
     <row r="64">
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr">
@@ -4932,7 +4952,7 @@
         </is>
       </c>
       <c r="V64" s="4" t="n">
-        <v>15054</v>
+        <v>15349</v>
       </c>
       <c r="X64" s="4" t="n">
         <v>8</v>
@@ -4964,7 +4984,7 @@
     <row r="65">
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
@@ -4973,7 +4993,7 @@
         </is>
       </c>
       <c r="V65" s="7" t="n">
-        <v>14169</v>
+        <v>14872</v>
       </c>
       <c r="X65" s="7" t="n">
         <v>2</v>
@@ -5005,7 +5025,7 @@
     <row r="66">
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr">
@@ -5014,7 +5034,7 @@
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>14056</v>
+        <v>15054</v>
       </c>
       <c r="X66" s="4" t="n">
         <v>125</v>
@@ -5046,7 +5066,7 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
@@ -5055,7 +5075,7 @@
         </is>
       </c>
       <c r="V67" s="7" t="n">
-        <v>15058</v>
+        <v>14169</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>11</v>
@@ -5087,16 +5107,16 @@
     <row r="68">
       <c r="T68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U68" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V68" s="4" t="n">
-        <v>77546</v>
+        <v>14056</v>
       </c>
       <c r="X68" s="4" t="n">
         <v>67</v>
@@ -5128,16 +5148,16 @@
     <row r="69">
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>77823</v>
+        <v>15058</v>
       </c>
       <c r="X69" s="7" t="n">
         <v>27</v>
@@ -5169,16 +5189,16 @@
     <row r="70">
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U70" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V70" s="4" t="n">
-        <v>81723</v>
+        <v>14814</v>
       </c>
       <c r="X70" s="4" t="n">
         <v>17</v>
@@ -5210,7 +5230,7 @@
     <row r="71">
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U71" s="7" t="inlineStr">
@@ -5219,7 +5239,7 @@
         </is>
       </c>
       <c r="V71" s="7" t="n">
-        <v>78398</v>
+        <v>77546</v>
       </c>
       <c r="X71" s="7" t="n">
         <v>85</v>
@@ -5251,7 +5271,7 @@
     <row r="72">
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U72" s="4" t="inlineStr">
@@ -5260,7 +5280,7 @@
         </is>
       </c>
       <c r="V72" s="4" t="n">
-        <v>78030</v>
+        <v>77823</v>
       </c>
       <c r="X72" s="4" t="n">
         <v>14</v>
@@ -5292,7 +5312,7 @@
     <row r="73">
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U73" s="7" t="inlineStr">
@@ -5301,7 +5321,7 @@
         </is>
       </c>
       <c r="V73" s="7" t="n">
-        <v>76646</v>
+        <v>81723</v>
       </c>
       <c r="X73" s="7" t="n">
         <v>4</v>
@@ -5333,7 +5353,7 @@
     <row r="74">
       <c r="T74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U74" s="4" t="inlineStr">
@@ -5342,7 +5362,7 @@
         </is>
       </c>
       <c r="V74" s="4" t="n">
-        <v>76742</v>
+        <v>78398</v>
       </c>
       <c r="X74" s="4" t="n">
         <v>126</v>
@@ -5374,7 +5394,7 @@
     <row r="75">
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U75" s="7" t="inlineStr">
@@ -5383,7 +5403,7 @@
         </is>
       </c>
       <c r="V75" s="7" t="n">
-        <v>79003</v>
+        <v>78030</v>
       </c>
       <c r="X75" s="7" t="n">
         <v>23</v>
@@ -5415,7 +5435,7 @@
     <row r="76">
       <c r="T76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U76" s="4" t="inlineStr">
@@ -5424,7 +5444,7 @@
         </is>
       </c>
       <c r="V76" s="4" t="n">
-        <v>78849</v>
+        <v>76646</v>
       </c>
       <c r="X76" s="4" t="n">
         <v>65</v>
@@ -5456,7 +5476,7 @@
     <row r="77">
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U77" s="7" t="inlineStr">
@@ -5465,7 +5485,7 @@
         </is>
       </c>
       <c r="V77" s="7" t="n">
-        <v>80667</v>
+        <v>76742</v>
       </c>
       <c r="X77" s="7" t="n">
         <v>28</v>
@@ -5497,7 +5517,7 @@
     <row r="78">
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U78" s="4" t="inlineStr">
@@ -5506,7 +5526,7 @@
         </is>
       </c>
       <c r="V78" s="4" t="n">
-        <v>78640</v>
+        <v>79003</v>
       </c>
       <c r="X78" s="4" t="n">
         <v>19</v>
@@ -5538,7 +5558,7 @@
     <row r="79">
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U79" s="7" t="inlineStr">
@@ -5547,7 +5567,7 @@
         </is>
       </c>
       <c r="V79" s="7" t="n">
-        <v>79108</v>
+        <v>78849</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>91</v>
@@ -5579,7 +5599,7 @@
     <row r="80">
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U80" s="4" t="inlineStr">
@@ -5588,7 +5608,7 @@
         </is>
       </c>
       <c r="V80" s="4" t="n">
-        <v>76911</v>
+        <v>80667</v>
       </c>
       <c r="X80" s="4" t="n">
         <v>21</v>
@@ -5620,7 +5640,7 @@
     <row r="81">
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U81" s="7" t="inlineStr">
@@ -5629,7 +5649,7 @@
         </is>
       </c>
       <c r="V81" s="7" t="n">
-        <v>77273</v>
+        <v>78640</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>2</v>
@@ -5661,7 +5681,7 @@
     <row r="82">
       <c r="T82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U82" s="4" t="inlineStr">
@@ -5670,7 +5690,7 @@
         </is>
       </c>
       <c r="V82" s="4" t="n">
-        <v>80657</v>
+        <v>79108</v>
       </c>
       <c r="X82" s="4" t="n">
         <v>99</v>
@@ -5702,7 +5722,7 @@
     <row r="83">
       <c r="T83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U83" s="7" t="inlineStr">
@@ -5711,7 +5731,7 @@
         </is>
       </c>
       <c r="V83" s="7" t="n">
-        <v>79898</v>
+        <v>76911</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>12</v>
@@ -5743,7 +5763,7 @@
     <row r="84">
       <c r="T84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U84" s="4" t="inlineStr">
@@ -5752,7 +5772,7 @@
         </is>
       </c>
       <c r="V84" s="4" t="n">
-        <v>82443</v>
+        <v>77273</v>
       </c>
       <c r="X84" s="4" t="n">
         <v>70</v>
@@ -5784,7 +5804,7 @@
     <row r="85">
       <c r="T85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U85" s="7" t="inlineStr">
@@ -5793,7 +5813,7 @@
         </is>
       </c>
       <c r="V85" s="7" t="n">
-        <v>80658</v>
+        <v>80657</v>
       </c>
       <c r="X85" s="7" t="n">
         <v>30</v>
@@ -5825,7 +5845,7 @@
     <row r="86">
       <c r="T86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U86" s="4" t="inlineStr">
@@ -5834,7 +5854,7 @@
         </is>
       </c>
       <c r="V86" s="4" t="n">
-        <v>78475</v>
+        <v>79898</v>
       </c>
       <c r="X86" s="4" t="n">
         <v>15</v>
@@ -5866,7 +5886,7 @@
     <row r="87">
       <c r="T87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U87" s="7" t="inlineStr">
@@ -5875,7 +5895,7 @@
         </is>
       </c>
       <c r="V87" s="7" t="n">
-        <v>76874</v>
+        <v>82443</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>73</v>
@@ -5907,7 +5927,7 @@
     <row r="88">
       <c r="T88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U88" s="4" t="inlineStr">
@@ -5916,7 +5936,7 @@
         </is>
       </c>
       <c r="V88" s="4" t="n">
-        <v>77058</v>
+        <v>80658</v>
       </c>
       <c r="X88" s="4" t="n">
         <v>5</v>
@@ -5948,7 +5968,7 @@
     <row r="89">
       <c r="T89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U89" s="7" t="inlineStr">
@@ -5957,7 +5977,7 @@
         </is>
       </c>
       <c r="V89" s="7" t="n">
-        <v>79206</v>
+        <v>78475</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>1</v>
@@ -5989,16 +6009,16 @@
     <row r="90">
       <c r="T90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U90" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V90" s="4" t="n">
-        <v>721</v>
+        <v>76874</v>
       </c>
       <c r="X90" s="4" t="n">
         <v>107</v>
@@ -6030,16 +6050,16 @@
     <row r="91">
       <c r="T91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U91" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V91" s="7" t="n">
-        <v>715</v>
+        <v>77058</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>13</v>
@@ -6071,16 +6091,16 @@
     <row r="92">
       <c r="T92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U92" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V92" s="4" t="n">
-        <v>745</v>
+        <v>79206</v>
       </c>
       <c r="X92" s="4" t="n">
         <v>56</v>
@@ -6112,16 +6132,16 @@
     <row r="93">
       <c r="T93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U93" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V93" s="7" t="n">
-        <v>702</v>
+        <v>79070</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>32</v>
@@ -6153,7 +6173,7 @@
     <row r="94">
       <c r="T94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U94" s="4" t="inlineStr">
@@ -6162,7 +6182,7 @@
         </is>
       </c>
       <c r="V94" s="4" t="n">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="X94" s="4" t="n">
         <v>13</v>
@@ -6194,7 +6214,7 @@
     <row r="95">
       <c r="T95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U95" s="7" t="inlineStr">
@@ -6203,7 +6223,7 @@
         </is>
       </c>
       <c r="V95" s="7" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>78</v>
@@ -6235,7 +6255,7 @@
     <row r="96">
       <c r="T96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U96" s="4" t="inlineStr">
@@ -6244,7 +6264,7 @@
         </is>
       </c>
       <c r="V96" s="4" t="n">
-        <v>696</v>
+        <v>745</v>
       </c>
       <c r="X96" s="4" t="n">
         <v>10</v>
@@ -6276,7 +6296,7 @@
     <row r="97">
       <c r="T97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U97" s="7" t="inlineStr">
@@ -6285,7 +6305,7 @@
         </is>
       </c>
       <c r="V97" s="7" t="n">
-        <v>750</v>
+        <v>702</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>1</v>
@@ -6317,7 +6337,7 @@
     <row r="98">
       <c r="T98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U98" s="4" t="inlineStr">
@@ -6326,7 +6346,7 @@
         </is>
       </c>
       <c r="V98" s="4" t="n">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="X98" s="4" t="n">
         <v>114</v>
@@ -6358,7 +6378,7 @@
     <row r="99">
       <c r="T99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U99" s="7" t="inlineStr">
@@ -6367,7 +6387,7 @@
         </is>
       </c>
       <c r="V99" s="7" t="n">
-        <v>748</v>
+        <v>700</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>15</v>
@@ -6399,7 +6419,7 @@
     <row r="100">
       <c r="T100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U100" s="4" t="inlineStr">
@@ -6408,7 +6428,7 @@
         </is>
       </c>
       <c r="V100" s="4" t="n">
-        <v>736</v>
+        <v>696</v>
       </c>
       <c r="X100" s="4" t="n">
         <v>53</v>
@@ -6440,7 +6460,7 @@
     <row r="101">
       <c r="T101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U101" s="7" t="inlineStr">
@@ -6449,7 +6469,7 @@
         </is>
       </c>
       <c r="V101" s="7" t="n">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>32</v>
@@ -6481,7 +6501,7 @@
     <row r="102">
       <c r="T102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U102" s="4" t="inlineStr">
@@ -6490,7 +6510,7 @@
         </is>
       </c>
       <c r="V102" s="4" t="n">
-        <v>707</v>
+        <v>729</v>
       </c>
       <c r="X102" s="4" t="n">
         <v>14</v>
@@ -6522,7 +6542,7 @@
     <row r="103">
       <c r="T103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U103" s="7" t="inlineStr">
@@ -6531,7 +6551,7 @@
         </is>
       </c>
       <c r="V103" s="7" t="n">
-        <v>713</v>
+        <v>748</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>80</v>
@@ -6563,7 +6583,7 @@
     <row r="104">
       <c r="T104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U104" s="4" t="inlineStr">
@@ -6572,7 +6592,7 @@
         </is>
       </c>
       <c r="V104" s="4" t="n">
-        <v>786</v>
+        <v>736</v>
       </c>
       <c r="X104" s="4" t="n">
         <v>1</v>
@@ -6604,7 +6624,7 @@
     <row r="105">
       <c r="T105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U105" s="7" t="inlineStr">
@@ -6613,7 +6633,7 @@
         </is>
       </c>
       <c r="V105" s="7" t="n">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>9</v>
@@ -6645,7 +6665,7 @@
     <row r="106">
       <c r="T106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U106" s="4" t="inlineStr">
@@ -6654,7 +6674,7 @@
         </is>
       </c>
       <c r="V106" s="4" t="n">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="X106" s="4" t="n">
         <v>4</v>
@@ -6686,7 +6706,7 @@
     <row r="107">
       <c r="T107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U107" s="7" t="inlineStr">
@@ -6695,7 +6715,7 @@
         </is>
       </c>
       <c r="V107" s="7" t="n">
-        <v>695</v>
+        <v>713</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>97</v>
@@ -6727,7 +6747,7 @@
     <row r="108">
       <c r="T108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U108" s="4" t="inlineStr">
@@ -6736,7 +6756,7 @@
         </is>
       </c>
       <c r="V108" s="4" t="n">
-        <v>693</v>
+        <v>786</v>
       </c>
       <c r="X108" s="4" t="n">
         <v>10</v>
@@ -6768,7 +6788,7 @@
     <row r="109">
       <c r="T109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U109" s="7" t="inlineStr">
@@ -6777,7 +6797,7 @@
         </is>
       </c>
       <c r="V109" s="7" t="n">
-        <v>686</v>
+        <v>730</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>52</v>
@@ -6809,7 +6829,7 @@
     <row r="110">
       <c r="T110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U110" s="4" t="inlineStr">
@@ -6818,7 +6838,7 @@
         </is>
       </c>
       <c r="V110" s="4" t="n">
-        <v>673</v>
+        <v>726</v>
       </c>
       <c r="X110" s="4" t="n">
         <v>37</v>
@@ -6850,7 +6870,7 @@
     <row r="111">
       <c r="T111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U111" s="7" t="inlineStr">
@@ -6859,7 +6879,7 @@
         </is>
       </c>
       <c r="V111" s="7" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>18</v>
@@ -6891,16 +6911,16 @@
     <row r="112">
       <c r="T112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U112" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V112" s="4" t="n">
-        <v>47976</v>
+        <v>693</v>
       </c>
       <c r="X112" s="4" t="n">
         <v>64</v>
@@ -6932,16 +6952,16 @@
     <row r="113">
       <c r="T113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U113" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V113" s="7" t="n">
-        <v>47122</v>
+        <v>686</v>
       </c>
       <c r="X113" s="7" t="n">
         <v>7</v>
@@ -6973,16 +6993,16 @@
     <row r="114">
       <c r="T114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U114" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V114" s="4" t="n">
-        <v>47233</v>
+        <v>673</v>
       </c>
       <c r="X114" s="4" t="n">
         <v>106</v>
@@ -7014,16 +7034,16 @@
     <row r="115">
       <c r="T115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U115" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V115" s="7" t="n">
-        <v>48580</v>
+        <v>752</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>14</v>
@@ -7055,16 +7075,16 @@
     <row r="116">
       <c r="T116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U116" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V116" s="4" t="n">
-        <v>47383</v>
+        <v>717</v>
       </c>
       <c r="X116" s="4" t="n">
         <v>65</v>
@@ -7096,7 +7116,7 @@
     <row r="117">
       <c r="T117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
@@ -7105,7 +7125,7 @@
         </is>
       </c>
       <c r="V117" s="7" t="n">
-        <v>46456</v>
+        <v>47976</v>
       </c>
       <c r="X117" s="7" t="n">
         <v>24</v>
@@ -7137,7 +7157,7 @@
     <row r="118">
       <c r="T118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U118" s="4" t="inlineStr">
@@ -7146,7 +7166,7 @@
         </is>
       </c>
       <c r="V118" s="4" t="n">
-        <v>46400</v>
+        <v>47122</v>
       </c>
       <c r="X118" s="4" t="n">
         <v>14</v>
@@ -7178,7 +7198,7 @@
     <row r="119">
       <c r="T119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U119" s="7" t="inlineStr">
@@ -7187,7 +7207,7 @@
         </is>
       </c>
       <c r="V119" s="7" t="n">
-        <v>47755</v>
+        <v>47233</v>
       </c>
       <c r="X119" s="7" t="n">
         <v>66</v>
@@ -7219,7 +7239,7 @@
     <row r="120">
       <c r="T120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U120" s="4" t="inlineStr">
@@ -7228,7 +7248,7 @@
         </is>
       </c>
       <c r="V120" s="4" t="n">
-        <v>47520</v>
+        <v>48580</v>
       </c>
       <c r="X120" s="4" t="n">
         <v>1</v>
@@ -7260,7 +7280,7 @@
     <row r="121">
       <c r="T121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U121" s="7" t="inlineStr">
@@ -7269,7 +7289,7 @@
         </is>
       </c>
       <c r="V121" s="7" t="n">
-        <v>47354</v>
+        <v>47383</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>9</v>
@@ -7301,7 +7321,7 @@
     <row r="122">
       <c r="T122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U122" s="4" t="inlineStr">
@@ -7310,7 +7330,7 @@
         </is>
       </c>
       <c r="V122" s="4" t="n">
-        <v>49015</v>
+        <v>46456</v>
       </c>
       <c r="X122" s="4" t="n">
         <v>116</v>
@@ -7342,7 +7362,7 @@
     <row r="123">
       <c r="T123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
@@ -7351,7 +7371,7 @@
         </is>
       </c>
       <c r="V123" s="7" t="n">
-        <v>48832</v>
+        <v>46400</v>
       </c>
       <c r="X123" s="7" t="n">
         <v>17</v>
@@ -7383,7 +7403,7 @@
     <row r="124">
       <c r="T124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U124" s="4" t="inlineStr">
@@ -7392,7 +7412,7 @@
         </is>
       </c>
       <c r="V124" s="4" t="n">
-        <v>46644</v>
+        <v>47755</v>
       </c>
       <c r="X124" s="4" t="n">
         <v>52</v>
@@ -7424,7 +7444,7 @@
     <row r="125">
       <c r="T125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U125" s="7" t="inlineStr">
@@ -7433,7 +7453,7 @@
         </is>
       </c>
       <c r="V125" s="7" t="n">
-        <v>46416</v>
+        <v>47520</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>38</v>
@@ -7465,7 +7485,7 @@
     <row r="126">
       <c r="T126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U126" s="4" t="inlineStr">
@@ -7474,7 +7494,7 @@
         </is>
       </c>
       <c r="V126" s="4" t="n">
-        <v>48419</v>
+        <v>47354</v>
       </c>
       <c r="X126" s="4" t="n">
         <v>19</v>
@@ -7506,7 +7526,7 @@
     <row r="127">
       <c r="T127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U127" s="7" t="inlineStr">
@@ -7515,7 +7535,7 @@
         </is>
       </c>
       <c r="V127" s="7" t="n">
-        <v>47500</v>
+        <v>49015</v>
       </c>
       <c r="X127" s="7" t="n">
         <v>79</v>
@@ -7547,7 +7567,7 @@
     <row r="128">
       <c r="T128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U128" s="4" t="inlineStr">
@@ -7556,7 +7576,7 @@
         </is>
       </c>
       <c r="V128" s="4" t="n">
-        <v>47954</v>
+        <v>48832</v>
       </c>
       <c r="X128" s="4" t="n">
         <v>9</v>
@@ -7588,7 +7608,7 @@
     <row r="129">
       <c r="T129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
@@ -7597,7 +7617,7 @@
         </is>
       </c>
       <c r="V129" s="7" t="n">
-        <v>49088</v>
+        <v>46644</v>
       </c>
       <c r="X129" s="7" t="n">
         <v>1</v>
@@ -7629,7 +7649,7 @@
     <row r="130">
       <c r="T130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U130" s="4" t="inlineStr">
@@ -7638,7 +7658,7 @@
         </is>
       </c>
       <c r="V130" s="4" t="n">
-        <v>48111</v>
+        <v>46416</v>
       </c>
       <c r="X130" s="4" t="n">
         <v>134</v>
@@ -7670,7 +7690,7 @@
     <row r="131">
       <c r="T131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U131" s="7" t="inlineStr">
@@ -7679,7 +7699,7 @@
         </is>
       </c>
       <c r="V131" s="7" t="n">
-        <v>46535</v>
+        <v>48419</v>
       </c>
       <c r="X131" s="7" t="n">
         <v>22</v>
@@ -7711,7 +7731,7 @@
     <row r="132">
       <c r="T132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U132" s="4" t="inlineStr">
@@ -7720,7 +7740,7 @@
         </is>
       </c>
       <c r="V132" s="4" t="n">
-        <v>46063</v>
+        <v>47500</v>
       </c>
       <c r="X132" s="4" t="n">
         <v>65</v>
@@ -7752,7 +7772,7 @@
     <row r="133">
       <c r="T133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
@@ -7761,7 +7781,7 @@
         </is>
       </c>
       <c r="V133" s="7" t="n">
-        <v>48085</v>
+        <v>47954</v>
       </c>
       <c r="X133" s="7" t="n">
         <v>29</v>
@@ -7793,16 +7813,16 @@
     <row r="134">
       <c r="T134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U134" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V134" s="4" t="n">
-        <v>1</v>
+        <v>49088</v>
       </c>
       <c r="X134" s="4" t="n">
         <v>12</v>
@@ -7834,16 +7854,16 @@
     <row r="135">
       <c r="T135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U135" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V135" s="7" t="n">
-        <v>1</v>
+        <v>48111</v>
       </c>
       <c r="X135" s="7" t="n">
         <v>82</v>
@@ -7875,16 +7895,16 @@
     <row r="136">
       <c r="T136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U136" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V136" s="4" t="n">
-        <v>1</v>
+        <v>46535</v>
       </c>
       <c r="X136" s="4" t="n">
         <v>1</v>
@@ -7916,16 +7936,16 @@
     <row r="137">
       <c r="T137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U137" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V137" s="7" t="n">
-        <v>1</v>
+        <v>46063</v>
       </c>
       <c r="X137" s="7" t="n">
         <v>7</v>
@@ -7957,16 +7977,16 @@
     <row r="138">
       <c r="T138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U138" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V138" s="4" t="n">
-        <v>1</v>
+        <v>48085</v>
       </c>
       <c r="X138" s="4" t="n">
         <v>1</v>
@@ -7998,16 +8018,16 @@
     <row r="139">
       <c r="T139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V139" s="7" t="n">
-        <v>1</v>
+        <v>47472</v>
       </c>
       <c r="X139" s="7" t="n">
         <v>107</v>
@@ -8039,7 +8059,7 @@
     <row r="140">
       <c r="T140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U140" s="4" t="inlineStr">
@@ -8080,7 +8100,7 @@
     <row r="141">
       <c r="T141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
@@ -8121,7 +8141,7 @@
     <row r="142">
       <c r="T142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U142" s="4" t="inlineStr">
@@ -8162,7 +8182,7 @@
     <row r="143">
       <c r="T143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
@@ -8203,7 +8223,7 @@
     <row r="144">
       <c r="T144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U144" s="4" t="inlineStr">
@@ -8244,7 +8264,7 @@
     <row r="145">
       <c r="T145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U145" s="7" t="inlineStr">
@@ -8285,7 +8305,7 @@
     <row r="146">
       <c r="T146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U146" s="4" t="inlineStr">
@@ -8326,7 +8346,7 @@
     <row r="147">
       <c r="T147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
@@ -8367,7 +8387,7 @@
     <row r="148">
       <c r="T148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U148" s="4" t="inlineStr">
@@ -8408,7 +8428,7 @@
     <row r="149">
       <c r="T149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U149" s="7" t="inlineStr">
@@ -8449,7 +8469,7 @@
     <row r="150">
       <c r="T150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U150" s="4" t="inlineStr">
@@ -8490,7 +8510,7 @@
     <row r="151">
       <c r="T151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
@@ -8531,7 +8551,7 @@
     <row r="152">
       <c r="T152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U152" s="4" t="inlineStr">
@@ -8572,7 +8592,7 @@
     <row r="153">
       <c r="T153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
@@ -8613,12 +8633,12 @@
     <row r="154">
       <c r="T154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U154" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V154" s="4" t="n">
@@ -8654,12 +8674,12 @@
     <row r="155">
       <c r="T155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U155" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V155" s="7" t="n">
@@ -8695,12 +8715,12 @@
     <row r="156">
       <c r="T156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U156" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V156" s="4" t="n">
@@ -8736,12 +8756,12 @@
     <row r="157">
       <c r="T157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V157" s="7" t="n">
@@ -8777,12 +8797,12 @@
     <row r="158">
       <c r="T158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U158" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V158" s="4" t="n">
@@ -8818,12 +8838,12 @@
     <row r="159">
       <c r="T159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V159" s="7" t="n">
@@ -8859,7 +8879,7 @@
     <row r="160">
       <c r="T160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U160" s="4" t="inlineStr">
@@ -8900,7 +8920,7 @@
     <row r="161">
       <c r="T161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
@@ -8941,7 +8961,7 @@
     <row r="162">
       <c r="T162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U162" s="4" t="inlineStr">
@@ -8982,7 +9002,7 @@
     <row r="163">
       <c r="T163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
@@ -9023,7 +9043,7 @@
     <row r="164">
       <c r="T164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U164" s="4" t="inlineStr">
@@ -9064,7 +9084,7 @@
     <row r="165">
       <c r="T165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U165" s="7" t="inlineStr">
@@ -9105,7 +9125,7 @@
     <row r="166">
       <c r="T166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U166" s="4" t="inlineStr">
@@ -9146,7 +9166,7 @@
     <row r="167">
       <c r="T167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
@@ -9187,7 +9207,7 @@
     <row r="168">
       <c r="T168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U168" s="4" t="inlineStr">
@@ -9228,7 +9248,7 @@
     <row r="169">
       <c r="T169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U169" s="7" t="inlineStr">
@@ -9269,7 +9289,7 @@
     <row r="170">
       <c r="T170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U170" s="4" t="inlineStr">
@@ -9310,7 +9330,7 @@
     <row r="171">
       <c r="T171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U171" s="7" t="inlineStr">
@@ -9351,7 +9371,7 @@
     <row r="172">
       <c r="T172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U172" s="4" t="inlineStr">
@@ -9392,7 +9412,7 @@
     <row r="173">
       <c r="T173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
@@ -9433,7 +9453,7 @@
     <row r="174">
       <c r="T174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U174" s="4" t="inlineStr">
@@ -9474,7 +9494,7 @@
     <row r="175">
       <c r="T175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
@@ -9515,16 +9535,16 @@
     <row r="176">
       <c r="T176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U176" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V176" s="4" t="n">
-        <v>9927</v>
+        <v>1</v>
       </c>
       <c r="X176" s="4" t="n">
         <v>20</v>
@@ -9556,19 +9576,19 @@
     <row r="177">
       <c r="T177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U177" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V177" s="7" t="n">
-        <v>9839</v>
+        <v>1</v>
       </c>
       <c r="X177" s="7" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y177" s="7" t="inlineStr">
         <is>
@@ -9597,16 +9617,16 @@
     <row r="178">
       <c r="T178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U178" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V178" s="4" t="n">
-        <v>9918</v>
+        <v>1</v>
       </c>
       <c r="X178" s="4" t="n">
         <v>7</v>
@@ -9638,16 +9658,16 @@
     <row r="179">
       <c r="T179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V179" s="7" t="n">
-        <v>10435</v>
+        <v>1</v>
       </c>
       <c r="X179" s="7" t="n">
         <v>2</v>
@@ -9679,20 +9699,30 @@
     <row r="180">
       <c r="T180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U180" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V180" s="4" t="n">
-        <v>10050</v>
-      </c>
-      <c r="X180" s="4" t="n"/>
-      <c r="Y180" s="4" t="n"/>
-      <c r="Z180" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X180" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="Y180" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z180" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB180" s="4" t="n">
         <v>6</v>
       </c>
@@ -9710,20 +9740,30 @@
     <row r="181">
       <c r="T181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U181" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V181" s="7" t="n">
-        <v>9768</v>
-      </c>
-      <c r="X181" s="7" t="n"/>
-      <c r="Y181" s="7" t="n"/>
-      <c r="Z181" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X181" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y181" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z181" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB181" s="7" t="n">
         <v>2</v>
       </c>
@@ -9741,7 +9781,7 @@
     <row r="182">
       <c r="T182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U182" s="4" t="inlineStr">
@@ -9750,11 +9790,21 @@
         </is>
       </c>
       <c r="V182" s="4" t="n">
-        <v>9920</v>
-      </c>
-      <c r="X182" s="4" t="n"/>
-      <c r="Y182" s="4" t="n"/>
-      <c r="Z182" s="4" t="n"/>
+        <v>9927</v>
+      </c>
+      <c r="X182" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y182" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z182" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB182" s="4" t="n">
         <v>388</v>
       </c>
@@ -9772,7 +9822,7 @@
     <row r="183">
       <c r="T183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U183" s="7" t="inlineStr">
@@ -9781,11 +9831,21 @@
         </is>
       </c>
       <c r="V183" s="7" t="n">
-        <v>10435</v>
-      </c>
-      <c r="X183" s="7" t="n"/>
-      <c r="Y183" s="7" t="n"/>
-      <c r="Z183" s="7" t="n"/>
+        <v>9839</v>
+      </c>
+      <c r="X183" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y183" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z183" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB183" s="7" t="n">
         <v>28</v>
       </c>
@@ -9803,7 +9863,7 @@
     <row r="184">
       <c r="T184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U184" s="4" t="inlineStr">
@@ -9812,11 +9872,21 @@
         </is>
       </c>
       <c r="V184" s="4" t="n">
-        <v>10434</v>
-      </c>
-      <c r="X184" s="4" t="n"/>
-      <c r="Y184" s="4" t="n"/>
-      <c r="Z184" s="4" t="n"/>
+        <v>9918</v>
+      </c>
+      <c r="X184" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y184" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z184" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB184" s="4" t="n">
         <v>122</v>
       </c>
@@ -9834,7 +9904,7 @@
     <row r="185">
       <c r="T185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U185" s="7" t="inlineStr">
@@ -9843,11 +9913,21 @@
         </is>
       </c>
       <c r="V185" s="7" t="n">
-        <v>10284</v>
-      </c>
-      <c r="X185" s="7" t="n"/>
-      <c r="Y185" s="7" t="n"/>
-      <c r="Z185" s="7" t="n"/>
+        <v>10435</v>
+      </c>
+      <c r="X185" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="Y185" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z185" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB185" s="7" t="n">
         <v>45</v>
       </c>
@@ -9865,7 +9945,7 @@
     <row r="186">
       <c r="T186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U186" s="4" t="inlineStr">
@@ -9874,11 +9954,21 @@
         </is>
       </c>
       <c r="V186" s="4" t="n">
-        <v>10458</v>
-      </c>
-      <c r="X186" s="4" t="n"/>
-      <c r="Y186" s="4" t="n"/>
-      <c r="Z186" s="4" t="n"/>
+        <v>10050</v>
+      </c>
+      <c r="X186" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y186" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z186" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB186" s="4" t="n">
         <v>43</v>
       </c>
@@ -9896,7 +9986,7 @@
     <row r="187">
       <c r="T187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U187" s="7" t="inlineStr">
@@ -9905,11 +9995,21 @@
         </is>
       </c>
       <c r="V187" s="7" t="n">
-        <v>10153</v>
-      </c>
-      <c r="X187" s="7" t="n"/>
-      <c r="Y187" s="7" t="n"/>
-      <c r="Z187" s="7" t="n"/>
+        <v>9768</v>
+      </c>
+      <c r="X187" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y187" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z187" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB187" s="7" t="n">
         <v>2</v>
       </c>
@@ -9927,7 +10027,7 @@
     <row r="188">
       <c r="T188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U188" s="4" t="inlineStr">
@@ -9936,7 +10036,7 @@
         </is>
       </c>
       <c r="V188" s="4" t="n">
-        <v>9843</v>
+        <v>9920</v>
       </c>
       <c r="X188" s="4" t="n"/>
       <c r="Y188" s="4" t="n"/>
@@ -9958,7 +10058,7 @@
     <row r="189">
       <c r="T189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U189" s="7" t="inlineStr">
@@ -9967,7 +10067,7 @@
         </is>
       </c>
       <c r="V189" s="7" t="n">
-        <v>10433</v>
+        <v>10435</v>
       </c>
       <c r="X189" s="7" t="n"/>
       <c r="Y189" s="7" t="n"/>
@@ -9989,7 +10089,7 @@
     <row r="190">
       <c r="T190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U190" s="4" t="inlineStr">
@@ -9998,7 +10098,7 @@
         </is>
       </c>
       <c r="V190" s="4" t="n">
-        <v>10670</v>
+        <v>10434</v>
       </c>
       <c r="X190" s="4" t="n"/>
       <c r="Y190" s="4" t="n"/>
@@ -10020,7 +10120,7 @@
     <row r="191">
       <c r="T191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U191" s="7" t="inlineStr">
@@ -10029,7 +10129,7 @@
         </is>
       </c>
       <c r="V191" s="7" t="n">
-        <v>10599</v>
+        <v>10284</v>
       </c>
       <c r="X191" s="7" t="n"/>
       <c r="Y191" s="7" t="n"/>
@@ -10051,7 +10151,7 @@
     <row r="192">
       <c r="T192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U192" s="4" t="inlineStr">
@@ -10060,7 +10160,7 @@
         </is>
       </c>
       <c r="V192" s="4" t="n">
-        <v>10619</v>
+        <v>10458</v>
       </c>
       <c r="X192" s="4" t="n"/>
       <c r="Y192" s="4" t="n"/>
@@ -10082,7 +10182,7 @@
     <row r="193">
       <c r="T193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U193" s="7" t="inlineStr">
@@ -10091,7 +10191,7 @@
         </is>
       </c>
       <c r="V193" s="7" t="n">
-        <v>10415</v>
+        <v>10153</v>
       </c>
       <c r="X193" s="7" t="n"/>
       <c r="Y193" s="7" t="n"/>
@@ -10113,7 +10213,7 @@
     <row r="194">
       <c r="T194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U194" s="4" t="inlineStr">
@@ -10122,7 +10222,7 @@
         </is>
       </c>
       <c r="V194" s="4" t="n">
-        <v>10065</v>
+        <v>9843</v>
       </c>
       <c r="X194" s="4" t="n"/>
       <c r="Y194" s="4" t="n"/>
@@ -10144,7 +10244,7 @@
     <row r="195">
       <c r="T195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U195" s="7" t="inlineStr">
@@ -10153,7 +10253,7 @@
         </is>
       </c>
       <c r="V195" s="7" t="n">
-        <v>10158</v>
+        <v>10433</v>
       </c>
       <c r="X195" s="7" t="n"/>
       <c r="Y195" s="7" t="n"/>
@@ -10175,7 +10275,7 @@
     <row r="196">
       <c r="T196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U196" s="4" t="inlineStr">
@@ -10184,7 +10284,7 @@
         </is>
       </c>
       <c r="V196" s="4" t="n">
-        <v>10333</v>
+        <v>10670</v>
       </c>
       <c r="X196" s="4" t="n"/>
       <c r="Y196" s="4" t="n"/>
@@ -10206,7 +10306,7 @@
     <row r="197">
       <c r="T197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U197" s="7" t="inlineStr">
@@ -10215,7 +10315,7 @@
         </is>
       </c>
       <c r="V197" s="7" t="n">
-        <v>10414</v>
+        <v>10599</v>
       </c>
       <c r="X197" s="7" t="n"/>
       <c r="Y197" s="7" t="n"/>
@@ -10237,16 +10337,16 @@
     <row r="198">
       <c r="T198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U198" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation50987</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V198" s="4" t="n">
-        <v>1</v>
+        <v>10619</v>
       </c>
       <c r="X198" s="4" t="n"/>
       <c r="Y198" s="4" t="n"/>
@@ -10268,16 +10368,16 @@
     <row r="199">
       <c r="T199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U199" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation75114</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V199" s="7" t="n">
-        <v>1</v>
+        <v>10415</v>
       </c>
       <c r="X199" s="7" t="n"/>
       <c r="Y199" s="7" t="n"/>
@@ -10299,16 +10399,16 @@
     <row r="200">
       <c r="T200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U200" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V200" s="4" t="n">
-        <v>21493</v>
+        <v>10065</v>
       </c>
       <c r="X200" s="4" t="n"/>
       <c r="Y200" s="4" t="n"/>
@@ -10330,133 +10430,193 @@
     <row r="201">
       <c r="T201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U201" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V201" s="7" t="n">
-        <v>21012</v>
+        <v>10158</v>
       </c>
       <c r="X201" s="7" t="n"/>
       <c r="Y201" s="7" t="n"/>
       <c r="Z201" s="7" t="n"/>
-      <c r="AB201" s="7" t="n"/>
-      <c r="AC201" s="7" t="n"/>
-      <c r="AD201" s="7" t="n"/>
+      <c r="AB201" s="7" t="n">
+        <v>321</v>
+      </c>
+      <c r="AC201" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD201" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="T202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U202" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V202" s="4" t="n">
-        <v>21635</v>
+        <v>10333</v>
       </c>
       <c r="X202" s="4" t="n"/>
       <c r="Y202" s="4" t="n"/>
       <c r="Z202" s="4" t="n"/>
-      <c r="AB202" s="4" t="n"/>
-      <c r="AC202" s="4" t="n"/>
-      <c r="AD202" s="4" t="n"/>
+      <c r="AB202" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC202" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD202" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="T203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U203" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V203" s="7" t="n">
-        <v>21969</v>
+        <v>10414</v>
       </c>
       <c r="X203" s="7" t="n"/>
       <c r="Y203" s="7" t="n"/>
       <c r="Z203" s="7" t="n"/>
-      <c r="AB203" s="7" t="n"/>
-      <c r="AC203" s="7" t="n"/>
-      <c r="AD203" s="7" t="n"/>
+      <c r="AB203" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AC203" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD203" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="T204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U204" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V204" s="4" t="n">
-        <v>21723</v>
+        <v>10453</v>
       </c>
       <c r="X204" s="4" t="n"/>
       <c r="Y204" s="4" t="n"/>
       <c r="Z204" s="4" t="n"/>
-      <c r="AB204" s="4" t="n"/>
-      <c r="AC204" s="4" t="n"/>
-      <c r="AD204" s="4" t="n"/>
+      <c r="AB204" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC204" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD204" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="T205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U205" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation50987</t>
         </is>
       </c>
       <c r="V205" s="7" t="n">
-        <v>20879</v>
+        <v>1</v>
       </c>
       <c r="X205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
       <c r="Z205" s="7" t="n"/>
-      <c r="AB205" s="7" t="n"/>
-      <c r="AC205" s="7" t="n"/>
-      <c r="AD205" s="7" t="n"/>
+      <c r="AB205" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC205" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD205" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="T206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U206" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation75114</t>
         </is>
       </c>
       <c r="V206" s="4" t="n">
-        <v>20783</v>
+        <v>1</v>
       </c>
       <c r="X206" s="4" t="n"/>
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="n"/>
-      <c r="AB206" s="4" t="n"/>
-      <c r="AC206" s="4" t="n"/>
-      <c r="AD206" s="4" t="n"/>
+      <c r="AB206" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="AC206" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD206" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="T207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U207" s="7" t="inlineStr">
@@ -10465,19 +10625,29 @@
         </is>
       </c>
       <c r="V207" s="7" t="n">
-        <v>21875</v>
+        <v>21493</v>
       </c>
       <c r="X207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
       <c r="Z207" s="7" t="n"/>
-      <c r="AB207" s="7" t="n"/>
-      <c r="AC207" s="7" t="n"/>
-      <c r="AD207" s="7" t="n"/>
+      <c r="AB207" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC207" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD207" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="T208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U208" s="4" t="inlineStr">
@@ -10486,19 +10656,29 @@
         </is>
       </c>
       <c r="V208" s="4" t="n">
-        <v>22103</v>
+        <v>21012</v>
       </c>
       <c r="X208" s="4" t="n"/>
       <c r="Y208" s="4" t="n"/>
       <c r="Z208" s="4" t="n"/>
-      <c r="AB208" s="4" t="n"/>
-      <c r="AC208" s="4" t="n"/>
-      <c r="AD208" s="4" t="n"/>
+      <c r="AB208" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC208" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD208" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="T209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U209" s="7" t="inlineStr">
@@ -10507,19 +10687,29 @@
         </is>
       </c>
       <c r="V209" s="7" t="n">
-        <v>22799</v>
+        <v>21635</v>
       </c>
       <c r="X209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
       <c r="Z209" s="7" t="n"/>
-      <c r="AB209" s="7" t="n"/>
-      <c r="AC209" s="7" t="n"/>
-      <c r="AD209" s="7" t="n"/>
+      <c r="AB209" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC209" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD209" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="T210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U210" s="4" t="inlineStr">
@@ -10528,7 +10718,7 @@
         </is>
       </c>
       <c r="V210" s="4" t="n">
-        <v>22705</v>
+        <v>21969</v>
       </c>
       <c r="X210" s="4" t="n"/>
       <c r="Y210" s="4" t="n"/>
@@ -10540,7 +10730,7 @@
     <row r="211">
       <c r="T211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U211" s="7" t="inlineStr">
@@ -10549,7 +10739,7 @@
         </is>
       </c>
       <c r="V211" s="7" t="n">
-        <v>21885</v>
+        <v>21723</v>
       </c>
       <c r="X211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
@@ -10561,7 +10751,7 @@
     <row r="212">
       <c r="T212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U212" s="4" t="inlineStr">
@@ -10570,7 +10760,7 @@
         </is>
       </c>
       <c r="V212" s="4" t="n">
-        <v>21360</v>
+        <v>20879</v>
       </c>
       <c r="X212" s="4" t="n"/>
       <c r="Y212" s="4" t="n"/>
@@ -10582,7 +10772,7 @@
     <row r="213">
       <c r="T213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U213" s="7" t="inlineStr">
@@ -10591,7 +10781,7 @@
         </is>
       </c>
       <c r="V213" s="7" t="n">
-        <v>20612</v>
+        <v>20783</v>
       </c>
       <c r="X213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
@@ -10603,7 +10793,7 @@
     <row r="214">
       <c r="T214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U214" s="4" t="inlineStr">
@@ -10612,7 +10802,7 @@
         </is>
       </c>
       <c r="V214" s="4" t="n">
-        <v>22101</v>
+        <v>21875</v>
       </c>
       <c r="X214" s="4" t="n"/>
       <c r="Y214" s="4" t="n"/>
@@ -10624,7 +10814,7 @@
     <row r="215">
       <c r="T215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U215" s="7" t="inlineStr">
@@ -10633,7 +10823,7 @@
         </is>
       </c>
       <c r="V215" s="7" t="n">
-        <v>22665</v>
+        <v>22103</v>
       </c>
       <c r="X215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
@@ -10645,7 +10835,7 @@
     <row r="216">
       <c r="T216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U216" s="4" t="inlineStr">
@@ -10654,7 +10844,7 @@
         </is>
       </c>
       <c r="V216" s="4" t="n">
-        <v>22473</v>
+        <v>22799</v>
       </c>
       <c r="X216" s="4" t="n"/>
       <c r="Y216" s="4" t="n"/>
@@ -10666,7 +10856,7 @@
     <row r="217">
       <c r="T217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U217" s="7" t="inlineStr">
@@ -10675,7 +10865,7 @@
         </is>
       </c>
       <c r="V217" s="7" t="n">
-        <v>22903</v>
+        <v>22705</v>
       </c>
       <c r="X217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
@@ -10687,7 +10877,7 @@
     <row r="218">
       <c r="T218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U218" s="4" t="inlineStr">
@@ -10696,7 +10886,7 @@
         </is>
       </c>
       <c r="V218" s="4" t="n">
-        <v>21829</v>
+        <v>21885</v>
       </c>
       <c r="X218" s="4" t="n"/>
       <c r="Y218" s="4" t="n"/>
@@ -10708,7 +10898,7 @@
     <row r="219">
       <c r="T219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U219" s="7" t="inlineStr">
@@ -10717,7 +10907,7 @@
         </is>
       </c>
       <c r="V219" s="7" t="n">
-        <v>20959</v>
+        <v>21360</v>
       </c>
       <c r="X219" s="7" t="n"/>
       <c r="Y219" s="7" t="n"/>
@@ -10729,7 +10919,7 @@
     <row r="220">
       <c r="T220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U220" s="4" t="inlineStr">
@@ -10738,7 +10928,7 @@
         </is>
       </c>
       <c r="V220" s="4" t="n">
-        <v>20856</v>
+        <v>20612</v>
       </c>
       <c r="X220" s="4" t="n"/>
       <c r="Y220" s="4" t="n"/>
@@ -10750,7 +10940,7 @@
     <row r="221">
       <c r="T221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U221" s="7" t="inlineStr">
@@ -10759,7 +10949,7 @@
         </is>
       </c>
       <c r="V221" s="7" t="n">
-        <v>23061</v>
+        <v>22101</v>
       </c>
       <c r="X221" s="7" t="n"/>
       <c r="Y221" s="7" t="n"/>
@@ -10771,16 +10961,16 @@
     <row r="222">
       <c r="T222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U222" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V222" s="4" t="n">
-        <v>16634</v>
+        <v>22665</v>
       </c>
       <c r="X222" s="4" t="n"/>
       <c r="Y222" s="4" t="n"/>
@@ -10792,16 +10982,16 @@
     <row r="223">
       <c r="T223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U223" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V223" s="7" t="n">
-        <v>16721</v>
+        <v>22473</v>
       </c>
       <c r="X223" s="7" t="n"/>
       <c r="Y223" s="7" t="n"/>
@@ -10813,16 +11003,16 @@
     <row r="224">
       <c r="T224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U224" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V224" s="4" t="n">
-        <v>16586</v>
+        <v>22903</v>
       </c>
       <c r="X224" s="4" t="n"/>
       <c r="Y224" s="4" t="n"/>
@@ -10834,16 +11024,16 @@
     <row r="225">
       <c r="T225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U225" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V225" s="7" t="n">
-        <v>16419</v>
+        <v>21829</v>
       </c>
       <c r="X225" s="7" t="n"/>
       <c r="Y225" s="7" t="n"/>
@@ -10855,16 +11045,16 @@
     <row r="226">
       <c r="T226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U226" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V226" s="4" t="n">
-        <v>15946</v>
+        <v>20959</v>
       </c>
       <c r="X226" s="4" t="n"/>
       <c r="Y226" s="4" t="n"/>
@@ -10876,16 +11066,16 @@
     <row r="227">
       <c r="T227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U227" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V227" s="7" t="n">
-        <v>16042</v>
+        <v>20856</v>
       </c>
       <c r="X227" s="7" t="n"/>
       <c r="Y227" s="7" t="n"/>
@@ -10897,16 +11087,16 @@
     <row r="228">
       <c r="T228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U228" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V228" s="4" t="n">
-        <v>16409</v>
+        <v>23061</v>
       </c>
       <c r="X228" s="4" t="n"/>
       <c r="Y228" s="4" t="n"/>
@@ -10918,16 +11108,16 @@
     <row r="229">
       <c r="T229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U229" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V229" s="7" t="n">
-        <v>16831</v>
+        <v>21952</v>
       </c>
       <c r="X229" s="7" t="n"/>
       <c r="Y229" s="7" t="n"/>
@@ -10939,7 +11129,7 @@
     <row r="230">
       <c r="T230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U230" s="4" t="inlineStr">
@@ -10948,7 +11138,7 @@
         </is>
       </c>
       <c r="V230" s="4" t="n">
-        <v>16886</v>
+        <v>16634</v>
       </c>
       <c r="X230" s="4" t="n"/>
       <c r="Y230" s="4" t="n"/>
@@ -10960,7 +11150,7 @@
     <row r="231">
       <c r="T231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U231" s="7" t="inlineStr">
@@ -10969,7 +11159,7 @@
         </is>
       </c>
       <c r="V231" s="7" t="n">
-        <v>16694</v>
+        <v>16721</v>
       </c>
       <c r="X231" s="7" t="n"/>
       <c r="Y231" s="7" t="n"/>
@@ -10981,7 +11171,7 @@
     <row r="232">
       <c r="T232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U232" s="4" t="inlineStr">
@@ -10990,7 +11180,7 @@
         </is>
       </c>
       <c r="V232" s="4" t="n">
-        <v>16659</v>
+        <v>16586</v>
       </c>
       <c r="X232" s="4" t="n"/>
       <c r="Y232" s="4" t="n"/>
@@ -11002,7 +11192,7 @@
     <row r="233">
       <c r="T233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U233" s="7" t="inlineStr">
@@ -11011,7 +11201,7 @@
         </is>
       </c>
       <c r="V233" s="7" t="n">
-        <v>16268</v>
+        <v>16419</v>
       </c>
       <c r="X233" s="7" t="n"/>
       <c r="Y233" s="7" t="n"/>
@@ -11023,7 +11213,7 @@
     <row r="234">
       <c r="T234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U234" s="4" t="inlineStr">
@@ -11032,7 +11222,7 @@
         </is>
       </c>
       <c r="V234" s="4" t="n">
-        <v>16259</v>
+        <v>15946</v>
       </c>
       <c r="X234" s="4" t="n"/>
       <c r="Y234" s="4" t="n"/>
@@ -11044,7 +11234,7 @@
     <row r="235">
       <c r="T235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U235" s="7" t="inlineStr">
@@ -11053,7 +11243,7 @@
         </is>
       </c>
       <c r="V235" s="7" t="n">
-        <v>16600</v>
+        <v>16042</v>
       </c>
       <c r="X235" s="7" t="n"/>
       <c r="Y235" s="7" t="n"/>
@@ -11065,7 +11255,7 @@
     <row r="236">
       <c r="T236" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U236" s="4" t="inlineStr">
@@ -11074,7 +11264,7 @@
         </is>
       </c>
       <c r="V236" s="4" t="n">
-        <v>16913</v>
+        <v>16409</v>
       </c>
       <c r="X236" s="4" t="n"/>
       <c r="Y236" s="4" t="n"/>
@@ -11086,7 +11276,7 @@
     <row r="237">
       <c r="T237" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U237" s="7" t="inlineStr">
@@ -11095,7 +11285,7 @@
         </is>
       </c>
       <c r="V237" s="7" t="n">
-        <v>16991</v>
+        <v>16831</v>
       </c>
       <c r="X237" s="7" t="n"/>
       <c r="Y237" s="7" t="n"/>
@@ -11107,7 +11297,7 @@
     <row r="238">
       <c r="T238" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U238" s="4" t="inlineStr">
@@ -11116,7 +11306,7 @@
         </is>
       </c>
       <c r="V238" s="4" t="n">
-        <v>17365</v>
+        <v>16886</v>
       </c>
       <c r="X238" s="4" t="n"/>
       <c r="Y238" s="4" t="n"/>
@@ -11128,7 +11318,7 @@
     <row r="239">
       <c r="T239" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U239" s="7" t="inlineStr">
@@ -11137,7 +11327,7 @@
         </is>
       </c>
       <c r="V239" s="7" t="n">
-        <v>16944</v>
+        <v>16694</v>
       </c>
       <c r="X239" s="7" t="n"/>
       <c r="Y239" s="7" t="n"/>
@@ -11149,7 +11339,7 @@
     <row r="240">
       <c r="T240" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U240" s="4" t="inlineStr">
@@ -11158,7 +11348,7 @@
         </is>
       </c>
       <c r="V240" s="4" t="n">
-        <v>16518</v>
+        <v>16659</v>
       </c>
       <c r="X240" s="4" t="n"/>
       <c r="Y240" s="4" t="n"/>
@@ -11170,7 +11360,7 @@
     <row r="241">
       <c r="T241" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U241" s="7" t="inlineStr">
@@ -11179,7 +11369,7 @@
         </is>
       </c>
       <c r="V241" s="7" t="n">
-        <v>16634</v>
+        <v>16268</v>
       </c>
       <c r="X241" s="7" t="n"/>
       <c r="Y241" s="7" t="n"/>
@@ -11191,7 +11381,7 @@
     <row r="242">
       <c r="T242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U242" s="4" t="inlineStr">
@@ -11200,7 +11390,7 @@
         </is>
       </c>
       <c r="V242" s="4" t="n">
-        <v>16711</v>
+        <v>16259</v>
       </c>
       <c r="X242" s="4" t="n"/>
       <c r="Y242" s="4" t="n"/>
@@ -11212,7 +11402,7 @@
     <row r="243">
       <c r="T243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U243" s="7" t="inlineStr">
@@ -11221,7 +11411,7 @@
         </is>
       </c>
       <c r="V243" s="7" t="n">
-        <v>17379</v>
+        <v>16600</v>
       </c>
       <c r="X243" s="7" t="n"/>
       <c r="Y243" s="7" t="n"/>
@@ -11233,16 +11423,16 @@
     <row r="244">
       <c r="T244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U244" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V244" s="4" t="n">
-        <v>724</v>
+        <v>16913</v>
       </c>
       <c r="X244" s="4" t="n"/>
       <c r="Y244" s="4" t="n"/>
@@ -11254,16 +11444,16 @@
     <row r="245">
       <c r="T245" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U245" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V245" s="7" t="n">
-        <v>746</v>
+        <v>16991</v>
       </c>
       <c r="X245" s="7" t="n"/>
       <c r="Y245" s="7" t="n"/>
@@ -11275,16 +11465,16 @@
     <row r="246">
       <c r="T246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U246" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V246" s="4" t="n">
-        <v>723</v>
+        <v>17365</v>
       </c>
       <c r="X246" s="4" t="n"/>
       <c r="Y246" s="4" t="n"/>
@@ -11296,16 +11486,16 @@
     <row r="247">
       <c r="T247" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U247" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V247" s="7" t="n">
-        <v>708</v>
+        <v>16944</v>
       </c>
       <c r="X247" s="7" t="n"/>
       <c r="Y247" s="7" t="n"/>
@@ -11317,16 +11507,16 @@
     <row r="248">
       <c r="T248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U248" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V248" s="4" t="n">
-        <v>735</v>
+        <v>16518</v>
       </c>
       <c r="X248" s="4" t="n"/>
       <c r="Y248" s="4" t="n"/>
@@ -11338,16 +11528,16 @@
     <row r="249">
       <c r="T249" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U249" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V249" s="7" t="n">
-        <v>714</v>
+        <v>16634</v>
       </c>
       <c r="X249" s="7" t="n"/>
       <c r="Y249" s="7" t="n"/>
@@ -11359,16 +11549,16 @@
     <row r="250">
       <c r="T250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U250" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V250" s="4" t="n">
-        <v>706</v>
+        <v>16711</v>
       </c>
       <c r="X250" s="4" t="n"/>
       <c r="Y250" s="4" t="n"/>
@@ -11380,16 +11570,16 @@
     <row r="251">
       <c r="T251" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U251" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V251" s="7" t="n">
-        <v>729</v>
+        <v>17379</v>
       </c>
       <c r="X251" s="7" t="n"/>
       <c r="Y251" s="7" t="n"/>
@@ -11401,16 +11591,16 @@
     <row r="252">
       <c r="T252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U252" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V252" s="4" t="n">
-        <v>719</v>
+        <v>17551</v>
       </c>
       <c r="X252" s="4" t="n"/>
       <c r="Y252" s="4" t="n"/>
@@ -11422,7 +11612,7 @@
     <row r="253">
       <c r="T253" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U253" s="7" t="inlineStr">
@@ -11431,7 +11621,7 @@
         </is>
       </c>
       <c r="V253" s="7" t="n">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="X253" s="7" t="n"/>
       <c r="Y253" s="7" t="n"/>
@@ -11443,7 +11633,7 @@
     <row r="254">
       <c r="T254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U254" s="4" t="inlineStr">
@@ -11452,7 +11642,7 @@
         </is>
       </c>
       <c r="V254" s="4" t="n">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="X254" s="4" t="n"/>
       <c r="Y254" s="4" t="n"/>
@@ -11464,7 +11654,7 @@
     <row r="255">
       <c r="T255" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U255" s="7" t="inlineStr">
@@ -11473,7 +11663,7 @@
         </is>
       </c>
       <c r="V255" s="7" t="n">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="X255" s="7" t="n"/>
       <c r="Y255" s="7" t="n"/>
@@ -11485,7 +11675,7 @@
     <row r="256">
       <c r="T256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U256" s="4" t="inlineStr">
@@ -11506,7 +11696,7 @@
     <row r="257">
       <c r="T257" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U257" s="7" t="inlineStr">
@@ -11515,7 +11705,7 @@
         </is>
       </c>
       <c r="V257" s="7" t="n">
-        <v>698</v>
+        <v>735</v>
       </c>
       <c r="X257" s="7" t="n"/>
       <c r="Y257" s="7" t="n"/>
@@ -11527,7 +11717,7 @@
     <row r="258">
       <c r="T258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U258" s="4" t="inlineStr">
@@ -11536,7 +11726,7 @@
         </is>
       </c>
       <c r="V258" s="4" t="n">
-        <v>691</v>
+        <v>714</v>
       </c>
       <c r="X258" s="4" t="n"/>
       <c r="Y258" s="4" t="n"/>
@@ -11548,7 +11738,7 @@
     <row r="259">
       <c r="T259" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U259" s="7" t="inlineStr">
@@ -11557,7 +11747,7 @@
         </is>
       </c>
       <c r="V259" s="7" t="n">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="X259" s="7" t="n"/>
       <c r="Y259" s="7" t="n"/>
@@ -11569,7 +11759,7 @@
     <row r="260">
       <c r="T260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U260" s="4" t="inlineStr">
@@ -11578,7 +11768,7 @@
         </is>
       </c>
       <c r="V260" s="4" t="n">
-        <v>706</v>
+        <v>729</v>
       </c>
       <c r="X260" s="4" t="n"/>
       <c r="Y260" s="4" t="n"/>
@@ -11590,7 +11780,7 @@
     <row r="261">
       <c r="T261" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U261" s="7" t="inlineStr">
@@ -11599,7 +11789,7 @@
         </is>
       </c>
       <c r="V261" s="7" t="n">
-        <v>701</v>
+        <v>719</v>
       </c>
       <c r="X261" s="7" t="n"/>
       <c r="Y261" s="7" t="n"/>
@@ -11611,7 +11801,7 @@
     <row r="262">
       <c r="T262" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U262" s="4" t="inlineStr">
@@ -11620,7 +11810,7 @@
         </is>
       </c>
       <c r="V262" s="4" t="n">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="X262" s="4" t="n"/>
       <c r="Y262" s="4" t="n"/>
@@ -11632,7 +11822,7 @@
     <row r="263">
       <c r="T263" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U263" s="7" t="inlineStr">
@@ -11641,7 +11831,7 @@
         </is>
       </c>
       <c r="V263" s="7" t="n">
-        <v>704</v>
+        <v>730</v>
       </c>
       <c r="X263" s="7" t="n"/>
       <c r="Y263" s="7" t="n"/>
@@ -11653,7 +11843,7 @@
     <row r="264">
       <c r="T264" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U264" s="4" t="inlineStr">
@@ -11662,7 +11852,7 @@
         </is>
       </c>
       <c r="V264" s="4" t="n">
-        <v>670</v>
+        <v>740</v>
       </c>
       <c r="X264" s="4" t="n"/>
       <c r="Y264" s="4" t="n"/>
@@ -11674,7 +11864,7 @@
     <row r="265">
       <c r="T265" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U265" s="7" t="inlineStr">
@@ -11683,7 +11873,7 @@
         </is>
       </c>
       <c r="V265" s="7" t="n">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="X265" s="7" t="n"/>
       <c r="Y265" s="7" t="n"/>
@@ -11695,16 +11885,16 @@
     <row r="266">
       <c r="T266" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U266" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V266" s="4" t="n">
-        <v>2188</v>
+        <v>698</v>
       </c>
       <c r="X266" s="4" t="n"/>
       <c r="Y266" s="4" t="n"/>
@@ -11716,16 +11906,16 @@
     <row r="267">
       <c r="T267" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U267" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V267" s="7" t="n">
-        <v>2046</v>
+        <v>691</v>
       </c>
       <c r="X267" s="7" t="n"/>
       <c r="Y267" s="7" t="n"/>
@@ -11737,16 +11927,16 @@
     <row r="268">
       <c r="T268" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U268" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V268" s="4" t="n">
-        <v>2338</v>
+        <v>695</v>
       </c>
       <c r="X268" s="4" t="n"/>
       <c r="Y268" s="4" t="n"/>
@@ -11758,16 +11948,16 @@
     <row r="269">
       <c r="T269" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U269" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V269" s="7" t="n">
-        <v>2152</v>
+        <v>706</v>
       </c>
       <c r="X269" s="7" t="n"/>
       <c r="Y269" s="7" t="n"/>
@@ -11779,16 +11969,16 @@
     <row r="270">
       <c r="T270" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U270" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V270" s="4" t="n">
-        <v>2003</v>
+        <v>701</v>
       </c>
       <c r="X270" s="4" t="n"/>
       <c r="Y270" s="4" t="n"/>
@@ -11800,16 +11990,16 @@
     <row r="271">
       <c r="T271" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U271" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V271" s="7" t="n">
-        <v>1895</v>
+        <v>706</v>
       </c>
       <c r="X271" s="7" t="n"/>
       <c r="Y271" s="7" t="n"/>
@@ -11821,16 +12011,16 @@
     <row r="272">
       <c r="T272" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U272" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V272" s="4" t="n">
-        <v>1935</v>
+        <v>704</v>
       </c>
       <c r="X272" s="4" t="n"/>
       <c r="Y272" s="4" t="n"/>
@@ -11842,16 +12032,16 @@
     <row r="273">
       <c r="T273" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U273" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V273" s="7" t="n">
-        <v>2037</v>
+        <v>670</v>
       </c>
       <c r="X273" s="7" t="n"/>
       <c r="Y273" s="7" t="n"/>
@@ -11863,16 +12053,16 @@
     <row r="274">
       <c r="T274" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U274" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V274" s="4" t="n">
-        <v>2049</v>
+        <v>694</v>
       </c>
       <c r="X274" s="4" t="n"/>
       <c r="Y274" s="4" t="n"/>
@@ -11884,16 +12074,16 @@
     <row r="275">
       <c r="T275" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U275" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V275" s="7" t="n">
-        <v>2325</v>
+        <v>702</v>
       </c>
       <c r="X275" s="7" t="n"/>
       <c r="Y275" s="7" t="n"/>
@@ -11905,7 +12095,7 @@
     <row r="276">
       <c r="T276" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U276" s="4" t="inlineStr">
@@ -11914,7 +12104,7 @@
         </is>
       </c>
       <c r="V276" s="4" t="n">
-        <v>2216</v>
+        <v>2188</v>
       </c>
       <c r="X276" s="4" t="n"/>
       <c r="Y276" s="4" t="n"/>
@@ -11926,7 +12116,7 @@
     <row r="277">
       <c r="T277" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U277" s="7" t="inlineStr">
@@ -11935,7 +12125,7 @@
         </is>
       </c>
       <c r="V277" s="7" t="n">
-        <v>2037</v>
+        <v>2046</v>
       </c>
       <c r="X277" s="7" t="n"/>
       <c r="Y277" s="7" t="n"/>
@@ -11947,7 +12137,7 @@
     <row r="278">
       <c r="T278" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U278" s="4" t="inlineStr">
@@ -11956,7 +12146,7 @@
         </is>
       </c>
       <c r="V278" s="4" t="n">
-        <v>2046</v>
+        <v>2338</v>
       </c>
       <c r="X278" s="4" t="n"/>
       <c r="Y278" s="4" t="n"/>
@@ -11968,7 +12158,7 @@
     <row r="279">
       <c r="T279" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U279" s="7" t="inlineStr">
@@ -11977,7 +12167,7 @@
         </is>
       </c>
       <c r="V279" s="7" t="n">
-        <v>2035</v>
+        <v>2152</v>
       </c>
       <c r="X279" s="7" t="n"/>
       <c r="Y279" s="7" t="n"/>
@@ -11989,7 +12179,7 @@
     <row r="280">
       <c r="T280" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U280" s="4" t="inlineStr">
@@ -11998,7 +12188,7 @@
         </is>
       </c>
       <c r="V280" s="4" t="n">
-        <v>2182</v>
+        <v>2003</v>
       </c>
       <c r="X280" s="4" t="n"/>
       <c r="Y280" s="4" t="n"/>
@@ -12010,7 +12200,7 @@
     <row r="281">
       <c r="T281" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U281" s="7" t="inlineStr">
@@ -12019,7 +12209,7 @@
         </is>
       </c>
       <c r="V281" s="7" t="n">
-        <v>2156</v>
+        <v>1895</v>
       </c>
       <c r="X281" s="7" t="n"/>
       <c r="Y281" s="7" t="n"/>
@@ -12031,7 +12221,7 @@
     <row r="282">
       <c r="T282" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U282" s="4" t="inlineStr">
@@ -12040,7 +12230,7 @@
         </is>
       </c>
       <c r="V282" s="4" t="n">
-        <v>2437</v>
+        <v>1935</v>
       </c>
       <c r="X282" s="4" t="n"/>
       <c r="Y282" s="4" t="n"/>
@@ -12052,7 +12242,7 @@
     <row r="283">
       <c r="T283" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U283" s="7" t="inlineStr">
@@ -12061,7 +12251,7 @@
         </is>
       </c>
       <c r="V283" s="7" t="n">
-        <v>2214</v>
+        <v>2037</v>
       </c>
       <c r="X283" s="7" t="n"/>
       <c r="Y283" s="7" t="n"/>
@@ -12073,7 +12263,7 @@
     <row r="284">
       <c r="T284" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U284" s="4" t="inlineStr">
@@ -12082,7 +12272,7 @@
         </is>
       </c>
       <c r="V284" s="4" t="n">
-        <v>2200</v>
+        <v>2049</v>
       </c>
       <c r="X284" s="4" t="n"/>
       <c r="Y284" s="4" t="n"/>
@@ -12094,7 +12284,7 @@
     <row r="285">
       <c r="T285" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U285" s="7" t="inlineStr">
@@ -12103,7 +12293,7 @@
         </is>
       </c>
       <c r="V285" s="7" t="n">
-        <v>1973</v>
+        <v>2325</v>
       </c>
       <c r="X285" s="7" t="n"/>
       <c r="Y285" s="7" t="n"/>
@@ -12115,7 +12305,7 @@
     <row r="286">
       <c r="T286" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U286" s="4" t="inlineStr">
@@ -12124,7 +12314,7 @@
         </is>
       </c>
       <c r="V286" s="4" t="n">
-        <v>1980</v>
+        <v>2216</v>
       </c>
       <c r="X286" s="4" t="n"/>
       <c r="Y286" s="4" t="n"/>
@@ -12136,7 +12326,7 @@
     <row r="287">
       <c r="T287" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U287" s="7" t="inlineStr">
@@ -12145,7 +12335,7 @@
         </is>
       </c>
       <c r="V287" s="7" t="n">
-        <v>2075</v>
+        <v>2037</v>
       </c>
       <c r="X287" s="7" t="n"/>
       <c r="Y287" s="7" t="n"/>
@@ -12153,6 +12343,237 @@
       <c r="AB287" s="7" t="n"/>
       <c r="AC287" s="7" t="n"/>
       <c r="AD287" s="7" t="n"/>
+    </row>
+    <row r="288">
+      <c r="T288" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U288" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V288" s="4" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X288" s="4" t="n"/>
+      <c r="Y288" s="4" t="n"/>
+      <c r="Z288" s="4" t="n"/>
+      <c r="AB288" s="4" t="n"/>
+      <c r="AC288" s="4" t="n"/>
+      <c r="AD288" s="4" t="n"/>
+    </row>
+    <row r="289">
+      <c r="T289" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="U289" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V289" s="7" t="n">
+        <v>2035</v>
+      </c>
+      <c r="X289" s="7" t="n"/>
+      <c r="Y289" s="7" t="n"/>
+      <c r="Z289" s="7" t="n"/>
+      <c r="AB289" s="7" t="n"/>
+      <c r="AC289" s="7" t="n"/>
+      <c r="AD289" s="7" t="n"/>
+    </row>
+    <row r="290">
+      <c r="T290" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U290" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V290" s="4" t="n">
+        <v>2182</v>
+      </c>
+      <c r="X290" s="4" t="n"/>
+      <c r="Y290" s="4" t="n"/>
+      <c r="Z290" s="4" t="n"/>
+      <c r="AB290" s="4" t="n"/>
+      <c r="AC290" s="4" t="n"/>
+      <c r="AD290" s="4" t="n"/>
+    </row>
+    <row r="291">
+      <c r="T291" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="U291" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V291" s="7" t="n">
+        <v>2156</v>
+      </c>
+      <c r="X291" s="7" t="n"/>
+      <c r="Y291" s="7" t="n"/>
+      <c r="Z291" s="7" t="n"/>
+      <c r="AB291" s="7" t="n"/>
+      <c r="AC291" s="7" t="n"/>
+      <c r="AD291" s="7" t="n"/>
+    </row>
+    <row r="292">
+      <c r="T292" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="U292" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V292" s="4" t="n">
+        <v>2437</v>
+      </c>
+      <c r="X292" s="4" t="n"/>
+      <c r="Y292" s="4" t="n"/>
+      <c r="Z292" s="4" t="n"/>
+      <c r="AB292" s="4" t="n"/>
+      <c r="AC292" s="4" t="n"/>
+      <c r="AD292" s="4" t="n"/>
+    </row>
+    <row r="293">
+      <c r="T293" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="U293" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V293" s="7" t="n">
+        <v>2214</v>
+      </c>
+      <c r="X293" s="7" t="n"/>
+      <c r="Y293" s="7" t="n"/>
+      <c r="Z293" s="7" t="n"/>
+      <c r="AB293" s="7" t="n"/>
+      <c r="AC293" s="7" t="n"/>
+      <c r="AD293" s="7" t="n"/>
+    </row>
+    <row r="294">
+      <c r="T294" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U294" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V294" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="X294" s="4" t="n"/>
+      <c r="Y294" s="4" t="n"/>
+      <c r="Z294" s="4" t="n"/>
+      <c r="AB294" s="4" t="n"/>
+      <c r="AC294" s="4" t="n"/>
+      <c r="AD294" s="4" t="n"/>
+    </row>
+    <row r="295">
+      <c r="T295" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U295" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V295" s="7" t="n">
+        <v>1973</v>
+      </c>
+      <c r="X295" s="7" t="n"/>
+      <c r="Y295" s="7" t="n"/>
+      <c r="Z295" s="7" t="n"/>
+      <c r="AB295" s="7" t="n"/>
+      <c r="AC295" s="7" t="n"/>
+      <c r="AD295" s="7" t="n"/>
+    </row>
+    <row r="296">
+      <c r="T296" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U296" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V296" s="4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="X296" s="4" t="n"/>
+      <c r="Y296" s="4" t="n"/>
+      <c r="Z296" s="4" t="n"/>
+      <c r="AB296" s="4" t="n"/>
+      <c r="AC296" s="4" t="n"/>
+      <c r="AD296" s="4" t="n"/>
+    </row>
+    <row r="297">
+      <c r="T297" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U297" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V297" s="7" t="n">
+        <v>2075</v>
+      </c>
+      <c r="X297" s="7" t="n"/>
+      <c r="Y297" s="7" t="n"/>
+      <c r="Z297" s="7" t="n"/>
+      <c r="AB297" s="7" t="n"/>
+      <c r="AC297" s="7" t="n"/>
+      <c r="AD297" s="7" t="n"/>
+    </row>
+    <row r="298">
+      <c r="T298" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="U298" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V298" s="4" t="n">
+        <v>2191</v>
+      </c>
+      <c r="X298" s="4" t="n"/>
+      <c r="Y298" s="4" t="n"/>
+      <c r="Z298" s="4" t="n"/>
+      <c r="AB298" s="4" t="n"/>
+      <c r="AC298" s="4" t="n"/>
+      <c r="AD298" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -716,10 +716,10 @@
         <v>0.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -752,10 +752,10 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -788,10 +788,10 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -824,10 +824,10 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -860,10 +860,10 @@
         <v>0.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -896,10 +896,10 @@
         <v>0.95</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -932,10 +932,10 @@
         <v>0.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -968,10 +968,10 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1004,10 +1004,10 @@
         <v>0.95</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1040,10 +1040,10 @@
         <v>0.95</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD298"/>
+  <dimension ref="A1:AD209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1344,15 +1344,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>103</v>
       </c>
@@ -1429,15 +1423,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>13</v>
       </c>
@@ -1514,15 +1502,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>64</v>
       </c>
@@ -1593,15 +1575,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>30</v>
       </c>
@@ -1678,15 +1654,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>21</v>
       </c>
@@ -1763,15 +1733,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>73</v>
       </c>
@@ -1848,15 +1812,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>15</v>
       </c>
@@ -1927,15 +1885,9 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>1</v>
       </c>
@@ -2014,15 +1966,9 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>105</v>
       </c>
@@ -2093,15 +2039,9 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>19</v>
       </c>
@@ -2172,15 +2112,9 @@
         <f>$B$2+H12+M12</f>
         <v/>
       </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>82</v>
       </c>
@@ -2251,15 +2185,9 @@
         <f>$B$2+H13+M13</f>
         <v/>
       </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>25</v>
       </c>
@@ -2330,15 +2258,9 @@
         <f>$B$2+H14+M14</f>
         <v/>
       </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>15</v>
       </c>
@@ -2409,15 +2331,9 @@
         <f>$B$2+H15+M15</f>
         <v/>
       </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>75</v>
       </c>
@@ -2488,15 +2404,9 @@
         <f>$B$2+H16+M16</f>
         <v/>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>9</v>
       </c>
@@ -2567,15 +2477,9 @@
         <f>$B$2+H17+M17</f>
         <v/>
       </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>1</v>
       </c>
@@ -2646,15 +2550,9 @@
         <f>$B$2+H18+M18</f>
         <v/>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>145</v>
       </c>
@@ -2725,15 +2623,9 @@
         <f>$B$2+H19+M19</f>
         <v/>
       </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>19</v>
       </c>
@@ -2804,15 +2696,9 @@
         <f>$B$2+H20+M20</f>
         <v/>
       </c>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>74</v>
       </c>
@@ -2883,15 +2769,9 @@
         <f>$B$2+H21+M21</f>
         <v/>
       </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr"/>
-      <c r="V21" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>26</v>
       </c>
@@ -2962,15 +2842,9 @@
         <f>$B$2+H22+M22</f>
         <v/>
       </c>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>9</v>
       </c>
@@ -3041,15 +2915,9 @@
         <f>$B$2+H23+M23</f>
         <v/>
       </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr"/>
-      <c r="V23" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
         <v>74</v>
       </c>
@@ -3120,15 +2988,9 @@
         <f>$B$2+H24+M24</f>
         <v/>
       </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
         <v>11</v>
       </c>
@@ -3175,19 +3037,9 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>5365</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>101</v>
       </c>
@@ -3234,19 +3086,9 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>5741</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
         <v>11</v>
       </c>
@@ -3293,19 +3135,9 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>5451</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
         <v>73</v>
       </c>
@@ -3352,19 +3184,9 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>5458</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
         <v>31</v>
       </c>
@@ -3411,19 +3233,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>5664</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>13</v>
       </c>
@@ -3470,19 +3282,9 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>5241</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
         <v>78</v>
       </c>
@@ -3529,19 +3331,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>5102</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
@@ -3597,19 +3389,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>5388</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>9</v>
       </c>
@@ -3670,19 +3452,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
@@ -3711,19 +3483,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>5348</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>119</v>
       </c>
@@ -3752,19 +3514,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>5329</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>13</v>
       </c>
@@ -3793,19 +3545,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>5436</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>67</v>
       </c>
@@ -3834,19 +3576,9 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>5081</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
         <v>32</v>
       </c>
@@ -3875,19 +3607,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>5034</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
         <v>13</v>
       </c>
@@ -3916,19 +3638,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>93</v>
       </c>
@@ -3957,19 +3669,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>5513</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>12</v>
       </c>
@@ -3998,19 +3700,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>5477</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>2</v>
       </c>
@@ -4039,19 +3731,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>5526</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>113</v>
       </c>
@@ -4080,19 +3762,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>12</v>
       </c>
@@ -4121,19 +3793,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>4933</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>69</v>
       </c>
@@ -4162,19 +3824,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>4866</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>40</v>
       </c>
@@ -4203,19 +3855,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>5232</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>17</v>
       </c>
@@ -4244,19 +3886,9 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>5576</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>83</v>
       </c>
@@ -4285,19 +3917,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>14969</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>9</v>
       </c>
@@ -4326,19 +3948,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>14818</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>124</v>
       </c>
@@ -4367,19 +3979,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>15263</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>19</v>
       </c>
@@ -4408,19 +4010,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>55</v>
       </c>
@@ -4449,19 +4041,9 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>14968</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
         <v>35</v>
       </c>
@@ -4490,19 +4072,9 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>14113</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>15</v>
       </c>
@@ -4531,19 +4103,9 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>14162</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>82</v>
       </c>
@@ -4572,19 +4134,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>1</v>
       </c>
@@ -4613,19 +4165,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>14</v>
       </c>
@@ -4654,19 +4196,9 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>15546</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>2</v>
       </c>
@@ -4695,19 +4227,9 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>14882</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
         <v>101</v>
       </c>
@@ -4736,19 +4258,9 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>14998</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
         <v>10</v>
       </c>
@@ -4777,19 +4289,9 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>14354</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
         <v>72</v>
       </c>
@@ -4818,19 +4320,9 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>14362</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
         <v>35</v>
       </c>
@@ -4859,19 +4351,9 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>15089</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
         <v>13</v>
       </c>
@@ -4900,19 +4382,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>14802</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>71</v>
       </c>
@@ -4941,19 +4413,9 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>15349</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
         <v>8</v>
       </c>
@@ -4982,19 +4444,9 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>14872</v>
-      </c>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
         <v>2</v>
       </c>
@@ -5023,19 +4475,9 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>15054</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>125</v>
       </c>
@@ -5064,19 +4506,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>14169</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>11</v>
       </c>
@@ -5105,19 +4537,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>14056</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>67</v>
       </c>
@@ -5146,19 +4568,9 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>15058</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>27</v>
       </c>
@@ -5187,19 +4599,9 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>14814</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
         <v>17</v>
       </c>
@@ -5228,19 +4630,9 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>77546</v>
-      </c>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
         <v>85</v>
       </c>
@@ -5269,19 +4661,9 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>77823</v>
-      </c>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
         <v>14</v>
       </c>
@@ -5310,19 +4692,9 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>81723</v>
-      </c>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
         <v>4</v>
       </c>
@@ -5351,19 +4723,9 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>78398</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
         <v>126</v>
       </c>
@@ -5392,19 +4754,9 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>78030</v>
-      </c>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
         <v>23</v>
       </c>
@@ -5433,19 +4785,9 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>76646</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>65</v>
       </c>
@@ -5474,19 +4816,9 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>76742</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
         <v>28</v>
       </c>
@@ -5515,19 +4847,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>79003</v>
-      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
         <v>19</v>
       </c>
@@ -5556,19 +4878,9 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>78849</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>91</v>
       </c>
@@ -5597,19 +4909,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>80667</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>21</v>
       </c>
@@ -5638,19 +4940,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>78640</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
         <v>2</v>
       </c>
@@ -5679,19 +4971,9 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>79108</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
         <v>99</v>
       </c>
@@ -5720,19 +5002,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>76911</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>12</v>
       </c>
@@ -5761,19 +5033,9 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>77273</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
         <v>70</v>
       </c>
@@ -5802,19 +5064,9 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>80657</v>
-      </c>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
         <v>30</v>
       </c>
@@ -5843,19 +5095,9 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>79898</v>
-      </c>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
         <v>15</v>
       </c>
@@ -5884,19 +5126,9 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>82443</v>
-      </c>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
         <v>73</v>
       </c>
@@ -5925,19 +5157,9 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>80658</v>
-      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
         <v>5</v>
       </c>
@@ -5966,19 +5188,9 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>78475</v>
-      </c>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
         <v>1</v>
       </c>
@@ -6007,19 +5219,9 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>76874</v>
-      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
         <v>107</v>
       </c>
@@ -6048,19 +5250,9 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>77058</v>
-      </c>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
         <v>13</v>
       </c>
@@ -6089,19 +5281,9 @@
       </c>
     </row>
     <row r="92">
-      <c r="T92" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V92" s="4" t="n">
-        <v>79206</v>
-      </c>
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
       <c r="X92" s="4" t="n">
         <v>56</v>
       </c>
@@ -6130,19 +5312,9 @@
       </c>
     </row>
     <row r="93">
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U93" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>79070</v>
-      </c>
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
         <v>32</v>
       </c>
@@ -6171,19 +5343,9 @@
       </c>
     </row>
     <row r="94">
-      <c r="T94" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
         <v>13</v>
       </c>
@@ -6212,19 +5374,9 @@
       </c>
     </row>
     <row r="95">
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>715</v>
-      </c>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
         <v>78</v>
       </c>
@@ -6253,19 +5405,9 @@
       </c>
     </row>
     <row r="96">
-      <c r="T96" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V96" s="4" t="n">
-        <v>745</v>
-      </c>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
       <c r="X96" s="4" t="n">
         <v>10</v>
       </c>
@@ -6294,19 +5436,9 @@
       </c>
     </row>
     <row r="97">
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V97" s="7" t="n">
-        <v>702</v>
-      </c>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
         <v>1</v>
       </c>
@@ -6335,19 +5467,9 @@
       </c>
     </row>
     <row r="98">
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>743</v>
-      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
         <v>114</v>
       </c>
@@ -6376,19 +5498,9 @@
       </c>
     </row>
     <row r="99">
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V99" s="7" t="n">
-        <v>700</v>
-      </c>
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
         <v>15</v>
       </c>
@@ -6417,19 +5529,9 @@
       </c>
     </row>
     <row r="100">
-      <c r="T100" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
         <v>53</v>
       </c>
@@ -6458,19 +5560,9 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U101" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V101" s="7" t="n">
-        <v>750</v>
-      </c>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
         <v>32</v>
       </c>
@@ -6499,19 +5591,9 @@
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n">
-        <v>729</v>
-      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
         <v>14</v>
       </c>
@@ -6540,19 +5622,9 @@
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V103" s="7" t="n">
-        <v>748</v>
-      </c>
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
         <v>80</v>
       </c>
@@ -6581,19 +5653,9 @@
       </c>
     </row>
     <row r="104">
-      <c r="T104" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U104" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V104" s="4" t="n">
-        <v>736</v>
-      </c>
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="4" t="n"/>
+      <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
         <v>1</v>
       </c>
@@ -6622,19 +5684,9 @@
       </c>
     </row>
     <row r="105">
-      <c r="T105" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U105" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>737</v>
-      </c>
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
         <v>9</v>
       </c>
@@ -6663,19 +5715,9 @@
       </c>
     </row>
     <row r="106">
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="n">
-        <v>707</v>
-      </c>
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="4" t="n"/>
+      <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
         <v>4</v>
       </c>
@@ -6704,19 +5746,9 @@
       </c>
     </row>
     <row r="107">
-      <c r="T107" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U107" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V107" s="7" t="n">
-        <v>713</v>
-      </c>
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
         <v>97</v>
       </c>
@@ -6745,19 +5777,9 @@
       </c>
     </row>
     <row r="108">
-      <c r="T108" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U108" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V108" s="4" t="n">
-        <v>786</v>
-      </c>
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="4" t="n"/>
+      <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
         <v>10</v>
       </c>
@@ -6786,19 +5808,9 @@
       </c>
     </row>
     <row r="109">
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U109" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V109" s="7" t="n">
-        <v>730</v>
-      </c>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
         <v>52</v>
       </c>
@@ -6827,19 +5839,9 @@
       </c>
     </row>
     <row r="110">
-      <c r="T110" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U110" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V110" s="4" t="n">
-        <v>726</v>
-      </c>
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="n"/>
       <c r="X110" s="4" t="n">
         <v>37</v>
       </c>
@@ -6868,19 +5870,9 @@
       </c>
     </row>
     <row r="111">
-      <c r="T111" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U111" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V111" s="7" t="n">
-        <v>695</v>
-      </c>
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
       <c r="X111" s="7" t="n">
         <v>18</v>
       </c>
@@ -6909,19 +5901,9 @@
       </c>
     </row>
     <row r="112">
-      <c r="T112" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U112" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V112" s="4" t="n">
-        <v>693</v>
-      </c>
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="4" t="n"/>
+      <c r="V112" s="4" t="n"/>
       <c r="X112" s="4" t="n">
         <v>64</v>
       </c>
@@ -6950,19 +5932,9 @@
       </c>
     </row>
     <row r="113">
-      <c r="T113" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U113" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V113" s="7" t="n">
-        <v>686</v>
-      </c>
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
         <v>7</v>
       </c>
@@ -6991,19 +5963,9 @@
       </c>
     </row>
     <row r="114">
-      <c r="T114" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U114" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V114" s="4" t="n">
-        <v>673</v>
-      </c>
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="n"/>
       <c r="X114" s="4" t="n">
         <v>106</v>
       </c>
@@ -7032,19 +5994,9 @@
       </c>
     </row>
     <row r="115">
-      <c r="T115" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U115" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V115" s="7" t="n">
-        <v>752</v>
-      </c>
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
       <c r="X115" s="7" t="n">
         <v>14</v>
       </c>
@@ -7073,19 +6025,9 @@
       </c>
     </row>
     <row r="116">
-      <c r="T116" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U116" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V116" s="4" t="n">
-        <v>717</v>
-      </c>
+      <c r="T116" s="4" t="n"/>
+      <c r="U116" s="4" t="n"/>
+      <c r="V116" s="4" t="n"/>
       <c r="X116" s="4" t="n">
         <v>65</v>
       </c>
@@ -7114,19 +6056,9 @@
       </c>
     </row>
     <row r="117">
-      <c r="T117" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U117" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V117" s="7" t="n">
-        <v>47976</v>
-      </c>
+      <c r="T117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
       <c r="X117" s="7" t="n">
         <v>24</v>
       </c>
@@ -7155,19 +6087,9 @@
       </c>
     </row>
     <row r="118">
-      <c r="T118" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U118" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V118" s="4" t="n">
-        <v>47122</v>
-      </c>
+      <c r="T118" s="4" t="n"/>
+      <c r="U118" s="4" t="n"/>
+      <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
         <v>14</v>
       </c>
@@ -7196,19 +6118,9 @@
       </c>
     </row>
     <row r="119">
-      <c r="T119" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U119" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V119" s="7" t="n">
-        <v>47233</v>
-      </c>
+      <c r="T119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
         <v>66</v>
       </c>
@@ -7237,19 +6149,9 @@
       </c>
     </row>
     <row r="120">
-      <c r="T120" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U120" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="n">
-        <v>48580</v>
-      </c>
+      <c r="T120" s="4" t="n"/>
+      <c r="U120" s="4" t="n"/>
+      <c r="V120" s="4" t="n"/>
       <c r="X120" s="4" t="n">
         <v>1</v>
       </c>
@@ -7278,19 +6180,9 @@
       </c>
     </row>
     <row r="121">
-      <c r="T121" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U121" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>47383</v>
-      </c>
+      <c r="T121" s="7" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
       <c r="X121" s="7" t="n">
         <v>9</v>
       </c>
@@ -7319,19 +6211,9 @@
       </c>
     </row>
     <row r="122">
-      <c r="T122" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U122" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V122" s="4" t="n">
-        <v>46456</v>
-      </c>
+      <c r="T122" s="4" t="n"/>
+      <c r="U122" s="4" t="n"/>
+      <c r="V122" s="4" t="n"/>
       <c r="X122" s="4" t="n">
         <v>116</v>
       </c>
@@ -7360,19 +6242,9 @@
       </c>
     </row>
     <row r="123">
-      <c r="T123" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U123" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V123" s="7" t="n">
-        <v>46400</v>
-      </c>
+      <c r="T123" s="7" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
       <c r="X123" s="7" t="n">
         <v>17</v>
       </c>
@@ -7401,19 +6273,9 @@
       </c>
     </row>
     <row r="124">
-      <c r="T124" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U124" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="n">
-        <v>47755</v>
-      </c>
+      <c r="T124" s="4" t="n"/>
+      <c r="U124" s="4" t="n"/>
+      <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
         <v>52</v>
       </c>
@@ -7442,19 +6304,9 @@
       </c>
     </row>
     <row r="125">
-      <c r="T125" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V125" s="7" t="n">
-        <v>47520</v>
-      </c>
+      <c r="T125" s="7" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
         <v>38</v>
       </c>
@@ -7483,19 +6335,9 @@
       </c>
     </row>
     <row r="126">
-      <c r="T126" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U126" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V126" s="4" t="n">
-        <v>47354</v>
-      </c>
+      <c r="T126" s="4" t="n"/>
+      <c r="U126" s="4" t="n"/>
+      <c r="V126" s="4" t="n"/>
       <c r="X126" s="4" t="n">
         <v>19</v>
       </c>
@@ -7524,19 +6366,9 @@
       </c>
     </row>
     <row r="127">
-      <c r="T127" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U127" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V127" s="7" t="n">
-        <v>49015</v>
-      </c>
+      <c r="T127" s="7" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
       <c r="X127" s="7" t="n">
         <v>79</v>
       </c>
@@ -7565,19 +6397,9 @@
       </c>
     </row>
     <row r="128">
-      <c r="T128" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U128" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V128" s="4" t="n">
-        <v>48832</v>
-      </c>
+      <c r="T128" s="4" t="n"/>
+      <c r="U128" s="4" t="n"/>
+      <c r="V128" s="4" t="n"/>
       <c r="X128" s="4" t="n">
         <v>9</v>
       </c>
@@ -7606,19 +6428,9 @@
       </c>
     </row>
     <row r="129">
-      <c r="T129" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U129" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V129" s="7" t="n">
-        <v>46644</v>
-      </c>
+      <c r="T129" s="7" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
       <c r="X129" s="7" t="n">
         <v>1</v>
       </c>
@@ -7647,19 +6459,9 @@
       </c>
     </row>
     <row r="130">
-      <c r="T130" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U130" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V130" s="4" t="n">
-        <v>46416</v>
-      </c>
+      <c r="T130" s="4" t="n"/>
+      <c r="U130" s="4" t="n"/>
+      <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
         <v>134</v>
       </c>
@@ -7688,19 +6490,9 @@
       </c>
     </row>
     <row r="131">
-      <c r="T131" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U131" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V131" s="7" t="n">
-        <v>48419</v>
-      </c>
+      <c r="T131" s="7" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
         <v>22</v>
       </c>
@@ -7729,19 +6521,9 @@
       </c>
     </row>
     <row r="132">
-      <c r="T132" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U132" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V132" s="4" t="n">
-        <v>47500</v>
-      </c>
+      <c r="T132" s="4" t="n"/>
+      <c r="U132" s="4" t="n"/>
+      <c r="V132" s="4" t="n"/>
       <c r="X132" s="4" t="n">
         <v>65</v>
       </c>
@@ -7770,19 +6552,9 @@
       </c>
     </row>
     <row r="133">
-      <c r="T133" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U133" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V133" s="7" t="n">
-        <v>47954</v>
-      </c>
+      <c r="T133" s="7" t="n"/>
+      <c r="U133" s="7" t="n"/>
+      <c r="V133" s="7" t="n"/>
       <c r="X133" s="7" t="n">
         <v>29</v>
       </c>
@@ -7811,19 +6583,9 @@
       </c>
     </row>
     <row r="134">
-      <c r="T134" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U134" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V134" s="4" t="n">
-        <v>49088</v>
-      </c>
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="4" t="n"/>
+      <c r="V134" s="4" t="n"/>
       <c r="X134" s="4" t="n">
         <v>12</v>
       </c>
@@ -7852,19 +6614,9 @@
       </c>
     </row>
     <row r="135">
-      <c r="T135" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U135" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V135" s="7" t="n">
-        <v>48111</v>
-      </c>
+      <c r="T135" s="7" t="n"/>
+      <c r="U135" s="7" t="n"/>
+      <c r="V135" s="7" t="n"/>
       <c r="X135" s="7" t="n">
         <v>82</v>
       </c>
@@ -7893,19 +6645,9 @@
       </c>
     </row>
     <row r="136">
-      <c r="T136" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U136" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V136" s="4" t="n">
-        <v>46535</v>
-      </c>
+      <c r="T136" s="4" t="n"/>
+      <c r="U136" s="4" t="n"/>
+      <c r="V136" s="4" t="n"/>
       <c r="X136" s="4" t="n">
         <v>1</v>
       </c>
@@ -7934,19 +6676,9 @@
       </c>
     </row>
     <row r="137">
-      <c r="T137" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U137" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V137" s="7" t="n">
-        <v>46063</v>
-      </c>
+      <c r="T137" s="7" t="n"/>
+      <c r="U137" s="7" t="n"/>
+      <c r="V137" s="7" t="n"/>
       <c r="X137" s="7" t="n">
         <v>7</v>
       </c>
@@ -7975,19 +6707,9 @@
       </c>
     </row>
     <row r="138">
-      <c r="T138" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U138" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V138" s="4" t="n">
-        <v>48085</v>
-      </c>
+      <c r="T138" s="4" t="n"/>
+      <c r="U138" s="4" t="n"/>
+      <c r="V138" s="4" t="n"/>
       <c r="X138" s="4" t="n">
         <v>1</v>
       </c>
@@ -8016,19 +6738,9 @@
       </c>
     </row>
     <row r="139">
-      <c r="T139" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U139" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V139" s="7" t="n">
-        <v>47472</v>
-      </c>
+      <c r="T139" s="7" t="n"/>
+      <c r="U139" s="7" t="n"/>
+      <c r="V139" s="7" t="n"/>
       <c r="X139" s="7" t="n">
         <v>107</v>
       </c>
@@ -8057,19 +6769,9 @@
       </c>
     </row>
     <row r="140">
-      <c r="T140" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U140" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V140" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T140" s="4" t="n"/>
+      <c r="U140" s="4" t="n"/>
+      <c r="V140" s="4" t="n"/>
       <c r="X140" s="4" t="n">
         <v>24</v>
       </c>
@@ -8098,19 +6800,9 @@
       </c>
     </row>
     <row r="141">
-      <c r="T141" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U141" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V141" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T141" s="7" t="n"/>
+      <c r="U141" s="7" t="n"/>
+      <c r="V141" s="7" t="n"/>
       <c r="X141" s="7" t="n">
         <v>68</v>
       </c>
@@ -8139,19 +6831,9 @@
       </c>
     </row>
     <row r="142">
-      <c r="T142" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U142" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V142" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T142" s="4" t="n"/>
+      <c r="U142" s="4" t="n"/>
+      <c r="V142" s="4" t="n"/>
       <c r="X142" s="4" t="n">
         <v>18</v>
       </c>
@@ -8180,19 +6862,9 @@
       </c>
     </row>
     <row r="143">
-      <c r="T143" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U143" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V143" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T143" s="7" t="n"/>
+      <c r="U143" s="7" t="n"/>
+      <c r="V143" s="7" t="n"/>
       <c r="X143" s="7" t="n">
         <v>12</v>
       </c>
@@ -8221,19 +6893,9 @@
       </c>
     </row>
     <row r="144">
-      <c r="T144" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U144" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V144" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T144" s="4" t="n"/>
+      <c r="U144" s="4" t="n"/>
+      <c r="V144" s="4" t="n"/>
       <c r="X144" s="4" t="n">
         <v>70</v>
       </c>
@@ -8262,19 +6924,9 @@
       </c>
     </row>
     <row r="145">
-      <c r="T145" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U145" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V145" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T145" s="7" t="n"/>
+      <c r="U145" s="7" t="n"/>
+      <c r="V145" s="7" t="n"/>
       <c r="X145" s="7" t="n">
         <v>2</v>
       </c>
@@ -8303,19 +6955,9 @@
       </c>
     </row>
     <row r="146">
-      <c r="T146" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U146" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V146" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
       <c r="X146" s="4" t="n">
         <v>6</v>
       </c>
@@ -8344,19 +6986,9 @@
       </c>
     </row>
     <row r="147">
-      <c r="T147" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U147" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V147" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T147" s="7" t="n"/>
+      <c r="U147" s="7" t="n"/>
+      <c r="V147" s="7" t="n"/>
       <c r="X147" s="7" t="n">
         <v>2</v>
       </c>
@@ -8385,19 +7017,9 @@
       </c>
     </row>
     <row r="148">
-      <c r="T148" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U148" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V148" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T148" s="4" t="n"/>
+      <c r="U148" s="4" t="n"/>
+      <c r="V148" s="4" t="n"/>
       <c r="X148" s="4" t="n">
         <v>115</v>
       </c>
@@ -8426,19 +7048,9 @@
       </c>
     </row>
     <row r="149">
-      <c r="T149" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U149" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V149" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T149" s="7" t="n"/>
+      <c r="U149" s="7" t="n"/>
+      <c r="V149" s="7" t="n"/>
       <c r="X149" s="7" t="n">
         <v>20</v>
       </c>
@@ -8467,19 +7079,9 @@
       </c>
     </row>
     <row r="150">
-      <c r="T150" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U150" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="4" t="n"/>
+      <c r="V150" s="4" t="n"/>
       <c r="X150" s="4" t="n">
         <v>69</v>
       </c>
@@ -8508,19 +7110,9 @@
       </c>
     </row>
     <row r="151">
-      <c r="T151" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V151" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T151" s="7" t="n"/>
+      <c r="U151" s="7" t="n"/>
+      <c r="V151" s="7" t="n"/>
       <c r="X151" s="7" t="n">
         <v>41</v>
       </c>
@@ -8549,19 +7141,9 @@
       </c>
     </row>
     <row r="152">
-      <c r="T152" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U152" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="4" t="n"/>
+      <c r="V152" s="4" t="n"/>
       <c r="X152" s="4" t="n">
         <v>5</v>
       </c>
@@ -8590,19 +7172,9 @@
       </c>
     </row>
     <row r="153">
-      <c r="T153" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U153" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V153" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T153" s="7" t="n"/>
+      <c r="U153" s="7" t="n"/>
+      <c r="V153" s="7" t="n"/>
       <c r="X153" s="7" t="n">
         <v>95</v>
       </c>
@@ -8631,19 +7203,9 @@
       </c>
     </row>
     <row r="154">
-      <c r="T154" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U154" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T154" s="4" t="n"/>
+      <c r="U154" s="4" t="n"/>
+      <c r="V154" s="4" t="n"/>
       <c r="X154" s="4" t="n">
         <v>1</v>
       </c>
@@ -8672,19 +7234,9 @@
       </c>
     </row>
     <row r="155">
-      <c r="T155" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V155" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T155" s="7" t="n"/>
+      <c r="U155" s="7" t="n"/>
+      <c r="V155" s="7" t="n"/>
       <c r="X155" s="7" t="n">
         <v>9</v>
       </c>
@@ -8713,19 +7265,9 @@
       </c>
     </row>
     <row r="156">
-      <c r="T156" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U156" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="4" t="n"/>
+      <c r="V156" s="4" t="n"/>
       <c r="X156" s="4" t="n">
         <v>2</v>
       </c>
@@ -8754,19 +7296,9 @@
       </c>
     </row>
     <row r="157">
-      <c r="T157" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U157" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V157" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T157" s="7" t="n"/>
+      <c r="U157" s="7" t="n"/>
+      <c r="V157" s="7" t="n"/>
       <c r="X157" s="7" t="n">
         <v>114</v>
       </c>
@@ -8795,19 +7327,9 @@
       </c>
     </row>
     <row r="158">
-      <c r="T158" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U158" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V158" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T158" s="4" t="n"/>
+      <c r="U158" s="4" t="n"/>
+      <c r="V158" s="4" t="n"/>
       <c r="X158" s="4" t="n">
         <v>16</v>
       </c>
@@ -8836,19 +7358,9 @@
       </c>
     </row>
     <row r="159">
-      <c r="T159" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U159" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V159" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T159" s="7" t="n"/>
+      <c r="U159" s="7" t="n"/>
+      <c r="V159" s="7" t="n"/>
       <c r="X159" s="7" t="n">
         <v>60</v>
       </c>
@@ -8877,19 +7389,9 @@
       </c>
     </row>
     <row r="160">
-      <c r="T160" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U160" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="4" t="n"/>
+      <c r="V160" s="4" t="n"/>
       <c r="X160" s="4" t="n">
         <v>41</v>
       </c>
@@ -8918,19 +7420,9 @@
       </c>
     </row>
     <row r="161">
-      <c r="T161" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U161" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V161" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T161" s="7" t="n"/>
+      <c r="U161" s="7" t="n"/>
+      <c r="V161" s="7" t="n"/>
       <c r="X161" s="7" t="n">
         <v>14</v>
       </c>
@@ -8959,19 +7451,9 @@
       </c>
     </row>
     <row r="162">
-      <c r="T162" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U162" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V162" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="4" t="n"/>
+      <c r="V162" s="4" t="n"/>
       <c r="X162" s="4" t="n">
         <v>84</v>
       </c>
@@ -9000,19 +7482,9 @@
       </c>
     </row>
     <row r="163">
-      <c r="T163" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U163" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V163" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T163" s="7" t="n"/>
+      <c r="U163" s="7" t="n"/>
+      <c r="V163" s="7" t="n"/>
       <c r="X163" s="7" t="n">
         <v>8</v>
       </c>
@@ -9041,19 +7513,9 @@
       </c>
     </row>
     <row r="164">
-      <c r="T164" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U164" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V164" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="4" t="n"/>
+      <c r="V164" s="4" t="n"/>
       <c r="X164" s="4" t="n">
         <v>1</v>
       </c>
@@ -9082,19 +7544,9 @@
       </c>
     </row>
     <row r="165">
-      <c r="T165" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U165" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V165" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T165" s="7" t="n"/>
+      <c r="U165" s="7" t="n"/>
+      <c r="V165" s="7" t="n"/>
       <c r="X165" s="7" t="n">
         <v>144</v>
       </c>
@@ -9123,19 +7575,9 @@
       </c>
     </row>
     <row r="166">
-      <c r="T166" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U166" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V166" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="4" t="n"/>
+      <c r="V166" s="4" t="n"/>
       <c r="X166" s="4" t="n">
         <v>16</v>
       </c>
@@ -9164,19 +7606,9 @@
       </c>
     </row>
     <row r="167">
-      <c r="T167" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U167" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V167" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T167" s="7" t="n"/>
+      <c r="U167" s="7" t="n"/>
+      <c r="V167" s="7" t="n"/>
       <c r="X167" s="7" t="n">
         <v>66</v>
       </c>
@@ -9205,19 +7637,9 @@
       </c>
     </row>
     <row r="168">
-      <c r="T168" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U168" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V168" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="4" t="n"/>
+      <c r="V168" s="4" t="n"/>
       <c r="X168" s="4" t="n">
         <v>35</v>
       </c>
@@ -9246,19 +7668,9 @@
       </c>
     </row>
     <row r="169">
-      <c r="T169" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U169" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V169" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T169" s="7" t="n"/>
+      <c r="U169" s="7" t="n"/>
+      <c r="V169" s="7" t="n"/>
       <c r="X169" s="7" t="n">
         <v>15</v>
       </c>
@@ -9287,19 +7699,9 @@
       </c>
     </row>
     <row r="170">
-      <c r="T170" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U170" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V170" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="4" t="n"/>
+      <c r="V170" s="4" t="n"/>
       <c r="X170" s="4" t="n">
         <v>83</v>
       </c>
@@ -9328,19 +7730,9 @@
       </c>
     </row>
     <row r="171">
-      <c r="T171" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U171" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V171" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T171" s="7" t="n"/>
+      <c r="U171" s="7" t="n"/>
+      <c r="V171" s="7" t="n"/>
       <c r="X171" s="7" t="n">
         <v>6</v>
       </c>
@@ -9369,19 +7761,9 @@
       </c>
     </row>
     <row r="172">
-      <c r="T172" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U172" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V172" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="4" t="n"/>
+      <c r="V172" s="4" t="n"/>
       <c r="X172" s="4" t="n">
         <v>104</v>
       </c>
@@ -9410,19 +7792,9 @@
       </c>
     </row>
     <row r="173">
-      <c r="T173" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U173" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V173" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T173" s="7" t="n"/>
+      <c r="U173" s="7" t="n"/>
+      <c r="V173" s="7" t="n"/>
       <c r="X173" s="7" t="n">
         <v>17</v>
       </c>
@@ -9451,19 +7823,9 @@
       </c>
     </row>
     <row r="174">
-      <c r="T174" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U174" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V174" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="n"/>
+      <c r="V174" s="4" t="n"/>
       <c r="X174" s="4" t="n">
         <v>72</v>
       </c>
@@ -9492,19 +7854,9 @@
       </c>
     </row>
     <row r="175">
-      <c r="T175" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U175" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V175" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T175" s="7" t="n"/>
+      <c r="U175" s="7" t="n"/>
+      <c r="V175" s="7" t="n"/>
       <c r="X175" s="7" t="n">
         <v>43</v>
       </c>
@@ -9533,19 +7885,9 @@
       </c>
     </row>
     <row r="176">
-      <c r="T176" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U176" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V176" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="4" t="n"/>
+      <c r="V176" s="4" t="n"/>
       <c r="X176" s="4" t="n">
         <v>20</v>
       </c>
@@ -9574,19 +7916,9 @@
       </c>
     </row>
     <row r="177">
-      <c r="T177" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U177" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V177" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T177" s="7" t="n"/>
+      <c r="U177" s="7" t="n"/>
+      <c r="V177" s="7" t="n"/>
       <c r="X177" s="7" t="n">
         <v>134</v>
       </c>
@@ -9615,19 +7947,9 @@
       </c>
     </row>
     <row r="178">
-      <c r="T178" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U178" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V178" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T178" s="4" t="n"/>
+      <c r="U178" s="4" t="n"/>
+      <c r="V178" s="4" t="n"/>
       <c r="X178" s="4" t="n">
         <v>7</v>
       </c>
@@ -9656,19 +7978,9 @@
       </c>
     </row>
     <row r="179">
-      <c r="T179" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U179" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V179" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T179" s="7" t="n"/>
+      <c r="U179" s="7" t="n"/>
+      <c r="V179" s="7" t="n"/>
       <c r="X179" s="7" t="n">
         <v>2</v>
       </c>
@@ -9697,21 +8009,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="T180" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U180" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V180" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T180" s="4" t="n"/>
+      <c r="U180" s="4" t="n"/>
+      <c r="V180" s="4" t="n"/>
       <c r="X180" s="4" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y180" s="4" t="inlineStr">
         <is>
@@ -9738,19 +8040,9 @@
       </c>
     </row>
     <row r="181">
-      <c r="T181" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U181" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V181" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T181" s="7" t="n"/>
+      <c r="U181" s="7" t="n"/>
+      <c r="V181" s="7" t="n"/>
       <c r="X181" s="7" t="n">
         <v>17</v>
       </c>
@@ -9779,19 +8071,9 @@
       </c>
     </row>
     <row r="182">
-      <c r="T182" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U182" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V182" s="4" t="n">
-        <v>9927</v>
-      </c>
+      <c r="T182" s="4" t="n"/>
+      <c r="U182" s="4" t="n"/>
+      <c r="V182" s="4" t="n"/>
       <c r="X182" s="4" t="n">
         <v>66</v>
       </c>
@@ -9820,19 +8102,9 @@
       </c>
     </row>
     <row r="183">
-      <c r="T183" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U183" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V183" s="7" t="n">
-        <v>9839</v>
-      </c>
+      <c r="T183" s="7" t="n"/>
+      <c r="U183" s="7" t="n"/>
+      <c r="V183" s="7" t="n"/>
       <c r="X183" s="7" t="n">
         <v>29</v>
       </c>
@@ -9861,21 +8133,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="T184" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U184" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V184" s="4" t="n">
-        <v>9918</v>
-      </c>
+      <c r="T184" s="4" t="n"/>
+      <c r="U184" s="4" t="n"/>
+      <c r="V184" s="4" t="n"/>
       <c r="X184" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y184" s="4" t="inlineStr">
         <is>
@@ -9902,19 +8164,9 @@
       </c>
     </row>
     <row r="185">
-      <c r="T185" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U185" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V185" s="7" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T185" s="7" t="n"/>
+      <c r="U185" s="7" t="n"/>
+      <c r="V185" s="7" t="n"/>
       <c r="X185" s="7" t="n">
         <v>134</v>
       </c>
@@ -9943,19 +8195,9 @@
       </c>
     </row>
     <row r="186">
-      <c r="T186" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U186" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V186" s="4" t="n">
-        <v>10050</v>
-      </c>
+      <c r="T186" s="4" t="n"/>
+      <c r="U186" s="4" t="n"/>
+      <c r="V186" s="4" t="n"/>
       <c r="X186" s="4" t="n">
         <v>9</v>
       </c>
@@ -9984,19 +8226,9 @@
       </c>
     </row>
     <row r="187">
-      <c r="T187" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U187" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V187" s="7" t="n">
-        <v>9768</v>
-      </c>
+      <c r="T187" s="7" t="n"/>
+      <c r="U187" s="7" t="n"/>
+      <c r="V187" s="7" t="n"/>
       <c r="X187" s="7" t="n">
         <v>1</v>
       </c>
@@ -10025,19 +8257,9 @@
       </c>
     </row>
     <row r="188">
-      <c r="T188" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U188" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V188" s="4" t="n">
-        <v>9920</v>
-      </c>
+      <c r="T188" s="4" t="n"/>
+      <c r="U188" s="4" t="n"/>
+      <c r="V188" s="4" t="n"/>
       <c r="X188" s="4" t="n"/>
       <c r="Y188" s="4" t="n"/>
       <c r="Z188" s="4" t="n"/>
@@ -10056,19 +8278,9 @@
       </c>
     </row>
     <row r="189">
-      <c r="T189" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U189" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V189" s="7" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T189" s="7" t="n"/>
+      <c r="U189" s="7" t="n"/>
+      <c r="V189" s="7" t="n"/>
       <c r="X189" s="7" t="n"/>
       <c r="Y189" s="7" t="n"/>
       <c r="Z189" s="7" t="n"/>
@@ -10087,19 +8299,9 @@
       </c>
     </row>
     <row r="190">
-      <c r="T190" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U190" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V190" s="4" t="n">
-        <v>10434</v>
-      </c>
+      <c r="T190" s="4" t="n"/>
+      <c r="U190" s="4" t="n"/>
+      <c r="V190" s="4" t="n"/>
       <c r="X190" s="4" t="n"/>
       <c r="Y190" s="4" t="n"/>
       <c r="Z190" s="4" t="n"/>
@@ -10118,19 +8320,9 @@
       </c>
     </row>
     <row r="191">
-      <c r="T191" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U191" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V191" s="7" t="n">
-        <v>10284</v>
-      </c>
+      <c r="T191" s="7" t="n"/>
+      <c r="U191" s="7" t="n"/>
+      <c r="V191" s="7" t="n"/>
       <c r="X191" s="7" t="n"/>
       <c r="Y191" s="7" t="n"/>
       <c r="Z191" s="7" t="n"/>
@@ -10149,19 +8341,9 @@
       </c>
     </row>
     <row r="192">
-      <c r="T192" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U192" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V192" s="4" t="n">
-        <v>10458</v>
-      </c>
+      <c r="T192" s="4" t="n"/>
+      <c r="U192" s="4" t="n"/>
+      <c r="V192" s="4" t="n"/>
       <c r="X192" s="4" t="n"/>
       <c r="Y192" s="4" t="n"/>
       <c r="Z192" s="4" t="n"/>
@@ -10180,19 +8362,9 @@
       </c>
     </row>
     <row r="193">
-      <c r="T193" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U193" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V193" s="7" t="n">
-        <v>10153</v>
-      </c>
+      <c r="T193" s="7" t="n"/>
+      <c r="U193" s="7" t="n"/>
+      <c r="V193" s="7" t="n"/>
       <c r="X193" s="7" t="n"/>
       <c r="Y193" s="7" t="n"/>
       <c r="Z193" s="7" t="n"/>
@@ -10211,19 +8383,9 @@
       </c>
     </row>
     <row r="194">
-      <c r="T194" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U194" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V194" s="4" t="n">
-        <v>9843</v>
-      </c>
+      <c r="T194" s="4" t="n"/>
+      <c r="U194" s="4" t="n"/>
+      <c r="V194" s="4" t="n"/>
       <c r="X194" s="4" t="n"/>
       <c r="Y194" s="4" t="n"/>
       <c r="Z194" s="4" t="n"/>
@@ -10242,19 +8404,9 @@
       </c>
     </row>
     <row r="195">
-      <c r="T195" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U195" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V195" s="7" t="n">
-        <v>10433</v>
-      </c>
+      <c r="T195" s="7" t="n"/>
+      <c r="U195" s="7" t="n"/>
+      <c r="V195" s="7" t="n"/>
       <c r="X195" s="7" t="n"/>
       <c r="Y195" s="7" t="n"/>
       <c r="Z195" s="7" t="n"/>
@@ -10273,19 +8425,9 @@
       </c>
     </row>
     <row r="196">
-      <c r="T196" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U196" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V196" s="4" t="n">
-        <v>10670</v>
-      </c>
+      <c r="T196" s="4" t="n"/>
+      <c r="U196" s="4" t="n"/>
+      <c r="V196" s="4" t="n"/>
       <c r="X196" s="4" t="n"/>
       <c r="Y196" s="4" t="n"/>
       <c r="Z196" s="4" t="n"/>
@@ -10304,19 +8446,9 @@
       </c>
     </row>
     <row r="197">
-      <c r="T197" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U197" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V197" s="7" t="n">
-        <v>10599</v>
-      </c>
+      <c r="T197" s="7" t="n"/>
+      <c r="U197" s="7" t="n"/>
+      <c r="V197" s="7" t="n"/>
       <c r="X197" s="7" t="n"/>
       <c r="Y197" s="7" t="n"/>
       <c r="Z197" s="7" t="n"/>
@@ -10335,19 +8467,9 @@
       </c>
     </row>
     <row r="198">
-      <c r="T198" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U198" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V198" s="4" t="n">
-        <v>10619</v>
-      </c>
+      <c r="T198" s="4" t="n"/>
+      <c r="U198" s="4" t="n"/>
+      <c r="V198" s="4" t="n"/>
       <c r="X198" s="4" t="n"/>
       <c r="Y198" s="4" t="n"/>
       <c r="Z198" s="4" t="n"/>
@@ -10366,19 +8488,9 @@
       </c>
     </row>
     <row r="199">
-      <c r="T199" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U199" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V199" s="7" t="n">
-        <v>10415</v>
-      </c>
+      <c r="T199" s="7" t="n"/>
+      <c r="U199" s="7" t="n"/>
+      <c r="V199" s="7" t="n"/>
       <c r="X199" s="7" t="n"/>
       <c r="Y199" s="7" t="n"/>
       <c r="Z199" s="7" t="n"/>
@@ -10397,19 +8509,9 @@
       </c>
     </row>
     <row r="200">
-      <c r="T200" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U200" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V200" s="4" t="n">
-        <v>10065</v>
-      </c>
+      <c r="T200" s="4" t="n"/>
+      <c r="U200" s="4" t="n"/>
+      <c r="V200" s="4" t="n"/>
       <c r="X200" s="4" t="n"/>
       <c r="Y200" s="4" t="n"/>
       <c r="Z200" s="4" t="n"/>
@@ -10428,19 +8530,9 @@
       </c>
     </row>
     <row r="201">
-      <c r="T201" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U201" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V201" s="7" t="n">
-        <v>10158</v>
-      </c>
+      <c r="T201" s="7" t="n"/>
+      <c r="U201" s="7" t="n"/>
+      <c r="V201" s="7" t="n"/>
       <c r="X201" s="7" t="n"/>
       <c r="Y201" s="7" t="n"/>
       <c r="Z201" s="7" t="n"/>
@@ -10459,19 +8551,9 @@
       </c>
     </row>
     <row r="202">
-      <c r="T202" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U202" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V202" s="4" t="n">
-        <v>10333</v>
-      </c>
+      <c r="T202" s="4" t="n"/>
+      <c r="U202" s="4" t="n"/>
+      <c r="V202" s="4" t="n"/>
       <c r="X202" s="4" t="n"/>
       <c r="Y202" s="4" t="n"/>
       <c r="Z202" s="4" t="n"/>
@@ -10490,19 +8572,9 @@
       </c>
     </row>
     <row r="203">
-      <c r="T203" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U203" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V203" s="7" t="n">
-        <v>10414</v>
-      </c>
+      <c r="T203" s="7" t="n"/>
+      <c r="U203" s="7" t="n"/>
+      <c r="V203" s="7" t="n"/>
       <c r="X203" s="7" t="n"/>
       <c r="Y203" s="7" t="n"/>
       <c r="Z203" s="7" t="n"/>
@@ -10521,19 +8593,9 @@
       </c>
     </row>
     <row r="204">
-      <c r="T204" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U204" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V204" s="4" t="n">
-        <v>10453</v>
-      </c>
+      <c r="T204" s="4" t="n"/>
+      <c r="U204" s="4" t="n"/>
+      <c r="V204" s="4" t="n"/>
       <c r="X204" s="4" t="n"/>
       <c r="Y204" s="4" t="n"/>
       <c r="Z204" s="4" t="n"/>
@@ -10552,19 +8614,9 @@
       </c>
     </row>
     <row r="205">
-      <c r="T205" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U205" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation50987</t>
-        </is>
-      </c>
-      <c r="V205" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T205" s="7" t="n"/>
+      <c r="U205" s="7" t="n"/>
+      <c r="V205" s="7" t="n"/>
       <c r="X205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
       <c r="Z205" s="7" t="n"/>
@@ -10583,19 +8635,9 @@
       </c>
     </row>
     <row r="206">
-      <c r="T206" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U206" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation75114</t>
-        </is>
-      </c>
-      <c r="V206" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T206" s="4" t="n"/>
+      <c r="U206" s="4" t="n"/>
+      <c r="V206" s="4" t="n"/>
       <c r="X206" s="4" t="n"/>
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="n"/>
@@ -10614,19 +8656,9 @@
       </c>
     </row>
     <row r="207">
-      <c r="T207" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U207" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V207" s="7" t="n">
-        <v>21493</v>
-      </c>
+      <c r="T207" s="7" t="n"/>
+      <c r="U207" s="7" t="n"/>
+      <c r="V207" s="7" t="n"/>
       <c r="X207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
       <c r="Z207" s="7" t="n"/>
@@ -10645,19 +8677,9 @@
       </c>
     </row>
     <row r="208">
-      <c r="T208" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U208" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V208" s="4" t="n">
-        <v>21012</v>
-      </c>
+      <c r="T208" s="4" t="n"/>
+      <c r="U208" s="4" t="n"/>
+      <c r="V208" s="4" t="n"/>
       <c r="X208" s="4" t="n"/>
       <c r="Y208" s="4" t="n"/>
       <c r="Z208" s="4" t="n"/>
@@ -10676,19 +8698,9 @@
       </c>
     </row>
     <row r="209">
-      <c r="T209" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U209" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V209" s="7" t="n">
-        <v>21635</v>
-      </c>
+      <c r="T209" s="7" t="n"/>
+      <c r="U209" s="7" t="n"/>
+      <c r="V209" s="7" t="n"/>
       <c r="X209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
       <c r="Z209" s="7" t="n"/>
@@ -10705,1875 +8717,6 @@
           <t>com.logistics.rider.foody</t>
         </is>
       </c>
-    </row>
-    <row r="210">
-      <c r="T210" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U210" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V210" s="4" t="n">
-        <v>21969</v>
-      </c>
-      <c r="X210" s="4" t="n"/>
-      <c r="Y210" s="4" t="n"/>
-      <c r="Z210" s="4" t="n"/>
-      <c r="AB210" s="4" t="n"/>
-      <c r="AC210" s="4" t="n"/>
-      <c r="AD210" s="4" t="n"/>
-    </row>
-    <row r="211">
-      <c r="T211" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U211" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V211" s="7" t="n">
-        <v>21723</v>
-      </c>
-      <c r="X211" s="7" t="n"/>
-      <c r="Y211" s="7" t="n"/>
-      <c r="Z211" s="7" t="n"/>
-      <c r="AB211" s="7" t="n"/>
-      <c r="AC211" s="7" t="n"/>
-      <c r="AD211" s="7" t="n"/>
-    </row>
-    <row r="212">
-      <c r="T212" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U212" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V212" s="4" t="n">
-        <v>20879</v>
-      </c>
-      <c r="X212" s="4" t="n"/>
-      <c r="Y212" s="4" t="n"/>
-      <c r="Z212" s="4" t="n"/>
-      <c r="AB212" s="4" t="n"/>
-      <c r="AC212" s="4" t="n"/>
-      <c r="AD212" s="4" t="n"/>
-    </row>
-    <row r="213">
-      <c r="T213" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U213" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V213" s="7" t="n">
-        <v>20783</v>
-      </c>
-      <c r="X213" s="7" t="n"/>
-      <c r="Y213" s="7" t="n"/>
-      <c r="Z213" s="7" t="n"/>
-      <c r="AB213" s="7" t="n"/>
-      <c r="AC213" s="7" t="n"/>
-      <c r="AD213" s="7" t="n"/>
-    </row>
-    <row r="214">
-      <c r="T214" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U214" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V214" s="4" t="n">
-        <v>21875</v>
-      </c>
-      <c r="X214" s="4" t="n"/>
-      <c r="Y214" s="4" t="n"/>
-      <c r="Z214" s="4" t="n"/>
-      <c r="AB214" s="4" t="n"/>
-      <c r="AC214" s="4" t="n"/>
-      <c r="AD214" s="4" t="n"/>
-    </row>
-    <row r="215">
-      <c r="T215" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U215" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V215" s="7" t="n">
-        <v>22103</v>
-      </c>
-      <c r="X215" s="7" t="n"/>
-      <c r="Y215" s="7" t="n"/>
-      <c r="Z215" s="7" t="n"/>
-      <c r="AB215" s="7" t="n"/>
-      <c r="AC215" s="7" t="n"/>
-      <c r="AD215" s="7" t="n"/>
-    </row>
-    <row r="216">
-      <c r="T216" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U216" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V216" s="4" t="n">
-        <v>22799</v>
-      </c>
-      <c r="X216" s="4" t="n"/>
-      <c r="Y216" s="4" t="n"/>
-      <c r="Z216" s="4" t="n"/>
-      <c r="AB216" s="4" t="n"/>
-      <c r="AC216" s="4" t="n"/>
-      <c r="AD216" s="4" t="n"/>
-    </row>
-    <row r="217">
-      <c r="T217" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U217" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V217" s="7" t="n">
-        <v>22705</v>
-      </c>
-      <c r="X217" s="7" t="n"/>
-      <c r="Y217" s="7" t="n"/>
-      <c r="Z217" s="7" t="n"/>
-      <c r="AB217" s="7" t="n"/>
-      <c r="AC217" s="7" t="n"/>
-      <c r="AD217" s="7" t="n"/>
-    </row>
-    <row r="218">
-      <c r="T218" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U218" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V218" s="4" t="n">
-        <v>21885</v>
-      </c>
-      <c r="X218" s="4" t="n"/>
-      <c r="Y218" s="4" t="n"/>
-      <c r="Z218" s="4" t="n"/>
-      <c r="AB218" s="4" t="n"/>
-      <c r="AC218" s="4" t="n"/>
-      <c r="AD218" s="4" t="n"/>
-    </row>
-    <row r="219">
-      <c r="T219" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U219" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V219" s="7" t="n">
-        <v>21360</v>
-      </c>
-      <c r="X219" s="7" t="n"/>
-      <c r="Y219" s="7" t="n"/>
-      <c r="Z219" s="7" t="n"/>
-      <c r="AB219" s="7" t="n"/>
-      <c r="AC219" s="7" t="n"/>
-      <c r="AD219" s="7" t="n"/>
-    </row>
-    <row r="220">
-      <c r="T220" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U220" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V220" s="4" t="n">
-        <v>20612</v>
-      </c>
-      <c r="X220" s="4" t="n"/>
-      <c r="Y220" s="4" t="n"/>
-      <c r="Z220" s="4" t="n"/>
-      <c r="AB220" s="4" t="n"/>
-      <c r="AC220" s="4" t="n"/>
-      <c r="AD220" s="4" t="n"/>
-    </row>
-    <row r="221">
-      <c r="T221" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U221" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V221" s="7" t="n">
-        <v>22101</v>
-      </c>
-      <c r="X221" s="7" t="n"/>
-      <c r="Y221" s="7" t="n"/>
-      <c r="Z221" s="7" t="n"/>
-      <c r="AB221" s="7" t="n"/>
-      <c r="AC221" s="7" t="n"/>
-      <c r="AD221" s="7" t="n"/>
-    </row>
-    <row r="222">
-      <c r="T222" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U222" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V222" s="4" t="n">
-        <v>22665</v>
-      </c>
-      <c r="X222" s="4" t="n"/>
-      <c r="Y222" s="4" t="n"/>
-      <c r="Z222" s="4" t="n"/>
-      <c r="AB222" s="4" t="n"/>
-      <c r="AC222" s="4" t="n"/>
-      <c r="AD222" s="4" t="n"/>
-    </row>
-    <row r="223">
-      <c r="T223" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U223" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V223" s="7" t="n">
-        <v>22473</v>
-      </c>
-      <c r="X223" s="7" t="n"/>
-      <c r="Y223" s="7" t="n"/>
-      <c r="Z223" s="7" t="n"/>
-      <c r="AB223" s="7" t="n"/>
-      <c r="AC223" s="7" t="n"/>
-      <c r="AD223" s="7" t="n"/>
-    </row>
-    <row r="224">
-      <c r="T224" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U224" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V224" s="4" t="n">
-        <v>22903</v>
-      </c>
-      <c r="X224" s="4" t="n"/>
-      <c r="Y224" s="4" t="n"/>
-      <c r="Z224" s="4" t="n"/>
-      <c r="AB224" s="4" t="n"/>
-      <c r="AC224" s="4" t="n"/>
-      <c r="AD224" s="4" t="n"/>
-    </row>
-    <row r="225">
-      <c r="T225" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U225" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V225" s="7" t="n">
-        <v>21829</v>
-      </c>
-      <c r="X225" s="7" t="n"/>
-      <c r="Y225" s="7" t="n"/>
-      <c r="Z225" s="7" t="n"/>
-      <c r="AB225" s="7" t="n"/>
-      <c r="AC225" s="7" t="n"/>
-      <c r="AD225" s="7" t="n"/>
-    </row>
-    <row r="226">
-      <c r="T226" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U226" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V226" s="4" t="n">
-        <v>20959</v>
-      </c>
-      <c r="X226" s="4" t="n"/>
-      <c r="Y226" s="4" t="n"/>
-      <c r="Z226" s="4" t="n"/>
-      <c r="AB226" s="4" t="n"/>
-      <c r="AC226" s="4" t="n"/>
-      <c r="AD226" s="4" t="n"/>
-    </row>
-    <row r="227">
-      <c r="T227" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U227" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V227" s="7" t="n">
-        <v>20856</v>
-      </c>
-      <c r="X227" s="7" t="n"/>
-      <c r="Y227" s="7" t="n"/>
-      <c r="Z227" s="7" t="n"/>
-      <c r="AB227" s="7" t="n"/>
-      <c r="AC227" s="7" t="n"/>
-      <c r="AD227" s="7" t="n"/>
-    </row>
-    <row r="228">
-      <c r="T228" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U228" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V228" s="4" t="n">
-        <v>23061</v>
-      </c>
-      <c r="X228" s="4" t="n"/>
-      <c r="Y228" s="4" t="n"/>
-      <c r="Z228" s="4" t="n"/>
-      <c r="AB228" s="4" t="n"/>
-      <c r="AC228" s="4" t="n"/>
-      <c r="AD228" s="4" t="n"/>
-    </row>
-    <row r="229">
-      <c r="T229" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U229" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V229" s="7" t="n">
-        <v>21952</v>
-      </c>
-      <c r="X229" s="7" t="n"/>
-      <c r="Y229" s="7" t="n"/>
-      <c r="Z229" s="7" t="n"/>
-      <c r="AB229" s="7" t="n"/>
-      <c r="AC229" s="7" t="n"/>
-      <c r="AD229" s="7" t="n"/>
-    </row>
-    <row r="230">
-      <c r="T230" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U230" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V230" s="4" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X230" s="4" t="n"/>
-      <c r="Y230" s="4" t="n"/>
-      <c r="Z230" s="4" t="n"/>
-      <c r="AB230" s="4" t="n"/>
-      <c r="AC230" s="4" t="n"/>
-      <c r="AD230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="T231" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U231" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V231" s="7" t="n">
-        <v>16721</v>
-      </c>
-      <c r="X231" s="7" t="n"/>
-      <c r="Y231" s="7" t="n"/>
-      <c r="Z231" s="7" t="n"/>
-      <c r="AB231" s="7" t="n"/>
-      <c r="AC231" s="7" t="n"/>
-      <c r="AD231" s="7" t="n"/>
-    </row>
-    <row r="232">
-      <c r="T232" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U232" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V232" s="4" t="n">
-        <v>16586</v>
-      </c>
-      <c r="X232" s="4" t="n"/>
-      <c r="Y232" s="4" t="n"/>
-      <c r="Z232" s="4" t="n"/>
-      <c r="AB232" s="4" t="n"/>
-      <c r="AC232" s="4" t="n"/>
-      <c r="AD232" s="4" t="n"/>
-    </row>
-    <row r="233">
-      <c r="T233" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U233" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V233" s="7" t="n">
-        <v>16419</v>
-      </c>
-      <c r="X233" s="7" t="n"/>
-      <c r="Y233" s="7" t="n"/>
-      <c r="Z233" s="7" t="n"/>
-      <c r="AB233" s="7" t="n"/>
-      <c r="AC233" s="7" t="n"/>
-      <c r="AD233" s="7" t="n"/>
-    </row>
-    <row r="234">
-      <c r="T234" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U234" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V234" s="4" t="n">
-        <v>15946</v>
-      </c>
-      <c r="X234" s="4" t="n"/>
-      <c r="Y234" s="4" t="n"/>
-      <c r="Z234" s="4" t="n"/>
-      <c r="AB234" s="4" t="n"/>
-      <c r="AC234" s="4" t="n"/>
-      <c r="AD234" s="4" t="n"/>
-    </row>
-    <row r="235">
-      <c r="T235" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U235" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V235" s="7" t="n">
-        <v>16042</v>
-      </c>
-      <c r="X235" s="7" t="n"/>
-      <c r="Y235" s="7" t="n"/>
-      <c r="Z235" s="7" t="n"/>
-      <c r="AB235" s="7" t="n"/>
-      <c r="AC235" s="7" t="n"/>
-      <c r="AD235" s="7" t="n"/>
-    </row>
-    <row r="236">
-      <c r="T236" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U236" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V236" s="4" t="n">
-        <v>16409</v>
-      </c>
-      <c r="X236" s="4" t="n"/>
-      <c r="Y236" s="4" t="n"/>
-      <c r="Z236" s="4" t="n"/>
-      <c r="AB236" s="4" t="n"/>
-      <c r="AC236" s="4" t="n"/>
-      <c r="AD236" s="4" t="n"/>
-    </row>
-    <row r="237">
-      <c r="T237" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U237" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V237" s="7" t="n">
-        <v>16831</v>
-      </c>
-      <c r="X237" s="7" t="n"/>
-      <c r="Y237" s="7" t="n"/>
-      <c r="Z237" s="7" t="n"/>
-      <c r="AB237" s="7" t="n"/>
-      <c r="AC237" s="7" t="n"/>
-      <c r="AD237" s="7" t="n"/>
-    </row>
-    <row r="238">
-      <c r="T238" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U238" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V238" s="4" t="n">
-        <v>16886</v>
-      </c>
-      <c r="X238" s="4" t="n"/>
-      <c r="Y238" s="4" t="n"/>
-      <c r="Z238" s="4" t="n"/>
-      <c r="AB238" s="4" t="n"/>
-      <c r="AC238" s="4" t="n"/>
-      <c r="AD238" s="4" t="n"/>
-    </row>
-    <row r="239">
-      <c r="T239" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U239" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V239" s="7" t="n">
-        <v>16694</v>
-      </c>
-      <c r="X239" s="7" t="n"/>
-      <c r="Y239" s="7" t="n"/>
-      <c r="Z239" s="7" t="n"/>
-      <c r="AB239" s="7" t="n"/>
-      <c r="AC239" s="7" t="n"/>
-      <c r="AD239" s="7" t="n"/>
-    </row>
-    <row r="240">
-      <c r="T240" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U240" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V240" s="4" t="n">
-        <v>16659</v>
-      </c>
-      <c r="X240" s="4" t="n"/>
-      <c r="Y240" s="4" t="n"/>
-      <c r="Z240" s="4" t="n"/>
-      <c r="AB240" s="4" t="n"/>
-      <c r="AC240" s="4" t="n"/>
-      <c r="AD240" s="4" t="n"/>
-    </row>
-    <row r="241">
-      <c r="T241" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U241" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V241" s="7" t="n">
-        <v>16268</v>
-      </c>
-      <c r="X241" s="7" t="n"/>
-      <c r="Y241" s="7" t="n"/>
-      <c r="Z241" s="7" t="n"/>
-      <c r="AB241" s="7" t="n"/>
-      <c r="AC241" s="7" t="n"/>
-      <c r="AD241" s="7" t="n"/>
-    </row>
-    <row r="242">
-      <c r="T242" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U242" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V242" s="4" t="n">
-        <v>16259</v>
-      </c>
-      <c r="X242" s="4" t="n"/>
-      <c r="Y242" s="4" t="n"/>
-      <c r="Z242" s="4" t="n"/>
-      <c r="AB242" s="4" t="n"/>
-      <c r="AC242" s="4" t="n"/>
-      <c r="AD242" s="4" t="n"/>
-    </row>
-    <row r="243">
-      <c r="T243" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U243" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V243" s="7" t="n">
-        <v>16600</v>
-      </c>
-      <c r="X243" s="7" t="n"/>
-      <c r="Y243" s="7" t="n"/>
-      <c r="Z243" s="7" t="n"/>
-      <c r="AB243" s="7" t="n"/>
-      <c r="AC243" s="7" t="n"/>
-      <c r="AD243" s="7" t="n"/>
-    </row>
-    <row r="244">
-      <c r="T244" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U244" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V244" s="4" t="n">
-        <v>16913</v>
-      </c>
-      <c r="X244" s="4" t="n"/>
-      <c r="Y244" s="4" t="n"/>
-      <c r="Z244" s="4" t="n"/>
-      <c r="AB244" s="4" t="n"/>
-      <c r="AC244" s="4" t="n"/>
-      <c r="AD244" s="4" t="n"/>
-    </row>
-    <row r="245">
-      <c r="T245" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U245" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V245" s="7" t="n">
-        <v>16991</v>
-      </c>
-      <c r="X245" s="7" t="n"/>
-      <c r="Y245" s="7" t="n"/>
-      <c r="Z245" s="7" t="n"/>
-      <c r="AB245" s="7" t="n"/>
-      <c r="AC245" s="7" t="n"/>
-      <c r="AD245" s="7" t="n"/>
-    </row>
-    <row r="246">
-      <c r="T246" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U246" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V246" s="4" t="n">
-        <v>17365</v>
-      </c>
-      <c r="X246" s="4" t="n"/>
-      <c r="Y246" s="4" t="n"/>
-      <c r="Z246" s="4" t="n"/>
-      <c r="AB246" s="4" t="n"/>
-      <c r="AC246" s="4" t="n"/>
-      <c r="AD246" s="4" t="n"/>
-    </row>
-    <row r="247">
-      <c r="T247" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U247" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V247" s="7" t="n">
-        <v>16944</v>
-      </c>
-      <c r="X247" s="7" t="n"/>
-      <c r="Y247" s="7" t="n"/>
-      <c r="Z247" s="7" t="n"/>
-      <c r="AB247" s="7" t="n"/>
-      <c r="AC247" s="7" t="n"/>
-      <c r="AD247" s="7" t="n"/>
-    </row>
-    <row r="248">
-      <c r="T248" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U248" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V248" s="4" t="n">
-        <v>16518</v>
-      </c>
-      <c r="X248" s="4" t="n"/>
-      <c r="Y248" s="4" t="n"/>
-      <c r="Z248" s="4" t="n"/>
-      <c r="AB248" s="4" t="n"/>
-      <c r="AC248" s="4" t="n"/>
-      <c r="AD248" s="4" t="n"/>
-    </row>
-    <row r="249">
-      <c r="T249" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U249" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V249" s="7" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X249" s="7" t="n"/>
-      <c r="Y249" s="7" t="n"/>
-      <c r="Z249" s="7" t="n"/>
-      <c r="AB249" s="7" t="n"/>
-      <c r="AC249" s="7" t="n"/>
-      <c r="AD249" s="7" t="n"/>
-    </row>
-    <row r="250">
-      <c r="T250" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U250" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V250" s="4" t="n">
-        <v>16711</v>
-      </c>
-      <c r="X250" s="4" t="n"/>
-      <c r="Y250" s="4" t="n"/>
-      <c r="Z250" s="4" t="n"/>
-      <c r="AB250" s="4" t="n"/>
-      <c r="AC250" s="4" t="n"/>
-      <c r="AD250" s="4" t="n"/>
-    </row>
-    <row r="251">
-      <c r="T251" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U251" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V251" s="7" t="n">
-        <v>17379</v>
-      </c>
-      <c r="X251" s="7" t="n"/>
-      <c r="Y251" s="7" t="n"/>
-      <c r="Z251" s="7" t="n"/>
-      <c r="AB251" s="7" t="n"/>
-      <c r="AC251" s="7" t="n"/>
-      <c r="AD251" s="7" t="n"/>
-    </row>
-    <row r="252">
-      <c r="T252" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U252" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V252" s="4" t="n">
-        <v>17551</v>
-      </c>
-      <c r="X252" s="4" t="n"/>
-      <c r="Y252" s="4" t="n"/>
-      <c r="Z252" s="4" t="n"/>
-      <c r="AB252" s="4" t="n"/>
-      <c r="AC252" s="4" t="n"/>
-      <c r="AD252" s="4" t="n"/>
-    </row>
-    <row r="253">
-      <c r="T253" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U253" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V253" s="7" t="n">
-        <v>724</v>
-      </c>
-      <c r="X253" s="7" t="n"/>
-      <c r="Y253" s="7" t="n"/>
-      <c r="Z253" s="7" t="n"/>
-      <c r="AB253" s="7" t="n"/>
-      <c r="AC253" s="7" t="n"/>
-      <c r="AD253" s="7" t="n"/>
-    </row>
-    <row r="254">
-      <c r="T254" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U254" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V254" s="4" t="n">
-        <v>746</v>
-      </c>
-      <c r="X254" s="4" t="n"/>
-      <c r="Y254" s="4" t="n"/>
-      <c r="Z254" s="4" t="n"/>
-      <c r="AB254" s="4" t="n"/>
-      <c r="AC254" s="4" t="n"/>
-      <c r="AD254" s="4" t="n"/>
-    </row>
-    <row r="255">
-      <c r="T255" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U255" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V255" s="7" t="n">
-        <v>723</v>
-      </c>
-      <c r="X255" s="7" t="n"/>
-      <c r="Y255" s="7" t="n"/>
-      <c r="Z255" s="7" t="n"/>
-      <c r="AB255" s="7" t="n"/>
-      <c r="AC255" s="7" t="n"/>
-      <c r="AD255" s="7" t="n"/>
-    </row>
-    <row r="256">
-      <c r="T256" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U256" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V256" s="4" t="n">
-        <v>708</v>
-      </c>
-      <c r="X256" s="4" t="n"/>
-      <c r="Y256" s="4" t="n"/>
-      <c r="Z256" s="4" t="n"/>
-      <c r="AB256" s="4" t="n"/>
-      <c r="AC256" s="4" t="n"/>
-      <c r="AD256" s="4" t="n"/>
-    </row>
-    <row r="257">
-      <c r="T257" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U257" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V257" s="7" t="n">
-        <v>735</v>
-      </c>
-      <c r="X257" s="7" t="n"/>
-      <c r="Y257" s="7" t="n"/>
-      <c r="Z257" s="7" t="n"/>
-      <c r="AB257" s="7" t="n"/>
-      <c r="AC257" s="7" t="n"/>
-      <c r="AD257" s="7" t="n"/>
-    </row>
-    <row r="258">
-      <c r="T258" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U258" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V258" s="4" t="n">
-        <v>714</v>
-      </c>
-      <c r="X258" s="4" t="n"/>
-      <c r="Y258" s="4" t="n"/>
-      <c r="Z258" s="4" t="n"/>
-      <c r="AB258" s="4" t="n"/>
-      <c r="AC258" s="4" t="n"/>
-      <c r="AD258" s="4" t="n"/>
-    </row>
-    <row r="259">
-      <c r="T259" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U259" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V259" s="7" t="n">
-        <v>706</v>
-      </c>
-      <c r="X259" s="7" t="n"/>
-      <c r="Y259" s="7" t="n"/>
-      <c r="Z259" s="7" t="n"/>
-      <c r="AB259" s="7" t="n"/>
-      <c r="AC259" s="7" t="n"/>
-      <c r="AD259" s="7" t="n"/>
-    </row>
-    <row r="260">
-      <c r="T260" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U260" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V260" s="4" t="n">
-        <v>729</v>
-      </c>
-      <c r="X260" s="4" t="n"/>
-      <c r="Y260" s="4" t="n"/>
-      <c r="Z260" s="4" t="n"/>
-      <c r="AB260" s="4" t="n"/>
-      <c r="AC260" s="4" t="n"/>
-      <c r="AD260" s="4" t="n"/>
-    </row>
-    <row r="261">
-      <c r="T261" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U261" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V261" s="7" t="n">
-        <v>719</v>
-      </c>
-      <c r="X261" s="7" t="n"/>
-      <c r="Y261" s="7" t="n"/>
-      <c r="Z261" s="7" t="n"/>
-      <c r="AB261" s="7" t="n"/>
-      <c r="AC261" s="7" t="n"/>
-      <c r="AD261" s="7" t="n"/>
-    </row>
-    <row r="262">
-      <c r="T262" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U262" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V262" s="4" t="n">
-        <v>719</v>
-      </c>
-      <c r="X262" s="4" t="n"/>
-      <c r="Y262" s="4" t="n"/>
-      <c r="Z262" s="4" t="n"/>
-      <c r="AB262" s="4" t="n"/>
-      <c r="AC262" s="4" t="n"/>
-      <c r="AD262" s="4" t="n"/>
-    </row>
-    <row r="263">
-      <c r="T263" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U263" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V263" s="7" t="n">
-        <v>730</v>
-      </c>
-      <c r="X263" s="7" t="n"/>
-      <c r="Y263" s="7" t="n"/>
-      <c r="Z263" s="7" t="n"/>
-      <c r="AB263" s="7" t="n"/>
-      <c r="AC263" s="7" t="n"/>
-      <c r="AD263" s="7" t="n"/>
-    </row>
-    <row r="264">
-      <c r="T264" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U264" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V264" s="4" t="n">
-        <v>740</v>
-      </c>
-      <c r="X264" s="4" t="n"/>
-      <c r="Y264" s="4" t="n"/>
-      <c r="Z264" s="4" t="n"/>
-      <c r="AB264" s="4" t="n"/>
-      <c r="AC264" s="4" t="n"/>
-      <c r="AD264" s="4" t="n"/>
-    </row>
-    <row r="265">
-      <c r="T265" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U265" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V265" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="X265" s="7" t="n"/>
-      <c r="Y265" s="7" t="n"/>
-      <c r="Z265" s="7" t="n"/>
-      <c r="AB265" s="7" t="n"/>
-      <c r="AC265" s="7" t="n"/>
-      <c r="AD265" s="7" t="n"/>
-    </row>
-    <row r="266">
-      <c r="T266" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U266" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V266" s="4" t="n">
-        <v>698</v>
-      </c>
-      <c r="X266" s="4" t="n"/>
-      <c r="Y266" s="4" t="n"/>
-      <c r="Z266" s="4" t="n"/>
-      <c r="AB266" s="4" t="n"/>
-      <c r="AC266" s="4" t="n"/>
-      <c r="AD266" s="4" t="n"/>
-    </row>
-    <row r="267">
-      <c r="T267" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U267" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V267" s="7" t="n">
-        <v>691</v>
-      </c>
-      <c r="X267" s="7" t="n"/>
-      <c r="Y267" s="7" t="n"/>
-      <c r="Z267" s="7" t="n"/>
-      <c r="AB267" s="7" t="n"/>
-      <c r="AC267" s="7" t="n"/>
-      <c r="AD267" s="7" t="n"/>
-    </row>
-    <row r="268">
-      <c r="T268" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U268" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V268" s="4" t="n">
-        <v>695</v>
-      </c>
-      <c r="X268" s="4" t="n"/>
-      <c r="Y268" s="4" t="n"/>
-      <c r="Z268" s="4" t="n"/>
-      <c r="AB268" s="4" t="n"/>
-      <c r="AC268" s="4" t="n"/>
-      <c r="AD268" s="4" t="n"/>
-    </row>
-    <row r="269">
-      <c r="T269" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U269" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V269" s="7" t="n">
-        <v>706</v>
-      </c>
-      <c r="X269" s="7" t="n"/>
-      <c r="Y269" s="7" t="n"/>
-      <c r="Z269" s="7" t="n"/>
-      <c r="AB269" s="7" t="n"/>
-      <c r="AC269" s="7" t="n"/>
-      <c r="AD269" s="7" t="n"/>
-    </row>
-    <row r="270">
-      <c r="T270" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U270" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V270" s="4" t="n">
-        <v>701</v>
-      </c>
-      <c r="X270" s="4" t="n"/>
-      <c r="Y270" s="4" t="n"/>
-      <c r="Z270" s="4" t="n"/>
-      <c r="AB270" s="4" t="n"/>
-      <c r="AC270" s="4" t="n"/>
-      <c r="AD270" s="4" t="n"/>
-    </row>
-    <row r="271">
-      <c r="T271" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U271" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V271" s="7" t="n">
-        <v>706</v>
-      </c>
-      <c r="X271" s="7" t="n"/>
-      <c r="Y271" s="7" t="n"/>
-      <c r="Z271" s="7" t="n"/>
-      <c r="AB271" s="7" t="n"/>
-      <c r="AC271" s="7" t="n"/>
-      <c r="AD271" s="7" t="n"/>
-    </row>
-    <row r="272">
-      <c r="T272" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U272" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V272" s="4" t="n">
-        <v>704</v>
-      </c>
-      <c r="X272" s="4" t="n"/>
-      <c r="Y272" s="4" t="n"/>
-      <c r="Z272" s="4" t="n"/>
-      <c r="AB272" s="4" t="n"/>
-      <c r="AC272" s="4" t="n"/>
-      <c r="AD272" s="4" t="n"/>
-    </row>
-    <row r="273">
-      <c r="T273" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U273" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V273" s="7" t="n">
-        <v>670</v>
-      </c>
-      <c r="X273" s="7" t="n"/>
-      <c r="Y273" s="7" t="n"/>
-      <c r="Z273" s="7" t="n"/>
-      <c r="AB273" s="7" t="n"/>
-      <c r="AC273" s="7" t="n"/>
-      <c r="AD273" s="7" t="n"/>
-    </row>
-    <row r="274">
-      <c r="T274" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U274" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V274" s="4" t="n">
-        <v>694</v>
-      </c>
-      <c r="X274" s="4" t="n"/>
-      <c r="Y274" s="4" t="n"/>
-      <c r="Z274" s="4" t="n"/>
-      <c r="AB274" s="4" t="n"/>
-      <c r="AC274" s="4" t="n"/>
-      <c r="AD274" s="4" t="n"/>
-    </row>
-    <row r="275">
-      <c r="T275" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U275" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V275" s="7" t="n">
-        <v>702</v>
-      </c>
-      <c r="X275" s="7" t="n"/>
-      <c r="Y275" s="7" t="n"/>
-      <c r="Z275" s="7" t="n"/>
-      <c r="AB275" s="7" t="n"/>
-      <c r="AC275" s="7" t="n"/>
-      <c r="AD275" s="7" t="n"/>
-    </row>
-    <row r="276">
-      <c r="T276" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U276" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V276" s="4" t="n">
-        <v>2188</v>
-      </c>
-      <c r="X276" s="4" t="n"/>
-      <c r="Y276" s="4" t="n"/>
-      <c r="Z276" s="4" t="n"/>
-      <c r="AB276" s="4" t="n"/>
-      <c r="AC276" s="4" t="n"/>
-      <c r="AD276" s="4" t="n"/>
-    </row>
-    <row r="277">
-      <c r="T277" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U277" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V277" s="7" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X277" s="7" t="n"/>
-      <c r="Y277" s="7" t="n"/>
-      <c r="Z277" s="7" t="n"/>
-      <c r="AB277" s="7" t="n"/>
-      <c r="AC277" s="7" t="n"/>
-      <c r="AD277" s="7" t="n"/>
-    </row>
-    <row r="278">
-      <c r="T278" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U278" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V278" s="4" t="n">
-        <v>2338</v>
-      </c>
-      <c r="X278" s="4" t="n"/>
-      <c r="Y278" s="4" t="n"/>
-      <c r="Z278" s="4" t="n"/>
-      <c r="AB278" s="4" t="n"/>
-      <c r="AC278" s="4" t="n"/>
-      <c r="AD278" s="4" t="n"/>
-    </row>
-    <row r="279">
-      <c r="T279" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U279" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V279" s="7" t="n">
-        <v>2152</v>
-      </c>
-      <c r="X279" s="7" t="n"/>
-      <c r="Y279" s="7" t="n"/>
-      <c r="Z279" s="7" t="n"/>
-      <c r="AB279" s="7" t="n"/>
-      <c r="AC279" s="7" t="n"/>
-      <c r="AD279" s="7" t="n"/>
-    </row>
-    <row r="280">
-      <c r="T280" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U280" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V280" s="4" t="n">
-        <v>2003</v>
-      </c>
-      <c r="X280" s="4" t="n"/>
-      <c r="Y280" s="4" t="n"/>
-      <c r="Z280" s="4" t="n"/>
-      <c r="AB280" s="4" t="n"/>
-      <c r="AC280" s="4" t="n"/>
-      <c r="AD280" s="4" t="n"/>
-    </row>
-    <row r="281">
-      <c r="T281" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U281" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V281" s="7" t="n">
-        <v>1895</v>
-      </c>
-      <c r="X281" s="7" t="n"/>
-      <c r="Y281" s="7" t="n"/>
-      <c r="Z281" s="7" t="n"/>
-      <c r="AB281" s="7" t="n"/>
-      <c r="AC281" s="7" t="n"/>
-      <c r="AD281" s="7" t="n"/>
-    </row>
-    <row r="282">
-      <c r="T282" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U282" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V282" s="4" t="n">
-        <v>1935</v>
-      </c>
-      <c r="X282" s="4" t="n"/>
-      <c r="Y282" s="4" t="n"/>
-      <c r="Z282" s="4" t="n"/>
-      <c r="AB282" s="4" t="n"/>
-      <c r="AC282" s="4" t="n"/>
-      <c r="AD282" s="4" t="n"/>
-    </row>
-    <row r="283">
-      <c r="T283" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U283" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V283" s="7" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X283" s="7" t="n"/>
-      <c r="Y283" s="7" t="n"/>
-      <c r="Z283" s="7" t="n"/>
-      <c r="AB283" s="7" t="n"/>
-      <c r="AC283" s="7" t="n"/>
-      <c r="AD283" s="7" t="n"/>
-    </row>
-    <row r="284">
-      <c r="T284" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U284" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V284" s="4" t="n">
-        <v>2049</v>
-      </c>
-      <c r="X284" s="4" t="n"/>
-      <c r="Y284" s="4" t="n"/>
-      <c r="Z284" s="4" t="n"/>
-      <c r="AB284" s="4" t="n"/>
-      <c r="AC284" s="4" t="n"/>
-      <c r="AD284" s="4" t="n"/>
-    </row>
-    <row r="285">
-      <c r="T285" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U285" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V285" s="7" t="n">
-        <v>2325</v>
-      </c>
-      <c r="X285" s="7" t="n"/>
-      <c r="Y285" s="7" t="n"/>
-      <c r="Z285" s="7" t="n"/>
-      <c r="AB285" s="7" t="n"/>
-      <c r="AC285" s="7" t="n"/>
-      <c r="AD285" s="7" t="n"/>
-    </row>
-    <row r="286">
-      <c r="T286" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U286" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V286" s="4" t="n">
-        <v>2216</v>
-      </c>
-      <c r="X286" s="4" t="n"/>
-      <c r="Y286" s="4" t="n"/>
-      <c r="Z286" s="4" t="n"/>
-      <c r="AB286" s="4" t="n"/>
-      <c r="AC286" s="4" t="n"/>
-      <c r="AD286" s="4" t="n"/>
-    </row>
-    <row r="287">
-      <c r="T287" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U287" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V287" s="7" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X287" s="7" t="n"/>
-      <c r="Y287" s="7" t="n"/>
-      <c r="Z287" s="7" t="n"/>
-      <c r="AB287" s="7" t="n"/>
-      <c r="AC287" s="7" t="n"/>
-      <c r="AD287" s="7" t="n"/>
-    </row>
-    <row r="288">
-      <c r="T288" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U288" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V288" s="4" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X288" s="4" t="n"/>
-      <c r="Y288" s="4" t="n"/>
-      <c r="Z288" s="4" t="n"/>
-      <c r="AB288" s="4" t="n"/>
-      <c r="AC288" s="4" t="n"/>
-      <c r="AD288" s="4" t="n"/>
-    </row>
-    <row r="289">
-      <c r="T289" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U289" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V289" s="7" t="n">
-        <v>2035</v>
-      </c>
-      <c r="X289" s="7" t="n"/>
-      <c r="Y289" s="7" t="n"/>
-      <c r="Z289" s="7" t="n"/>
-      <c r="AB289" s="7" t="n"/>
-      <c r="AC289" s="7" t="n"/>
-      <c r="AD289" s="7" t="n"/>
-    </row>
-    <row r="290">
-      <c r="T290" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U290" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V290" s="4" t="n">
-        <v>2182</v>
-      </c>
-      <c r="X290" s="4" t="n"/>
-      <c r="Y290" s="4" t="n"/>
-      <c r="Z290" s="4" t="n"/>
-      <c r="AB290" s="4" t="n"/>
-      <c r="AC290" s="4" t="n"/>
-      <c r="AD290" s="4" t="n"/>
-    </row>
-    <row r="291">
-      <c r="T291" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U291" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V291" s="7" t="n">
-        <v>2156</v>
-      </c>
-      <c r="X291" s="7" t="n"/>
-      <c r="Y291" s="7" t="n"/>
-      <c r="Z291" s="7" t="n"/>
-      <c r="AB291" s="7" t="n"/>
-      <c r="AC291" s="7" t="n"/>
-      <c r="AD291" s="7" t="n"/>
-    </row>
-    <row r="292">
-      <c r="T292" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U292" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V292" s="4" t="n">
-        <v>2437</v>
-      </c>
-      <c r="X292" s="4" t="n"/>
-      <c r="Y292" s="4" t="n"/>
-      <c r="Z292" s="4" t="n"/>
-      <c r="AB292" s="4" t="n"/>
-      <c r="AC292" s="4" t="n"/>
-      <c r="AD292" s="4" t="n"/>
-    </row>
-    <row r="293">
-      <c r="T293" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U293" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V293" s="7" t="n">
-        <v>2214</v>
-      </c>
-      <c r="X293" s="7" t="n"/>
-      <c r="Y293" s="7" t="n"/>
-      <c r="Z293" s="7" t="n"/>
-      <c r="AB293" s="7" t="n"/>
-      <c r="AC293" s="7" t="n"/>
-      <c r="AD293" s="7" t="n"/>
-    </row>
-    <row r="294">
-      <c r="T294" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U294" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V294" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="X294" s="4" t="n"/>
-      <c r="Y294" s="4" t="n"/>
-      <c r="Z294" s="4" t="n"/>
-      <c r="AB294" s="4" t="n"/>
-      <c r="AC294" s="4" t="n"/>
-      <c r="AD294" s="4" t="n"/>
-    </row>
-    <row r="295">
-      <c r="T295" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U295" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V295" s="7" t="n">
-        <v>1973</v>
-      </c>
-      <c r="X295" s="7" t="n"/>
-      <c r="Y295" s="7" t="n"/>
-      <c r="Z295" s="7" t="n"/>
-      <c r="AB295" s="7" t="n"/>
-      <c r="AC295" s="7" t="n"/>
-      <c r="AD295" s="7" t="n"/>
-    </row>
-    <row r="296">
-      <c r="T296" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U296" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V296" s="4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="X296" s="4" t="n"/>
-      <c r="Y296" s="4" t="n"/>
-      <c r="Z296" s="4" t="n"/>
-      <c r="AB296" s="4" t="n"/>
-      <c r="AC296" s="4" t="n"/>
-      <c r="AD296" s="4" t="n"/>
-    </row>
-    <row r="297">
-      <c r="T297" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U297" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V297" s="7" t="n">
-        <v>2075</v>
-      </c>
-      <c r="X297" s="7" t="n"/>
-      <c r="Y297" s="7" t="n"/>
-      <c r="Z297" s="7" t="n"/>
-      <c r="AB297" s="7" t="n"/>
-      <c r="AC297" s="7" t="n"/>
-      <c r="AD297" s="7" t="n"/>
-    </row>
-    <row r="298">
-      <c r="T298" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U298" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V298" s="4" t="n">
-        <v>2191</v>
-      </c>
-      <c r="X298" s="4" t="n"/>
-      <c r="Y298" s="4" t="n"/>
-      <c r="Z298" s="4" t="n"/>
-      <c r="AB298" s="4" t="n"/>
-      <c r="AC298" s="4" t="n"/>
-      <c r="AD298" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -716,7 +716,7 @@
         <v>0.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.27</v>
@@ -752,7 +752,7 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>1.27</v>
@@ -788,7 +788,7 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>1.27</v>
@@ -824,7 +824,7 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>1.27</v>
@@ -860,7 +860,7 @@
         <v>0.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>1.27</v>
@@ -896,7 +896,7 @@
         <v>0.95</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>1.27</v>
@@ -932,7 +932,7 @@
         <v>0.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>1.27</v>
@@ -968,7 +968,7 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1.27</v>
@@ -1004,7 +1004,7 @@
         <v>0.95</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>1.27</v>
@@ -1040,7 +1040,7 @@
         <v>0.95</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>1.27</v>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD298"/>
+  <dimension ref="A1:AD310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3164,29 +3164,49 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
+      <c r="D25" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C25)</f>
+        <v/>
+      </c>
       <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
+      <c r="G25" s="7">
+        <f>ROUND((1-E25/D25)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H25" s="7">
+        <f>MIN(1,(G25-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
+      <c r="K25" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="7">
+        <f>ROUND(100*(1-K25/D25),2)</f>
+        <v/>
+      </c>
+      <c r="M25" s="7">
+        <f>MAX(0,(L25-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N25" s="7">
+        <f>$B$2+H25+M25</f>
+        <v/>
+      </c>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="U25" s="7" t="inlineStr"/>
       <c r="V25" s="7" t="n">
-        <v>5365</v>
+        <v>1</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>101</v>
@@ -3236,7 +3256,7 @@
       <c r="N26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
@@ -3245,7 +3265,7 @@
         </is>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5741</v>
+        <v>5365</v>
       </c>
       <c r="X26" s="4" t="n">
         <v>11</v>
@@ -3295,7 +3315,7 @@
       <c r="N27" s="7" t="n"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -3304,7 +3324,7 @@
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>5451</v>
+        <v>5741</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>73</v>
@@ -3354,7 +3374,7 @@
       <c r="N28" s="4" t="n"/>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
@@ -3363,7 +3383,7 @@
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5458</v>
+        <v>5451</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>31</v>
@@ -3413,7 +3433,7 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -3422,7 +3442,7 @@
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>5664</v>
+        <v>5458</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>13</v>
@@ -3472,7 +3492,7 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3481,7 +3501,7 @@
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5241</v>
+        <v>5664</v>
       </c>
       <c r="X30" s="4" t="n">
         <v>78</v>
@@ -3531,7 +3551,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -3540,7 +3560,7 @@
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>5102</v>
+        <v>5241</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>1</v>
@@ -3599,7 +3619,7 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3608,7 +3628,7 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5388</v>
+        <v>5102</v>
       </c>
       <c r="X32" s="4" t="n">
         <v>9</v>
@@ -3639,7 +3659,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D24)</f>
+        <f>AVERAGE(D2:D25)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3649,7 +3669,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H24)</f>
+        <f>AVERAGE(H2:H25)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3672,7 +3692,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -3681,7 +3701,7 @@
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>5339</v>
+        <v>5388</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>1</v>
@@ -3713,7 +3733,7 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3722,7 +3742,7 @@
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5348</v>
+        <v>5339</v>
       </c>
       <c r="X34" s="4" t="n">
         <v>119</v>
@@ -3754,7 +3774,7 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -3763,7 +3783,7 @@
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>5329</v>
+        <v>5348</v>
       </c>
       <c r="X35" s="7" t="n">
         <v>13</v>
@@ -3795,7 +3815,7 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
@@ -3804,7 +3824,7 @@
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>5436</v>
+        <v>5329</v>
       </c>
       <c r="X36" s="4" t="n">
         <v>67</v>
@@ -3836,7 +3856,7 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
@@ -3845,7 +3865,7 @@
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>5081</v>
+        <v>5436</v>
       </c>
       <c r="X37" s="7" t="n">
         <v>32</v>
@@ -3877,7 +3897,7 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
@@ -3886,7 +3906,7 @@
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>5034</v>
+        <v>5081</v>
       </c>
       <c r="X38" s="4" t="n">
         <v>13</v>
@@ -3918,7 +3938,7 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
@@ -3927,7 +3947,7 @@
         </is>
       </c>
       <c r="V39" s="7" t="n">
-        <v>5557</v>
+        <v>5034</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>93</v>
@@ -3959,7 +3979,7 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
@@ -3968,7 +3988,7 @@
         </is>
       </c>
       <c r="V40" s="4" t="n">
-        <v>5513</v>
+        <v>5557</v>
       </c>
       <c r="X40" s="4" t="n">
         <v>12</v>
@@ -4000,7 +4020,7 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
@@ -4009,7 +4029,7 @@
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>5477</v>
+        <v>5513</v>
       </c>
       <c r="X41" s="7" t="n">
         <v>2</v>
@@ -4041,7 +4061,7 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
@@ -4050,7 +4070,7 @@
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>5526</v>
+        <v>5477</v>
       </c>
       <c r="X42" s="4" t="n">
         <v>113</v>
@@ -4082,7 +4102,7 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
@@ -4091,7 +4111,7 @@
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>5339</v>
+        <v>5526</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>12</v>
@@ -4123,7 +4143,7 @@
     <row r="44">
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U44" s="4" t="inlineStr">
@@ -4132,7 +4152,7 @@
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>4933</v>
+        <v>5339</v>
       </c>
       <c r="X44" s="4" t="n">
         <v>69</v>
@@ -4164,7 +4184,7 @@
     <row r="45">
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
@@ -4173,7 +4193,7 @@
         </is>
       </c>
       <c r="V45" s="7" t="n">
-        <v>4866</v>
+        <v>4933</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>40</v>
@@ -4205,7 +4225,7 @@
     <row r="46">
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
@@ -4214,7 +4234,7 @@
         </is>
       </c>
       <c r="V46" s="4" t="n">
-        <v>5232</v>
+        <v>4866</v>
       </c>
       <c r="X46" s="4" t="n">
         <v>17</v>
@@ -4246,7 +4266,7 @@
     <row r="47">
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
@@ -4255,7 +4275,7 @@
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>5576</v>
+        <v>5232</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>83</v>
@@ -4287,16 +4307,16 @@
     <row r="48">
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>14969</v>
+        <v>5576</v>
       </c>
       <c r="X48" s="4" t="n">
         <v>9</v>
@@ -4328,16 +4348,16 @@
     <row r="49">
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V49" s="7" t="n">
-        <v>14818</v>
+        <v>5287</v>
       </c>
       <c r="X49" s="7" t="n">
         <v>124</v>
@@ -4369,7 +4389,7 @@
     <row r="50">
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U50" s="4" t="inlineStr">
@@ -4378,7 +4398,7 @@
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>15263</v>
+        <v>14969</v>
       </c>
       <c r="X50" s="4" t="n">
         <v>19</v>
@@ -4410,7 +4430,7 @@
     <row r="51">
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
@@ -4419,7 +4439,7 @@
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>14815</v>
+        <v>14818</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>55</v>
@@ -4451,7 +4471,7 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
@@ -4460,7 +4480,7 @@
         </is>
       </c>
       <c r="V52" s="4" t="n">
-        <v>14968</v>
+        <v>15263</v>
       </c>
       <c r="X52" s="4" t="n">
         <v>35</v>
@@ -4492,7 +4512,7 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
@@ -4501,7 +4521,7 @@
         </is>
       </c>
       <c r="V53" s="7" t="n">
-        <v>14113</v>
+        <v>14815</v>
       </c>
       <c r="X53" s="7" t="n">
         <v>15</v>
@@ -4533,7 +4553,7 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
@@ -4542,7 +4562,7 @@
         </is>
       </c>
       <c r="V54" s="4" t="n">
-        <v>14162</v>
+        <v>14968</v>
       </c>
       <c r="X54" s="4" t="n">
         <v>82</v>
@@ -4574,7 +4594,7 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
@@ -4583,7 +4603,7 @@
         </is>
       </c>
       <c r="V55" s="7" t="n">
-        <v>14815</v>
+        <v>14113</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>1</v>
@@ -4615,7 +4635,7 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
@@ -4624,7 +4644,7 @@
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>14815</v>
+        <v>14162</v>
       </c>
       <c r="X56" s="4" t="n">
         <v>14</v>
@@ -4656,7 +4676,7 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
@@ -4665,7 +4685,7 @@
         </is>
       </c>
       <c r="V57" s="7" t="n">
-        <v>15546</v>
+        <v>14815</v>
       </c>
       <c r="X57" s="7" t="n">
         <v>2</v>
@@ -4697,7 +4717,7 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U58" s="4" t="inlineStr">
@@ -4706,7 +4726,7 @@
         </is>
       </c>
       <c r="V58" s="4" t="n">
-        <v>14882</v>
+        <v>14815</v>
       </c>
       <c r="X58" s="4" t="n">
         <v>101</v>
@@ -4738,7 +4758,7 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
@@ -4747,7 +4767,7 @@
         </is>
       </c>
       <c r="V59" s="7" t="n">
-        <v>14998</v>
+        <v>15546</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>10</v>
@@ -4779,7 +4799,7 @@
     <row r="60">
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U60" s="4" t="inlineStr">
@@ -4788,7 +4808,7 @@
         </is>
       </c>
       <c r="V60" s="4" t="n">
-        <v>14354</v>
+        <v>14882</v>
       </c>
       <c r="X60" s="4" t="n">
         <v>72</v>
@@ -4820,7 +4840,7 @@
     <row r="61">
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
@@ -4829,7 +4849,7 @@
         </is>
       </c>
       <c r="V61" s="7" t="n">
-        <v>14362</v>
+        <v>14998</v>
       </c>
       <c r="X61" s="7" t="n">
         <v>35</v>
@@ -4861,7 +4881,7 @@
     <row r="62">
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U62" s="4" t="inlineStr">
@@ -4870,7 +4890,7 @@
         </is>
       </c>
       <c r="V62" s="4" t="n">
-        <v>15089</v>
+        <v>14354</v>
       </c>
       <c r="X62" s="4" t="n">
         <v>13</v>
@@ -4902,7 +4922,7 @@
     <row r="63">
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
@@ -4911,7 +4931,7 @@
         </is>
       </c>
       <c r="V63" s="7" t="n">
-        <v>14802</v>
+        <v>14362</v>
       </c>
       <c r="X63" s="7" t="n">
         <v>71</v>
@@ -4943,7 +4963,7 @@
     <row r="64">
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr">
@@ -4952,7 +4972,7 @@
         </is>
       </c>
       <c r="V64" s="4" t="n">
-        <v>15349</v>
+        <v>15089</v>
       </c>
       <c r="X64" s="4" t="n">
         <v>8</v>
@@ -4984,7 +5004,7 @@
     <row r="65">
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
@@ -4993,7 +5013,7 @@
         </is>
       </c>
       <c r="V65" s="7" t="n">
-        <v>14872</v>
+        <v>14802</v>
       </c>
       <c r="X65" s="7" t="n">
         <v>2</v>
@@ -5025,7 +5045,7 @@
     <row r="66">
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr">
@@ -5034,7 +5054,7 @@
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>15054</v>
+        <v>15349</v>
       </c>
       <c r="X66" s="4" t="n">
         <v>125</v>
@@ -5066,7 +5086,7 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
@@ -5075,7 +5095,7 @@
         </is>
       </c>
       <c r="V67" s="7" t="n">
-        <v>14169</v>
+        <v>14872</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>11</v>
@@ -5107,7 +5127,7 @@
     <row r="68">
       <c r="T68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U68" s="4" t="inlineStr">
@@ -5116,7 +5136,7 @@
         </is>
       </c>
       <c r="V68" s="4" t="n">
-        <v>14056</v>
+        <v>15054</v>
       </c>
       <c r="X68" s="4" t="n">
         <v>67</v>
@@ -5148,7 +5168,7 @@
     <row r="69">
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
@@ -5157,7 +5177,7 @@
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>15058</v>
+        <v>14169</v>
       </c>
       <c r="X69" s="7" t="n">
         <v>27</v>
@@ -5189,7 +5209,7 @@
     <row r="70">
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U70" s="4" t="inlineStr">
@@ -5198,7 +5218,7 @@
         </is>
       </c>
       <c r="V70" s="4" t="n">
-        <v>14814</v>
+        <v>14056</v>
       </c>
       <c r="X70" s="4" t="n">
         <v>17</v>
@@ -5230,16 +5250,16 @@
     <row r="71">
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U71" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V71" s="7" t="n">
-        <v>77546</v>
+        <v>15058</v>
       </c>
       <c r="X71" s="7" t="n">
         <v>85</v>
@@ -5271,16 +5291,16 @@
     <row r="72">
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U72" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V72" s="4" t="n">
-        <v>77823</v>
+        <v>14814</v>
       </c>
       <c r="X72" s="4" t="n">
         <v>14</v>
@@ -5312,16 +5332,16 @@
     <row r="73">
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U73" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V73" s="7" t="n">
-        <v>81723</v>
+        <v>15440</v>
       </c>
       <c r="X73" s="7" t="n">
         <v>4</v>
@@ -5353,7 +5373,7 @@
     <row r="74">
       <c r="T74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U74" s="4" t="inlineStr">
@@ -5362,7 +5382,7 @@
         </is>
       </c>
       <c r="V74" s="4" t="n">
-        <v>78398</v>
+        <v>77546</v>
       </c>
       <c r="X74" s="4" t="n">
         <v>126</v>
@@ -5394,7 +5414,7 @@
     <row r="75">
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U75" s="7" t="inlineStr">
@@ -5403,7 +5423,7 @@
         </is>
       </c>
       <c r="V75" s="7" t="n">
-        <v>78030</v>
+        <v>77823</v>
       </c>
       <c r="X75" s="7" t="n">
         <v>23</v>
@@ -5435,7 +5455,7 @@
     <row r="76">
       <c r="T76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U76" s="4" t="inlineStr">
@@ -5444,7 +5464,7 @@
         </is>
       </c>
       <c r="V76" s="4" t="n">
-        <v>76646</v>
+        <v>81723</v>
       </c>
       <c r="X76" s="4" t="n">
         <v>65</v>
@@ -5476,7 +5496,7 @@
     <row r="77">
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U77" s="7" t="inlineStr">
@@ -5485,7 +5505,7 @@
         </is>
       </c>
       <c r="V77" s="7" t="n">
-        <v>76742</v>
+        <v>78398</v>
       </c>
       <c r="X77" s="7" t="n">
         <v>28</v>
@@ -5517,7 +5537,7 @@
     <row r="78">
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U78" s="4" t="inlineStr">
@@ -5526,7 +5546,7 @@
         </is>
       </c>
       <c r="V78" s="4" t="n">
-        <v>79003</v>
+        <v>78030</v>
       </c>
       <c r="X78" s="4" t="n">
         <v>19</v>
@@ -5558,7 +5578,7 @@
     <row r="79">
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U79" s="7" t="inlineStr">
@@ -5567,7 +5587,7 @@
         </is>
       </c>
       <c r="V79" s="7" t="n">
-        <v>78849</v>
+        <v>76646</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>91</v>
@@ -5599,7 +5619,7 @@
     <row r="80">
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U80" s="4" t="inlineStr">
@@ -5608,7 +5628,7 @@
         </is>
       </c>
       <c r="V80" s="4" t="n">
-        <v>80667</v>
+        <v>76742</v>
       </c>
       <c r="X80" s="4" t="n">
         <v>21</v>
@@ -5640,7 +5660,7 @@
     <row r="81">
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U81" s="7" t="inlineStr">
@@ -5649,7 +5669,7 @@
         </is>
       </c>
       <c r="V81" s="7" t="n">
-        <v>78640</v>
+        <v>79003</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>2</v>
@@ -5681,7 +5701,7 @@
     <row r="82">
       <c r="T82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U82" s="4" t="inlineStr">
@@ -5690,7 +5710,7 @@
         </is>
       </c>
       <c r="V82" s="4" t="n">
-        <v>79108</v>
+        <v>78849</v>
       </c>
       <c r="X82" s="4" t="n">
         <v>99</v>
@@ -5722,7 +5742,7 @@
     <row r="83">
       <c r="T83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U83" s="7" t="inlineStr">
@@ -5731,7 +5751,7 @@
         </is>
       </c>
       <c r="V83" s="7" t="n">
-        <v>76911</v>
+        <v>80667</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>12</v>
@@ -5763,7 +5783,7 @@
     <row r="84">
       <c r="T84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U84" s="4" t="inlineStr">
@@ -5772,7 +5792,7 @@
         </is>
       </c>
       <c r="V84" s="4" t="n">
-        <v>77273</v>
+        <v>78640</v>
       </c>
       <c r="X84" s="4" t="n">
         <v>70</v>
@@ -5804,7 +5824,7 @@
     <row r="85">
       <c r="T85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U85" s="7" t="inlineStr">
@@ -5813,7 +5833,7 @@
         </is>
       </c>
       <c r="V85" s="7" t="n">
-        <v>80657</v>
+        <v>79108</v>
       </c>
       <c r="X85" s="7" t="n">
         <v>30</v>
@@ -5845,7 +5865,7 @@
     <row r="86">
       <c r="T86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U86" s="4" t="inlineStr">
@@ -5854,7 +5874,7 @@
         </is>
       </c>
       <c r="V86" s="4" t="n">
-        <v>79898</v>
+        <v>76911</v>
       </c>
       <c r="X86" s="4" t="n">
         <v>15</v>
@@ -5886,7 +5906,7 @@
     <row r="87">
       <c r="T87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U87" s="7" t="inlineStr">
@@ -5895,7 +5915,7 @@
         </is>
       </c>
       <c r="V87" s="7" t="n">
-        <v>82443</v>
+        <v>77273</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>73</v>
@@ -5927,7 +5947,7 @@
     <row r="88">
       <c r="T88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U88" s="4" t="inlineStr">
@@ -5936,7 +5956,7 @@
         </is>
       </c>
       <c r="V88" s="4" t="n">
-        <v>80658</v>
+        <v>80657</v>
       </c>
       <c r="X88" s="4" t="n">
         <v>5</v>
@@ -5968,7 +5988,7 @@
     <row r="89">
       <c r="T89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U89" s="7" t="inlineStr">
@@ -5977,7 +5997,7 @@
         </is>
       </c>
       <c r="V89" s="7" t="n">
-        <v>78475</v>
+        <v>79898</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>1</v>
@@ -6009,7 +6029,7 @@
     <row r="90">
       <c r="T90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U90" s="4" t="inlineStr">
@@ -6018,7 +6038,7 @@
         </is>
       </c>
       <c r="V90" s="4" t="n">
-        <v>76874</v>
+        <v>82443</v>
       </c>
       <c r="X90" s="4" t="n">
         <v>107</v>
@@ -6050,7 +6070,7 @@
     <row r="91">
       <c r="T91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U91" s="7" t="inlineStr">
@@ -6059,7 +6079,7 @@
         </is>
       </c>
       <c r="V91" s="7" t="n">
-        <v>77058</v>
+        <v>80658</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>13</v>
@@ -6091,7 +6111,7 @@
     <row r="92">
       <c r="T92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U92" s="4" t="inlineStr">
@@ -6100,7 +6120,7 @@
         </is>
       </c>
       <c r="V92" s="4" t="n">
-        <v>79206</v>
+        <v>78475</v>
       </c>
       <c r="X92" s="4" t="n">
         <v>56</v>
@@ -6132,7 +6152,7 @@
     <row r="93">
       <c r="T93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U93" s="7" t="inlineStr">
@@ -6141,7 +6161,7 @@
         </is>
       </c>
       <c r="V93" s="7" t="n">
-        <v>79070</v>
+        <v>76874</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>32</v>
@@ -6173,16 +6193,16 @@
     <row r="94">
       <c r="T94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U94" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V94" s="4" t="n">
-        <v>721</v>
+        <v>77058</v>
       </c>
       <c r="X94" s="4" t="n">
         <v>13</v>
@@ -6214,16 +6234,16 @@
     <row r="95">
       <c r="T95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U95" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V95" s="7" t="n">
-        <v>715</v>
+        <v>79206</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>78</v>
@@ -6255,16 +6275,16 @@
     <row r="96">
       <c r="T96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U96" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V96" s="4" t="n">
-        <v>745</v>
+        <v>79070</v>
       </c>
       <c r="X96" s="4" t="n">
         <v>10</v>
@@ -6296,16 +6316,16 @@
     <row r="97">
       <c r="T97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U97" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V97" s="7" t="n">
-        <v>702</v>
+        <v>81246</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>1</v>
@@ -6337,7 +6357,7 @@
     <row r="98">
       <c r="T98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U98" s="4" t="inlineStr">
@@ -6346,7 +6366,7 @@
         </is>
       </c>
       <c r="V98" s="4" t="n">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="X98" s="4" t="n">
         <v>114</v>
@@ -6378,7 +6398,7 @@
     <row r="99">
       <c r="T99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U99" s="7" t="inlineStr">
@@ -6387,7 +6407,7 @@
         </is>
       </c>
       <c r="V99" s="7" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>15</v>
@@ -6419,7 +6439,7 @@
     <row r="100">
       <c r="T100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U100" s="4" t="inlineStr">
@@ -6428,7 +6448,7 @@
         </is>
       </c>
       <c r="V100" s="4" t="n">
-        <v>696</v>
+        <v>745</v>
       </c>
       <c r="X100" s="4" t="n">
         <v>53</v>
@@ -6460,7 +6480,7 @@
     <row r="101">
       <c r="T101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U101" s="7" t="inlineStr">
@@ -6469,7 +6489,7 @@
         </is>
       </c>
       <c r="V101" s="7" t="n">
-        <v>750</v>
+        <v>702</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>32</v>
@@ -6501,7 +6521,7 @@
     <row r="102">
       <c r="T102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U102" s="4" t="inlineStr">
@@ -6510,7 +6530,7 @@
         </is>
       </c>
       <c r="V102" s="4" t="n">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="X102" s="4" t="n">
         <v>14</v>
@@ -6542,7 +6562,7 @@
     <row r="103">
       <c r="T103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U103" s="7" t="inlineStr">
@@ -6551,7 +6571,7 @@
         </is>
       </c>
       <c r="V103" s="7" t="n">
-        <v>748</v>
+        <v>700</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>80</v>
@@ -6583,7 +6603,7 @@
     <row r="104">
       <c r="T104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U104" s="4" t="inlineStr">
@@ -6592,7 +6612,7 @@
         </is>
       </c>
       <c r="V104" s="4" t="n">
-        <v>736</v>
+        <v>696</v>
       </c>
       <c r="X104" s="4" t="n">
         <v>1</v>
@@ -6624,7 +6644,7 @@
     <row r="105">
       <c r="T105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U105" s="7" t="inlineStr">
@@ -6633,7 +6653,7 @@
         </is>
       </c>
       <c r="V105" s="7" t="n">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>9</v>
@@ -6665,7 +6685,7 @@
     <row r="106">
       <c r="T106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U106" s="4" t="inlineStr">
@@ -6674,7 +6694,7 @@
         </is>
       </c>
       <c r="V106" s="4" t="n">
-        <v>707</v>
+        <v>729</v>
       </c>
       <c r="X106" s="4" t="n">
         <v>4</v>
@@ -6706,7 +6726,7 @@
     <row r="107">
       <c r="T107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U107" s="7" t="inlineStr">
@@ -6715,7 +6735,7 @@
         </is>
       </c>
       <c r="V107" s="7" t="n">
-        <v>713</v>
+        <v>748</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>97</v>
@@ -6747,7 +6767,7 @@
     <row r="108">
       <c r="T108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U108" s="4" t="inlineStr">
@@ -6756,7 +6776,7 @@
         </is>
       </c>
       <c r="V108" s="4" t="n">
-        <v>786</v>
+        <v>736</v>
       </c>
       <c r="X108" s="4" t="n">
         <v>10</v>
@@ -6788,7 +6808,7 @@
     <row r="109">
       <c r="T109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U109" s="7" t="inlineStr">
@@ -6797,7 +6817,7 @@
         </is>
       </c>
       <c r="V109" s="7" t="n">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>52</v>
@@ -6829,7 +6849,7 @@
     <row r="110">
       <c r="T110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U110" s="4" t="inlineStr">
@@ -6838,7 +6858,7 @@
         </is>
       </c>
       <c r="V110" s="4" t="n">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="X110" s="4" t="n">
         <v>37</v>
@@ -6870,7 +6890,7 @@
     <row r="111">
       <c r="T111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U111" s="7" t="inlineStr">
@@ -6879,7 +6899,7 @@
         </is>
       </c>
       <c r="V111" s="7" t="n">
-        <v>695</v>
+        <v>713</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>18</v>
@@ -6911,7 +6931,7 @@
     <row r="112">
       <c r="T112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U112" s="4" t="inlineStr">
@@ -6920,7 +6940,7 @@
         </is>
       </c>
       <c r="V112" s="4" t="n">
-        <v>693</v>
+        <v>786</v>
       </c>
       <c r="X112" s="4" t="n">
         <v>64</v>
@@ -6952,7 +6972,7 @@
     <row r="113">
       <c r="T113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U113" s="7" t="inlineStr">
@@ -6961,7 +6981,7 @@
         </is>
       </c>
       <c r="V113" s="7" t="n">
-        <v>686</v>
+        <v>730</v>
       </c>
       <c r="X113" s="7" t="n">
         <v>7</v>
@@ -6993,7 +7013,7 @@
     <row r="114">
       <c r="T114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U114" s="4" t="inlineStr">
@@ -7002,7 +7022,7 @@
         </is>
       </c>
       <c r="V114" s="4" t="n">
-        <v>673</v>
+        <v>726</v>
       </c>
       <c r="X114" s="4" t="n">
         <v>106</v>
@@ -7034,7 +7054,7 @@
     <row r="115">
       <c r="T115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U115" s="7" t="inlineStr">
@@ -7043,7 +7063,7 @@
         </is>
       </c>
       <c r="V115" s="7" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>14</v>
@@ -7075,7 +7095,7 @@
     <row r="116">
       <c r="T116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U116" s="4" t="inlineStr">
@@ -7084,7 +7104,7 @@
         </is>
       </c>
       <c r="V116" s="4" t="n">
-        <v>717</v>
+        <v>693</v>
       </c>
       <c r="X116" s="4" t="n">
         <v>65</v>
@@ -7116,16 +7136,16 @@
     <row r="117">
       <c r="T117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V117" s="7" t="n">
-        <v>47976</v>
+        <v>686</v>
       </c>
       <c r="X117" s="7" t="n">
         <v>24</v>
@@ -7157,16 +7177,16 @@
     <row r="118">
       <c r="T118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U118" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V118" s="4" t="n">
-        <v>47122</v>
+        <v>673</v>
       </c>
       <c r="X118" s="4" t="n">
         <v>14</v>
@@ -7198,16 +7218,16 @@
     <row r="119">
       <c r="T119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U119" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V119" s="7" t="n">
-        <v>47233</v>
+        <v>752</v>
       </c>
       <c r="X119" s="7" t="n">
         <v>66</v>
@@ -7239,16 +7259,16 @@
     <row r="120">
       <c r="T120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U120" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V120" s="4" t="n">
-        <v>48580</v>
+        <v>717</v>
       </c>
       <c r="X120" s="4" t="n">
         <v>1</v>
@@ -7280,16 +7300,16 @@
     <row r="121">
       <c r="T121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U121" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V121" s="7" t="n">
-        <v>47383</v>
+        <v>706</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>9</v>
@@ -7321,7 +7341,7 @@
     <row r="122">
       <c r="T122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U122" s="4" t="inlineStr">
@@ -7330,7 +7350,7 @@
         </is>
       </c>
       <c r="V122" s="4" t="n">
-        <v>46456</v>
+        <v>47976</v>
       </c>
       <c r="X122" s="4" t="n">
         <v>116</v>
@@ -7362,7 +7382,7 @@
     <row r="123">
       <c r="T123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
@@ -7371,7 +7391,7 @@
         </is>
       </c>
       <c r="V123" s="7" t="n">
-        <v>46400</v>
+        <v>47122</v>
       </c>
       <c r="X123" s="7" t="n">
         <v>17</v>
@@ -7403,7 +7423,7 @@
     <row r="124">
       <c r="T124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U124" s="4" t="inlineStr">
@@ -7412,7 +7432,7 @@
         </is>
       </c>
       <c r="V124" s="4" t="n">
-        <v>47755</v>
+        <v>47233</v>
       </c>
       <c r="X124" s="4" t="n">
         <v>52</v>
@@ -7444,7 +7464,7 @@
     <row r="125">
       <c r="T125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U125" s="7" t="inlineStr">
@@ -7453,7 +7473,7 @@
         </is>
       </c>
       <c r="V125" s="7" t="n">
-        <v>47520</v>
+        <v>48580</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>38</v>
@@ -7485,7 +7505,7 @@
     <row r="126">
       <c r="T126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U126" s="4" t="inlineStr">
@@ -7494,7 +7514,7 @@
         </is>
       </c>
       <c r="V126" s="4" t="n">
-        <v>47354</v>
+        <v>47383</v>
       </c>
       <c r="X126" s="4" t="n">
         <v>19</v>
@@ -7526,7 +7546,7 @@
     <row r="127">
       <c r="T127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U127" s="7" t="inlineStr">
@@ -7535,7 +7555,7 @@
         </is>
       </c>
       <c r="V127" s="7" t="n">
-        <v>49015</v>
+        <v>46456</v>
       </c>
       <c r="X127" s="7" t="n">
         <v>79</v>
@@ -7567,7 +7587,7 @@
     <row r="128">
       <c r="T128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U128" s="4" t="inlineStr">
@@ -7576,7 +7596,7 @@
         </is>
       </c>
       <c r="V128" s="4" t="n">
-        <v>48832</v>
+        <v>46400</v>
       </c>
       <c r="X128" s="4" t="n">
         <v>9</v>
@@ -7608,7 +7628,7 @@
     <row r="129">
       <c r="T129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
@@ -7617,7 +7637,7 @@
         </is>
       </c>
       <c r="V129" s="7" t="n">
-        <v>46644</v>
+        <v>47755</v>
       </c>
       <c r="X129" s="7" t="n">
         <v>1</v>
@@ -7649,7 +7669,7 @@
     <row r="130">
       <c r="T130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U130" s="4" t="inlineStr">
@@ -7658,7 +7678,7 @@
         </is>
       </c>
       <c r="V130" s="4" t="n">
-        <v>46416</v>
+        <v>47520</v>
       </c>
       <c r="X130" s="4" t="n">
         <v>134</v>
@@ -7690,7 +7710,7 @@
     <row r="131">
       <c r="T131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U131" s="7" t="inlineStr">
@@ -7699,7 +7719,7 @@
         </is>
       </c>
       <c r="V131" s="7" t="n">
-        <v>48419</v>
+        <v>47354</v>
       </c>
       <c r="X131" s="7" t="n">
         <v>22</v>
@@ -7731,7 +7751,7 @@
     <row r="132">
       <c r="T132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U132" s="4" t="inlineStr">
@@ -7740,7 +7760,7 @@
         </is>
       </c>
       <c r="V132" s="4" t="n">
-        <v>47500</v>
+        <v>49015</v>
       </c>
       <c r="X132" s="4" t="n">
         <v>65</v>
@@ -7772,7 +7792,7 @@
     <row r="133">
       <c r="T133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
@@ -7781,7 +7801,7 @@
         </is>
       </c>
       <c r="V133" s="7" t="n">
-        <v>47954</v>
+        <v>48832</v>
       </c>
       <c r="X133" s="7" t="n">
         <v>29</v>
@@ -7813,7 +7833,7 @@
     <row r="134">
       <c r="T134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U134" s="4" t="inlineStr">
@@ -7822,7 +7842,7 @@
         </is>
       </c>
       <c r="V134" s="4" t="n">
-        <v>49088</v>
+        <v>46644</v>
       </c>
       <c r="X134" s="4" t="n">
         <v>12</v>
@@ -7854,7 +7874,7 @@
     <row r="135">
       <c r="T135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U135" s="7" t="inlineStr">
@@ -7863,7 +7883,7 @@
         </is>
       </c>
       <c r="V135" s="7" t="n">
-        <v>48111</v>
+        <v>46416</v>
       </c>
       <c r="X135" s="7" t="n">
         <v>82</v>
@@ -7895,7 +7915,7 @@
     <row r="136">
       <c r="T136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U136" s="4" t="inlineStr">
@@ -7904,7 +7924,7 @@
         </is>
       </c>
       <c r="V136" s="4" t="n">
-        <v>46535</v>
+        <v>48419</v>
       </c>
       <c r="X136" s="4" t="n">
         <v>1</v>
@@ -7936,7 +7956,7 @@
     <row r="137">
       <c r="T137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U137" s="7" t="inlineStr">
@@ -7945,7 +7965,7 @@
         </is>
       </c>
       <c r="V137" s="7" t="n">
-        <v>46063</v>
+        <v>47500</v>
       </c>
       <c r="X137" s="7" t="n">
         <v>7</v>
@@ -7977,7 +7997,7 @@
     <row r="138">
       <c r="T138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U138" s="4" t="inlineStr">
@@ -7986,7 +8006,7 @@
         </is>
       </c>
       <c r="V138" s="4" t="n">
-        <v>48085</v>
+        <v>47954</v>
       </c>
       <c r="X138" s="4" t="n">
         <v>1</v>
@@ -8018,7 +8038,7 @@
     <row r="139">
       <c r="T139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
@@ -8027,7 +8047,7 @@
         </is>
       </c>
       <c r="V139" s="7" t="n">
-        <v>47472</v>
+        <v>49088</v>
       </c>
       <c r="X139" s="7" t="n">
         <v>107</v>
@@ -8059,16 +8079,16 @@
     <row r="140">
       <c r="T140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U140" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V140" s="4" t="n">
-        <v>1</v>
+        <v>48111</v>
       </c>
       <c r="X140" s="4" t="n">
         <v>24</v>
@@ -8100,16 +8120,16 @@
     <row r="141">
       <c r="T141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V141" s="7" t="n">
-        <v>1</v>
+        <v>46535</v>
       </c>
       <c r="X141" s="7" t="n">
         <v>68</v>
@@ -8141,16 +8161,16 @@
     <row r="142">
       <c r="T142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U142" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V142" s="4" t="n">
-        <v>1</v>
+        <v>46063</v>
       </c>
       <c r="X142" s="4" t="n">
         <v>18</v>
@@ -8182,16 +8202,16 @@
     <row r="143">
       <c r="T143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V143" s="7" t="n">
-        <v>1</v>
+        <v>48085</v>
       </c>
       <c r="X143" s="7" t="n">
         <v>12</v>
@@ -8223,16 +8243,16 @@
     <row r="144">
       <c r="T144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U144" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V144" s="4" t="n">
-        <v>1</v>
+        <v>47472</v>
       </c>
       <c r="X144" s="4" t="n">
         <v>70</v>
@@ -8264,16 +8284,16 @@
     <row r="145">
       <c r="T145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U145" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V145" s="7" t="n">
-        <v>1</v>
+        <v>47003</v>
       </c>
       <c r="X145" s="7" t="n">
         <v>2</v>
@@ -8305,7 +8325,7 @@
     <row r="146">
       <c r="T146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U146" s="4" t="inlineStr">
@@ -8346,7 +8366,7 @@
     <row r="147">
       <c r="T147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
@@ -8387,7 +8407,7 @@
     <row r="148">
       <c r="T148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U148" s="4" t="inlineStr">
@@ -8428,7 +8448,7 @@
     <row r="149">
       <c r="T149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U149" s="7" t="inlineStr">
@@ -8469,7 +8489,7 @@
     <row r="150">
       <c r="T150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U150" s="4" t="inlineStr">
@@ -8510,7 +8530,7 @@
     <row r="151">
       <c r="T151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
@@ -8551,7 +8571,7 @@
     <row r="152">
       <c r="T152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U152" s="4" t="inlineStr">
@@ -8592,7 +8612,7 @@
     <row r="153">
       <c r="T153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
@@ -8633,7 +8653,7 @@
     <row r="154">
       <c r="T154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U154" s="4" t="inlineStr">
@@ -8674,7 +8694,7 @@
     <row r="155">
       <c r="T155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U155" s="7" t="inlineStr">
@@ -8715,7 +8735,7 @@
     <row r="156">
       <c r="T156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U156" s="4" t="inlineStr">
@@ -8756,7 +8776,7 @@
     <row r="157">
       <c r="T157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -8797,7 +8817,7 @@
     <row r="158">
       <c r="T158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U158" s="4" t="inlineStr">
@@ -8838,7 +8858,7 @@
     <row r="159">
       <c r="T159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
@@ -8879,12 +8899,12 @@
     <row r="160">
       <c r="T160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U160" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V160" s="4" t="n">
@@ -8920,12 +8940,12 @@
     <row r="161">
       <c r="T161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V161" s="7" t="n">
@@ -8961,12 +8981,12 @@
     <row r="162">
       <c r="T162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U162" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V162" s="4" t="n">
@@ -9002,12 +9022,12 @@
     <row r="163">
       <c r="T163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V163" s="7" t="n">
@@ -9043,12 +9063,12 @@
     <row r="164">
       <c r="T164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U164" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V164" s="4" t="n">
@@ -9084,12 +9104,12 @@
     <row r="165">
       <c r="T165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V165" s="7" t="n">
@@ -9125,7 +9145,7 @@
     <row r="166">
       <c r="T166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U166" s="4" t="inlineStr">
@@ -9166,7 +9186,7 @@
     <row r="167">
       <c r="T167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
@@ -9207,7 +9227,7 @@
     <row r="168">
       <c r="T168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U168" s="4" t="inlineStr">
@@ -9248,7 +9268,7 @@
     <row r="169">
       <c r="T169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U169" s="7" t="inlineStr">
@@ -9289,7 +9309,7 @@
     <row r="170">
       <c r="T170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U170" s="4" t="inlineStr">
@@ -9330,7 +9350,7 @@
     <row r="171">
       <c r="T171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U171" s="7" t="inlineStr">
@@ -9371,7 +9391,7 @@
     <row r="172">
       <c r="T172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U172" s="4" t="inlineStr">
@@ -9412,7 +9432,7 @@
     <row r="173">
       <c r="T173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
@@ -9453,7 +9473,7 @@
     <row r="174">
       <c r="T174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U174" s="4" t="inlineStr">
@@ -9494,7 +9514,7 @@
     <row r="175">
       <c r="T175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
@@ -9535,7 +9555,7 @@
     <row r="176">
       <c r="T176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U176" s="4" t="inlineStr">
@@ -9576,7 +9596,7 @@
     <row r="177">
       <c r="T177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U177" s="7" t="inlineStr">
@@ -9617,7 +9637,7 @@
     <row r="178">
       <c r="T178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U178" s="4" t="inlineStr">
@@ -9658,7 +9678,7 @@
     <row r="179">
       <c r="T179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr">
@@ -9699,7 +9719,7 @@
     <row r="180">
       <c r="T180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U180" s="4" t="inlineStr">
@@ -9711,7 +9731,7 @@
         <v>1</v>
       </c>
       <c r="X180" s="4" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y180" s="4" t="inlineStr">
         <is>
@@ -9740,7 +9760,7 @@
     <row r="181">
       <c r="T181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U181" s="7" t="inlineStr">
@@ -9781,16 +9801,16 @@
     <row r="182">
       <c r="T182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U182" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V182" s="4" t="n">
-        <v>9927</v>
+        <v>1</v>
       </c>
       <c r="X182" s="4" t="n">
         <v>66</v>
@@ -9822,16 +9842,16 @@
     <row r="183">
       <c r="T183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U183" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V183" s="7" t="n">
-        <v>9839</v>
+        <v>1</v>
       </c>
       <c r="X183" s="7" t="n">
         <v>29</v>
@@ -9863,19 +9883,19 @@
     <row r="184">
       <c r="T184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U184" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V184" s="4" t="n">
-        <v>9918</v>
+        <v>1</v>
       </c>
       <c r="X184" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y184" s="4" t="inlineStr">
         <is>
@@ -9904,19 +9924,19 @@
     <row r="185">
       <c r="T185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U185" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V185" s="7" t="n">
-        <v>10435</v>
+        <v>1</v>
       </c>
       <c r="X185" s="7" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y185" s="7" t="inlineStr">
         <is>
@@ -9945,16 +9965,16 @@
     <row r="186">
       <c r="T186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U186" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V186" s="4" t="n">
-        <v>10050</v>
+        <v>1</v>
       </c>
       <c r="X186" s="4" t="n">
         <v>9</v>
@@ -9986,16 +10006,16 @@
     <row r="187">
       <c r="T187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U187" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V187" s="7" t="n">
-        <v>9768</v>
+        <v>1</v>
       </c>
       <c r="X187" s="7" t="n">
         <v>1</v>
@@ -10027,20 +10047,30 @@
     <row r="188">
       <c r="T188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U188" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V188" s="4" t="n">
-        <v>9920</v>
-      </c>
-      <c r="X188" s="4" t="n"/>
-      <c r="Y188" s="4" t="n"/>
-      <c r="Z188" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X188" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="Y188" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z188" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB188" s="4" t="n">
         <v>105</v>
       </c>
@@ -10058,7 +10088,7 @@
     <row r="189">
       <c r="T189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U189" s="7" t="inlineStr">
@@ -10067,11 +10097,21 @@
         </is>
       </c>
       <c r="V189" s="7" t="n">
-        <v>10435</v>
-      </c>
-      <c r="X189" s="7" t="n"/>
-      <c r="Y189" s="7" t="n"/>
-      <c r="Z189" s="7" t="n"/>
+        <v>9927</v>
+      </c>
+      <c r="X189" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y189" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z189" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB189" s="7" t="n">
         <v>1</v>
       </c>
@@ -10089,7 +10129,7 @@
     <row r="190">
       <c r="T190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U190" s="4" t="inlineStr">
@@ -10098,11 +10138,21 @@
         </is>
       </c>
       <c r="V190" s="4" t="n">
-        <v>10434</v>
-      </c>
-      <c r="X190" s="4" t="n"/>
-      <c r="Y190" s="4" t="n"/>
-      <c r="Z190" s="4" t="n"/>
+        <v>9839</v>
+      </c>
+      <c r="X190" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y190" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z190" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB190" s="4" t="n">
         <v>2</v>
       </c>
@@ -10120,7 +10170,7 @@
     <row r="191">
       <c r="T191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U191" s="7" t="inlineStr">
@@ -10129,11 +10179,21 @@
         </is>
       </c>
       <c r="V191" s="7" t="n">
-        <v>10284</v>
-      </c>
-      <c r="X191" s="7" t="n"/>
-      <c r="Y191" s="7" t="n"/>
-      <c r="Z191" s="7" t="n"/>
+        <v>9918</v>
+      </c>
+      <c r="X191" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y191" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z191" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB191" s="7" t="n">
         <v>1</v>
       </c>
@@ -10151,7 +10211,7 @@
     <row r="192">
       <c r="T192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U192" s="4" t="inlineStr">
@@ -10160,11 +10220,21 @@
         </is>
       </c>
       <c r="V192" s="4" t="n">
-        <v>10458</v>
-      </c>
-      <c r="X192" s="4" t="n"/>
-      <c r="Y192" s="4" t="n"/>
-      <c r="Z192" s="4" t="n"/>
+        <v>10435</v>
+      </c>
+      <c r="X192" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y192" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z192" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB192" s="4" t="n">
         <v>292</v>
       </c>
@@ -10182,7 +10252,7 @@
     <row r="193">
       <c r="T193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U193" s="7" t="inlineStr">
@@ -10191,11 +10261,21 @@
         </is>
       </c>
       <c r="V193" s="7" t="n">
-        <v>10153</v>
-      </c>
-      <c r="X193" s="7" t="n"/>
-      <c r="Y193" s="7" t="n"/>
-      <c r="Z193" s="7" t="n"/>
+        <v>10050</v>
+      </c>
+      <c r="X193" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="Y193" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z193" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB193" s="7" t="n">
         <v>31</v>
       </c>
@@ -10213,7 +10293,7 @@
     <row r="194">
       <c r="T194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U194" s="4" t="inlineStr">
@@ -10222,11 +10302,21 @@
         </is>
       </c>
       <c r="V194" s="4" t="n">
-        <v>9843</v>
-      </c>
-      <c r="X194" s="4" t="n"/>
-      <c r="Y194" s="4" t="n"/>
-      <c r="Z194" s="4" t="n"/>
+        <v>9768</v>
+      </c>
+      <c r="X194" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y194" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z194" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB194" s="4" t="n">
         <v>157</v>
       </c>
@@ -10244,7 +10334,7 @@
     <row r="195">
       <c r="T195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U195" s="7" t="inlineStr">
@@ -10253,11 +10343,21 @@
         </is>
       </c>
       <c r="V195" s="7" t="n">
-        <v>10433</v>
-      </c>
-      <c r="X195" s="7" t="n"/>
-      <c r="Y195" s="7" t="n"/>
-      <c r="Z195" s="7" t="n"/>
+        <v>9920</v>
+      </c>
+      <c r="X195" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y195" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z195" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB195" s="7" t="n">
         <v>46</v>
       </c>
@@ -10275,7 +10375,7 @@
     <row r="196">
       <c r="T196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U196" s="4" t="inlineStr">
@@ -10284,7 +10384,7 @@
         </is>
       </c>
       <c r="V196" s="4" t="n">
-        <v>10670</v>
+        <v>10435</v>
       </c>
       <c r="X196" s="4" t="n"/>
       <c r="Y196" s="4" t="n"/>
@@ -10306,7 +10406,7 @@
     <row r="197">
       <c r="T197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U197" s="7" t="inlineStr">
@@ -10315,7 +10415,7 @@
         </is>
       </c>
       <c r="V197" s="7" t="n">
-        <v>10599</v>
+        <v>10434</v>
       </c>
       <c r="X197" s="7" t="n"/>
       <c r="Y197" s="7" t="n"/>
@@ -10337,7 +10437,7 @@
     <row r="198">
       <c r="T198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U198" s="4" t="inlineStr">
@@ -10346,7 +10446,7 @@
         </is>
       </c>
       <c r="V198" s="4" t="n">
-        <v>10619</v>
+        <v>10284</v>
       </c>
       <c r="X198" s="4" t="n"/>
       <c r="Y198" s="4" t="n"/>
@@ -10368,7 +10468,7 @@
     <row r="199">
       <c r="T199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U199" s="7" t="inlineStr">
@@ -10377,7 +10477,7 @@
         </is>
       </c>
       <c r="V199" s="7" t="n">
-        <v>10415</v>
+        <v>10458</v>
       </c>
       <c r="X199" s="7" t="n"/>
       <c r="Y199" s="7" t="n"/>
@@ -10399,7 +10499,7 @@
     <row r="200">
       <c r="T200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U200" s="4" t="inlineStr">
@@ -10408,7 +10508,7 @@
         </is>
       </c>
       <c r="V200" s="4" t="n">
-        <v>10065</v>
+        <v>10153</v>
       </c>
       <c r="X200" s="4" t="n"/>
       <c r="Y200" s="4" t="n"/>
@@ -10430,7 +10530,7 @@
     <row r="201">
       <c r="T201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U201" s="7" t="inlineStr">
@@ -10439,7 +10539,7 @@
         </is>
       </c>
       <c r="V201" s="7" t="n">
-        <v>10158</v>
+        <v>9843</v>
       </c>
       <c r="X201" s="7" t="n"/>
       <c r="Y201" s="7" t="n"/>
@@ -10461,7 +10561,7 @@
     <row r="202">
       <c r="T202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U202" s="4" t="inlineStr">
@@ -10470,7 +10570,7 @@
         </is>
       </c>
       <c r="V202" s="4" t="n">
-        <v>10333</v>
+        <v>10433</v>
       </c>
       <c r="X202" s="4" t="n"/>
       <c r="Y202" s="4" t="n"/>
@@ -10492,7 +10592,7 @@
     <row r="203">
       <c r="T203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U203" s="7" t="inlineStr">
@@ -10501,7 +10601,7 @@
         </is>
       </c>
       <c r="V203" s="7" t="n">
-        <v>10414</v>
+        <v>10670</v>
       </c>
       <c r="X203" s="7" t="n"/>
       <c r="Y203" s="7" t="n"/>
@@ -10523,7 +10623,7 @@
     <row r="204">
       <c r="T204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U204" s="4" t="inlineStr">
@@ -10532,7 +10632,7 @@
         </is>
       </c>
       <c r="V204" s="4" t="n">
-        <v>10453</v>
+        <v>10599</v>
       </c>
       <c r="X204" s="4" t="n"/>
       <c r="Y204" s="4" t="n"/>
@@ -10554,16 +10654,16 @@
     <row r="205">
       <c r="T205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U205" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation50987</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V205" s="7" t="n">
-        <v>1</v>
+        <v>10619</v>
       </c>
       <c r="X205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
@@ -10585,16 +10685,16 @@
     <row r="206">
       <c r="T206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U206" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation75114</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V206" s="4" t="n">
-        <v>1</v>
+        <v>10415</v>
       </c>
       <c r="X206" s="4" t="n"/>
       <c r="Y206" s="4" t="n"/>
@@ -10616,16 +10716,16 @@
     <row r="207">
       <c r="T207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U207" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V207" s="7" t="n">
-        <v>21493</v>
+        <v>10065</v>
       </c>
       <c r="X207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
@@ -10647,16 +10747,16 @@
     <row r="208">
       <c r="T208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U208" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V208" s="4" t="n">
-        <v>21012</v>
+        <v>10158</v>
       </c>
       <c r="X208" s="4" t="n"/>
       <c r="Y208" s="4" t="n"/>
@@ -10678,16 +10778,16 @@
     <row r="209">
       <c r="T209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U209" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V209" s="7" t="n">
-        <v>21635</v>
+        <v>10333</v>
       </c>
       <c r="X209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
@@ -10709,112 +10809,162 @@
     <row r="210">
       <c r="T210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U210" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V210" s="4" t="n">
-        <v>21969</v>
+        <v>10414</v>
       </c>
       <c r="X210" s="4" t="n"/>
       <c r="Y210" s="4" t="n"/>
       <c r="Z210" s="4" t="n"/>
-      <c r="AB210" s="4" t="n"/>
-      <c r="AC210" s="4" t="n"/>
-      <c r="AD210" s="4" t="n"/>
+      <c r="AB210" s="4" t="n">
+        <v>351</v>
+      </c>
+      <c r="AC210" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD210" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="T211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U211" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V211" s="7" t="n">
-        <v>21723</v>
+        <v>10453</v>
       </c>
       <c r="X211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
       <c r="Z211" s="7" t="n"/>
-      <c r="AB211" s="7" t="n"/>
-      <c r="AC211" s="7" t="n"/>
-      <c r="AD211" s="7" t="n"/>
+      <c r="AB211" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC211" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD211" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="T212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U212" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V212" s="4" t="n">
-        <v>20879</v>
+        <v>10879</v>
       </c>
       <c r="X212" s="4" t="n"/>
       <c r="Y212" s="4" t="n"/>
       <c r="Z212" s="4" t="n"/>
-      <c r="AB212" s="4" t="n"/>
-      <c r="AC212" s="4" t="n"/>
-      <c r="AD212" s="4" t="n"/>
+      <c r="AB212" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="AC212" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD212" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="T213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U213" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation50987</t>
         </is>
       </c>
       <c r="V213" s="7" t="n">
-        <v>20783</v>
+        <v>1</v>
       </c>
       <c r="X213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
       <c r="Z213" s="7" t="n"/>
-      <c r="AB213" s="7" t="n"/>
-      <c r="AC213" s="7" t="n"/>
-      <c r="AD213" s="7" t="n"/>
+      <c r="AB213" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="AC213" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD213" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="T214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U214" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation75114</t>
         </is>
       </c>
       <c r="V214" s="4" t="n">
-        <v>21875</v>
+        <v>1</v>
       </c>
       <c r="X214" s="4" t="n"/>
       <c r="Y214" s="4" t="n"/>
       <c r="Z214" s="4" t="n"/>
-      <c r="AB214" s="4" t="n"/>
-      <c r="AC214" s="4" t="n"/>
-      <c r="AD214" s="4" t="n"/>
+      <c r="AB214" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC214" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD214" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="T215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U215" s="7" t="inlineStr">
@@ -10823,19 +10973,29 @@
         </is>
       </c>
       <c r="V215" s="7" t="n">
-        <v>22103</v>
+        <v>21493</v>
       </c>
       <c r="X215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
       <c r="Z215" s="7" t="n"/>
-      <c r="AB215" s="7" t="n"/>
-      <c r="AC215" s="7" t="n"/>
-      <c r="AD215" s="7" t="n"/>
+      <c r="AB215" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="AC215" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD215" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="T216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U216" s="4" t="inlineStr">
@@ -10844,19 +11004,29 @@
         </is>
       </c>
       <c r="V216" s="4" t="n">
-        <v>22799</v>
+        <v>21012</v>
       </c>
       <c r="X216" s="4" t="n"/>
       <c r="Y216" s="4" t="n"/>
       <c r="Z216" s="4" t="n"/>
-      <c r="AB216" s="4" t="n"/>
-      <c r="AC216" s="4" t="n"/>
-      <c r="AD216" s="4" t="n"/>
+      <c r="AB216" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC216" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD216" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="T217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U217" s="7" t="inlineStr">
@@ -10865,19 +11035,29 @@
         </is>
       </c>
       <c r="V217" s="7" t="n">
-        <v>22705</v>
+        <v>21635</v>
       </c>
       <c r="X217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
       <c r="Z217" s="7" t="n"/>
-      <c r="AB217" s="7" t="n"/>
-      <c r="AC217" s="7" t="n"/>
-      <c r="AD217" s="7" t="n"/>
+      <c r="AB217" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC217" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD217" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="T218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U218" s="4" t="inlineStr">
@@ -10886,19 +11066,29 @@
         </is>
       </c>
       <c r="V218" s="4" t="n">
-        <v>21885</v>
+        <v>21969</v>
       </c>
       <c r="X218" s="4" t="n"/>
       <c r="Y218" s="4" t="n"/>
       <c r="Z218" s="4" t="n"/>
-      <c r="AB218" s="4" t="n"/>
-      <c r="AC218" s="4" t="n"/>
-      <c r="AD218" s="4" t="n"/>
+      <c r="AB218" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC218" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD218" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="T219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U219" s="7" t="inlineStr">
@@ -10907,7 +11097,7 @@
         </is>
       </c>
       <c r="V219" s="7" t="n">
-        <v>21360</v>
+        <v>21723</v>
       </c>
       <c r="X219" s="7" t="n"/>
       <c r="Y219" s="7" t="n"/>
@@ -10919,7 +11109,7 @@
     <row r="220">
       <c r="T220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U220" s="4" t="inlineStr">
@@ -10928,7 +11118,7 @@
         </is>
       </c>
       <c r="V220" s="4" t="n">
-        <v>20612</v>
+        <v>20879</v>
       </c>
       <c r="X220" s="4" t="n"/>
       <c r="Y220" s="4" t="n"/>
@@ -10940,7 +11130,7 @@
     <row r="221">
       <c r="T221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U221" s="7" t="inlineStr">
@@ -10949,7 +11139,7 @@
         </is>
       </c>
       <c r="V221" s="7" t="n">
-        <v>22101</v>
+        <v>20783</v>
       </c>
       <c r="X221" s="7" t="n"/>
       <c r="Y221" s="7" t="n"/>
@@ -10961,7 +11151,7 @@
     <row r="222">
       <c r="T222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U222" s="4" t="inlineStr">
@@ -10970,7 +11160,7 @@
         </is>
       </c>
       <c r="V222" s="4" t="n">
-        <v>22665</v>
+        <v>21875</v>
       </c>
       <c r="X222" s="4" t="n"/>
       <c r="Y222" s="4" t="n"/>
@@ -10982,7 +11172,7 @@
     <row r="223">
       <c r="T223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U223" s="7" t="inlineStr">
@@ -10991,7 +11181,7 @@
         </is>
       </c>
       <c r="V223" s="7" t="n">
-        <v>22473</v>
+        <v>22103</v>
       </c>
       <c r="X223" s="7" t="n"/>
       <c r="Y223" s="7" t="n"/>
@@ -11003,7 +11193,7 @@
     <row r="224">
       <c r="T224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U224" s="4" t="inlineStr">
@@ -11012,7 +11202,7 @@
         </is>
       </c>
       <c r="V224" s="4" t="n">
-        <v>22903</v>
+        <v>22799</v>
       </c>
       <c r="X224" s="4" t="n"/>
       <c r="Y224" s="4" t="n"/>
@@ -11024,7 +11214,7 @@
     <row r="225">
       <c r="T225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U225" s="7" t="inlineStr">
@@ -11033,7 +11223,7 @@
         </is>
       </c>
       <c r="V225" s="7" t="n">
-        <v>21829</v>
+        <v>22705</v>
       </c>
       <c r="X225" s="7" t="n"/>
       <c r="Y225" s="7" t="n"/>
@@ -11045,7 +11235,7 @@
     <row r="226">
       <c r="T226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U226" s="4" t="inlineStr">
@@ -11054,7 +11244,7 @@
         </is>
       </c>
       <c r="V226" s="4" t="n">
-        <v>20959</v>
+        <v>21885</v>
       </c>
       <c r="X226" s="4" t="n"/>
       <c r="Y226" s="4" t="n"/>
@@ -11066,7 +11256,7 @@
     <row r="227">
       <c r="T227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U227" s="7" t="inlineStr">
@@ -11075,7 +11265,7 @@
         </is>
       </c>
       <c r="V227" s="7" t="n">
-        <v>20856</v>
+        <v>21360</v>
       </c>
       <c r="X227" s="7" t="n"/>
       <c r="Y227" s="7" t="n"/>
@@ -11087,7 +11277,7 @@
     <row r="228">
       <c r="T228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U228" s="4" t="inlineStr">
@@ -11096,7 +11286,7 @@
         </is>
       </c>
       <c r="V228" s="4" t="n">
-        <v>23061</v>
+        <v>20612</v>
       </c>
       <c r="X228" s="4" t="n"/>
       <c r="Y228" s="4" t="n"/>
@@ -11108,7 +11298,7 @@
     <row r="229">
       <c r="T229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U229" s="7" t="inlineStr">
@@ -11117,7 +11307,7 @@
         </is>
       </c>
       <c r="V229" s="7" t="n">
-        <v>21952</v>
+        <v>22101</v>
       </c>
       <c r="X229" s="7" t="n"/>
       <c r="Y229" s="7" t="n"/>
@@ -11129,16 +11319,16 @@
     <row r="230">
       <c r="T230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U230" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V230" s="4" t="n">
-        <v>16634</v>
+        <v>22665</v>
       </c>
       <c r="X230" s="4" t="n"/>
       <c r="Y230" s="4" t="n"/>
@@ -11150,16 +11340,16 @@
     <row r="231">
       <c r="T231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U231" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V231" s="7" t="n">
-        <v>16721</v>
+        <v>22473</v>
       </c>
       <c r="X231" s="7" t="n"/>
       <c r="Y231" s="7" t="n"/>
@@ -11171,16 +11361,16 @@
     <row r="232">
       <c r="T232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U232" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V232" s="4" t="n">
-        <v>16586</v>
+        <v>22903</v>
       </c>
       <c r="X232" s="4" t="n"/>
       <c r="Y232" s="4" t="n"/>
@@ -11192,16 +11382,16 @@
     <row r="233">
       <c r="T233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U233" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V233" s="7" t="n">
-        <v>16419</v>
+        <v>21829</v>
       </c>
       <c r="X233" s="7" t="n"/>
       <c r="Y233" s="7" t="n"/>
@@ -11213,16 +11403,16 @@
     <row r="234">
       <c r="T234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U234" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V234" s="4" t="n">
-        <v>15946</v>
+        <v>20959</v>
       </c>
       <c r="X234" s="4" t="n"/>
       <c r="Y234" s="4" t="n"/>
@@ -11234,16 +11424,16 @@
     <row r="235">
       <c r="T235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U235" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V235" s="7" t="n">
-        <v>16042</v>
+        <v>20856</v>
       </c>
       <c r="X235" s="7" t="n"/>
       <c r="Y235" s="7" t="n"/>
@@ -11255,16 +11445,16 @@
     <row r="236">
       <c r="T236" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U236" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V236" s="4" t="n">
-        <v>16409</v>
+        <v>23061</v>
       </c>
       <c r="X236" s="4" t="n"/>
       <c r="Y236" s="4" t="n"/>
@@ -11276,16 +11466,16 @@
     <row r="237">
       <c r="T237" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U237" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V237" s="7" t="n">
-        <v>16831</v>
+        <v>21952</v>
       </c>
       <c r="X237" s="7" t="n"/>
       <c r="Y237" s="7" t="n"/>
@@ -11297,16 +11487,16 @@
     <row r="238">
       <c r="T238" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U238" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V238" s="4" t="n">
-        <v>16886</v>
+        <v>22608</v>
       </c>
       <c r="X238" s="4" t="n"/>
       <c r="Y238" s="4" t="n"/>
@@ -11318,7 +11508,7 @@
     <row r="239">
       <c r="T239" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U239" s="7" t="inlineStr">
@@ -11327,7 +11517,7 @@
         </is>
       </c>
       <c r="V239" s="7" t="n">
-        <v>16694</v>
+        <v>16634</v>
       </c>
       <c r="X239" s="7" t="n"/>
       <c r="Y239" s="7" t="n"/>
@@ -11339,7 +11529,7 @@
     <row r="240">
       <c r="T240" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U240" s="4" t="inlineStr">
@@ -11348,7 +11538,7 @@
         </is>
       </c>
       <c r="V240" s="4" t="n">
-        <v>16659</v>
+        <v>16721</v>
       </c>
       <c r="X240" s="4" t="n"/>
       <c r="Y240" s="4" t="n"/>
@@ -11360,7 +11550,7 @@
     <row r="241">
       <c r="T241" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U241" s="7" t="inlineStr">
@@ -11369,7 +11559,7 @@
         </is>
       </c>
       <c r="V241" s="7" t="n">
-        <v>16268</v>
+        <v>16586</v>
       </c>
       <c r="X241" s="7" t="n"/>
       <c r="Y241" s="7" t="n"/>
@@ -11381,7 +11571,7 @@
     <row r="242">
       <c r="T242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U242" s="4" t="inlineStr">
@@ -11390,7 +11580,7 @@
         </is>
       </c>
       <c r="V242" s="4" t="n">
-        <v>16259</v>
+        <v>16419</v>
       </c>
       <c r="X242" s="4" t="n"/>
       <c r="Y242" s="4" t="n"/>
@@ -11402,7 +11592,7 @@
     <row r="243">
       <c r="T243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U243" s="7" t="inlineStr">
@@ -11411,7 +11601,7 @@
         </is>
       </c>
       <c r="V243" s="7" t="n">
-        <v>16600</v>
+        <v>15946</v>
       </c>
       <c r="X243" s="7" t="n"/>
       <c r="Y243" s="7" t="n"/>
@@ -11423,7 +11613,7 @@
     <row r="244">
       <c r="T244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U244" s="4" t="inlineStr">
@@ -11432,7 +11622,7 @@
         </is>
       </c>
       <c r="V244" s="4" t="n">
-        <v>16913</v>
+        <v>16042</v>
       </c>
       <c r="X244" s="4" t="n"/>
       <c r="Y244" s="4" t="n"/>
@@ -11444,7 +11634,7 @@
     <row r="245">
       <c r="T245" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U245" s="7" t="inlineStr">
@@ -11453,7 +11643,7 @@
         </is>
       </c>
       <c r="V245" s="7" t="n">
-        <v>16991</v>
+        <v>16409</v>
       </c>
       <c r="X245" s="7" t="n"/>
       <c r="Y245" s="7" t="n"/>
@@ -11465,7 +11655,7 @@
     <row r="246">
       <c r="T246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U246" s="4" t="inlineStr">
@@ -11474,7 +11664,7 @@
         </is>
       </c>
       <c r="V246" s="4" t="n">
-        <v>17365</v>
+        <v>16831</v>
       </c>
       <c r="X246" s="4" t="n"/>
       <c r="Y246" s="4" t="n"/>
@@ -11486,7 +11676,7 @@
     <row r="247">
       <c r="T247" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U247" s="7" t="inlineStr">
@@ -11495,7 +11685,7 @@
         </is>
       </c>
       <c r="V247" s="7" t="n">
-        <v>16944</v>
+        <v>16886</v>
       </c>
       <c r="X247" s="7" t="n"/>
       <c r="Y247" s="7" t="n"/>
@@ -11507,7 +11697,7 @@
     <row r="248">
       <c r="T248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U248" s="4" t="inlineStr">
@@ -11516,7 +11706,7 @@
         </is>
       </c>
       <c r="V248" s="4" t="n">
-        <v>16518</v>
+        <v>16694</v>
       </c>
       <c r="X248" s="4" t="n"/>
       <c r="Y248" s="4" t="n"/>
@@ -11528,7 +11718,7 @@
     <row r="249">
       <c r="T249" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U249" s="7" t="inlineStr">
@@ -11537,7 +11727,7 @@
         </is>
       </c>
       <c r="V249" s="7" t="n">
-        <v>16634</v>
+        <v>16659</v>
       </c>
       <c r="X249" s="7" t="n"/>
       <c r="Y249" s="7" t="n"/>
@@ -11549,7 +11739,7 @@
     <row r="250">
       <c r="T250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U250" s="4" t="inlineStr">
@@ -11558,7 +11748,7 @@
         </is>
       </c>
       <c r="V250" s="4" t="n">
-        <v>16711</v>
+        <v>16268</v>
       </c>
       <c r="X250" s="4" t="n"/>
       <c r="Y250" s="4" t="n"/>
@@ -11570,7 +11760,7 @@
     <row r="251">
       <c r="T251" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U251" s="7" t="inlineStr">
@@ -11579,7 +11769,7 @@
         </is>
       </c>
       <c r="V251" s="7" t="n">
-        <v>17379</v>
+        <v>16259</v>
       </c>
       <c r="X251" s="7" t="n"/>
       <c r="Y251" s="7" t="n"/>
@@ -11591,7 +11781,7 @@
     <row r="252">
       <c r="T252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U252" s="4" t="inlineStr">
@@ -11600,7 +11790,7 @@
         </is>
       </c>
       <c r="V252" s="4" t="n">
-        <v>17551</v>
+        <v>16600</v>
       </c>
       <c r="X252" s="4" t="n"/>
       <c r="Y252" s="4" t="n"/>
@@ -11612,16 +11802,16 @@
     <row r="253">
       <c r="T253" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U253" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V253" s="7" t="n">
-        <v>724</v>
+        <v>16913</v>
       </c>
       <c r="X253" s="7" t="n"/>
       <c r="Y253" s="7" t="n"/>
@@ -11633,16 +11823,16 @@
     <row r="254">
       <c r="T254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U254" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V254" s="4" t="n">
-        <v>746</v>
+        <v>16991</v>
       </c>
       <c r="X254" s="4" t="n"/>
       <c r="Y254" s="4" t="n"/>
@@ -11654,16 +11844,16 @@
     <row r="255">
       <c r="T255" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U255" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V255" s="7" t="n">
-        <v>723</v>
+        <v>17365</v>
       </c>
       <c r="X255" s="7" t="n"/>
       <c r="Y255" s="7" t="n"/>
@@ -11675,16 +11865,16 @@
     <row r="256">
       <c r="T256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U256" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V256" s="4" t="n">
-        <v>708</v>
+        <v>16944</v>
       </c>
       <c r="X256" s="4" t="n"/>
       <c r="Y256" s="4" t="n"/>
@@ -11696,16 +11886,16 @@
     <row r="257">
       <c r="T257" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U257" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V257" s="7" t="n">
-        <v>735</v>
+        <v>16518</v>
       </c>
       <c r="X257" s="7" t="n"/>
       <c r="Y257" s="7" t="n"/>
@@ -11717,16 +11907,16 @@
     <row r="258">
       <c r="T258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U258" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V258" s="4" t="n">
-        <v>714</v>
+        <v>16634</v>
       </c>
       <c r="X258" s="4" t="n"/>
       <c r="Y258" s="4" t="n"/>
@@ -11738,16 +11928,16 @@
     <row r="259">
       <c r="T259" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U259" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V259" s="7" t="n">
-        <v>706</v>
+        <v>16711</v>
       </c>
       <c r="X259" s="7" t="n"/>
       <c r="Y259" s="7" t="n"/>
@@ -11759,16 +11949,16 @@
     <row r="260">
       <c r="T260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U260" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V260" s="4" t="n">
-        <v>729</v>
+        <v>17379</v>
       </c>
       <c r="X260" s="4" t="n"/>
       <c r="Y260" s="4" t="n"/>
@@ -11780,16 +11970,16 @@
     <row r="261">
       <c r="T261" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U261" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V261" s="7" t="n">
-        <v>719</v>
+        <v>17551</v>
       </c>
       <c r="X261" s="7" t="n"/>
       <c r="Y261" s="7" t="n"/>
@@ -11801,16 +11991,16 @@
     <row r="262">
       <c r="T262" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U262" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V262" s="4" t="n">
-        <v>719</v>
+        <v>17474</v>
       </c>
       <c r="X262" s="4" t="n"/>
       <c r="Y262" s="4" t="n"/>
@@ -11822,7 +12012,7 @@
     <row r="263">
       <c r="T263" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U263" s="7" t="inlineStr">
@@ -11831,7 +12021,7 @@
         </is>
       </c>
       <c r="V263" s="7" t="n">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="X263" s="7" t="n"/>
       <c r="Y263" s="7" t="n"/>
@@ -11843,7 +12033,7 @@
     <row r="264">
       <c r="T264" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U264" s="4" t="inlineStr">
@@ -11852,7 +12042,7 @@
         </is>
       </c>
       <c r="V264" s="4" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="X264" s="4" t="n"/>
       <c r="Y264" s="4" t="n"/>
@@ -11864,7 +12054,7 @@
     <row r="265">
       <c r="T265" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U265" s="7" t="inlineStr">
@@ -11873,7 +12063,7 @@
         </is>
       </c>
       <c r="V265" s="7" t="n">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="X265" s="7" t="n"/>
       <c r="Y265" s="7" t="n"/>
@@ -11885,7 +12075,7 @@
     <row r="266">
       <c r="T266" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U266" s="4" t="inlineStr">
@@ -11894,7 +12084,7 @@
         </is>
       </c>
       <c r="V266" s="4" t="n">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="X266" s="4" t="n"/>
       <c r="Y266" s="4" t="n"/>
@@ -11906,7 +12096,7 @@
     <row r="267">
       <c r="T267" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U267" s="7" t="inlineStr">
@@ -11915,7 +12105,7 @@
         </is>
       </c>
       <c r="V267" s="7" t="n">
-        <v>691</v>
+        <v>735</v>
       </c>
       <c r="X267" s="7" t="n"/>
       <c r="Y267" s="7" t="n"/>
@@ -11927,7 +12117,7 @@
     <row r="268">
       <c r="T268" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U268" s="4" t="inlineStr">
@@ -11936,7 +12126,7 @@
         </is>
       </c>
       <c r="V268" s="4" t="n">
-        <v>695</v>
+        <v>714</v>
       </c>
       <c r="X268" s="4" t="n"/>
       <c r="Y268" s="4" t="n"/>
@@ -11948,7 +12138,7 @@
     <row r="269">
       <c r="T269" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U269" s="7" t="inlineStr">
@@ -11969,7 +12159,7 @@
     <row r="270">
       <c r="T270" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U270" s="4" t="inlineStr">
@@ -11978,7 +12168,7 @@
         </is>
       </c>
       <c r="V270" s="4" t="n">
-        <v>701</v>
+        <v>729</v>
       </c>
       <c r="X270" s="4" t="n"/>
       <c r="Y270" s="4" t="n"/>
@@ -11990,7 +12180,7 @@
     <row r="271">
       <c r="T271" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U271" s="7" t="inlineStr">
@@ -11999,7 +12189,7 @@
         </is>
       </c>
       <c r="V271" s="7" t="n">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="X271" s="7" t="n"/>
       <c r="Y271" s="7" t="n"/>
@@ -12011,7 +12201,7 @@
     <row r="272">
       <c r="T272" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U272" s="4" t="inlineStr">
@@ -12020,7 +12210,7 @@
         </is>
       </c>
       <c r="V272" s="4" t="n">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="X272" s="4" t="n"/>
       <c r="Y272" s="4" t="n"/>
@@ -12032,7 +12222,7 @@
     <row r="273">
       <c r="T273" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U273" s="7" t="inlineStr">
@@ -12041,7 +12231,7 @@
         </is>
       </c>
       <c r="V273" s="7" t="n">
-        <v>670</v>
+        <v>730</v>
       </c>
       <c r="X273" s="7" t="n"/>
       <c r="Y273" s="7" t="n"/>
@@ -12053,7 +12243,7 @@
     <row r="274">
       <c r="T274" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U274" s="4" t="inlineStr">
@@ -12062,7 +12252,7 @@
         </is>
       </c>
       <c r="V274" s="4" t="n">
-        <v>694</v>
+        <v>740</v>
       </c>
       <c r="X274" s="4" t="n"/>
       <c r="Y274" s="4" t="n"/>
@@ -12074,7 +12264,7 @@
     <row r="275">
       <c r="T275" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U275" s="7" t="inlineStr">
@@ -12083,7 +12273,7 @@
         </is>
       </c>
       <c r="V275" s="7" t="n">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="X275" s="7" t="n"/>
       <c r="Y275" s="7" t="n"/>
@@ -12095,16 +12285,16 @@
     <row r="276">
       <c r="T276" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U276" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V276" s="4" t="n">
-        <v>2188</v>
+        <v>698</v>
       </c>
       <c r="X276" s="4" t="n"/>
       <c r="Y276" s="4" t="n"/>
@@ -12116,16 +12306,16 @@
     <row r="277">
       <c r="T277" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U277" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V277" s="7" t="n">
-        <v>2046</v>
+        <v>691</v>
       </c>
       <c r="X277" s="7" t="n"/>
       <c r="Y277" s="7" t="n"/>
@@ -12137,16 +12327,16 @@
     <row r="278">
       <c r="T278" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U278" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V278" s="4" t="n">
-        <v>2338</v>
+        <v>695</v>
       </c>
       <c r="X278" s="4" t="n"/>
       <c r="Y278" s="4" t="n"/>
@@ -12158,16 +12348,16 @@
     <row r="279">
       <c r="T279" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U279" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V279" s="7" t="n">
-        <v>2152</v>
+        <v>706</v>
       </c>
       <c r="X279" s="7" t="n"/>
       <c r="Y279" s="7" t="n"/>
@@ -12179,16 +12369,16 @@
     <row r="280">
       <c r="T280" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U280" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V280" s="4" t="n">
-        <v>2003</v>
+        <v>701</v>
       </c>
       <c r="X280" s="4" t="n"/>
       <c r="Y280" s="4" t="n"/>
@@ -12200,16 +12390,16 @@
     <row r="281">
       <c r="T281" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U281" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V281" s="7" t="n">
-        <v>1895</v>
+        <v>706</v>
       </c>
       <c r="X281" s="7" t="n"/>
       <c r="Y281" s="7" t="n"/>
@@ -12221,16 +12411,16 @@
     <row r="282">
       <c r="T282" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U282" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V282" s="4" t="n">
-        <v>1935</v>
+        <v>704</v>
       </c>
       <c r="X282" s="4" t="n"/>
       <c r="Y282" s="4" t="n"/>
@@ -12242,16 +12432,16 @@
     <row r="283">
       <c r="T283" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U283" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V283" s="7" t="n">
-        <v>2037</v>
+        <v>670</v>
       </c>
       <c r="X283" s="7" t="n"/>
       <c r="Y283" s="7" t="n"/>
@@ -12263,16 +12453,16 @@
     <row r="284">
       <c r="T284" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U284" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V284" s="4" t="n">
-        <v>2049</v>
+        <v>694</v>
       </c>
       <c r="X284" s="4" t="n"/>
       <c r="Y284" s="4" t="n"/>
@@ -12284,16 +12474,16 @@
     <row r="285">
       <c r="T285" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U285" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V285" s="7" t="n">
-        <v>2325</v>
+        <v>702</v>
       </c>
       <c r="X285" s="7" t="n"/>
       <c r="Y285" s="7" t="n"/>
@@ -12305,16 +12495,16 @@
     <row r="286">
       <c r="T286" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U286" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V286" s="4" t="n">
-        <v>2216</v>
+        <v>708</v>
       </c>
       <c r="X286" s="4" t="n"/>
       <c r="Y286" s="4" t="n"/>
@@ -12326,7 +12516,7 @@
     <row r="287">
       <c r="T287" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U287" s="7" t="inlineStr">
@@ -12335,7 +12525,7 @@
         </is>
       </c>
       <c r="V287" s="7" t="n">
-        <v>2037</v>
+        <v>2188</v>
       </c>
       <c r="X287" s="7" t="n"/>
       <c r="Y287" s="7" t="n"/>
@@ -12347,7 +12537,7 @@
     <row r="288">
       <c r="T288" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U288" s="4" t="inlineStr">
@@ -12368,7 +12558,7 @@
     <row r="289">
       <c r="T289" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U289" s="7" t="inlineStr">
@@ -12377,7 +12567,7 @@
         </is>
       </c>
       <c r="V289" s="7" t="n">
-        <v>2035</v>
+        <v>2338</v>
       </c>
       <c r="X289" s="7" t="n"/>
       <c r="Y289" s="7" t="n"/>
@@ -12389,7 +12579,7 @@
     <row r="290">
       <c r="T290" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U290" s="4" t="inlineStr">
@@ -12398,7 +12588,7 @@
         </is>
       </c>
       <c r="V290" s="4" t="n">
-        <v>2182</v>
+        <v>2152</v>
       </c>
       <c r="X290" s="4" t="n"/>
       <c r="Y290" s="4" t="n"/>
@@ -12410,7 +12600,7 @@
     <row r="291">
       <c r="T291" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U291" s="7" t="inlineStr">
@@ -12419,7 +12609,7 @@
         </is>
       </c>
       <c r="V291" s="7" t="n">
-        <v>2156</v>
+        <v>2003</v>
       </c>
       <c r="X291" s="7" t="n"/>
       <c r="Y291" s="7" t="n"/>
@@ -12431,7 +12621,7 @@
     <row r="292">
       <c r="T292" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U292" s="4" t="inlineStr">
@@ -12440,7 +12630,7 @@
         </is>
       </c>
       <c r="V292" s="4" t="n">
-        <v>2437</v>
+        <v>1895</v>
       </c>
       <c r="X292" s="4" t="n"/>
       <c r="Y292" s="4" t="n"/>
@@ -12452,7 +12642,7 @@
     <row r="293">
       <c r="T293" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U293" s="7" t="inlineStr">
@@ -12461,7 +12651,7 @@
         </is>
       </c>
       <c r="V293" s="7" t="n">
-        <v>2214</v>
+        <v>1935</v>
       </c>
       <c r="X293" s="7" t="n"/>
       <c r="Y293" s="7" t="n"/>
@@ -12473,7 +12663,7 @@
     <row r="294">
       <c r="T294" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U294" s="4" t="inlineStr">
@@ -12482,7 +12672,7 @@
         </is>
       </c>
       <c r="V294" s="4" t="n">
-        <v>2200</v>
+        <v>2037</v>
       </c>
       <c r="X294" s="4" t="n"/>
       <c r="Y294" s="4" t="n"/>
@@ -12494,7 +12684,7 @@
     <row r="295">
       <c r="T295" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U295" s="7" t="inlineStr">
@@ -12503,7 +12693,7 @@
         </is>
       </c>
       <c r="V295" s="7" t="n">
-        <v>1973</v>
+        <v>2049</v>
       </c>
       <c r="X295" s="7" t="n"/>
       <c r="Y295" s="7" t="n"/>
@@ -12515,7 +12705,7 @@
     <row r="296">
       <c r="T296" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U296" s="4" t="inlineStr">
@@ -12524,7 +12714,7 @@
         </is>
       </c>
       <c r="V296" s="4" t="n">
-        <v>1980</v>
+        <v>2325</v>
       </c>
       <c r="X296" s="4" t="n"/>
       <c r="Y296" s="4" t="n"/>
@@ -12536,7 +12726,7 @@
     <row r="297">
       <c r="T297" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U297" s="7" t="inlineStr">
@@ -12545,7 +12735,7 @@
         </is>
       </c>
       <c r="V297" s="7" t="n">
-        <v>2075</v>
+        <v>2216</v>
       </c>
       <c r="X297" s="7" t="n"/>
       <c r="Y297" s="7" t="n"/>
@@ -12557,7 +12747,7 @@
     <row r="298">
       <c r="T298" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U298" s="4" t="inlineStr">
@@ -12566,7 +12756,7 @@
         </is>
       </c>
       <c r="V298" s="4" t="n">
-        <v>2191</v>
+        <v>2037</v>
       </c>
       <c r="X298" s="4" t="n"/>
       <c r="Y298" s="4" t="n"/>
@@ -12574,6 +12764,258 @@
       <c r="AB298" s="4" t="n"/>
       <c r="AC298" s="4" t="n"/>
       <c r="AD298" s="4" t="n"/>
+    </row>
+    <row r="299">
+      <c r="T299" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U299" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V299" s="7" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X299" s="7" t="n"/>
+      <c r="Y299" s="7" t="n"/>
+      <c r="Z299" s="7" t="n"/>
+      <c r="AB299" s="7" t="n"/>
+      <c r="AC299" s="7" t="n"/>
+      <c r="AD299" s="7" t="n"/>
+    </row>
+    <row r="300">
+      <c r="T300" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="U300" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V300" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="X300" s="4" t="n"/>
+      <c r="Y300" s="4" t="n"/>
+      <c r="Z300" s="4" t="n"/>
+      <c r="AB300" s="4" t="n"/>
+      <c r="AC300" s="4" t="n"/>
+      <c r="AD300" s="4" t="n"/>
+    </row>
+    <row r="301">
+      <c r="T301" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U301" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V301" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="X301" s="7" t="n"/>
+      <c r="Y301" s="7" t="n"/>
+      <c r="Z301" s="7" t="n"/>
+      <c r="AB301" s="7" t="n"/>
+      <c r="AC301" s="7" t="n"/>
+      <c r="AD301" s="7" t="n"/>
+    </row>
+    <row r="302">
+      <c r="T302" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="U302" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V302" s="4" t="n">
+        <v>2156</v>
+      </c>
+      <c r="X302" s="4" t="n"/>
+      <c r="Y302" s="4" t="n"/>
+      <c r="Z302" s="4" t="n"/>
+      <c r="AB302" s="4" t="n"/>
+      <c r="AC302" s="4" t="n"/>
+      <c r="AD302" s="4" t="n"/>
+    </row>
+    <row r="303">
+      <c r="T303" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="U303" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V303" s="7" t="n">
+        <v>2437</v>
+      </c>
+      <c r="X303" s="7" t="n"/>
+      <c r="Y303" s="7" t="n"/>
+      <c r="Z303" s="7" t="n"/>
+      <c r="AB303" s="7" t="n"/>
+      <c r="AC303" s="7" t="n"/>
+      <c r="AD303" s="7" t="n"/>
+    </row>
+    <row r="304">
+      <c r="T304" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="U304" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V304" s="4" t="n">
+        <v>2214</v>
+      </c>
+      <c r="X304" s="4" t="n"/>
+      <c r="Y304" s="4" t="n"/>
+      <c r="Z304" s="4" t="n"/>
+      <c r="AB304" s="4" t="n"/>
+      <c r="AC304" s="4" t="n"/>
+      <c r="AD304" s="4" t="n"/>
+    </row>
+    <row r="305">
+      <c r="T305" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U305" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V305" s="7" t="n">
+        <v>2200</v>
+      </c>
+      <c r="X305" s="7" t="n"/>
+      <c r="Y305" s="7" t="n"/>
+      <c r="Z305" s="7" t="n"/>
+      <c r="AB305" s="7" t="n"/>
+      <c r="AC305" s="7" t="n"/>
+      <c r="AD305" s="7" t="n"/>
+    </row>
+    <row r="306">
+      <c r="T306" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U306" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V306" s="4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="X306" s="4" t="n"/>
+      <c r="Y306" s="4" t="n"/>
+      <c r="Z306" s="4" t="n"/>
+      <c r="AB306" s="4" t="n"/>
+      <c r="AC306" s="4" t="n"/>
+      <c r="AD306" s="4" t="n"/>
+    </row>
+    <row r="307">
+      <c r="T307" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U307" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V307" s="7" t="n">
+        <v>1980</v>
+      </c>
+      <c r="X307" s="7" t="n"/>
+      <c r="Y307" s="7" t="n"/>
+      <c r="Z307" s="7" t="n"/>
+      <c r="AB307" s="7" t="n"/>
+      <c r="AC307" s="7" t="n"/>
+      <c r="AD307" s="7" t="n"/>
+    </row>
+    <row r="308">
+      <c r="T308" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U308" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V308" s="4" t="n">
+        <v>2075</v>
+      </c>
+      <c r="X308" s="4" t="n"/>
+      <c r="Y308" s="4" t="n"/>
+      <c r="Z308" s="4" t="n"/>
+      <c r="AB308" s="4" t="n"/>
+      <c r="AC308" s="4" t="n"/>
+      <c r="AD308" s="4" t="n"/>
+    </row>
+    <row r="309">
+      <c r="T309" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="U309" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V309" s="7" t="n">
+        <v>2191</v>
+      </c>
+      <c r="X309" s="7" t="n"/>
+      <c r="Y309" s="7" t="n"/>
+      <c r="Z309" s="7" t="n"/>
+      <c r="AB309" s="7" t="n"/>
+      <c r="AC309" s="7" t="n"/>
+      <c r="AD309" s="7" t="n"/>
+    </row>
+    <row r="310">
+      <c r="T310" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="U310" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V310" s="4" t="n">
+        <v>2328</v>
+      </c>
+      <c r="X310" s="4" t="n"/>
+      <c r="Y310" s="4" t="n"/>
+      <c r="Z310" s="4" t="n"/>
+      <c r="AB310" s="4" t="n"/>
+      <c r="AC310" s="4" t="n"/>
+      <c r="AD310" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -716,10 +716,10 @@
         <v>0.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -752,10 +752,10 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -788,10 +788,10 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -824,10 +824,10 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -860,10 +860,10 @@
         <v>0.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -896,10 +896,10 @@
         <v>0.95</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -932,10 +932,10 @@
         <v>0.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -968,10 +968,10 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1004,10 +1004,10 @@
         <v>0.95</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1040,10 +1040,10 @@
         <v>0.95</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD310"/>
+  <dimension ref="A1:AD218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1344,15 +1344,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>103</v>
       </c>
@@ -1429,15 +1423,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>13</v>
       </c>
@@ -1514,15 +1502,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>64</v>
       </c>
@@ -1593,15 +1575,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>30</v>
       </c>
@@ -1678,15 +1654,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>21</v>
       </c>
@@ -1763,15 +1733,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>73</v>
       </c>
@@ -1848,15 +1812,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>15</v>
       </c>
@@ -1927,15 +1885,9 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>1</v>
       </c>
@@ -2014,15 +1966,9 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>105</v>
       </c>
@@ -2093,15 +2039,9 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>19</v>
       </c>
@@ -2172,15 +2112,9 @@
         <f>$B$2+H12+M12</f>
         <v/>
       </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>82</v>
       </c>
@@ -2251,15 +2185,9 @@
         <f>$B$2+H13+M13</f>
         <v/>
       </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>25</v>
       </c>
@@ -2330,15 +2258,9 @@
         <f>$B$2+H14+M14</f>
         <v/>
       </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>15</v>
       </c>
@@ -2409,15 +2331,9 @@
         <f>$B$2+H15+M15</f>
         <v/>
       </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>75</v>
       </c>
@@ -2488,15 +2404,9 @@
         <f>$B$2+H16+M16</f>
         <v/>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>9</v>
       </c>
@@ -2567,15 +2477,9 @@
         <f>$B$2+H17+M17</f>
         <v/>
       </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>1</v>
       </c>
@@ -2646,15 +2550,9 @@
         <f>$B$2+H18+M18</f>
         <v/>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>145</v>
       </c>
@@ -2725,15 +2623,9 @@
         <f>$B$2+H19+M19</f>
         <v/>
       </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>19</v>
       </c>
@@ -2804,15 +2696,9 @@
         <f>$B$2+H20+M20</f>
         <v/>
       </c>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>74</v>
       </c>
@@ -2883,15 +2769,9 @@
         <f>$B$2+H21+M21</f>
         <v/>
       </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr"/>
-      <c r="V21" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>26</v>
       </c>
@@ -2962,15 +2842,9 @@
         <f>$B$2+H22+M22</f>
         <v/>
       </c>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>9</v>
       </c>
@@ -3041,15 +2915,9 @@
         <f>$B$2+H23+M23</f>
         <v/>
       </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr"/>
-      <c r="V23" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
         <v>74</v>
       </c>
@@ -3120,15 +2988,9 @@
         <f>$B$2+H24+M24</f>
         <v/>
       </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
         <v>11</v>
       </c>
@@ -3199,15 +3061,9 @@
         <f>$B$2+H25+M25</f>
         <v/>
       </c>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr"/>
-      <c r="V25" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>101</v>
       </c>
@@ -3254,19 +3110,9 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>5365</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
         <v>11</v>
       </c>
@@ -3313,19 +3159,9 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>5741</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
         <v>73</v>
       </c>
@@ -3372,19 +3208,9 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>5451</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
         <v>31</v>
       </c>
@@ -3431,19 +3257,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>5458</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>13</v>
       </c>
@@ -3490,19 +3306,9 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>5664</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
         <v>78</v>
       </c>
@@ -3549,19 +3355,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>5241</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
@@ -3617,19 +3413,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>5102</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>9</v>
       </c>
@@ -3690,19 +3476,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>5388</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
@@ -3731,19 +3507,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>119</v>
       </c>
@@ -3772,19 +3538,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>5348</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>13</v>
       </c>
@@ -3813,19 +3569,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>5329</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>67</v>
       </c>
@@ -3854,19 +3600,9 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>5436</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
         <v>32</v>
       </c>
@@ -3895,19 +3631,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>5081</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
         <v>13</v>
       </c>
@@ -3936,19 +3662,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>5034</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>93</v>
       </c>
@@ -3977,19 +3693,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>12</v>
       </c>
@@ -4018,19 +3724,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>5513</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>2</v>
       </c>
@@ -4059,19 +3755,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>5477</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>113</v>
       </c>
@@ -4100,19 +3786,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>5526</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>12</v>
       </c>
@@ -4141,19 +3817,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>69</v>
       </c>
@@ -4182,19 +3848,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>4933</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>40</v>
       </c>
@@ -4223,19 +3879,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>4866</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>17</v>
       </c>
@@ -4264,19 +3910,9 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>5232</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>83</v>
       </c>
@@ -4305,19 +3941,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>5576</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>9</v>
       </c>
@@ -4346,19 +3972,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>5287</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>124</v>
       </c>
@@ -4387,19 +4003,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>14969</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>19</v>
       </c>
@@ -4428,19 +4034,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>14818</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>55</v>
       </c>
@@ -4469,19 +4065,9 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>15263</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
         <v>35</v>
       </c>
@@ -4510,19 +4096,9 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>15</v>
       </c>
@@ -4551,19 +4127,9 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>14968</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>82</v>
       </c>
@@ -4592,19 +4158,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>14113</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>1</v>
       </c>
@@ -4633,19 +4189,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>14162</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>14</v>
       </c>
@@ -4674,19 +4220,9 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>2</v>
       </c>
@@ -4715,19 +4251,9 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
         <v>101</v>
       </c>
@@ -4756,19 +4282,9 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>15546</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
         <v>10</v>
       </c>
@@ -4797,19 +4313,9 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>14882</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
         <v>72</v>
       </c>
@@ -4838,19 +4344,9 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>14998</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
         <v>35</v>
       </c>
@@ -4879,19 +4375,9 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>14354</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
         <v>13</v>
       </c>
@@ -4920,19 +4406,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>14362</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>71</v>
       </c>
@@ -4961,19 +4437,9 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>15089</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
         <v>8</v>
       </c>
@@ -5002,19 +4468,9 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>14802</v>
-      </c>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
         <v>2</v>
       </c>
@@ -5043,19 +4499,9 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>15349</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>125</v>
       </c>
@@ -5084,19 +4530,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>14872</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>11</v>
       </c>
@@ -5125,19 +4561,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>15054</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>67</v>
       </c>
@@ -5166,19 +4592,9 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>14169</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>27</v>
       </c>
@@ -5207,19 +4623,9 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>14056</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
         <v>17</v>
       </c>
@@ -5248,19 +4654,9 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>15058</v>
-      </c>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
         <v>85</v>
       </c>
@@ -5289,19 +4685,9 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>14814</v>
-      </c>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
         <v>14</v>
       </c>
@@ -5330,19 +4716,9 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>15440</v>
-      </c>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
         <v>4</v>
       </c>
@@ -5371,19 +4747,9 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>77546</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
         <v>126</v>
       </c>
@@ -5412,19 +4778,9 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>77823</v>
-      </c>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
         <v>23</v>
       </c>
@@ -5453,19 +4809,9 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>81723</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>65</v>
       </c>
@@ -5494,19 +4840,9 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>78398</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
         <v>28</v>
       </c>
@@ -5535,19 +4871,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>78030</v>
-      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
         <v>19</v>
       </c>
@@ -5576,19 +4902,9 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>76646</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>91</v>
       </c>
@@ -5617,19 +4933,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>76742</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>21</v>
       </c>
@@ -5658,19 +4964,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>79003</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
         <v>2</v>
       </c>
@@ -5699,19 +4995,9 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>78849</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
         <v>99</v>
       </c>
@@ -5740,19 +5026,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>80667</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>12</v>
       </c>
@@ -5781,19 +5057,9 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>78640</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
         <v>70</v>
       </c>
@@ -5822,19 +5088,9 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>79108</v>
-      </c>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
         <v>30</v>
       </c>
@@ -5863,19 +5119,9 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>76911</v>
-      </c>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
         <v>15</v>
       </c>
@@ -5904,19 +5150,9 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>77273</v>
-      </c>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
         <v>73</v>
       </c>
@@ -5945,19 +5181,9 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>80657</v>
-      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
         <v>5</v>
       </c>
@@ -5986,19 +5212,9 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>79898</v>
-      </c>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
         <v>1</v>
       </c>
@@ -6027,19 +5243,9 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>82443</v>
-      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
         <v>107</v>
       </c>
@@ -6068,19 +5274,9 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>80658</v>
-      </c>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
         <v>13</v>
       </c>
@@ -6109,19 +5305,9 @@
       </c>
     </row>
     <row r="92">
-      <c r="T92" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V92" s="4" t="n">
-        <v>78475</v>
-      </c>
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
       <c r="X92" s="4" t="n">
         <v>56</v>
       </c>
@@ -6150,19 +5336,9 @@
       </c>
     </row>
     <row r="93">
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U93" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>76874</v>
-      </c>
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
         <v>32</v>
       </c>
@@ -6191,19 +5367,9 @@
       </c>
     </row>
     <row r="94">
-      <c r="T94" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>77058</v>
-      </c>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
         <v>13</v>
       </c>
@@ -6232,19 +5398,9 @@
       </c>
     </row>
     <row r="95">
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>79206</v>
-      </c>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
         <v>78</v>
       </c>
@@ -6273,19 +5429,9 @@
       </c>
     </row>
     <row r="96">
-      <c r="T96" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V96" s="4" t="n">
-        <v>79070</v>
-      </c>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
       <c r="X96" s="4" t="n">
         <v>10</v>
       </c>
@@ -6314,19 +5460,9 @@
       </c>
     </row>
     <row r="97">
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V97" s="7" t="n">
-        <v>81246</v>
-      </c>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
         <v>1</v>
       </c>
@@ -6355,19 +5491,9 @@
       </c>
     </row>
     <row r="98">
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
         <v>114</v>
       </c>
@@ -6396,19 +5522,9 @@
       </c>
     </row>
     <row r="99">
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V99" s="7" t="n">
-        <v>715</v>
-      </c>
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
         <v>15</v>
       </c>
@@ -6437,19 +5553,9 @@
       </c>
     </row>
     <row r="100">
-      <c r="T100" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>745</v>
-      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
         <v>53</v>
       </c>
@@ -6478,19 +5584,9 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U101" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V101" s="7" t="n">
-        <v>702</v>
-      </c>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
         <v>32</v>
       </c>
@@ -6519,19 +5615,9 @@
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n">
-        <v>743</v>
-      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
         <v>14</v>
       </c>
@@ -6560,19 +5646,9 @@
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V103" s="7" t="n">
-        <v>700</v>
-      </c>
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
         <v>80</v>
       </c>
@@ -6601,19 +5677,9 @@
       </c>
     </row>
     <row r="104">
-      <c r="T104" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U104" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V104" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="4" t="n"/>
+      <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
         <v>1</v>
       </c>
@@ -6642,19 +5708,9 @@
       </c>
     </row>
     <row r="105">
-      <c r="T105" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U105" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>750</v>
-      </c>
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
         <v>9</v>
       </c>
@@ -6683,19 +5739,9 @@
       </c>
     </row>
     <row r="106">
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="n">
-        <v>729</v>
-      </c>
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="4" t="n"/>
+      <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
         <v>4</v>
       </c>
@@ -6724,19 +5770,9 @@
       </c>
     </row>
     <row r="107">
-      <c r="T107" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U107" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V107" s="7" t="n">
-        <v>748</v>
-      </c>
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
         <v>97</v>
       </c>
@@ -6765,19 +5801,9 @@
       </c>
     </row>
     <row r="108">
-      <c r="T108" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U108" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V108" s="4" t="n">
-        <v>736</v>
-      </c>
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="4" t="n"/>
+      <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
         <v>10</v>
       </c>
@@ -6806,19 +5832,9 @@
       </c>
     </row>
     <row r="109">
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U109" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V109" s="7" t="n">
-        <v>737</v>
-      </c>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
         <v>52</v>
       </c>
@@ -6847,19 +5863,9 @@
       </c>
     </row>
     <row r="110">
-      <c r="T110" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U110" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V110" s="4" t="n">
-        <v>707</v>
-      </c>
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="n"/>
       <c r="X110" s="4" t="n">
         <v>37</v>
       </c>
@@ -6888,19 +5894,9 @@
       </c>
     </row>
     <row r="111">
-      <c r="T111" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U111" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V111" s="7" t="n">
-        <v>713</v>
-      </c>
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
       <c r="X111" s="7" t="n">
         <v>18</v>
       </c>
@@ -6929,19 +5925,9 @@
       </c>
     </row>
     <row r="112">
-      <c r="T112" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U112" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V112" s="4" t="n">
-        <v>786</v>
-      </c>
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="4" t="n"/>
+      <c r="V112" s="4" t="n"/>
       <c r="X112" s="4" t="n">
         <v>64</v>
       </c>
@@ -6970,19 +5956,9 @@
       </c>
     </row>
     <row r="113">
-      <c r="T113" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U113" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V113" s="7" t="n">
-        <v>730</v>
-      </c>
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
         <v>7</v>
       </c>
@@ -7011,19 +5987,9 @@
       </c>
     </row>
     <row r="114">
-      <c r="T114" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U114" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V114" s="4" t="n">
-        <v>726</v>
-      </c>
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="n"/>
       <c r="X114" s="4" t="n">
         <v>106</v>
       </c>
@@ -7052,19 +6018,9 @@
       </c>
     </row>
     <row r="115">
-      <c r="T115" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U115" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V115" s="7" t="n">
-        <v>695</v>
-      </c>
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
       <c r="X115" s="7" t="n">
         <v>14</v>
       </c>
@@ -7093,19 +6049,9 @@
       </c>
     </row>
     <row r="116">
-      <c r="T116" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U116" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V116" s="4" t="n">
-        <v>693</v>
-      </c>
+      <c r="T116" s="4" t="n"/>
+      <c r="U116" s="4" t="n"/>
+      <c r="V116" s="4" t="n"/>
       <c r="X116" s="4" t="n">
         <v>65</v>
       </c>
@@ -7134,19 +6080,9 @@
       </c>
     </row>
     <row r="117">
-      <c r="T117" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U117" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V117" s="7" t="n">
-        <v>686</v>
-      </c>
+      <c r="T117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
       <c r="X117" s="7" t="n">
         <v>24</v>
       </c>
@@ -7175,19 +6111,9 @@
       </c>
     </row>
     <row r="118">
-      <c r="T118" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U118" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V118" s="4" t="n">
-        <v>673</v>
-      </c>
+      <c r="T118" s="4" t="n"/>
+      <c r="U118" s="4" t="n"/>
+      <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
         <v>14</v>
       </c>
@@ -7216,19 +6142,9 @@
       </c>
     </row>
     <row r="119">
-      <c r="T119" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U119" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V119" s="7" t="n">
-        <v>752</v>
-      </c>
+      <c r="T119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
         <v>66</v>
       </c>
@@ -7257,19 +6173,9 @@
       </c>
     </row>
     <row r="120">
-      <c r="T120" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U120" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="n">
-        <v>717</v>
-      </c>
+      <c r="T120" s="4" t="n"/>
+      <c r="U120" s="4" t="n"/>
+      <c r="V120" s="4" t="n"/>
       <c r="X120" s="4" t="n">
         <v>1</v>
       </c>
@@ -7298,19 +6204,9 @@
       </c>
     </row>
     <row r="121">
-      <c r="T121" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U121" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>706</v>
-      </c>
+      <c r="T121" s="7" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
       <c r="X121" s="7" t="n">
         <v>9</v>
       </c>
@@ -7339,19 +6235,9 @@
       </c>
     </row>
     <row r="122">
-      <c r="T122" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U122" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V122" s="4" t="n">
-        <v>47976</v>
-      </c>
+      <c r="T122" s="4" t="n"/>
+      <c r="U122" s="4" t="n"/>
+      <c r="V122" s="4" t="n"/>
       <c r="X122" s="4" t="n">
         <v>116</v>
       </c>
@@ -7380,19 +6266,9 @@
       </c>
     </row>
     <row r="123">
-      <c r="T123" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U123" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V123" s="7" t="n">
-        <v>47122</v>
-      </c>
+      <c r="T123" s="7" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
       <c r="X123" s="7" t="n">
         <v>17</v>
       </c>
@@ -7421,19 +6297,9 @@
       </c>
     </row>
     <row r="124">
-      <c r="T124" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U124" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="n">
-        <v>47233</v>
-      </c>
+      <c r="T124" s="4" t="n"/>
+      <c r="U124" s="4" t="n"/>
+      <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
         <v>52</v>
       </c>
@@ -7462,19 +6328,9 @@
       </c>
     </row>
     <row r="125">
-      <c r="T125" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V125" s="7" t="n">
-        <v>48580</v>
-      </c>
+      <c r="T125" s="7" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
         <v>38</v>
       </c>
@@ -7503,19 +6359,9 @@
       </c>
     </row>
     <row r="126">
-      <c r="T126" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U126" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V126" s="4" t="n">
-        <v>47383</v>
-      </c>
+      <c r="T126" s="4" t="n"/>
+      <c r="U126" s="4" t="n"/>
+      <c r="V126" s="4" t="n"/>
       <c r="X126" s="4" t="n">
         <v>19</v>
       </c>
@@ -7544,19 +6390,9 @@
       </c>
     </row>
     <row r="127">
-      <c r="T127" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U127" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V127" s="7" t="n">
-        <v>46456</v>
-      </c>
+      <c r="T127" s="7" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
       <c r="X127" s="7" t="n">
         <v>79</v>
       </c>
@@ -7585,19 +6421,9 @@
       </c>
     </row>
     <row r="128">
-      <c r="T128" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U128" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V128" s="4" t="n">
-        <v>46400</v>
-      </c>
+      <c r="T128" s="4" t="n"/>
+      <c r="U128" s="4" t="n"/>
+      <c r="V128" s="4" t="n"/>
       <c r="X128" s="4" t="n">
         <v>9</v>
       </c>
@@ -7626,19 +6452,9 @@
       </c>
     </row>
     <row r="129">
-      <c r="T129" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U129" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V129" s="7" t="n">
-        <v>47755</v>
-      </c>
+      <c r="T129" s="7" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
       <c r="X129" s="7" t="n">
         <v>1</v>
       </c>
@@ -7667,19 +6483,9 @@
       </c>
     </row>
     <row r="130">
-      <c r="T130" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U130" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V130" s="4" t="n">
-        <v>47520</v>
-      </c>
+      <c r="T130" s="4" t="n"/>
+      <c r="U130" s="4" t="n"/>
+      <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
         <v>134</v>
       </c>
@@ -7708,19 +6514,9 @@
       </c>
     </row>
     <row r="131">
-      <c r="T131" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U131" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V131" s="7" t="n">
-        <v>47354</v>
-      </c>
+      <c r="T131" s="7" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
         <v>22</v>
       </c>
@@ -7749,19 +6545,9 @@
       </c>
     </row>
     <row r="132">
-      <c r="T132" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U132" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V132" s="4" t="n">
-        <v>49015</v>
-      </c>
+      <c r="T132" s="4" t="n"/>
+      <c r="U132" s="4" t="n"/>
+      <c r="V132" s="4" t="n"/>
       <c r="X132" s="4" t="n">
         <v>65</v>
       </c>
@@ -7790,19 +6576,9 @@
       </c>
     </row>
     <row r="133">
-      <c r="T133" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U133" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V133" s="7" t="n">
-        <v>48832</v>
-      </c>
+      <c r="T133" s="7" t="n"/>
+      <c r="U133" s="7" t="n"/>
+      <c r="V133" s="7" t="n"/>
       <c r="X133" s="7" t="n">
         <v>29</v>
       </c>
@@ -7831,19 +6607,9 @@
       </c>
     </row>
     <row r="134">
-      <c r="T134" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U134" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V134" s="4" t="n">
-        <v>46644</v>
-      </c>
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="4" t="n"/>
+      <c r="V134" s="4" t="n"/>
       <c r="X134" s="4" t="n">
         <v>12</v>
       </c>
@@ -7872,19 +6638,9 @@
       </c>
     </row>
     <row r="135">
-      <c r="T135" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U135" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V135" s="7" t="n">
-        <v>46416</v>
-      </c>
+      <c r="T135" s="7" t="n"/>
+      <c r="U135" s="7" t="n"/>
+      <c r="V135" s="7" t="n"/>
       <c r="X135" s="7" t="n">
         <v>82</v>
       </c>
@@ -7913,19 +6669,9 @@
       </c>
     </row>
     <row r="136">
-      <c r="T136" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U136" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V136" s="4" t="n">
-        <v>48419</v>
-      </c>
+      <c r="T136" s="4" t="n"/>
+      <c r="U136" s="4" t="n"/>
+      <c r="V136" s="4" t="n"/>
       <c r="X136" s="4" t="n">
         <v>1</v>
       </c>
@@ -7954,19 +6700,9 @@
       </c>
     </row>
     <row r="137">
-      <c r="T137" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U137" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V137" s="7" t="n">
-        <v>47500</v>
-      </c>
+      <c r="T137" s="7" t="n"/>
+      <c r="U137" s="7" t="n"/>
+      <c r="V137" s="7" t="n"/>
       <c r="X137" s="7" t="n">
         <v>7</v>
       </c>
@@ -7995,19 +6731,9 @@
       </c>
     </row>
     <row r="138">
-      <c r="T138" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U138" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V138" s="4" t="n">
-        <v>47954</v>
-      </c>
+      <c r="T138" s="4" t="n"/>
+      <c r="U138" s="4" t="n"/>
+      <c r="V138" s="4" t="n"/>
       <c r="X138" s="4" t="n">
         <v>1</v>
       </c>
@@ -8036,19 +6762,9 @@
       </c>
     </row>
     <row r="139">
-      <c r="T139" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U139" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V139" s="7" t="n">
-        <v>49088</v>
-      </c>
+      <c r="T139" s="7" t="n"/>
+      <c r="U139" s="7" t="n"/>
+      <c r="V139" s="7" t="n"/>
       <c r="X139" s="7" t="n">
         <v>107</v>
       </c>
@@ -8077,19 +6793,9 @@
       </c>
     </row>
     <row r="140">
-      <c r="T140" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U140" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V140" s="4" t="n">
-        <v>48111</v>
-      </c>
+      <c r="T140" s="4" t="n"/>
+      <c r="U140" s="4" t="n"/>
+      <c r="V140" s="4" t="n"/>
       <c r="X140" s="4" t="n">
         <v>24</v>
       </c>
@@ -8118,19 +6824,9 @@
       </c>
     </row>
     <row r="141">
-      <c r="T141" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U141" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V141" s="7" t="n">
-        <v>46535</v>
-      </c>
+      <c r="T141" s="7" t="n"/>
+      <c r="U141" s="7" t="n"/>
+      <c r="V141" s="7" t="n"/>
       <c r="X141" s="7" t="n">
         <v>68</v>
       </c>
@@ -8159,19 +6855,9 @@
       </c>
     </row>
     <row r="142">
-      <c r="T142" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U142" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V142" s="4" t="n">
-        <v>46063</v>
-      </c>
+      <c r="T142" s="4" t="n"/>
+      <c r="U142" s="4" t="n"/>
+      <c r="V142" s="4" t="n"/>
       <c r="X142" s="4" t="n">
         <v>18</v>
       </c>
@@ -8200,19 +6886,9 @@
       </c>
     </row>
     <row r="143">
-      <c r="T143" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U143" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V143" s="7" t="n">
-        <v>48085</v>
-      </c>
+      <c r="T143" s="7" t="n"/>
+      <c r="U143" s="7" t="n"/>
+      <c r="V143" s="7" t="n"/>
       <c r="X143" s="7" t="n">
         <v>12</v>
       </c>
@@ -8241,19 +6917,9 @@
       </c>
     </row>
     <row r="144">
-      <c r="T144" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U144" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V144" s="4" t="n">
-        <v>47472</v>
-      </c>
+      <c r="T144" s="4" t="n"/>
+      <c r="U144" s="4" t="n"/>
+      <c r="V144" s="4" t="n"/>
       <c r="X144" s="4" t="n">
         <v>70</v>
       </c>
@@ -8282,19 +6948,9 @@
       </c>
     </row>
     <row r="145">
-      <c r="T145" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U145" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V145" s="7" t="n">
-        <v>47003</v>
-      </c>
+      <c r="T145" s="7" t="n"/>
+      <c r="U145" s="7" t="n"/>
+      <c r="V145" s="7" t="n"/>
       <c r="X145" s="7" t="n">
         <v>2</v>
       </c>
@@ -8323,19 +6979,9 @@
       </c>
     </row>
     <row r="146">
-      <c r="T146" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U146" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V146" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
       <c r="X146" s="4" t="n">
         <v>6</v>
       </c>
@@ -8364,19 +7010,9 @@
       </c>
     </row>
     <row r="147">
-      <c r="T147" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U147" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V147" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T147" s="7" t="n"/>
+      <c r="U147" s="7" t="n"/>
+      <c r="V147" s="7" t="n"/>
       <c r="X147" s="7" t="n">
         <v>2</v>
       </c>
@@ -8405,19 +7041,9 @@
       </c>
     </row>
     <row r="148">
-      <c r="T148" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U148" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V148" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T148" s="4" t="n"/>
+      <c r="U148" s="4" t="n"/>
+      <c r="V148" s="4" t="n"/>
       <c r="X148" s="4" t="n">
         <v>115</v>
       </c>
@@ -8446,19 +7072,9 @@
       </c>
     </row>
     <row r="149">
-      <c r="T149" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U149" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V149" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T149" s="7" t="n"/>
+      <c r="U149" s="7" t="n"/>
+      <c r="V149" s="7" t="n"/>
       <c r="X149" s="7" t="n">
         <v>20</v>
       </c>
@@ -8487,19 +7103,9 @@
       </c>
     </row>
     <row r="150">
-      <c r="T150" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U150" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="4" t="n"/>
+      <c r="V150" s="4" t="n"/>
       <c r="X150" s="4" t="n">
         <v>69</v>
       </c>
@@ -8528,19 +7134,9 @@
       </c>
     </row>
     <row r="151">
-      <c r="T151" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V151" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T151" s="7" t="n"/>
+      <c r="U151" s="7" t="n"/>
+      <c r="V151" s="7" t="n"/>
       <c r="X151" s="7" t="n">
         <v>41</v>
       </c>
@@ -8569,19 +7165,9 @@
       </c>
     </row>
     <row r="152">
-      <c r="T152" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U152" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="4" t="n"/>
+      <c r="V152" s="4" t="n"/>
       <c r="X152" s="4" t="n">
         <v>5</v>
       </c>
@@ -8610,19 +7196,9 @@
       </c>
     </row>
     <row r="153">
-      <c r="T153" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U153" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V153" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T153" s="7" t="n"/>
+      <c r="U153" s="7" t="n"/>
+      <c r="V153" s="7" t="n"/>
       <c r="X153" s="7" t="n">
         <v>95</v>
       </c>
@@ -8651,19 +7227,9 @@
       </c>
     </row>
     <row r="154">
-      <c r="T154" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U154" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T154" s="4" t="n"/>
+      <c r="U154" s="4" t="n"/>
+      <c r="V154" s="4" t="n"/>
       <c r="X154" s="4" t="n">
         <v>1</v>
       </c>
@@ -8692,19 +7258,9 @@
       </c>
     </row>
     <row r="155">
-      <c r="T155" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V155" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T155" s="7" t="n"/>
+      <c r="U155" s="7" t="n"/>
+      <c r="V155" s="7" t="n"/>
       <c r="X155" s="7" t="n">
         <v>9</v>
       </c>
@@ -8733,19 +7289,9 @@
       </c>
     </row>
     <row r="156">
-      <c r="T156" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U156" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="4" t="n"/>
+      <c r="V156" s="4" t="n"/>
       <c r="X156" s="4" t="n">
         <v>2</v>
       </c>
@@ -8774,19 +7320,9 @@
       </c>
     </row>
     <row r="157">
-      <c r="T157" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U157" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V157" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T157" s="7" t="n"/>
+      <c r="U157" s="7" t="n"/>
+      <c r="V157" s="7" t="n"/>
       <c r="X157" s="7" t="n">
         <v>114</v>
       </c>
@@ -8815,19 +7351,9 @@
       </c>
     </row>
     <row r="158">
-      <c r="T158" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U158" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V158" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T158" s="4" t="n"/>
+      <c r="U158" s="4" t="n"/>
+      <c r="V158" s="4" t="n"/>
       <c r="X158" s="4" t="n">
         <v>16</v>
       </c>
@@ -8856,19 +7382,9 @@
       </c>
     </row>
     <row r="159">
-      <c r="T159" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U159" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V159" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T159" s="7" t="n"/>
+      <c r="U159" s="7" t="n"/>
+      <c r="V159" s="7" t="n"/>
       <c r="X159" s="7" t="n">
         <v>60</v>
       </c>
@@ -8897,19 +7413,9 @@
       </c>
     </row>
     <row r="160">
-      <c r="T160" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U160" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="4" t="n"/>
+      <c r="V160" s="4" t="n"/>
       <c r="X160" s="4" t="n">
         <v>41</v>
       </c>
@@ -8938,19 +7444,9 @@
       </c>
     </row>
     <row r="161">
-      <c r="T161" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U161" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V161" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T161" s="7" t="n"/>
+      <c r="U161" s="7" t="n"/>
+      <c r="V161" s="7" t="n"/>
       <c r="X161" s="7" t="n">
         <v>14</v>
       </c>
@@ -8979,19 +7475,9 @@
       </c>
     </row>
     <row r="162">
-      <c r="T162" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U162" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V162" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="4" t="n"/>
+      <c r="V162" s="4" t="n"/>
       <c r="X162" s="4" t="n">
         <v>84</v>
       </c>
@@ -9020,19 +7506,9 @@
       </c>
     </row>
     <row r="163">
-      <c r="T163" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U163" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V163" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T163" s="7" t="n"/>
+      <c r="U163" s="7" t="n"/>
+      <c r="V163" s="7" t="n"/>
       <c r="X163" s="7" t="n">
         <v>8</v>
       </c>
@@ -9061,19 +7537,9 @@
       </c>
     </row>
     <row r="164">
-      <c r="T164" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U164" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V164" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="4" t="n"/>
+      <c r="V164" s="4" t="n"/>
       <c r="X164" s="4" t="n">
         <v>1</v>
       </c>
@@ -9102,19 +7568,9 @@
       </c>
     </row>
     <row r="165">
-      <c r="T165" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U165" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V165" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T165" s="7" t="n"/>
+      <c r="U165" s="7" t="n"/>
+      <c r="V165" s="7" t="n"/>
       <c r="X165" s="7" t="n">
         <v>144</v>
       </c>
@@ -9143,19 +7599,9 @@
       </c>
     </row>
     <row r="166">
-      <c r="T166" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U166" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V166" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="4" t="n"/>
+      <c r="V166" s="4" t="n"/>
       <c r="X166" s="4" t="n">
         <v>16</v>
       </c>
@@ -9184,19 +7630,9 @@
       </c>
     </row>
     <row r="167">
-      <c r="T167" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U167" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V167" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T167" s="7" t="n"/>
+      <c r="U167" s="7" t="n"/>
+      <c r="V167" s="7" t="n"/>
       <c r="X167" s="7" t="n">
         <v>66</v>
       </c>
@@ -9225,19 +7661,9 @@
       </c>
     </row>
     <row r="168">
-      <c r="T168" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U168" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V168" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="4" t="n"/>
+      <c r="V168" s="4" t="n"/>
       <c r="X168" s="4" t="n">
         <v>35</v>
       </c>
@@ -9266,19 +7692,9 @@
       </c>
     </row>
     <row r="169">
-      <c r="T169" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U169" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V169" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T169" s="7" t="n"/>
+      <c r="U169" s="7" t="n"/>
+      <c r="V169" s="7" t="n"/>
       <c r="X169" s="7" t="n">
         <v>15</v>
       </c>
@@ -9307,19 +7723,9 @@
       </c>
     </row>
     <row r="170">
-      <c r="T170" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U170" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V170" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="4" t="n"/>
+      <c r="V170" s="4" t="n"/>
       <c r="X170" s="4" t="n">
         <v>83</v>
       </c>
@@ -9348,19 +7754,9 @@
       </c>
     </row>
     <row r="171">
-      <c r="T171" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U171" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V171" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T171" s="7" t="n"/>
+      <c r="U171" s="7" t="n"/>
+      <c r="V171" s="7" t="n"/>
       <c r="X171" s="7" t="n">
         <v>6</v>
       </c>
@@ -9389,19 +7785,9 @@
       </c>
     </row>
     <row r="172">
-      <c r="T172" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U172" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V172" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="4" t="n"/>
+      <c r="V172" s="4" t="n"/>
       <c r="X172" s="4" t="n">
         <v>104</v>
       </c>
@@ -9430,19 +7816,9 @@
       </c>
     </row>
     <row r="173">
-      <c r="T173" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U173" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V173" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T173" s="7" t="n"/>
+      <c r="U173" s="7" t="n"/>
+      <c r="V173" s="7" t="n"/>
       <c r="X173" s="7" t="n">
         <v>17</v>
       </c>
@@ -9471,19 +7847,9 @@
       </c>
     </row>
     <row r="174">
-      <c r="T174" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U174" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V174" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="n"/>
+      <c r="V174" s="4" t="n"/>
       <c r="X174" s="4" t="n">
         <v>72</v>
       </c>
@@ -9512,19 +7878,9 @@
       </c>
     </row>
     <row r="175">
-      <c r="T175" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U175" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V175" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T175" s="7" t="n"/>
+      <c r="U175" s="7" t="n"/>
+      <c r="V175" s="7" t="n"/>
       <c r="X175" s="7" t="n">
         <v>43</v>
       </c>
@@ -9553,19 +7909,9 @@
       </c>
     </row>
     <row r="176">
-      <c r="T176" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U176" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V176" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="4" t="n"/>
+      <c r="V176" s="4" t="n"/>
       <c r="X176" s="4" t="n">
         <v>20</v>
       </c>
@@ -9594,19 +7940,9 @@
       </c>
     </row>
     <row r="177">
-      <c r="T177" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U177" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V177" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T177" s="7" t="n"/>
+      <c r="U177" s="7" t="n"/>
+      <c r="V177" s="7" t="n"/>
       <c r="X177" s="7" t="n">
         <v>134</v>
       </c>
@@ -9635,19 +7971,9 @@
       </c>
     </row>
     <row r="178">
-      <c r="T178" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U178" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V178" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T178" s="4" t="n"/>
+      <c r="U178" s="4" t="n"/>
+      <c r="V178" s="4" t="n"/>
       <c r="X178" s="4" t="n">
         <v>7</v>
       </c>
@@ -9676,19 +8002,9 @@
       </c>
     </row>
     <row r="179">
-      <c r="T179" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U179" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V179" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T179" s="7" t="n"/>
+      <c r="U179" s="7" t="n"/>
+      <c r="V179" s="7" t="n"/>
       <c r="X179" s="7" t="n">
         <v>2</v>
       </c>
@@ -9717,19 +8033,9 @@
       </c>
     </row>
     <row r="180">
-      <c r="T180" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U180" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V180" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T180" s="4" t="n"/>
+      <c r="U180" s="4" t="n"/>
+      <c r="V180" s="4" t="n"/>
       <c r="X180" s="4" t="n">
         <v>129</v>
       </c>
@@ -9758,19 +8064,9 @@
       </c>
     </row>
     <row r="181">
-      <c r="T181" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U181" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V181" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T181" s="7" t="n"/>
+      <c r="U181" s="7" t="n"/>
+      <c r="V181" s="7" t="n"/>
       <c r="X181" s="7" t="n">
         <v>17</v>
       </c>
@@ -9799,19 +8095,9 @@
       </c>
     </row>
     <row r="182">
-      <c r="T182" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U182" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V182" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T182" s="4" t="n"/>
+      <c r="U182" s="4" t="n"/>
+      <c r="V182" s="4" t="n"/>
       <c r="X182" s="4" t="n">
         <v>66</v>
       </c>
@@ -9840,19 +8126,9 @@
       </c>
     </row>
     <row r="183">
-      <c r="T183" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U183" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V183" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T183" s="7" t="n"/>
+      <c r="U183" s="7" t="n"/>
+      <c r="V183" s="7" t="n"/>
       <c r="X183" s="7" t="n">
         <v>29</v>
       </c>
@@ -9881,19 +8157,9 @@
       </c>
     </row>
     <row r="184">
-      <c r="T184" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U184" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V184" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T184" s="4" t="n"/>
+      <c r="U184" s="4" t="n"/>
+      <c r="V184" s="4" t="n"/>
       <c r="X184" s="4" t="n">
         <v>21</v>
       </c>
@@ -9922,19 +8188,9 @@
       </c>
     </row>
     <row r="185">
-      <c r="T185" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U185" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V185" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T185" s="7" t="n"/>
+      <c r="U185" s="7" t="n"/>
+      <c r="V185" s="7" t="n"/>
       <c r="X185" s="7" t="n">
         <v>135</v>
       </c>
@@ -9963,19 +8219,9 @@
       </c>
     </row>
     <row r="186">
-      <c r="T186" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U186" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V186" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T186" s="4" t="n"/>
+      <c r="U186" s="4" t="n"/>
+      <c r="V186" s="4" t="n"/>
       <c r="X186" s="4" t="n">
         <v>9</v>
       </c>
@@ -10004,19 +8250,9 @@
       </c>
     </row>
     <row r="187">
-      <c r="T187" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U187" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V187" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T187" s="7" t="n"/>
+      <c r="U187" s="7" t="n"/>
+      <c r="V187" s="7" t="n"/>
       <c r="X187" s="7" t="n">
         <v>1</v>
       </c>
@@ -10045,19 +8281,9 @@
       </c>
     </row>
     <row r="188">
-      <c r="T188" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U188" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V188" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T188" s="4" t="n"/>
+      <c r="U188" s="4" t="n"/>
+      <c r="V188" s="4" t="n"/>
       <c r="X188" s="4" t="n">
         <v>126</v>
       </c>
@@ -10086,19 +8312,9 @@
       </c>
     </row>
     <row r="189">
-      <c r="T189" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U189" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V189" s="7" t="n">
-        <v>9927</v>
-      </c>
+      <c r="T189" s="7" t="n"/>
+      <c r="U189" s="7" t="n"/>
+      <c r="V189" s="7" t="n"/>
       <c r="X189" s="7" t="n">
         <v>17</v>
       </c>
@@ -10127,19 +8343,9 @@
       </c>
     </row>
     <row r="190">
-      <c r="T190" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U190" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V190" s="4" t="n">
-        <v>9839</v>
-      </c>
+      <c r="T190" s="4" t="n"/>
+      <c r="U190" s="4" t="n"/>
+      <c r="V190" s="4" t="n"/>
       <c r="X190" s="4" t="n">
         <v>63</v>
       </c>
@@ -10168,19 +8374,9 @@
       </c>
     </row>
     <row r="191">
-      <c r="T191" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U191" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V191" s="7" t="n">
-        <v>9918</v>
-      </c>
+      <c r="T191" s="7" t="n"/>
+      <c r="U191" s="7" t="n"/>
+      <c r="V191" s="7" t="n"/>
       <c r="X191" s="7" t="n">
         <v>35</v>
       </c>
@@ -10209,19 +8405,9 @@
       </c>
     </row>
     <row r="192">
-      <c r="T192" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U192" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V192" s="4" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T192" s="4" t="n"/>
+      <c r="U192" s="4" t="n"/>
+      <c r="V192" s="4" t="n"/>
       <c r="X192" s="4" t="n">
         <v>26</v>
       </c>
@@ -10250,21 +8436,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="T193" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U193" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V193" s="7" t="n">
-        <v>10050</v>
-      </c>
+      <c r="T193" s="7" t="n"/>
+      <c r="U193" s="7" t="n"/>
+      <c r="V193" s="7" t="n"/>
       <c r="X193" s="7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y193" s="7" t="inlineStr">
         <is>
@@ -10291,19 +8467,9 @@
       </c>
     </row>
     <row r="194">
-      <c r="T194" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U194" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V194" s="4" t="n">
-        <v>9768</v>
-      </c>
+      <c r="T194" s="4" t="n"/>
+      <c r="U194" s="4" t="n"/>
+      <c r="V194" s="4" t="n"/>
       <c r="X194" s="4" t="n">
         <v>6</v>
       </c>
@@ -10332,19 +8498,9 @@
       </c>
     </row>
     <row r="195">
-      <c r="T195" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U195" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V195" s="7" t="n">
-        <v>9920</v>
-      </c>
+      <c r="T195" s="7" t="n"/>
+      <c r="U195" s="7" t="n"/>
+      <c r="V195" s="7" t="n"/>
       <c r="X195" s="7" t="n">
         <v>2</v>
       </c>
@@ -10373,19 +8529,9 @@
       </c>
     </row>
     <row r="196">
-      <c r="T196" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U196" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V196" s="4" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T196" s="4" t="n"/>
+      <c r="U196" s="4" t="n"/>
+      <c r="V196" s="4" t="n"/>
       <c r="X196" s="4" t="n"/>
       <c r="Y196" s="4" t="n"/>
       <c r="Z196" s="4" t="n"/>
@@ -10404,19 +8550,9 @@
       </c>
     </row>
     <row r="197">
-      <c r="T197" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U197" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V197" s="7" t="n">
-        <v>10434</v>
-      </c>
+      <c r="T197" s="7" t="n"/>
+      <c r="U197" s="7" t="n"/>
+      <c r="V197" s="7" t="n"/>
       <c r="X197" s="7" t="n"/>
       <c r="Y197" s="7" t="n"/>
       <c r="Z197" s="7" t="n"/>
@@ -10435,19 +8571,9 @@
       </c>
     </row>
     <row r="198">
-      <c r="T198" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U198" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V198" s="4" t="n">
-        <v>10284</v>
-      </c>
+      <c r="T198" s="4" t="n"/>
+      <c r="U198" s="4" t="n"/>
+      <c r="V198" s="4" t="n"/>
       <c r="X198" s="4" t="n"/>
       <c r="Y198" s="4" t="n"/>
       <c r="Z198" s="4" t="n"/>
@@ -10466,19 +8592,9 @@
       </c>
     </row>
     <row r="199">
-      <c r="T199" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U199" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V199" s="7" t="n">
-        <v>10458</v>
-      </c>
+      <c r="T199" s="7" t="n"/>
+      <c r="U199" s="7" t="n"/>
+      <c r="V199" s="7" t="n"/>
       <c r="X199" s="7" t="n"/>
       <c r="Y199" s="7" t="n"/>
       <c r="Z199" s="7" t="n"/>
@@ -10497,19 +8613,9 @@
       </c>
     </row>
     <row r="200">
-      <c r="T200" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U200" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V200" s="4" t="n">
-        <v>10153</v>
-      </c>
+      <c r="T200" s="4" t="n"/>
+      <c r="U200" s="4" t="n"/>
+      <c r="V200" s="4" t="n"/>
       <c r="X200" s="4" t="n"/>
       <c r="Y200" s="4" t="n"/>
       <c r="Z200" s="4" t="n"/>
@@ -10528,19 +8634,9 @@
       </c>
     </row>
     <row r="201">
-      <c r="T201" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U201" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V201" s="7" t="n">
-        <v>9843</v>
-      </c>
+      <c r="T201" s="7" t="n"/>
+      <c r="U201" s="7" t="n"/>
+      <c r="V201" s="7" t="n"/>
       <c r="X201" s="7" t="n"/>
       <c r="Y201" s="7" t="n"/>
       <c r="Z201" s="7" t="n"/>
@@ -10559,19 +8655,9 @@
       </c>
     </row>
     <row r="202">
-      <c r="T202" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U202" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V202" s="4" t="n">
-        <v>10433</v>
-      </c>
+      <c r="T202" s="4" t="n"/>
+      <c r="U202" s="4" t="n"/>
+      <c r="V202" s="4" t="n"/>
       <c r="X202" s="4" t="n"/>
       <c r="Y202" s="4" t="n"/>
       <c r="Z202" s="4" t="n"/>
@@ -10590,19 +8676,9 @@
       </c>
     </row>
     <row r="203">
-      <c r="T203" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U203" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V203" s="7" t="n">
-        <v>10670</v>
-      </c>
+      <c r="T203" s="7" t="n"/>
+      <c r="U203" s="7" t="n"/>
+      <c r="V203" s="7" t="n"/>
       <c r="X203" s="7" t="n"/>
       <c r="Y203" s="7" t="n"/>
       <c r="Z203" s="7" t="n"/>
@@ -10621,19 +8697,9 @@
       </c>
     </row>
     <row r="204">
-      <c r="T204" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U204" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V204" s="4" t="n">
-        <v>10599</v>
-      </c>
+      <c r="T204" s="4" t="n"/>
+      <c r="U204" s="4" t="n"/>
+      <c r="V204" s="4" t="n"/>
       <c r="X204" s="4" t="n"/>
       <c r="Y204" s="4" t="n"/>
       <c r="Z204" s="4" t="n"/>
@@ -10652,19 +8718,9 @@
       </c>
     </row>
     <row r="205">
-      <c r="T205" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U205" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V205" s="7" t="n">
-        <v>10619</v>
-      </c>
+      <c r="T205" s="7" t="n"/>
+      <c r="U205" s="7" t="n"/>
+      <c r="V205" s="7" t="n"/>
       <c r="X205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
       <c r="Z205" s="7" t="n"/>
@@ -10683,19 +8739,9 @@
       </c>
     </row>
     <row r="206">
-      <c r="T206" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U206" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V206" s="4" t="n">
-        <v>10415</v>
-      </c>
+      <c r="T206" s="4" t="n"/>
+      <c r="U206" s="4" t="n"/>
+      <c r="V206" s="4" t="n"/>
       <c r="X206" s="4" t="n"/>
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="n"/>
@@ -10714,19 +8760,9 @@
       </c>
     </row>
     <row r="207">
-      <c r="T207" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U207" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V207" s="7" t="n">
-        <v>10065</v>
-      </c>
+      <c r="T207" s="7" t="n"/>
+      <c r="U207" s="7" t="n"/>
+      <c r="V207" s="7" t="n"/>
       <c r="X207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
       <c r="Z207" s="7" t="n"/>
@@ -10745,19 +8781,9 @@
       </c>
     </row>
     <row r="208">
-      <c r="T208" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U208" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V208" s="4" t="n">
-        <v>10158</v>
-      </c>
+      <c r="T208" s="4" t="n"/>
+      <c r="U208" s="4" t="n"/>
+      <c r="V208" s="4" t="n"/>
       <c r="X208" s="4" t="n"/>
       <c r="Y208" s="4" t="n"/>
       <c r="Z208" s="4" t="n"/>
@@ -10776,19 +8802,9 @@
       </c>
     </row>
     <row r="209">
-      <c r="T209" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U209" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V209" s="7" t="n">
-        <v>10333</v>
-      </c>
+      <c r="T209" s="7" t="n"/>
+      <c r="U209" s="7" t="n"/>
+      <c r="V209" s="7" t="n"/>
       <c r="X209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
       <c r="Z209" s="7" t="n"/>
@@ -10807,19 +8823,9 @@
       </c>
     </row>
     <row r="210">
-      <c r="T210" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U210" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V210" s="4" t="n">
-        <v>10414</v>
-      </c>
+      <c r="T210" s="4" t="n"/>
+      <c r="U210" s="4" t="n"/>
+      <c r="V210" s="4" t="n"/>
       <c r="X210" s="4" t="n"/>
       <c r="Y210" s="4" t="n"/>
       <c r="Z210" s="4" t="n"/>
@@ -10838,19 +8844,9 @@
       </c>
     </row>
     <row r="211">
-      <c r="T211" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U211" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V211" s="7" t="n">
-        <v>10453</v>
-      </c>
+      <c r="T211" s="7" t="n"/>
+      <c r="U211" s="7" t="n"/>
+      <c r="V211" s="7" t="n"/>
       <c r="X211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
       <c r="Z211" s="7" t="n"/>
@@ -10869,19 +8865,9 @@
       </c>
     </row>
     <row r="212">
-      <c r="T212" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U212" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V212" s="4" t="n">
-        <v>10879</v>
-      </c>
+      <c r="T212" s="4" t="n"/>
+      <c r="U212" s="4" t="n"/>
+      <c r="V212" s="4" t="n"/>
       <c r="X212" s="4" t="n"/>
       <c r="Y212" s="4" t="n"/>
       <c r="Z212" s="4" t="n"/>
@@ -10900,19 +8886,9 @@
       </c>
     </row>
     <row r="213">
-      <c r="T213" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U213" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation50987</t>
-        </is>
-      </c>
-      <c r="V213" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T213" s="7" t="n"/>
+      <c r="U213" s="7" t="n"/>
+      <c r="V213" s="7" t="n"/>
       <c r="X213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
       <c r="Z213" s="7" t="n"/>
@@ -10931,19 +8907,9 @@
       </c>
     </row>
     <row r="214">
-      <c r="T214" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U214" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation75114</t>
-        </is>
-      </c>
-      <c r="V214" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T214" s="4" t="n"/>
+      <c r="U214" s="4" t="n"/>
+      <c r="V214" s="4" t="n"/>
       <c r="X214" s="4" t="n"/>
       <c r="Y214" s="4" t="n"/>
       <c r="Z214" s="4" t="n"/>
@@ -10962,19 +8928,9 @@
       </c>
     </row>
     <row r="215">
-      <c r="T215" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U215" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V215" s="7" t="n">
-        <v>21493</v>
-      </c>
+      <c r="T215" s="7" t="n"/>
+      <c r="U215" s="7" t="n"/>
+      <c r="V215" s="7" t="n"/>
       <c r="X215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
       <c r="Z215" s="7" t="n"/>
@@ -10993,19 +8949,9 @@
       </c>
     </row>
     <row r="216">
-      <c r="T216" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U216" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V216" s="4" t="n">
-        <v>21012</v>
-      </c>
+      <c r="T216" s="4" t="n"/>
+      <c r="U216" s="4" t="n"/>
+      <c r="V216" s="4" t="n"/>
       <c r="X216" s="4" t="n"/>
       <c r="Y216" s="4" t="n"/>
       <c r="Z216" s="4" t="n"/>
@@ -11024,19 +8970,9 @@
       </c>
     </row>
     <row r="217">
-      <c r="T217" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U217" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V217" s="7" t="n">
-        <v>21635</v>
-      </c>
+      <c r="T217" s="7" t="n"/>
+      <c r="U217" s="7" t="n"/>
+      <c r="V217" s="7" t="n"/>
       <c r="X217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
       <c r="Z217" s="7" t="n"/>
@@ -11055,19 +8991,9 @@
       </c>
     </row>
     <row r="218">
-      <c r="T218" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U218" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V218" s="4" t="n">
-        <v>21969</v>
-      </c>
+      <c r="T218" s="4" t="n"/>
+      <c r="U218" s="4" t="n"/>
+      <c r="V218" s="4" t="n"/>
       <c r="X218" s="4" t="n"/>
       <c r="Y218" s="4" t="n"/>
       <c r="Z218" s="4" t="n"/>
@@ -11084,1938 +9010,6 @@
           <t>com.logistics.rider.foody</t>
         </is>
       </c>
-    </row>
-    <row r="219">
-      <c r="T219" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U219" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V219" s="7" t="n">
-        <v>21723</v>
-      </c>
-      <c r="X219" s="7" t="n"/>
-      <c r="Y219" s="7" t="n"/>
-      <c r="Z219" s="7" t="n"/>
-      <c r="AB219" s="7" t="n"/>
-      <c r="AC219" s="7" t="n"/>
-      <c r="AD219" s="7" t="n"/>
-    </row>
-    <row r="220">
-      <c r="T220" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U220" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V220" s="4" t="n">
-        <v>20879</v>
-      </c>
-      <c r="X220" s="4" t="n"/>
-      <c r="Y220" s="4" t="n"/>
-      <c r="Z220" s="4" t="n"/>
-      <c r="AB220" s="4" t="n"/>
-      <c r="AC220" s="4" t="n"/>
-      <c r="AD220" s="4" t="n"/>
-    </row>
-    <row r="221">
-      <c r="T221" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U221" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V221" s="7" t="n">
-        <v>20783</v>
-      </c>
-      <c r="X221" s="7" t="n"/>
-      <c r="Y221" s="7" t="n"/>
-      <c r="Z221" s="7" t="n"/>
-      <c r="AB221" s="7" t="n"/>
-      <c r="AC221" s="7" t="n"/>
-      <c r="AD221" s="7" t="n"/>
-    </row>
-    <row r="222">
-      <c r="T222" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U222" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V222" s="4" t="n">
-        <v>21875</v>
-      </c>
-      <c r="X222" s="4" t="n"/>
-      <c r="Y222" s="4" t="n"/>
-      <c r="Z222" s="4" t="n"/>
-      <c r="AB222" s="4" t="n"/>
-      <c r="AC222" s="4" t="n"/>
-      <c r="AD222" s="4" t="n"/>
-    </row>
-    <row r="223">
-      <c r="T223" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U223" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V223" s="7" t="n">
-        <v>22103</v>
-      </c>
-      <c r="X223" s="7" t="n"/>
-      <c r="Y223" s="7" t="n"/>
-      <c r="Z223" s="7" t="n"/>
-      <c r="AB223" s="7" t="n"/>
-      <c r="AC223" s="7" t="n"/>
-      <c r="AD223" s="7" t="n"/>
-    </row>
-    <row r="224">
-      <c r="T224" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U224" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V224" s="4" t="n">
-        <v>22799</v>
-      </c>
-      <c r="X224" s="4" t="n"/>
-      <c r="Y224" s="4" t="n"/>
-      <c r="Z224" s="4" t="n"/>
-      <c r="AB224" s="4" t="n"/>
-      <c r="AC224" s="4" t="n"/>
-      <c r="AD224" s="4" t="n"/>
-    </row>
-    <row r="225">
-      <c r="T225" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U225" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V225" s="7" t="n">
-        <v>22705</v>
-      </c>
-      <c r="X225" s="7" t="n"/>
-      <c r="Y225" s="7" t="n"/>
-      <c r="Z225" s="7" t="n"/>
-      <c r="AB225" s="7" t="n"/>
-      <c r="AC225" s="7" t="n"/>
-      <c r="AD225" s="7" t="n"/>
-    </row>
-    <row r="226">
-      <c r="T226" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U226" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V226" s="4" t="n">
-        <v>21885</v>
-      </c>
-      <c r="X226" s="4" t="n"/>
-      <c r="Y226" s="4" t="n"/>
-      <c r="Z226" s="4" t="n"/>
-      <c r="AB226" s="4" t="n"/>
-      <c r="AC226" s="4" t="n"/>
-      <c r="AD226" s="4" t="n"/>
-    </row>
-    <row r="227">
-      <c r="T227" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U227" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V227" s="7" t="n">
-        <v>21360</v>
-      </c>
-      <c r="X227" s="7" t="n"/>
-      <c r="Y227" s="7" t="n"/>
-      <c r="Z227" s="7" t="n"/>
-      <c r="AB227" s="7" t="n"/>
-      <c r="AC227" s="7" t="n"/>
-      <c r="AD227" s="7" t="n"/>
-    </row>
-    <row r="228">
-      <c r="T228" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U228" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V228" s="4" t="n">
-        <v>20612</v>
-      </c>
-      <c r="X228" s="4" t="n"/>
-      <c r="Y228" s="4" t="n"/>
-      <c r="Z228" s="4" t="n"/>
-      <c r="AB228" s="4" t="n"/>
-      <c r="AC228" s="4" t="n"/>
-      <c r="AD228" s="4" t="n"/>
-    </row>
-    <row r="229">
-      <c r="T229" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U229" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V229" s="7" t="n">
-        <v>22101</v>
-      </c>
-      <c r="X229" s="7" t="n"/>
-      <c r="Y229" s="7" t="n"/>
-      <c r="Z229" s="7" t="n"/>
-      <c r="AB229" s="7" t="n"/>
-      <c r="AC229" s="7" t="n"/>
-      <c r="AD229" s="7" t="n"/>
-    </row>
-    <row r="230">
-      <c r="T230" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U230" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V230" s="4" t="n">
-        <v>22665</v>
-      </c>
-      <c r="X230" s="4" t="n"/>
-      <c r="Y230" s="4" t="n"/>
-      <c r="Z230" s="4" t="n"/>
-      <c r="AB230" s="4" t="n"/>
-      <c r="AC230" s="4" t="n"/>
-      <c r="AD230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="T231" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U231" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V231" s="7" t="n">
-        <v>22473</v>
-      </c>
-      <c r="X231" s="7" t="n"/>
-      <c r="Y231" s="7" t="n"/>
-      <c r="Z231" s="7" t="n"/>
-      <c r="AB231" s="7" t="n"/>
-      <c r="AC231" s="7" t="n"/>
-      <c r="AD231" s="7" t="n"/>
-    </row>
-    <row r="232">
-      <c r="T232" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U232" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V232" s="4" t="n">
-        <v>22903</v>
-      </c>
-      <c r="X232" s="4" t="n"/>
-      <c r="Y232" s="4" t="n"/>
-      <c r="Z232" s="4" t="n"/>
-      <c r="AB232" s="4" t="n"/>
-      <c r="AC232" s="4" t="n"/>
-      <c r="AD232" s="4" t="n"/>
-    </row>
-    <row r="233">
-      <c r="T233" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U233" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V233" s="7" t="n">
-        <v>21829</v>
-      </c>
-      <c r="X233" s="7" t="n"/>
-      <c r="Y233" s="7" t="n"/>
-      <c r="Z233" s="7" t="n"/>
-      <c r="AB233" s="7" t="n"/>
-      <c r="AC233" s="7" t="n"/>
-      <c r="AD233" s="7" t="n"/>
-    </row>
-    <row r="234">
-      <c r="T234" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U234" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V234" s="4" t="n">
-        <v>20959</v>
-      </c>
-      <c r="X234" s="4" t="n"/>
-      <c r="Y234" s="4" t="n"/>
-      <c r="Z234" s="4" t="n"/>
-      <c r="AB234" s="4" t="n"/>
-      <c r="AC234" s="4" t="n"/>
-      <c r="AD234" s="4" t="n"/>
-    </row>
-    <row r="235">
-      <c r="T235" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U235" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V235" s="7" t="n">
-        <v>20856</v>
-      </c>
-      <c r="X235" s="7" t="n"/>
-      <c r="Y235" s="7" t="n"/>
-      <c r="Z235" s="7" t="n"/>
-      <c r="AB235" s="7" t="n"/>
-      <c r="AC235" s="7" t="n"/>
-      <c r="AD235" s="7" t="n"/>
-    </row>
-    <row r="236">
-      <c r="T236" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U236" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V236" s="4" t="n">
-        <v>23061</v>
-      </c>
-      <c r="X236" s="4" t="n"/>
-      <c r="Y236" s="4" t="n"/>
-      <c r="Z236" s="4" t="n"/>
-      <c r="AB236" s="4" t="n"/>
-      <c r="AC236" s="4" t="n"/>
-      <c r="AD236" s="4" t="n"/>
-    </row>
-    <row r="237">
-      <c r="T237" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U237" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V237" s="7" t="n">
-        <v>21952</v>
-      </c>
-      <c r="X237" s="7" t="n"/>
-      <c r="Y237" s="7" t="n"/>
-      <c r="Z237" s="7" t="n"/>
-      <c r="AB237" s="7" t="n"/>
-      <c r="AC237" s="7" t="n"/>
-      <c r="AD237" s="7" t="n"/>
-    </row>
-    <row r="238">
-      <c r="T238" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U238" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V238" s="4" t="n">
-        <v>22608</v>
-      </c>
-      <c r="X238" s="4" t="n"/>
-      <c r="Y238" s="4" t="n"/>
-      <c r="Z238" s="4" t="n"/>
-      <c r="AB238" s="4" t="n"/>
-      <c r="AC238" s="4" t="n"/>
-      <c r="AD238" s="4" t="n"/>
-    </row>
-    <row r="239">
-      <c r="T239" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U239" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V239" s="7" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X239" s="7" t="n"/>
-      <c r="Y239" s="7" t="n"/>
-      <c r="Z239" s="7" t="n"/>
-      <c r="AB239" s="7" t="n"/>
-      <c r="AC239" s="7" t="n"/>
-      <c r="AD239" s="7" t="n"/>
-    </row>
-    <row r="240">
-      <c r="T240" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U240" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V240" s="4" t="n">
-        <v>16721</v>
-      </c>
-      <c r="X240" s="4" t="n"/>
-      <c r="Y240" s="4" t="n"/>
-      <c r="Z240" s="4" t="n"/>
-      <c r="AB240" s="4" t="n"/>
-      <c r="AC240" s="4" t="n"/>
-      <c r="AD240" s="4" t="n"/>
-    </row>
-    <row r="241">
-      <c r="T241" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U241" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V241" s="7" t="n">
-        <v>16586</v>
-      </c>
-      <c r="X241" s="7" t="n"/>
-      <c r="Y241" s="7" t="n"/>
-      <c r="Z241" s="7" t="n"/>
-      <c r="AB241" s="7" t="n"/>
-      <c r="AC241" s="7" t="n"/>
-      <c r="AD241" s="7" t="n"/>
-    </row>
-    <row r="242">
-      <c r="T242" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U242" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V242" s="4" t="n">
-        <v>16419</v>
-      </c>
-      <c r="X242" s="4" t="n"/>
-      <c r="Y242" s="4" t="n"/>
-      <c r="Z242" s="4" t="n"/>
-      <c r="AB242" s="4" t="n"/>
-      <c r="AC242" s="4" t="n"/>
-      <c r="AD242" s="4" t="n"/>
-    </row>
-    <row r="243">
-      <c r="T243" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U243" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V243" s="7" t="n">
-        <v>15946</v>
-      </c>
-      <c r="X243" s="7" t="n"/>
-      <c r="Y243" s="7" t="n"/>
-      <c r="Z243" s="7" t="n"/>
-      <c r="AB243" s="7" t="n"/>
-      <c r="AC243" s="7" t="n"/>
-      <c r="AD243" s="7" t="n"/>
-    </row>
-    <row r="244">
-      <c r="T244" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U244" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V244" s="4" t="n">
-        <v>16042</v>
-      </c>
-      <c r="X244" s="4" t="n"/>
-      <c r="Y244" s="4" t="n"/>
-      <c r="Z244" s="4" t="n"/>
-      <c r="AB244" s="4" t="n"/>
-      <c r="AC244" s="4" t="n"/>
-      <c r="AD244" s="4" t="n"/>
-    </row>
-    <row r="245">
-      <c r="T245" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U245" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V245" s="7" t="n">
-        <v>16409</v>
-      </c>
-      <c r="X245" s="7" t="n"/>
-      <c r="Y245" s="7" t="n"/>
-      <c r="Z245" s="7" t="n"/>
-      <c r="AB245" s="7" t="n"/>
-      <c r="AC245" s="7" t="n"/>
-      <c r="AD245" s="7" t="n"/>
-    </row>
-    <row r="246">
-      <c r="T246" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U246" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V246" s="4" t="n">
-        <v>16831</v>
-      </c>
-      <c r="X246" s="4" t="n"/>
-      <c r="Y246" s="4" t="n"/>
-      <c r="Z246" s="4" t="n"/>
-      <c r="AB246" s="4" t="n"/>
-      <c r="AC246" s="4" t="n"/>
-      <c r="AD246" s="4" t="n"/>
-    </row>
-    <row r="247">
-      <c r="T247" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U247" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V247" s="7" t="n">
-        <v>16886</v>
-      </c>
-      <c r="X247" s="7" t="n"/>
-      <c r="Y247" s="7" t="n"/>
-      <c r="Z247" s="7" t="n"/>
-      <c r="AB247" s="7" t="n"/>
-      <c r="AC247" s="7" t="n"/>
-      <c r="AD247" s="7" t="n"/>
-    </row>
-    <row r="248">
-      <c r="T248" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U248" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V248" s="4" t="n">
-        <v>16694</v>
-      </c>
-      <c r="X248" s="4" t="n"/>
-      <c r="Y248" s="4" t="n"/>
-      <c r="Z248" s="4" t="n"/>
-      <c r="AB248" s="4" t="n"/>
-      <c r="AC248" s="4" t="n"/>
-      <c r="AD248" s="4" t="n"/>
-    </row>
-    <row r="249">
-      <c r="T249" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U249" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V249" s="7" t="n">
-        <v>16659</v>
-      </c>
-      <c r="X249" s="7" t="n"/>
-      <c r="Y249" s="7" t="n"/>
-      <c r="Z249" s="7" t="n"/>
-      <c r="AB249" s="7" t="n"/>
-      <c r="AC249" s="7" t="n"/>
-      <c r="AD249" s="7" t="n"/>
-    </row>
-    <row r="250">
-      <c r="T250" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U250" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V250" s="4" t="n">
-        <v>16268</v>
-      </c>
-      <c r="X250" s="4" t="n"/>
-      <c r="Y250" s="4" t="n"/>
-      <c r="Z250" s="4" t="n"/>
-      <c r="AB250" s="4" t="n"/>
-      <c r="AC250" s="4" t="n"/>
-      <c r="AD250" s="4" t="n"/>
-    </row>
-    <row r="251">
-      <c r="T251" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U251" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V251" s="7" t="n">
-        <v>16259</v>
-      </c>
-      <c r="X251" s="7" t="n"/>
-      <c r="Y251" s="7" t="n"/>
-      <c r="Z251" s="7" t="n"/>
-      <c r="AB251" s="7" t="n"/>
-      <c r="AC251" s="7" t="n"/>
-      <c r="AD251" s="7" t="n"/>
-    </row>
-    <row r="252">
-      <c r="T252" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U252" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V252" s="4" t="n">
-        <v>16600</v>
-      </c>
-      <c r="X252" s="4" t="n"/>
-      <c r="Y252" s="4" t="n"/>
-      <c r="Z252" s="4" t="n"/>
-      <c r="AB252" s="4" t="n"/>
-      <c r="AC252" s="4" t="n"/>
-      <c r="AD252" s="4" t="n"/>
-    </row>
-    <row r="253">
-      <c r="T253" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U253" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V253" s="7" t="n">
-        <v>16913</v>
-      </c>
-      <c r="X253" s="7" t="n"/>
-      <c r="Y253" s="7" t="n"/>
-      <c r="Z253" s="7" t="n"/>
-      <c r="AB253" s="7" t="n"/>
-      <c r="AC253" s="7" t="n"/>
-      <c r="AD253" s="7" t="n"/>
-    </row>
-    <row r="254">
-      <c r="T254" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U254" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V254" s="4" t="n">
-        <v>16991</v>
-      </c>
-      <c r="X254" s="4" t="n"/>
-      <c r="Y254" s="4" t="n"/>
-      <c r="Z254" s="4" t="n"/>
-      <c r="AB254" s="4" t="n"/>
-      <c r="AC254" s="4" t="n"/>
-      <c r="AD254" s="4" t="n"/>
-    </row>
-    <row r="255">
-      <c r="T255" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U255" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V255" s="7" t="n">
-        <v>17365</v>
-      </c>
-      <c r="X255" s="7" t="n"/>
-      <c r="Y255" s="7" t="n"/>
-      <c r="Z255" s="7" t="n"/>
-      <c r="AB255" s="7" t="n"/>
-      <c r="AC255" s="7" t="n"/>
-      <c r="AD255" s="7" t="n"/>
-    </row>
-    <row r="256">
-      <c r="T256" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U256" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V256" s="4" t="n">
-        <v>16944</v>
-      </c>
-      <c r="X256" s="4" t="n"/>
-      <c r="Y256" s="4" t="n"/>
-      <c r="Z256" s="4" t="n"/>
-      <c r="AB256" s="4" t="n"/>
-      <c r="AC256" s="4" t="n"/>
-      <c r="AD256" s="4" t="n"/>
-    </row>
-    <row r="257">
-      <c r="T257" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U257" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V257" s="7" t="n">
-        <v>16518</v>
-      </c>
-      <c r="X257" s="7" t="n"/>
-      <c r="Y257" s="7" t="n"/>
-      <c r="Z257" s="7" t="n"/>
-      <c r="AB257" s="7" t="n"/>
-      <c r="AC257" s="7" t="n"/>
-      <c r="AD257" s="7" t="n"/>
-    </row>
-    <row r="258">
-      <c r="T258" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U258" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V258" s="4" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X258" s="4" t="n"/>
-      <c r="Y258" s="4" t="n"/>
-      <c r="Z258" s="4" t="n"/>
-      <c r="AB258" s="4" t="n"/>
-      <c r="AC258" s="4" t="n"/>
-      <c r="AD258" s="4" t="n"/>
-    </row>
-    <row r="259">
-      <c r="T259" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U259" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V259" s="7" t="n">
-        <v>16711</v>
-      </c>
-      <c r="X259" s="7" t="n"/>
-      <c r="Y259" s="7" t="n"/>
-      <c r="Z259" s="7" t="n"/>
-      <c r="AB259" s="7" t="n"/>
-      <c r="AC259" s="7" t="n"/>
-      <c r="AD259" s="7" t="n"/>
-    </row>
-    <row r="260">
-      <c r="T260" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U260" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V260" s="4" t="n">
-        <v>17379</v>
-      </c>
-      <c r="X260" s="4" t="n"/>
-      <c r="Y260" s="4" t="n"/>
-      <c r="Z260" s="4" t="n"/>
-      <c r="AB260" s="4" t="n"/>
-      <c r="AC260" s="4" t="n"/>
-      <c r="AD260" s="4" t="n"/>
-    </row>
-    <row r="261">
-      <c r="T261" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U261" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V261" s="7" t="n">
-        <v>17551</v>
-      </c>
-      <c r="X261" s="7" t="n"/>
-      <c r="Y261" s="7" t="n"/>
-      <c r="Z261" s="7" t="n"/>
-      <c r="AB261" s="7" t="n"/>
-      <c r="AC261" s="7" t="n"/>
-      <c r="AD261" s="7" t="n"/>
-    </row>
-    <row r="262">
-      <c r="T262" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U262" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V262" s="4" t="n">
-        <v>17474</v>
-      </c>
-      <c r="X262" s="4" t="n"/>
-      <c r="Y262" s="4" t="n"/>
-      <c r="Z262" s="4" t="n"/>
-      <c r="AB262" s="4" t="n"/>
-      <c r="AC262" s="4" t="n"/>
-      <c r="AD262" s="4" t="n"/>
-    </row>
-    <row r="263">
-      <c r="T263" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U263" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V263" s="7" t="n">
-        <v>724</v>
-      </c>
-      <c r="X263" s="7" t="n"/>
-      <c r="Y263" s="7" t="n"/>
-      <c r="Z263" s="7" t="n"/>
-      <c r="AB263" s="7" t="n"/>
-      <c r="AC263" s="7" t="n"/>
-      <c r="AD263" s="7" t="n"/>
-    </row>
-    <row r="264">
-      <c r="T264" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U264" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V264" s="4" t="n">
-        <v>746</v>
-      </c>
-      <c r="X264" s="4" t="n"/>
-      <c r="Y264" s="4" t="n"/>
-      <c r="Z264" s="4" t="n"/>
-      <c r="AB264" s="4" t="n"/>
-      <c r="AC264" s="4" t="n"/>
-      <c r="AD264" s="4" t="n"/>
-    </row>
-    <row r="265">
-      <c r="T265" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U265" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V265" s="7" t="n">
-        <v>723</v>
-      </c>
-      <c r="X265" s="7" t="n"/>
-      <c r="Y265" s="7" t="n"/>
-      <c r="Z265" s="7" t="n"/>
-      <c r="AB265" s="7" t="n"/>
-      <c r="AC265" s="7" t="n"/>
-      <c r="AD265" s="7" t="n"/>
-    </row>
-    <row r="266">
-      <c r="T266" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U266" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V266" s="4" t="n">
-        <v>708</v>
-      </c>
-      <c r="X266" s="4" t="n"/>
-      <c r="Y266" s="4" t="n"/>
-      <c r="Z266" s="4" t="n"/>
-      <c r="AB266" s="4" t="n"/>
-      <c r="AC266" s="4" t="n"/>
-      <c r="AD266" s="4" t="n"/>
-    </row>
-    <row r="267">
-      <c r="T267" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U267" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V267" s="7" t="n">
-        <v>735</v>
-      </c>
-      <c r="X267" s="7" t="n"/>
-      <c r="Y267" s="7" t="n"/>
-      <c r="Z267" s="7" t="n"/>
-      <c r="AB267" s="7" t="n"/>
-      <c r="AC267" s="7" t="n"/>
-      <c r="AD267" s="7" t="n"/>
-    </row>
-    <row r="268">
-      <c r="T268" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U268" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V268" s="4" t="n">
-        <v>714</v>
-      </c>
-      <c r="X268" s="4" t="n"/>
-      <c r="Y268" s="4" t="n"/>
-      <c r="Z268" s="4" t="n"/>
-      <c r="AB268" s="4" t="n"/>
-      <c r="AC268" s="4" t="n"/>
-      <c r="AD268" s="4" t="n"/>
-    </row>
-    <row r="269">
-      <c r="T269" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U269" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V269" s="7" t="n">
-        <v>706</v>
-      </c>
-      <c r="X269" s="7" t="n"/>
-      <c r="Y269" s="7" t="n"/>
-      <c r="Z269" s="7" t="n"/>
-      <c r="AB269" s="7" t="n"/>
-      <c r="AC269" s="7" t="n"/>
-      <c r="AD269" s="7" t="n"/>
-    </row>
-    <row r="270">
-      <c r="T270" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U270" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V270" s="4" t="n">
-        <v>729</v>
-      </c>
-      <c r="X270" s="4" t="n"/>
-      <c r="Y270" s="4" t="n"/>
-      <c r="Z270" s="4" t="n"/>
-      <c r="AB270" s="4" t="n"/>
-      <c r="AC270" s="4" t="n"/>
-      <c r="AD270" s="4" t="n"/>
-    </row>
-    <row r="271">
-      <c r="T271" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U271" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V271" s="7" t="n">
-        <v>719</v>
-      </c>
-      <c r="X271" s="7" t="n"/>
-      <c r="Y271" s="7" t="n"/>
-      <c r="Z271" s="7" t="n"/>
-      <c r="AB271" s="7" t="n"/>
-      <c r="AC271" s="7" t="n"/>
-      <c r="AD271" s="7" t="n"/>
-    </row>
-    <row r="272">
-      <c r="T272" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U272" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V272" s="4" t="n">
-        <v>719</v>
-      </c>
-      <c r="X272" s="4" t="n"/>
-      <c r="Y272" s="4" t="n"/>
-      <c r="Z272" s="4" t="n"/>
-      <c r="AB272" s="4" t="n"/>
-      <c r="AC272" s="4" t="n"/>
-      <c r="AD272" s="4" t="n"/>
-    </row>
-    <row r="273">
-      <c r="T273" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U273" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V273" s="7" t="n">
-        <v>730</v>
-      </c>
-      <c r="X273" s="7" t="n"/>
-      <c r="Y273" s="7" t="n"/>
-      <c r="Z273" s="7" t="n"/>
-      <c r="AB273" s="7" t="n"/>
-      <c r="AC273" s="7" t="n"/>
-      <c r="AD273" s="7" t="n"/>
-    </row>
-    <row r="274">
-      <c r="T274" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U274" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V274" s="4" t="n">
-        <v>740</v>
-      </c>
-      <c r="X274" s="4" t="n"/>
-      <c r="Y274" s="4" t="n"/>
-      <c r="Z274" s="4" t="n"/>
-      <c r="AB274" s="4" t="n"/>
-      <c r="AC274" s="4" t="n"/>
-      <c r="AD274" s="4" t="n"/>
-    </row>
-    <row r="275">
-      <c r="T275" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U275" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V275" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="X275" s="7" t="n"/>
-      <c r="Y275" s="7" t="n"/>
-      <c r="Z275" s="7" t="n"/>
-      <c r="AB275" s="7" t="n"/>
-      <c r="AC275" s="7" t="n"/>
-      <c r="AD275" s="7" t="n"/>
-    </row>
-    <row r="276">
-      <c r="T276" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U276" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V276" s="4" t="n">
-        <v>698</v>
-      </c>
-      <c r="X276" s="4" t="n"/>
-      <c r="Y276" s="4" t="n"/>
-      <c r="Z276" s="4" t="n"/>
-      <c r="AB276" s="4" t="n"/>
-      <c r="AC276" s="4" t="n"/>
-      <c r="AD276" s="4" t="n"/>
-    </row>
-    <row r="277">
-      <c r="T277" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U277" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V277" s="7" t="n">
-        <v>691</v>
-      </c>
-      <c r="X277" s="7" t="n"/>
-      <c r="Y277" s="7" t="n"/>
-      <c r="Z277" s="7" t="n"/>
-      <c r="AB277" s="7" t="n"/>
-      <c r="AC277" s="7" t="n"/>
-      <c r="AD277" s="7" t="n"/>
-    </row>
-    <row r="278">
-      <c r="T278" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U278" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V278" s="4" t="n">
-        <v>695</v>
-      </c>
-      <c r="X278" s="4" t="n"/>
-      <c r="Y278" s="4" t="n"/>
-      <c r="Z278" s="4" t="n"/>
-      <c r="AB278" s="4" t="n"/>
-      <c r="AC278" s="4" t="n"/>
-      <c r="AD278" s="4" t="n"/>
-    </row>
-    <row r="279">
-      <c r="T279" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U279" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V279" s="7" t="n">
-        <v>706</v>
-      </c>
-      <c r="X279" s="7" t="n"/>
-      <c r="Y279" s="7" t="n"/>
-      <c r="Z279" s="7" t="n"/>
-      <c r="AB279" s="7" t="n"/>
-      <c r="AC279" s="7" t="n"/>
-      <c r="AD279" s="7" t="n"/>
-    </row>
-    <row r="280">
-      <c r="T280" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U280" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V280" s="4" t="n">
-        <v>701</v>
-      </c>
-      <c r="X280" s="4" t="n"/>
-      <c r="Y280" s="4" t="n"/>
-      <c r="Z280" s="4" t="n"/>
-      <c r="AB280" s="4" t="n"/>
-      <c r="AC280" s="4" t="n"/>
-      <c r="AD280" s="4" t="n"/>
-    </row>
-    <row r="281">
-      <c r="T281" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U281" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V281" s="7" t="n">
-        <v>706</v>
-      </c>
-      <c r="X281" s="7" t="n"/>
-      <c r="Y281" s="7" t="n"/>
-      <c r="Z281" s="7" t="n"/>
-      <c r="AB281" s="7" t="n"/>
-      <c r="AC281" s="7" t="n"/>
-      <c r="AD281" s="7" t="n"/>
-    </row>
-    <row r="282">
-      <c r="T282" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U282" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V282" s="4" t="n">
-        <v>704</v>
-      </c>
-      <c r="X282" s="4" t="n"/>
-      <c r="Y282" s="4" t="n"/>
-      <c r="Z282" s="4" t="n"/>
-      <c r="AB282" s="4" t="n"/>
-      <c r="AC282" s="4" t="n"/>
-      <c r="AD282" s="4" t="n"/>
-    </row>
-    <row r="283">
-      <c r="T283" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U283" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V283" s="7" t="n">
-        <v>670</v>
-      </c>
-      <c r="X283" s="7" t="n"/>
-      <c r="Y283" s="7" t="n"/>
-      <c r="Z283" s="7" t="n"/>
-      <c r="AB283" s="7" t="n"/>
-      <c r="AC283" s="7" t="n"/>
-      <c r="AD283" s="7" t="n"/>
-    </row>
-    <row r="284">
-      <c r="T284" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U284" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V284" s="4" t="n">
-        <v>694</v>
-      </c>
-      <c r="X284" s="4" t="n"/>
-      <c r="Y284" s="4" t="n"/>
-      <c r="Z284" s="4" t="n"/>
-      <c r="AB284" s="4" t="n"/>
-      <c r="AC284" s="4" t="n"/>
-      <c r="AD284" s="4" t="n"/>
-    </row>
-    <row r="285">
-      <c r="T285" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U285" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V285" s="7" t="n">
-        <v>702</v>
-      </c>
-      <c r="X285" s="7" t="n"/>
-      <c r="Y285" s="7" t="n"/>
-      <c r="Z285" s="7" t="n"/>
-      <c r="AB285" s="7" t="n"/>
-      <c r="AC285" s="7" t="n"/>
-      <c r="AD285" s="7" t="n"/>
-    </row>
-    <row r="286">
-      <c r="T286" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U286" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V286" s="4" t="n">
-        <v>708</v>
-      </c>
-      <c r="X286" s="4" t="n"/>
-      <c r="Y286" s="4" t="n"/>
-      <c r="Z286" s="4" t="n"/>
-      <c r="AB286" s="4" t="n"/>
-      <c r="AC286" s="4" t="n"/>
-      <c r="AD286" s="4" t="n"/>
-    </row>
-    <row r="287">
-      <c r="T287" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U287" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V287" s="7" t="n">
-        <v>2188</v>
-      </c>
-      <c r="X287" s="7" t="n"/>
-      <c r="Y287" s="7" t="n"/>
-      <c r="Z287" s="7" t="n"/>
-      <c r="AB287" s="7" t="n"/>
-      <c r="AC287" s="7" t="n"/>
-      <c r="AD287" s="7" t="n"/>
-    </row>
-    <row r="288">
-      <c r="T288" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U288" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V288" s="4" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X288" s="4" t="n"/>
-      <c r="Y288" s="4" t="n"/>
-      <c r="Z288" s="4" t="n"/>
-      <c r="AB288" s="4" t="n"/>
-      <c r="AC288" s="4" t="n"/>
-      <c r="AD288" s="4" t="n"/>
-    </row>
-    <row r="289">
-      <c r="T289" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U289" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V289" s="7" t="n">
-        <v>2338</v>
-      </c>
-      <c r="X289" s="7" t="n"/>
-      <c r="Y289" s="7" t="n"/>
-      <c r="Z289" s="7" t="n"/>
-      <c r="AB289" s="7" t="n"/>
-      <c r="AC289" s="7" t="n"/>
-      <c r="AD289" s="7" t="n"/>
-    </row>
-    <row r="290">
-      <c r="T290" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U290" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V290" s="4" t="n">
-        <v>2152</v>
-      </c>
-      <c r="X290" s="4" t="n"/>
-      <c r="Y290" s="4" t="n"/>
-      <c r="Z290" s="4" t="n"/>
-      <c r="AB290" s="4" t="n"/>
-      <c r="AC290" s="4" t="n"/>
-      <c r="AD290" s="4" t="n"/>
-    </row>
-    <row r="291">
-      <c r="T291" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U291" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V291" s="7" t="n">
-        <v>2003</v>
-      </c>
-      <c r="X291" s="7" t="n"/>
-      <c r="Y291" s="7" t="n"/>
-      <c r="Z291" s="7" t="n"/>
-      <c r="AB291" s="7" t="n"/>
-      <c r="AC291" s="7" t="n"/>
-      <c r="AD291" s="7" t="n"/>
-    </row>
-    <row r="292">
-      <c r="T292" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U292" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V292" s="4" t="n">
-        <v>1895</v>
-      </c>
-      <c r="X292" s="4" t="n"/>
-      <c r="Y292" s="4" t="n"/>
-      <c r="Z292" s="4" t="n"/>
-      <c r="AB292" s="4" t="n"/>
-      <c r="AC292" s="4" t="n"/>
-      <c r="AD292" s="4" t="n"/>
-    </row>
-    <row r="293">
-      <c r="T293" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U293" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V293" s="7" t="n">
-        <v>1935</v>
-      </c>
-      <c r="X293" s="7" t="n"/>
-      <c r="Y293" s="7" t="n"/>
-      <c r="Z293" s="7" t="n"/>
-      <c r="AB293" s="7" t="n"/>
-      <c r="AC293" s="7" t="n"/>
-      <c r="AD293" s="7" t="n"/>
-    </row>
-    <row r="294">
-      <c r="T294" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U294" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V294" s="4" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X294" s="4" t="n"/>
-      <c r="Y294" s="4" t="n"/>
-      <c r="Z294" s="4" t="n"/>
-      <c r="AB294" s="4" t="n"/>
-      <c r="AC294" s="4" t="n"/>
-      <c r="AD294" s="4" t="n"/>
-    </row>
-    <row r="295">
-      <c r="T295" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U295" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V295" s="7" t="n">
-        <v>2049</v>
-      </c>
-      <c r="X295" s="7" t="n"/>
-      <c r="Y295" s="7" t="n"/>
-      <c r="Z295" s="7" t="n"/>
-      <c r="AB295" s="7" t="n"/>
-      <c r="AC295" s="7" t="n"/>
-      <c r="AD295" s="7" t="n"/>
-    </row>
-    <row r="296">
-      <c r="T296" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U296" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V296" s="4" t="n">
-        <v>2325</v>
-      </c>
-      <c r="X296" s="4" t="n"/>
-      <c r="Y296" s="4" t="n"/>
-      <c r="Z296" s="4" t="n"/>
-      <c r="AB296" s="4" t="n"/>
-      <c r="AC296" s="4" t="n"/>
-      <c r="AD296" s="4" t="n"/>
-    </row>
-    <row r="297">
-      <c r="T297" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U297" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V297" s="7" t="n">
-        <v>2216</v>
-      </c>
-      <c r="X297" s="7" t="n"/>
-      <c r="Y297" s="7" t="n"/>
-      <c r="Z297" s="7" t="n"/>
-      <c r="AB297" s="7" t="n"/>
-      <c r="AC297" s="7" t="n"/>
-      <c r="AD297" s="7" t="n"/>
-    </row>
-    <row r="298">
-      <c r="T298" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U298" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V298" s="4" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X298" s="4" t="n"/>
-      <c r="Y298" s="4" t="n"/>
-      <c r="Z298" s="4" t="n"/>
-      <c r="AB298" s="4" t="n"/>
-      <c r="AC298" s="4" t="n"/>
-      <c r="AD298" s="4" t="n"/>
-    </row>
-    <row r="299">
-      <c r="T299" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U299" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V299" s="7" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X299" s="7" t="n"/>
-      <c r="Y299" s="7" t="n"/>
-      <c r="Z299" s="7" t="n"/>
-      <c r="AB299" s="7" t="n"/>
-      <c r="AC299" s="7" t="n"/>
-      <c r="AD299" s="7" t="n"/>
-    </row>
-    <row r="300">
-      <c r="T300" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U300" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V300" s="4" t="n">
-        <v>2035</v>
-      </c>
-      <c r="X300" s="4" t="n"/>
-      <c r="Y300" s="4" t="n"/>
-      <c r="Z300" s="4" t="n"/>
-      <c r="AB300" s="4" t="n"/>
-      <c r="AC300" s="4" t="n"/>
-      <c r="AD300" s="4" t="n"/>
-    </row>
-    <row r="301">
-      <c r="T301" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U301" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V301" s="7" t="n">
-        <v>2182</v>
-      </c>
-      <c r="X301" s="7" t="n"/>
-      <c r="Y301" s="7" t="n"/>
-      <c r="Z301" s="7" t="n"/>
-      <c r="AB301" s="7" t="n"/>
-      <c r="AC301" s="7" t="n"/>
-      <c r="AD301" s="7" t="n"/>
-    </row>
-    <row r="302">
-      <c r="T302" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U302" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V302" s="4" t="n">
-        <v>2156</v>
-      </c>
-      <c r="X302" s="4" t="n"/>
-      <c r="Y302" s="4" t="n"/>
-      <c r="Z302" s="4" t="n"/>
-      <c r="AB302" s="4" t="n"/>
-      <c r="AC302" s="4" t="n"/>
-      <c r="AD302" s="4" t="n"/>
-    </row>
-    <row r="303">
-      <c r="T303" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U303" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V303" s="7" t="n">
-        <v>2437</v>
-      </c>
-      <c r="X303" s="7" t="n"/>
-      <c r="Y303" s="7" t="n"/>
-      <c r="Z303" s="7" t="n"/>
-      <c r="AB303" s="7" t="n"/>
-      <c r="AC303" s="7" t="n"/>
-      <c r="AD303" s="7" t="n"/>
-    </row>
-    <row r="304">
-      <c r="T304" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U304" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V304" s="4" t="n">
-        <v>2214</v>
-      </c>
-      <c r="X304" s="4" t="n"/>
-      <c r="Y304" s="4" t="n"/>
-      <c r="Z304" s="4" t="n"/>
-      <c r="AB304" s="4" t="n"/>
-      <c r="AC304" s="4" t="n"/>
-      <c r="AD304" s="4" t="n"/>
-    </row>
-    <row r="305">
-      <c r="T305" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U305" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V305" s="7" t="n">
-        <v>2200</v>
-      </c>
-      <c r="X305" s="7" t="n"/>
-      <c r="Y305" s="7" t="n"/>
-      <c r="Z305" s="7" t="n"/>
-      <c r="AB305" s="7" t="n"/>
-      <c r="AC305" s="7" t="n"/>
-      <c r="AD305" s="7" t="n"/>
-    </row>
-    <row r="306">
-      <c r="T306" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U306" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V306" s="4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="X306" s="4" t="n"/>
-      <c r="Y306" s="4" t="n"/>
-      <c r="Z306" s="4" t="n"/>
-      <c r="AB306" s="4" t="n"/>
-      <c r="AC306" s="4" t="n"/>
-      <c r="AD306" s="4" t="n"/>
-    </row>
-    <row r="307">
-      <c r="T307" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U307" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V307" s="7" t="n">
-        <v>1980</v>
-      </c>
-      <c r="X307" s="7" t="n"/>
-      <c r="Y307" s="7" t="n"/>
-      <c r="Z307" s="7" t="n"/>
-      <c r="AB307" s="7" t="n"/>
-      <c r="AC307" s="7" t="n"/>
-      <c r="AD307" s="7" t="n"/>
-    </row>
-    <row r="308">
-      <c r="T308" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U308" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V308" s="4" t="n">
-        <v>2075</v>
-      </c>
-      <c r="X308" s="4" t="n"/>
-      <c r="Y308" s="4" t="n"/>
-      <c r="Z308" s="4" t="n"/>
-      <c r="AB308" s="4" t="n"/>
-      <c r="AC308" s="4" t="n"/>
-      <c r="AD308" s="4" t="n"/>
-    </row>
-    <row r="309">
-      <c r="T309" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U309" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V309" s="7" t="n">
-        <v>2191</v>
-      </c>
-      <c r="X309" s="7" t="n"/>
-      <c r="Y309" s="7" t="n"/>
-      <c r="Z309" s="7" t="n"/>
-      <c r="AB309" s="7" t="n"/>
-      <c r="AC309" s="7" t="n"/>
-      <c r="AD309" s="7" t="n"/>
-    </row>
-    <row r="310">
-      <c r="T310" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U310" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V310" s="4" t="n">
-        <v>2328</v>
-      </c>
-      <c r="X310" s="4" t="n"/>
-      <c r="Y310" s="4" t="n"/>
-      <c r="Z310" s="4" t="n"/>
-      <c r="AB310" s="4" t="n"/>
-      <c r="AC310" s="4" t="n"/>
-      <c r="AD310" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD310"/>
+  <dimension ref="A1:AD323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3243,29 +3243,49 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
+      <c r="D26" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C26)</f>
+        <v/>
+      </c>
+      <c r="E26" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C26)</f>
+        <v/>
+      </c>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
+      <c r="G26" s="4">
+        <f>ROUND((1-E26/D26)*100,2)</f>
+        <v/>
+      </c>
+      <c r="H26" s="4">
+        <f>MIN(1,(G26-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
+      <c r="K26" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="4">
+        <f>ROUND(100*(1-K26/D26),2)</f>
+        <v/>
+      </c>
+      <c r="M26" s="4">
+        <f>MAX(0,(L26-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N26" s="4">
+        <f>$B$2+H26+M26</f>
+        <v/>
+      </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr"/>
       <c r="V26" s="4" t="n">
-        <v>5365</v>
+        <v>1</v>
       </c>
       <c r="X26" s="4" t="n">
         <v>11</v>
@@ -3315,7 +3335,7 @@
       <c r="N27" s="7" t="n"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -3324,7 +3344,7 @@
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>5741</v>
+        <v>5365</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>73</v>
@@ -3374,7 +3394,7 @@
       <c r="N28" s="4" t="n"/>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
@@ -3383,7 +3403,7 @@
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5451</v>
+        <v>5741</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>31</v>
@@ -3433,7 +3453,7 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -3442,7 +3462,7 @@
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>5458</v>
+        <v>5451</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>13</v>
@@ -3492,7 +3512,7 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3501,7 +3521,7 @@
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5664</v>
+        <v>5458</v>
       </c>
       <c r="X30" s="4" t="n">
         <v>78</v>
@@ -3551,7 +3571,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -3560,7 +3580,7 @@
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>5241</v>
+        <v>5664</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>1</v>
@@ -3619,7 +3639,7 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3628,7 +3648,7 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5102</v>
+        <v>5241</v>
       </c>
       <c r="X32" s="4" t="n">
         <v>9</v>
@@ -3659,7 +3679,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D25)</f>
+        <f>AVERAGE(D2:D26)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3669,7 +3689,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H25)</f>
+        <f>AVERAGE(H2:H26)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3692,7 +3712,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -3701,7 +3721,7 @@
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>5388</v>
+        <v>5102</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>1</v>
@@ -3733,7 +3753,7 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3742,7 +3762,7 @@
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5339</v>
+        <v>5388</v>
       </c>
       <c r="X34" s="4" t="n">
         <v>119</v>
@@ -3774,7 +3794,7 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -3783,7 +3803,7 @@
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>5348</v>
+        <v>5339</v>
       </c>
       <c r="X35" s="7" t="n">
         <v>13</v>
@@ -3815,7 +3835,7 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
@@ -3824,7 +3844,7 @@
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>5329</v>
+        <v>5348</v>
       </c>
       <c r="X36" s="4" t="n">
         <v>67</v>
@@ -3856,7 +3876,7 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
@@ -3865,7 +3885,7 @@
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>5436</v>
+        <v>5329</v>
       </c>
       <c r="X37" s="7" t="n">
         <v>32</v>
@@ -3897,7 +3917,7 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
@@ -3906,7 +3926,7 @@
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>5081</v>
+        <v>5436</v>
       </c>
       <c r="X38" s="4" t="n">
         <v>13</v>
@@ -3938,7 +3958,7 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
@@ -3947,7 +3967,7 @@
         </is>
       </c>
       <c r="V39" s="7" t="n">
-        <v>5034</v>
+        <v>5081</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>93</v>
@@ -3979,7 +3999,7 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
@@ -3988,7 +4008,7 @@
         </is>
       </c>
       <c r="V40" s="4" t="n">
-        <v>5557</v>
+        <v>5034</v>
       </c>
       <c r="X40" s="4" t="n">
         <v>12</v>
@@ -4020,7 +4040,7 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
@@ -4029,7 +4049,7 @@
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>5513</v>
+        <v>5557</v>
       </c>
       <c r="X41" s="7" t="n">
         <v>2</v>
@@ -4061,7 +4081,7 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
@@ -4070,7 +4090,7 @@
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>5477</v>
+        <v>5513</v>
       </c>
       <c r="X42" s="4" t="n">
         <v>113</v>
@@ -4102,7 +4122,7 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
@@ -4111,7 +4131,7 @@
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>5526</v>
+        <v>5477</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>12</v>
@@ -4143,7 +4163,7 @@
     <row r="44">
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U44" s="4" t="inlineStr">
@@ -4152,7 +4172,7 @@
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>5339</v>
+        <v>5526</v>
       </c>
       <c r="X44" s="4" t="n">
         <v>69</v>
@@ -4184,7 +4204,7 @@
     <row r="45">
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
@@ -4193,7 +4213,7 @@
         </is>
       </c>
       <c r="V45" s="7" t="n">
-        <v>4933</v>
+        <v>5339</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>40</v>
@@ -4225,7 +4245,7 @@
     <row r="46">
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
@@ -4234,7 +4254,7 @@
         </is>
       </c>
       <c r="V46" s="4" t="n">
-        <v>4866</v>
+        <v>4933</v>
       </c>
       <c r="X46" s="4" t="n">
         <v>17</v>
@@ -4266,7 +4286,7 @@
     <row r="47">
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
@@ -4275,7 +4295,7 @@
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>5232</v>
+        <v>4866</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>83</v>
@@ -4307,7 +4327,7 @@
     <row r="48">
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
@@ -4316,7 +4336,7 @@
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>5576</v>
+        <v>5232</v>
       </c>
       <c r="X48" s="4" t="n">
         <v>9</v>
@@ -4348,7 +4368,7 @@
     <row r="49">
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
@@ -4357,7 +4377,7 @@
         </is>
       </c>
       <c r="V49" s="7" t="n">
-        <v>5287</v>
+        <v>5576</v>
       </c>
       <c r="X49" s="7" t="n">
         <v>124</v>
@@ -4389,16 +4409,16 @@
     <row r="50">
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U50" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>14969</v>
+        <v>5287</v>
       </c>
       <c r="X50" s="4" t="n">
         <v>19</v>
@@ -4430,16 +4450,16 @@
     <row r="51">
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>14818</v>
+        <v>5275</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>55</v>
@@ -4471,7 +4491,7 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
@@ -4480,7 +4500,7 @@
         </is>
       </c>
       <c r="V52" s="4" t="n">
-        <v>15263</v>
+        <v>14969</v>
       </c>
       <c r="X52" s="4" t="n">
         <v>35</v>
@@ -4512,7 +4532,7 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
@@ -4521,7 +4541,7 @@
         </is>
       </c>
       <c r="V53" s="7" t="n">
-        <v>14815</v>
+        <v>14818</v>
       </c>
       <c r="X53" s="7" t="n">
         <v>15</v>
@@ -4553,7 +4573,7 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
@@ -4562,7 +4582,7 @@
         </is>
       </c>
       <c r="V54" s="4" t="n">
-        <v>14968</v>
+        <v>15263</v>
       </c>
       <c r="X54" s="4" t="n">
         <v>82</v>
@@ -4594,7 +4614,7 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
@@ -4603,7 +4623,7 @@
         </is>
       </c>
       <c r="V55" s="7" t="n">
-        <v>14113</v>
+        <v>14815</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>1</v>
@@ -4635,7 +4655,7 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
@@ -4644,7 +4664,7 @@
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>14162</v>
+        <v>14968</v>
       </c>
       <c r="X56" s="4" t="n">
         <v>14</v>
@@ -4676,7 +4696,7 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
@@ -4685,7 +4705,7 @@
         </is>
       </c>
       <c r="V57" s="7" t="n">
-        <v>14815</v>
+        <v>14113</v>
       </c>
       <c r="X57" s="7" t="n">
         <v>2</v>
@@ -4717,7 +4737,7 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U58" s="4" t="inlineStr">
@@ -4726,7 +4746,7 @@
         </is>
       </c>
       <c r="V58" s="4" t="n">
-        <v>14815</v>
+        <v>14162</v>
       </c>
       <c r="X58" s="4" t="n">
         <v>101</v>
@@ -4758,7 +4778,7 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
@@ -4767,7 +4787,7 @@
         </is>
       </c>
       <c r="V59" s="7" t="n">
-        <v>15546</v>
+        <v>14815</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>10</v>
@@ -4799,7 +4819,7 @@
     <row r="60">
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U60" s="4" t="inlineStr">
@@ -4808,7 +4828,7 @@
         </is>
       </c>
       <c r="V60" s="4" t="n">
-        <v>14882</v>
+        <v>14815</v>
       </c>
       <c r="X60" s="4" t="n">
         <v>72</v>
@@ -4840,7 +4860,7 @@
     <row r="61">
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
@@ -4849,7 +4869,7 @@
         </is>
       </c>
       <c r="V61" s="7" t="n">
-        <v>14998</v>
+        <v>15546</v>
       </c>
       <c r="X61" s="7" t="n">
         <v>35</v>
@@ -4881,7 +4901,7 @@
     <row r="62">
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U62" s="4" t="inlineStr">
@@ -4890,7 +4910,7 @@
         </is>
       </c>
       <c r="V62" s="4" t="n">
-        <v>14354</v>
+        <v>14882</v>
       </c>
       <c r="X62" s="4" t="n">
         <v>13</v>
@@ -4922,7 +4942,7 @@
     <row r="63">
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
@@ -4931,7 +4951,7 @@
         </is>
       </c>
       <c r="V63" s="7" t="n">
-        <v>14362</v>
+        <v>14998</v>
       </c>
       <c r="X63" s="7" t="n">
         <v>71</v>
@@ -4963,7 +4983,7 @@
     <row r="64">
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr">
@@ -4972,7 +4992,7 @@
         </is>
       </c>
       <c r="V64" s="4" t="n">
-        <v>15089</v>
+        <v>14354</v>
       </c>
       <c r="X64" s="4" t="n">
         <v>8</v>
@@ -5004,7 +5024,7 @@
     <row r="65">
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
@@ -5013,7 +5033,7 @@
         </is>
       </c>
       <c r="V65" s="7" t="n">
-        <v>14802</v>
+        <v>14362</v>
       </c>
       <c r="X65" s="7" t="n">
         <v>2</v>
@@ -5045,7 +5065,7 @@
     <row r="66">
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr">
@@ -5054,7 +5074,7 @@
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>15349</v>
+        <v>15089</v>
       </c>
       <c r="X66" s="4" t="n">
         <v>125</v>
@@ -5086,7 +5106,7 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
@@ -5095,7 +5115,7 @@
         </is>
       </c>
       <c r="V67" s="7" t="n">
-        <v>14872</v>
+        <v>14802</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>11</v>
@@ -5127,7 +5147,7 @@
     <row r="68">
       <c r="T68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U68" s="4" t="inlineStr">
@@ -5136,7 +5156,7 @@
         </is>
       </c>
       <c r="V68" s="4" t="n">
-        <v>15054</v>
+        <v>15349</v>
       </c>
       <c r="X68" s="4" t="n">
         <v>67</v>
@@ -5168,7 +5188,7 @@
     <row r="69">
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
@@ -5177,7 +5197,7 @@
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>14169</v>
+        <v>14872</v>
       </c>
       <c r="X69" s="7" t="n">
         <v>27</v>
@@ -5209,7 +5229,7 @@
     <row r="70">
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U70" s="4" t="inlineStr">
@@ -5218,7 +5238,7 @@
         </is>
       </c>
       <c r="V70" s="4" t="n">
-        <v>14056</v>
+        <v>15054</v>
       </c>
       <c r="X70" s="4" t="n">
         <v>17</v>
@@ -5250,7 +5270,7 @@
     <row r="71">
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U71" s="7" t="inlineStr">
@@ -5259,7 +5279,7 @@
         </is>
       </c>
       <c r="V71" s="7" t="n">
-        <v>15058</v>
+        <v>14169</v>
       </c>
       <c r="X71" s="7" t="n">
         <v>85</v>
@@ -5291,7 +5311,7 @@
     <row r="72">
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U72" s="4" t="inlineStr">
@@ -5300,7 +5320,7 @@
         </is>
       </c>
       <c r="V72" s="4" t="n">
-        <v>14814</v>
+        <v>14056</v>
       </c>
       <c r="X72" s="4" t="n">
         <v>14</v>
@@ -5332,7 +5352,7 @@
     <row r="73">
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U73" s="7" t="inlineStr">
@@ -5341,7 +5361,7 @@
         </is>
       </c>
       <c r="V73" s="7" t="n">
-        <v>15440</v>
+        <v>15058</v>
       </c>
       <c r="X73" s="7" t="n">
         <v>4</v>
@@ -5373,16 +5393,16 @@
     <row r="74">
       <c r="T74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U74" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V74" s="4" t="n">
-        <v>77546</v>
+        <v>14814</v>
       </c>
       <c r="X74" s="4" t="n">
         <v>126</v>
@@ -5414,16 +5434,16 @@
     <row r="75">
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U75" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V75" s="7" t="n">
-        <v>77823</v>
+        <v>15440</v>
       </c>
       <c r="X75" s="7" t="n">
         <v>23</v>
@@ -5455,16 +5475,16 @@
     <row r="76">
       <c r="T76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U76" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V76" s="4" t="n">
-        <v>81723</v>
+        <v>14832</v>
       </c>
       <c r="X76" s="4" t="n">
         <v>65</v>
@@ -5496,7 +5516,7 @@
     <row r="77">
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U77" s="7" t="inlineStr">
@@ -5505,7 +5525,7 @@
         </is>
       </c>
       <c r="V77" s="7" t="n">
-        <v>78398</v>
+        <v>77546</v>
       </c>
       <c r="X77" s="7" t="n">
         <v>28</v>
@@ -5537,7 +5557,7 @@
     <row r="78">
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U78" s="4" t="inlineStr">
@@ -5546,7 +5566,7 @@
         </is>
       </c>
       <c r="V78" s="4" t="n">
-        <v>78030</v>
+        <v>77823</v>
       </c>
       <c r="X78" s="4" t="n">
         <v>19</v>
@@ -5578,7 +5598,7 @@
     <row r="79">
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U79" s="7" t="inlineStr">
@@ -5587,7 +5607,7 @@
         </is>
       </c>
       <c r="V79" s="7" t="n">
-        <v>76646</v>
+        <v>81723</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>91</v>
@@ -5619,7 +5639,7 @@
     <row r="80">
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U80" s="4" t="inlineStr">
@@ -5628,7 +5648,7 @@
         </is>
       </c>
       <c r="V80" s="4" t="n">
-        <v>76742</v>
+        <v>78398</v>
       </c>
       <c r="X80" s="4" t="n">
         <v>21</v>
@@ -5660,7 +5680,7 @@
     <row r="81">
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U81" s="7" t="inlineStr">
@@ -5669,7 +5689,7 @@
         </is>
       </c>
       <c r="V81" s="7" t="n">
-        <v>79003</v>
+        <v>78030</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>2</v>
@@ -5701,7 +5721,7 @@
     <row r="82">
       <c r="T82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U82" s="4" t="inlineStr">
@@ -5710,7 +5730,7 @@
         </is>
       </c>
       <c r="V82" s="4" t="n">
-        <v>78849</v>
+        <v>76646</v>
       </c>
       <c r="X82" s="4" t="n">
         <v>99</v>
@@ -5742,7 +5762,7 @@
     <row r="83">
       <c r="T83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U83" s="7" t="inlineStr">
@@ -5751,7 +5771,7 @@
         </is>
       </c>
       <c r="V83" s="7" t="n">
-        <v>80667</v>
+        <v>76742</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>12</v>
@@ -5783,7 +5803,7 @@
     <row r="84">
       <c r="T84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U84" s="4" t="inlineStr">
@@ -5792,7 +5812,7 @@
         </is>
       </c>
       <c r="V84" s="4" t="n">
-        <v>78640</v>
+        <v>79003</v>
       </c>
       <c r="X84" s="4" t="n">
         <v>70</v>
@@ -5824,7 +5844,7 @@
     <row r="85">
       <c r="T85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U85" s="7" t="inlineStr">
@@ -5833,7 +5853,7 @@
         </is>
       </c>
       <c r="V85" s="7" t="n">
-        <v>79108</v>
+        <v>78849</v>
       </c>
       <c r="X85" s="7" t="n">
         <v>30</v>
@@ -5865,7 +5885,7 @@
     <row r="86">
       <c r="T86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U86" s="4" t="inlineStr">
@@ -5874,7 +5894,7 @@
         </is>
       </c>
       <c r="V86" s="4" t="n">
-        <v>76911</v>
+        <v>80667</v>
       </c>
       <c r="X86" s="4" t="n">
         <v>15</v>
@@ -5906,7 +5926,7 @@
     <row r="87">
       <c r="T87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U87" s="7" t="inlineStr">
@@ -5915,7 +5935,7 @@
         </is>
       </c>
       <c r="V87" s="7" t="n">
-        <v>77273</v>
+        <v>78640</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>73</v>
@@ -5947,7 +5967,7 @@
     <row r="88">
       <c r="T88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U88" s="4" t="inlineStr">
@@ -5956,7 +5976,7 @@
         </is>
       </c>
       <c r="V88" s="4" t="n">
-        <v>80657</v>
+        <v>79108</v>
       </c>
       <c r="X88" s="4" t="n">
         <v>5</v>
@@ -5988,7 +6008,7 @@
     <row r="89">
       <c r="T89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U89" s="7" t="inlineStr">
@@ -5997,7 +6017,7 @@
         </is>
       </c>
       <c r="V89" s="7" t="n">
-        <v>79898</v>
+        <v>76911</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>1</v>
@@ -6029,7 +6049,7 @@
     <row r="90">
       <c r="T90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U90" s="4" t="inlineStr">
@@ -6038,7 +6058,7 @@
         </is>
       </c>
       <c r="V90" s="4" t="n">
-        <v>82443</v>
+        <v>77273</v>
       </c>
       <c r="X90" s="4" t="n">
         <v>107</v>
@@ -6070,7 +6090,7 @@
     <row r="91">
       <c r="T91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U91" s="7" t="inlineStr">
@@ -6079,7 +6099,7 @@
         </is>
       </c>
       <c r="V91" s="7" t="n">
-        <v>80658</v>
+        <v>80657</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>13</v>
@@ -6111,7 +6131,7 @@
     <row r="92">
       <c r="T92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U92" s="4" t="inlineStr">
@@ -6120,7 +6140,7 @@
         </is>
       </c>
       <c r="V92" s="4" t="n">
-        <v>78475</v>
+        <v>79898</v>
       </c>
       <c r="X92" s="4" t="n">
         <v>56</v>
@@ -6152,7 +6172,7 @@
     <row r="93">
       <c r="T93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U93" s="7" t="inlineStr">
@@ -6161,7 +6181,7 @@
         </is>
       </c>
       <c r="V93" s="7" t="n">
-        <v>76874</v>
+        <v>82443</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>32</v>
@@ -6193,7 +6213,7 @@
     <row r="94">
       <c r="T94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U94" s="4" t="inlineStr">
@@ -6202,7 +6222,7 @@
         </is>
       </c>
       <c r="V94" s="4" t="n">
-        <v>77058</v>
+        <v>80658</v>
       </c>
       <c r="X94" s="4" t="n">
         <v>13</v>
@@ -6234,7 +6254,7 @@
     <row r="95">
       <c r="T95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U95" s="7" t="inlineStr">
@@ -6243,7 +6263,7 @@
         </is>
       </c>
       <c r="V95" s="7" t="n">
-        <v>79206</v>
+        <v>78475</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>78</v>
@@ -6275,7 +6295,7 @@
     <row r="96">
       <c r="T96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U96" s="4" t="inlineStr">
@@ -6284,7 +6304,7 @@
         </is>
       </c>
       <c r="V96" s="4" t="n">
-        <v>79070</v>
+        <v>76874</v>
       </c>
       <c r="X96" s="4" t="n">
         <v>10</v>
@@ -6316,7 +6336,7 @@
     <row r="97">
       <c r="T97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U97" s="7" t="inlineStr">
@@ -6325,7 +6345,7 @@
         </is>
       </c>
       <c r="V97" s="7" t="n">
-        <v>81246</v>
+        <v>77058</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>1</v>
@@ -6357,16 +6377,16 @@
     <row r="98">
       <c r="T98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U98" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V98" s="4" t="n">
-        <v>721</v>
+        <v>79206</v>
       </c>
       <c r="X98" s="4" t="n">
         <v>114</v>
@@ -6398,16 +6418,16 @@
     <row r="99">
       <c r="T99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U99" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V99" s="7" t="n">
-        <v>715</v>
+        <v>79070</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>15</v>
@@ -6439,16 +6459,16 @@
     <row r="100">
       <c r="T100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U100" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V100" s="4" t="n">
-        <v>745</v>
+        <v>81246</v>
       </c>
       <c r="X100" s="4" t="n">
         <v>53</v>
@@ -6480,16 +6500,16 @@
     <row r="101">
       <c r="T101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U101" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V101" s="7" t="n">
-        <v>702</v>
+        <v>80308</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>32</v>
@@ -6521,7 +6541,7 @@
     <row r="102">
       <c r="T102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U102" s="4" t="inlineStr">
@@ -6530,7 +6550,7 @@
         </is>
       </c>
       <c r="V102" s="4" t="n">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="X102" s="4" t="n">
         <v>14</v>
@@ -6562,7 +6582,7 @@
     <row r="103">
       <c r="T103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U103" s="7" t="inlineStr">
@@ -6571,7 +6591,7 @@
         </is>
       </c>
       <c r="V103" s="7" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>80</v>
@@ -6603,7 +6623,7 @@
     <row r="104">
       <c r="T104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U104" s="4" t="inlineStr">
@@ -6612,7 +6632,7 @@
         </is>
       </c>
       <c r="V104" s="4" t="n">
-        <v>696</v>
+        <v>745</v>
       </c>
       <c r="X104" s="4" t="n">
         <v>1</v>
@@ -6644,7 +6664,7 @@
     <row r="105">
       <c r="T105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U105" s="7" t="inlineStr">
@@ -6653,7 +6673,7 @@
         </is>
       </c>
       <c r="V105" s="7" t="n">
-        <v>750</v>
+        <v>702</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>9</v>
@@ -6685,7 +6705,7 @@
     <row r="106">
       <c r="T106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U106" s="4" t="inlineStr">
@@ -6694,7 +6714,7 @@
         </is>
       </c>
       <c r="V106" s="4" t="n">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="X106" s="4" t="n">
         <v>4</v>
@@ -6726,7 +6746,7 @@
     <row r="107">
       <c r="T107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U107" s="7" t="inlineStr">
@@ -6735,7 +6755,7 @@
         </is>
       </c>
       <c r="V107" s="7" t="n">
-        <v>748</v>
+        <v>700</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>97</v>
@@ -6767,7 +6787,7 @@
     <row r="108">
       <c r="T108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U108" s="4" t="inlineStr">
@@ -6776,7 +6796,7 @@
         </is>
       </c>
       <c r="V108" s="4" t="n">
-        <v>736</v>
+        <v>696</v>
       </c>
       <c r="X108" s="4" t="n">
         <v>10</v>
@@ -6808,7 +6828,7 @@
     <row r="109">
       <c r="T109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U109" s="7" t="inlineStr">
@@ -6817,7 +6837,7 @@
         </is>
       </c>
       <c r="V109" s="7" t="n">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>52</v>
@@ -6849,7 +6869,7 @@
     <row r="110">
       <c r="T110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U110" s="4" t="inlineStr">
@@ -6858,7 +6878,7 @@
         </is>
       </c>
       <c r="V110" s="4" t="n">
-        <v>707</v>
+        <v>729</v>
       </c>
       <c r="X110" s="4" t="n">
         <v>37</v>
@@ -6890,7 +6910,7 @@
     <row r="111">
       <c r="T111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U111" s="7" t="inlineStr">
@@ -6899,7 +6919,7 @@
         </is>
       </c>
       <c r="V111" s="7" t="n">
-        <v>713</v>
+        <v>748</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>18</v>
@@ -6931,7 +6951,7 @@
     <row r="112">
       <c r="T112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U112" s="4" t="inlineStr">
@@ -6940,7 +6960,7 @@
         </is>
       </c>
       <c r="V112" s="4" t="n">
-        <v>786</v>
+        <v>736</v>
       </c>
       <c r="X112" s="4" t="n">
         <v>64</v>
@@ -6972,7 +6992,7 @@
     <row r="113">
       <c r="T113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U113" s="7" t="inlineStr">
@@ -6981,7 +7001,7 @@
         </is>
       </c>
       <c r="V113" s="7" t="n">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="X113" s="7" t="n">
         <v>7</v>
@@ -7013,7 +7033,7 @@
     <row r="114">
       <c r="T114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U114" s="4" t="inlineStr">
@@ -7022,7 +7042,7 @@
         </is>
       </c>
       <c r="V114" s="4" t="n">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="X114" s="4" t="n">
         <v>106</v>
@@ -7054,7 +7074,7 @@
     <row r="115">
       <c r="T115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U115" s="7" t="inlineStr">
@@ -7063,7 +7083,7 @@
         </is>
       </c>
       <c r="V115" s="7" t="n">
-        <v>695</v>
+        <v>713</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>14</v>
@@ -7095,7 +7115,7 @@
     <row r="116">
       <c r="T116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U116" s="4" t="inlineStr">
@@ -7104,7 +7124,7 @@
         </is>
       </c>
       <c r="V116" s="4" t="n">
-        <v>693</v>
+        <v>786</v>
       </c>
       <c r="X116" s="4" t="n">
         <v>65</v>
@@ -7136,7 +7156,7 @@
     <row r="117">
       <c r="T117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
@@ -7145,7 +7165,7 @@
         </is>
       </c>
       <c r="V117" s="7" t="n">
-        <v>686</v>
+        <v>730</v>
       </c>
       <c r="X117" s="7" t="n">
         <v>24</v>
@@ -7177,7 +7197,7 @@
     <row r="118">
       <c r="T118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U118" s="4" t="inlineStr">
@@ -7186,7 +7206,7 @@
         </is>
       </c>
       <c r="V118" s="4" t="n">
-        <v>673</v>
+        <v>726</v>
       </c>
       <c r="X118" s="4" t="n">
         <v>14</v>
@@ -7218,7 +7238,7 @@
     <row r="119">
       <c r="T119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U119" s="7" t="inlineStr">
@@ -7227,7 +7247,7 @@
         </is>
       </c>
       <c r="V119" s="7" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="X119" s="7" t="n">
         <v>66</v>
@@ -7259,7 +7279,7 @@
     <row r="120">
       <c r="T120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U120" s="4" t="inlineStr">
@@ -7268,7 +7288,7 @@
         </is>
       </c>
       <c r="V120" s="4" t="n">
-        <v>717</v>
+        <v>693</v>
       </c>
       <c r="X120" s="4" t="n">
         <v>1</v>
@@ -7300,7 +7320,7 @@
     <row r="121">
       <c r="T121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U121" s="7" t="inlineStr">
@@ -7309,7 +7329,7 @@
         </is>
       </c>
       <c r="V121" s="7" t="n">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>9</v>
@@ -7341,16 +7361,16 @@
     <row r="122">
       <c r="T122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U122" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V122" s="4" t="n">
-        <v>47976</v>
+        <v>673</v>
       </c>
       <c r="X122" s="4" t="n">
         <v>116</v>
@@ -7382,16 +7402,16 @@
     <row r="123">
       <c r="T123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V123" s="7" t="n">
-        <v>47122</v>
+        <v>752</v>
       </c>
       <c r="X123" s="7" t="n">
         <v>17</v>
@@ -7423,16 +7443,16 @@
     <row r="124">
       <c r="T124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U124" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V124" s="4" t="n">
-        <v>47233</v>
+        <v>717</v>
       </c>
       <c r="X124" s="4" t="n">
         <v>52</v>
@@ -7464,16 +7484,16 @@
     <row r="125">
       <c r="T125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U125" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V125" s="7" t="n">
-        <v>48580</v>
+        <v>706</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>38</v>
@@ -7505,16 +7525,16 @@
     <row r="126">
       <c r="T126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U126" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V126" s="4" t="n">
-        <v>47383</v>
+        <v>703</v>
       </c>
       <c r="X126" s="4" t="n">
         <v>19</v>
@@ -7546,7 +7566,7 @@
     <row r="127">
       <c r="T127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U127" s="7" t="inlineStr">
@@ -7555,7 +7575,7 @@
         </is>
       </c>
       <c r="V127" s="7" t="n">
-        <v>46456</v>
+        <v>47976</v>
       </c>
       <c r="X127" s="7" t="n">
         <v>79</v>
@@ -7587,7 +7607,7 @@
     <row r="128">
       <c r="T128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U128" s="4" t="inlineStr">
@@ -7596,7 +7616,7 @@
         </is>
       </c>
       <c r="V128" s="4" t="n">
-        <v>46400</v>
+        <v>47122</v>
       </c>
       <c r="X128" s="4" t="n">
         <v>9</v>
@@ -7628,7 +7648,7 @@
     <row r="129">
       <c r="T129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
@@ -7637,7 +7657,7 @@
         </is>
       </c>
       <c r="V129" s="7" t="n">
-        <v>47755</v>
+        <v>47233</v>
       </c>
       <c r="X129" s="7" t="n">
         <v>1</v>
@@ -7669,7 +7689,7 @@
     <row r="130">
       <c r="T130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U130" s="4" t="inlineStr">
@@ -7678,7 +7698,7 @@
         </is>
       </c>
       <c r="V130" s="4" t="n">
-        <v>47520</v>
+        <v>48580</v>
       </c>
       <c r="X130" s="4" t="n">
         <v>134</v>
@@ -7710,7 +7730,7 @@
     <row r="131">
       <c r="T131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U131" s="7" t="inlineStr">
@@ -7719,7 +7739,7 @@
         </is>
       </c>
       <c r="V131" s="7" t="n">
-        <v>47354</v>
+        <v>47383</v>
       </c>
       <c r="X131" s="7" t="n">
         <v>22</v>
@@ -7751,7 +7771,7 @@
     <row r="132">
       <c r="T132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U132" s="4" t="inlineStr">
@@ -7760,7 +7780,7 @@
         </is>
       </c>
       <c r="V132" s="4" t="n">
-        <v>49015</v>
+        <v>46456</v>
       </c>
       <c r="X132" s="4" t="n">
         <v>65</v>
@@ -7792,7 +7812,7 @@
     <row r="133">
       <c r="T133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
@@ -7801,7 +7821,7 @@
         </is>
       </c>
       <c r="V133" s="7" t="n">
-        <v>48832</v>
+        <v>46400</v>
       </c>
       <c r="X133" s="7" t="n">
         <v>29</v>
@@ -7833,7 +7853,7 @@
     <row r="134">
       <c r="T134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U134" s="4" t="inlineStr">
@@ -7842,7 +7862,7 @@
         </is>
       </c>
       <c r="V134" s="4" t="n">
-        <v>46644</v>
+        <v>47755</v>
       </c>
       <c r="X134" s="4" t="n">
         <v>12</v>
@@ -7874,7 +7894,7 @@
     <row r="135">
       <c r="T135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U135" s="7" t="inlineStr">
@@ -7883,7 +7903,7 @@
         </is>
       </c>
       <c r="V135" s="7" t="n">
-        <v>46416</v>
+        <v>47520</v>
       </c>
       <c r="X135" s="7" t="n">
         <v>82</v>
@@ -7915,7 +7935,7 @@
     <row r="136">
       <c r="T136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U136" s="4" t="inlineStr">
@@ -7924,7 +7944,7 @@
         </is>
       </c>
       <c r="V136" s="4" t="n">
-        <v>48419</v>
+        <v>47354</v>
       </c>
       <c r="X136" s="4" t="n">
         <v>1</v>
@@ -7956,7 +7976,7 @@
     <row r="137">
       <c r="T137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U137" s="7" t="inlineStr">
@@ -7965,7 +7985,7 @@
         </is>
       </c>
       <c r="V137" s="7" t="n">
-        <v>47500</v>
+        <v>49015</v>
       </c>
       <c r="X137" s="7" t="n">
         <v>7</v>
@@ -7997,7 +8017,7 @@
     <row r="138">
       <c r="T138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U138" s="4" t="inlineStr">
@@ -8006,7 +8026,7 @@
         </is>
       </c>
       <c r="V138" s="4" t="n">
-        <v>47954</v>
+        <v>48832</v>
       </c>
       <c r="X138" s="4" t="n">
         <v>1</v>
@@ -8038,7 +8058,7 @@
     <row r="139">
       <c r="T139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
@@ -8047,7 +8067,7 @@
         </is>
       </c>
       <c r="V139" s="7" t="n">
-        <v>49088</v>
+        <v>46644</v>
       </c>
       <c r="X139" s="7" t="n">
         <v>107</v>
@@ -8079,7 +8099,7 @@
     <row r="140">
       <c r="T140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U140" s="4" t="inlineStr">
@@ -8088,7 +8108,7 @@
         </is>
       </c>
       <c r="V140" s="4" t="n">
-        <v>48111</v>
+        <v>46416</v>
       </c>
       <c r="X140" s="4" t="n">
         <v>24</v>
@@ -8120,7 +8140,7 @@
     <row r="141">
       <c r="T141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
@@ -8129,7 +8149,7 @@
         </is>
       </c>
       <c r="V141" s="7" t="n">
-        <v>46535</v>
+        <v>48419</v>
       </c>
       <c r="X141" s="7" t="n">
         <v>68</v>
@@ -8161,7 +8181,7 @@
     <row r="142">
       <c r="T142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U142" s="4" t="inlineStr">
@@ -8170,7 +8190,7 @@
         </is>
       </c>
       <c r="V142" s="4" t="n">
-        <v>46063</v>
+        <v>47500</v>
       </c>
       <c r="X142" s="4" t="n">
         <v>18</v>
@@ -8202,7 +8222,7 @@
     <row r="143">
       <c r="T143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
@@ -8211,7 +8231,7 @@
         </is>
       </c>
       <c r="V143" s="7" t="n">
-        <v>48085</v>
+        <v>47954</v>
       </c>
       <c r="X143" s="7" t="n">
         <v>12</v>
@@ -8243,7 +8263,7 @@
     <row r="144">
       <c r="T144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U144" s="4" t="inlineStr">
@@ -8252,7 +8272,7 @@
         </is>
       </c>
       <c r="V144" s="4" t="n">
-        <v>47472</v>
+        <v>49088</v>
       </c>
       <c r="X144" s="4" t="n">
         <v>70</v>
@@ -8284,7 +8304,7 @@
     <row r="145">
       <c r="T145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U145" s="7" t="inlineStr">
@@ -8293,7 +8313,7 @@
         </is>
       </c>
       <c r="V145" s="7" t="n">
-        <v>47003</v>
+        <v>48111</v>
       </c>
       <c r="X145" s="7" t="n">
         <v>2</v>
@@ -8325,16 +8345,16 @@
     <row r="146">
       <c r="T146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U146" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V146" s="4" t="n">
-        <v>1</v>
+        <v>46535</v>
       </c>
       <c r="X146" s="4" t="n">
         <v>6</v>
@@ -8366,16 +8386,16 @@
     <row r="147">
       <c r="T147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V147" s="7" t="n">
-        <v>1</v>
+        <v>46063</v>
       </c>
       <c r="X147" s="7" t="n">
         <v>2</v>
@@ -8407,16 +8427,16 @@
     <row r="148">
       <c r="T148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U148" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V148" s="4" t="n">
-        <v>1</v>
+        <v>48085</v>
       </c>
       <c r="X148" s="4" t="n">
         <v>115</v>
@@ -8448,16 +8468,16 @@
     <row r="149">
       <c r="T149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U149" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V149" s="7" t="n">
-        <v>1</v>
+        <v>47472</v>
       </c>
       <c r="X149" s="7" t="n">
         <v>20</v>
@@ -8489,16 +8509,16 @@
     <row r="150">
       <c r="T150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U150" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V150" s="4" t="n">
-        <v>1</v>
+        <v>47003</v>
       </c>
       <c r="X150" s="4" t="n">
         <v>69</v>
@@ -8530,16 +8550,16 @@
     <row r="151">
       <c r="T151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V151" s="7" t="n">
-        <v>1</v>
+        <v>48466</v>
       </c>
       <c r="X151" s="7" t="n">
         <v>41</v>
@@ -8571,7 +8591,7 @@
     <row r="152">
       <c r="T152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U152" s="4" t="inlineStr">
@@ -8612,7 +8632,7 @@
     <row r="153">
       <c r="T153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
@@ -8653,7 +8673,7 @@
     <row r="154">
       <c r="T154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U154" s="4" t="inlineStr">
@@ -8694,7 +8714,7 @@
     <row r="155">
       <c r="T155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U155" s="7" t="inlineStr">
@@ -8735,7 +8755,7 @@
     <row r="156">
       <c r="T156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U156" s="4" t="inlineStr">
@@ -8776,7 +8796,7 @@
     <row r="157">
       <c r="T157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
@@ -8817,7 +8837,7 @@
     <row r="158">
       <c r="T158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U158" s="4" t="inlineStr">
@@ -8858,7 +8878,7 @@
     <row r="159">
       <c r="T159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
@@ -8899,7 +8919,7 @@
     <row r="160">
       <c r="T160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U160" s="4" t="inlineStr">
@@ -8940,7 +8960,7 @@
     <row r="161">
       <c r="T161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
@@ -8981,7 +9001,7 @@
     <row r="162">
       <c r="T162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U162" s="4" t="inlineStr">
@@ -9022,7 +9042,7 @@
     <row r="163">
       <c r="T163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
@@ -9063,7 +9083,7 @@
     <row r="164">
       <c r="T164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U164" s="4" t="inlineStr">
@@ -9104,7 +9124,7 @@
     <row r="165">
       <c r="T165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U165" s="7" t="inlineStr">
@@ -9145,12 +9165,12 @@
     <row r="166">
       <c r="T166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U166" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V166" s="4" t="n">
@@ -9186,12 +9206,12 @@
     <row r="167">
       <c r="T167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V167" s="7" t="n">
@@ -9227,12 +9247,12 @@
     <row r="168">
       <c r="T168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U168" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V168" s="4" t="n">
@@ -9268,12 +9288,12 @@
     <row r="169">
       <c r="T169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U169" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V169" s="7" t="n">
@@ -9309,12 +9329,12 @@
     <row r="170">
       <c r="T170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U170" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V170" s="4" t="n">
@@ -9350,12 +9370,12 @@
     <row r="171">
       <c r="T171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U171" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V171" s="7" t="n">
@@ -9391,12 +9411,12 @@
     <row r="172">
       <c r="T172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U172" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V172" s="4" t="n">
@@ -9432,7 +9452,7 @@
     <row r="173">
       <c r="T173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
@@ -9473,7 +9493,7 @@
     <row r="174">
       <c r="T174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U174" s="4" t="inlineStr">
@@ -9514,7 +9534,7 @@
     <row r="175">
       <c r="T175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
@@ -9555,7 +9575,7 @@
     <row r="176">
       <c r="T176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U176" s="4" t="inlineStr">
@@ -9596,7 +9616,7 @@
     <row r="177">
       <c r="T177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U177" s="7" t="inlineStr">
@@ -9637,7 +9657,7 @@
     <row r="178">
       <c r="T178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U178" s="4" t="inlineStr">
@@ -9678,7 +9698,7 @@
     <row r="179">
       <c r="T179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr">
@@ -9719,7 +9739,7 @@
     <row r="180">
       <c r="T180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U180" s="4" t="inlineStr">
@@ -9760,7 +9780,7 @@
     <row r="181">
       <c r="T181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U181" s="7" t="inlineStr">
@@ -9801,7 +9821,7 @@
     <row r="182">
       <c r="T182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U182" s="4" t="inlineStr">
@@ -9842,7 +9862,7 @@
     <row r="183">
       <c r="T183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U183" s="7" t="inlineStr">
@@ -9883,7 +9903,7 @@
     <row r="184">
       <c r="T184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U184" s="4" t="inlineStr">
@@ -9924,7 +9944,7 @@
     <row r="185">
       <c r="T185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U185" s="7" t="inlineStr">
@@ -9965,7 +9985,7 @@
     <row r="186">
       <c r="T186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U186" s="4" t="inlineStr">
@@ -10006,7 +10026,7 @@
     <row r="187">
       <c r="T187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U187" s="7" t="inlineStr">
@@ -10047,7 +10067,7 @@
     <row r="188">
       <c r="T188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U188" s="4" t="inlineStr">
@@ -10088,16 +10108,16 @@
     <row r="189">
       <c r="T189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U189" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V189" s="7" t="n">
-        <v>9927</v>
+        <v>1</v>
       </c>
       <c r="X189" s="7" t="n">
         <v>17</v>
@@ -10129,16 +10149,16 @@
     <row r="190">
       <c r="T190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U190" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V190" s="4" t="n">
-        <v>9839</v>
+        <v>1</v>
       </c>
       <c r="X190" s="4" t="n">
         <v>63</v>
@@ -10170,16 +10190,16 @@
     <row r="191">
       <c r="T191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U191" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V191" s="7" t="n">
-        <v>9918</v>
+        <v>1</v>
       </c>
       <c r="X191" s="7" t="n">
         <v>35</v>
@@ -10211,16 +10231,16 @@
     <row r="192">
       <c r="T192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U192" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V192" s="4" t="n">
-        <v>10435</v>
+        <v>1</v>
       </c>
       <c r="X192" s="4" t="n">
         <v>26</v>
@@ -10252,19 +10272,19 @@
     <row r="193">
       <c r="T193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U193" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V193" s="7" t="n">
-        <v>10050</v>
+        <v>1</v>
       </c>
       <c r="X193" s="7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y193" s="7" t="inlineStr">
         <is>
@@ -10293,16 +10313,16 @@
     <row r="194">
       <c r="T194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U194" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V194" s="4" t="n">
-        <v>9768</v>
+        <v>1</v>
       </c>
       <c r="X194" s="4" t="n">
         <v>6</v>
@@ -10334,16 +10354,16 @@
     <row r="195">
       <c r="T195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U195" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V195" s="7" t="n">
-        <v>9920</v>
+        <v>1</v>
       </c>
       <c r="X195" s="7" t="n">
         <v>2</v>
@@ -10375,20 +10395,30 @@
     <row r="196">
       <c r="T196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U196" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V196" s="4" t="n">
-        <v>10435</v>
-      </c>
-      <c r="X196" s="4" t="n"/>
-      <c r="Y196" s="4" t="n"/>
-      <c r="Z196" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X196" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y196" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z196" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB196" s="4" t="n">
         <v>55</v>
       </c>
@@ -10406,7 +10436,7 @@
     <row r="197">
       <c r="T197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U197" s="7" t="inlineStr">
@@ -10415,11 +10445,21 @@
         </is>
       </c>
       <c r="V197" s="7" t="n">
-        <v>10434</v>
-      </c>
-      <c r="X197" s="7" t="n"/>
-      <c r="Y197" s="7" t="n"/>
-      <c r="Z197" s="7" t="n"/>
+        <v>9927</v>
+      </c>
+      <c r="X197" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y197" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z197" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB197" s="7" t="n">
         <v>122</v>
       </c>
@@ -10437,7 +10477,7 @@
     <row r="198">
       <c r="T198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U198" s="4" t="inlineStr">
@@ -10446,11 +10486,21 @@
         </is>
       </c>
       <c r="V198" s="4" t="n">
-        <v>10284</v>
-      </c>
-      <c r="X198" s="4" t="n"/>
-      <c r="Y198" s="4" t="n"/>
-      <c r="Z198" s="4" t="n"/>
+        <v>9839</v>
+      </c>
+      <c r="X198" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y198" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z198" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB198" s="4" t="n">
         <v>1</v>
       </c>
@@ -10468,7 +10518,7 @@
     <row r="199">
       <c r="T199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U199" s="7" t="inlineStr">
@@ -10477,11 +10527,21 @@
         </is>
       </c>
       <c r="V199" s="7" t="n">
-        <v>10458</v>
-      </c>
-      <c r="X199" s="7" t="n"/>
-      <c r="Y199" s="7" t="n"/>
-      <c r="Z199" s="7" t="n"/>
+        <v>9918</v>
+      </c>
+      <c r="X199" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y199" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z199" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB199" s="7" t="n">
         <v>6</v>
       </c>
@@ -10499,7 +10559,7 @@
     <row r="200">
       <c r="T200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U200" s="4" t="inlineStr">
@@ -10508,11 +10568,21 @@
         </is>
       </c>
       <c r="V200" s="4" t="n">
-        <v>10153</v>
-      </c>
-      <c r="X200" s="4" t="n"/>
-      <c r="Y200" s="4" t="n"/>
-      <c r="Z200" s="4" t="n"/>
+        <v>10435</v>
+      </c>
+      <c r="X200" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y200" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z200" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB200" s="4" t="n">
         <v>2</v>
       </c>
@@ -10530,7 +10600,7 @@
     <row r="201">
       <c r="T201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U201" s="7" t="inlineStr">
@@ -10539,11 +10609,21 @@
         </is>
       </c>
       <c r="V201" s="7" t="n">
-        <v>9843</v>
-      </c>
-      <c r="X201" s="7" t="n"/>
-      <c r="Y201" s="7" t="n"/>
-      <c r="Z201" s="7" t="n"/>
+        <v>10050</v>
+      </c>
+      <c r="X201" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y201" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z201" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB201" s="7" t="n">
         <v>321</v>
       </c>
@@ -10561,7 +10641,7 @@
     <row r="202">
       <c r="T202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U202" s="4" t="inlineStr">
@@ -10570,11 +10650,21 @@
         </is>
       </c>
       <c r="V202" s="4" t="n">
-        <v>10433</v>
-      </c>
-      <c r="X202" s="4" t="n"/>
-      <c r="Y202" s="4" t="n"/>
-      <c r="Z202" s="4" t="n"/>
+        <v>9768</v>
+      </c>
+      <c r="X202" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y202" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z202" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB202" s="4" t="n">
         <v>28</v>
       </c>
@@ -10592,7 +10682,7 @@
     <row r="203">
       <c r="T203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U203" s="7" t="inlineStr">
@@ -10601,11 +10691,21 @@
         </is>
       </c>
       <c r="V203" s="7" t="n">
-        <v>10670</v>
-      </c>
-      <c r="X203" s="7" t="n"/>
-      <c r="Y203" s="7" t="n"/>
-      <c r="Z203" s="7" t="n"/>
+        <v>9920</v>
+      </c>
+      <c r="X203" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y203" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z203" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB203" s="7" t="n">
         <v>150</v>
       </c>
@@ -10623,7 +10723,7 @@
     <row r="204">
       <c r="T204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U204" s="4" t="inlineStr">
@@ -10632,11 +10732,21 @@
         </is>
       </c>
       <c r="V204" s="4" t="n">
-        <v>10599</v>
-      </c>
-      <c r="X204" s="4" t="n"/>
-      <c r="Y204" s="4" t="n"/>
-      <c r="Z204" s="4" t="n"/>
+        <v>10435</v>
+      </c>
+      <c r="X204" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y204" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z204" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB204" s="4" t="n">
         <v>55</v>
       </c>
@@ -10654,7 +10764,7 @@
     <row r="205">
       <c r="T205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U205" s="7" t="inlineStr">
@@ -10663,7 +10773,7 @@
         </is>
       </c>
       <c r="V205" s="7" t="n">
-        <v>10619</v>
+        <v>10434</v>
       </c>
       <c r="X205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
@@ -10685,7 +10795,7 @@
     <row r="206">
       <c r="T206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U206" s="4" t="inlineStr">
@@ -10694,7 +10804,7 @@
         </is>
       </c>
       <c r="V206" s="4" t="n">
-        <v>10415</v>
+        <v>10284</v>
       </c>
       <c r="X206" s="4" t="n"/>
       <c r="Y206" s="4" t="n"/>
@@ -10716,7 +10826,7 @@
     <row r="207">
       <c r="T207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U207" s="7" t="inlineStr">
@@ -10725,7 +10835,7 @@
         </is>
       </c>
       <c r="V207" s="7" t="n">
-        <v>10065</v>
+        <v>10458</v>
       </c>
       <c r="X207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
@@ -10747,7 +10857,7 @@
     <row r="208">
       <c r="T208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U208" s="4" t="inlineStr">
@@ -10756,7 +10866,7 @@
         </is>
       </c>
       <c r="V208" s="4" t="n">
-        <v>10158</v>
+        <v>10153</v>
       </c>
       <c r="X208" s="4" t="n"/>
       <c r="Y208" s="4" t="n"/>
@@ -10778,7 +10888,7 @@
     <row r="209">
       <c r="T209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U209" s="7" t="inlineStr">
@@ -10787,7 +10897,7 @@
         </is>
       </c>
       <c r="V209" s="7" t="n">
-        <v>10333</v>
+        <v>9843</v>
       </c>
       <c r="X209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
@@ -10809,7 +10919,7 @@
     <row r="210">
       <c r="T210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U210" s="4" t="inlineStr">
@@ -10818,7 +10928,7 @@
         </is>
       </c>
       <c r="V210" s="4" t="n">
-        <v>10414</v>
+        <v>10433</v>
       </c>
       <c r="X210" s="4" t="n"/>
       <c r="Y210" s="4" t="n"/>
@@ -10840,7 +10950,7 @@
     <row r="211">
       <c r="T211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U211" s="7" t="inlineStr">
@@ -10849,7 +10959,7 @@
         </is>
       </c>
       <c r="V211" s="7" t="n">
-        <v>10453</v>
+        <v>10670</v>
       </c>
       <c r="X211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
@@ -10871,7 +10981,7 @@
     <row r="212">
       <c r="T212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U212" s="4" t="inlineStr">
@@ -10880,7 +10990,7 @@
         </is>
       </c>
       <c r="V212" s="4" t="n">
-        <v>10879</v>
+        <v>10599</v>
       </c>
       <c r="X212" s="4" t="n"/>
       <c r="Y212" s="4" t="n"/>
@@ -10902,16 +11012,16 @@
     <row r="213">
       <c r="T213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U213" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation50987</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V213" s="7" t="n">
-        <v>1</v>
+        <v>10619</v>
       </c>
       <c r="X213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
@@ -10933,16 +11043,16 @@
     <row r="214">
       <c r="T214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U214" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation75114</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V214" s="4" t="n">
-        <v>1</v>
+        <v>10415</v>
       </c>
       <c r="X214" s="4" t="n"/>
       <c r="Y214" s="4" t="n"/>
@@ -10964,16 +11074,16 @@
     <row r="215">
       <c r="T215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U215" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V215" s="7" t="n">
-        <v>21493</v>
+        <v>10065</v>
       </c>
       <c r="X215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
@@ -10995,16 +11105,16 @@
     <row r="216">
       <c r="T216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U216" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V216" s="4" t="n">
-        <v>21012</v>
+        <v>10158</v>
       </c>
       <c r="X216" s="4" t="n"/>
       <c r="Y216" s="4" t="n"/>
@@ -11026,16 +11136,16 @@
     <row r="217">
       <c r="T217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U217" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V217" s="7" t="n">
-        <v>21635</v>
+        <v>10333</v>
       </c>
       <c r="X217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
@@ -11057,16 +11167,16 @@
     <row r="218">
       <c r="T218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U218" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V218" s="4" t="n">
-        <v>21969</v>
+        <v>10414</v>
       </c>
       <c r="X218" s="4" t="n"/>
       <c r="Y218" s="4" t="n"/>
@@ -11088,112 +11198,162 @@
     <row r="219">
       <c r="T219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U219" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V219" s="7" t="n">
-        <v>21723</v>
+        <v>10453</v>
       </c>
       <c r="X219" s="7" t="n"/>
       <c r="Y219" s="7" t="n"/>
       <c r="Z219" s="7" t="n"/>
-      <c r="AB219" s="7" t="n"/>
-      <c r="AC219" s="7" t="n"/>
-      <c r="AD219" s="7" t="n"/>
+      <c r="AB219" s="7" t="n">
+        <v>337</v>
+      </c>
+      <c r="AC219" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD219" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="T220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U220" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V220" s="4" t="n">
-        <v>20879</v>
+        <v>10879</v>
       </c>
       <c r="X220" s="4" t="n"/>
       <c r="Y220" s="4" t="n"/>
       <c r="Z220" s="4" t="n"/>
-      <c r="AB220" s="4" t="n"/>
-      <c r="AC220" s="4" t="n"/>
-      <c r="AD220" s="4" t="n"/>
+      <c r="AB220" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC220" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD220" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="T221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U221" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V221" s="7" t="n">
-        <v>20783</v>
+        <v>10826</v>
       </c>
       <c r="X221" s="7" t="n"/>
       <c r="Y221" s="7" t="n"/>
       <c r="Z221" s="7" t="n"/>
-      <c r="AB221" s="7" t="n"/>
-      <c r="AC221" s="7" t="n"/>
-      <c r="AD221" s="7" t="n"/>
+      <c r="AB221" s="7" t="n">
+        <v>141</v>
+      </c>
+      <c r="AC221" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD221" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="T222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U222" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation50987</t>
         </is>
       </c>
       <c r="V222" s="4" t="n">
-        <v>21875</v>
+        <v>1</v>
       </c>
       <c r="X222" s="4" t="n"/>
       <c r="Y222" s="4" t="n"/>
       <c r="Z222" s="4" t="n"/>
-      <c r="AB222" s="4" t="n"/>
-      <c r="AC222" s="4" t="n"/>
-      <c r="AD222" s="4" t="n"/>
+      <c r="AB222" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC222" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD222" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="T223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U223" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation75114</t>
         </is>
       </c>
       <c r="V223" s="7" t="n">
-        <v>22103</v>
+        <v>1</v>
       </c>
       <c r="X223" s="7" t="n"/>
       <c r="Y223" s="7" t="n"/>
       <c r="Z223" s="7" t="n"/>
-      <c r="AB223" s="7" t="n"/>
-      <c r="AC223" s="7" t="n"/>
-      <c r="AD223" s="7" t="n"/>
+      <c r="AB223" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC223" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD223" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="T224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U224" s="4" t="inlineStr">
@@ -11202,19 +11362,29 @@
         </is>
       </c>
       <c r="V224" s="4" t="n">
-        <v>22799</v>
+        <v>21493</v>
       </c>
       <c r="X224" s="4" t="n"/>
       <c r="Y224" s="4" t="n"/>
       <c r="Z224" s="4" t="n"/>
-      <c r="AB224" s="4" t="n"/>
-      <c r="AC224" s="4" t="n"/>
-      <c r="AD224" s="4" t="n"/>
+      <c r="AB224" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC224" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD224" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="T225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U225" s="7" t="inlineStr">
@@ -11223,19 +11393,29 @@
         </is>
       </c>
       <c r="V225" s="7" t="n">
-        <v>22705</v>
+        <v>21012</v>
       </c>
       <c r="X225" s="7" t="n"/>
       <c r="Y225" s="7" t="n"/>
       <c r="Z225" s="7" t="n"/>
-      <c r="AB225" s="7" t="n"/>
-      <c r="AC225" s="7" t="n"/>
-      <c r="AD225" s="7" t="n"/>
+      <c r="AB225" s="7" t="n">
+        <v>133</v>
+      </c>
+      <c r="AC225" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD225" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="T226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U226" s="4" t="inlineStr">
@@ -11244,19 +11424,29 @@
         </is>
       </c>
       <c r="V226" s="4" t="n">
-        <v>21885</v>
+        <v>21635</v>
       </c>
       <c r="X226" s="4" t="n"/>
       <c r="Y226" s="4" t="n"/>
       <c r="Z226" s="4" t="n"/>
-      <c r="AB226" s="4" t="n"/>
-      <c r="AC226" s="4" t="n"/>
-      <c r="AD226" s="4" t="n"/>
+      <c r="AB226" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC226" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD226" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="T227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U227" s="7" t="inlineStr">
@@ -11265,19 +11455,29 @@
         </is>
       </c>
       <c r="V227" s="7" t="n">
-        <v>21360</v>
+        <v>21969</v>
       </c>
       <c r="X227" s="7" t="n"/>
       <c r="Y227" s="7" t="n"/>
       <c r="Z227" s="7" t="n"/>
-      <c r="AB227" s="7" t="n"/>
-      <c r="AC227" s="7" t="n"/>
-      <c r="AD227" s="7" t="n"/>
+      <c r="AB227" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC227" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD227" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="T228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U228" s="4" t="inlineStr">
@@ -11286,7 +11486,7 @@
         </is>
       </c>
       <c r="V228" s="4" t="n">
-        <v>20612</v>
+        <v>21723</v>
       </c>
       <c r="X228" s="4" t="n"/>
       <c r="Y228" s="4" t="n"/>
@@ -11298,7 +11498,7 @@
     <row r="229">
       <c r="T229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U229" s="7" t="inlineStr">
@@ -11307,7 +11507,7 @@
         </is>
       </c>
       <c r="V229" s="7" t="n">
-        <v>22101</v>
+        <v>20879</v>
       </c>
       <c r="X229" s="7" t="n"/>
       <c r="Y229" s="7" t="n"/>
@@ -11319,7 +11519,7 @@
     <row r="230">
       <c r="T230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U230" s="4" t="inlineStr">
@@ -11328,7 +11528,7 @@
         </is>
       </c>
       <c r="V230" s="4" t="n">
-        <v>22665</v>
+        <v>20783</v>
       </c>
       <c r="X230" s="4" t="n"/>
       <c r="Y230" s="4" t="n"/>
@@ -11340,7 +11540,7 @@
     <row r="231">
       <c r="T231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U231" s="7" t="inlineStr">
@@ -11349,7 +11549,7 @@
         </is>
       </c>
       <c r="V231" s="7" t="n">
-        <v>22473</v>
+        <v>21875</v>
       </c>
       <c r="X231" s="7" t="n"/>
       <c r="Y231" s="7" t="n"/>
@@ -11361,7 +11561,7 @@
     <row r="232">
       <c r="T232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U232" s="4" t="inlineStr">
@@ -11370,7 +11570,7 @@
         </is>
       </c>
       <c r="V232" s="4" t="n">
-        <v>22903</v>
+        <v>22103</v>
       </c>
       <c r="X232" s="4" t="n"/>
       <c r="Y232" s="4" t="n"/>
@@ -11382,7 +11582,7 @@
     <row r="233">
       <c r="T233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U233" s="7" t="inlineStr">
@@ -11391,7 +11591,7 @@
         </is>
       </c>
       <c r="V233" s="7" t="n">
-        <v>21829</v>
+        <v>22799</v>
       </c>
       <c r="X233" s="7" t="n"/>
       <c r="Y233" s="7" t="n"/>
@@ -11403,7 +11603,7 @@
     <row r="234">
       <c r="T234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U234" s="4" t="inlineStr">
@@ -11412,7 +11612,7 @@
         </is>
       </c>
       <c r="V234" s="4" t="n">
-        <v>20959</v>
+        <v>22705</v>
       </c>
       <c r="X234" s="4" t="n"/>
       <c r="Y234" s="4" t="n"/>
@@ -11424,7 +11624,7 @@
     <row r="235">
       <c r="T235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U235" s="7" t="inlineStr">
@@ -11433,7 +11633,7 @@
         </is>
       </c>
       <c r="V235" s="7" t="n">
-        <v>20856</v>
+        <v>21885</v>
       </c>
       <c r="X235" s="7" t="n"/>
       <c r="Y235" s="7" t="n"/>
@@ -11445,7 +11645,7 @@
     <row r="236">
       <c r="T236" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U236" s="4" t="inlineStr">
@@ -11454,7 +11654,7 @@
         </is>
       </c>
       <c r="V236" s="4" t="n">
-        <v>23061</v>
+        <v>21360</v>
       </c>
       <c r="X236" s="4" t="n"/>
       <c r="Y236" s="4" t="n"/>
@@ -11466,7 +11666,7 @@
     <row r="237">
       <c r="T237" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U237" s="7" t="inlineStr">
@@ -11475,7 +11675,7 @@
         </is>
       </c>
       <c r="V237" s="7" t="n">
-        <v>21952</v>
+        <v>20612</v>
       </c>
       <c r="X237" s="7" t="n"/>
       <c r="Y237" s="7" t="n"/>
@@ -11487,7 +11687,7 @@
     <row r="238">
       <c r="T238" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U238" s="4" t="inlineStr">
@@ -11496,7 +11696,7 @@
         </is>
       </c>
       <c r="V238" s="4" t="n">
-        <v>22608</v>
+        <v>22101</v>
       </c>
       <c r="X238" s="4" t="n"/>
       <c r="Y238" s="4" t="n"/>
@@ -11508,16 +11708,16 @@
     <row r="239">
       <c r="T239" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U239" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V239" s="7" t="n">
-        <v>16634</v>
+        <v>22665</v>
       </c>
       <c r="X239" s="7" t="n"/>
       <c r="Y239" s="7" t="n"/>
@@ -11529,16 +11729,16 @@
     <row r="240">
       <c r="T240" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U240" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V240" s="4" t="n">
-        <v>16721</v>
+        <v>22473</v>
       </c>
       <c r="X240" s="4" t="n"/>
       <c r="Y240" s="4" t="n"/>
@@ -11550,16 +11750,16 @@
     <row r="241">
       <c r="T241" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U241" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V241" s="7" t="n">
-        <v>16586</v>
+        <v>22903</v>
       </c>
       <c r="X241" s="7" t="n"/>
       <c r="Y241" s="7" t="n"/>
@@ -11571,16 +11771,16 @@
     <row r="242">
       <c r="T242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U242" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V242" s="4" t="n">
-        <v>16419</v>
+        <v>21829</v>
       </c>
       <c r="X242" s="4" t="n"/>
       <c r="Y242" s="4" t="n"/>
@@ -11592,16 +11792,16 @@
     <row r="243">
       <c r="T243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U243" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V243" s="7" t="n">
-        <v>15946</v>
+        <v>20959</v>
       </c>
       <c r="X243" s="7" t="n"/>
       <c r="Y243" s="7" t="n"/>
@@ -11613,16 +11813,16 @@
     <row r="244">
       <c r="T244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U244" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V244" s="4" t="n">
-        <v>16042</v>
+        <v>20856</v>
       </c>
       <c r="X244" s="4" t="n"/>
       <c r="Y244" s="4" t="n"/>
@@ -11634,16 +11834,16 @@
     <row r="245">
       <c r="T245" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U245" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V245" s="7" t="n">
-        <v>16409</v>
+        <v>23061</v>
       </c>
       <c r="X245" s="7" t="n"/>
       <c r="Y245" s="7" t="n"/>
@@ -11655,16 +11855,16 @@
     <row r="246">
       <c r="T246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U246" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V246" s="4" t="n">
-        <v>16831</v>
+        <v>21952</v>
       </c>
       <c r="X246" s="4" t="n"/>
       <c r="Y246" s="4" t="n"/>
@@ -11676,16 +11876,16 @@
     <row r="247">
       <c r="T247" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U247" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V247" s="7" t="n">
-        <v>16886</v>
+        <v>22608</v>
       </c>
       <c r="X247" s="7" t="n"/>
       <c r="Y247" s="7" t="n"/>
@@ -11697,16 +11897,16 @@
     <row r="248">
       <c r="T248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U248" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V248" s="4" t="n">
-        <v>16694</v>
+        <v>22674</v>
       </c>
       <c r="X248" s="4" t="n"/>
       <c r="Y248" s="4" t="n"/>
@@ -11718,7 +11918,7 @@
     <row r="249">
       <c r="T249" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U249" s="7" t="inlineStr">
@@ -11727,7 +11927,7 @@
         </is>
       </c>
       <c r="V249" s="7" t="n">
-        <v>16659</v>
+        <v>16634</v>
       </c>
       <c r="X249" s="7" t="n"/>
       <c r="Y249" s="7" t="n"/>
@@ -11739,7 +11939,7 @@
     <row r="250">
       <c r="T250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U250" s="4" t="inlineStr">
@@ -11748,7 +11948,7 @@
         </is>
       </c>
       <c r="V250" s="4" t="n">
-        <v>16268</v>
+        <v>16721</v>
       </c>
       <c r="X250" s="4" t="n"/>
       <c r="Y250" s="4" t="n"/>
@@ -11760,7 +11960,7 @@
     <row r="251">
       <c r="T251" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U251" s="7" t="inlineStr">
@@ -11769,7 +11969,7 @@
         </is>
       </c>
       <c r="V251" s="7" t="n">
-        <v>16259</v>
+        <v>16586</v>
       </c>
       <c r="X251" s="7" t="n"/>
       <c r="Y251" s="7" t="n"/>
@@ -11781,7 +11981,7 @@
     <row r="252">
       <c r="T252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U252" s="4" t="inlineStr">
@@ -11790,7 +11990,7 @@
         </is>
       </c>
       <c r="V252" s="4" t="n">
-        <v>16600</v>
+        <v>16419</v>
       </c>
       <c r="X252" s="4" t="n"/>
       <c r="Y252" s="4" t="n"/>
@@ -11802,7 +12002,7 @@
     <row r="253">
       <c r="T253" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U253" s="7" t="inlineStr">
@@ -11811,7 +12011,7 @@
         </is>
       </c>
       <c r="V253" s="7" t="n">
-        <v>16913</v>
+        <v>15946</v>
       </c>
       <c r="X253" s="7" t="n"/>
       <c r="Y253" s="7" t="n"/>
@@ -11823,7 +12023,7 @@
     <row r="254">
       <c r="T254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U254" s="4" t="inlineStr">
@@ -11832,7 +12032,7 @@
         </is>
       </c>
       <c r="V254" s="4" t="n">
-        <v>16991</v>
+        <v>16042</v>
       </c>
       <c r="X254" s="4" t="n"/>
       <c r="Y254" s="4" t="n"/>
@@ -11844,7 +12044,7 @@
     <row r="255">
       <c r="T255" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U255" s="7" t="inlineStr">
@@ -11853,7 +12053,7 @@
         </is>
       </c>
       <c r="V255" s="7" t="n">
-        <v>17365</v>
+        <v>16409</v>
       </c>
       <c r="X255" s="7" t="n"/>
       <c r="Y255" s="7" t="n"/>
@@ -11865,7 +12065,7 @@
     <row r="256">
       <c r="T256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U256" s="4" t="inlineStr">
@@ -11874,7 +12074,7 @@
         </is>
       </c>
       <c r="V256" s="4" t="n">
-        <v>16944</v>
+        <v>16831</v>
       </c>
       <c r="X256" s="4" t="n"/>
       <c r="Y256" s="4" t="n"/>
@@ -11886,7 +12086,7 @@
     <row r="257">
       <c r="T257" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U257" s="7" t="inlineStr">
@@ -11895,7 +12095,7 @@
         </is>
       </c>
       <c r="V257" s="7" t="n">
-        <v>16518</v>
+        <v>16886</v>
       </c>
       <c r="X257" s="7" t="n"/>
       <c r="Y257" s="7" t="n"/>
@@ -11907,7 +12107,7 @@
     <row r="258">
       <c r="T258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U258" s="4" t="inlineStr">
@@ -11916,7 +12116,7 @@
         </is>
       </c>
       <c r="V258" s="4" t="n">
-        <v>16634</v>
+        <v>16694</v>
       </c>
       <c r="X258" s="4" t="n"/>
       <c r="Y258" s="4" t="n"/>
@@ -11928,7 +12128,7 @@
     <row r="259">
       <c r="T259" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U259" s="7" t="inlineStr">
@@ -11937,7 +12137,7 @@
         </is>
       </c>
       <c r="V259" s="7" t="n">
-        <v>16711</v>
+        <v>16659</v>
       </c>
       <c r="X259" s="7" t="n"/>
       <c r="Y259" s="7" t="n"/>
@@ -11949,7 +12149,7 @@
     <row r="260">
       <c r="T260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U260" s="4" t="inlineStr">
@@ -11958,7 +12158,7 @@
         </is>
       </c>
       <c r="V260" s="4" t="n">
-        <v>17379</v>
+        <v>16268</v>
       </c>
       <c r="X260" s="4" t="n"/>
       <c r="Y260" s="4" t="n"/>
@@ -11970,7 +12170,7 @@
     <row r="261">
       <c r="T261" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U261" s="7" t="inlineStr">
@@ -11979,7 +12179,7 @@
         </is>
       </c>
       <c r="V261" s="7" t="n">
-        <v>17551</v>
+        <v>16259</v>
       </c>
       <c r="X261" s="7" t="n"/>
       <c r="Y261" s="7" t="n"/>
@@ -11991,7 +12191,7 @@
     <row r="262">
       <c r="T262" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U262" s="4" t="inlineStr">
@@ -12000,7 +12200,7 @@
         </is>
       </c>
       <c r="V262" s="4" t="n">
-        <v>17474</v>
+        <v>16600</v>
       </c>
       <c r="X262" s="4" t="n"/>
       <c r="Y262" s="4" t="n"/>
@@ -12012,16 +12212,16 @@
     <row r="263">
       <c r="T263" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U263" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V263" s="7" t="n">
-        <v>724</v>
+        <v>16913</v>
       </c>
       <c r="X263" s="7" t="n"/>
       <c r="Y263" s="7" t="n"/>
@@ -12033,16 +12233,16 @@
     <row r="264">
       <c r="T264" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U264" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V264" s="4" t="n">
-        <v>746</v>
+        <v>16991</v>
       </c>
       <c r="X264" s="4" t="n"/>
       <c r="Y264" s="4" t="n"/>
@@ -12054,16 +12254,16 @@
     <row r="265">
       <c r="T265" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U265" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V265" s="7" t="n">
-        <v>723</v>
+        <v>17365</v>
       </c>
       <c r="X265" s="7" t="n"/>
       <c r="Y265" s="7" t="n"/>
@@ -12075,16 +12275,16 @@
     <row r="266">
       <c r="T266" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U266" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V266" s="4" t="n">
-        <v>708</v>
+        <v>16944</v>
       </c>
       <c r="X266" s="4" t="n"/>
       <c r="Y266" s="4" t="n"/>
@@ -12096,16 +12296,16 @@
     <row r="267">
       <c r="T267" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U267" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V267" s="7" t="n">
-        <v>735</v>
+        <v>16518</v>
       </c>
       <c r="X267" s="7" t="n"/>
       <c r="Y267" s="7" t="n"/>
@@ -12117,16 +12317,16 @@
     <row r="268">
       <c r="T268" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U268" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V268" s="4" t="n">
-        <v>714</v>
+        <v>16634</v>
       </c>
       <c r="X268" s="4" t="n"/>
       <c r="Y268" s="4" t="n"/>
@@ -12138,16 +12338,16 @@
     <row r="269">
       <c r="T269" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U269" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V269" s="7" t="n">
-        <v>706</v>
+        <v>16711</v>
       </c>
       <c r="X269" s="7" t="n"/>
       <c r="Y269" s="7" t="n"/>
@@ -12159,16 +12359,16 @@
     <row r="270">
       <c r="T270" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U270" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V270" s="4" t="n">
-        <v>729</v>
+        <v>17379</v>
       </c>
       <c r="X270" s="4" t="n"/>
       <c r="Y270" s="4" t="n"/>
@@ -12180,16 +12380,16 @@
     <row r="271">
       <c r="T271" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U271" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V271" s="7" t="n">
-        <v>719</v>
+        <v>17551</v>
       </c>
       <c r="X271" s="7" t="n"/>
       <c r="Y271" s="7" t="n"/>
@@ -12201,16 +12401,16 @@
     <row r="272">
       <c r="T272" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U272" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V272" s="4" t="n">
-        <v>719</v>
+        <v>17474</v>
       </c>
       <c r="X272" s="4" t="n"/>
       <c r="Y272" s="4" t="n"/>
@@ -12222,16 +12422,16 @@
     <row r="273">
       <c r="T273" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U273" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V273" s="7" t="n">
-        <v>730</v>
+        <v>17309</v>
       </c>
       <c r="X273" s="7" t="n"/>
       <c r="Y273" s="7" t="n"/>
@@ -12243,7 +12443,7 @@
     <row r="274">
       <c r="T274" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U274" s="4" t="inlineStr">
@@ -12252,7 +12452,7 @@
         </is>
       </c>
       <c r="V274" s="4" t="n">
-        <v>740</v>
+        <v>724</v>
       </c>
       <c r="X274" s="4" t="n"/>
       <c r="Y274" s="4" t="n"/>
@@ -12264,7 +12464,7 @@
     <row r="275">
       <c r="T275" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U275" s="7" t="inlineStr">
@@ -12273,7 +12473,7 @@
         </is>
       </c>
       <c r="V275" s="7" t="n">
-        <v>708</v>
+        <v>746</v>
       </c>
       <c r="X275" s="7" t="n"/>
       <c r="Y275" s="7" t="n"/>
@@ -12285,7 +12485,7 @@
     <row r="276">
       <c r="T276" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U276" s="4" t="inlineStr">
@@ -12294,7 +12494,7 @@
         </is>
       </c>
       <c r="V276" s="4" t="n">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="X276" s="4" t="n"/>
       <c r="Y276" s="4" t="n"/>
@@ -12306,7 +12506,7 @@
     <row r="277">
       <c r="T277" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U277" s="7" t="inlineStr">
@@ -12315,7 +12515,7 @@
         </is>
       </c>
       <c r="V277" s="7" t="n">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="X277" s="7" t="n"/>
       <c r="Y277" s="7" t="n"/>
@@ -12327,7 +12527,7 @@
     <row r="278">
       <c r="T278" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U278" s="4" t="inlineStr">
@@ -12336,7 +12536,7 @@
         </is>
       </c>
       <c r="V278" s="4" t="n">
-        <v>695</v>
+        <v>735</v>
       </c>
       <c r="X278" s="4" t="n"/>
       <c r="Y278" s="4" t="n"/>
@@ -12348,7 +12548,7 @@
     <row r="279">
       <c r="T279" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U279" s="7" t="inlineStr">
@@ -12357,7 +12557,7 @@
         </is>
       </c>
       <c r="V279" s="7" t="n">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="X279" s="7" t="n"/>
       <c r="Y279" s="7" t="n"/>
@@ -12369,7 +12569,7 @@
     <row r="280">
       <c r="T280" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U280" s="4" t="inlineStr">
@@ -12378,7 +12578,7 @@
         </is>
       </c>
       <c r="V280" s="4" t="n">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="X280" s="4" t="n"/>
       <c r="Y280" s="4" t="n"/>
@@ -12390,7 +12590,7 @@
     <row r="281">
       <c r="T281" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U281" s="7" t="inlineStr">
@@ -12399,7 +12599,7 @@
         </is>
       </c>
       <c r="V281" s="7" t="n">
-        <v>706</v>
+        <v>729</v>
       </c>
       <c r="X281" s="7" t="n"/>
       <c r="Y281" s="7" t="n"/>
@@ -12411,7 +12611,7 @@
     <row r="282">
       <c r="T282" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U282" s="4" t="inlineStr">
@@ -12420,7 +12620,7 @@
         </is>
       </c>
       <c r="V282" s="4" t="n">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="X282" s="4" t="n"/>
       <c r="Y282" s="4" t="n"/>
@@ -12432,7 +12632,7 @@
     <row r="283">
       <c r="T283" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U283" s="7" t="inlineStr">
@@ -12441,7 +12641,7 @@
         </is>
       </c>
       <c r="V283" s="7" t="n">
-        <v>670</v>
+        <v>719</v>
       </c>
       <c r="X283" s="7" t="n"/>
       <c r="Y283" s="7" t="n"/>
@@ -12453,7 +12653,7 @@
     <row r="284">
       <c r="T284" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U284" s="4" t="inlineStr">
@@ -12462,7 +12662,7 @@
         </is>
       </c>
       <c r="V284" s="4" t="n">
-        <v>694</v>
+        <v>730</v>
       </c>
       <c r="X284" s="4" t="n"/>
       <c r="Y284" s="4" t="n"/>
@@ -12474,7 +12674,7 @@
     <row r="285">
       <c r="T285" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U285" s="7" t="inlineStr">
@@ -12483,7 +12683,7 @@
         </is>
       </c>
       <c r="V285" s="7" t="n">
-        <v>702</v>
+        <v>740</v>
       </c>
       <c r="X285" s="7" t="n"/>
       <c r="Y285" s="7" t="n"/>
@@ -12495,7 +12695,7 @@
     <row r="286">
       <c r="T286" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U286" s="4" t="inlineStr">
@@ -12516,16 +12716,16 @@
     <row r="287">
       <c r="T287" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U287" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V287" s="7" t="n">
-        <v>2188</v>
+        <v>698</v>
       </c>
       <c r="X287" s="7" t="n"/>
       <c r="Y287" s="7" t="n"/>
@@ -12537,16 +12737,16 @@
     <row r="288">
       <c r="T288" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U288" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V288" s="4" t="n">
-        <v>2046</v>
+        <v>691</v>
       </c>
       <c r="X288" s="4" t="n"/>
       <c r="Y288" s="4" t="n"/>
@@ -12558,16 +12758,16 @@
     <row r="289">
       <c r="T289" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U289" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V289" s="7" t="n">
-        <v>2338</v>
+        <v>695</v>
       </c>
       <c r="X289" s="7" t="n"/>
       <c r="Y289" s="7" t="n"/>
@@ -12579,16 +12779,16 @@
     <row r="290">
       <c r="T290" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U290" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V290" s="4" t="n">
-        <v>2152</v>
+        <v>706</v>
       </c>
       <c r="X290" s="4" t="n"/>
       <c r="Y290" s="4" t="n"/>
@@ -12600,16 +12800,16 @@
     <row r="291">
       <c r="T291" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U291" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V291" s="7" t="n">
-        <v>2003</v>
+        <v>701</v>
       </c>
       <c r="X291" s="7" t="n"/>
       <c r="Y291" s="7" t="n"/>
@@ -12621,16 +12821,16 @@
     <row r="292">
       <c r="T292" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U292" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V292" s="4" t="n">
-        <v>1895</v>
+        <v>706</v>
       </c>
       <c r="X292" s="4" t="n"/>
       <c r="Y292" s="4" t="n"/>
@@ -12642,16 +12842,16 @@
     <row r="293">
       <c r="T293" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U293" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V293" s="7" t="n">
-        <v>1935</v>
+        <v>704</v>
       </c>
       <c r="X293" s="7" t="n"/>
       <c r="Y293" s="7" t="n"/>
@@ -12663,16 +12863,16 @@
     <row r="294">
       <c r="T294" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U294" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V294" s="4" t="n">
-        <v>2037</v>
+        <v>670</v>
       </c>
       <c r="X294" s="4" t="n"/>
       <c r="Y294" s="4" t="n"/>
@@ -12684,16 +12884,16 @@
     <row r="295">
       <c r="T295" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U295" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V295" s="7" t="n">
-        <v>2049</v>
+        <v>694</v>
       </c>
       <c r="X295" s="7" t="n"/>
       <c r="Y295" s="7" t="n"/>
@@ -12705,16 +12905,16 @@
     <row r="296">
       <c r="T296" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U296" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V296" s="4" t="n">
-        <v>2325</v>
+        <v>702</v>
       </c>
       <c r="X296" s="4" t="n"/>
       <c r="Y296" s="4" t="n"/>
@@ -12726,16 +12926,16 @@
     <row r="297">
       <c r="T297" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U297" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V297" s="7" t="n">
-        <v>2216</v>
+        <v>708</v>
       </c>
       <c r="X297" s="7" t="n"/>
       <c r="Y297" s="7" t="n"/>
@@ -12747,16 +12947,16 @@
     <row r="298">
       <c r="T298" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U298" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V298" s="4" t="n">
-        <v>2037</v>
+        <v>669</v>
       </c>
       <c r="X298" s="4" t="n"/>
       <c r="Y298" s="4" t="n"/>
@@ -12768,7 +12968,7 @@
     <row r="299">
       <c r="T299" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U299" s="7" t="inlineStr">
@@ -12777,7 +12977,7 @@
         </is>
       </c>
       <c r="V299" s="7" t="n">
-        <v>2046</v>
+        <v>2188</v>
       </c>
       <c r="X299" s="7" t="n"/>
       <c r="Y299" s="7" t="n"/>
@@ -12789,7 +12989,7 @@
     <row r="300">
       <c r="T300" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U300" s="4" t="inlineStr">
@@ -12798,7 +12998,7 @@
         </is>
       </c>
       <c r="V300" s="4" t="n">
-        <v>2035</v>
+        <v>2046</v>
       </c>
       <c r="X300" s="4" t="n"/>
       <c r="Y300" s="4" t="n"/>
@@ -12810,7 +13010,7 @@
     <row r="301">
       <c r="T301" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U301" s="7" t="inlineStr">
@@ -12819,7 +13019,7 @@
         </is>
       </c>
       <c r="V301" s="7" t="n">
-        <v>2182</v>
+        <v>2338</v>
       </c>
       <c r="X301" s="7" t="n"/>
       <c r="Y301" s="7" t="n"/>
@@ -12831,7 +13031,7 @@
     <row r="302">
       <c r="T302" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U302" s="4" t="inlineStr">
@@ -12840,7 +13040,7 @@
         </is>
       </c>
       <c r="V302" s="4" t="n">
-        <v>2156</v>
+        <v>2152</v>
       </c>
       <c r="X302" s="4" t="n"/>
       <c r="Y302" s="4" t="n"/>
@@ -12852,7 +13052,7 @@
     <row r="303">
       <c r="T303" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U303" s="7" t="inlineStr">
@@ -12861,7 +13061,7 @@
         </is>
       </c>
       <c r="V303" s="7" t="n">
-        <v>2437</v>
+        <v>2003</v>
       </c>
       <c r="X303" s="7" t="n"/>
       <c r="Y303" s="7" t="n"/>
@@ -12873,7 +13073,7 @@
     <row r="304">
       <c r="T304" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U304" s="4" t="inlineStr">
@@ -12882,7 +13082,7 @@
         </is>
       </c>
       <c r="V304" s="4" t="n">
-        <v>2214</v>
+        <v>1895</v>
       </c>
       <c r="X304" s="4" t="n"/>
       <c r="Y304" s="4" t="n"/>
@@ -12894,7 +13094,7 @@
     <row r="305">
       <c r="T305" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U305" s="7" t="inlineStr">
@@ -12903,7 +13103,7 @@
         </is>
       </c>
       <c r="V305" s="7" t="n">
-        <v>2200</v>
+        <v>1935</v>
       </c>
       <c r="X305" s="7" t="n"/>
       <c r="Y305" s="7" t="n"/>
@@ -12915,7 +13115,7 @@
     <row r="306">
       <c r="T306" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U306" s="4" t="inlineStr">
@@ -12924,7 +13124,7 @@
         </is>
       </c>
       <c r="V306" s="4" t="n">
-        <v>1973</v>
+        <v>2037</v>
       </c>
       <c r="X306" s="4" t="n"/>
       <c r="Y306" s="4" t="n"/>
@@ -12936,7 +13136,7 @@
     <row r="307">
       <c r="T307" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U307" s="7" t="inlineStr">
@@ -12945,7 +13145,7 @@
         </is>
       </c>
       <c r="V307" s="7" t="n">
-        <v>1980</v>
+        <v>2049</v>
       </c>
       <c r="X307" s="7" t="n"/>
       <c r="Y307" s="7" t="n"/>
@@ -12957,7 +13157,7 @@
     <row r="308">
       <c r="T308" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U308" s="4" t="inlineStr">
@@ -12966,7 +13166,7 @@
         </is>
       </c>
       <c r="V308" s="4" t="n">
-        <v>2075</v>
+        <v>2325</v>
       </c>
       <c r="X308" s="4" t="n"/>
       <c r="Y308" s="4" t="n"/>
@@ -12978,7 +13178,7 @@
     <row r="309">
       <c r="T309" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U309" s="7" t="inlineStr">
@@ -12987,7 +13187,7 @@
         </is>
       </c>
       <c r="V309" s="7" t="n">
-        <v>2191</v>
+        <v>2216</v>
       </c>
       <c r="X309" s="7" t="n"/>
       <c r="Y309" s="7" t="n"/>
@@ -12999,7 +13199,7 @@
     <row r="310">
       <c r="T310" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U310" s="4" t="inlineStr">
@@ -13008,7 +13208,7 @@
         </is>
       </c>
       <c r="V310" s="4" t="n">
-        <v>2328</v>
+        <v>2037</v>
       </c>
       <c r="X310" s="4" t="n"/>
       <c r="Y310" s="4" t="n"/>
@@ -13016,6 +13216,279 @@
       <c r="AB310" s="4" t="n"/>
       <c r="AC310" s="4" t="n"/>
       <c r="AD310" s="4" t="n"/>
+    </row>
+    <row r="311">
+      <c r="T311" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U311" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V311" s="7" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X311" s="7" t="n"/>
+      <c r="Y311" s="7" t="n"/>
+      <c r="Z311" s="7" t="n"/>
+      <c r="AB311" s="7" t="n"/>
+      <c r="AC311" s="7" t="n"/>
+      <c r="AD311" s="7" t="n"/>
+    </row>
+    <row r="312">
+      <c r="T312" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="U312" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V312" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="X312" s="4" t="n"/>
+      <c r="Y312" s="4" t="n"/>
+      <c r="Z312" s="4" t="n"/>
+      <c r="AB312" s="4" t="n"/>
+      <c r="AC312" s="4" t="n"/>
+      <c r="AD312" s="4" t="n"/>
+    </row>
+    <row r="313">
+      <c r="T313" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U313" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V313" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="X313" s="7" t="n"/>
+      <c r="Y313" s="7" t="n"/>
+      <c r="Z313" s="7" t="n"/>
+      <c r="AB313" s="7" t="n"/>
+      <c r="AC313" s="7" t="n"/>
+      <c r="AD313" s="7" t="n"/>
+    </row>
+    <row r="314">
+      <c r="T314" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="U314" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V314" s="4" t="n">
+        <v>2156</v>
+      </c>
+      <c r="X314" s="4" t="n"/>
+      <c r="Y314" s="4" t="n"/>
+      <c r="Z314" s="4" t="n"/>
+      <c r="AB314" s="4" t="n"/>
+      <c r="AC314" s="4" t="n"/>
+      <c r="AD314" s="4" t="n"/>
+    </row>
+    <row r="315">
+      <c r="T315" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="U315" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V315" s="7" t="n">
+        <v>2437</v>
+      </c>
+      <c r="X315" s="7" t="n"/>
+      <c r="Y315" s="7" t="n"/>
+      <c r="Z315" s="7" t="n"/>
+      <c r="AB315" s="7" t="n"/>
+      <c r="AC315" s="7" t="n"/>
+      <c r="AD315" s="7" t="n"/>
+    </row>
+    <row r="316">
+      <c r="T316" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="U316" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V316" s="4" t="n">
+        <v>2214</v>
+      </c>
+      <c r="X316" s="4" t="n"/>
+      <c r="Y316" s="4" t="n"/>
+      <c r="Z316" s="4" t="n"/>
+      <c r="AB316" s="4" t="n"/>
+      <c r="AC316" s="4" t="n"/>
+      <c r="AD316" s="4" t="n"/>
+    </row>
+    <row r="317">
+      <c r="T317" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U317" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V317" s="7" t="n">
+        <v>2200</v>
+      </c>
+      <c r="X317" s="7" t="n"/>
+      <c r="Y317" s="7" t="n"/>
+      <c r="Z317" s="7" t="n"/>
+      <c r="AB317" s="7" t="n"/>
+      <c r="AC317" s="7" t="n"/>
+      <c r="AD317" s="7" t="n"/>
+    </row>
+    <row r="318">
+      <c r="T318" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U318" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V318" s="4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="X318" s="4" t="n"/>
+      <c r="Y318" s="4" t="n"/>
+      <c r="Z318" s="4" t="n"/>
+      <c r="AB318" s="4" t="n"/>
+      <c r="AC318" s="4" t="n"/>
+      <c r="AD318" s="4" t="n"/>
+    </row>
+    <row r="319">
+      <c r="T319" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U319" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V319" s="7" t="n">
+        <v>1980</v>
+      </c>
+      <c r="X319" s="7" t="n"/>
+      <c r="Y319" s="7" t="n"/>
+      <c r="Z319" s="7" t="n"/>
+      <c r="AB319" s="7" t="n"/>
+      <c r="AC319" s="7" t="n"/>
+      <c r="AD319" s="7" t="n"/>
+    </row>
+    <row r="320">
+      <c r="T320" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U320" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V320" s="4" t="n">
+        <v>2075</v>
+      </c>
+      <c r="X320" s="4" t="n"/>
+      <c r="Y320" s="4" t="n"/>
+      <c r="Z320" s="4" t="n"/>
+      <c r="AB320" s="4" t="n"/>
+      <c r="AC320" s="4" t="n"/>
+      <c r="AD320" s="4" t="n"/>
+    </row>
+    <row r="321">
+      <c r="T321" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="U321" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V321" s="7" t="n">
+        <v>2191</v>
+      </c>
+      <c r="X321" s="7" t="n"/>
+      <c r="Y321" s="7" t="n"/>
+      <c r="Z321" s="7" t="n"/>
+      <c r="AB321" s="7" t="n"/>
+      <c r="AC321" s="7" t="n"/>
+      <c r="AD321" s="7" t="n"/>
+    </row>
+    <row r="322">
+      <c r="T322" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="U322" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V322" s="4" t="n">
+        <v>2328</v>
+      </c>
+      <c r="X322" s="4" t="n"/>
+      <c r="Y322" s="4" t="n"/>
+      <c r="Z322" s="4" t="n"/>
+      <c r="AB322" s="4" t="n"/>
+      <c r="AC322" s="4" t="n"/>
+      <c r="AD322" s="4" t="n"/>
+    </row>
+    <row r="323">
+      <c r="T323" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="U323" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V323" s="7" t="n">
+        <v>2131</v>
+      </c>
+      <c r="X323" s="7" t="n"/>
+      <c r="Y323" s="7" t="n"/>
+      <c r="Z323" s="7" t="n"/>
+      <c r="AB323" s="7" t="n"/>
+      <c r="AC323" s="7" t="n"/>
+      <c r="AD323" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -699,11 +699,11 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A2&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A2&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A2&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A2&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A2&amp;"*"),M2))*100,2)</f>
         <v/>
       </c>
       <c r="C2" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A2&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A2&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A2&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A2&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A2&amp;"*"),M2))*100,2)</f>
         <v/>
       </c>
       <c r="D2" s="4" t="n">
@@ -735,11 +735,11 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A3&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A3&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A3&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A3&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A3&amp;"*"),M3))*100,2)</f>
         <v/>
       </c>
       <c r="C3" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A3&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A3&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A3&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A3&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A3&amp;"*"),M3))*100,2)</f>
         <v/>
       </c>
       <c r="D3" s="7" t="n">
@@ -771,11 +771,11 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A4&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A4&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A4&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A4&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A4&amp;"*"),M4))*100,2)</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A4&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A4&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A4&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A4&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A4&amp;"*"),M4))*100,2)</f>
         <v/>
       </c>
       <c r="D4" s="4" t="n">
@@ -807,11 +807,11 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A5&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A5&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A5&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A5&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A5&amp;"*"),M5))*100,2)</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A5&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A5&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A5&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A5&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A5&amp;"*"),M5))*100,2)</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A6&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A6&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A6&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A6&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A6&amp;"*"),M6))*100,2)</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A6&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A6&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A6&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A6&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A6&amp;"*"),M6))*100,2)</f>
         <v/>
       </c>
       <c r="D6" s="4" t="n">
@@ -879,11 +879,11 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A7&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A7&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A7&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A7&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A7&amp;"*"),M7))*100,2)</f>
         <v/>
       </c>
       <c r="C7" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A7&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A7&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A7&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A7&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A7&amp;"*"),M7))*100,2)</f>
         <v/>
       </c>
       <c r="D7" s="7" t="n">
@@ -915,11 +915,11 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A8&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A8&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A8&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A8&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A8&amp;"*"),M8))*100,2)</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A8&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A8&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A8&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A8&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A8&amp;"*"),M8))*100,2)</f>
         <v/>
       </c>
       <c r="D8" s="4" t="n">
@@ -951,11 +951,11 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A9&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A9&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A9&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A9&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A9&amp;"*"),M9))*100,2)</f>
         <v/>
       </c>
       <c r="C9" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A9&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A9&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A9&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A9&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A9&amp;"*"),M9))*100,2)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="n">
@@ -987,11 +987,11 @@
         </is>
       </c>
       <c r="B10" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A10&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A10&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A10&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A10&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A10&amp;"*"),M10))*100,2)</f>
         <v/>
       </c>
       <c r="C10" s="4">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A10&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A10&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A10&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A10&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A10&amp;"*"),M10))*100,2)</f>
         <v/>
       </c>
       <c r="D10" s="4" t="n">
@@ -1023,11 +1023,11 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A11&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A11&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$X:$X,Dashboard!$Z:$Z,"*"&amp;$A11&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A11&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A11&amp;"*"),M11))*100,2)</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A11&amp;"*")/SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A11&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(Dashboard!$AB:$AB,Dashboard!$AD:$AD,"*"&amp;$A11&amp;"*")/IF(SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A11&amp;"*")&gt;0,SUMIFS(Dashboard!$V:$V,Dashboard!$U:$U,"*"&amp;$A11&amp;"*"),M11))*100,2)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4">
-        <f>ROUND((1-E2/D2)*100,2)</f>
+        <f>ROUND((1-E2/IF(D2&gt;0,D2,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="L2" s="4">
-        <f>ROUND(100*(1-K2/D2),2)</f>
+        <f>ROUND(100*(1-K2/IF(D2&gt;0,D2,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M2" s="4">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="7">
-        <f>ROUND((1-E3/D3)*100,2)</f>
+        <f>ROUND((1-E3/IF(D3&gt;0,D3,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H3" s="7">
@@ -1418,7 +1418,7 @@
         <v/>
       </c>
       <c r="L3" s="7">
-        <f>ROUND(100*(1-K3/D3),2)</f>
+        <f>ROUND(100*(1-K3/IF(D3&gt;0,D3,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M3" s="7">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4">
-        <f>ROUND((1-E4/D4)*100,2)</f>
+        <f>ROUND((1-E4/IF(D4&gt;0,D4,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="L4" s="4">
-        <f>ROUND(100*(1-K4/D4),2)</f>
+        <f>ROUND(100*(1-K4/IF(D4&gt;0,D4,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M4" s="4">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7">
-        <f>ROUND((1-E5/D5)*100,2)</f>
+        <f>ROUND((1-E5/IF(D5&gt;0,D5,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H5" s="7">
@@ -1582,7 +1582,7 @@
         <v/>
       </c>
       <c r="L5" s="7">
-        <f>ROUND(100*(1-K5/D5),2)</f>
+        <f>ROUND(100*(1-K5/IF(D5&gt;0,D5,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M5" s="7">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4">
-        <f>ROUND((1-E6/D6)*100,2)</f>
+        <f>ROUND((1-E6/IF(D6&gt;0,D6,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="L6" s="4">
-        <f>ROUND(100*(1-K6/D6),2)</f>
+        <f>ROUND(100*(1-K6/IF(D6&gt;0,D6,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M6" s="4">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7">
-        <f>ROUND((1-E7/D7)*100,2)</f>
+        <f>ROUND((1-E7/IF(D7&gt;0,D7,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H7" s="7">
@@ -1752,7 +1752,7 @@
         <v/>
       </c>
       <c r="L7" s="7">
-        <f>ROUND(100*(1-K7/D7),2)</f>
+        <f>ROUND(100*(1-K7/IF(D7&gt;0,D7,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M7" s="7">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4">
-        <f>ROUND((1-E8/D8)*100,2)</f>
+        <f>ROUND((1-E8/IF(D8&gt;0,D8,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -1837,7 +1837,7 @@
         <v/>
       </c>
       <c r="L8" s="4">
-        <f>ROUND(100*(1-K8/D8),2)</f>
+        <f>ROUND(100*(1-K8/IF(D8&gt;0,D8,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M8" s="4">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7">
-        <f>ROUND((1-E9/D9)*100,2)</f>
+        <f>ROUND((1-E9/IF(D9&gt;0,D9,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H9" s="7">
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="L9" s="7">
-        <f>ROUND(100*(1-K9/D9),2)</f>
+        <f>ROUND(100*(1-K9/IF(D9&gt;0,D9,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M9" s="7">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4">
-        <f>ROUND((1-E10/D10)*100,2)</f>
+        <f>ROUND((1-E10/IF(D10&gt;0,D10,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -2003,7 +2003,7 @@
         <v/>
       </c>
       <c r="L10" s="4">
-        <f>ROUND(100*(1-K10/D10),2)</f>
+        <f>ROUND(100*(1-K10/IF(D10&gt;0,D10,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M10" s="4">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7">
-        <f>ROUND((1-E11/D11)*100,2)</f>
+        <f>ROUND((1-E11/IF(D11&gt;0,D11,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H11" s="7">
@@ -2082,7 +2082,7 @@
         <v/>
       </c>
       <c r="L11" s="7">
-        <f>ROUND(100*(1-K11/D11),2)</f>
+        <f>ROUND(100*(1-K11/IF(D11&gt;0,D11,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M11" s="7">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4">
-        <f>ROUND((1-E12/D12)*100,2)</f>
+        <f>ROUND((1-E12/IF(D12&gt;0,D12,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="L12" s="4">
-        <f>ROUND(100*(1-K12/D12),2)</f>
+        <f>ROUND(100*(1-K12/IF(D12&gt;0,D12,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M12" s="4">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7">
-        <f>ROUND((1-E13/D13)*100,2)</f>
+        <f>ROUND((1-E13/IF(D13&gt;0,D13,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H13" s="7">
@@ -2240,7 +2240,7 @@
         <v/>
       </c>
       <c r="L13" s="7">
-        <f>ROUND(100*(1-K13/D13),2)</f>
+        <f>ROUND(100*(1-K13/IF(D13&gt;0,D13,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M13" s="7">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4">
-        <f>ROUND((1-E14/D14)*100,2)</f>
+        <f>ROUND((1-E14/IF(D14&gt;0,D14,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="L14" s="4">
-        <f>ROUND(100*(1-K14/D14),2)</f>
+        <f>ROUND(100*(1-K14/IF(D14&gt;0,D14,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M14" s="4">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7">
-        <f>ROUND((1-E15/D15)*100,2)</f>
+        <f>ROUND((1-E15/IF(D15&gt;0,D15,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H15" s="7">
@@ -2398,7 +2398,7 @@
         <v/>
       </c>
       <c r="L15" s="7">
-        <f>ROUND(100*(1-K15/D15),2)</f>
+        <f>ROUND(100*(1-K15/IF(D15&gt;0,D15,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M15" s="7">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4">
-        <f>ROUND((1-E16/D16)*100,2)</f>
+        <f>ROUND((1-E16/IF(D16&gt;0,D16,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -2477,7 +2477,7 @@
         <v/>
       </c>
       <c r="L16" s="4">
-        <f>ROUND(100*(1-K16/D16),2)</f>
+        <f>ROUND(100*(1-K16/IF(D16&gt;0,D16,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M16" s="4">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7">
-        <f>ROUND((1-E17/D17)*100,2)</f>
+        <f>ROUND((1-E17/IF(D17&gt;0,D17,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H17" s="7">
@@ -2556,7 +2556,7 @@
         <v/>
       </c>
       <c r="L17" s="7">
-        <f>ROUND(100*(1-K17/D17),2)</f>
+        <f>ROUND(100*(1-K17/IF(D17&gt;0,D17,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M17" s="7">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4">
-        <f>ROUND((1-E18/D18)*100,2)</f>
+        <f>ROUND((1-E18/IF(D18&gt;0,D18,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H18" s="4">
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L18" s="4">
-        <f>ROUND(100*(1-K18/D18),2)</f>
+        <f>ROUND(100*(1-K18/IF(D18&gt;0,D18,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M18" s="4">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7">
-        <f>ROUND((1-E19/D19)*100,2)</f>
+        <f>ROUND((1-E19/IF(D19&gt;0,D19,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H19" s="7">
@@ -2714,7 +2714,7 @@
         <v/>
       </c>
       <c r="L19" s="7">
-        <f>ROUND(100*(1-K19/D19),2)</f>
+        <f>ROUND(100*(1-K19/IF(D19&gt;0,D19,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M19" s="7">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4">
-        <f>ROUND((1-E20/D20)*100,2)</f>
+        <f>ROUND((1-E20/IF(D20&gt;0,D20,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H20" s="4">
@@ -2793,7 +2793,7 @@
         <v/>
       </c>
       <c r="L20" s="4">
-        <f>ROUND(100*(1-K20/D20),2)</f>
+        <f>ROUND(100*(1-K20/IF(D20&gt;0,D20,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M20" s="4">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7">
-        <f>ROUND((1-E21/D21)*100,2)</f>
+        <f>ROUND((1-E21/IF(D21&gt;0,D21,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H21" s="7">
@@ -2872,7 +2872,7 @@
         <v/>
       </c>
       <c r="L21" s="7">
-        <f>ROUND(100*(1-K21/D21),2)</f>
+        <f>ROUND(100*(1-K21/IF(D21&gt;0,D21,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M21" s="7">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4">
-        <f>ROUND((1-E22/D22)*100,2)</f>
+        <f>ROUND((1-E22/IF(D22&gt;0,D22,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H22" s="4">
@@ -2951,7 +2951,7 @@
         <v/>
       </c>
       <c r="L22" s="4">
-        <f>ROUND(100*(1-K22/D22),2)</f>
+        <f>ROUND(100*(1-K22/IF(D22&gt;0,D22,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M22" s="4">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7">
-        <f>ROUND((1-E23/D23)*100,2)</f>
+        <f>ROUND((1-E23/IF(D23&gt;0,D23,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H23" s="7">
@@ -3030,7 +3030,7 @@
         <v/>
       </c>
       <c r="L23" s="7">
-        <f>ROUND(100*(1-K23/D23),2)</f>
+        <f>ROUND(100*(1-K23/IF(D23&gt;0,D23,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M23" s="7">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4">
-        <f>ROUND((1-E24/D24)*100,2)</f>
+        <f>ROUND((1-E24/IF(D24&gt;0,D24,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H24" s="4">
@@ -3109,7 +3109,7 @@
         <v/>
       </c>
       <c r="L24" s="4">
-        <f>ROUND(100*(1-K24/D24),2)</f>
+        <f>ROUND(100*(1-K24/IF(D24&gt;0,D24,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M24" s="4">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7">
-        <f>ROUND((1-E25/D25)*100,2)</f>
+        <f>ROUND((1-E25/IF(D25&gt;0,D25,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H25" s="7">
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="L25" s="7">
-        <f>ROUND(100*(1-K25/D25),2)</f>
+        <f>ROUND(100*(1-K25/IF(D25&gt;0,D25,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M25" s="7">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4">
-        <f>ROUND((1-E26/D26)*100,2)</f>
+        <f>ROUND((1-E26/IF(D26&gt;0,D26,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
         <v/>
       </c>
       <c r="H26" s="4">
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="L26" s="4">
-        <f>ROUND(100*(1-K26/D26),2)</f>
+        <f>ROUND(100*(1-K26/IF(D26&gt;0,D26,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
         <v/>
       </c>
       <c r="M26" s="4">
@@ -3685,7 +3685,7 @@
       <c r="E33" s="27" t="n"/>
       <c r="F33" s="27" t="n"/>
       <c r="G33" s="28">
-        <f>TRUNC((1-SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*")/SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*")/IF(SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*")&gt;0,SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*"),SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")))*100,2)</f>
         <v/>
       </c>
       <c r="H33" s="29">
@@ -3699,7 +3699,7 @@
       <c r="J33" s="27" t="n"/>
       <c r="K33" s="27" t="n"/>
       <c r="L33" s="28">
-        <f>TRUNC((1-SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*")/SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*"))*100,2)</f>
+        <f>TRUNC((1-SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*")/IF(SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*")&gt;0,SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*"),SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")))*100,2)</f>
         <v/>
       </c>
       <c r="M33" s="29">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -716,10 +716,10 @@
         <v>0.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -752,10 +752,10 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -788,10 +788,10 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -824,10 +824,10 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -860,10 +860,10 @@
         <v>0.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -896,10 +896,10 @@
         <v>0.95</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -932,10 +932,10 @@
         <v>0.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -968,10 +968,10 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1004,10 +1004,10 @@
         <v>0.95</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1040,10 +1040,10 @@
         <v>0.95</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD323"/>
+  <dimension ref="A1:AD227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1344,15 +1344,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>103</v>
       </c>
@@ -1429,15 +1423,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>13</v>
       </c>
@@ -1514,15 +1502,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>64</v>
       </c>
@@ -1593,15 +1575,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>30</v>
       </c>
@@ -1678,15 +1654,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>21</v>
       </c>
@@ -1763,15 +1733,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>73</v>
       </c>
@@ -1848,15 +1812,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>15</v>
       </c>
@@ -1927,15 +1885,9 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>1</v>
       </c>
@@ -2014,15 +1966,9 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>105</v>
       </c>
@@ -2093,15 +2039,9 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>19</v>
       </c>
@@ -2172,15 +2112,9 @@
         <f>$B$2+H12+M12</f>
         <v/>
       </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>82</v>
       </c>
@@ -2251,15 +2185,9 @@
         <f>$B$2+H13+M13</f>
         <v/>
       </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>25</v>
       </c>
@@ -2330,15 +2258,9 @@
         <f>$B$2+H14+M14</f>
         <v/>
       </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>15</v>
       </c>
@@ -2409,15 +2331,9 @@
         <f>$B$2+H15+M15</f>
         <v/>
       </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>75</v>
       </c>
@@ -2488,15 +2404,9 @@
         <f>$B$2+H16+M16</f>
         <v/>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>9</v>
       </c>
@@ -2567,15 +2477,9 @@
         <f>$B$2+H17+M17</f>
         <v/>
       </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>1</v>
       </c>
@@ -2646,15 +2550,9 @@
         <f>$B$2+H18+M18</f>
         <v/>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>145</v>
       </c>
@@ -2725,15 +2623,9 @@
         <f>$B$2+H19+M19</f>
         <v/>
       </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>19</v>
       </c>
@@ -2804,15 +2696,9 @@
         <f>$B$2+H20+M20</f>
         <v/>
       </c>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>74</v>
       </c>
@@ -2883,15 +2769,9 @@
         <f>$B$2+H21+M21</f>
         <v/>
       </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr"/>
-      <c r="V21" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>26</v>
       </c>
@@ -2962,15 +2842,9 @@
         <f>$B$2+H22+M22</f>
         <v/>
       </c>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>9</v>
       </c>
@@ -3041,15 +2915,9 @@
         <f>$B$2+H23+M23</f>
         <v/>
       </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr"/>
-      <c r="V23" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
         <v>74</v>
       </c>
@@ -3120,15 +2988,9 @@
         <f>$B$2+H24+M24</f>
         <v/>
       </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
         <v>11</v>
       </c>
@@ -3199,15 +3061,9 @@
         <f>$B$2+H25+M25</f>
         <v/>
       </c>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr"/>
-      <c r="V25" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>101</v>
       </c>
@@ -3278,15 +3134,9 @@
         <f>$B$2+H26+M26</f>
         <v/>
       </c>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
         <v>11</v>
       </c>
@@ -3333,19 +3183,9 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>5365</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
         <v>73</v>
       </c>
@@ -3392,19 +3232,9 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>5741</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
         <v>31</v>
       </c>
@@ -3451,19 +3281,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>5451</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>13</v>
       </c>
@@ -3510,19 +3330,9 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>5458</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
         <v>78</v>
       </c>
@@ -3569,19 +3379,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>5664</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
@@ -3637,19 +3437,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>5241</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>9</v>
       </c>
@@ -3710,19 +3500,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>5102</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
@@ -3751,19 +3531,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>5388</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>119</v>
       </c>
@@ -3792,19 +3562,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>13</v>
       </c>
@@ -3833,19 +3593,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>5348</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>67</v>
       </c>
@@ -3874,19 +3624,9 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>5329</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
         <v>32</v>
       </c>
@@ -3915,19 +3655,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>5436</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
         <v>13</v>
       </c>
@@ -3956,19 +3686,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>5081</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>93</v>
       </c>
@@ -3997,19 +3717,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>5034</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>12</v>
       </c>
@@ -4038,19 +3748,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>2</v>
       </c>
@@ -4079,19 +3779,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>5513</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>113</v>
       </c>
@@ -4120,19 +3810,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>5477</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>12</v>
       </c>
@@ -4161,19 +3841,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>5526</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>69</v>
       </c>
@@ -4202,19 +3872,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>5339</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>40</v>
       </c>
@@ -4243,19 +3903,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>4933</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>17</v>
       </c>
@@ -4284,19 +3934,9 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>4866</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>83</v>
       </c>
@@ -4325,19 +3965,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>5232</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>9</v>
       </c>
@@ -4366,19 +3996,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>5576</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>124</v>
       </c>
@@ -4407,19 +4027,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>5287</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>19</v>
       </c>
@@ -4448,19 +4058,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>5275</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>55</v>
       </c>
@@ -4489,19 +4089,9 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>14969</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
         <v>35</v>
       </c>
@@ -4530,19 +4120,9 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>14818</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>15</v>
       </c>
@@ -4571,19 +4151,9 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>15263</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>82</v>
       </c>
@@ -4612,19 +4182,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>1</v>
       </c>
@@ -4653,19 +4213,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>14968</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>14</v>
       </c>
@@ -4694,19 +4244,9 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>14113</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>2</v>
       </c>
@@ -4735,19 +4275,9 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>14162</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
         <v>101</v>
       </c>
@@ -4776,19 +4306,9 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
         <v>10</v>
       </c>
@@ -4817,19 +4337,9 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>14815</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
         <v>72</v>
       </c>
@@ -4858,19 +4368,9 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>15546</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
         <v>35</v>
       </c>
@@ -4899,19 +4399,9 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>14882</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
         <v>13</v>
       </c>
@@ -4940,19 +4430,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>14998</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>71</v>
       </c>
@@ -4981,19 +4461,9 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>14354</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
         <v>8</v>
       </c>
@@ -5022,19 +4492,9 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>14362</v>
-      </c>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
         <v>2</v>
       </c>
@@ -5063,19 +4523,9 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>15089</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>125</v>
       </c>
@@ -5104,19 +4554,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>14802</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>11</v>
       </c>
@@ -5145,19 +4585,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>15349</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>67</v>
       </c>
@@ -5186,19 +4616,9 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>14872</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>27</v>
       </c>
@@ -5227,19 +4647,9 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>15054</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
         <v>17</v>
       </c>
@@ -5268,19 +4678,9 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>14169</v>
-      </c>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
         <v>85</v>
       </c>
@@ -5309,19 +4709,9 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>14056</v>
-      </c>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
         <v>14</v>
       </c>
@@ -5350,19 +4740,9 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>15058</v>
-      </c>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
         <v>4</v>
       </c>
@@ -5391,19 +4771,9 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>14814</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
         <v>126</v>
       </c>
@@ -5432,19 +4802,9 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>15440</v>
-      </c>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
         <v>23</v>
       </c>
@@ -5473,19 +4833,9 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>14832</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>65</v>
       </c>
@@ -5514,19 +4864,9 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>77546</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
         <v>28</v>
       </c>
@@ -5555,19 +4895,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>77823</v>
-      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
         <v>19</v>
       </c>
@@ -5596,19 +4926,9 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>81723</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>91</v>
       </c>
@@ -5637,19 +4957,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>78398</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>21</v>
       </c>
@@ -5678,19 +4988,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>78030</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
         <v>2</v>
       </c>
@@ -5719,19 +5019,9 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>76646</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
         <v>99</v>
       </c>
@@ -5760,19 +5050,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>76742</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>12</v>
       </c>
@@ -5801,19 +5081,9 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>79003</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
         <v>70</v>
       </c>
@@ -5842,19 +5112,9 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>78849</v>
-      </c>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
         <v>30</v>
       </c>
@@ -5883,19 +5143,9 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>80667</v>
-      </c>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
         <v>15</v>
       </c>
@@ -5924,19 +5174,9 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>78640</v>
-      </c>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
         <v>73</v>
       </c>
@@ -5965,19 +5205,9 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>79108</v>
-      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
         <v>5</v>
       </c>
@@ -6006,19 +5236,9 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>76911</v>
-      </c>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
         <v>1</v>
       </c>
@@ -6047,19 +5267,9 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>77273</v>
-      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
         <v>107</v>
       </c>
@@ -6088,19 +5298,9 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>80657</v>
-      </c>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
         <v>13</v>
       </c>
@@ -6129,19 +5329,9 @@
       </c>
     </row>
     <row r="92">
-      <c r="T92" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V92" s="4" t="n">
-        <v>79898</v>
-      </c>
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
       <c r="X92" s="4" t="n">
         <v>56</v>
       </c>
@@ -6170,19 +5360,9 @@
       </c>
     </row>
     <row r="93">
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U93" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>82443</v>
-      </c>
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
         <v>32</v>
       </c>
@@ -6211,19 +5391,9 @@
       </c>
     </row>
     <row r="94">
-      <c r="T94" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>80658</v>
-      </c>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
         <v>13</v>
       </c>
@@ -6252,19 +5422,9 @@
       </c>
     </row>
     <row r="95">
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>78475</v>
-      </c>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
         <v>78</v>
       </c>
@@ -6293,19 +5453,9 @@
       </c>
     </row>
     <row r="96">
-      <c r="T96" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V96" s="4" t="n">
-        <v>76874</v>
-      </c>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
       <c r="X96" s="4" t="n">
         <v>10</v>
       </c>
@@ -6334,19 +5484,9 @@
       </c>
     </row>
     <row r="97">
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V97" s="7" t="n">
-        <v>77058</v>
-      </c>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
         <v>1</v>
       </c>
@@ -6375,19 +5515,9 @@
       </c>
     </row>
     <row r="98">
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>79206</v>
-      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
         <v>114</v>
       </c>
@@ -6416,19 +5546,9 @@
       </c>
     </row>
     <row r="99">
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V99" s="7" t="n">
-        <v>79070</v>
-      </c>
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
         <v>15</v>
       </c>
@@ -6457,19 +5577,9 @@
       </c>
     </row>
     <row r="100">
-      <c r="T100" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>81246</v>
-      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
         <v>53</v>
       </c>
@@ -6498,19 +5608,9 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U101" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V101" s="7" t="n">
-        <v>80308</v>
-      </c>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
         <v>32</v>
       </c>
@@ -6539,19 +5639,9 @@
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
         <v>14</v>
       </c>
@@ -6580,19 +5670,9 @@
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V103" s="7" t="n">
-        <v>715</v>
-      </c>
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
         <v>80</v>
       </c>
@@ -6621,19 +5701,9 @@
       </c>
     </row>
     <row r="104">
-      <c r="T104" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U104" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V104" s="4" t="n">
-        <v>745</v>
-      </c>
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="4" t="n"/>
+      <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
         <v>1</v>
       </c>
@@ -6662,19 +5732,9 @@
       </c>
     </row>
     <row r="105">
-      <c r="T105" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U105" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>702</v>
-      </c>
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
         <v>9</v>
       </c>
@@ -6703,19 +5763,9 @@
       </c>
     </row>
     <row r="106">
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="n">
-        <v>743</v>
-      </c>
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="4" t="n"/>
+      <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
         <v>4</v>
       </c>
@@ -6744,19 +5794,9 @@
       </c>
     </row>
     <row r="107">
-      <c r="T107" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U107" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V107" s="7" t="n">
-        <v>700</v>
-      </c>
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
         <v>97</v>
       </c>
@@ -6785,19 +5825,9 @@
       </c>
     </row>
     <row r="108">
-      <c r="T108" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U108" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V108" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="4" t="n"/>
+      <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
         <v>10</v>
       </c>
@@ -6826,19 +5856,9 @@
       </c>
     </row>
     <row r="109">
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U109" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V109" s="7" t="n">
-        <v>750</v>
-      </c>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
         <v>52</v>
       </c>
@@ -6867,19 +5887,9 @@
       </c>
     </row>
     <row r="110">
-      <c r="T110" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U110" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V110" s="4" t="n">
-        <v>729</v>
-      </c>
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="n"/>
       <c r="X110" s="4" t="n">
         <v>37</v>
       </c>
@@ -6908,19 +5918,9 @@
       </c>
     </row>
     <row r="111">
-      <c r="T111" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U111" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V111" s="7" t="n">
-        <v>748</v>
-      </c>
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
       <c r="X111" s="7" t="n">
         <v>18</v>
       </c>
@@ -6949,19 +5949,9 @@
       </c>
     </row>
     <row r="112">
-      <c r="T112" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U112" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V112" s="4" t="n">
-        <v>736</v>
-      </c>
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="4" t="n"/>
+      <c r="V112" s="4" t="n"/>
       <c r="X112" s="4" t="n">
         <v>64</v>
       </c>
@@ -6990,19 +5980,9 @@
       </c>
     </row>
     <row r="113">
-      <c r="T113" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U113" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V113" s="7" t="n">
-        <v>737</v>
-      </c>
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
         <v>7</v>
       </c>
@@ -7031,19 +6011,9 @@
       </c>
     </row>
     <row r="114">
-      <c r="T114" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U114" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V114" s="4" t="n">
-        <v>707</v>
-      </c>
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="n"/>
       <c r="X114" s="4" t="n">
         <v>106</v>
       </c>
@@ -7072,19 +6042,9 @@
       </c>
     </row>
     <row r="115">
-      <c r="T115" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U115" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V115" s="7" t="n">
-        <v>713</v>
-      </c>
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
       <c r="X115" s="7" t="n">
         <v>14</v>
       </c>
@@ -7113,19 +6073,9 @@
       </c>
     </row>
     <row r="116">
-      <c r="T116" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U116" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V116" s="4" t="n">
-        <v>786</v>
-      </c>
+      <c r="T116" s="4" t="n"/>
+      <c r="U116" s="4" t="n"/>
+      <c r="V116" s="4" t="n"/>
       <c r="X116" s="4" t="n">
         <v>65</v>
       </c>
@@ -7154,19 +6104,9 @@
       </c>
     </row>
     <row r="117">
-      <c r="T117" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U117" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V117" s="7" t="n">
-        <v>730</v>
-      </c>
+      <c r="T117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
       <c r="X117" s="7" t="n">
         <v>24</v>
       </c>
@@ -7195,19 +6135,9 @@
       </c>
     </row>
     <row r="118">
-      <c r="T118" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U118" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V118" s="4" t="n">
-        <v>726</v>
-      </c>
+      <c r="T118" s="4" t="n"/>
+      <c r="U118" s="4" t="n"/>
+      <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
         <v>14</v>
       </c>
@@ -7236,19 +6166,9 @@
       </c>
     </row>
     <row r="119">
-      <c r="T119" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U119" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V119" s="7" t="n">
-        <v>695</v>
-      </c>
+      <c r="T119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
         <v>66</v>
       </c>
@@ -7277,19 +6197,9 @@
       </c>
     </row>
     <row r="120">
-      <c r="T120" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U120" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V120" s="4" t="n">
-        <v>693</v>
-      </c>
+      <c r="T120" s="4" t="n"/>
+      <c r="U120" s="4" t="n"/>
+      <c r="V120" s="4" t="n"/>
       <c r="X120" s="4" t="n">
         <v>1</v>
       </c>
@@ -7318,19 +6228,9 @@
       </c>
     </row>
     <row r="121">
-      <c r="T121" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U121" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V121" s="7" t="n">
-        <v>686</v>
-      </c>
+      <c r="T121" s="7" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
       <c r="X121" s="7" t="n">
         <v>9</v>
       </c>
@@ -7359,19 +6259,9 @@
       </c>
     </row>
     <row r="122">
-      <c r="T122" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U122" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V122" s="4" t="n">
-        <v>673</v>
-      </c>
+      <c r="T122" s="4" t="n"/>
+      <c r="U122" s="4" t="n"/>
+      <c r="V122" s="4" t="n"/>
       <c r="X122" s="4" t="n">
         <v>116</v>
       </c>
@@ -7400,19 +6290,9 @@
       </c>
     </row>
     <row r="123">
-      <c r="T123" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U123" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V123" s="7" t="n">
-        <v>752</v>
-      </c>
+      <c r="T123" s="7" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
       <c r="X123" s="7" t="n">
         <v>17</v>
       </c>
@@ -7441,19 +6321,9 @@
       </c>
     </row>
     <row r="124">
-      <c r="T124" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U124" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="n">
-        <v>717</v>
-      </c>
+      <c r="T124" s="4" t="n"/>
+      <c r="U124" s="4" t="n"/>
+      <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
         <v>52</v>
       </c>
@@ -7482,19 +6352,9 @@
       </c>
     </row>
     <row r="125">
-      <c r="T125" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U125" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V125" s="7" t="n">
-        <v>706</v>
-      </c>
+      <c r="T125" s="7" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
         <v>38</v>
       </c>
@@ -7523,19 +6383,9 @@
       </c>
     </row>
     <row r="126">
-      <c r="T126" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U126" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V126" s="4" t="n">
-        <v>703</v>
-      </c>
+      <c r="T126" s="4" t="n"/>
+      <c r="U126" s="4" t="n"/>
+      <c r="V126" s="4" t="n"/>
       <c r="X126" s="4" t="n">
         <v>19</v>
       </c>
@@ -7564,19 +6414,9 @@
       </c>
     </row>
     <row r="127">
-      <c r="T127" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U127" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V127" s="7" t="n">
-        <v>47976</v>
-      </c>
+      <c r="T127" s="7" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
       <c r="X127" s="7" t="n">
         <v>79</v>
       </c>
@@ -7605,19 +6445,9 @@
       </c>
     </row>
     <row r="128">
-      <c r="T128" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U128" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V128" s="4" t="n">
-        <v>47122</v>
-      </c>
+      <c r="T128" s="4" t="n"/>
+      <c r="U128" s="4" t="n"/>
+      <c r="V128" s="4" t="n"/>
       <c r="X128" s="4" t="n">
         <v>9</v>
       </c>
@@ -7646,19 +6476,9 @@
       </c>
     </row>
     <row r="129">
-      <c r="T129" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U129" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V129" s="7" t="n">
-        <v>47233</v>
-      </c>
+      <c r="T129" s="7" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
       <c r="X129" s="7" t="n">
         <v>1</v>
       </c>
@@ -7687,19 +6507,9 @@
       </c>
     </row>
     <row r="130">
-      <c r="T130" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U130" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V130" s="4" t="n">
-        <v>48580</v>
-      </c>
+      <c r="T130" s="4" t="n"/>
+      <c r="U130" s="4" t="n"/>
+      <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
         <v>134</v>
       </c>
@@ -7728,19 +6538,9 @@
       </c>
     </row>
     <row r="131">
-      <c r="T131" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U131" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V131" s="7" t="n">
-        <v>47383</v>
-      </c>
+      <c r="T131" s="7" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
         <v>22</v>
       </c>
@@ -7769,19 +6569,9 @@
       </c>
     </row>
     <row r="132">
-      <c r="T132" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U132" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V132" s="4" t="n">
-        <v>46456</v>
-      </c>
+      <c r="T132" s="4" t="n"/>
+      <c r="U132" s="4" t="n"/>
+      <c r="V132" s="4" t="n"/>
       <c r="X132" s="4" t="n">
         <v>65</v>
       </c>
@@ -7810,19 +6600,9 @@
       </c>
     </row>
     <row r="133">
-      <c r="T133" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U133" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V133" s="7" t="n">
-        <v>46400</v>
-      </c>
+      <c r="T133" s="7" t="n"/>
+      <c r="U133" s="7" t="n"/>
+      <c r="V133" s="7" t="n"/>
       <c r="X133" s="7" t="n">
         <v>29</v>
       </c>
@@ -7851,19 +6631,9 @@
       </c>
     </row>
     <row r="134">
-      <c r="T134" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U134" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V134" s="4" t="n">
-        <v>47755</v>
-      </c>
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="4" t="n"/>
+      <c r="V134" s="4" t="n"/>
       <c r="X134" s="4" t="n">
         <v>12</v>
       </c>
@@ -7892,19 +6662,9 @@
       </c>
     </row>
     <row r="135">
-      <c r="T135" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U135" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V135" s="7" t="n">
-        <v>47520</v>
-      </c>
+      <c r="T135" s="7" t="n"/>
+      <c r="U135" s="7" t="n"/>
+      <c r="V135" s="7" t="n"/>
       <c r="X135" s="7" t="n">
         <v>82</v>
       </c>
@@ -7933,19 +6693,9 @@
       </c>
     </row>
     <row r="136">
-      <c r="T136" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U136" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V136" s="4" t="n">
-        <v>47354</v>
-      </c>
+      <c r="T136" s="4" t="n"/>
+      <c r="U136" s="4" t="n"/>
+      <c r="V136" s="4" t="n"/>
       <c r="X136" s="4" t="n">
         <v>1</v>
       </c>
@@ -7974,19 +6724,9 @@
       </c>
     </row>
     <row r="137">
-      <c r="T137" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U137" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V137" s="7" t="n">
-        <v>49015</v>
-      </c>
+      <c r="T137" s="7" t="n"/>
+      <c r="U137" s="7" t="n"/>
+      <c r="V137" s="7" t="n"/>
       <c r="X137" s="7" t="n">
         <v>7</v>
       </c>
@@ -8015,19 +6755,9 @@
       </c>
     </row>
     <row r="138">
-      <c r="T138" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U138" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V138" s="4" t="n">
-        <v>48832</v>
-      </c>
+      <c r="T138" s="4" t="n"/>
+      <c r="U138" s="4" t="n"/>
+      <c r="V138" s="4" t="n"/>
       <c r="X138" s="4" t="n">
         <v>1</v>
       </c>
@@ -8056,19 +6786,9 @@
       </c>
     </row>
     <row r="139">
-      <c r="T139" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U139" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V139" s="7" t="n">
-        <v>46644</v>
-      </c>
+      <c r="T139" s="7" t="n"/>
+      <c r="U139" s="7" t="n"/>
+      <c r="V139" s="7" t="n"/>
       <c r="X139" s="7" t="n">
         <v>107</v>
       </c>
@@ -8097,19 +6817,9 @@
       </c>
     </row>
     <row r="140">
-      <c r="T140" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U140" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V140" s="4" t="n">
-        <v>46416</v>
-      </c>
+      <c r="T140" s="4" t="n"/>
+      <c r="U140" s="4" t="n"/>
+      <c r="V140" s="4" t="n"/>
       <c r="X140" s="4" t="n">
         <v>24</v>
       </c>
@@ -8138,19 +6848,9 @@
       </c>
     </row>
     <row r="141">
-      <c r="T141" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U141" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V141" s="7" t="n">
-        <v>48419</v>
-      </c>
+      <c r="T141" s="7" t="n"/>
+      <c r="U141" s="7" t="n"/>
+      <c r="V141" s="7" t="n"/>
       <c r="X141" s="7" t="n">
         <v>68</v>
       </c>
@@ -8179,19 +6879,9 @@
       </c>
     </row>
     <row r="142">
-      <c r="T142" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U142" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V142" s="4" t="n">
-        <v>47500</v>
-      </c>
+      <c r="T142" s="4" t="n"/>
+      <c r="U142" s="4" t="n"/>
+      <c r="V142" s="4" t="n"/>
       <c r="X142" s="4" t="n">
         <v>18</v>
       </c>
@@ -8220,19 +6910,9 @@
       </c>
     </row>
     <row r="143">
-      <c r="T143" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U143" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V143" s="7" t="n">
-        <v>47954</v>
-      </c>
+      <c r="T143" s="7" t="n"/>
+      <c r="U143" s="7" t="n"/>
+      <c r="V143" s="7" t="n"/>
       <c r="X143" s="7" t="n">
         <v>12</v>
       </c>
@@ -8261,19 +6941,9 @@
       </c>
     </row>
     <row r="144">
-      <c r="T144" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U144" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V144" s="4" t="n">
-        <v>49088</v>
-      </c>
+      <c r="T144" s="4" t="n"/>
+      <c r="U144" s="4" t="n"/>
+      <c r="V144" s="4" t="n"/>
       <c r="X144" s="4" t="n">
         <v>70</v>
       </c>
@@ -8302,19 +6972,9 @@
       </c>
     </row>
     <row r="145">
-      <c r="T145" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U145" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V145" s="7" t="n">
-        <v>48111</v>
-      </c>
+      <c r="T145" s="7" t="n"/>
+      <c r="U145" s="7" t="n"/>
+      <c r="V145" s="7" t="n"/>
       <c r="X145" s="7" t="n">
         <v>2</v>
       </c>
@@ -8343,19 +7003,9 @@
       </c>
     </row>
     <row r="146">
-      <c r="T146" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U146" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V146" s="4" t="n">
-        <v>46535</v>
-      </c>
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
       <c r="X146" s="4" t="n">
         <v>6</v>
       </c>
@@ -8384,19 +7034,9 @@
       </c>
     </row>
     <row r="147">
-      <c r="T147" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U147" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V147" s="7" t="n">
-        <v>46063</v>
-      </c>
+      <c r="T147" s="7" t="n"/>
+      <c r="U147" s="7" t="n"/>
+      <c r="V147" s="7" t="n"/>
       <c r="X147" s="7" t="n">
         <v>2</v>
       </c>
@@ -8425,19 +7065,9 @@
       </c>
     </row>
     <row r="148">
-      <c r="T148" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U148" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V148" s="4" t="n">
-        <v>48085</v>
-      </c>
+      <c r="T148" s="4" t="n"/>
+      <c r="U148" s="4" t="n"/>
+      <c r="V148" s="4" t="n"/>
       <c r="X148" s="4" t="n">
         <v>115</v>
       </c>
@@ -8466,19 +7096,9 @@
       </c>
     </row>
     <row r="149">
-      <c r="T149" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U149" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V149" s="7" t="n">
-        <v>47472</v>
-      </c>
+      <c r="T149" s="7" t="n"/>
+      <c r="U149" s="7" t="n"/>
+      <c r="V149" s="7" t="n"/>
       <c r="X149" s="7" t="n">
         <v>20</v>
       </c>
@@ -8507,19 +7127,9 @@
       </c>
     </row>
     <row r="150">
-      <c r="T150" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U150" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V150" s="4" t="n">
-        <v>47003</v>
-      </c>
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="4" t="n"/>
+      <c r="V150" s="4" t="n"/>
       <c r="X150" s="4" t="n">
         <v>69</v>
       </c>
@@ -8548,19 +7158,9 @@
       </c>
     </row>
     <row r="151">
-      <c r="T151" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U151" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V151" s="7" t="n">
-        <v>48466</v>
-      </c>
+      <c r="T151" s="7" t="n"/>
+      <c r="U151" s="7" t="n"/>
+      <c r="V151" s="7" t="n"/>
       <c r="X151" s="7" t="n">
         <v>41</v>
       </c>
@@ -8589,19 +7189,9 @@
       </c>
     </row>
     <row r="152">
-      <c r="T152" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U152" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V152" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="4" t="n"/>
+      <c r="V152" s="4" t="n"/>
       <c r="X152" s="4" t="n">
         <v>5</v>
       </c>
@@ -8630,19 +7220,9 @@
       </c>
     </row>
     <row r="153">
-      <c r="T153" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U153" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V153" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T153" s="7" t="n"/>
+      <c r="U153" s="7" t="n"/>
+      <c r="V153" s="7" t="n"/>
       <c r="X153" s="7" t="n">
         <v>95</v>
       </c>
@@ -8671,19 +7251,9 @@
       </c>
     </row>
     <row r="154">
-      <c r="T154" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U154" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T154" s="4" t="n"/>
+      <c r="U154" s="4" t="n"/>
+      <c r="V154" s="4" t="n"/>
       <c r="X154" s="4" t="n">
         <v>1</v>
       </c>
@@ -8712,19 +7282,9 @@
       </c>
     </row>
     <row r="155">
-      <c r="T155" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U155" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V155" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T155" s="7" t="n"/>
+      <c r="U155" s="7" t="n"/>
+      <c r="V155" s="7" t="n"/>
       <c r="X155" s="7" t="n">
         <v>9</v>
       </c>
@@ -8753,19 +7313,9 @@
       </c>
     </row>
     <row r="156">
-      <c r="T156" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U156" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="4" t="n"/>
+      <c r="V156" s="4" t="n"/>
       <c r="X156" s="4" t="n">
         <v>2</v>
       </c>
@@ -8794,19 +7344,9 @@
       </c>
     </row>
     <row r="157">
-      <c r="T157" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U157" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V157" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T157" s="7" t="n"/>
+      <c r="U157" s="7" t="n"/>
+      <c r="V157" s="7" t="n"/>
       <c r="X157" s="7" t="n">
         <v>114</v>
       </c>
@@ -8835,19 +7375,9 @@
       </c>
     </row>
     <row r="158">
-      <c r="T158" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U158" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V158" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T158" s="4" t="n"/>
+      <c r="U158" s="4" t="n"/>
+      <c r="V158" s="4" t="n"/>
       <c r="X158" s="4" t="n">
         <v>16</v>
       </c>
@@ -8876,19 +7406,9 @@
       </c>
     </row>
     <row r="159">
-      <c r="T159" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U159" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V159" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T159" s="7" t="n"/>
+      <c r="U159" s="7" t="n"/>
+      <c r="V159" s="7" t="n"/>
       <c r="X159" s="7" t="n">
         <v>60</v>
       </c>
@@ -8917,19 +7437,9 @@
       </c>
     </row>
     <row r="160">
-      <c r="T160" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U160" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="4" t="n"/>
+      <c r="V160" s="4" t="n"/>
       <c r="X160" s="4" t="n">
         <v>41</v>
       </c>
@@ -8958,19 +7468,9 @@
       </c>
     </row>
     <row r="161">
-      <c r="T161" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U161" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V161" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T161" s="7" t="n"/>
+      <c r="U161" s="7" t="n"/>
+      <c r="V161" s="7" t="n"/>
       <c r="X161" s="7" t="n">
         <v>14</v>
       </c>
@@ -8999,19 +7499,9 @@
       </c>
     </row>
     <row r="162">
-      <c r="T162" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U162" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V162" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="4" t="n"/>
+      <c r="V162" s="4" t="n"/>
       <c r="X162" s="4" t="n">
         <v>84</v>
       </c>
@@ -9040,19 +7530,9 @@
       </c>
     </row>
     <row r="163">
-      <c r="T163" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U163" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V163" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T163" s="7" t="n"/>
+      <c r="U163" s="7" t="n"/>
+      <c r="V163" s="7" t="n"/>
       <c r="X163" s="7" t="n">
         <v>8</v>
       </c>
@@ -9081,19 +7561,9 @@
       </c>
     </row>
     <row r="164">
-      <c r="T164" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U164" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V164" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="4" t="n"/>
+      <c r="V164" s="4" t="n"/>
       <c r="X164" s="4" t="n">
         <v>1</v>
       </c>
@@ -9122,19 +7592,9 @@
       </c>
     </row>
     <row r="165">
-      <c r="T165" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U165" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V165" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T165" s="7" t="n"/>
+      <c r="U165" s="7" t="n"/>
+      <c r="V165" s="7" t="n"/>
       <c r="X165" s="7" t="n">
         <v>144</v>
       </c>
@@ -9163,19 +7623,9 @@
       </c>
     </row>
     <row r="166">
-      <c r="T166" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U166" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V166" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="4" t="n"/>
+      <c r="V166" s="4" t="n"/>
       <c r="X166" s="4" t="n">
         <v>16</v>
       </c>
@@ -9204,19 +7654,9 @@
       </c>
     </row>
     <row r="167">
-      <c r="T167" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U167" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V167" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T167" s="7" t="n"/>
+      <c r="U167" s="7" t="n"/>
+      <c r="V167" s="7" t="n"/>
       <c r="X167" s="7" t="n">
         <v>66</v>
       </c>
@@ -9245,19 +7685,9 @@
       </c>
     </row>
     <row r="168">
-      <c r="T168" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U168" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V168" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="4" t="n"/>
+      <c r="V168" s="4" t="n"/>
       <c r="X168" s="4" t="n">
         <v>35</v>
       </c>
@@ -9286,19 +7716,9 @@
       </c>
     </row>
     <row r="169">
-      <c r="T169" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U169" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V169" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T169" s="7" t="n"/>
+      <c r="U169" s="7" t="n"/>
+      <c r="V169" s="7" t="n"/>
       <c r="X169" s="7" t="n">
         <v>15</v>
       </c>
@@ -9327,19 +7747,9 @@
       </c>
     </row>
     <row r="170">
-      <c r="T170" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U170" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V170" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="4" t="n"/>
+      <c r="V170" s="4" t="n"/>
       <c r="X170" s="4" t="n">
         <v>83</v>
       </c>
@@ -9368,19 +7778,9 @@
       </c>
     </row>
     <row r="171">
-      <c r="T171" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U171" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V171" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T171" s="7" t="n"/>
+      <c r="U171" s="7" t="n"/>
+      <c r="V171" s="7" t="n"/>
       <c r="X171" s="7" t="n">
         <v>6</v>
       </c>
@@ -9409,19 +7809,9 @@
       </c>
     </row>
     <row r="172">
-      <c r="T172" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U172" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V172" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="4" t="n"/>
+      <c r="V172" s="4" t="n"/>
       <c r="X172" s="4" t="n">
         <v>104</v>
       </c>
@@ -9450,19 +7840,9 @@
       </c>
     </row>
     <row r="173">
-      <c r="T173" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U173" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V173" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T173" s="7" t="n"/>
+      <c r="U173" s="7" t="n"/>
+      <c r="V173" s="7" t="n"/>
       <c r="X173" s="7" t="n">
         <v>17</v>
       </c>
@@ -9491,19 +7871,9 @@
       </c>
     </row>
     <row r="174">
-      <c r="T174" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U174" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V174" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="n"/>
+      <c r="V174" s="4" t="n"/>
       <c r="X174" s="4" t="n">
         <v>72</v>
       </c>
@@ -9532,19 +7902,9 @@
       </c>
     </row>
     <row r="175">
-      <c r="T175" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U175" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V175" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T175" s="7" t="n"/>
+      <c r="U175" s="7" t="n"/>
+      <c r="V175" s="7" t="n"/>
       <c r="X175" s="7" t="n">
         <v>43</v>
       </c>
@@ -9573,19 +7933,9 @@
       </c>
     </row>
     <row r="176">
-      <c r="T176" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U176" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V176" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="4" t="n"/>
+      <c r="V176" s="4" t="n"/>
       <c r="X176" s="4" t="n">
         <v>20</v>
       </c>
@@ -9614,19 +7964,9 @@
       </c>
     </row>
     <row r="177">
-      <c r="T177" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U177" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V177" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T177" s="7" t="n"/>
+      <c r="U177" s="7" t="n"/>
+      <c r="V177" s="7" t="n"/>
       <c r="X177" s="7" t="n">
         <v>134</v>
       </c>
@@ -9655,19 +7995,9 @@
       </c>
     </row>
     <row r="178">
-      <c r="T178" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U178" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V178" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T178" s="4" t="n"/>
+      <c r="U178" s="4" t="n"/>
+      <c r="V178" s="4" t="n"/>
       <c r="X178" s="4" t="n">
         <v>7</v>
       </c>
@@ -9696,19 +8026,9 @@
       </c>
     </row>
     <row r="179">
-      <c r="T179" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U179" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V179" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T179" s="7" t="n"/>
+      <c r="U179" s="7" t="n"/>
+      <c r="V179" s="7" t="n"/>
       <c r="X179" s="7" t="n">
         <v>2</v>
       </c>
@@ -9737,19 +8057,9 @@
       </c>
     </row>
     <row r="180">
-      <c r="T180" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U180" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V180" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T180" s="4" t="n"/>
+      <c r="U180" s="4" t="n"/>
+      <c r="V180" s="4" t="n"/>
       <c r="X180" s="4" t="n">
         <v>129</v>
       </c>
@@ -9778,19 +8088,9 @@
       </c>
     </row>
     <row r="181">
-      <c r="T181" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U181" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V181" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T181" s="7" t="n"/>
+      <c r="U181" s="7" t="n"/>
+      <c r="V181" s="7" t="n"/>
       <c r="X181" s="7" t="n">
         <v>17</v>
       </c>
@@ -9819,19 +8119,9 @@
       </c>
     </row>
     <row r="182">
-      <c r="T182" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U182" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V182" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T182" s="4" t="n"/>
+      <c r="U182" s="4" t="n"/>
+      <c r="V182" s="4" t="n"/>
       <c r="X182" s="4" t="n">
         <v>66</v>
       </c>
@@ -9860,19 +8150,9 @@
       </c>
     </row>
     <row r="183">
-      <c r="T183" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U183" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V183" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T183" s="7" t="n"/>
+      <c r="U183" s="7" t="n"/>
+      <c r="V183" s="7" t="n"/>
       <c r="X183" s="7" t="n">
         <v>29</v>
       </c>
@@ -9901,19 +8181,9 @@
       </c>
     </row>
     <row r="184">
-      <c r="T184" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U184" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V184" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T184" s="4" t="n"/>
+      <c r="U184" s="4" t="n"/>
+      <c r="V184" s="4" t="n"/>
       <c r="X184" s="4" t="n">
         <v>21</v>
       </c>
@@ -9942,19 +8212,9 @@
       </c>
     </row>
     <row r="185">
-      <c r="T185" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U185" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V185" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T185" s="7" t="n"/>
+      <c r="U185" s="7" t="n"/>
+      <c r="V185" s="7" t="n"/>
       <c r="X185" s="7" t="n">
         <v>135</v>
       </c>
@@ -9983,19 +8243,9 @@
       </c>
     </row>
     <row r="186">
-      <c r="T186" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U186" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V186" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T186" s="4" t="n"/>
+      <c r="U186" s="4" t="n"/>
+      <c r="V186" s="4" t="n"/>
       <c r="X186" s="4" t="n">
         <v>9</v>
       </c>
@@ -10024,19 +8274,9 @@
       </c>
     </row>
     <row r="187">
-      <c r="T187" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U187" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V187" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T187" s="7" t="n"/>
+      <c r="U187" s="7" t="n"/>
+      <c r="V187" s="7" t="n"/>
       <c r="X187" s="7" t="n">
         <v>1</v>
       </c>
@@ -10065,19 +8305,9 @@
       </c>
     </row>
     <row r="188">
-      <c r="T188" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U188" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V188" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T188" s="4" t="n"/>
+      <c r="U188" s="4" t="n"/>
+      <c r="V188" s="4" t="n"/>
       <c r="X188" s="4" t="n">
         <v>126</v>
       </c>
@@ -10106,19 +8336,9 @@
       </c>
     </row>
     <row r="189">
-      <c r="T189" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U189" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V189" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T189" s="7" t="n"/>
+      <c r="U189" s="7" t="n"/>
+      <c r="V189" s="7" t="n"/>
       <c r="X189" s="7" t="n">
         <v>17</v>
       </c>
@@ -10147,19 +8367,9 @@
       </c>
     </row>
     <row r="190">
-      <c r="T190" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U190" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V190" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T190" s="4" t="n"/>
+      <c r="U190" s="4" t="n"/>
+      <c r="V190" s="4" t="n"/>
       <c r="X190" s="4" t="n">
         <v>63</v>
       </c>
@@ -10188,19 +8398,9 @@
       </c>
     </row>
     <row r="191">
-      <c r="T191" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U191" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V191" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T191" s="7" t="n"/>
+      <c r="U191" s="7" t="n"/>
+      <c r="V191" s="7" t="n"/>
       <c r="X191" s="7" t="n">
         <v>35</v>
       </c>
@@ -10229,19 +8429,9 @@
       </c>
     </row>
     <row r="192">
-      <c r="T192" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U192" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V192" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T192" s="4" t="n"/>
+      <c r="U192" s="4" t="n"/>
+      <c r="V192" s="4" t="n"/>
       <c r="X192" s="4" t="n">
         <v>26</v>
       </c>
@@ -10270,19 +8460,9 @@
       </c>
     </row>
     <row r="193">
-      <c r="T193" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U193" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V193" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T193" s="7" t="n"/>
+      <c r="U193" s="7" t="n"/>
+      <c r="V193" s="7" t="n"/>
       <c r="X193" s="7" t="n">
         <v>88</v>
       </c>
@@ -10311,19 +8491,9 @@
       </c>
     </row>
     <row r="194">
-      <c r="T194" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U194" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V194" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T194" s="4" t="n"/>
+      <c r="U194" s="4" t="n"/>
+      <c r="V194" s="4" t="n"/>
       <c r="X194" s="4" t="n">
         <v>6</v>
       </c>
@@ -10352,19 +8522,9 @@
       </c>
     </row>
     <row r="195">
-      <c r="T195" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U195" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V195" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T195" s="7" t="n"/>
+      <c r="U195" s="7" t="n"/>
+      <c r="V195" s="7" t="n"/>
       <c r="X195" s="7" t="n">
         <v>2</v>
       </c>
@@ -10393,19 +8553,9 @@
       </c>
     </row>
     <row r="196">
-      <c r="T196" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U196" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
-        </is>
-      </c>
-      <c r="V196" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T196" s="4" t="n"/>
+      <c r="U196" s="4" t="n"/>
+      <c r="V196" s="4" t="n"/>
       <c r="X196" s="4" t="n">
         <v>110</v>
       </c>
@@ -10434,19 +8584,9 @@
       </c>
     </row>
     <row r="197">
-      <c r="T197" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U197" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V197" s="7" t="n">
-        <v>9927</v>
-      </c>
+      <c r="T197" s="7" t="n"/>
+      <c r="U197" s="7" t="n"/>
+      <c r="V197" s="7" t="n"/>
       <c r="X197" s="7" t="n">
         <v>23</v>
       </c>
@@ -10475,19 +8615,9 @@
       </c>
     </row>
     <row r="198">
-      <c r="T198" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U198" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V198" s="4" t="n">
-        <v>9839</v>
-      </c>
+      <c r="T198" s="4" t="n"/>
+      <c r="U198" s="4" t="n"/>
+      <c r="V198" s="4" t="n"/>
       <c r="X198" s="4" t="n">
         <v>70</v>
       </c>
@@ -10516,19 +8646,9 @@
       </c>
     </row>
     <row r="199">
-      <c r="T199" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U199" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V199" s="7" t="n">
-        <v>9918</v>
-      </c>
+      <c r="T199" s="7" t="n"/>
+      <c r="U199" s="7" t="n"/>
+      <c r="V199" s="7" t="n"/>
       <c r="X199" s="7" t="n">
         <v>45</v>
       </c>
@@ -10557,19 +8677,9 @@
       </c>
     </row>
     <row r="200">
-      <c r="T200" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U200" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V200" s="4" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T200" s="4" t="n"/>
+      <c r="U200" s="4" t="n"/>
+      <c r="V200" s="4" t="n"/>
       <c r="X200" s="4" t="n">
         <v>11</v>
       </c>
@@ -10598,19 +8708,9 @@
       </c>
     </row>
     <row r="201">
-      <c r="T201" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U201" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V201" s="7" t="n">
-        <v>10050</v>
-      </c>
+      <c r="T201" s="7" t="n"/>
+      <c r="U201" s="7" t="n"/>
+      <c r="V201" s="7" t="n"/>
       <c r="X201" s="7" t="n">
         <v>67</v>
       </c>
@@ -10639,19 +8739,9 @@
       </c>
     </row>
     <row r="202">
-      <c r="T202" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U202" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V202" s="4" t="n">
-        <v>9768</v>
-      </c>
+      <c r="T202" s="4" t="n"/>
+      <c r="U202" s="4" t="n"/>
+      <c r="V202" s="4" t="n"/>
       <c r="X202" s="4" t="n">
         <v>1</v>
       </c>
@@ -10680,19 +8770,9 @@
       </c>
     </row>
     <row r="203">
-      <c r="T203" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U203" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V203" s="7" t="n">
-        <v>9920</v>
-      </c>
+      <c r="T203" s="7" t="n"/>
+      <c r="U203" s="7" t="n"/>
+      <c r="V203" s="7" t="n"/>
       <c r="X203" s="7" t="n">
         <v>9</v>
       </c>
@@ -10721,19 +8801,9 @@
       </c>
     </row>
     <row r="204">
-      <c r="T204" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U204" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V204" s="4" t="n">
-        <v>10435</v>
-      </c>
+      <c r="T204" s="4" t="n"/>
+      <c r="U204" s="4" t="n"/>
+      <c r="V204" s="4" t="n"/>
       <c r="X204" s="4" t="n">
         <v>3</v>
       </c>
@@ -10762,19 +8832,9 @@
       </c>
     </row>
     <row r="205">
-      <c r="T205" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U205" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V205" s="7" t="n">
-        <v>10434</v>
-      </c>
+      <c r="T205" s="7" t="n"/>
+      <c r="U205" s="7" t="n"/>
+      <c r="V205" s="7" t="n"/>
       <c r="X205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
       <c r="Z205" s="7" t="n"/>
@@ -10793,19 +8853,9 @@
       </c>
     </row>
     <row r="206">
-      <c r="T206" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U206" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V206" s="4" t="n">
-        <v>10284</v>
-      </c>
+      <c r="T206" s="4" t="n"/>
+      <c r="U206" s="4" t="n"/>
+      <c r="V206" s="4" t="n"/>
       <c r="X206" s="4" t="n"/>
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="n"/>
@@ -10824,19 +8874,9 @@
       </c>
     </row>
     <row r="207">
-      <c r="T207" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U207" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V207" s="7" t="n">
-        <v>10458</v>
-      </c>
+      <c r="T207" s="7" t="n"/>
+      <c r="U207" s="7" t="n"/>
+      <c r="V207" s="7" t="n"/>
       <c r="X207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
       <c r="Z207" s="7" t="n"/>
@@ -10855,19 +8895,9 @@
       </c>
     </row>
     <row r="208">
-      <c r="T208" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U208" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V208" s="4" t="n">
-        <v>10153</v>
-      </c>
+      <c r="T208" s="4" t="n"/>
+      <c r="U208" s="4" t="n"/>
+      <c r="V208" s="4" t="n"/>
       <c r="X208" s="4" t="n"/>
       <c r="Y208" s="4" t="n"/>
       <c r="Z208" s="4" t="n"/>
@@ -10886,19 +8916,9 @@
       </c>
     </row>
     <row r="209">
-      <c r="T209" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U209" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V209" s="7" t="n">
-        <v>9843</v>
-      </c>
+      <c r="T209" s="7" t="n"/>
+      <c r="U209" s="7" t="n"/>
+      <c r="V209" s="7" t="n"/>
       <c r="X209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
       <c r="Z209" s="7" t="n"/>
@@ -10917,19 +8937,9 @@
       </c>
     </row>
     <row r="210">
-      <c r="T210" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U210" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V210" s="4" t="n">
-        <v>10433</v>
-      </c>
+      <c r="T210" s="4" t="n"/>
+      <c r="U210" s="4" t="n"/>
+      <c r="V210" s="4" t="n"/>
       <c r="X210" s="4" t="n"/>
       <c r="Y210" s="4" t="n"/>
       <c r="Z210" s="4" t="n"/>
@@ -10948,19 +8958,9 @@
       </c>
     </row>
     <row r="211">
-      <c r="T211" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U211" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V211" s="7" t="n">
-        <v>10670</v>
-      </c>
+      <c r="T211" s="7" t="n"/>
+      <c r="U211" s="7" t="n"/>
+      <c r="V211" s="7" t="n"/>
       <c r="X211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
       <c r="Z211" s="7" t="n"/>
@@ -10979,19 +8979,9 @@
       </c>
     </row>
     <row r="212">
-      <c r="T212" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U212" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V212" s="4" t="n">
-        <v>10599</v>
-      </c>
+      <c r="T212" s="4" t="n"/>
+      <c r="U212" s="4" t="n"/>
+      <c r="V212" s="4" t="n"/>
       <c r="X212" s="4" t="n"/>
       <c r="Y212" s="4" t="n"/>
       <c r="Z212" s="4" t="n"/>
@@ -11010,19 +9000,9 @@
       </c>
     </row>
     <row r="213">
-      <c r="T213" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U213" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V213" s="7" t="n">
-        <v>10619</v>
-      </c>
+      <c r="T213" s="7" t="n"/>
+      <c r="U213" s="7" t="n"/>
+      <c r="V213" s="7" t="n"/>
       <c r="X213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
       <c r="Z213" s="7" t="n"/>
@@ -11041,19 +9021,9 @@
       </c>
     </row>
     <row r="214">
-      <c r="T214" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U214" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V214" s="4" t="n">
-        <v>10415</v>
-      </c>
+      <c r="T214" s="4" t="n"/>
+      <c r="U214" s="4" t="n"/>
+      <c r="V214" s="4" t="n"/>
       <c r="X214" s="4" t="n"/>
       <c r="Y214" s="4" t="n"/>
       <c r="Z214" s="4" t="n"/>
@@ -11072,19 +9042,9 @@
       </c>
     </row>
     <row r="215">
-      <c r="T215" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U215" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V215" s="7" t="n">
-        <v>10065</v>
-      </c>
+      <c r="T215" s="7" t="n"/>
+      <c r="U215" s="7" t="n"/>
+      <c r="V215" s="7" t="n"/>
       <c r="X215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
       <c r="Z215" s="7" t="n"/>
@@ -11103,19 +9063,9 @@
       </c>
     </row>
     <row r="216">
-      <c r="T216" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U216" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V216" s="4" t="n">
-        <v>10158</v>
-      </c>
+      <c r="T216" s="4" t="n"/>
+      <c r="U216" s="4" t="n"/>
+      <c r="V216" s="4" t="n"/>
       <c r="X216" s="4" t="n"/>
       <c r="Y216" s="4" t="n"/>
       <c r="Z216" s="4" t="n"/>
@@ -11134,19 +9084,9 @@
       </c>
     </row>
     <row r="217">
-      <c r="T217" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U217" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V217" s="7" t="n">
-        <v>10333</v>
-      </c>
+      <c r="T217" s="7" t="n"/>
+      <c r="U217" s="7" t="n"/>
+      <c r="V217" s="7" t="n"/>
       <c r="X217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
       <c r="Z217" s="7" t="n"/>
@@ -11165,19 +9105,9 @@
       </c>
     </row>
     <row r="218">
-      <c r="T218" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U218" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V218" s="4" t="n">
-        <v>10414</v>
-      </c>
+      <c r="T218" s="4" t="n"/>
+      <c r="U218" s="4" t="n"/>
+      <c r="V218" s="4" t="n"/>
       <c r="X218" s="4" t="n"/>
       <c r="Y218" s="4" t="n"/>
       <c r="Z218" s="4" t="n"/>
@@ -11196,19 +9126,9 @@
       </c>
     </row>
     <row r="219">
-      <c r="T219" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U219" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V219" s="7" t="n">
-        <v>10453</v>
-      </c>
+      <c r="T219" s="7" t="n"/>
+      <c r="U219" s="7" t="n"/>
+      <c r="V219" s="7" t="n"/>
       <c r="X219" s="7" t="n"/>
       <c r="Y219" s="7" t="n"/>
       <c r="Z219" s="7" t="n"/>
@@ -11227,19 +9147,9 @@
       </c>
     </row>
     <row r="220">
-      <c r="T220" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U220" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V220" s="4" t="n">
-        <v>10879</v>
-      </c>
+      <c r="T220" s="4" t="n"/>
+      <c r="U220" s="4" t="n"/>
+      <c r="V220" s="4" t="n"/>
       <c r="X220" s="4" t="n"/>
       <c r="Y220" s="4" t="n"/>
       <c r="Z220" s="4" t="n"/>
@@ -11258,19 +9168,9 @@
       </c>
     </row>
     <row r="221">
-      <c r="T221" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U221" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V221" s="7" t="n">
-        <v>10826</v>
-      </c>
+      <c r="T221" s="7" t="n"/>
+      <c r="U221" s="7" t="n"/>
+      <c r="V221" s="7" t="n"/>
       <c r="X221" s="7" t="n"/>
       <c r="Y221" s="7" t="n"/>
       <c r="Z221" s="7" t="n"/>
@@ -11289,19 +9189,9 @@
       </c>
     </row>
     <row r="222">
-      <c r="T222" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U222" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation50987</t>
-        </is>
-      </c>
-      <c r="V222" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T222" s="4" t="n"/>
+      <c r="U222" s="4" t="n"/>
+      <c r="V222" s="4" t="n"/>
       <c r="X222" s="4" t="n"/>
       <c r="Y222" s="4" t="n"/>
       <c r="Z222" s="4" t="n"/>
@@ -11320,19 +9210,9 @@
       </c>
     </row>
     <row r="223">
-      <c r="T223" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U223" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation75114</t>
-        </is>
-      </c>
-      <c r="V223" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T223" s="7" t="n"/>
+      <c r="U223" s="7" t="n"/>
+      <c r="V223" s="7" t="n"/>
       <c r="X223" s="7" t="n"/>
       <c r="Y223" s="7" t="n"/>
       <c r="Z223" s="7" t="n"/>
@@ -11351,19 +9231,9 @@
       </c>
     </row>
     <row r="224">
-      <c r="T224" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U224" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V224" s="4" t="n">
-        <v>21493</v>
-      </c>
+      <c r="T224" s="4" t="n"/>
+      <c r="U224" s="4" t="n"/>
+      <c r="V224" s="4" t="n"/>
       <c r="X224" s="4" t="n"/>
       <c r="Y224" s="4" t="n"/>
       <c r="Z224" s="4" t="n"/>
@@ -11382,19 +9252,9 @@
       </c>
     </row>
     <row r="225">
-      <c r="T225" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U225" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V225" s="7" t="n">
-        <v>21012</v>
-      </c>
+      <c r="T225" s="7" t="n"/>
+      <c r="U225" s="7" t="n"/>
+      <c r="V225" s="7" t="n"/>
       <c r="X225" s="7" t="n"/>
       <c r="Y225" s="7" t="n"/>
       <c r="Z225" s="7" t="n"/>
@@ -11413,19 +9273,9 @@
       </c>
     </row>
     <row r="226">
-      <c r="T226" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U226" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V226" s="4" t="n">
-        <v>21635</v>
-      </c>
+      <c r="T226" s="4" t="n"/>
+      <c r="U226" s="4" t="n"/>
+      <c r="V226" s="4" t="n"/>
       <c r="X226" s="4" t="n"/>
       <c r="Y226" s="4" t="n"/>
       <c r="Z226" s="4" t="n"/>
@@ -11444,19 +9294,9 @@
       </c>
     </row>
     <row r="227">
-      <c r="T227" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U227" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V227" s="7" t="n">
-        <v>21969</v>
-      </c>
+      <c r="T227" s="7" t="n"/>
+      <c r="U227" s="7" t="n"/>
+      <c r="V227" s="7" t="n"/>
       <c r="X227" s="7" t="n"/>
       <c r="Y227" s="7" t="n"/>
       <c r="Z227" s="7" t="n"/>
@@ -11473,2022 +9313,6 @@
           <t>com.logistics.rider.foody</t>
         </is>
       </c>
-    </row>
-    <row r="228">
-      <c r="T228" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U228" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V228" s="4" t="n">
-        <v>21723</v>
-      </c>
-      <c r="X228" s="4" t="n"/>
-      <c r="Y228" s="4" t="n"/>
-      <c r="Z228" s="4" t="n"/>
-      <c r="AB228" s="4" t="n"/>
-      <c r="AC228" s="4" t="n"/>
-      <c r="AD228" s="4" t="n"/>
-    </row>
-    <row r="229">
-      <c r="T229" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U229" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V229" s="7" t="n">
-        <v>20879</v>
-      </c>
-      <c r="X229" s="7" t="n"/>
-      <c r="Y229" s="7" t="n"/>
-      <c r="Z229" s="7" t="n"/>
-      <c r="AB229" s="7" t="n"/>
-      <c r="AC229" s="7" t="n"/>
-      <c r="AD229" s="7" t="n"/>
-    </row>
-    <row r="230">
-      <c r="T230" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U230" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V230" s="4" t="n">
-        <v>20783</v>
-      </c>
-      <c r="X230" s="4" t="n"/>
-      <c r="Y230" s="4" t="n"/>
-      <c r="Z230" s="4" t="n"/>
-      <c r="AB230" s="4" t="n"/>
-      <c r="AC230" s="4" t="n"/>
-      <c r="AD230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="T231" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U231" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V231" s="7" t="n">
-        <v>21875</v>
-      </c>
-      <c r="X231" s="7" t="n"/>
-      <c r="Y231" s="7" t="n"/>
-      <c r="Z231" s="7" t="n"/>
-      <c r="AB231" s="7" t="n"/>
-      <c r="AC231" s="7" t="n"/>
-      <c r="AD231" s="7" t="n"/>
-    </row>
-    <row r="232">
-      <c r="T232" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U232" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V232" s="4" t="n">
-        <v>22103</v>
-      </c>
-      <c r="X232" s="4" t="n"/>
-      <c r="Y232" s="4" t="n"/>
-      <c r="Z232" s="4" t="n"/>
-      <c r="AB232" s="4" t="n"/>
-      <c r="AC232" s="4" t="n"/>
-      <c r="AD232" s="4" t="n"/>
-    </row>
-    <row r="233">
-      <c r="T233" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U233" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V233" s="7" t="n">
-        <v>22799</v>
-      </c>
-      <c r="X233" s="7" t="n"/>
-      <c r="Y233" s="7" t="n"/>
-      <c r="Z233" s="7" t="n"/>
-      <c r="AB233" s="7" t="n"/>
-      <c r="AC233" s="7" t="n"/>
-      <c r="AD233" s="7" t="n"/>
-    </row>
-    <row r="234">
-      <c r="T234" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U234" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V234" s="4" t="n">
-        <v>22705</v>
-      </c>
-      <c r="X234" s="4" t="n"/>
-      <c r="Y234" s="4" t="n"/>
-      <c r="Z234" s="4" t="n"/>
-      <c r="AB234" s="4" t="n"/>
-      <c r="AC234" s="4" t="n"/>
-      <c r="AD234" s="4" t="n"/>
-    </row>
-    <row r="235">
-      <c r="T235" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U235" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V235" s="7" t="n">
-        <v>21885</v>
-      </c>
-      <c r="X235" s="7" t="n"/>
-      <c r="Y235" s="7" t="n"/>
-      <c r="Z235" s="7" t="n"/>
-      <c r="AB235" s="7" t="n"/>
-      <c r="AC235" s="7" t="n"/>
-      <c r="AD235" s="7" t="n"/>
-    </row>
-    <row r="236">
-      <c r="T236" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U236" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V236" s="4" t="n">
-        <v>21360</v>
-      </c>
-      <c r="X236" s="4" t="n"/>
-      <c r="Y236" s="4" t="n"/>
-      <c r="Z236" s="4" t="n"/>
-      <c r="AB236" s="4" t="n"/>
-      <c r="AC236" s="4" t="n"/>
-      <c r="AD236" s="4" t="n"/>
-    </row>
-    <row r="237">
-      <c r="T237" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U237" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V237" s="7" t="n">
-        <v>20612</v>
-      </c>
-      <c r="X237" s="7" t="n"/>
-      <c r="Y237" s="7" t="n"/>
-      <c r="Z237" s="7" t="n"/>
-      <c r="AB237" s="7" t="n"/>
-      <c r="AC237" s="7" t="n"/>
-      <c r="AD237" s="7" t="n"/>
-    </row>
-    <row r="238">
-      <c r="T238" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U238" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V238" s="4" t="n">
-        <v>22101</v>
-      </c>
-      <c r="X238" s="4" t="n"/>
-      <c r="Y238" s="4" t="n"/>
-      <c r="Z238" s="4" t="n"/>
-      <c r="AB238" s="4" t="n"/>
-      <c r="AC238" s="4" t="n"/>
-      <c r="AD238" s="4" t="n"/>
-    </row>
-    <row r="239">
-      <c r="T239" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U239" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V239" s="7" t="n">
-        <v>22665</v>
-      </c>
-      <c r="X239" s="7" t="n"/>
-      <c r="Y239" s="7" t="n"/>
-      <c r="Z239" s="7" t="n"/>
-      <c r="AB239" s="7" t="n"/>
-      <c r="AC239" s="7" t="n"/>
-      <c r="AD239" s="7" t="n"/>
-    </row>
-    <row r="240">
-      <c r="T240" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U240" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V240" s="4" t="n">
-        <v>22473</v>
-      </c>
-      <c r="X240" s="4" t="n"/>
-      <c r="Y240" s="4" t="n"/>
-      <c r="Z240" s="4" t="n"/>
-      <c r="AB240" s="4" t="n"/>
-      <c r="AC240" s="4" t="n"/>
-      <c r="AD240" s="4" t="n"/>
-    </row>
-    <row r="241">
-      <c r="T241" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U241" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V241" s="7" t="n">
-        <v>22903</v>
-      </c>
-      <c r="X241" s="7" t="n"/>
-      <c r="Y241" s="7" t="n"/>
-      <c r="Z241" s="7" t="n"/>
-      <c r="AB241" s="7" t="n"/>
-      <c r="AC241" s="7" t="n"/>
-      <c r="AD241" s="7" t="n"/>
-    </row>
-    <row r="242">
-      <c r="T242" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U242" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V242" s="4" t="n">
-        <v>21829</v>
-      </c>
-      <c r="X242" s="4" t="n"/>
-      <c r="Y242" s="4" t="n"/>
-      <c r="Z242" s="4" t="n"/>
-      <c r="AB242" s="4" t="n"/>
-      <c r="AC242" s="4" t="n"/>
-      <c r="AD242" s="4" t="n"/>
-    </row>
-    <row r="243">
-      <c r="T243" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U243" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V243" s="7" t="n">
-        <v>20959</v>
-      </c>
-      <c r="X243" s="7" t="n"/>
-      <c r="Y243" s="7" t="n"/>
-      <c r="Z243" s="7" t="n"/>
-      <c r="AB243" s="7" t="n"/>
-      <c r="AC243" s="7" t="n"/>
-      <c r="AD243" s="7" t="n"/>
-    </row>
-    <row r="244">
-      <c r="T244" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U244" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V244" s="4" t="n">
-        <v>20856</v>
-      </c>
-      <c r="X244" s="4" t="n"/>
-      <c r="Y244" s="4" t="n"/>
-      <c r="Z244" s="4" t="n"/>
-      <c r="AB244" s="4" t="n"/>
-      <c r="AC244" s="4" t="n"/>
-      <c r="AD244" s="4" t="n"/>
-    </row>
-    <row r="245">
-      <c r="T245" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U245" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V245" s="7" t="n">
-        <v>23061</v>
-      </c>
-      <c r="X245" s="7" t="n"/>
-      <c r="Y245" s="7" t="n"/>
-      <c r="Z245" s="7" t="n"/>
-      <c r="AB245" s="7" t="n"/>
-      <c r="AC245" s="7" t="n"/>
-      <c r="AD245" s="7" t="n"/>
-    </row>
-    <row r="246">
-      <c r="T246" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U246" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V246" s="4" t="n">
-        <v>21952</v>
-      </c>
-      <c r="X246" s="4" t="n"/>
-      <c r="Y246" s="4" t="n"/>
-      <c r="Z246" s="4" t="n"/>
-      <c r="AB246" s="4" t="n"/>
-      <c r="AC246" s="4" t="n"/>
-      <c r="AD246" s="4" t="n"/>
-    </row>
-    <row r="247">
-      <c r="T247" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U247" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V247" s="7" t="n">
-        <v>22608</v>
-      </c>
-      <c r="X247" s="7" t="n"/>
-      <c r="Y247" s="7" t="n"/>
-      <c r="Z247" s="7" t="n"/>
-      <c r="AB247" s="7" t="n"/>
-      <c r="AC247" s="7" t="n"/>
-      <c r="AD247" s="7" t="n"/>
-    </row>
-    <row r="248">
-      <c r="T248" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U248" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V248" s="4" t="n">
-        <v>22674</v>
-      </c>
-      <c r="X248" s="4" t="n"/>
-      <c r="Y248" s="4" t="n"/>
-      <c r="Z248" s="4" t="n"/>
-      <c r="AB248" s="4" t="n"/>
-      <c r="AC248" s="4" t="n"/>
-      <c r="AD248" s="4" t="n"/>
-    </row>
-    <row r="249">
-      <c r="T249" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U249" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V249" s="7" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X249" s="7" t="n"/>
-      <c r="Y249" s="7" t="n"/>
-      <c r="Z249" s="7" t="n"/>
-      <c r="AB249" s="7" t="n"/>
-      <c r="AC249" s="7" t="n"/>
-      <c r="AD249" s="7" t="n"/>
-    </row>
-    <row r="250">
-      <c r="T250" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U250" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V250" s="4" t="n">
-        <v>16721</v>
-      </c>
-      <c r="X250" s="4" t="n"/>
-      <c r="Y250" s="4" t="n"/>
-      <c r="Z250" s="4" t="n"/>
-      <c r="AB250" s="4" t="n"/>
-      <c r="AC250" s="4" t="n"/>
-      <c r="AD250" s="4" t="n"/>
-    </row>
-    <row r="251">
-      <c r="T251" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U251" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V251" s="7" t="n">
-        <v>16586</v>
-      </c>
-      <c r="X251" s="7" t="n"/>
-      <c r="Y251" s="7" t="n"/>
-      <c r="Z251" s="7" t="n"/>
-      <c r="AB251" s="7" t="n"/>
-      <c r="AC251" s="7" t="n"/>
-      <c r="AD251" s="7" t="n"/>
-    </row>
-    <row r="252">
-      <c r="T252" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U252" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V252" s="4" t="n">
-        <v>16419</v>
-      </c>
-      <c r="X252" s="4" t="n"/>
-      <c r="Y252" s="4" t="n"/>
-      <c r="Z252" s="4" t="n"/>
-      <c r="AB252" s="4" t="n"/>
-      <c r="AC252" s="4" t="n"/>
-      <c r="AD252" s="4" t="n"/>
-    </row>
-    <row r="253">
-      <c r="T253" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U253" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V253" s="7" t="n">
-        <v>15946</v>
-      </c>
-      <c r="X253" s="7" t="n"/>
-      <c r="Y253" s="7" t="n"/>
-      <c r="Z253" s="7" t="n"/>
-      <c r="AB253" s="7" t="n"/>
-      <c r="AC253" s="7" t="n"/>
-      <c r="AD253" s="7" t="n"/>
-    </row>
-    <row r="254">
-      <c r="T254" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U254" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V254" s="4" t="n">
-        <v>16042</v>
-      </c>
-      <c r="X254" s="4" t="n"/>
-      <c r="Y254" s="4" t="n"/>
-      <c r="Z254" s="4" t="n"/>
-      <c r="AB254" s="4" t="n"/>
-      <c r="AC254" s="4" t="n"/>
-      <c r="AD254" s="4" t="n"/>
-    </row>
-    <row r="255">
-      <c r="T255" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U255" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V255" s="7" t="n">
-        <v>16409</v>
-      </c>
-      <c r="X255" s="7" t="n"/>
-      <c r="Y255" s="7" t="n"/>
-      <c r="Z255" s="7" t="n"/>
-      <c r="AB255" s="7" t="n"/>
-      <c r="AC255" s="7" t="n"/>
-      <c r="AD255" s="7" t="n"/>
-    </row>
-    <row r="256">
-      <c r="T256" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U256" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V256" s="4" t="n">
-        <v>16831</v>
-      </c>
-      <c r="X256" s="4" t="n"/>
-      <c r="Y256" s="4" t="n"/>
-      <c r="Z256" s="4" t="n"/>
-      <c r="AB256" s="4" t="n"/>
-      <c r="AC256" s="4" t="n"/>
-      <c r="AD256" s="4" t="n"/>
-    </row>
-    <row r="257">
-      <c r="T257" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U257" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V257" s="7" t="n">
-        <v>16886</v>
-      </c>
-      <c r="X257" s="7" t="n"/>
-      <c r="Y257" s="7" t="n"/>
-      <c r="Z257" s="7" t="n"/>
-      <c r="AB257" s="7" t="n"/>
-      <c r="AC257" s="7" t="n"/>
-      <c r="AD257" s="7" t="n"/>
-    </row>
-    <row r="258">
-      <c r="T258" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U258" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V258" s="4" t="n">
-        <v>16694</v>
-      </c>
-      <c r="X258" s="4" t="n"/>
-      <c r="Y258" s="4" t="n"/>
-      <c r="Z258" s="4" t="n"/>
-      <c r="AB258" s="4" t="n"/>
-      <c r="AC258" s="4" t="n"/>
-      <c r="AD258" s="4" t="n"/>
-    </row>
-    <row r="259">
-      <c r="T259" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U259" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V259" s="7" t="n">
-        <v>16659</v>
-      </c>
-      <c r="X259" s="7" t="n"/>
-      <c r="Y259" s="7" t="n"/>
-      <c r="Z259" s="7" t="n"/>
-      <c r="AB259" s="7" t="n"/>
-      <c r="AC259" s="7" t="n"/>
-      <c r="AD259" s="7" t="n"/>
-    </row>
-    <row r="260">
-      <c r="T260" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U260" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V260" s="4" t="n">
-        <v>16268</v>
-      </c>
-      <c r="X260" s="4" t="n"/>
-      <c r="Y260" s="4" t="n"/>
-      <c r="Z260" s="4" t="n"/>
-      <c r="AB260" s="4" t="n"/>
-      <c r="AC260" s="4" t="n"/>
-      <c r="AD260" s="4" t="n"/>
-    </row>
-    <row r="261">
-      <c r="T261" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U261" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V261" s="7" t="n">
-        <v>16259</v>
-      </c>
-      <c r="X261" s="7" t="n"/>
-      <c r="Y261" s="7" t="n"/>
-      <c r="Z261" s="7" t="n"/>
-      <c r="AB261" s="7" t="n"/>
-      <c r="AC261" s="7" t="n"/>
-      <c r="AD261" s="7" t="n"/>
-    </row>
-    <row r="262">
-      <c r="T262" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U262" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V262" s="4" t="n">
-        <v>16600</v>
-      </c>
-      <c r="X262" s="4" t="n"/>
-      <c r="Y262" s="4" t="n"/>
-      <c r="Z262" s="4" t="n"/>
-      <c r="AB262" s="4" t="n"/>
-      <c r="AC262" s="4" t="n"/>
-      <c r="AD262" s="4" t="n"/>
-    </row>
-    <row r="263">
-      <c r="T263" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U263" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V263" s="7" t="n">
-        <v>16913</v>
-      </c>
-      <c r="X263" s="7" t="n"/>
-      <c r="Y263" s="7" t="n"/>
-      <c r="Z263" s="7" t="n"/>
-      <c r="AB263" s="7" t="n"/>
-      <c r="AC263" s="7" t="n"/>
-      <c r="AD263" s="7" t="n"/>
-    </row>
-    <row r="264">
-      <c r="T264" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U264" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V264" s="4" t="n">
-        <v>16991</v>
-      </c>
-      <c r="X264" s="4" t="n"/>
-      <c r="Y264" s="4" t="n"/>
-      <c r="Z264" s="4" t="n"/>
-      <c r="AB264" s="4" t="n"/>
-      <c r="AC264" s="4" t="n"/>
-      <c r="AD264" s="4" t="n"/>
-    </row>
-    <row r="265">
-      <c r="T265" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U265" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V265" s="7" t="n">
-        <v>17365</v>
-      </c>
-      <c r="X265" s="7" t="n"/>
-      <c r="Y265" s="7" t="n"/>
-      <c r="Z265" s="7" t="n"/>
-      <c r="AB265" s="7" t="n"/>
-      <c r="AC265" s="7" t="n"/>
-      <c r="AD265" s="7" t="n"/>
-    </row>
-    <row r="266">
-      <c r="T266" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U266" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V266" s="4" t="n">
-        <v>16944</v>
-      </c>
-      <c r="X266" s="4" t="n"/>
-      <c r="Y266" s="4" t="n"/>
-      <c r="Z266" s="4" t="n"/>
-      <c r="AB266" s="4" t="n"/>
-      <c r="AC266" s="4" t="n"/>
-      <c r="AD266" s="4" t="n"/>
-    </row>
-    <row r="267">
-      <c r="T267" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U267" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V267" s="7" t="n">
-        <v>16518</v>
-      </c>
-      <c r="X267" s="7" t="n"/>
-      <c r="Y267" s="7" t="n"/>
-      <c r="Z267" s="7" t="n"/>
-      <c r="AB267" s="7" t="n"/>
-      <c r="AC267" s="7" t="n"/>
-      <c r="AD267" s="7" t="n"/>
-    </row>
-    <row r="268">
-      <c r="T268" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U268" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V268" s="4" t="n">
-        <v>16634</v>
-      </c>
-      <c r="X268" s="4" t="n"/>
-      <c r="Y268" s="4" t="n"/>
-      <c r="Z268" s="4" t="n"/>
-      <c r="AB268" s="4" t="n"/>
-      <c r="AC268" s="4" t="n"/>
-      <c r="AD268" s="4" t="n"/>
-    </row>
-    <row r="269">
-      <c r="T269" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U269" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V269" s="7" t="n">
-        <v>16711</v>
-      </c>
-      <c r="X269" s="7" t="n"/>
-      <c r="Y269" s="7" t="n"/>
-      <c r="Z269" s="7" t="n"/>
-      <c r="AB269" s="7" t="n"/>
-      <c r="AC269" s="7" t="n"/>
-      <c r="AD269" s="7" t="n"/>
-    </row>
-    <row r="270">
-      <c r="T270" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U270" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V270" s="4" t="n">
-        <v>17379</v>
-      </c>
-      <c r="X270" s="4" t="n"/>
-      <c r="Y270" s="4" t="n"/>
-      <c r="Z270" s="4" t="n"/>
-      <c r="AB270" s="4" t="n"/>
-      <c r="AC270" s="4" t="n"/>
-      <c r="AD270" s="4" t="n"/>
-    </row>
-    <row r="271">
-      <c r="T271" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U271" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V271" s="7" t="n">
-        <v>17551</v>
-      </c>
-      <c r="X271" s="7" t="n"/>
-      <c r="Y271" s="7" t="n"/>
-      <c r="Z271" s="7" t="n"/>
-      <c r="AB271" s="7" t="n"/>
-      <c r="AC271" s="7" t="n"/>
-      <c r="AD271" s="7" t="n"/>
-    </row>
-    <row r="272">
-      <c r="T272" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U272" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V272" s="4" t="n">
-        <v>17474</v>
-      </c>
-      <c r="X272" s="4" t="n"/>
-      <c r="Y272" s="4" t="n"/>
-      <c r="Z272" s="4" t="n"/>
-      <c r="AB272" s="4" t="n"/>
-      <c r="AC272" s="4" t="n"/>
-      <c r="AD272" s="4" t="n"/>
-    </row>
-    <row r="273">
-      <c r="T273" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U273" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V273" s="7" t="n">
-        <v>17309</v>
-      </c>
-      <c r="X273" s="7" t="n"/>
-      <c r="Y273" s="7" t="n"/>
-      <c r="Z273" s="7" t="n"/>
-      <c r="AB273" s="7" t="n"/>
-      <c r="AC273" s="7" t="n"/>
-      <c r="AD273" s="7" t="n"/>
-    </row>
-    <row r="274">
-      <c r="T274" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U274" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V274" s="4" t="n">
-        <v>724</v>
-      </c>
-      <c r="X274" s="4" t="n"/>
-      <c r="Y274" s="4" t="n"/>
-      <c r="Z274" s="4" t="n"/>
-      <c r="AB274" s="4" t="n"/>
-      <c r="AC274" s="4" t="n"/>
-      <c r="AD274" s="4" t="n"/>
-    </row>
-    <row r="275">
-      <c r="T275" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U275" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V275" s="7" t="n">
-        <v>746</v>
-      </c>
-      <c r="X275" s="7" t="n"/>
-      <c r="Y275" s="7" t="n"/>
-      <c r="Z275" s="7" t="n"/>
-      <c r="AB275" s="7" t="n"/>
-      <c r="AC275" s="7" t="n"/>
-      <c r="AD275" s="7" t="n"/>
-    </row>
-    <row r="276">
-      <c r="T276" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U276" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V276" s="4" t="n">
-        <v>723</v>
-      </c>
-      <c r="X276" s="4" t="n"/>
-      <c r="Y276" s="4" t="n"/>
-      <c r="Z276" s="4" t="n"/>
-      <c r="AB276" s="4" t="n"/>
-      <c r="AC276" s="4" t="n"/>
-      <c r="AD276" s="4" t="n"/>
-    </row>
-    <row r="277">
-      <c r="T277" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U277" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V277" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="X277" s="7" t="n"/>
-      <c r="Y277" s="7" t="n"/>
-      <c r="Z277" s="7" t="n"/>
-      <c r="AB277" s="7" t="n"/>
-      <c r="AC277" s="7" t="n"/>
-      <c r="AD277" s="7" t="n"/>
-    </row>
-    <row r="278">
-      <c r="T278" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U278" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V278" s="4" t="n">
-        <v>735</v>
-      </c>
-      <c r="X278" s="4" t="n"/>
-      <c r="Y278" s="4" t="n"/>
-      <c r="Z278" s="4" t="n"/>
-      <c r="AB278" s="4" t="n"/>
-      <c r="AC278" s="4" t="n"/>
-      <c r="AD278" s="4" t="n"/>
-    </row>
-    <row r="279">
-      <c r="T279" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U279" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V279" s="7" t="n">
-        <v>714</v>
-      </c>
-      <c r="X279" s="7" t="n"/>
-      <c r="Y279" s="7" t="n"/>
-      <c r="Z279" s="7" t="n"/>
-      <c r="AB279" s="7" t="n"/>
-      <c r="AC279" s="7" t="n"/>
-      <c r="AD279" s="7" t="n"/>
-    </row>
-    <row r="280">
-      <c r="T280" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U280" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V280" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X280" s="4" t="n"/>
-      <c r="Y280" s="4" t="n"/>
-      <c r="Z280" s="4" t="n"/>
-      <c r="AB280" s="4" t="n"/>
-      <c r="AC280" s="4" t="n"/>
-      <c r="AD280" s="4" t="n"/>
-    </row>
-    <row r="281">
-      <c r="T281" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U281" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V281" s="7" t="n">
-        <v>729</v>
-      </c>
-      <c r="X281" s="7" t="n"/>
-      <c r="Y281" s="7" t="n"/>
-      <c r="Z281" s="7" t="n"/>
-      <c r="AB281" s="7" t="n"/>
-      <c r="AC281" s="7" t="n"/>
-      <c r="AD281" s="7" t="n"/>
-    </row>
-    <row r="282">
-      <c r="T282" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U282" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V282" s="4" t="n">
-        <v>719</v>
-      </c>
-      <c r="X282" s="4" t="n"/>
-      <c r="Y282" s="4" t="n"/>
-      <c r="Z282" s="4" t="n"/>
-      <c r="AB282" s="4" t="n"/>
-      <c r="AC282" s="4" t="n"/>
-      <c r="AD282" s="4" t="n"/>
-    </row>
-    <row r="283">
-      <c r="T283" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U283" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V283" s="7" t="n">
-        <v>719</v>
-      </c>
-      <c r="X283" s="7" t="n"/>
-      <c r="Y283" s="7" t="n"/>
-      <c r="Z283" s="7" t="n"/>
-      <c r="AB283" s="7" t="n"/>
-      <c r="AC283" s="7" t="n"/>
-      <c r="AD283" s="7" t="n"/>
-    </row>
-    <row r="284">
-      <c r="T284" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U284" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V284" s="4" t="n">
-        <v>730</v>
-      </c>
-      <c r="X284" s="4" t="n"/>
-      <c r="Y284" s="4" t="n"/>
-      <c r="Z284" s="4" t="n"/>
-      <c r="AB284" s="4" t="n"/>
-      <c r="AC284" s="4" t="n"/>
-      <c r="AD284" s="4" t="n"/>
-    </row>
-    <row r="285">
-      <c r="T285" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U285" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V285" s="7" t="n">
-        <v>740</v>
-      </c>
-      <c r="X285" s="7" t="n"/>
-      <c r="Y285" s="7" t="n"/>
-      <c r="Z285" s="7" t="n"/>
-      <c r="AB285" s="7" t="n"/>
-      <c r="AC285" s="7" t="n"/>
-      <c r="AD285" s="7" t="n"/>
-    </row>
-    <row r="286">
-      <c r="T286" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U286" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V286" s="4" t="n">
-        <v>708</v>
-      </c>
-      <c r="X286" s="4" t="n"/>
-      <c r="Y286" s="4" t="n"/>
-      <c r="Z286" s="4" t="n"/>
-      <c r="AB286" s="4" t="n"/>
-      <c r="AC286" s="4" t="n"/>
-      <c r="AD286" s="4" t="n"/>
-    </row>
-    <row r="287">
-      <c r="T287" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U287" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V287" s="7" t="n">
-        <v>698</v>
-      </c>
-      <c r="X287" s="7" t="n"/>
-      <c r="Y287" s="7" t="n"/>
-      <c r="Z287" s="7" t="n"/>
-      <c r="AB287" s="7" t="n"/>
-      <c r="AC287" s="7" t="n"/>
-      <c r="AD287" s="7" t="n"/>
-    </row>
-    <row r="288">
-      <c r="T288" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U288" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V288" s="4" t="n">
-        <v>691</v>
-      </c>
-      <c r="X288" s="4" t="n"/>
-      <c r="Y288" s="4" t="n"/>
-      <c r="Z288" s="4" t="n"/>
-      <c r="AB288" s="4" t="n"/>
-      <c r="AC288" s="4" t="n"/>
-      <c r="AD288" s="4" t="n"/>
-    </row>
-    <row r="289">
-      <c r="T289" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U289" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V289" s="7" t="n">
-        <v>695</v>
-      </c>
-      <c r="X289" s="7" t="n"/>
-      <c r="Y289" s="7" t="n"/>
-      <c r="Z289" s="7" t="n"/>
-      <c r="AB289" s="7" t="n"/>
-      <c r="AC289" s="7" t="n"/>
-      <c r="AD289" s="7" t="n"/>
-    </row>
-    <row r="290">
-      <c r="T290" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U290" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V290" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X290" s="4" t="n"/>
-      <c r="Y290" s="4" t="n"/>
-      <c r="Z290" s="4" t="n"/>
-      <c r="AB290" s="4" t="n"/>
-      <c r="AC290" s="4" t="n"/>
-      <c r="AD290" s="4" t="n"/>
-    </row>
-    <row r="291">
-      <c r="T291" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U291" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V291" s="7" t="n">
-        <v>701</v>
-      </c>
-      <c r="X291" s="7" t="n"/>
-      <c r="Y291" s="7" t="n"/>
-      <c r="Z291" s="7" t="n"/>
-      <c r="AB291" s="7" t="n"/>
-      <c r="AC291" s="7" t="n"/>
-      <c r="AD291" s="7" t="n"/>
-    </row>
-    <row r="292">
-      <c r="T292" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U292" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V292" s="4" t="n">
-        <v>706</v>
-      </c>
-      <c r="X292" s="4" t="n"/>
-      <c r="Y292" s="4" t="n"/>
-      <c r="Z292" s="4" t="n"/>
-      <c r="AB292" s="4" t="n"/>
-      <c r="AC292" s="4" t="n"/>
-      <c r="AD292" s="4" t="n"/>
-    </row>
-    <row r="293">
-      <c r="T293" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U293" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V293" s="7" t="n">
-        <v>704</v>
-      </c>
-      <c r="X293" s="7" t="n"/>
-      <c r="Y293" s="7" t="n"/>
-      <c r="Z293" s="7" t="n"/>
-      <c r="AB293" s="7" t="n"/>
-      <c r="AC293" s="7" t="n"/>
-      <c r="AD293" s="7" t="n"/>
-    </row>
-    <row r="294">
-      <c r="T294" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U294" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V294" s="4" t="n">
-        <v>670</v>
-      </c>
-      <c r="X294" s="4" t="n"/>
-      <c r="Y294" s="4" t="n"/>
-      <c r="Z294" s="4" t="n"/>
-      <c r="AB294" s="4" t="n"/>
-      <c r="AC294" s="4" t="n"/>
-      <c r="AD294" s="4" t="n"/>
-    </row>
-    <row r="295">
-      <c r="T295" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U295" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V295" s="7" t="n">
-        <v>694</v>
-      </c>
-      <c r="X295" s="7" t="n"/>
-      <c r="Y295" s="7" t="n"/>
-      <c r="Z295" s="7" t="n"/>
-      <c r="AB295" s="7" t="n"/>
-      <c r="AC295" s="7" t="n"/>
-      <c r="AD295" s="7" t="n"/>
-    </row>
-    <row r="296">
-      <c r="T296" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U296" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V296" s="4" t="n">
-        <v>702</v>
-      </c>
-      <c r="X296" s="4" t="n"/>
-      <c r="Y296" s="4" t="n"/>
-      <c r="Z296" s="4" t="n"/>
-      <c r="AB296" s="4" t="n"/>
-      <c r="AC296" s="4" t="n"/>
-      <c r="AD296" s="4" t="n"/>
-    </row>
-    <row r="297">
-      <c r="T297" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U297" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V297" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="X297" s="7" t="n"/>
-      <c r="Y297" s="7" t="n"/>
-      <c r="Z297" s="7" t="n"/>
-      <c r="AB297" s="7" t="n"/>
-      <c r="AC297" s="7" t="n"/>
-      <c r="AD297" s="7" t="n"/>
-    </row>
-    <row r="298">
-      <c r="T298" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U298" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V298" s="4" t="n">
-        <v>669</v>
-      </c>
-      <c r="X298" s="4" t="n"/>
-      <c r="Y298" s="4" t="n"/>
-      <c r="Z298" s="4" t="n"/>
-      <c r="AB298" s="4" t="n"/>
-      <c r="AC298" s="4" t="n"/>
-      <c r="AD298" s="4" t="n"/>
-    </row>
-    <row r="299">
-      <c r="T299" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U299" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V299" s="7" t="n">
-        <v>2188</v>
-      </c>
-      <c r="X299" s="7" t="n"/>
-      <c r="Y299" s="7" t="n"/>
-      <c r="Z299" s="7" t="n"/>
-      <c r="AB299" s="7" t="n"/>
-      <c r="AC299" s="7" t="n"/>
-      <c r="AD299" s="7" t="n"/>
-    </row>
-    <row r="300">
-      <c r="T300" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U300" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V300" s="4" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X300" s="4" t="n"/>
-      <c r="Y300" s="4" t="n"/>
-      <c r="Z300" s="4" t="n"/>
-      <c r="AB300" s="4" t="n"/>
-      <c r="AC300" s="4" t="n"/>
-      <c r="AD300" s="4" t="n"/>
-    </row>
-    <row r="301">
-      <c r="T301" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U301" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V301" s="7" t="n">
-        <v>2338</v>
-      </c>
-      <c r="X301" s="7" t="n"/>
-      <c r="Y301" s="7" t="n"/>
-      <c r="Z301" s="7" t="n"/>
-      <c r="AB301" s="7" t="n"/>
-      <c r="AC301" s="7" t="n"/>
-      <c r="AD301" s="7" t="n"/>
-    </row>
-    <row r="302">
-      <c r="T302" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="U302" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V302" s="4" t="n">
-        <v>2152</v>
-      </c>
-      <c r="X302" s="4" t="n"/>
-      <c r="Y302" s="4" t="n"/>
-      <c r="Z302" s="4" t="n"/>
-      <c r="AB302" s="4" t="n"/>
-      <c r="AC302" s="4" t="n"/>
-      <c r="AD302" s="4" t="n"/>
-    </row>
-    <row r="303">
-      <c r="T303" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="U303" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V303" s="7" t="n">
-        <v>2003</v>
-      </c>
-      <c r="X303" s="7" t="n"/>
-      <c r="Y303" s="7" t="n"/>
-      <c r="Z303" s="7" t="n"/>
-      <c r="AB303" s="7" t="n"/>
-      <c r="AC303" s="7" t="n"/>
-      <c r="AD303" s="7" t="n"/>
-    </row>
-    <row r="304">
-      <c r="T304" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="U304" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V304" s="4" t="n">
-        <v>1895</v>
-      </c>
-      <c r="X304" s="4" t="n"/>
-      <c r="Y304" s="4" t="n"/>
-      <c r="Z304" s="4" t="n"/>
-      <c r="AB304" s="4" t="n"/>
-      <c r="AC304" s="4" t="n"/>
-      <c r="AD304" s="4" t="n"/>
-    </row>
-    <row r="305">
-      <c r="T305" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U305" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V305" s="7" t="n">
-        <v>1935</v>
-      </c>
-      <c r="X305" s="7" t="n"/>
-      <c r="Y305" s="7" t="n"/>
-      <c r="Z305" s="7" t="n"/>
-      <c r="AB305" s="7" t="n"/>
-      <c r="AC305" s="7" t="n"/>
-      <c r="AD305" s="7" t="n"/>
-    </row>
-    <row r="306">
-      <c r="T306" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="U306" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V306" s="4" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X306" s="4" t="n"/>
-      <c r="Y306" s="4" t="n"/>
-      <c r="Z306" s="4" t="n"/>
-      <c r="AB306" s="4" t="n"/>
-      <c r="AC306" s="4" t="n"/>
-      <c r="AD306" s="4" t="n"/>
-    </row>
-    <row r="307">
-      <c r="T307" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="U307" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V307" s="7" t="n">
-        <v>2049</v>
-      </c>
-      <c r="X307" s="7" t="n"/>
-      <c r="Y307" s="7" t="n"/>
-      <c r="Z307" s="7" t="n"/>
-      <c r="AB307" s="7" t="n"/>
-      <c r="AC307" s="7" t="n"/>
-      <c r="AD307" s="7" t="n"/>
-    </row>
-    <row r="308">
-      <c r="T308" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="U308" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V308" s="4" t="n">
-        <v>2325</v>
-      </c>
-      <c r="X308" s="4" t="n"/>
-      <c r="Y308" s="4" t="n"/>
-      <c r="Z308" s="4" t="n"/>
-      <c r="AB308" s="4" t="n"/>
-      <c r="AC308" s="4" t="n"/>
-      <c r="AD308" s="4" t="n"/>
-    </row>
-    <row r="309">
-      <c r="T309" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="U309" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V309" s="7" t="n">
-        <v>2216</v>
-      </c>
-      <c r="X309" s="7" t="n"/>
-      <c r="Y309" s="7" t="n"/>
-      <c r="Z309" s="7" t="n"/>
-      <c r="AB309" s="7" t="n"/>
-      <c r="AC309" s="7" t="n"/>
-      <c r="AD309" s="7" t="n"/>
-    </row>
-    <row r="310">
-      <c r="T310" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="U310" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V310" s="4" t="n">
-        <v>2037</v>
-      </c>
-      <c r="X310" s="4" t="n"/>
-      <c r="Y310" s="4" t="n"/>
-      <c r="Z310" s="4" t="n"/>
-      <c r="AB310" s="4" t="n"/>
-      <c r="AC310" s="4" t="n"/>
-      <c r="AD310" s="4" t="n"/>
-    </row>
-    <row r="311">
-      <c r="T311" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U311" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V311" s="7" t="n">
-        <v>2046</v>
-      </c>
-      <c r="X311" s="7" t="n"/>
-      <c r="Y311" s="7" t="n"/>
-      <c r="Z311" s="7" t="n"/>
-      <c r="AB311" s="7" t="n"/>
-      <c r="AC311" s="7" t="n"/>
-      <c r="AD311" s="7" t="n"/>
-    </row>
-    <row r="312">
-      <c r="T312" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="U312" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V312" s="4" t="n">
-        <v>2035</v>
-      </c>
-      <c r="X312" s="4" t="n"/>
-      <c r="Y312" s="4" t="n"/>
-      <c r="Z312" s="4" t="n"/>
-      <c r="AB312" s="4" t="n"/>
-      <c r="AC312" s="4" t="n"/>
-      <c r="AD312" s="4" t="n"/>
-    </row>
-    <row r="313">
-      <c r="T313" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="U313" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V313" s="7" t="n">
-        <v>2182</v>
-      </c>
-      <c r="X313" s="7" t="n"/>
-      <c r="Y313" s="7" t="n"/>
-      <c r="Z313" s="7" t="n"/>
-      <c r="AB313" s="7" t="n"/>
-      <c r="AC313" s="7" t="n"/>
-      <c r="AD313" s="7" t="n"/>
-    </row>
-    <row r="314">
-      <c r="T314" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="U314" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V314" s="4" t="n">
-        <v>2156</v>
-      </c>
-      <c r="X314" s="4" t="n"/>
-      <c r="Y314" s="4" t="n"/>
-      <c r="Z314" s="4" t="n"/>
-      <c r="AB314" s="4" t="n"/>
-      <c r="AC314" s="4" t="n"/>
-      <c r="AD314" s="4" t="n"/>
-    </row>
-    <row r="315">
-      <c r="T315" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="U315" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V315" s="7" t="n">
-        <v>2437</v>
-      </c>
-      <c r="X315" s="7" t="n"/>
-      <c r="Y315" s="7" t="n"/>
-      <c r="Z315" s="7" t="n"/>
-      <c r="AB315" s="7" t="n"/>
-      <c r="AC315" s="7" t="n"/>
-      <c r="AD315" s="7" t="n"/>
-    </row>
-    <row r="316">
-      <c r="T316" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="U316" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V316" s="4" t="n">
-        <v>2214</v>
-      </c>
-      <c r="X316" s="4" t="n"/>
-      <c r="Y316" s="4" t="n"/>
-      <c r="Z316" s="4" t="n"/>
-      <c r="AB316" s="4" t="n"/>
-      <c r="AC316" s="4" t="n"/>
-      <c r="AD316" s="4" t="n"/>
-    </row>
-    <row r="317">
-      <c r="T317" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U317" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V317" s="7" t="n">
-        <v>2200</v>
-      </c>
-      <c r="X317" s="7" t="n"/>
-      <c r="Y317" s="7" t="n"/>
-      <c r="Z317" s="7" t="n"/>
-      <c r="AB317" s="7" t="n"/>
-      <c r="AC317" s="7" t="n"/>
-      <c r="AD317" s="7" t="n"/>
-    </row>
-    <row r="318">
-      <c r="T318" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U318" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V318" s="4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="X318" s="4" t="n"/>
-      <c r="Y318" s="4" t="n"/>
-      <c r="Z318" s="4" t="n"/>
-      <c r="AB318" s="4" t="n"/>
-      <c r="AC318" s="4" t="n"/>
-      <c r="AD318" s="4" t="n"/>
-    </row>
-    <row r="319">
-      <c r="T319" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U319" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V319" s="7" t="n">
-        <v>1980</v>
-      </c>
-      <c r="X319" s="7" t="n"/>
-      <c r="Y319" s="7" t="n"/>
-      <c r="Z319" s="7" t="n"/>
-      <c r="AB319" s="7" t="n"/>
-      <c r="AC319" s="7" t="n"/>
-      <c r="AD319" s="7" t="n"/>
-    </row>
-    <row r="320">
-      <c r="T320" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U320" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V320" s="4" t="n">
-        <v>2075</v>
-      </c>
-      <c r="X320" s="4" t="n"/>
-      <c r="Y320" s="4" t="n"/>
-      <c r="Z320" s="4" t="n"/>
-      <c r="AB320" s="4" t="n"/>
-      <c r="AC320" s="4" t="n"/>
-      <c r="AD320" s="4" t="n"/>
-    </row>
-    <row r="321">
-      <c r="T321" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="U321" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V321" s="7" t="n">
-        <v>2191</v>
-      </c>
-      <c r="X321" s="7" t="n"/>
-      <c r="Y321" s="7" t="n"/>
-      <c r="Z321" s="7" t="n"/>
-      <c r="AB321" s="7" t="n"/>
-      <c r="AC321" s="7" t="n"/>
-      <c r="AD321" s="7" t="n"/>
-    </row>
-    <row r="322">
-      <c r="T322" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="U322" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V322" s="4" t="n">
-        <v>2328</v>
-      </c>
-      <c r="X322" s="4" t="n"/>
-      <c r="Y322" s="4" t="n"/>
-      <c r="Z322" s="4" t="n"/>
-      <c r="AB322" s="4" t="n"/>
-      <c r="AC322" s="4" t="n"/>
-      <c r="AD322" s="4" t="n"/>
-    </row>
-    <row r="323">
-      <c r="T323" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="U323" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V323" s="7" t="n">
-        <v>2131</v>
-      </c>
-      <c r="X323" s="7" t="n"/>
-      <c r="Y323" s="7" t="n"/>
-      <c r="Z323" s="7" t="n"/>
-      <c r="AB323" s="7" t="n"/>
-      <c r="AC323" s="7" t="n"/>
-      <c r="AD323" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD227"/>
+  <dimension ref="A1:AD237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3172,17 +3172,41 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
+      <c r="D27" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C27)</f>
+        <v/>
+      </c>
       <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="G27" s="7">
+        <f>ROUND((1-E27/IF(D27&gt;0,D27,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
+        <v/>
+      </c>
+      <c r="H27" s="7">
+        <f>MIN(1,(G27-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
+      <c r="K27" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="7">
+        <f>ROUND(100*(1-K27/IF(D27&gt;0,D27,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
+        <v/>
+      </c>
+      <c r="M27" s="7">
+        <f>MAX(0,(L27-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N27" s="7">
+        <f>$B$2+H27+M27</f>
+        <v/>
+      </c>
       <c r="T27" s="7" t="n"/>
       <c r="U27" s="7" t="n"/>
       <c r="V27" s="7" t="n"/>
@@ -3469,7 +3493,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D26)</f>
+        <f>AVERAGE(D2:D27)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3479,7 +3503,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H26)</f>
+        <f>AVERAGE(H2:H27)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -8557,7 +8581,7 @@
       <c r="U196" s="4" t="n"/>
       <c r="V196" s="4" t="n"/>
       <c r="X196" s="4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y196" s="4" t="inlineStr">
         <is>
@@ -8835,9 +8859,19 @@
       <c r="T205" s="7" t="n"/>
       <c r="U205" s="7" t="n"/>
       <c r="V205" s="7" t="n"/>
-      <c r="X205" s="7" t="n"/>
-      <c r="Y205" s="7" t="n"/>
-      <c r="Z205" s="7" t="n"/>
+      <c r="X205" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y205" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z205" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB205" s="7" t="n">
         <v>51</v>
       </c>
@@ -8856,9 +8890,19 @@
       <c r="T206" s="4" t="n"/>
       <c r="U206" s="4" t="n"/>
       <c r="V206" s="4" t="n"/>
-      <c r="X206" s="4" t="n"/>
-      <c r="Y206" s="4" t="n"/>
-      <c r="Z206" s="4" t="n"/>
+      <c r="X206" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y206" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z206" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB206" s="4" t="n">
         <v>127</v>
       </c>
@@ -8877,9 +8921,19 @@
       <c r="T207" s="7" t="n"/>
       <c r="U207" s="7" t="n"/>
       <c r="V207" s="7" t="n"/>
-      <c r="X207" s="7" t="n"/>
-      <c r="Y207" s="7" t="n"/>
-      <c r="Z207" s="7" t="n"/>
+      <c r="X207" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y207" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z207" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB207" s="7" t="n">
         <v>2</v>
       </c>
@@ -8898,9 +8952,19 @@
       <c r="T208" s="4" t="n"/>
       <c r="U208" s="4" t="n"/>
       <c r="V208" s="4" t="n"/>
-      <c r="X208" s="4" t="n"/>
-      <c r="Y208" s="4" t="n"/>
-      <c r="Z208" s="4" t="n"/>
+      <c r="X208" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y208" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z208" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB208" s="4" t="n">
         <v>11</v>
       </c>
@@ -8919,9 +8983,19 @@
       <c r="T209" s="7" t="n"/>
       <c r="U209" s="7" t="n"/>
       <c r="V209" s="7" t="n"/>
-      <c r="X209" s="7" t="n"/>
-      <c r="Y209" s="7" t="n"/>
-      <c r="Z209" s="7" t="n"/>
+      <c r="X209" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y209" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z209" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB209" s="7" t="n">
         <v>3</v>
       </c>
@@ -8940,9 +9014,19 @@
       <c r="T210" s="4" t="n"/>
       <c r="U210" s="4" t="n"/>
       <c r="V210" s="4" t="n"/>
-      <c r="X210" s="4" t="n"/>
-      <c r="Y210" s="4" t="n"/>
-      <c r="Z210" s="4" t="n"/>
+      <c r="X210" s="4" t="n">
+        <v>541</v>
+      </c>
+      <c r="Y210" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z210" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB210" s="4" t="n">
         <v>351</v>
       </c>
@@ -8961,9 +9045,19 @@
       <c r="T211" s="7" t="n"/>
       <c r="U211" s="7" t="n"/>
       <c r="V211" s="7" t="n"/>
-      <c r="X211" s="7" t="n"/>
-      <c r="Y211" s="7" t="n"/>
-      <c r="Z211" s="7" t="n"/>
+      <c r="X211" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y211" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z211" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB211" s="7" t="n">
         <v>37</v>
       </c>
@@ -8982,9 +9076,19 @@
       <c r="T212" s="4" t="n"/>
       <c r="U212" s="4" t="n"/>
       <c r="V212" s="4" t="n"/>
-      <c r="X212" s="4" t="n"/>
-      <c r="Y212" s="4" t="n"/>
-      <c r="Z212" s="4" t="n"/>
+      <c r="X212" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y212" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z212" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB212" s="4" t="n">
         <v>152</v>
       </c>
@@ -9314,6 +9418,216 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="T228" s="4" t="n"/>
+      <c r="U228" s="4" t="n"/>
+      <c r="V228" s="4" t="n"/>
+      <c r="X228" s="4" t="n"/>
+      <c r="Y228" s="4" t="n"/>
+      <c r="Z228" s="4" t="n"/>
+      <c r="AB228" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="AC228" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD228" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="T229" s="7" t="n"/>
+      <c r="U229" s="7" t="n"/>
+      <c r="V229" s="7" t="n"/>
+      <c r="X229" s="7" t="n"/>
+      <c r="Y229" s="7" t="n"/>
+      <c r="Z229" s="7" t="n"/>
+      <c r="AB229" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC229" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD229" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="T230" s="4" t="n"/>
+      <c r="U230" s="4" t="n"/>
+      <c r="V230" s="4" t="n"/>
+      <c r="X230" s="4" t="n"/>
+      <c r="Y230" s="4" t="n"/>
+      <c r="Z230" s="4" t="n"/>
+      <c r="AB230" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="AC230" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD230" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="T231" s="7" t="n"/>
+      <c r="U231" s="7" t="n"/>
+      <c r="V231" s="7" t="n"/>
+      <c r="X231" s="7" t="n"/>
+      <c r="Y231" s="7" t="n"/>
+      <c r="Z231" s="7" t="n"/>
+      <c r="AB231" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC231" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD231" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="T232" s="4" t="n"/>
+      <c r="U232" s="4" t="n"/>
+      <c r="V232" s="4" t="n"/>
+      <c r="X232" s="4" t="n"/>
+      <c r="Y232" s="4" t="n"/>
+      <c r="Z232" s="4" t="n"/>
+      <c r="AB232" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC232" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD232" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="T233" s="7" t="n"/>
+      <c r="U233" s="7" t="n"/>
+      <c r="V233" s="7" t="n"/>
+      <c r="X233" s="7" t="n"/>
+      <c r="Y233" s="7" t="n"/>
+      <c r="Z233" s="7" t="n"/>
+      <c r="AB233" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC233" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD233" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="T234" s="4" t="n"/>
+      <c r="U234" s="4" t="n"/>
+      <c r="V234" s="4" t="n"/>
+      <c r="X234" s="4" t="n"/>
+      <c r="Y234" s="4" t="n"/>
+      <c r="Z234" s="4" t="n"/>
+      <c r="AB234" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="AC234" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD234" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="T235" s="7" t="n"/>
+      <c r="U235" s="7" t="n"/>
+      <c r="V235" s="7" t="n"/>
+      <c r="X235" s="7" t="n"/>
+      <c r="Y235" s="7" t="n"/>
+      <c r="Z235" s="7" t="n"/>
+      <c r="AB235" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC235" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD235" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="T236" s="4" t="n"/>
+      <c r="U236" s="4" t="n"/>
+      <c r="V236" s="4" t="n"/>
+      <c r="X236" s="4" t="n"/>
+      <c r="Y236" s="4" t="n"/>
+      <c r="Z236" s="4" t="n"/>
+      <c r="AB236" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC236" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD236" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="T237" s="7" t="n"/>
+      <c r="U237" s="7" t="n"/>
+      <c r="V237" s="7" t="n"/>
+      <c r="X237" s="7" t="n"/>
+      <c r="Y237" s="7" t="n"/>
+      <c r="Z237" s="7" t="n"/>
+      <c r="AB237" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC237" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD237" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD237"/>
+  <dimension ref="A1:AD246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3245,17 +3245,41 @@
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
+      <c r="D28" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C28)</f>
+        <v/>
+      </c>
       <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
+      <c r="G28" s="4">
+        <f>ROUND((1-E28/IF(D28&gt;0,D28,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
+        <v/>
+      </c>
+      <c r="H28" s="4">
+        <f>MIN(1,(G28-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
+      <c r="K28" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="4">
+        <f>ROUND(100*(1-K28/IF(D28&gt;0,D28,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
+        <v/>
+      </c>
+      <c r="M28" s="4">
+        <f>MAX(0,(L28-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N28" s="4">
+        <f>$B$2+H28+M28</f>
+        <v/>
+      </c>
       <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
@@ -3493,7 +3517,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D27)</f>
+        <f>AVERAGE(D2:D28)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3503,7 +3527,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H27)</f>
+        <f>AVERAGE(H2:H28)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -9015,7 +9039,7 @@
       <c r="U210" s="4" t="n"/>
       <c r="V210" s="4" t="n"/>
       <c r="X210" s="4" t="n">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="Y210" s="4" t="inlineStr">
         <is>
@@ -9107,9 +9131,19 @@
       <c r="T213" s="7" t="n"/>
       <c r="U213" s="7" t="n"/>
       <c r="V213" s="7" t="n"/>
-      <c r="X213" s="7" t="n"/>
-      <c r="Y213" s="7" t="n"/>
-      <c r="Z213" s="7" t="n"/>
+      <c r="X213" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="Y213" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z213" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB213" s="7" t="n">
         <v>59</v>
       </c>
@@ -9128,9 +9162,19 @@
       <c r="T214" s="4" t="n"/>
       <c r="U214" s="4" t="n"/>
       <c r="V214" s="4" t="n"/>
-      <c r="X214" s="4" t="n"/>
-      <c r="Y214" s="4" t="n"/>
-      <c r="Z214" s="4" t="n"/>
+      <c r="X214" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y214" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z214" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB214" s="4" t="n">
         <v>47</v>
       </c>
@@ -9149,9 +9193,19 @@
       <c r="T215" s="7" t="n"/>
       <c r="U215" s="7" t="n"/>
       <c r="V215" s="7" t="n"/>
-      <c r="X215" s="7" t="n"/>
-      <c r="Y215" s="7" t="n"/>
-      <c r="Z215" s="7" t="n"/>
+      <c r="X215" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y215" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z215" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB215" s="7" t="n">
         <v>149</v>
       </c>
@@ -9170,9 +9224,19 @@
       <c r="T216" s="4" t="n"/>
       <c r="U216" s="4" t="n"/>
       <c r="V216" s="4" t="n"/>
-      <c r="X216" s="4" t="n"/>
-      <c r="Y216" s="4" t="n"/>
-      <c r="Z216" s="4" t="n"/>
+      <c r="X216" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y216" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z216" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB216" s="4" t="n">
         <v>4</v>
       </c>
@@ -9191,9 +9255,19 @@
       <c r="T217" s="7" t="n"/>
       <c r="U217" s="7" t="n"/>
       <c r="V217" s="7" t="n"/>
-      <c r="X217" s="7" t="n"/>
-      <c r="Y217" s="7" t="n"/>
-      <c r="Z217" s="7" t="n"/>
+      <c r="X217" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y217" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z217" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB217" s="7" t="n">
         <v>2</v>
       </c>
@@ -9212,9 +9286,19 @@
       <c r="T218" s="4" t="n"/>
       <c r="U218" s="4" t="n"/>
       <c r="V218" s="4" t="n"/>
-      <c r="X218" s="4" t="n"/>
-      <c r="Y218" s="4" t="n"/>
-      <c r="Z218" s="4" t="n"/>
+      <c r="X218" s="4" t="n">
+        <v>514</v>
+      </c>
+      <c r="Y218" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z218" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB218" s="4" t="n">
         <v>4</v>
       </c>
@@ -9233,9 +9317,19 @@
       <c r="T219" s="7" t="n"/>
       <c r="U219" s="7" t="n"/>
       <c r="V219" s="7" t="n"/>
-      <c r="X219" s="7" t="n"/>
-      <c r="Y219" s="7" t="n"/>
-      <c r="Z219" s="7" t="n"/>
+      <c r="X219" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y219" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z219" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB219" s="7" t="n">
         <v>337</v>
       </c>
@@ -9254,9 +9348,19 @@
       <c r="T220" s="4" t="n"/>
       <c r="U220" s="4" t="n"/>
       <c r="V220" s="4" t="n"/>
-      <c r="X220" s="4" t="n"/>
-      <c r="Y220" s="4" t="n"/>
-      <c r="Z220" s="4" t="n"/>
+      <c r="X220" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y220" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z220" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB220" s="4" t="n">
         <v>34</v>
       </c>
@@ -9275,9 +9379,19 @@
       <c r="T221" s="7" t="n"/>
       <c r="U221" s="7" t="n"/>
       <c r="V221" s="7" t="n"/>
-      <c r="X221" s="7" t="n"/>
-      <c r="Y221" s="7" t="n"/>
-      <c r="Z221" s="7" t="n"/>
+      <c r="X221" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y221" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z221" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB221" s="7" t="n">
         <v>141</v>
       </c>
@@ -9628,6 +9742,195 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="T238" s="4" t="n"/>
+      <c r="U238" s="4" t="n"/>
+      <c r="V238" s="4" t="n"/>
+      <c r="X238" s="4" t="n"/>
+      <c r="Y238" s="4" t="n"/>
+      <c r="Z238" s="4" t="n"/>
+      <c r="AB238" s="4" t="n">
+        <v>324</v>
+      </c>
+      <c r="AC238" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD238" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="T239" s="7" t="n"/>
+      <c r="U239" s="7" t="n"/>
+      <c r="V239" s="7" t="n"/>
+      <c r="X239" s="7" t="n"/>
+      <c r="Y239" s="7" t="n"/>
+      <c r="Z239" s="7" t="n"/>
+      <c r="AB239" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC239" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD239" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="T240" s="4" t="n"/>
+      <c r="U240" s="4" t="n"/>
+      <c r="V240" s="4" t="n"/>
+      <c r="X240" s="4" t="n"/>
+      <c r="Y240" s="4" t="n"/>
+      <c r="Z240" s="4" t="n"/>
+      <c r="AB240" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="AC240" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD240" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="T241" s="7" t="n"/>
+      <c r="U241" s="7" t="n"/>
+      <c r="V241" s="7" t="n"/>
+      <c r="X241" s="7" t="n"/>
+      <c r="Y241" s="7" t="n"/>
+      <c r="Z241" s="7" t="n"/>
+      <c r="AB241" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC241" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD241" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="T242" s="4" t="n"/>
+      <c r="U242" s="4" t="n"/>
+      <c r="V242" s="4" t="n"/>
+      <c r="X242" s="4" t="n"/>
+      <c r="Y242" s="4" t="n"/>
+      <c r="Z242" s="4" t="n"/>
+      <c r="AB242" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC242" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD242" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="T243" s="7" t="n"/>
+      <c r="U243" s="7" t="n"/>
+      <c r="V243" s="7" t="n"/>
+      <c r="X243" s="7" t="n"/>
+      <c r="Y243" s="7" t="n"/>
+      <c r="Z243" s="7" t="n"/>
+      <c r="AB243" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="AC243" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD243" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="T244" s="4" t="n"/>
+      <c r="U244" s="4" t="n"/>
+      <c r="V244" s="4" t="n"/>
+      <c r="X244" s="4" t="n"/>
+      <c r="Y244" s="4" t="n"/>
+      <c r="Z244" s="4" t="n"/>
+      <c r="AB244" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC244" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD244" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="T245" s="7" t="n"/>
+      <c r="U245" s="7" t="n"/>
+      <c r="V245" s="7" t="n"/>
+      <c r="X245" s="7" t="n"/>
+      <c r="Y245" s="7" t="n"/>
+      <c r="Z245" s="7" t="n"/>
+      <c r="AB245" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC245" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD245" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="T246" s="4" t="n"/>
+      <c r="U246" s="4" t="n"/>
+      <c r="V246" s="4" t="n"/>
+      <c r="X246" s="4" t="n"/>
+      <c r="Y246" s="4" t="n"/>
+      <c r="Z246" s="4" t="n"/>
+      <c r="AB246" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC246" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD246" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -716,7 +716,7 @@
         <v>0.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.27</v>
@@ -752,7 +752,7 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>1.27</v>
@@ -788,7 +788,7 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>1.27</v>
@@ -824,7 +824,7 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>1.27</v>
@@ -860,7 +860,7 @@
         <v>0.95</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>1.27</v>
@@ -896,7 +896,7 @@
         <v>0.95</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>1.27</v>
@@ -932,7 +932,7 @@
         <v>0.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>1.27</v>
@@ -968,7 +968,7 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1.27</v>
@@ -1004,7 +1004,7 @@
         <v>0.95</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>1.27</v>
@@ -1040,7 +1040,7 @@
         <v>0.95</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>1.27</v>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD323"/>
+  <dimension ref="A1:AD362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3322,29 +3322,49 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
+      <c r="D27" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C27)</f>
+        <v/>
+      </c>
       <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="G27" s="7">
+        <f>ROUND((1-E27/IF(D27&gt;0,D27,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
+        <v/>
+      </c>
+      <c r="H27" s="7">
+        <f>MIN(1,(G27-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
+      <c r="K27" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="7">
+        <f>ROUND(100*(1-K27/IF(D27&gt;0,D27,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
+        <v/>
+      </c>
+      <c r="M27" s="7">
+        <f>MAX(0,(L27-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N27" s="7">
+        <f>$B$2+H27+M27</f>
+        <v/>
+      </c>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr"/>
       <c r="V27" s="7" t="n">
-        <v>5365</v>
+        <v>1</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>73</v>
@@ -3381,29 +3401,49 @@
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
+      <c r="D28" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C28)</f>
+        <v/>
+      </c>
       <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
+      <c r="G28" s="4">
+        <f>ROUND((1-E28/IF(D28&gt;0,D28,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
+        <v/>
+      </c>
+      <c r="H28" s="4">
+        <f>MIN(1,(G28-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
+      <c r="K28" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="4">
+        <f>ROUND(100*(1-K28/IF(D28&gt;0,D28,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
+        <v/>
+      </c>
+      <c r="M28" s="4">
+        <f>MAX(0,(L28-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N28" s="4">
+        <f>$B$2+H28+M28</f>
+        <v/>
+      </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr"/>
       <c r="V28" s="4" t="n">
-        <v>5741</v>
+        <v>1</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>31</v>
@@ -3440,29 +3480,49 @@
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
+      <c r="D29" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C29)</f>
+        <v/>
+      </c>
       <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
+      <c r="G29" s="7">
+        <f>ROUND((1-E29/IF(D29&gt;0,D29,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100,2)</f>
+        <v/>
+      </c>
+      <c r="H29" s="7">
+        <f>MIN(1,(G29-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
+      <c r="K29" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="7">
+        <f>ROUND(100*(1-K29/IF(D29&gt;0,D29,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)),2)</f>
+        <v/>
+      </c>
+      <c r="M29" s="7">
+        <f>MAX(0,(L29-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N29" s="7">
+        <f>$B$2+H29+M29</f>
+        <v/>
+      </c>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="U29" s="7" t="inlineStr"/>
       <c r="V29" s="7" t="n">
-        <v>5451</v>
+        <v>1</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>13</v>
@@ -3512,7 +3572,7 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3521,7 +3581,7 @@
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5458</v>
+        <v>5365</v>
       </c>
       <c r="X30" s="4" t="n">
         <v>78</v>
@@ -3571,7 +3631,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -3580,7 +3640,7 @@
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>5664</v>
+        <v>5741</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>1</v>
@@ -3639,7 +3699,7 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3648,7 +3708,7 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5241</v>
+        <v>5451</v>
       </c>
       <c r="X32" s="4" t="n">
         <v>9</v>
@@ -3679,7 +3739,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D26)</f>
+        <f>AVERAGE(D2:D29)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3689,7 +3749,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H26)</f>
+        <f>AVERAGE(H2:H29)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3712,7 +3772,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -3721,7 +3781,7 @@
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>5102</v>
+        <v>5458</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>1</v>
@@ -3753,7 +3813,7 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3762,7 +3822,7 @@
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5388</v>
+        <v>5664</v>
       </c>
       <c r="X34" s="4" t="n">
         <v>119</v>
@@ -3794,7 +3854,7 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -3803,7 +3863,7 @@
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>5339</v>
+        <v>5241</v>
       </c>
       <c r="X35" s="7" t="n">
         <v>13</v>
@@ -3835,7 +3895,7 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
@@ -3844,7 +3904,7 @@
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>5348</v>
+        <v>5102</v>
       </c>
       <c r="X36" s="4" t="n">
         <v>67</v>
@@ -3876,7 +3936,7 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
@@ -3885,7 +3945,7 @@
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>5329</v>
+        <v>5388</v>
       </c>
       <c r="X37" s="7" t="n">
         <v>32</v>
@@ -3917,7 +3977,7 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
@@ -3926,7 +3986,7 @@
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>5436</v>
+        <v>5339</v>
       </c>
       <c r="X38" s="4" t="n">
         <v>13</v>
@@ -3958,7 +4018,7 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
@@ -3967,7 +4027,7 @@
         </is>
       </c>
       <c r="V39" s="7" t="n">
-        <v>5081</v>
+        <v>5348</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>93</v>
@@ -3999,7 +4059,7 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
@@ -4008,7 +4068,7 @@
         </is>
       </c>
       <c r="V40" s="4" t="n">
-        <v>5034</v>
+        <v>5329</v>
       </c>
       <c r="X40" s="4" t="n">
         <v>12</v>
@@ -4040,7 +4100,7 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
@@ -4049,7 +4109,7 @@
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>5557</v>
+        <v>5436</v>
       </c>
       <c r="X41" s="7" t="n">
         <v>2</v>
@@ -4081,7 +4141,7 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
@@ -4090,7 +4150,7 @@
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>5513</v>
+        <v>5081</v>
       </c>
       <c r="X42" s="4" t="n">
         <v>113</v>
@@ -4122,7 +4182,7 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
@@ -4131,7 +4191,7 @@
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>5477</v>
+        <v>5034</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>12</v>
@@ -4163,7 +4223,7 @@
     <row r="44">
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U44" s="4" t="inlineStr">
@@ -4172,7 +4232,7 @@
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>5526</v>
+        <v>5557</v>
       </c>
       <c r="X44" s="4" t="n">
         <v>69</v>
@@ -4204,7 +4264,7 @@
     <row r="45">
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
@@ -4213,7 +4273,7 @@
         </is>
       </c>
       <c r="V45" s="7" t="n">
-        <v>5339</v>
+        <v>5513</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>40</v>
@@ -4245,7 +4305,7 @@
     <row r="46">
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
@@ -4254,7 +4314,7 @@
         </is>
       </c>
       <c r="V46" s="4" t="n">
-        <v>4933</v>
+        <v>5477</v>
       </c>
       <c r="X46" s="4" t="n">
         <v>17</v>
@@ -4286,7 +4346,7 @@
     <row r="47">
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
@@ -4295,7 +4355,7 @@
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>4866</v>
+        <v>5526</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>83</v>
@@ -4327,7 +4387,7 @@
     <row r="48">
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
@@ -4336,7 +4396,7 @@
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>5232</v>
+        <v>5339</v>
       </c>
       <c r="X48" s="4" t="n">
         <v>9</v>
@@ -4368,7 +4428,7 @@
     <row r="49">
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
@@ -4377,7 +4437,7 @@
         </is>
       </c>
       <c r="V49" s="7" t="n">
-        <v>5576</v>
+        <v>4933</v>
       </c>
       <c r="X49" s="7" t="n">
         <v>124</v>
@@ -4409,7 +4469,7 @@
     <row r="50">
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U50" s="4" t="inlineStr">
@@ -4418,7 +4478,7 @@
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>5287</v>
+        <v>4866</v>
       </c>
       <c r="X50" s="4" t="n">
         <v>19</v>
@@ -4450,7 +4510,7 @@
     <row r="51">
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
@@ -4459,7 +4519,7 @@
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>5275</v>
+        <v>5232</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>55</v>
@@ -4491,16 +4551,16 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V52" s="4" t="n">
-        <v>14969</v>
+        <v>5576</v>
       </c>
       <c r="X52" s="4" t="n">
         <v>35</v>
@@ -4532,16 +4592,16 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V53" s="7" t="n">
-        <v>14818</v>
+        <v>5287</v>
       </c>
       <c r="X53" s="7" t="n">
         <v>15</v>
@@ -4573,16 +4633,16 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V54" s="4" t="n">
-        <v>15263</v>
+        <v>5275</v>
       </c>
       <c r="X54" s="4" t="n">
         <v>82</v>
@@ -4614,16 +4674,16 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V55" s="7" t="n">
-        <v>14815</v>
+        <v>5471</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>1</v>
@@ -4655,16 +4715,16 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>14968</v>
+        <v>4993</v>
       </c>
       <c r="X56" s="4" t="n">
         <v>14</v>
@@ -4696,16 +4756,16 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V57" s="7" t="n">
-        <v>14113</v>
+        <v>4964</v>
       </c>
       <c r="X57" s="7" t="n">
         <v>2</v>
@@ -4737,7 +4797,7 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U58" s="4" t="inlineStr">
@@ -4746,7 +4806,7 @@
         </is>
       </c>
       <c r="V58" s="4" t="n">
-        <v>14162</v>
+        <v>14969</v>
       </c>
       <c r="X58" s="4" t="n">
         <v>101</v>
@@ -4778,7 +4838,7 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
@@ -4787,7 +4847,7 @@
         </is>
       </c>
       <c r="V59" s="7" t="n">
-        <v>14815</v>
+        <v>14818</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>10</v>
@@ -4819,7 +4879,7 @@
     <row r="60">
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U60" s="4" t="inlineStr">
@@ -4828,7 +4888,7 @@
         </is>
       </c>
       <c r="V60" s="4" t="n">
-        <v>14815</v>
+        <v>15263</v>
       </c>
       <c r="X60" s="4" t="n">
         <v>72</v>
@@ -4860,7 +4920,7 @@
     <row r="61">
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
@@ -4869,7 +4929,7 @@
         </is>
       </c>
       <c r="V61" s="7" t="n">
-        <v>15546</v>
+        <v>14815</v>
       </c>
       <c r="X61" s="7" t="n">
         <v>35</v>
@@ -4901,7 +4961,7 @@
     <row r="62">
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U62" s="4" t="inlineStr">
@@ -4910,7 +4970,7 @@
         </is>
       </c>
       <c r="V62" s="4" t="n">
-        <v>14882</v>
+        <v>14968</v>
       </c>
       <c r="X62" s="4" t="n">
         <v>13</v>
@@ -4942,7 +5002,7 @@
     <row r="63">
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
@@ -4951,7 +5011,7 @@
         </is>
       </c>
       <c r="V63" s="7" t="n">
-        <v>14998</v>
+        <v>14113</v>
       </c>
       <c r="X63" s="7" t="n">
         <v>71</v>
@@ -4983,7 +5043,7 @@
     <row r="64">
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr">
@@ -4992,7 +5052,7 @@
         </is>
       </c>
       <c r="V64" s="4" t="n">
-        <v>14354</v>
+        <v>14162</v>
       </c>
       <c r="X64" s="4" t="n">
         <v>8</v>
@@ -5024,7 +5084,7 @@
     <row r="65">
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
@@ -5033,7 +5093,7 @@
         </is>
       </c>
       <c r="V65" s="7" t="n">
-        <v>14362</v>
+        <v>14815</v>
       </c>
       <c r="X65" s="7" t="n">
         <v>2</v>
@@ -5065,7 +5125,7 @@
     <row r="66">
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr">
@@ -5074,7 +5134,7 @@
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>15089</v>
+        <v>14815</v>
       </c>
       <c r="X66" s="4" t="n">
         <v>125</v>
@@ -5106,7 +5166,7 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
@@ -5115,7 +5175,7 @@
         </is>
       </c>
       <c r="V67" s="7" t="n">
-        <v>14802</v>
+        <v>15546</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>11</v>
@@ -5147,7 +5207,7 @@
     <row r="68">
       <c r="T68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U68" s="4" t="inlineStr">
@@ -5156,7 +5216,7 @@
         </is>
       </c>
       <c r="V68" s="4" t="n">
-        <v>15349</v>
+        <v>14882</v>
       </c>
       <c r="X68" s="4" t="n">
         <v>67</v>
@@ -5188,7 +5248,7 @@
     <row r="69">
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
@@ -5197,7 +5257,7 @@
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>14872</v>
+        <v>14998</v>
       </c>
       <c r="X69" s="7" t="n">
         <v>27</v>
@@ -5229,7 +5289,7 @@
     <row r="70">
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U70" s="4" t="inlineStr">
@@ -5238,7 +5298,7 @@
         </is>
       </c>
       <c r="V70" s="4" t="n">
-        <v>15054</v>
+        <v>14354</v>
       </c>
       <c r="X70" s="4" t="n">
         <v>17</v>
@@ -5270,7 +5330,7 @@
     <row r="71">
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U71" s="7" t="inlineStr">
@@ -5279,7 +5339,7 @@
         </is>
       </c>
       <c r="V71" s="7" t="n">
-        <v>14169</v>
+        <v>14362</v>
       </c>
       <c r="X71" s="7" t="n">
         <v>85</v>
@@ -5311,7 +5371,7 @@
     <row r="72">
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U72" s="4" t="inlineStr">
@@ -5320,7 +5380,7 @@
         </is>
       </c>
       <c r="V72" s="4" t="n">
-        <v>14056</v>
+        <v>15089</v>
       </c>
       <c r="X72" s="4" t="n">
         <v>14</v>
@@ -5352,7 +5412,7 @@
     <row r="73">
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U73" s="7" t="inlineStr">
@@ -5361,7 +5421,7 @@
         </is>
       </c>
       <c r="V73" s="7" t="n">
-        <v>15058</v>
+        <v>14802</v>
       </c>
       <c r="X73" s="7" t="n">
         <v>4</v>
@@ -5393,7 +5453,7 @@
     <row r="74">
       <c r="T74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U74" s="4" t="inlineStr">
@@ -5402,7 +5462,7 @@
         </is>
       </c>
       <c r="V74" s="4" t="n">
-        <v>14814</v>
+        <v>15349</v>
       </c>
       <c r="X74" s="4" t="n">
         <v>126</v>
@@ -5434,7 +5494,7 @@
     <row r="75">
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U75" s="7" t="inlineStr">
@@ -5443,7 +5503,7 @@
         </is>
       </c>
       <c r="V75" s="7" t="n">
-        <v>15440</v>
+        <v>14872</v>
       </c>
       <c r="X75" s="7" t="n">
         <v>23</v>
@@ -5475,7 +5535,7 @@
     <row r="76">
       <c r="T76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U76" s="4" t="inlineStr">
@@ -5484,7 +5544,7 @@
         </is>
       </c>
       <c r="V76" s="4" t="n">
-        <v>14832</v>
+        <v>15054</v>
       </c>
       <c r="X76" s="4" t="n">
         <v>65</v>
@@ -5516,16 +5576,16 @@
     <row r="77">
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U77" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V77" s="7" t="n">
-        <v>77546</v>
+        <v>14169</v>
       </c>
       <c r="X77" s="7" t="n">
         <v>28</v>
@@ -5557,16 +5617,16 @@
     <row r="78">
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V78" s="4" t="n">
-        <v>77823</v>
+        <v>14056</v>
       </c>
       <c r="X78" s="4" t="n">
         <v>19</v>
@@ -5598,16 +5658,16 @@
     <row r="79">
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U79" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V79" s="7" t="n">
-        <v>81723</v>
+        <v>15058</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>91</v>
@@ -5639,16 +5699,16 @@
     <row r="80">
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U80" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V80" s="4" t="n">
-        <v>78398</v>
+        <v>14814</v>
       </c>
       <c r="X80" s="4" t="n">
         <v>21</v>
@@ -5680,16 +5740,16 @@
     <row r="81">
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U81" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V81" s="7" t="n">
-        <v>78030</v>
+        <v>15440</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>2</v>
@@ -5721,16 +5781,16 @@
     <row r="82">
       <c r="T82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U82" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V82" s="4" t="n">
-        <v>76646</v>
+        <v>14832</v>
       </c>
       <c r="X82" s="4" t="n">
         <v>99</v>
@@ -5762,16 +5822,16 @@
     <row r="83">
       <c r="T83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U83" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V83" s="7" t="n">
-        <v>76742</v>
+        <v>14765</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>12</v>
@@ -5803,16 +5863,16 @@
     <row r="84">
       <c r="T84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U84" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V84" s="4" t="n">
-        <v>79003</v>
+        <v>14027</v>
       </c>
       <c r="X84" s="4" t="n">
         <v>70</v>
@@ -5844,16 +5904,16 @@
     <row r="85">
       <c r="T85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U85" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V85" s="7" t="n">
-        <v>78849</v>
+        <v>14274</v>
       </c>
       <c r="X85" s="7" t="n">
         <v>30</v>
@@ -5885,7 +5945,7 @@
     <row r="86">
       <c r="T86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U86" s="4" t="inlineStr">
@@ -5894,7 +5954,7 @@
         </is>
       </c>
       <c r="V86" s="4" t="n">
-        <v>80667</v>
+        <v>77546</v>
       </c>
       <c r="X86" s="4" t="n">
         <v>15</v>
@@ -5926,7 +5986,7 @@
     <row r="87">
       <c r="T87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U87" s="7" t="inlineStr">
@@ -5935,7 +5995,7 @@
         </is>
       </c>
       <c r="V87" s="7" t="n">
-        <v>78640</v>
+        <v>77823</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>73</v>
@@ -5967,7 +6027,7 @@
     <row r="88">
       <c r="T88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U88" s="4" t="inlineStr">
@@ -5976,7 +6036,7 @@
         </is>
       </c>
       <c r="V88" s="4" t="n">
-        <v>79108</v>
+        <v>81723</v>
       </c>
       <c r="X88" s="4" t="n">
         <v>5</v>
@@ -6008,7 +6068,7 @@
     <row r="89">
       <c r="T89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U89" s="7" t="inlineStr">
@@ -6017,7 +6077,7 @@
         </is>
       </c>
       <c r="V89" s="7" t="n">
-        <v>76911</v>
+        <v>78398</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>1</v>
@@ -6049,7 +6109,7 @@
     <row r="90">
       <c r="T90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U90" s="4" t="inlineStr">
@@ -6058,7 +6118,7 @@
         </is>
       </c>
       <c r="V90" s="4" t="n">
-        <v>77273</v>
+        <v>78030</v>
       </c>
       <c r="X90" s="4" t="n">
         <v>107</v>
@@ -6090,7 +6150,7 @@
     <row r="91">
       <c r="T91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U91" s="7" t="inlineStr">
@@ -6099,7 +6159,7 @@
         </is>
       </c>
       <c r="V91" s="7" t="n">
-        <v>80657</v>
+        <v>76646</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>13</v>
@@ -6131,7 +6191,7 @@
     <row r="92">
       <c r="T92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U92" s="4" t="inlineStr">
@@ -6140,7 +6200,7 @@
         </is>
       </c>
       <c r="V92" s="4" t="n">
-        <v>79898</v>
+        <v>76742</v>
       </c>
       <c r="X92" s="4" t="n">
         <v>56</v>
@@ -6172,7 +6232,7 @@
     <row r="93">
       <c r="T93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U93" s="7" t="inlineStr">
@@ -6181,7 +6241,7 @@
         </is>
       </c>
       <c r="V93" s="7" t="n">
-        <v>82443</v>
+        <v>79003</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>32</v>
@@ -6213,7 +6273,7 @@
     <row r="94">
       <c r="T94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U94" s="4" t="inlineStr">
@@ -6222,7 +6282,7 @@
         </is>
       </c>
       <c r="V94" s="4" t="n">
-        <v>80658</v>
+        <v>78849</v>
       </c>
       <c r="X94" s="4" t="n">
         <v>13</v>
@@ -6254,7 +6314,7 @@
     <row r="95">
       <c r="T95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U95" s="7" t="inlineStr">
@@ -6263,7 +6323,7 @@
         </is>
       </c>
       <c r="V95" s="7" t="n">
-        <v>78475</v>
+        <v>80667</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>78</v>
@@ -6295,7 +6355,7 @@
     <row r="96">
       <c r="T96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U96" s="4" t="inlineStr">
@@ -6304,7 +6364,7 @@
         </is>
       </c>
       <c r="V96" s="4" t="n">
-        <v>76874</v>
+        <v>78640</v>
       </c>
       <c r="X96" s="4" t="n">
         <v>10</v>
@@ -6336,7 +6396,7 @@
     <row r="97">
       <c r="T97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U97" s="7" t="inlineStr">
@@ -6345,7 +6405,7 @@
         </is>
       </c>
       <c r="V97" s="7" t="n">
-        <v>77058</v>
+        <v>79108</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>1</v>
@@ -6377,7 +6437,7 @@
     <row r="98">
       <c r="T98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U98" s="4" t="inlineStr">
@@ -6386,7 +6446,7 @@
         </is>
       </c>
       <c r="V98" s="4" t="n">
-        <v>79206</v>
+        <v>76911</v>
       </c>
       <c r="X98" s="4" t="n">
         <v>114</v>
@@ -6418,7 +6478,7 @@
     <row r="99">
       <c r="T99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U99" s="7" t="inlineStr">
@@ -6427,7 +6487,7 @@
         </is>
       </c>
       <c r="V99" s="7" t="n">
-        <v>79070</v>
+        <v>77273</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>15</v>
@@ -6459,7 +6519,7 @@
     <row r="100">
       <c r="T100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U100" s="4" t="inlineStr">
@@ -6468,7 +6528,7 @@
         </is>
       </c>
       <c r="V100" s="4" t="n">
-        <v>81246</v>
+        <v>80657</v>
       </c>
       <c r="X100" s="4" t="n">
         <v>53</v>
@@ -6500,7 +6560,7 @@
     <row r="101">
       <c r="T101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U101" s="7" t="inlineStr">
@@ -6509,7 +6569,7 @@
         </is>
       </c>
       <c r="V101" s="7" t="n">
-        <v>80308</v>
+        <v>79898</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>32</v>
@@ -6541,16 +6601,16 @@
     <row r="102">
       <c r="T102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U102" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V102" s="4" t="n">
-        <v>721</v>
+        <v>82443</v>
       </c>
       <c r="X102" s="4" t="n">
         <v>14</v>
@@ -6582,16 +6642,16 @@
     <row r="103">
       <c r="T103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U103" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V103" s="7" t="n">
-        <v>715</v>
+        <v>80658</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>80</v>
@@ -6623,16 +6683,16 @@
     <row r="104">
       <c r="T104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U104" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V104" s="4" t="n">
-        <v>745</v>
+        <v>78475</v>
       </c>
       <c r="X104" s="4" t="n">
         <v>1</v>
@@ -6664,16 +6724,16 @@
     <row r="105">
       <c r="T105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U105" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V105" s="7" t="n">
-        <v>702</v>
+        <v>76874</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>9</v>
@@ -6705,16 +6765,16 @@
     <row r="106">
       <c r="T106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U106" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V106" s="4" t="n">
-        <v>743</v>
+        <v>77058</v>
       </c>
       <c r="X106" s="4" t="n">
         <v>4</v>
@@ -6746,16 +6806,16 @@
     <row r="107">
       <c r="T107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U107" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V107" s="7" t="n">
-        <v>700</v>
+        <v>79206</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>97</v>
@@ -6787,16 +6847,16 @@
     <row r="108">
       <c r="T108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U108" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V108" s="4" t="n">
-        <v>696</v>
+        <v>79070</v>
       </c>
       <c r="X108" s="4" t="n">
         <v>10</v>
@@ -6828,16 +6888,16 @@
     <row r="109">
       <c r="T109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U109" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V109" s="7" t="n">
-        <v>750</v>
+        <v>81246</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>52</v>
@@ -6869,16 +6929,16 @@
     <row r="110">
       <c r="T110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U110" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V110" s="4" t="n">
-        <v>729</v>
+        <v>80308</v>
       </c>
       <c r="X110" s="4" t="n">
         <v>37</v>
@@ -6910,16 +6970,16 @@
     <row r="111">
       <c r="T111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U111" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V111" s="7" t="n">
-        <v>748</v>
+        <v>78998</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>18</v>
@@ -6951,16 +7011,16 @@
     <row r="112">
       <c r="T112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U112" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V112" s="4" t="n">
-        <v>736</v>
+        <v>77229</v>
       </c>
       <c r="X112" s="4" t="n">
         <v>64</v>
@@ -6992,16 +7052,16 @@
     <row r="113">
       <c r="T113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U113" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V113" s="7" t="n">
-        <v>737</v>
+        <v>78265</v>
       </c>
       <c r="X113" s="7" t="n">
         <v>7</v>
@@ -7033,7 +7093,7 @@
     <row r="114">
       <c r="T114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U114" s="4" t="inlineStr">
@@ -7042,7 +7102,7 @@
         </is>
       </c>
       <c r="V114" s="4" t="n">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="X114" s="4" t="n">
         <v>106</v>
@@ -7074,7 +7134,7 @@
     <row r="115">
       <c r="T115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U115" s="7" t="inlineStr">
@@ -7083,7 +7143,7 @@
         </is>
       </c>
       <c r="V115" s="7" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>14</v>
@@ -7115,7 +7175,7 @@
     <row r="116">
       <c r="T116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U116" s="4" t="inlineStr">
@@ -7124,7 +7184,7 @@
         </is>
       </c>
       <c r="V116" s="4" t="n">
-        <v>786</v>
+        <v>745</v>
       </c>
       <c r="X116" s="4" t="n">
         <v>65</v>
@@ -7156,7 +7216,7 @@
     <row r="117">
       <c r="T117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
@@ -7165,7 +7225,7 @@
         </is>
       </c>
       <c r="V117" s="7" t="n">
-        <v>730</v>
+        <v>702</v>
       </c>
       <c r="X117" s="7" t="n">
         <v>24</v>
@@ -7197,7 +7257,7 @@
     <row r="118">
       <c r="T118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U118" s="4" t="inlineStr">
@@ -7206,7 +7266,7 @@
         </is>
       </c>
       <c r="V118" s="4" t="n">
-        <v>726</v>
+        <v>743</v>
       </c>
       <c r="X118" s="4" t="n">
         <v>14</v>
@@ -7238,7 +7298,7 @@
     <row r="119">
       <c r="T119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U119" s="7" t="inlineStr">
@@ -7247,7 +7307,7 @@
         </is>
       </c>
       <c r="V119" s="7" t="n">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="X119" s="7" t="n">
         <v>66</v>
@@ -7279,7 +7339,7 @@
     <row r="120">
       <c r="T120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U120" s="4" t="inlineStr">
@@ -7288,7 +7348,7 @@
         </is>
       </c>
       <c r="V120" s="4" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="X120" s="4" t="n">
         <v>1</v>
@@ -7320,7 +7380,7 @@
     <row r="121">
       <c r="T121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U121" s="7" t="inlineStr">
@@ -7329,7 +7389,7 @@
         </is>
       </c>
       <c r="V121" s="7" t="n">
-        <v>686</v>
+        <v>750</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>9</v>
@@ -7361,7 +7421,7 @@
     <row r="122">
       <c r="T122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U122" s="4" t="inlineStr">
@@ -7370,7 +7430,7 @@
         </is>
       </c>
       <c r="V122" s="4" t="n">
-        <v>673</v>
+        <v>729</v>
       </c>
       <c r="X122" s="4" t="n">
         <v>116</v>
@@ -7402,7 +7462,7 @@
     <row r="123">
       <c r="T123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U123" s="7" t="inlineStr">
@@ -7411,7 +7471,7 @@
         </is>
       </c>
       <c r="V123" s="7" t="n">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="X123" s="7" t="n">
         <v>17</v>
@@ -7443,7 +7503,7 @@
     <row r="124">
       <c r="T124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U124" s="4" t="inlineStr">
@@ -7452,7 +7512,7 @@
         </is>
       </c>
       <c r="V124" s="4" t="n">
-        <v>717</v>
+        <v>736</v>
       </c>
       <c r="X124" s="4" t="n">
         <v>52</v>
@@ -7484,7 +7544,7 @@
     <row r="125">
       <c r="T125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U125" s="7" t="inlineStr">
@@ -7493,7 +7553,7 @@
         </is>
       </c>
       <c r="V125" s="7" t="n">
-        <v>706</v>
+        <v>737</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>38</v>
@@ -7525,7 +7585,7 @@
     <row r="126">
       <c r="T126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U126" s="4" t="inlineStr">
@@ -7534,7 +7594,7 @@
         </is>
       </c>
       <c r="V126" s="4" t="n">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="X126" s="4" t="n">
         <v>19</v>
@@ -7566,16 +7626,16 @@
     <row r="127">
       <c r="T127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U127" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V127" s="7" t="n">
-        <v>47976</v>
+        <v>713</v>
       </c>
       <c r="X127" s="7" t="n">
         <v>79</v>
@@ -7607,16 +7667,16 @@
     <row r="128">
       <c r="T128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U128" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V128" s="4" t="n">
-        <v>47122</v>
+        <v>786</v>
       </c>
       <c r="X128" s="4" t="n">
         <v>9</v>
@@ -7648,16 +7708,16 @@
     <row r="129">
       <c r="T129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V129" s="7" t="n">
-        <v>47233</v>
+        <v>730</v>
       </c>
       <c r="X129" s="7" t="n">
         <v>1</v>
@@ -7689,16 +7749,16 @@
     <row r="130">
       <c r="T130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U130" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V130" s="4" t="n">
-        <v>48580</v>
+        <v>726</v>
       </c>
       <c r="X130" s="4" t="n">
         <v>134</v>
@@ -7730,16 +7790,16 @@
     <row r="131">
       <c r="T131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U131" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V131" s="7" t="n">
-        <v>47383</v>
+        <v>695</v>
       </c>
       <c r="X131" s="7" t="n">
         <v>22</v>
@@ -7771,16 +7831,16 @@
     <row r="132">
       <c r="T132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U132" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V132" s="4" t="n">
-        <v>46456</v>
+        <v>693</v>
       </c>
       <c r="X132" s="4" t="n">
         <v>65</v>
@@ -7812,16 +7872,16 @@
     <row r="133">
       <c r="T133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U133" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V133" s="7" t="n">
-        <v>46400</v>
+        <v>686</v>
       </c>
       <c r="X133" s="7" t="n">
         <v>29</v>
@@ -7853,16 +7913,16 @@
     <row r="134">
       <c r="T134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U134" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V134" s="4" t="n">
-        <v>47755</v>
+        <v>673</v>
       </c>
       <c r="X134" s="4" t="n">
         <v>12</v>
@@ -7894,16 +7954,16 @@
     <row r="135">
       <c r="T135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U135" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V135" s="7" t="n">
-        <v>47520</v>
+        <v>752</v>
       </c>
       <c r="X135" s="7" t="n">
         <v>82</v>
@@ -7935,16 +7995,16 @@
     <row r="136">
       <c r="T136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U136" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V136" s="4" t="n">
-        <v>47354</v>
+        <v>717</v>
       </c>
       <c r="X136" s="4" t="n">
         <v>1</v>
@@ -7976,16 +8036,16 @@
     <row r="137">
       <c r="T137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U137" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V137" s="7" t="n">
-        <v>49015</v>
+        <v>706</v>
       </c>
       <c r="X137" s="7" t="n">
         <v>7</v>
@@ -8017,16 +8077,16 @@
     <row r="138">
       <c r="T138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U138" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V138" s="4" t="n">
-        <v>48832</v>
+        <v>703</v>
       </c>
       <c r="X138" s="4" t="n">
         <v>1</v>
@@ -8058,16 +8118,16 @@
     <row r="139">
       <c r="T139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U139" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V139" s="7" t="n">
-        <v>46644</v>
+        <v>714</v>
       </c>
       <c r="X139" s="7" t="n">
         <v>107</v>
@@ -8099,16 +8159,16 @@
     <row r="140">
       <c r="T140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U140" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V140" s="4" t="n">
-        <v>46416</v>
+        <v>695</v>
       </c>
       <c r="X140" s="4" t="n">
         <v>24</v>
@@ -8140,16 +8200,16 @@
     <row r="141">
       <c r="T141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V141" s="7" t="n">
-        <v>48419</v>
+        <v>694</v>
       </c>
       <c r="X141" s="7" t="n">
         <v>68</v>
@@ -8181,7 +8241,7 @@
     <row r="142">
       <c r="T142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U142" s="4" t="inlineStr">
@@ -8190,7 +8250,7 @@
         </is>
       </c>
       <c r="V142" s="4" t="n">
-        <v>47500</v>
+        <v>47976</v>
       </c>
       <c r="X142" s="4" t="n">
         <v>18</v>
@@ -8222,7 +8282,7 @@
     <row r="143">
       <c r="T143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U143" s="7" t="inlineStr">
@@ -8231,7 +8291,7 @@
         </is>
       </c>
       <c r="V143" s="7" t="n">
-        <v>47954</v>
+        <v>47122</v>
       </c>
       <c r="X143" s="7" t="n">
         <v>12</v>
@@ -8263,7 +8323,7 @@
     <row r="144">
       <c r="T144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U144" s="4" t="inlineStr">
@@ -8272,7 +8332,7 @@
         </is>
       </c>
       <c r="V144" s="4" t="n">
-        <v>49088</v>
+        <v>47233</v>
       </c>
       <c r="X144" s="4" t="n">
         <v>70</v>
@@ -8304,7 +8364,7 @@
     <row r="145">
       <c r="T145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U145" s="7" t="inlineStr">
@@ -8313,7 +8373,7 @@
         </is>
       </c>
       <c r="V145" s="7" t="n">
-        <v>48111</v>
+        <v>48580</v>
       </c>
       <c r="X145" s="7" t="n">
         <v>2</v>
@@ -8345,7 +8405,7 @@
     <row r="146">
       <c r="T146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U146" s="4" t="inlineStr">
@@ -8354,7 +8414,7 @@
         </is>
       </c>
       <c r="V146" s="4" t="n">
-        <v>46535</v>
+        <v>47383</v>
       </c>
       <c r="X146" s="4" t="n">
         <v>6</v>
@@ -8386,7 +8446,7 @@
     <row r="147">
       <c r="T147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U147" s="7" t="inlineStr">
@@ -8395,7 +8455,7 @@
         </is>
       </c>
       <c r="V147" s="7" t="n">
-        <v>46063</v>
+        <v>46456</v>
       </c>
       <c r="X147" s="7" t="n">
         <v>2</v>
@@ -8427,7 +8487,7 @@
     <row r="148">
       <c r="T148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U148" s="4" t="inlineStr">
@@ -8436,7 +8496,7 @@
         </is>
       </c>
       <c r="V148" s="4" t="n">
-        <v>48085</v>
+        <v>46400</v>
       </c>
       <c r="X148" s="4" t="n">
         <v>115</v>
@@ -8468,7 +8528,7 @@
     <row r="149">
       <c r="T149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U149" s="7" t="inlineStr">
@@ -8477,7 +8537,7 @@
         </is>
       </c>
       <c r="V149" s="7" t="n">
-        <v>47472</v>
+        <v>47755</v>
       </c>
       <c r="X149" s="7" t="n">
         <v>20</v>
@@ -8509,7 +8569,7 @@
     <row r="150">
       <c r="T150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U150" s="4" t="inlineStr">
@@ -8518,7 +8578,7 @@
         </is>
       </c>
       <c r="V150" s="4" t="n">
-        <v>47003</v>
+        <v>47520</v>
       </c>
       <c r="X150" s="4" t="n">
         <v>69</v>
@@ -8550,7 +8610,7 @@
     <row r="151">
       <c r="T151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U151" s="7" t="inlineStr">
@@ -8559,7 +8619,7 @@
         </is>
       </c>
       <c r="V151" s="7" t="n">
-        <v>48466</v>
+        <v>47354</v>
       </c>
       <c r="X151" s="7" t="n">
         <v>41</v>
@@ -8591,16 +8651,16 @@
     <row r="152">
       <c r="T152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U152" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V152" s="4" t="n">
-        <v>1</v>
+        <v>49015</v>
       </c>
       <c r="X152" s="4" t="n">
         <v>5</v>
@@ -8632,16 +8692,16 @@
     <row r="153">
       <c r="T153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U153" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V153" s="7" t="n">
-        <v>1</v>
+        <v>48832</v>
       </c>
       <c r="X153" s="7" t="n">
         <v>95</v>
@@ -8673,16 +8733,16 @@
     <row r="154">
       <c r="T154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U154" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V154" s="4" t="n">
-        <v>1</v>
+        <v>46644</v>
       </c>
       <c r="X154" s="4" t="n">
         <v>1</v>
@@ -8714,16 +8774,16 @@
     <row r="155">
       <c r="T155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U155" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V155" s="7" t="n">
-        <v>1</v>
+        <v>46416</v>
       </c>
       <c r="X155" s="7" t="n">
         <v>9</v>
@@ -8755,16 +8815,16 @@
     <row r="156">
       <c r="T156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U156" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V156" s="4" t="n">
-        <v>1</v>
+        <v>48419</v>
       </c>
       <c r="X156" s="4" t="n">
         <v>2</v>
@@ -8796,16 +8856,16 @@
     <row r="157">
       <c r="T157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U157" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V157" s="7" t="n">
-        <v>1</v>
+        <v>47500</v>
       </c>
       <c r="X157" s="7" t="n">
         <v>114</v>
@@ -8837,16 +8897,16 @@
     <row r="158">
       <c r="T158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U158" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V158" s="4" t="n">
-        <v>1</v>
+        <v>47954</v>
       </c>
       <c r="X158" s="4" t="n">
         <v>16</v>
@@ -8878,16 +8938,16 @@
     <row r="159">
       <c r="T159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U159" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V159" s="7" t="n">
-        <v>1</v>
+        <v>49088</v>
       </c>
       <c r="X159" s="7" t="n">
         <v>60</v>
@@ -8919,16 +8979,16 @@
     <row r="160">
       <c r="T160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U160" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V160" s="4" t="n">
-        <v>1</v>
+        <v>48111</v>
       </c>
       <c r="X160" s="4" t="n">
         <v>41</v>
@@ -8960,16 +9020,16 @@
     <row r="161">
       <c r="T161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U161" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V161" s="7" t="n">
-        <v>1</v>
+        <v>46535</v>
       </c>
       <c r="X161" s="7" t="n">
         <v>14</v>
@@ -9001,16 +9061,16 @@
     <row r="162">
       <c r="T162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U162" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V162" s="4" t="n">
-        <v>1</v>
+        <v>46063</v>
       </c>
       <c r="X162" s="4" t="n">
         <v>84</v>
@@ -9042,16 +9102,16 @@
     <row r="163">
       <c r="T163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U163" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V163" s="7" t="n">
-        <v>1</v>
+        <v>48085</v>
       </c>
       <c r="X163" s="7" t="n">
         <v>8</v>
@@ -9083,16 +9143,16 @@
     <row r="164">
       <c r="T164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U164" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V164" s="4" t="n">
-        <v>1</v>
+        <v>47472</v>
       </c>
       <c r="X164" s="4" t="n">
         <v>1</v>
@@ -9124,16 +9184,16 @@
     <row r="165">
       <c r="T165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U165" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V165" s="7" t="n">
-        <v>1</v>
+        <v>47003</v>
       </c>
       <c r="X165" s="7" t="n">
         <v>144</v>
@@ -9165,16 +9225,16 @@
     <row r="166">
       <c r="T166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U166" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V166" s="4" t="n">
-        <v>1</v>
+        <v>48466</v>
       </c>
       <c r="X166" s="4" t="n">
         <v>16</v>
@@ -9206,16 +9266,16 @@
     <row r="167">
       <c r="T167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U167" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V167" s="7" t="n">
-        <v>1</v>
+        <v>48027</v>
       </c>
       <c r="X167" s="7" t="n">
         <v>66</v>
@@ -9247,16 +9307,16 @@
     <row r="168">
       <c r="T168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U168" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V168" s="4" t="n">
-        <v>1</v>
+        <v>46480</v>
       </c>
       <c r="X168" s="4" t="n">
         <v>35</v>
@@ -9288,16 +9348,16 @@
     <row r="169">
       <c r="T169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U169" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V169" s="7" t="n">
-        <v>1</v>
+        <v>47128</v>
       </c>
       <c r="X169" s="7" t="n">
         <v>15</v>
@@ -9329,7 +9389,7 @@
     <row r="170">
       <c r="T170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U170" s="4" t="inlineStr">
@@ -9370,7 +9430,7 @@
     <row r="171">
       <c r="T171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U171" s="7" t="inlineStr">
@@ -9411,7 +9471,7 @@
     <row r="172">
       <c r="T172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U172" s="4" t="inlineStr">
@@ -9452,12 +9512,12 @@
     <row r="173">
       <c r="T173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U173" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V173" s="7" t="n">
@@ -9493,12 +9553,12 @@
     <row r="174">
       <c r="T174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U174" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V174" s="4" t="n">
@@ -9534,12 +9594,12 @@
     <row r="175">
       <c r="T175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U175" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V175" s="7" t="n">
@@ -9575,12 +9635,12 @@
     <row r="176">
       <c r="T176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U176" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V176" s="4" t="n">
@@ -9616,12 +9676,12 @@
     <row r="177">
       <c r="T177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U177" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V177" s="7" t="n">
@@ -9657,12 +9717,12 @@
     <row r="178">
       <c r="T178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U178" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V178" s="4" t="n">
@@ -9698,12 +9758,12 @@
     <row r="179">
       <c r="T179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V179" s="7" t="n">
@@ -9739,12 +9799,12 @@
     <row r="180">
       <c r="T180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U180" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V180" s="4" t="n">
@@ -9780,12 +9840,12 @@
     <row r="181">
       <c r="T181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U181" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V181" s="7" t="n">
@@ -9821,12 +9881,12 @@
     <row r="182">
       <c r="T182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U182" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V182" s="4" t="n">
@@ -9862,12 +9922,12 @@
     <row r="183">
       <c r="T183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U183" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V183" s="7" t="n">
@@ -9903,12 +9963,12 @@
     <row r="184">
       <c r="T184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U184" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V184" s="4" t="n">
@@ -9944,12 +10004,12 @@
     <row r="185">
       <c r="T185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U185" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V185" s="7" t="n">
@@ -9985,12 +10045,12 @@
     <row r="186">
       <c r="T186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U186" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V186" s="4" t="n">
@@ -10026,12 +10086,12 @@
     <row r="187">
       <c r="T187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U187" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V187" s="7" t="n">
@@ -10067,12 +10127,12 @@
     <row r="188">
       <c r="T188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U188" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V188" s="4" t="n">
@@ -10108,12 +10168,12 @@
     <row r="189">
       <c r="T189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U189" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V189" s="7" t="n">
@@ -10149,12 +10209,12 @@
     <row r="190">
       <c r="T190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U190" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V190" s="4" t="n">
@@ -10190,12 +10250,12 @@
     <row r="191">
       <c r="T191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U191" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V191" s="7" t="n">
@@ -10231,12 +10291,12 @@
     <row r="192">
       <c r="T192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U192" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V192" s="4" t="n">
@@ -10272,12 +10332,12 @@
     <row r="193">
       <c r="T193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U193" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V193" s="7" t="n">
@@ -10313,7 +10373,7 @@
     <row r="194">
       <c r="T194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U194" s="4" t="inlineStr">
@@ -10354,7 +10414,7 @@
     <row r="195">
       <c r="T195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U195" s="7" t="inlineStr">
@@ -10395,7 +10455,7 @@
     <row r="196">
       <c r="T196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U196" s="4" t="inlineStr">
@@ -10407,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="X196" s="4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y196" s="4" t="inlineStr">
         <is>
@@ -10436,16 +10496,16 @@
     <row r="197">
       <c r="T197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U197" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V197" s="7" t="n">
-        <v>9927</v>
+        <v>1</v>
       </c>
       <c r="X197" s="7" t="n">
         <v>23</v>
@@ -10477,16 +10537,16 @@
     <row r="198">
       <c r="T198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U198" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V198" s="4" t="n">
-        <v>9839</v>
+        <v>1</v>
       </c>
       <c r="X198" s="4" t="n">
         <v>70</v>
@@ -10518,16 +10578,16 @@
     <row r="199">
       <c r="T199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U199" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V199" s="7" t="n">
-        <v>9918</v>
+        <v>1</v>
       </c>
       <c r="X199" s="7" t="n">
         <v>45</v>
@@ -10559,16 +10619,16 @@
     <row r="200">
       <c r="T200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U200" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V200" s="4" t="n">
-        <v>10435</v>
+        <v>1</v>
       </c>
       <c r="X200" s="4" t="n">
         <v>11</v>
@@ -10600,16 +10660,16 @@
     <row r="201">
       <c r="T201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U201" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V201" s="7" t="n">
-        <v>10050</v>
+        <v>1</v>
       </c>
       <c r="X201" s="7" t="n">
         <v>67</v>
@@ -10641,16 +10701,16 @@
     <row r="202">
       <c r="T202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U202" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V202" s="4" t="n">
-        <v>9768</v>
+        <v>1</v>
       </c>
       <c r="X202" s="4" t="n">
         <v>1</v>
@@ -10682,16 +10742,16 @@
     <row r="203">
       <c r="T203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U203" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V203" s="7" t="n">
-        <v>9920</v>
+        <v>1</v>
       </c>
       <c r="X203" s="7" t="n">
         <v>9</v>
@@ -10723,16 +10783,16 @@
     <row r="204">
       <c r="T204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U204" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V204" s="4" t="n">
-        <v>10435</v>
+        <v>1</v>
       </c>
       <c r="X204" s="4" t="n">
         <v>3</v>
@@ -10764,20 +10824,30 @@
     <row r="205">
       <c r="T205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U205" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V205" s="7" t="n">
-        <v>10434</v>
-      </c>
-      <c r="X205" s="7" t="n"/>
-      <c r="Y205" s="7" t="n"/>
-      <c r="Z205" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X205" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y205" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z205" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB205" s="7" t="n">
         <v>51</v>
       </c>
@@ -10795,20 +10865,30 @@
     <row r="206">
       <c r="T206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U206" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V206" s="4" t="n">
-        <v>10284</v>
-      </c>
-      <c r="X206" s="4" t="n"/>
-      <c r="Y206" s="4" t="n"/>
-      <c r="Z206" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X206" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y206" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z206" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB206" s="4" t="n">
         <v>127</v>
       </c>
@@ -10826,20 +10906,30 @@
     <row r="207">
       <c r="T207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U207" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V207" s="7" t="n">
-        <v>10458</v>
-      </c>
-      <c r="X207" s="7" t="n"/>
-      <c r="Y207" s="7" t="n"/>
-      <c r="Z207" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X207" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y207" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z207" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB207" s="7" t="n">
         <v>2</v>
       </c>
@@ -10857,20 +10947,30 @@
     <row r="208">
       <c r="T208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U208" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V208" s="4" t="n">
-        <v>10153</v>
-      </c>
-      <c r="X208" s="4" t="n"/>
-      <c r="Y208" s="4" t="n"/>
-      <c r="Z208" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X208" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y208" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z208" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB208" s="4" t="n">
         <v>11</v>
       </c>
@@ -10888,20 +10988,30 @@
     <row r="209">
       <c r="T209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U209" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+        </is>
+      </c>
+      <c r="V209" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X209" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y209" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z209" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="V209" s="7" t="n">
-        <v>9843</v>
-      </c>
-      <c r="X209" s="7" t="n"/>
-      <c r="Y209" s="7" t="n"/>
-      <c r="Z209" s="7" t="n"/>
       <c r="AB209" s="7" t="n">
         <v>3</v>
       </c>
@@ -10919,20 +11029,30 @@
     <row r="210">
       <c r="T210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U210" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V210" s="4" t="n">
-        <v>10433</v>
-      </c>
-      <c r="X210" s="4" t="n"/>
-      <c r="Y210" s="4" t="n"/>
-      <c r="Z210" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X210" s="4" t="n">
+        <v>544</v>
+      </c>
+      <c r="Y210" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z210" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB210" s="4" t="n">
         <v>351</v>
       </c>
@@ -10950,20 +11070,30 @@
     <row r="211">
       <c r="T211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U211" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V211" s="7" t="n">
-        <v>10670</v>
-      </c>
-      <c r="X211" s="7" t="n"/>
-      <c r="Y211" s="7" t="n"/>
-      <c r="Z211" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X211" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y211" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z211" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB211" s="7" t="n">
         <v>37</v>
       </c>
@@ -10981,20 +11111,30 @@
     <row r="212">
       <c r="T212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U212" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V212" s="4" t="n">
-        <v>10599</v>
-      </c>
-      <c r="X212" s="4" t="n"/>
-      <c r="Y212" s="4" t="n"/>
-      <c r="Z212" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X212" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y212" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z212" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB212" s="4" t="n">
         <v>152</v>
       </c>
@@ -11012,20 +11152,30 @@
     <row r="213">
       <c r="T213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U213" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V213" s="7" t="n">
-        <v>10619</v>
-      </c>
-      <c r="X213" s="7" t="n"/>
-      <c r="Y213" s="7" t="n"/>
-      <c r="Z213" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X213" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="Y213" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z213" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB213" s="7" t="n">
         <v>59</v>
       </c>
@@ -11043,20 +11193,30 @@
     <row r="214">
       <c r="T214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U214" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V214" s="4" t="n">
-        <v>10415</v>
-      </c>
-      <c r="X214" s="4" t="n"/>
-      <c r="Y214" s="4" t="n"/>
-      <c r="Z214" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X214" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y214" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z214" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB214" s="4" t="n">
         <v>47</v>
       </c>
@@ -11074,20 +11234,30 @@
     <row r="215">
       <c r="T215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U215" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V215" s="7" t="n">
-        <v>10065</v>
-      </c>
-      <c r="X215" s="7" t="n"/>
-      <c r="Y215" s="7" t="n"/>
-      <c r="Z215" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X215" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y215" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z215" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB215" s="7" t="n">
         <v>149</v>
       </c>
@@ -11105,20 +11275,30 @@
     <row r="216">
       <c r="T216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U216" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V216" s="4" t="n">
-        <v>10158</v>
-      </c>
-      <c r="X216" s="4" t="n"/>
-      <c r="Y216" s="4" t="n"/>
-      <c r="Z216" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X216" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y216" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z216" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB216" s="4" t="n">
         <v>4</v>
       </c>
@@ -11136,20 +11316,30 @@
     <row r="217">
       <c r="T217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U217" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
+        </is>
+      </c>
+      <c r="V217" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X217" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y217" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z217" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="V217" s="7" t="n">
-        <v>10333</v>
-      </c>
-      <c r="X217" s="7" t="n"/>
-      <c r="Y217" s="7" t="n"/>
-      <c r="Z217" s="7" t="n"/>
       <c r="AB217" s="7" t="n">
         <v>2</v>
       </c>
@@ -11167,20 +11357,30 @@
     <row r="218">
       <c r="T218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U218" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V218" s="4" t="n">
-        <v>10414</v>
-      </c>
-      <c r="X218" s="4" t="n"/>
-      <c r="Y218" s="4" t="n"/>
-      <c r="Z218" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X218" s="4" t="n">
+        <v>519</v>
+      </c>
+      <c r="Y218" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z218" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB218" s="4" t="n">
         <v>4</v>
       </c>
@@ -11198,20 +11398,30 @@
     <row r="219">
       <c r="T219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U219" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V219" s="7" t="n">
-        <v>10453</v>
-      </c>
-      <c r="X219" s="7" t="n"/>
-      <c r="Y219" s="7" t="n"/>
-      <c r="Z219" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X219" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y219" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z219" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB219" s="7" t="n">
         <v>337</v>
       </c>
@@ -11229,20 +11439,30 @@
     <row r="220">
       <c r="T220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U220" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.GAB3RR77LN</t>
         </is>
       </c>
       <c r="V220" s="4" t="n">
-        <v>10879</v>
-      </c>
-      <c r="X220" s="4" t="n"/>
-      <c r="Y220" s="4" t="n"/>
-      <c r="Z220" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X220" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y220" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z220" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB220" s="4" t="n">
         <v>34</v>
       </c>
@@ -11260,7 +11480,7 @@
     <row r="221">
       <c r="T221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U221" s="7" t="inlineStr">
@@ -11269,11 +11489,21 @@
         </is>
       </c>
       <c r="V221" s="7" t="n">
-        <v>10826</v>
-      </c>
-      <c r="X221" s="7" t="n"/>
-      <c r="Y221" s="7" t="n"/>
-      <c r="Z221" s="7" t="n"/>
+        <v>9927</v>
+      </c>
+      <c r="X221" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y221" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z221" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB221" s="7" t="n">
         <v>141</v>
       </c>
@@ -11291,20 +11521,30 @@
     <row r="222">
       <c r="T222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U222" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation50987</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V222" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X222" s="4" t="n"/>
-      <c r="Y222" s="4" t="n"/>
-      <c r="Z222" s="4" t="n"/>
+        <v>9839</v>
+      </c>
+      <c r="X222" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y222" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z222" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
       <c r="AB222" s="4" t="n">
         <v>51</v>
       </c>
@@ -11322,20 +11562,30 @@
     <row r="223">
       <c r="T223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U223" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation75114</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V223" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X223" s="7" t="n"/>
-      <c r="Y223" s="7" t="n"/>
-      <c r="Z223" s="7" t="n"/>
+        <v>9918</v>
+      </c>
+      <c r="X223" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y223" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z223" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
       <c r="AB223" s="7" t="n">
         <v>33</v>
       </c>
@@ -11353,20 +11603,30 @@
     <row r="224">
       <c r="T224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U224" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V224" s="4" t="n">
-        <v>21493</v>
-      </c>
-      <c r="X224" s="4" t="n"/>
-      <c r="Y224" s="4" t="n"/>
-      <c r="Z224" s="4" t="n"/>
+        <v>10435</v>
+      </c>
+      <c r="X224" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y224" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z224" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
       <c r="AB224" s="4" t="n">
         <v>1</v>
       </c>
@@ -11384,20 +11644,30 @@
     <row r="225">
       <c r="T225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U225" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V225" s="7" t="n">
+        <v>10050</v>
+      </c>
+      <c r="X225" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y225" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z225" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V225" s="7" t="n">
-        <v>21012</v>
-      </c>
-      <c r="X225" s="7" t="n"/>
-      <c r="Y225" s="7" t="n"/>
-      <c r="Z225" s="7" t="n"/>
       <c r="AB225" s="7" t="n">
         <v>133</v>
       </c>
@@ -11415,20 +11685,30 @@
     <row r="226">
       <c r="T226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U226" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V226" s="4" t="n">
-        <v>21635</v>
-      </c>
-      <c r="X226" s="4" t="n"/>
-      <c r="Y226" s="4" t="n"/>
-      <c r="Z226" s="4" t="n"/>
+        <v>9768</v>
+      </c>
+      <c r="X226" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y226" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z226" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB226" s="4" t="n">
         <v>2</v>
       </c>
@@ -11446,20 +11726,30 @@
     <row r="227">
       <c r="T227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U227" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V227" s="7" t="n">
-        <v>21969</v>
-      </c>
-      <c r="X227" s="7" t="n"/>
-      <c r="Y227" s="7" t="n"/>
-      <c r="Z227" s="7" t="n"/>
+        <v>9920</v>
+      </c>
+      <c r="X227" s="7" t="n">
+        <v>511</v>
+      </c>
+      <c r="Y227" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z227" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB227" s="7" t="n">
         <v>1</v>
       </c>
@@ -11477,604 +11767,894 @@
     <row r="228">
       <c r="T228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U228" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V228" s="4" t="n">
-        <v>21723</v>
-      </c>
-      <c r="X228" s="4" t="n"/>
-      <c r="Y228" s="4" t="n"/>
-      <c r="Z228" s="4" t="n"/>
-      <c r="AB228" s="4" t="n"/>
-      <c r="AC228" s="4" t="n"/>
-      <c r="AD228" s="4" t="n"/>
+        <v>10435</v>
+      </c>
+      <c r="X228" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y228" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z228" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB228" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="AC228" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD228" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="T229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U229" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V229" s="7" t="n">
-        <v>20879</v>
+        <v>10434</v>
       </c>
       <c r="X229" s="7" t="n"/>
       <c r="Y229" s="7" t="n"/>
       <c r="Z229" s="7" t="n"/>
-      <c r="AB229" s="7" t="n"/>
-      <c r="AC229" s="7" t="n"/>
-      <c r="AD229" s="7" t="n"/>
+      <c r="AB229" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC229" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD229" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="T230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U230" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V230" s="4" t="n">
-        <v>20783</v>
+        <v>10284</v>
       </c>
       <c r="X230" s="4" t="n"/>
       <c r="Y230" s="4" t="n"/>
       <c r="Z230" s="4" t="n"/>
-      <c r="AB230" s="4" t="n"/>
-      <c r="AC230" s="4" t="n"/>
-      <c r="AD230" s="4" t="n"/>
+      <c r="AB230" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="AC230" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD230" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="T231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U231" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V231" s="7" t="n">
-        <v>21875</v>
+        <v>10458</v>
       </c>
       <c r="X231" s="7" t="n"/>
       <c r="Y231" s="7" t="n"/>
       <c r="Z231" s="7" t="n"/>
-      <c r="AB231" s="7" t="n"/>
-      <c r="AC231" s="7" t="n"/>
-      <c r="AD231" s="7" t="n"/>
+      <c r="AB231" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC231" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD231" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="T232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U232" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V232" s="4" t="n">
-        <v>22103</v>
+        <v>10153</v>
       </c>
       <c r="X232" s="4" t="n"/>
       <c r="Y232" s="4" t="n"/>
       <c r="Z232" s="4" t="n"/>
-      <c r="AB232" s="4" t="n"/>
-      <c r="AC232" s="4" t="n"/>
-      <c r="AD232" s="4" t="n"/>
+      <c r="AB232" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC232" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD232" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="T233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U233" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V233" s="7" t="n">
-        <v>22799</v>
+        <v>9843</v>
       </c>
       <c r="X233" s="7" t="n"/>
       <c r="Y233" s="7" t="n"/>
       <c r="Z233" s="7" t="n"/>
-      <c r="AB233" s="7" t="n"/>
-      <c r="AC233" s="7" t="n"/>
-      <c r="AD233" s="7" t="n"/>
+      <c r="AB233" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC233" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD233" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="T234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U234" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V234" s="4" t="n">
-        <v>22705</v>
+        <v>10433</v>
       </c>
       <c r="X234" s="4" t="n"/>
       <c r="Y234" s="4" t="n"/>
       <c r="Z234" s="4" t="n"/>
-      <c r="AB234" s="4" t="n"/>
-      <c r="AC234" s="4" t="n"/>
-      <c r="AD234" s="4" t="n"/>
+      <c r="AB234" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="AC234" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD234" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="T235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U235" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V235" s="7" t="n">
-        <v>21885</v>
+        <v>10670</v>
       </c>
       <c r="X235" s="7" t="n"/>
       <c r="Y235" s="7" t="n"/>
       <c r="Z235" s="7" t="n"/>
-      <c r="AB235" s="7" t="n"/>
-      <c r="AC235" s="7" t="n"/>
-      <c r="AD235" s="7" t="n"/>
+      <c r="AB235" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC235" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD235" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="T236" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U236" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V236" s="4" t="n">
-        <v>21360</v>
+        <v>10599</v>
       </c>
       <c r="X236" s="4" t="n"/>
       <c r="Y236" s="4" t="n"/>
       <c r="Z236" s="4" t="n"/>
-      <c r="AB236" s="4" t="n"/>
-      <c r="AC236" s="4" t="n"/>
-      <c r="AD236" s="4" t="n"/>
+      <c r="AB236" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC236" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD236" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="T237" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U237" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V237" s="7" t="n">
-        <v>20612</v>
+        <v>10619</v>
       </c>
       <c r="X237" s="7" t="n"/>
       <c r="Y237" s="7" t="n"/>
       <c r="Z237" s="7" t="n"/>
-      <c r="AB237" s="7" t="n"/>
-      <c r="AC237" s="7" t="n"/>
-      <c r="AD237" s="7" t="n"/>
+      <c r="AB237" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC237" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD237" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="T238" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U238" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V238" s="4" t="n">
-        <v>22101</v>
+        <v>10415</v>
       </c>
       <c r="X238" s="4" t="n"/>
       <c r="Y238" s="4" t="n"/>
       <c r="Z238" s="4" t="n"/>
-      <c r="AB238" s="4" t="n"/>
-      <c r="AC238" s="4" t="n"/>
-      <c r="AD238" s="4" t="n"/>
+      <c r="AB238" s="4" t="n">
+        <v>324</v>
+      </c>
+      <c r="AC238" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD238" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="T239" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U239" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V239" s="7" t="n">
-        <v>22665</v>
+        <v>10065</v>
       </c>
       <c r="X239" s="7" t="n"/>
       <c r="Y239" s="7" t="n"/>
       <c r="Z239" s="7" t="n"/>
-      <c r="AB239" s="7" t="n"/>
-      <c r="AC239" s="7" t="n"/>
-      <c r="AD239" s="7" t="n"/>
+      <c r="AB239" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC239" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD239" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="T240" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U240" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V240" s="4" t="n">
-        <v>22473</v>
+        <v>10158</v>
       </c>
       <c r="X240" s="4" t="n"/>
       <c r="Y240" s="4" t="n"/>
       <c r="Z240" s="4" t="n"/>
-      <c r="AB240" s="4" t="n"/>
-      <c r="AC240" s="4" t="n"/>
-      <c r="AD240" s="4" t="n"/>
+      <c r="AB240" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="AC240" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD240" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="T241" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U241" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V241" s="7" t="n">
-        <v>22903</v>
+        <v>10333</v>
       </c>
       <c r="X241" s="7" t="n"/>
       <c r="Y241" s="7" t="n"/>
       <c r="Z241" s="7" t="n"/>
-      <c r="AB241" s="7" t="n"/>
-      <c r="AC241" s="7" t="n"/>
-      <c r="AD241" s="7" t="n"/>
+      <c r="AB241" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC241" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD241" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="T242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U242" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V242" s="4" t="n">
-        <v>21829</v>
+        <v>10414</v>
       </c>
       <c r="X242" s="4" t="n"/>
       <c r="Y242" s="4" t="n"/>
       <c r="Z242" s="4" t="n"/>
-      <c r="AB242" s="4" t="n"/>
-      <c r="AC242" s="4" t="n"/>
-      <c r="AD242" s="4" t="n"/>
+      <c r="AB242" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC242" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD242" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="T243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U243" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V243" s="7" t="n">
-        <v>20959</v>
+        <v>10453</v>
       </c>
       <c r="X243" s="7" t="n"/>
       <c r="Y243" s="7" t="n"/>
       <c r="Z243" s="7" t="n"/>
-      <c r="AB243" s="7" t="n"/>
-      <c r="AC243" s="7" t="n"/>
-      <c r="AD243" s="7" t="n"/>
+      <c r="AB243" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="AC243" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD243" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="T244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U244" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V244" s="4" t="n">
-        <v>20856</v>
+        <v>10879</v>
       </c>
       <c r="X244" s="4" t="n"/>
       <c r="Y244" s="4" t="n"/>
       <c r="Z244" s="4" t="n"/>
-      <c r="AB244" s="4" t="n"/>
-      <c r="AC244" s="4" t="n"/>
-      <c r="AD244" s="4" t="n"/>
+      <c r="AB244" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC244" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD244" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="T245" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U245" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V245" s="7" t="n">
-        <v>23061</v>
+        <v>10826</v>
       </c>
       <c r="X245" s="7" t="n"/>
       <c r="Y245" s="7" t="n"/>
       <c r="Z245" s="7" t="n"/>
-      <c r="AB245" s="7" t="n"/>
-      <c r="AC245" s="7" t="n"/>
-      <c r="AD245" s="7" t="n"/>
+      <c r="AB245" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC245" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD245" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="T246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U246" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V246" s="4" t="n">
-        <v>21952</v>
+        <v>10310</v>
       </c>
       <c r="X246" s="4" t="n"/>
       <c r="Y246" s="4" t="n"/>
       <c r="Z246" s="4" t="n"/>
-      <c r="AB246" s="4" t="n"/>
-      <c r="AC246" s="4" t="n"/>
-      <c r="AD246" s="4" t="n"/>
+      <c r="AB246" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC246" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD246" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="T247" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U247" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V247" s="7" t="n">
-        <v>22608</v>
+        <v>10051</v>
       </c>
       <c r="X247" s="7" t="n"/>
       <c r="Y247" s="7" t="n"/>
       <c r="Z247" s="7" t="n"/>
-      <c r="AB247" s="7" t="n"/>
-      <c r="AC247" s="7" t="n"/>
-      <c r="AD247" s="7" t="n"/>
+      <c r="AB247" s="7" t="n">
+        <v>384</v>
+      </c>
+      <c r="AC247" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD247" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="T248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U248" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V248" s="4" t="n">
-        <v>22674</v>
+        <v>10327</v>
       </c>
       <c r="X248" s="4" t="n"/>
       <c r="Y248" s="4" t="n"/>
       <c r="Z248" s="4" t="n"/>
-      <c r="AB248" s="4" t="n"/>
-      <c r="AC248" s="4" t="n"/>
-      <c r="AD248" s="4" t="n"/>
+      <c r="AB248" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC248" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD248" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="T249" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U249" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.hungerstation50987</t>
         </is>
       </c>
       <c r="V249" s="7" t="n">
-        <v>16634</v>
+        <v>1</v>
       </c>
       <c r="X249" s="7" t="n"/>
       <c r="Y249" s="7" t="n"/>
       <c r="Z249" s="7" t="n"/>
-      <c r="AB249" s="7" t="n"/>
-      <c r="AC249" s="7" t="n"/>
-      <c r="AD249" s="7" t="n"/>
+      <c r="AB249" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="AC249" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD249" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="T250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U250" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.hungerstation75114</t>
         </is>
       </c>
       <c r="V250" s="4" t="n">
-        <v>16721</v>
+        <v>1</v>
       </c>
       <c r="X250" s="4" t="n"/>
       <c r="Y250" s="4" t="n"/>
       <c r="Z250" s="4" t="n"/>
-      <c r="AB250" s="4" t="n"/>
-      <c r="AC250" s="4" t="n"/>
-      <c r="AD250" s="4" t="n"/>
+      <c r="AB250" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC250" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD250" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="T251" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U251" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V251" s="7" t="n">
-        <v>16586</v>
+        <v>21493</v>
       </c>
       <c r="X251" s="7" t="n"/>
       <c r="Y251" s="7" t="n"/>
       <c r="Z251" s="7" t="n"/>
-      <c r="AB251" s="7" t="n"/>
-      <c r="AC251" s="7" t="n"/>
-      <c r="AD251" s="7" t="n"/>
+      <c r="AB251" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC251" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD251" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="T252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U252" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V252" s="4" t="n">
-        <v>16419</v>
+        <v>21012</v>
       </c>
       <c r="X252" s="4" t="n"/>
       <c r="Y252" s="4" t="n"/>
       <c r="Z252" s="4" t="n"/>
-      <c r="AB252" s="4" t="n"/>
-      <c r="AC252" s="4" t="n"/>
-      <c r="AD252" s="4" t="n"/>
+      <c r="AB252" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="AC252" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD252" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="T253" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U253" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V253" s="7" t="n">
-        <v>15946</v>
+        <v>21635</v>
       </c>
       <c r="X253" s="7" t="n"/>
       <c r="Y253" s="7" t="n"/>
       <c r="Z253" s="7" t="n"/>
-      <c r="AB253" s="7" t="n"/>
-      <c r="AC253" s="7" t="n"/>
-      <c r="AD253" s="7" t="n"/>
+      <c r="AB253" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC253" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD253" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="T254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U254" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V254" s="4" t="n">
-        <v>16042</v>
+        <v>21969</v>
       </c>
       <c r="X254" s="4" t="n"/>
       <c r="Y254" s="4" t="n"/>
       <c r="Z254" s="4" t="n"/>
-      <c r="AB254" s="4" t="n"/>
-      <c r="AC254" s="4" t="n"/>
-      <c r="AD254" s="4" t="n"/>
+      <c r="AB254" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC254" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD254" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="T255" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U255" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V255" s="7" t="n">
-        <v>16409</v>
+        <v>21723</v>
       </c>
       <c r="X255" s="7" t="n"/>
       <c r="Y255" s="7" t="n"/>
       <c r="Z255" s="7" t="n"/>
-      <c r="AB255" s="7" t="n"/>
-      <c r="AC255" s="7" t="n"/>
-      <c r="AD255" s="7" t="n"/>
+      <c r="AB255" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC255" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD255" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="T256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U256" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V256" s="4" t="n">
-        <v>16831</v>
+        <v>20879</v>
       </c>
       <c r="X256" s="4" t="n"/>
       <c r="Y256" s="4" t="n"/>
@@ -12086,16 +12666,16 @@
     <row r="257">
       <c r="T257" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U257" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V257" s="7" t="n">
-        <v>16886</v>
+        <v>20783</v>
       </c>
       <c r="X257" s="7" t="n"/>
       <c r="Y257" s="7" t="n"/>
@@ -12107,16 +12687,16 @@
     <row r="258">
       <c r="T258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U258" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V258" s="4" t="n">
-        <v>16694</v>
+        <v>21875</v>
       </c>
       <c r="X258" s="4" t="n"/>
       <c r="Y258" s="4" t="n"/>
@@ -12128,16 +12708,16 @@
     <row r="259">
       <c r="T259" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U259" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V259" s="7" t="n">
-        <v>16659</v>
+        <v>22103</v>
       </c>
       <c r="X259" s="7" t="n"/>
       <c r="Y259" s="7" t="n"/>
@@ -12149,16 +12729,16 @@
     <row r="260">
       <c r="T260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U260" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V260" s="4" t="n">
-        <v>16268</v>
+        <v>22799</v>
       </c>
       <c r="X260" s="4" t="n"/>
       <c r="Y260" s="4" t="n"/>
@@ -12170,16 +12750,16 @@
     <row r="261">
       <c r="T261" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U261" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V261" s="7" t="n">
-        <v>16259</v>
+        <v>22705</v>
       </c>
       <c r="X261" s="7" t="n"/>
       <c r="Y261" s="7" t="n"/>
@@ -12191,16 +12771,16 @@
     <row r="262">
       <c r="T262" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U262" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V262" s="4" t="n">
-        <v>16600</v>
+        <v>21885</v>
       </c>
       <c r="X262" s="4" t="n"/>
       <c r="Y262" s="4" t="n"/>
@@ -12212,16 +12792,16 @@
     <row r="263">
       <c r="T263" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U263" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V263" s="7" t="n">
-        <v>16913</v>
+        <v>21360</v>
       </c>
       <c r="X263" s="7" t="n"/>
       <c r="Y263" s="7" t="n"/>
@@ -12233,16 +12813,16 @@
     <row r="264">
       <c r="T264" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U264" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V264" s="4" t="n">
-        <v>16991</v>
+        <v>20612</v>
       </c>
       <c r="X264" s="4" t="n"/>
       <c r="Y264" s="4" t="n"/>
@@ -12254,16 +12834,16 @@
     <row r="265">
       <c r="T265" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U265" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V265" s="7" t="n">
-        <v>17365</v>
+        <v>22101</v>
       </c>
       <c r="X265" s="7" t="n"/>
       <c r="Y265" s="7" t="n"/>
@@ -12275,16 +12855,16 @@
     <row r="266">
       <c r="T266" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U266" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V266" s="4" t="n">
-        <v>16944</v>
+        <v>22665</v>
       </c>
       <c r="X266" s="4" t="n"/>
       <c r="Y266" s="4" t="n"/>
@@ -12296,16 +12876,16 @@
     <row r="267">
       <c r="T267" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U267" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V267" s="7" t="n">
-        <v>16518</v>
+        <v>22473</v>
       </c>
       <c r="X267" s="7" t="n"/>
       <c r="Y267" s="7" t="n"/>
@@ -12317,16 +12897,16 @@
     <row r="268">
       <c r="T268" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U268" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V268" s="4" t="n">
-        <v>16634</v>
+        <v>22903</v>
       </c>
       <c r="X268" s="4" t="n"/>
       <c r="Y268" s="4" t="n"/>
@@ -12338,16 +12918,16 @@
     <row r="269">
       <c r="T269" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U269" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V269" s="7" t="n">
-        <v>16711</v>
+        <v>21829</v>
       </c>
       <c r="X269" s="7" t="n"/>
       <c r="Y269" s="7" t="n"/>
@@ -12359,16 +12939,16 @@
     <row r="270">
       <c r="T270" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U270" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V270" s="4" t="n">
-        <v>17379</v>
+        <v>20959</v>
       </c>
       <c r="X270" s="4" t="n"/>
       <c r="Y270" s="4" t="n"/>
@@ -12380,16 +12960,16 @@
     <row r="271">
       <c r="T271" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U271" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V271" s="7" t="n">
-        <v>17551</v>
+        <v>20856</v>
       </c>
       <c r="X271" s="7" t="n"/>
       <c r="Y271" s="7" t="n"/>
@@ -12401,16 +12981,16 @@
     <row r="272">
       <c r="T272" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U272" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V272" s="4" t="n">
-        <v>17474</v>
+        <v>23061</v>
       </c>
       <c r="X272" s="4" t="n"/>
       <c r="Y272" s="4" t="n"/>
@@ -12422,16 +13002,16 @@
     <row r="273">
       <c r="T273" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U273" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V273" s="7" t="n">
-        <v>17309</v>
+        <v>21952</v>
       </c>
       <c r="X273" s="7" t="n"/>
       <c r="Y273" s="7" t="n"/>
@@ -12443,16 +13023,16 @@
     <row r="274">
       <c r="T274" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U274" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V274" s="4" t="n">
-        <v>724</v>
+        <v>22608</v>
       </c>
       <c r="X274" s="4" t="n"/>
       <c r="Y274" s="4" t="n"/>
@@ -12464,16 +13044,16 @@
     <row r="275">
       <c r="T275" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U275" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V275" s="7" t="n">
-        <v>746</v>
+        <v>22674</v>
       </c>
       <c r="X275" s="7" t="n"/>
       <c r="Y275" s="7" t="n"/>
@@ -12485,16 +13065,16 @@
     <row r="276">
       <c r="T276" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U276" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V276" s="4" t="n">
-        <v>723</v>
+        <v>21947</v>
       </c>
       <c r="X276" s="4" t="n"/>
       <c r="Y276" s="4" t="n"/>
@@ -12506,16 +13086,16 @@
     <row r="277">
       <c r="T277" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U277" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V277" s="7" t="n">
-        <v>708</v>
+        <v>22524</v>
       </c>
       <c r="X277" s="7" t="n"/>
       <c r="Y277" s="7" t="n"/>
@@ -12527,16 +13107,16 @@
     <row r="278">
       <c r="T278" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U278" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V278" s="4" t="n">
-        <v>735</v>
+        <v>21022</v>
       </c>
       <c r="X278" s="4" t="n"/>
       <c r="Y278" s="4" t="n"/>
@@ -12548,16 +13128,16 @@
     <row r="279">
       <c r="T279" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U279" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V279" s="7" t="n">
-        <v>714</v>
+        <v>16634</v>
       </c>
       <c r="X279" s="7" t="n"/>
       <c r="Y279" s="7" t="n"/>
@@ -12569,16 +13149,16 @@
     <row r="280">
       <c r="T280" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U280" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V280" s="4" t="n">
-        <v>706</v>
+        <v>16721</v>
       </c>
       <c r="X280" s="4" t="n"/>
       <c r="Y280" s="4" t="n"/>
@@ -12590,16 +13170,16 @@
     <row r="281">
       <c r="T281" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U281" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V281" s="7" t="n">
-        <v>729</v>
+        <v>16586</v>
       </c>
       <c r="X281" s="7" t="n"/>
       <c r="Y281" s="7" t="n"/>
@@ -12611,16 +13191,16 @@
     <row r="282">
       <c r="T282" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U282" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V282" s="4" t="n">
-        <v>719</v>
+        <v>16419</v>
       </c>
       <c r="X282" s="4" t="n"/>
       <c r="Y282" s="4" t="n"/>
@@ -12632,16 +13212,16 @@
     <row r="283">
       <c r="T283" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U283" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V283" s="7" t="n">
-        <v>719</v>
+        <v>15946</v>
       </c>
       <c r="X283" s="7" t="n"/>
       <c r="Y283" s="7" t="n"/>
@@ -12653,16 +13233,16 @@
     <row r="284">
       <c r="T284" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U284" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V284" s="4" t="n">
-        <v>730</v>
+        <v>16042</v>
       </c>
       <c r="X284" s="4" t="n"/>
       <c r="Y284" s="4" t="n"/>
@@ -12674,16 +13254,16 @@
     <row r="285">
       <c r="T285" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U285" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V285" s="7" t="n">
-        <v>740</v>
+        <v>16409</v>
       </c>
       <c r="X285" s="7" t="n"/>
       <c r="Y285" s="7" t="n"/>
@@ -12695,16 +13275,16 @@
     <row r="286">
       <c r="T286" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U286" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V286" s="4" t="n">
-        <v>708</v>
+        <v>16831</v>
       </c>
       <c r="X286" s="4" t="n"/>
       <c r="Y286" s="4" t="n"/>
@@ -12716,16 +13296,16 @@
     <row r="287">
       <c r="T287" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U287" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V287" s="7" t="n">
-        <v>698</v>
+        <v>16886</v>
       </c>
       <c r="X287" s="7" t="n"/>
       <c r="Y287" s="7" t="n"/>
@@ -12737,16 +13317,16 @@
     <row r="288">
       <c r="T288" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U288" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V288" s="4" t="n">
-        <v>691</v>
+        <v>16694</v>
       </c>
       <c r="X288" s="4" t="n"/>
       <c r="Y288" s="4" t="n"/>
@@ -12758,16 +13338,16 @@
     <row r="289">
       <c r="T289" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U289" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V289" s="7" t="n">
-        <v>695</v>
+        <v>16659</v>
       </c>
       <c r="X289" s="7" t="n"/>
       <c r="Y289" s="7" t="n"/>
@@ -12779,16 +13359,16 @@
     <row r="290">
       <c r="T290" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U290" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V290" s="4" t="n">
-        <v>706</v>
+        <v>16268</v>
       </c>
       <c r="X290" s="4" t="n"/>
       <c r="Y290" s="4" t="n"/>
@@ -12800,16 +13380,16 @@
     <row r="291">
       <c r="T291" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U291" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V291" s="7" t="n">
-        <v>701</v>
+        <v>16259</v>
       </c>
       <c r="X291" s="7" t="n"/>
       <c r="Y291" s="7" t="n"/>
@@ -12821,16 +13401,16 @@
     <row r="292">
       <c r="T292" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U292" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V292" s="4" t="n">
-        <v>706</v>
+        <v>16600</v>
       </c>
       <c r="X292" s="4" t="n"/>
       <c r="Y292" s="4" t="n"/>
@@ -12842,16 +13422,16 @@
     <row r="293">
       <c r="T293" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U293" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V293" s="7" t="n">
-        <v>704</v>
+        <v>16913</v>
       </c>
       <c r="X293" s="7" t="n"/>
       <c r="Y293" s="7" t="n"/>
@@ -12863,16 +13443,16 @@
     <row r="294">
       <c r="T294" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U294" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V294" s="4" t="n">
-        <v>670</v>
+        <v>16991</v>
       </c>
       <c r="X294" s="4" t="n"/>
       <c r="Y294" s="4" t="n"/>
@@ -12884,16 +13464,16 @@
     <row r="295">
       <c r="T295" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U295" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V295" s="7" t="n">
-        <v>694</v>
+        <v>17365</v>
       </c>
       <c r="X295" s="7" t="n"/>
       <c r="Y295" s="7" t="n"/>
@@ -12905,16 +13485,16 @@
     <row r="296">
       <c r="T296" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="U296" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V296" s="4" t="n">
-        <v>702</v>
+        <v>16944</v>
       </c>
       <c r="X296" s="4" t="n"/>
       <c r="Y296" s="4" t="n"/>
@@ -12926,16 +13506,16 @@
     <row r="297">
       <c r="T297" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="U297" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V297" s="7" t="n">
-        <v>708</v>
+        <v>16518</v>
       </c>
       <c r="X297" s="7" t="n"/>
       <c r="Y297" s="7" t="n"/>
@@ -12947,16 +13527,16 @@
     <row r="298">
       <c r="T298" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U298" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V298" s="4" t="n">
-        <v>669</v>
+        <v>16634</v>
       </c>
       <c r="X298" s="4" t="n"/>
       <c r="Y298" s="4" t="n"/>
@@ -12968,16 +13548,16 @@
     <row r="299">
       <c r="T299" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U299" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V299" s="7" t="n">
-        <v>2188</v>
+        <v>16711</v>
       </c>
       <c r="X299" s="7" t="n"/>
       <c r="Y299" s="7" t="n"/>
@@ -12989,16 +13569,16 @@
     <row r="300">
       <c r="T300" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U300" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V300" s="4" t="n">
-        <v>2046</v>
+        <v>17379</v>
       </c>
       <c r="X300" s="4" t="n"/>
       <c r="Y300" s="4" t="n"/>
@@ -13010,16 +13590,16 @@
     <row r="301">
       <c r="T301" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U301" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V301" s="7" t="n">
-        <v>2338</v>
+        <v>17551</v>
       </c>
       <c r="X301" s="7" t="n"/>
       <c r="Y301" s="7" t="n"/>
@@ -13031,16 +13611,16 @@
     <row r="302">
       <c r="T302" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="U302" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V302" s="4" t="n">
-        <v>2152</v>
+        <v>17474</v>
       </c>
       <c r="X302" s="4" t="n"/>
       <c r="Y302" s="4" t="n"/>
@@ -13052,16 +13632,16 @@
     <row r="303">
       <c r="T303" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="U303" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V303" s="7" t="n">
-        <v>2003</v>
+        <v>17309</v>
       </c>
       <c r="X303" s="7" t="n"/>
       <c r="Y303" s="7" t="n"/>
@@ -13073,16 +13653,16 @@
     <row r="304">
       <c r="T304" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="U304" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V304" s="4" t="n">
-        <v>1895</v>
+        <v>16624</v>
       </c>
       <c r="X304" s="4" t="n"/>
       <c r="Y304" s="4" t="n"/>
@@ -13094,16 +13674,16 @@
     <row r="305">
       <c r="T305" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U305" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V305" s="7" t="n">
-        <v>1935</v>
+        <v>16794</v>
       </c>
       <c r="X305" s="7" t="n"/>
       <c r="Y305" s="7" t="n"/>
@@ -13115,16 +13695,16 @@
     <row r="306">
       <c r="T306" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="U306" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V306" s="4" t="n">
-        <v>2037</v>
+        <v>17158</v>
       </c>
       <c r="X306" s="4" t="n"/>
       <c r="Y306" s="4" t="n"/>
@@ -13136,16 +13716,16 @@
     <row r="307">
       <c r="T307" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="U307" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V307" s="7" t="n">
-        <v>2049</v>
+        <v>724</v>
       </c>
       <c r="X307" s="7" t="n"/>
       <c r="Y307" s="7" t="n"/>
@@ -13157,16 +13737,16 @@
     <row r="308">
       <c r="T308" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="U308" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V308" s="4" t="n">
-        <v>2325</v>
+        <v>746</v>
       </c>
       <c r="X308" s="4" t="n"/>
       <c r="Y308" s="4" t="n"/>
@@ -13178,16 +13758,16 @@
     <row r="309">
       <c r="T309" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U309" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V309" s="7" t="n">
-        <v>2216</v>
+        <v>723</v>
       </c>
       <c r="X309" s="7" t="n"/>
       <c r="Y309" s="7" t="n"/>
@@ -13199,16 +13779,16 @@
     <row r="310">
       <c r="T310" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U310" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V310" s="4" t="n">
-        <v>2037</v>
+        <v>708</v>
       </c>
       <c r="X310" s="4" t="n"/>
       <c r="Y310" s="4" t="n"/>
@@ -13220,16 +13800,16 @@
     <row r="311">
       <c r="T311" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="U311" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V311" s="7" t="n">
-        <v>2046</v>
+        <v>735</v>
       </c>
       <c r="X311" s="7" t="n"/>
       <c r="Y311" s="7" t="n"/>
@@ -13241,16 +13821,16 @@
     <row r="312">
       <c r="T312" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U312" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V312" s="4" t="n">
-        <v>2035</v>
+        <v>714</v>
       </c>
       <c r="X312" s="4" t="n"/>
       <c r="Y312" s="4" t="n"/>
@@ -13262,16 +13842,16 @@
     <row r="313">
       <c r="T313" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="U313" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V313" s="7" t="n">
-        <v>2182</v>
+        <v>706</v>
       </c>
       <c r="X313" s="7" t="n"/>
       <c r="Y313" s="7" t="n"/>
@@ -13283,16 +13863,16 @@
     <row r="314">
       <c r="T314" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U314" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V314" s="4" t="n">
-        <v>2156</v>
+        <v>729</v>
       </c>
       <c r="X314" s="4" t="n"/>
       <c r="Y314" s="4" t="n"/>
@@ -13304,16 +13884,16 @@
     <row r="315">
       <c r="T315" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="U315" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V315" s="7" t="n">
-        <v>2437</v>
+        <v>719</v>
       </c>
       <c r="X315" s="7" t="n"/>
       <c r="Y315" s="7" t="n"/>
@@ -13325,16 +13905,16 @@
     <row r="316">
       <c r="T316" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U316" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V316" s="4" t="n">
-        <v>2214</v>
+        <v>719</v>
       </c>
       <c r="X316" s="4" t="n"/>
       <c r="Y316" s="4" t="n"/>
@@ -13346,16 +13926,16 @@
     <row r="317">
       <c r="T317" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="U317" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V317" s="7" t="n">
-        <v>2200</v>
+        <v>730</v>
       </c>
       <c r="X317" s="7" t="n"/>
       <c r="Y317" s="7" t="n"/>
@@ -13367,16 +13947,16 @@
     <row r="318">
       <c r="T318" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="U318" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V318" s="4" t="n">
-        <v>1973</v>
+        <v>740</v>
       </c>
       <c r="X318" s="4" t="n"/>
       <c r="Y318" s="4" t="n"/>
@@ -13388,16 +13968,16 @@
     <row r="319">
       <c r="T319" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="U319" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V319" s="7" t="n">
-        <v>1980</v>
+        <v>708</v>
       </c>
       <c r="X319" s="7" t="n"/>
       <c r="Y319" s="7" t="n"/>
@@ -13409,16 +13989,16 @@
     <row r="320">
       <c r="T320" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="U320" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V320" s="4" t="n">
-        <v>2075</v>
+        <v>698</v>
       </c>
       <c r="X320" s="4" t="n"/>
       <c r="Y320" s="4" t="n"/>
@@ -13430,16 +14010,16 @@
     <row r="321">
       <c r="T321" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="U321" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V321" s="7" t="n">
-        <v>2191</v>
+        <v>691</v>
       </c>
       <c r="X321" s="7" t="n"/>
       <c r="Y321" s="7" t="n"/>
@@ -13451,16 +14031,16 @@
     <row r="322">
       <c r="T322" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="U322" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V322" s="4" t="n">
-        <v>2328</v>
+        <v>695</v>
       </c>
       <c r="X322" s="4" t="n"/>
       <c r="Y322" s="4" t="n"/>
@@ -13472,16 +14052,16 @@
     <row r="323">
       <c r="T323" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U323" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V323" s="7" t="n">
-        <v>2131</v>
+        <v>706</v>
       </c>
       <c r="X323" s="7" t="n"/>
       <c r="Y323" s="7" t="n"/>
@@ -13489,6 +14069,825 @@
       <c r="AB323" s="7" t="n"/>
       <c r="AC323" s="7" t="n"/>
       <c r="AD323" s="7" t="n"/>
+    </row>
+    <row r="324">
+      <c r="T324" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="U324" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V324" s="4" t="n">
+        <v>701</v>
+      </c>
+      <c r="X324" s="4" t="n"/>
+      <c r="Y324" s="4" t="n"/>
+      <c r="Z324" s="4" t="n"/>
+      <c r="AB324" s="4" t="n"/>
+      <c r="AC324" s="4" t="n"/>
+      <c r="AD324" s="4" t="n"/>
+    </row>
+    <row r="325">
+      <c r="T325" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U325" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V325" s="7" t="n">
+        <v>706</v>
+      </c>
+      <c r="X325" s="7" t="n"/>
+      <c r="Y325" s="7" t="n"/>
+      <c r="Z325" s="7" t="n"/>
+      <c r="AB325" s="7" t="n"/>
+      <c r="AC325" s="7" t="n"/>
+      <c r="AD325" s="7" t="n"/>
+    </row>
+    <row r="326">
+      <c r="T326" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U326" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V326" s="4" t="n">
+        <v>704</v>
+      </c>
+      <c r="X326" s="4" t="n"/>
+      <c r="Y326" s="4" t="n"/>
+      <c r="Z326" s="4" t="n"/>
+      <c r="AB326" s="4" t="n"/>
+      <c r="AC326" s="4" t="n"/>
+      <c r="AD326" s="4" t="n"/>
+    </row>
+    <row r="327">
+      <c r="T327" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U327" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V327" s="7" t="n">
+        <v>670</v>
+      </c>
+      <c r="X327" s="7" t="n"/>
+      <c r="Y327" s="7" t="n"/>
+      <c r="Z327" s="7" t="n"/>
+      <c r="AB327" s="7" t="n"/>
+      <c r="AC327" s="7" t="n"/>
+      <c r="AD327" s="7" t="n"/>
+    </row>
+    <row r="328">
+      <c r="T328" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U328" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V328" s="4" t="n">
+        <v>694</v>
+      </c>
+      <c r="X328" s="4" t="n"/>
+      <c r="Y328" s="4" t="n"/>
+      <c r="Z328" s="4" t="n"/>
+      <c r="AB328" s="4" t="n"/>
+      <c r="AC328" s="4" t="n"/>
+      <c r="AD328" s="4" t="n"/>
+    </row>
+    <row r="329">
+      <c r="T329" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="U329" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V329" s="7" t="n">
+        <v>702</v>
+      </c>
+      <c r="X329" s="7" t="n"/>
+      <c r="Y329" s="7" t="n"/>
+      <c r="Z329" s="7" t="n"/>
+      <c r="AB329" s="7" t="n"/>
+      <c r="AC329" s="7" t="n"/>
+      <c r="AD329" s="7" t="n"/>
+    </row>
+    <row r="330">
+      <c r="T330" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="U330" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V330" s="4" t="n">
+        <v>708</v>
+      </c>
+      <c r="X330" s="4" t="n"/>
+      <c r="Y330" s="4" t="n"/>
+      <c r="Z330" s="4" t="n"/>
+      <c r="AB330" s="4" t="n"/>
+      <c r="AC330" s="4" t="n"/>
+      <c r="AD330" s="4" t="n"/>
+    </row>
+    <row r="331">
+      <c r="T331" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="U331" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V331" s="7" t="n">
+        <v>669</v>
+      </c>
+      <c r="X331" s="7" t="n"/>
+      <c r="Y331" s="7" t="n"/>
+      <c r="Z331" s="7" t="n"/>
+      <c r="AB331" s="7" t="n"/>
+      <c r="AC331" s="7" t="n"/>
+      <c r="AD331" s="7" t="n"/>
+    </row>
+    <row r="332">
+      <c r="T332" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="U332" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V332" s="4" t="n">
+        <v>699</v>
+      </c>
+      <c r="X332" s="4" t="n"/>
+      <c r="Y332" s="4" t="n"/>
+      <c r="Z332" s="4" t="n"/>
+      <c r="AB332" s="4" t="n"/>
+      <c r="AC332" s="4" t="n"/>
+      <c r="AD332" s="4" t="n"/>
+    </row>
+    <row r="333">
+      <c r="T333" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="U333" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V333" s="7" t="n">
+        <v>675</v>
+      </c>
+      <c r="X333" s="7" t="n"/>
+      <c r="Y333" s="7" t="n"/>
+      <c r="Z333" s="7" t="n"/>
+      <c r="AB333" s="7" t="n"/>
+      <c r="AC333" s="7" t="n"/>
+      <c r="AD333" s="7" t="n"/>
+    </row>
+    <row r="334">
+      <c r="T334" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="U334" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V334" s="4" t="n">
+        <v>682</v>
+      </c>
+      <c r="X334" s="4" t="n"/>
+      <c r="Y334" s="4" t="n"/>
+      <c r="Z334" s="4" t="n"/>
+      <c r="AB334" s="4" t="n"/>
+      <c r="AC334" s="4" t="n"/>
+      <c r="AD334" s="4" t="n"/>
+    </row>
+    <row r="335">
+      <c r="T335" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U335" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V335" s="7" t="n">
+        <v>2188</v>
+      </c>
+      <c r="X335" s="7" t="n"/>
+      <c r="Y335" s="7" t="n"/>
+      <c r="Z335" s="7" t="n"/>
+      <c r="AB335" s="7" t="n"/>
+      <c r="AC335" s="7" t="n"/>
+      <c r="AD335" s="7" t="n"/>
+    </row>
+    <row r="336">
+      <c r="T336" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="U336" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V336" s="4" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X336" s="4" t="n"/>
+      <c r="Y336" s="4" t="n"/>
+      <c r="Z336" s="4" t="n"/>
+      <c r="AB336" s="4" t="n"/>
+      <c r="AC336" s="4" t="n"/>
+      <c r="AD336" s="4" t="n"/>
+    </row>
+    <row r="337">
+      <c r="T337" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="U337" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V337" s="7" t="n">
+        <v>2338</v>
+      </c>
+      <c r="X337" s="7" t="n"/>
+      <c r="Y337" s="7" t="n"/>
+      <c r="Z337" s="7" t="n"/>
+      <c r="AB337" s="7" t="n"/>
+      <c r="AC337" s="7" t="n"/>
+      <c r="AD337" s="7" t="n"/>
+    </row>
+    <row r="338">
+      <c r="T338" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="U338" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V338" s="4" t="n">
+        <v>2152</v>
+      </c>
+      <c r="X338" s="4" t="n"/>
+      <c r="Y338" s="4" t="n"/>
+      <c r="Z338" s="4" t="n"/>
+      <c r="AB338" s="4" t="n"/>
+      <c r="AC338" s="4" t="n"/>
+      <c r="AD338" s="4" t="n"/>
+    </row>
+    <row r="339">
+      <c r="T339" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="U339" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V339" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="X339" s="7" t="n"/>
+      <c r="Y339" s="7" t="n"/>
+      <c r="Z339" s="7" t="n"/>
+      <c r="AB339" s="7" t="n"/>
+      <c r="AC339" s="7" t="n"/>
+      <c r="AD339" s="7" t="n"/>
+    </row>
+    <row r="340">
+      <c r="T340" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="U340" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V340" s="4" t="n">
+        <v>1895</v>
+      </c>
+      <c r="X340" s="4" t="n"/>
+      <c r="Y340" s="4" t="n"/>
+      <c r="Z340" s="4" t="n"/>
+      <c r="AB340" s="4" t="n"/>
+      <c r="AC340" s="4" t="n"/>
+      <c r="AD340" s="4" t="n"/>
+    </row>
+    <row r="341">
+      <c r="T341" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="U341" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V341" s="7" t="n">
+        <v>1935</v>
+      </c>
+      <c r="X341" s="7" t="n"/>
+      <c r="Y341" s="7" t="n"/>
+      <c r="Z341" s="7" t="n"/>
+      <c r="AB341" s="7" t="n"/>
+      <c r="AC341" s="7" t="n"/>
+      <c r="AD341" s="7" t="n"/>
+    </row>
+    <row r="342">
+      <c r="T342" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U342" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V342" s="4" t="n">
+        <v>2037</v>
+      </c>
+      <c r="X342" s="4" t="n"/>
+      <c r="Y342" s="4" t="n"/>
+      <c r="Z342" s="4" t="n"/>
+      <c r="AB342" s="4" t="n"/>
+      <c r="AC342" s="4" t="n"/>
+      <c r="AD342" s="4" t="n"/>
+    </row>
+    <row r="343">
+      <c r="T343" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="U343" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V343" s="7" t="n">
+        <v>2049</v>
+      </c>
+      <c r="X343" s="7" t="n"/>
+      <c r="Y343" s="7" t="n"/>
+      <c r="Z343" s="7" t="n"/>
+      <c r="AB343" s="7" t="n"/>
+      <c r="AC343" s="7" t="n"/>
+      <c r="AD343" s="7" t="n"/>
+    </row>
+    <row r="344">
+      <c r="T344" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="U344" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V344" s="4" t="n">
+        <v>2325</v>
+      </c>
+      <c r="X344" s="4" t="n"/>
+      <c r="Y344" s="4" t="n"/>
+      <c r="Z344" s="4" t="n"/>
+      <c r="AB344" s="4" t="n"/>
+      <c r="AC344" s="4" t="n"/>
+      <c r="AD344" s="4" t="n"/>
+    </row>
+    <row r="345">
+      <c r="T345" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="U345" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V345" s="7" t="n">
+        <v>2216</v>
+      </c>
+      <c r="X345" s="7" t="n"/>
+      <c r="Y345" s="7" t="n"/>
+      <c r="Z345" s="7" t="n"/>
+      <c r="AB345" s="7" t="n"/>
+      <c r="AC345" s="7" t="n"/>
+      <c r="AD345" s="7" t="n"/>
+    </row>
+    <row r="346">
+      <c r="T346" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="U346" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V346" s="4" t="n">
+        <v>2037</v>
+      </c>
+      <c r="X346" s="4" t="n"/>
+      <c r="Y346" s="4" t="n"/>
+      <c r="Z346" s="4" t="n"/>
+      <c r="AB346" s="4" t="n"/>
+      <c r="AC346" s="4" t="n"/>
+      <c r="AD346" s="4" t="n"/>
+    </row>
+    <row r="347">
+      <c r="T347" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U347" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V347" s="7" t="n">
+        <v>2046</v>
+      </c>
+      <c r="X347" s="7" t="n"/>
+      <c r="Y347" s="7" t="n"/>
+      <c r="Z347" s="7" t="n"/>
+      <c r="AB347" s="7" t="n"/>
+      <c r="AC347" s="7" t="n"/>
+      <c r="AD347" s="7" t="n"/>
+    </row>
+    <row r="348">
+      <c r="T348" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="U348" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V348" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="X348" s="4" t="n"/>
+      <c r="Y348" s="4" t="n"/>
+      <c r="Z348" s="4" t="n"/>
+      <c r="AB348" s="4" t="n"/>
+      <c r="AC348" s="4" t="n"/>
+      <c r="AD348" s="4" t="n"/>
+    </row>
+    <row r="349">
+      <c r="T349" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U349" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V349" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="X349" s="7" t="n"/>
+      <c r="Y349" s="7" t="n"/>
+      <c r="Z349" s="7" t="n"/>
+      <c r="AB349" s="7" t="n"/>
+      <c r="AC349" s="7" t="n"/>
+      <c r="AD349" s="7" t="n"/>
+    </row>
+    <row r="350">
+      <c r="T350" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="U350" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V350" s="4" t="n">
+        <v>2156</v>
+      </c>
+      <c r="X350" s="4" t="n"/>
+      <c r="Y350" s="4" t="n"/>
+      <c r="Z350" s="4" t="n"/>
+      <c r="AB350" s="4" t="n"/>
+      <c r="AC350" s="4" t="n"/>
+      <c r="AD350" s="4" t="n"/>
+    </row>
+    <row r="351">
+      <c r="T351" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="U351" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V351" s="7" t="n">
+        <v>2437</v>
+      </c>
+      <c r="X351" s="7" t="n"/>
+      <c r="Y351" s="7" t="n"/>
+      <c r="Z351" s="7" t="n"/>
+      <c r="AB351" s="7" t="n"/>
+      <c r="AC351" s="7" t="n"/>
+      <c r="AD351" s="7" t="n"/>
+    </row>
+    <row r="352">
+      <c r="T352" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="U352" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V352" s="4" t="n">
+        <v>2214</v>
+      </c>
+      <c r="X352" s="4" t="n"/>
+      <c r="Y352" s="4" t="n"/>
+      <c r="Z352" s="4" t="n"/>
+      <c r="AB352" s="4" t="n"/>
+      <c r="AC352" s="4" t="n"/>
+      <c r="AD352" s="4" t="n"/>
+    </row>
+    <row r="353">
+      <c r="T353" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="U353" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V353" s="7" t="n">
+        <v>2200</v>
+      </c>
+      <c r="X353" s="7" t="n"/>
+      <c r="Y353" s="7" t="n"/>
+      <c r="Z353" s="7" t="n"/>
+      <c r="AB353" s="7" t="n"/>
+      <c r="AC353" s="7" t="n"/>
+      <c r="AD353" s="7" t="n"/>
+    </row>
+    <row r="354">
+      <c r="T354" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U354" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V354" s="4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="X354" s="4" t="n"/>
+      <c r="Y354" s="4" t="n"/>
+      <c r="Z354" s="4" t="n"/>
+      <c r="AB354" s="4" t="n"/>
+      <c r="AC354" s="4" t="n"/>
+      <c r="AD354" s="4" t="n"/>
+    </row>
+    <row r="355">
+      <c r="T355" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U355" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V355" s="7" t="n">
+        <v>1980</v>
+      </c>
+      <c r="X355" s="7" t="n"/>
+      <c r="Y355" s="7" t="n"/>
+      <c r="Z355" s="7" t="n"/>
+      <c r="AB355" s="7" t="n"/>
+      <c r="AC355" s="7" t="n"/>
+      <c r="AD355" s="7" t="n"/>
+    </row>
+    <row r="356">
+      <c r="T356" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U356" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V356" s="4" t="n">
+        <v>2075</v>
+      </c>
+      <c r="X356" s="4" t="n"/>
+      <c r="Y356" s="4" t="n"/>
+      <c r="Z356" s="4" t="n"/>
+      <c r="AB356" s="4" t="n"/>
+      <c r="AC356" s="4" t="n"/>
+      <c r="AD356" s="4" t="n"/>
+    </row>
+    <row r="357">
+      <c r="T357" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="U357" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V357" s="7" t="n">
+        <v>2191</v>
+      </c>
+      <c r="X357" s="7" t="n"/>
+      <c r="Y357" s="7" t="n"/>
+      <c r="Z357" s="7" t="n"/>
+      <c r="AB357" s="7" t="n"/>
+      <c r="AC357" s="7" t="n"/>
+      <c r="AD357" s="7" t="n"/>
+    </row>
+    <row r="358">
+      <c r="T358" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="U358" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+